--- a/tratando_tabelas/finitura/entradas_finitura.xlsx
+++ b/tratando_tabelas/finitura/entradas_finitura.xlsx
@@ -20,12 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="912" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="187">
   <si>
     <t xml:space="preserve">Santri ADM 1.1.5.7 R1</t>
   </si>
   <si>
-    <t xml:space="preserve">Emitido em: 09/04/2026 16:56:12</t>
+    <t xml:space="preserve">Emitido em: 10/04/2026 15:09:21</t>
   </si>
   <si>
     <t xml:space="preserve">Relação de entradas - Sintético</t>
@@ -217,25 +217,22 @@
     <t xml:space="preserve">1.856 - DEXCO S.A - METAIS</t>
   </si>
   <si>
-    <t xml:space="preserve">5.048.935</t>
+    <t xml:space="preserve">5.050.871</t>
   </si>
   <si>
     <t xml:space="preserve">1</t>
   </si>
   <si>
-    <t xml:space="preserve">27/03/2026</t>
-  </si>
-  <si>
     <t xml:space="preserve">31/03/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">24/04/2026</t>
+    <t xml:space="preserve">28/04/2026</t>
   </si>
   <si>
     <t xml:space="preserve">XML</t>
   </si>
   <si>
-    <t xml:space="preserve">1.480,83</t>
+    <t xml:space="preserve">746,26</t>
   </si>
   <si>
     <t xml:space="preserve">Ag. chegada da mercadoria</t>
@@ -259,22 +256,10 @@
     <t xml:space="preserve">          </t>
   </si>
   <si>
-    <t xml:space="preserve">35260397837181002190550010050489351613447900</t>
+    <t xml:space="preserve">35260397837181002190550010050508711279023491</t>
   </si>
   <si>
     <t xml:space="preserve">Não</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.050.871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">746,26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260397837181002190550010050508711279023491</t>
   </si>
   <si>
     <t xml:space="preserve">5.050.848</t>
@@ -388,30 +373,6 @@
     <t xml:space="preserve">42260486532538003005550010013770411001107072</t>
   </si>
   <si>
-    <t xml:space="preserve">2.486 - ROCA SANITARIOS BRASIL LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.341.121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24/03/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">471,42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260375801902000126550000013411211152893380</t>
-  </si>
-  <si>
     <t xml:space="preserve">3.101 - INDUSTRIA E COMERCIO DE MOLDURAS SANTA LUZIA LTDA</t>
   </si>
   <si>
@@ -419,6 +380,12 @@
   </si>
   <si>
     <t xml:space="preserve">4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27/03/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24/04/2026</t>
   </si>
   <si>
     <t xml:space="preserve">6.870,46</t>
@@ -464,6 +431,9 @@
   </si>
   <si>
     <t xml:space="preserve">609.191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05/05/2026</t>
   </si>
   <si>
     <t xml:space="preserve">482,14</t>
@@ -529,10 +499,31 @@
     <t xml:space="preserve">8.720,40</t>
   </si>
   <si>
+    <t xml:space="preserve">S</t>
+  </si>
+  <si>
     <t xml:space="preserve">2.910</t>
   </si>
   <si>
     <t xml:space="preserve">42260375339051000141550080006048931151164109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.059 - JLR COM IMPORT. E EXP. DE MATERIAIS DE CONSTRUCAO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.242,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41260417781412000109550010000119661000316126</t>
   </si>
   <si>
     <t xml:space="preserve">Total geral</t>
@@ -16778,7 +16769,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BM42"/>
+  <dimension ref="A1:BM41"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="18"/>
@@ -17150,7 +17141,7 @@
     </row>
     <row r="5" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="n">
-        <v>304165</v>
+        <v>304192</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>64</v>
@@ -17168,16 +17159,16 @@
         <v>67</v>
       </c>
       <c r="I5" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="J5" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="J5" s="9" t="s">
+      <c r="K5" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="K5" s="11" t="s">
-        <v>70</v>
-      </c>
       <c r="L5" s="12" t="n">
-        <v>1480.83</v>
+        <v>746.26</v>
       </c>
       <c r="M5" s="12" t="n">
         <v>0</v>
@@ -17186,70 +17177,70 @@
         <v>1</v>
       </c>
       <c r="O5" s="12" t="n">
-        <v>1390.45</v>
+        <v>746.26</v>
       </c>
       <c r="P5" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q5" s="13" t="n">
-        <v>0.042195</v>
+        <v>0.034224</v>
       </c>
       <c r="R5" s="12" t="n">
-        <v>4.13</v>
+        <v>3.84</v>
       </c>
       <c r="S5" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T5" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="U5" s="15" t="s">
         <v>71</v>
-      </c>
-      <c r="U5" s="15" t="s">
-        <v>72</v>
       </c>
       <c r="V5" s="12" t="n">
         <v>28</v>
       </c>
       <c r="W5" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="X5" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y5" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="12" t="n">
+        <v>746.26</v>
+      </c>
+      <c r="AA5" s="12" t="n">
+        <v>29.85</v>
+      </c>
+      <c r="AB5" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="X5" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="Y5" s="12" t="n">
-        <v>90.38</v>
-      </c>
-      <c r="Z5" s="12" t="n">
-        <v>1390.45</v>
-      </c>
-      <c r="AA5" s="12" t="n">
-        <v>97.33</v>
-      </c>
-      <c r="AB5" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" s="14" t="s">
-        <v>74</v>
-      </c>
       <c r="AI5" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AJ5" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AK5" s="12" t="n">
         <v>0</v>
@@ -17258,90 +17249,90 @@
         <v>0</v>
       </c>
       <c r="AM5" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AN5" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AO5" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AP5" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AQ5" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR5" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AS5" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AT5" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AU5" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AV5" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AW5" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="AP5" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ5" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR5" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS5" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT5" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU5" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV5" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW5" s="14" t="s">
+      <c r="AX5" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="AX5" s="10" t="s">
+      <c r="AY5" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AZ5" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BA5" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BB5" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BC5" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BD5" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BE5" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BF5" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="BG5" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="AY5" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ5" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA5" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB5" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BC5" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD5" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE5" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BF5" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BG5" s="9" t="s">
+      <c r="BH5" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BI5" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="BJ5" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="BH5" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BI5" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="BJ5" s="9" t="s">
+      <c r="BK5" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="BL5" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="BM5" s="16" t="s">
         <v>79</v>
-      </c>
-      <c r="BK5" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BL5" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BM5" s="16" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="n">
-        <v>304192</v>
+        <v>304216</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>64</v>
@@ -17350,25 +17341,25 @@
       <c r="D6" s="9"/>
       <c r="E6" s="9"/>
       <c r="F6" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G6" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H6" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="J6" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="I6" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="J6" s="9" t="s">
-        <v>82</v>
-      </c>
       <c r="K6" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L6" s="12" t="n">
-        <v>746.26</v>
+        <v>738.32</v>
       </c>
       <c r="M6" s="12" t="n">
         <v>0</v>
@@ -17377,70 +17368,70 @@
         <v>1</v>
       </c>
       <c r="O6" s="12" t="n">
-        <v>746.26</v>
+        <v>693.26</v>
       </c>
       <c r="P6" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q6" s="13" t="n">
-        <v>0.034224</v>
+        <v>0.011556</v>
       </c>
       <c r="R6" s="12" t="n">
-        <v>3.84</v>
+        <v>1.23</v>
       </c>
       <c r="S6" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T6" s="14" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="U6" s="15" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="V6" s="12" t="n">
         <v>28</v>
       </c>
       <c r="W6" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="X6" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y6" s="12" t="n">
+        <v>45.06</v>
+      </c>
+      <c r="Z6" s="12" t="n">
+        <v>693.26</v>
+      </c>
+      <c r="AA6" s="12" t="n">
+        <v>48.53</v>
+      </c>
+      <c r="AB6" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="X6" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="Y6" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="12" t="n">
-        <v>746.26</v>
-      </c>
-      <c r="AA6" s="12" t="n">
-        <v>29.85</v>
-      </c>
-      <c r="AB6" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" s="14" t="s">
-        <v>74</v>
-      </c>
       <c r="AI6" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AJ6" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AK6" s="12" t="n">
         <v>0</v>
@@ -17449,117 +17440,117 @@
         <v>0</v>
       </c>
       <c r="AM6" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AN6" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AO6" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AP6" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AQ6" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR6" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AS6" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AT6" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AU6" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AV6" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AW6" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="AP6" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ6" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR6" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS6" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT6" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU6" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV6" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW6" s="14" t="s">
+      <c r="AX6" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="AX6" s="10" t="s">
+      <c r="AY6" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AZ6" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BA6" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BB6" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BC6" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BD6" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BE6" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BF6" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="BG6" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="AY6" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ6" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA6" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB6" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BC6" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD6" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE6" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BF6" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BG6" s="9" t="s">
-        <v>78</v>
-      </c>
       <c r="BH6" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BI6" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="BJ6" s="9" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="BK6" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BL6" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BM6" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="n">
-        <v>304216</v>
+        <v>304225</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
       <c r="F7" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="G7" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="G7" s="10" t="s">
-        <v>66</v>
-      </c>
       <c r="H7" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="J7" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="I7" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="J7" s="9" t="s">
-        <v>82</v>
-      </c>
       <c r="K7" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L7" s="12" t="n">
-        <v>738.32</v>
+        <v>6871.53</v>
       </c>
       <c r="M7" s="12" t="n">
         <v>0</v>
@@ -17568,16 +17559,16 @@
         <v>1</v>
       </c>
       <c r="O7" s="12" t="n">
-        <v>693.26</v>
+        <v>6871.53</v>
       </c>
       <c r="P7" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q7" s="13" t="n">
-        <v>0.011556</v>
+        <v>0.04634</v>
       </c>
       <c r="R7" s="12" t="n">
-        <v>1.23</v>
+        <v>7</v>
       </c>
       <c r="S7" s="12" t="n">
         <v>0</v>
@@ -17586,52 +17577,52 @@
         <v>86</v>
       </c>
       <c r="U7" s="15" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="V7" s="12" t="n">
         <v>28</v>
       </c>
       <c r="W7" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="X7" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y7" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="12" t="n">
+        <v>6871.53</v>
+      </c>
+      <c r="AA7" s="12" t="n">
+        <v>481.01</v>
+      </c>
+      <c r="AB7" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="X7" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="Y7" s="12" t="n">
-        <v>45.06</v>
-      </c>
-      <c r="Z7" s="12" t="n">
-        <v>693.26</v>
-      </c>
-      <c r="AA7" s="12" t="n">
-        <v>48.53</v>
-      </c>
-      <c r="AB7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" s="14" t="s">
-        <v>74</v>
-      </c>
       <c r="AI7" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AJ7" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AK7" s="12" t="n">
         <v>0</v>
@@ -17640,90 +17631,90 @@
         <v>0</v>
       </c>
       <c r="AM7" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AN7" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AO7" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AP7" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AQ7" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR7" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AS7" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AT7" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AU7" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AV7" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AW7" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="AP7" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ7" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR7" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS7" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT7" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU7" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV7" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW7" s="14" t="s">
+      <c r="AX7" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="AX7" s="10" t="s">
+      <c r="AY7" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AZ7" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BA7" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BB7" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BC7" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BD7" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BE7" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BF7" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="BG7" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="AY7" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ7" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA7" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB7" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BC7" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD7" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE7" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BF7" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BG7" s="9" t="s">
-        <v>78</v>
-      </c>
       <c r="BH7" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BI7" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="BJ7" s="9" t="s">
         <v>87</v>
       </c>
       <c r="BK7" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BL7" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BM7" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="n">
-        <v>304225</v>
+        <v>304260</v>
       </c>
       <c r="B8" s="9" t="s">
         <v>88</v>
@@ -17735,22 +17726,22 @@
         <v>89</v>
       </c>
       <c r="G8" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H8" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="H8" s="9" t="s">
-        <v>68</v>
-      </c>
       <c r="I8" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K8" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L8" s="12" t="n">
-        <v>6871.53</v>
+        <v>1438.46</v>
       </c>
       <c r="M8" s="12" t="n">
         <v>0</v>
@@ -17759,70 +17750,70 @@
         <v>1</v>
       </c>
       <c r="O8" s="12" t="n">
-        <v>6871.53</v>
+        <v>1310.67</v>
       </c>
       <c r="P8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q8" s="13" t="n">
-        <v>0.04634</v>
+        <v>0</v>
       </c>
       <c r="R8" s="12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="S8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T8" s="14" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="U8" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="V8" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="W8" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="V8" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="W8" s="9" t="s">
+      <c r="X8" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y8" s="12" t="n">
+        <v>127.79</v>
+      </c>
+      <c r="Z8" s="12" t="n">
+        <v>1310.67</v>
+      </c>
+      <c r="AA8" s="12" t="n">
+        <v>52.43</v>
+      </c>
+      <c r="AB8" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="X8" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="Y8" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="12" t="n">
-        <v>6871.53</v>
-      </c>
-      <c r="AA8" s="12" t="n">
-        <v>481.01</v>
-      </c>
-      <c r="AB8" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG8" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" s="14" t="s">
-        <v>74</v>
-      </c>
       <c r="AI8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AJ8" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AK8" s="12" t="n">
         <v>0</v>
@@ -17831,93 +17822,93 @@
         <v>0</v>
       </c>
       <c r="AM8" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AN8" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AO8" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AP8" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AQ8" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR8" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AS8" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AT8" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AU8" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AV8" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AW8" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="AP8" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ8" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR8" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS8" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT8" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU8" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV8" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW8" s="14" t="s">
+      <c r="AX8" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="AX8" s="10" t="s">
+      <c r="AY8" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AZ8" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BA8" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BB8" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BC8" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BD8" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BE8" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BF8" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="BG8" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="AY8" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ8" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA8" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB8" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BC8" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD8" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE8" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BF8" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BG8" s="9" t="s">
-        <v>78</v>
-      </c>
       <c r="BH8" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BI8" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="BJ8" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="BK8" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BL8" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BM8" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="n">
-        <v>304260</v>
+        <v>304261</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
@@ -17929,19 +17920,19 @@
         <v>66</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="K9" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L9" s="12" t="n">
-        <v>1438.46</v>
+        <v>1798.08</v>
       </c>
       <c r="M9" s="12" t="n">
         <v>0</v>
@@ -17950,7 +17941,7 @@
         <v>1</v>
       </c>
       <c r="O9" s="12" t="n">
-        <v>1310.67</v>
+        <v>1638.34</v>
       </c>
       <c r="P9" s="12" t="n">
         <v>0</v>
@@ -17965,55 +17956,55 @@
         <v>0</v>
       </c>
       <c r="T9" s="14" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="U9" s="15" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="V9" s="12" t="n">
         <v>42</v>
       </c>
       <c r="W9" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="X9" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y9" s="12" t="n">
+        <v>159.74</v>
+      </c>
+      <c r="Z9" s="12" t="n">
+        <v>1638.34</v>
+      </c>
+      <c r="AA9" s="12" t="n">
+        <v>65.53</v>
+      </c>
+      <c r="AB9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="X9" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="Y9" s="12" t="n">
-        <v>127.79</v>
-      </c>
-      <c r="Z9" s="12" t="n">
-        <v>1310.67</v>
-      </c>
-      <c r="AA9" s="12" t="n">
-        <v>52.43</v>
-      </c>
-      <c r="AB9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH9" s="14" t="s">
-        <v>74</v>
-      </c>
       <c r="AI9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AJ9" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AK9" s="12" t="n">
         <v>0</v>
@@ -18022,117 +18013,117 @@
         <v>0</v>
       </c>
       <c r="AM9" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AN9" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AO9" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AP9" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AQ9" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR9" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AS9" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AT9" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AU9" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AV9" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AW9" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="AP9" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ9" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR9" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS9" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT9" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU9" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV9" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW9" s="14" t="s">
+      <c r="AX9" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="AX9" s="10" t="s">
+      <c r="AY9" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AZ9" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BA9" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BB9" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BC9" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BD9" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BE9" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BF9" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="BG9" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="AY9" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ9" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA9" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB9" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BC9" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD9" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE9" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BF9" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BG9" s="9" t="s">
-        <v>78</v>
-      </c>
       <c r="BH9" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BI9" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="BJ9" s="9" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="BK9" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BL9" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BM9" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="n">
-        <v>304261</v>
+        <v>304343</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
       <c r="F10" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="J10" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="G10" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="J10" s="9" t="s">
-        <v>96</v>
-      </c>
       <c r="K10" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L10" s="12" t="n">
-        <v>1798.08</v>
+        <v>3288.6</v>
       </c>
       <c r="M10" s="12" t="n">
         <v>0</v>
@@ -18141,16 +18132,16 @@
         <v>1</v>
       </c>
       <c r="O10" s="12" t="n">
-        <v>1638.34</v>
+        <v>3288.6</v>
       </c>
       <c r="P10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q10" s="13" t="n">
-        <v>0</v>
+        <v>0.049896</v>
       </c>
       <c r="R10" s="12" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="S10" s="12" t="n">
         <v>0</v>
@@ -18159,52 +18150,52 @@
         <v>100</v>
       </c>
       <c r="U10" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="V10" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="W10" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="V10" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="W10" s="9" t="s">
+      <c r="X10" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="Y10" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="12" t="n">
+        <v>3288.6</v>
+      </c>
+      <c r="AA10" s="12" t="n">
+        <v>230.2</v>
+      </c>
+      <c r="AB10" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="X10" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="Y10" s="12" t="n">
-        <v>159.74</v>
-      </c>
-      <c r="Z10" s="12" t="n">
-        <v>1638.34</v>
-      </c>
-      <c r="AA10" s="12" t="n">
-        <v>65.53</v>
-      </c>
-      <c r="AB10" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" s="14" t="s">
-        <v>74</v>
-      </c>
       <c r="AI10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AJ10" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AK10" s="12" t="n">
         <v>0</v>
@@ -18213,93 +18204,93 @@
         <v>0</v>
       </c>
       <c r="AM10" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AN10" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AO10" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AP10" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AQ10" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR10" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AS10" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AT10" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AU10" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AV10" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AW10" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="AP10" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ10" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR10" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS10" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT10" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU10" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV10" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW10" s="14" t="s">
+      <c r="AX10" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="AX10" s="10" t="s">
+      <c r="AY10" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AZ10" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BA10" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BB10" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BC10" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BD10" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BE10" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BF10" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="BG10" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="AY10" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ10" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA10" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB10" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BC10" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD10" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE10" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BF10" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BG10" s="9" t="s">
-        <v>78</v>
-      </c>
       <c r="BH10" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BI10" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="BJ10" s="9" t="s">
         <v>101</v>
       </c>
       <c r="BK10" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BL10" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BM10" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="n">
-        <v>304343</v>
+        <v>304390</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
@@ -18308,67 +18299,67 @@
         <v>102</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="I11" s="9" t="s">
         <v>103</v>
       </c>
       <c r="J11" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K11" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="L11" s="12" t="n">
+        <v>496.19</v>
+      </c>
+      <c r="M11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="O11" s="12" t="n">
+        <v>476.99</v>
+      </c>
+      <c r="P11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="13" t="n">
+        <v>0.104397</v>
+      </c>
+      <c r="R11" s="12" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="S11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="K11" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="L11" s="12" t="n">
-        <v>3288.6</v>
-      </c>
-      <c r="M11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" s="12" t="n">
-        <v>3288.6</v>
-      </c>
-      <c r="P11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="13" t="n">
-        <v>0.049896</v>
-      </c>
-      <c r="R11" s="12" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="S11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" s="14" t="s">
-        <v>105</v>
-      </c>
       <c r="U11" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="V11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" s="9" t="s">
         <v>72</v>
-      </c>
-      <c r="V11" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="W11" s="9" t="s">
-        <v>73</v>
       </c>
       <c r="X11" s="9" t="s">
         <v>103</v>
       </c>
       <c r="Y11" s="12" t="n">
-        <v>0</v>
+        <v>19.2</v>
       </c>
       <c r="Z11" s="12" t="n">
-        <v>3288.6</v>
+        <v>476.99</v>
       </c>
       <c r="AA11" s="12" t="n">
-        <v>230.2</v>
+        <v>24.54</v>
       </c>
       <c r="AB11" s="12" t="n">
         <v>0</v>
@@ -18389,13 +18380,13 @@
         <v>0</v>
       </c>
       <c r="AH11" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AI11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AJ11" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AK11" s="12" t="n">
         <v>0</v>
@@ -18404,93 +18395,93 @@
         <v>0</v>
       </c>
       <c r="AM11" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AN11" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AO11" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AP11" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AQ11" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR11" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AS11" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AT11" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AU11" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AV11" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AW11" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="AP11" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ11" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR11" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS11" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT11" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU11" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV11" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW11" s="14" t="s">
-        <v>76</v>
-      </c>
       <c r="AX11" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="AY11" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AZ11" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BA11" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BB11" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BC11" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BD11" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BE11" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BF11" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="BG11" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="AY11" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ11" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA11" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB11" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BC11" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD11" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE11" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BF11" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BG11" s="9" t="s">
-        <v>78</v>
-      </c>
       <c r="BH11" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BI11" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="BJ11" s="9" t="s">
         <v>106</v>
       </c>
       <c r="BK11" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BL11" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BM11" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="n">
-        <v>304390</v>
+        <v>304417</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
@@ -18499,7 +18490,7 @@
         <v>107</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="H12" s="9" t="s">
         <v>103</v>
@@ -18508,58 +18499,58 @@
         <v>108</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="K12" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>496.19</v>
+        <v>909.41</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O12" s="12" t="n">
-        <v>476.99</v>
+        <v>909.41</v>
       </c>
       <c r="P12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" s="13" t="n">
-        <v>0.104397</v>
+        <v>0</v>
       </c>
       <c r="R12" s="12" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="S12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T12" s="14" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="U12" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="V12" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="W12" s="9" t="s">
         <v>72</v>
-      </c>
-      <c r="V12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" s="9" t="s">
-        <v>73</v>
       </c>
       <c r="X12" s="9" t="s">
         <v>108</v>
       </c>
       <c r="Y12" s="12" t="n">
-        <v>19.2</v>
+        <v>0</v>
       </c>
       <c r="Z12" s="12" t="n">
-        <v>476.99</v>
+        <v>909.41</v>
       </c>
       <c r="AA12" s="12" t="n">
-        <v>24.54</v>
+        <v>63.66</v>
       </c>
       <c r="AB12" s="12" t="n">
         <v>0</v>
@@ -18580,13 +18571,13 @@
         <v>0</v>
       </c>
       <c r="AH12" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AI12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AJ12" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AK12" s="12" t="n">
         <v>0</v>
@@ -18595,117 +18586,117 @@
         <v>0</v>
       </c>
       <c r="AM12" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AN12" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AO12" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AP12" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AQ12" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR12" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AS12" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AT12" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AU12" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AV12" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AW12" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="AP12" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ12" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR12" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS12" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT12" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU12" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV12" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW12" s="14" t="s">
+      <c r="AX12" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="AX12" s="10" t="s">
-        <v>110</v>
-      </c>
       <c r="AY12" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AZ12" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BA12" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BB12" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BC12" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BD12" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BE12" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BF12" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BG12" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="BH12" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BI12" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="BJ12" s="9" t="s">
         <v>111</v>
       </c>
       <c r="BK12" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BL12" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BM12" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="n">
-        <v>304417</v>
+        <v>304503</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
       <c r="F13" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="H13" s="9" t="s">
         <v>108</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="J13" s="9" t="s">
         <v>114</v>
       </c>
       <c r="K13" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>909.41</v>
+        <v>11314.6</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>0</v>
@@ -18714,7 +18705,7 @@
         <v>1</v>
       </c>
       <c r="O13" s="12" t="n">
-        <v>909.41</v>
+        <v>11314.6</v>
       </c>
       <c r="P13" s="12" t="n">
         <v>0</v>
@@ -18723,7 +18714,7 @@
         <v>0</v>
       </c>
       <c r="R13" s="12" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="S13" s="12" t="n">
         <v>0</v>
@@ -18732,52 +18723,52 @@
         <v>115</v>
       </c>
       <c r="U13" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="V13" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="W13" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="V13" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="W13" s="9" t="s">
+      <c r="X13" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="Y13" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="12" t="n">
+        <v>11314.6</v>
+      </c>
+      <c r="AA13" s="12" t="n">
+        <v>792.02</v>
+      </c>
+      <c r="AB13" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="X13" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="Y13" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" s="12" t="n">
-        <v>909.41</v>
-      </c>
-      <c r="AA13" s="12" t="n">
-        <v>63.66</v>
-      </c>
-      <c r="AB13" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF13" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG13" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH13" s="14" t="s">
-        <v>74</v>
-      </c>
       <c r="AI13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AJ13" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AK13" s="12" t="n">
         <v>0</v>
@@ -18786,90 +18777,90 @@
         <v>0</v>
       </c>
       <c r="AM13" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AN13" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AO13" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AP13" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AQ13" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR13" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AS13" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AT13" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AU13" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AV13" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AW13" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="AP13" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ13" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR13" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS13" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT13" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU13" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV13" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW13" s="14" t="s">
+      <c r="AX13" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="AX13" s="10" t="s">
+      <c r="AY13" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AZ13" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BA13" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BB13" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BC13" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BD13" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BE13" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BF13" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="BG13" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="AY13" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ13" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA13" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB13" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BC13" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD13" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE13" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BF13" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BG13" s="9" t="s">
-        <v>78</v>
-      </c>
       <c r="BH13" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BI13" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="BJ13" s="9" t="s">
         <v>116</v>
       </c>
       <c r="BK13" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BL13" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BM13" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="n">
-        <v>304503</v>
+        <v>304520</v>
       </c>
       <c r="B14" s="9" t="s">
         <v>117</v>
@@ -18881,94 +18872,94 @@
         <v>118</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="K14" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>11314.6</v>
+        <v>6870.46</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O14" s="12" t="n">
-        <v>11314.6</v>
+        <v>6870.46</v>
       </c>
       <c r="P14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q14" s="13" t="n">
-        <v>0</v>
+        <v>0.04644</v>
       </c>
       <c r="R14" s="12" t="n">
-        <v>33.3</v>
+        <v>25.27</v>
       </c>
       <c r="S14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T14" s="14" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="U14" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="V14" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="W14" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="V14" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="W14" s="9" t="s">
+      <c r="X14" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="Y14" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="12" t="n">
+        <v>6870.46</v>
+      </c>
+      <c r="AA14" s="12" t="n">
+        <v>480.93</v>
+      </c>
+      <c r="AB14" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="12" t="n">
+        <v>138.3</v>
+      </c>
+      <c r="AE14" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="X14" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="Y14" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="12" t="n">
-        <v>11314.6</v>
-      </c>
-      <c r="AA14" s="12" t="n">
-        <v>792.02</v>
-      </c>
-      <c r="AB14" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE14" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF14" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG14" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" s="14" t="s">
-        <v>74</v>
-      </c>
       <c r="AI14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AJ14" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AK14" s="12" t="n">
         <v>0</v>
@@ -18977,189 +18968,189 @@
         <v>0</v>
       </c>
       <c r="AM14" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AN14" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AO14" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AP14" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AQ14" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR14" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AS14" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AT14" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AU14" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AV14" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AW14" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="AP14" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ14" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR14" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS14" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT14" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU14" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV14" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW14" s="14" t="s">
+      <c r="AX14" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="AX14" s="10" t="s">
-        <v>77</v>
-      </c>
       <c r="AY14" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AZ14" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BA14" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BB14" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BC14" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BD14" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BE14" s="14" t="s">
-        <v>75</v>
+        <v>123</v>
       </c>
       <c r="BF14" s="9" t="s">
-        <v>75</v>
+        <v>124</v>
       </c>
       <c r="BG14" s="9" t="s">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="BH14" s="14" t="s">
-        <v>75</v>
+        <v>125</v>
       </c>
       <c r="BI14" s="9" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="BJ14" s="9" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="BK14" s="9" t="s">
-        <v>75</v>
+        <v>127</v>
       </c>
       <c r="BL14" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BM14" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="n">
-        <v>304506</v>
+        <v>304561</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
       <c r="F15" s="9" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>124</v>
+        <v>66</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>125</v>
+        <v>67</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>126</v>
+        <v>68</v>
       </c>
       <c r="K15" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>471.42</v>
+        <v>1446.24</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O15" s="12" t="n">
-        <v>471.42</v>
+        <v>1446.24</v>
       </c>
       <c r="P15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q15" s="13" t="n">
-        <v>0.000771</v>
+        <v>0.00268</v>
       </c>
       <c r="R15" s="12" t="n">
-        <v>0.87</v>
+        <v>8</v>
       </c>
       <c r="S15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T15" s="14" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="U15" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="V15" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="W15" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="V15" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="W15" s="9" t="s">
+      <c r="X15" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="Y15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="12" t="n">
+        <v>1446.24</v>
+      </c>
+      <c r="AA15" s="12" t="n">
+        <v>101.24</v>
+      </c>
+      <c r="AB15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="X15" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="Y15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="12" t="n">
-        <v>471.42</v>
-      </c>
-      <c r="AA15" s="12" t="n">
-        <v>33</v>
-      </c>
-      <c r="AB15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH15" s="14" t="s">
-        <v>74</v>
-      </c>
       <c r="AI15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AJ15" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AK15" s="12" t="n">
         <v>0</v>
@@ -19168,189 +19159,189 @@
         <v>0</v>
       </c>
       <c r="AM15" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AN15" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AO15" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AP15" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AQ15" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR15" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AS15" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AT15" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AU15" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AV15" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AW15" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="AP15" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ15" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR15" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS15" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT15" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU15" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV15" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW15" s="14" t="s">
-        <v>128</v>
-      </c>
       <c r="AX15" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="AY15" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AZ15" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BA15" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BB15" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BC15" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BD15" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BE15" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BF15" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="BG15" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="AY15" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ15" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA15" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB15" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BC15" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD15" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE15" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BF15" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BG15" s="9" t="s">
-        <v>78</v>
-      </c>
       <c r="BH15" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BI15" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="BJ15" s="9" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="BK15" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BL15" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BM15" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="n">
-        <v>304520</v>
+        <v>304624</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>130</v>
+        <v>83</v>
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
       <c r="F16" s="9" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>132</v>
+        <v>85</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>67</v>
+        <v>108</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="J16" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="K16" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="K16" s="11" t="s">
-        <v>70</v>
-      </c>
       <c r="L16" s="12" t="n">
-        <v>6870.46</v>
+        <v>803.16</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O16" s="12" t="n">
-        <v>6870.46</v>
+        <v>803.16</v>
       </c>
       <c r="P16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q16" s="13" t="n">
-        <v>0.04644</v>
+        <v>0.00374</v>
       </c>
       <c r="R16" s="12" t="n">
-        <v>25.27</v>
+        <v>0.8</v>
       </c>
       <c r="S16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T16" s="14" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="U16" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="V16" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="W16" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="V16" s="12" t="n">
-        <v>56</v>
-      </c>
-      <c r="W16" s="9" t="s">
+      <c r="X16" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="Y16" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="12" t="n">
+        <v>803.16</v>
+      </c>
+      <c r="AA16" s="12" t="n">
+        <v>56.22</v>
+      </c>
+      <c r="AB16" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="X16" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="Y16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" s="12" t="n">
-        <v>6870.46</v>
-      </c>
-      <c r="AA16" s="12" t="n">
-        <v>480.93</v>
-      </c>
-      <c r="AB16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" s="12" t="n">
-        <v>138.3</v>
-      </c>
-      <c r="AE16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" s="14" t="s">
-        <v>74</v>
-      </c>
       <c r="AI16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AJ16" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AK16" s="12" t="n">
         <v>0</v>
@@ -19359,117 +19350,117 @@
         <v>0</v>
       </c>
       <c r="AM16" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AN16" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AO16" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AP16" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AQ16" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR16" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AS16" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AT16" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AU16" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AV16" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AW16" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="AP16" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ16" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR16" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS16" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT16" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU16" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV16" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW16" s="14" t="s">
+      <c r="AX16" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="AX16" s="10" t="s">
+      <c r="AY16" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AZ16" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BA16" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BB16" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BC16" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BD16" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BE16" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BF16" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="BG16" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="AY16" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ16" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA16" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB16" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BC16" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD16" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE16" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="BF16" s="9" t="s">
+      <c r="BH16" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BI16" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="BJ16" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="BG16" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="BH16" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="BI16" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="BJ16" s="9" t="s">
-        <v>137</v>
-      </c>
       <c r="BK16" s="9" t="s">
-        <v>138</v>
+        <v>74</v>
       </c>
       <c r="BL16" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BM16" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="n">
-        <v>304561</v>
+        <v>304629</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
       <c r="F17" s="9" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>68</v>
+        <v>130</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>82</v>
+        <v>137</v>
       </c>
       <c r="K17" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>1446.24</v>
+        <v>482.14</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>0</v>
@@ -19478,70 +19469,70 @@
         <v>1</v>
       </c>
       <c r="O17" s="12" t="n">
-        <v>1446.24</v>
+        <v>482.14</v>
       </c>
       <c r="P17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q17" s="13" t="n">
-        <v>0.00268</v>
+        <v>0.007527</v>
       </c>
       <c r="R17" s="12" t="n">
-        <v>8</v>
+        <v>1.57</v>
       </c>
       <c r="S17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T17" s="14" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="U17" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="V17" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="W17" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="V17" s="12" t="n">
-        <v>56</v>
-      </c>
-      <c r="W17" s="9" t="s">
+      <c r="X17" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="Y17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="12" t="n">
+        <v>482.14</v>
+      </c>
+      <c r="AA17" s="12" t="n">
+        <v>33.75</v>
+      </c>
+      <c r="AB17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="X17" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="Y17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" s="12" t="n">
-        <v>1446.24</v>
-      </c>
-      <c r="AA17" s="12" t="n">
-        <v>101.24</v>
-      </c>
-      <c r="AB17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" s="14" t="s">
-        <v>74</v>
-      </c>
       <c r="AI17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AJ17" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AK17" s="12" t="n">
         <v>0</v>
@@ -19550,117 +19541,117 @@
         <v>0</v>
       </c>
       <c r="AM17" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AN17" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AO17" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AP17" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AQ17" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR17" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AS17" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AT17" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AU17" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AV17" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AW17" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="AP17" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ17" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR17" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS17" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT17" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU17" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV17" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW17" s="14" t="s">
+      <c r="AX17" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="AX17" s="10" t="s">
+      <c r="AY17" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AZ17" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BA17" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BB17" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BC17" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BD17" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BE17" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BF17" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="BG17" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="AY17" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ17" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA17" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB17" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BC17" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD17" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE17" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BF17" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BG17" s="9" t="s">
-        <v>78</v>
-      </c>
       <c r="BH17" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BI17" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="BJ17" s="9" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="BK17" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BL17" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BM17" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="n">
-        <v>304624</v>
+        <v>304690</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
       <c r="F18" s="9" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="G18" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="H18" s="9" t="s">
         <v>90</v>
-      </c>
-      <c r="H18" s="9" t="s">
-        <v>113</v>
       </c>
       <c r="I18" s="9" t="s">
         <v>141</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="K18" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>803.16</v>
+        <v>397.77</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>0</v>
@@ -19669,31 +19660,31 @@
         <v>1</v>
       </c>
       <c r="O18" s="12" t="n">
-        <v>803.16</v>
+        <v>397.77</v>
       </c>
       <c r="P18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q18" s="13" t="n">
-        <v>0.00374</v>
+        <v>0.000557</v>
       </c>
       <c r="R18" s="12" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="S18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T18" s="14" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="U18" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="V18" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" s="9" t="s">
         <v>72</v>
-      </c>
-      <c r="V18" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="W18" s="9" t="s">
-        <v>73</v>
       </c>
       <c r="X18" s="9" t="s">
         <v>141</v>
@@ -19702,10 +19693,10 @@
         <v>0</v>
       </c>
       <c r="Z18" s="12" t="n">
-        <v>803.16</v>
+        <v>397.77</v>
       </c>
       <c r="AA18" s="12" t="n">
-        <v>56.22</v>
+        <v>27.84</v>
       </c>
       <c r="AB18" s="12" t="n">
         <v>0</v>
@@ -19726,13 +19717,13 @@
         <v>0</v>
       </c>
       <c r="AH18" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AI18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AJ18" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AK18" s="12" t="n">
         <v>0</v>
@@ -19741,117 +19732,117 @@
         <v>0</v>
       </c>
       <c r="AM18" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AN18" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AO18" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AP18" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AQ18" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR18" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AS18" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AT18" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AU18" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AV18" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AW18" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="AP18" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ18" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR18" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS18" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT18" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU18" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV18" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW18" s="14" t="s">
-        <v>76</v>
-      </c>
       <c r="AX18" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="AY18" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AZ18" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BA18" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BB18" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BC18" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BD18" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BE18" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BF18" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="BG18" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="AY18" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ18" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA18" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB18" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BC18" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD18" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE18" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BF18" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BG18" s="9" t="s">
-        <v>78</v>
-      </c>
       <c r="BH18" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BI18" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="BJ18" s="9" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="BK18" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BL18" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BM18" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="n">
-        <v>304629</v>
+        <v>304691</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
       <c r="F19" s="9" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>141</v>
+        <v>120</v>
       </c>
       <c r="I19" s="9" t="s">
         <v>141</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>126</v>
+        <v>77</v>
       </c>
       <c r="K19" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>482.14</v>
+        <v>165.44</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>0</v>
@@ -19860,31 +19851,31 @@
         <v>1</v>
       </c>
       <c r="O19" s="12" t="n">
-        <v>482.14</v>
+        <v>165.44</v>
       </c>
       <c r="P19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q19" s="13" t="n">
-        <v>0.007527</v>
+        <v>0.00729</v>
       </c>
       <c r="R19" s="12" t="n">
-        <v>1.57</v>
+        <v>1.03</v>
       </c>
       <c r="S19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T19" s="14" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="U19" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="V19" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" s="9" t="s">
         <v>72</v>
-      </c>
-      <c r="V19" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="W19" s="9" t="s">
-        <v>73</v>
       </c>
       <c r="X19" s="9" t="s">
         <v>141</v>
@@ -19893,10 +19884,10 @@
         <v>0</v>
       </c>
       <c r="Z19" s="12" t="n">
-        <v>482.14</v>
+        <v>165.44</v>
       </c>
       <c r="AA19" s="12" t="n">
-        <v>33.75</v>
+        <v>11.58</v>
       </c>
       <c r="AB19" s="12" t="n">
         <v>0</v>
@@ -19917,13 +19908,13 @@
         <v>0</v>
       </c>
       <c r="AH19" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AI19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AJ19" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AK19" s="12" t="n">
         <v>0</v>
@@ -19932,117 +19923,117 @@
         <v>0</v>
       </c>
       <c r="AM19" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AN19" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AO19" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AP19" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AQ19" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR19" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AS19" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AT19" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AU19" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AV19" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AW19" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="AP19" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ19" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR19" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS19" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT19" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU19" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV19" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW19" s="14" t="s">
-        <v>76</v>
-      </c>
       <c r="AX19" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="AY19" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AZ19" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BA19" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BB19" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BC19" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BD19" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BE19" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BF19" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="BG19" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="AY19" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ19" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA19" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB19" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BC19" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD19" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE19" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BF19" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BG19" s="9" t="s">
-        <v>78</v>
-      </c>
       <c r="BH19" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BI19" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="BJ19" s="9" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="BK19" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BL19" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BM19" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="n">
-        <v>304690</v>
+        <v>304792</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>88</v>
+        <v>147</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
       <c r="F20" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="G20" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="I20" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="J20" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="G20" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="H20" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="I20" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="J20" s="9" t="s">
-        <v>78</v>
-      </c>
       <c r="K20" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>397.77</v>
+        <v>698.84</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>0</v>
@@ -20051,165 +20042,165 @@
         <v>1</v>
       </c>
       <c r="O20" s="12" t="n">
-        <v>397.77</v>
+        <v>698.84</v>
       </c>
       <c r="P20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q20" s="13" t="n">
-        <v>0.000557</v>
+        <v>0.026256</v>
       </c>
       <c r="R20" s="12" t="n">
-        <v>0.4</v>
+        <v>5.8</v>
       </c>
       <c r="S20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T20" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="U20" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="V20" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="W20" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="X20" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="Y20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="12" t="n">
+        <v>698.84</v>
+      </c>
+      <c r="AA20" s="12" t="n">
+        <v>48.92</v>
+      </c>
+      <c r="AB20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AI20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AK20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AN20" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AO20" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AP20" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AQ20" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR20" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AS20" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AT20" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AU20" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AV20" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AW20" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AX20" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="AY20" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AZ20" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BA20" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BB20" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BC20" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BD20" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BE20" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BF20" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="BG20" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="BH20" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BI20" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="BJ20" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="U20" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="V20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="X20" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="Y20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="12" t="n">
-        <v>397.77</v>
-      </c>
-      <c r="AA20" s="12" t="n">
-        <v>27.84</v>
-      </c>
-      <c r="AB20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH20" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ20" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AK20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM20" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AN20" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AO20" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AP20" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ20" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR20" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS20" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT20" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU20" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV20" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW20" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="AX20" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="AY20" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ20" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA20" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB20" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BC20" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD20" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE20" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BF20" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BG20" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="BH20" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BI20" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="BJ20" s="9" t="s">
-        <v>153</v>
-      </c>
       <c r="BK20" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BL20" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BM20" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="n">
-        <v>304691</v>
+        <v>304801</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>88</v>
+        <v>153</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
@@ -20218,22 +20209,22 @@
         <v>154</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>67</v>
+        <v>141</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="K21" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>165.44</v>
+        <v>1839.76</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>0</v>
@@ -20242,16 +20233,16 @@
         <v>1</v>
       </c>
       <c r="O21" s="12" t="n">
-        <v>165.44</v>
+        <v>1680.76</v>
       </c>
       <c r="P21" s="12" t="n">
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="Q21" s="13" t="n">
-        <v>0.00729</v>
+        <v>0</v>
       </c>
       <c r="R21" s="12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="S21" s="12" t="n">
         <v>0</v>
@@ -20260,52 +20251,52 @@
         <v>155</v>
       </c>
       <c r="U21" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="V21" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="W21" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="V21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" s="9" t="s">
+      <c r="X21" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="Y21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="12" t="n">
+        <v>1839.76</v>
+      </c>
+      <c r="AA21" s="12" t="n">
+        <v>73.59</v>
+      </c>
+      <c r="AB21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="X21" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="Y21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" s="12" t="n">
-        <v>165.44</v>
-      </c>
-      <c r="AA21" s="12" t="n">
-        <v>11.58</v>
-      </c>
-      <c r="AB21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH21" s="14" t="s">
-        <v>74</v>
-      </c>
       <c r="AI21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AJ21" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AK21" s="12" t="n">
         <v>0</v>
@@ -20314,117 +20305,117 @@
         <v>0</v>
       </c>
       <c r="AM21" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AN21" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AO21" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AP21" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AQ21" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR21" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AS21" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AT21" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AU21" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AV21" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AW21" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="AP21" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ21" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR21" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS21" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT21" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU21" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV21" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW21" s="14" t="s">
+      <c r="AX21" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="AX21" s="10" t="s">
-        <v>110</v>
-      </c>
       <c r="AY21" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AZ21" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BA21" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BB21" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BC21" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BD21" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BE21" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BF21" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BG21" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="BH21" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BI21" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="BJ21" s="9" t="s">
         <v>156</v>
       </c>
       <c r="BK21" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BL21" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BM21" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="n">
-        <v>304792</v>
+        <v>304810</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>157</v>
+        <v>83</v>
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
       <c r="F22" s="9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>151</v>
+        <v>67</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>160</v>
+        <v>77</v>
       </c>
       <c r="K22" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>698.84</v>
+        <v>8720.4</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>0</v>
@@ -20433,863 +20424,741 @@
         <v>1</v>
       </c>
       <c r="O22" s="12" t="n">
-        <v>698.84</v>
+        <v>8720.4</v>
       </c>
       <c r="P22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q22" s="13" t="n">
-        <v>0.026256</v>
+        <v>0.136536</v>
       </c>
       <c r="R22" s="12" t="n">
-        <v>5.8</v>
+        <v>24</v>
       </c>
       <c r="S22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T22" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="U22" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="V22" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="X22" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="Y22" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="12" t="n">
+        <v>8720.4</v>
+      </c>
+      <c r="AA22" s="12" t="n">
+        <v>610.43</v>
+      </c>
+      <c r="AB22" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AI22" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ22" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AK22" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL22" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM22" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AN22" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AO22" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AP22" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AQ22" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR22" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AS22" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AT22" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AU22" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AV22" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AW22" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="AX22" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="AY22" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AZ22" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BA22" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BB22" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BC22" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BD22" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BE22" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BF22" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="BG22" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="BH22" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BI22" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="BJ22" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="U22" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="V22" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="W22" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="X22" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="Y22" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z22" s="12" t="n">
-        <v>698.84</v>
-      </c>
-      <c r="AA22" s="12" t="n">
-        <v>48.92</v>
-      </c>
-      <c r="AB22" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC22" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD22" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE22" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF22" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG22" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH22" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI22" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ22" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AK22" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL22" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM22" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AN22" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AO22" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AP22" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ22" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR22" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS22" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT22" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU22" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV22" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW22" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="AX22" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="AY22" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ22" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA22" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB22" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BC22" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD22" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE22" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BF22" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BG22" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="BH22" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BI22" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="BJ22" s="9" t="s">
-        <v>162</v>
-      </c>
       <c r="BK22" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BL22" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BM22" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="n">
-        <v>304801</v>
+        <v>304880</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G23" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>151</v>
+        <v>108</v>
       </c>
       <c r="I23" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="J23" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="K23" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="L23" s="12" t="n">
+        <v>25242</v>
+      </c>
+      <c r="M23" s="12" t="n">
+        <v>5811.05</v>
+      </c>
+      <c r="N23" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="O23" s="12" t="n">
+        <v>28810.6</v>
+      </c>
+      <c r="P23" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="S23" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="U23" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="V23" s="12" t="n">
+        <v>120</v>
+      </c>
+      <c r="W23" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="X23" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="Y23" s="12" t="n">
+        <v>2242.45</v>
+      </c>
+      <c r="Z23" s="12" t="n">
+        <v>22999.55</v>
+      </c>
+      <c r="AA23" s="12" t="n">
+        <v>919.96</v>
+      </c>
+      <c r="AB23" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AI23" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AK23" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL23" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM23" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AN23" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AO23" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AP23" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AQ23" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR23" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AS23" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AT23" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AU23" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AV23" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AW23" s="14" t="s">
         <v>159</v>
       </c>
-      <c r="J23" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="K23" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="L23" s="12" t="n">
-        <v>1839.76</v>
-      </c>
-      <c r="M23" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O23" s="12" t="n">
-        <v>1680.76</v>
-      </c>
-      <c r="P23" s="12" t="n">
-        <v>159</v>
-      </c>
-      <c r="Q23" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" s="14" t="s">
-        <v>165</v>
-      </c>
-      <c r="U23" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="V23" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="W23" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="X23" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="Y23" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z23" s="12" t="n">
-        <v>1839.76</v>
-      </c>
-      <c r="AA23" s="12" t="n">
-        <v>73.59</v>
-      </c>
-      <c r="AB23" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC23" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD23" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE23" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF23" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG23" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH23" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI23" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ23" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AK23" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL23" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM23" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AN23" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AO23" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AP23" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ23" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR23" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS23" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT23" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU23" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV23" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW23" s="14" t="s">
+      <c r="AX23" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="AX23" s="10" t="s">
+      <c r="AY23" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AZ23" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BA23" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BB23" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BC23" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BD23" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BE23" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BF23" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="BG23" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="AY23" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ23" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA23" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB23" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BC23" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD23" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE23" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BF23" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BG23" s="9" t="s">
-        <v>78</v>
-      </c>
       <c r="BH23" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BI23" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="BJ23" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="BK23" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BL23" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BM23" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="8" t="n">
-        <v>304810</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="G24" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="H24" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="I24" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="J24" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="K24" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="L24" s="12" t="n">
-        <v>8720.4</v>
-      </c>
-      <c r="M24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O24" s="12" t="n">
-        <v>8720.4</v>
-      </c>
-      <c r="P24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="13" t="n">
-        <v>0.136536</v>
-      </c>
-      <c r="R24" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="S24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" s="14" t="s">
+      <c r="A24" s="4"/>
+    </row>
+    <row r="25" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="17" t="s">
         <v>168</v>
       </c>
-      <c r="U24" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="V24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="X24" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="Y24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z24" s="12" t="n">
-        <v>8720.4</v>
-      </c>
-      <c r="AA24" s="12" t="n">
-        <v>610.43</v>
-      </c>
-      <c r="AB24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH24" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ24" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AK24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM24" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AN24" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AO24" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AP24" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ24" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR24" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS24" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT24" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU24" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV24" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW24" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="AX24" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="AY24" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ24" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA24" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB24" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BC24" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD24" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE24" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BF24" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BG24" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="BH24" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BI24" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="BJ24" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="BK24" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BL24" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BM24" s="16" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4"/>
+      <c r="B25" s="17"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="17"/>
+      <c r="I25" s="17"/>
+      <c r="J25" s="17"/>
+      <c r="K25" s="17"/>
+      <c r="L25" s="17"/>
+      <c r="M25" s="17"/>
+      <c r="N25" s="17"/>
+      <c r="O25" s="17"/>
+      <c r="P25" s="17"/>
+      <c r="Q25" s="17"/>
+      <c r="R25" s="17"/>
+      <c r="S25" s="17"/>
+      <c r="T25" s="17"/>
+      <c r="U25" s="17"/>
+      <c r="V25" s="17"/>
     </row>
     <row r="26" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="17" t="s">
+      <c r="A26" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="B26" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C26" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D26" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="E26" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F26" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="G26" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H26" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="I26" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="B26" s="17"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="17"/>
-      <c r="G26" s="17"/>
-      <c r="H26" s="17"/>
-      <c r="I26" s="17"/>
-      <c r="J26" s="17"/>
-      <c r="K26" s="17"/>
-      <c r="L26" s="17"/>
-      <c r="M26" s="17"/>
-      <c r="N26" s="17"/>
-      <c r="O26" s="17"/>
-      <c r="P26" s="17"/>
-      <c r="Q26" s="17"/>
-      <c r="R26" s="17"/>
-      <c r="S26" s="17"/>
-      <c r="T26" s="17"/>
-      <c r="U26" s="17"/>
-      <c r="V26" s="17"/>
+      <c r="J26" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="K26" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="L26" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="M26" s="18" t="s">
+        <v>172</v>
+      </c>
+      <c r="N26" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="O26" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="P26" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q26" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="R26" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="S26" s="18" t="s">
+        <v>173</v>
+      </c>
+      <c r="T26" s="18" t="s">
+        <v>174</v>
+      </c>
+      <c r="U26" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="V26" s="18" t="s">
+        <v>37</v>
+      </c>
     </row>
-    <row r="27" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="B27" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C27" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D27" s="18" t="s">
-        <v>173</v>
-      </c>
-      <c r="E27" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F27" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="G27" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="H27" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="I27" s="18" t="s">
-        <v>174</v>
-      </c>
-      <c r="J27" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="K27" s="18" t="s">
+    <row r="27" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="19" t="n">
         <v>19</v>
       </c>
-      <c r="L27" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="M27" s="18" t="s">
+      <c r="B27" s="19" t="n">
+        <v>5811.05</v>
+      </c>
+      <c r="C27" s="19" t="n">
+        <v>159</v>
+      </c>
+      <c r="D27" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="19" t="n">
+        <v>2594.24</v>
+      </c>
+      <c r="F27" s="19" t="n">
+        <v>71673.42</v>
+      </c>
+      <c r="G27" s="19" t="n">
+        <v>4152.23</v>
+      </c>
+      <c r="H27" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="19" t="n">
+        <v>138.3</v>
+      </c>
+      <c r="K27" s="19" t="n">
+        <v>74267.66</v>
+      </c>
+      <c r="L27" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" s="20" t="n">
+        <v>0.477439</v>
+      </c>
+      <c r="S27" s="19" t="n">
+        <v>77325.47</v>
+      </c>
+      <c r="T27" s="19" t="n">
+        <v>74267.66</v>
+      </c>
+      <c r="U27" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B28" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C28" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D28" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="E28" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="F28" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="G28" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="H28" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="I28" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="J28" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="K28" s="18" t="s">
         <v>175</v>
       </c>
-      <c r="N27" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="O27" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="P27" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q27" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="R27" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="S27" s="18" t="s">
+      <c r="L28" s="18" t="s">
         <v>176</v>
       </c>
-      <c r="T27" s="18" t="s">
+      <c r="M28" s="18" t="s">
         <v>177</v>
       </c>
-      <c r="U27" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="V27" s="18" t="s">
-        <v>37</v>
-      </c>
     </row>
-    <row r="28" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="19" t="n">
-        <v>20</v>
-      </c>
-      <c r="B28" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" s="19" t="n">
-        <v>159</v>
-      </c>
-      <c r="D28" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="19" t="n">
-        <v>442.17</v>
-      </c>
-      <c r="F28" s="19" t="n">
-        <v>50535.74</v>
-      </c>
-      <c r="G28" s="19" t="n">
-        <v>3362.6</v>
-      </c>
-      <c r="H28" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="19" t="n">
-        <v>138.3</v>
-      </c>
-      <c r="K28" s="19" t="n">
-        <v>50977.91</v>
-      </c>
-      <c r="L28" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" s="20" t="n">
-        <v>0.520405</v>
-      </c>
-      <c r="S28" s="19" t="n">
-        <v>50376.74</v>
-      </c>
-      <c r="T28" s="19" t="n">
-        <v>50977.91</v>
-      </c>
-      <c r="U28" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" s="19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="B29" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C29" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="D29" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E29" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="F29" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="G29" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="H29" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="I29" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="J29" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="K29" s="18" t="s">
-        <v>178</v>
-      </c>
-      <c r="L29" s="18" t="s">
-        <v>179</v>
-      </c>
-      <c r="M29" s="18" t="s">
-        <v>180</v>
+    <row r="29" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="19" t="n">
+        <v>121.62</v>
+      </c>
+      <c r="B29" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="19" t="n">
+        <v>61.46</v>
+      </c>
+      <c r="E29" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="19" t="n">
-        <v>120.62</v>
-      </c>
-      <c r="B30" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C30" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" s="19" t="n">
-        <v>31.32</v>
-      </c>
-      <c r="E30" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" s="19" t="n">
-        <v>0</v>
-      </c>
+      <c r="A30" s="4"/>
     </row>
-    <row r="31" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="4"/>
+    <row r="31" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="21" t="s">
+        <v>178</v>
+      </c>
+      <c r="B31" s="21"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="21"/>
+      <c r="G31" s="21"/>
+      <c r="H31" s="21"/>
+      <c r="I31" s="21"/>
+      <c r="J31" s="21"/>
+      <c r="K31" s="21"/>
+      <c r="L31" s="21"/>
+      <c r="M31" s="21"/>
+      <c r="N31" s="21"/>
+      <c r="O31" s="21"/>
+      <c r="P31" s="21"/>
+      <c r="Q31" s="21"/>
+      <c r="R31" s="21"/>
+      <c r="S31" s="21"/>
+      <c r="T31" s="21"/>
+      <c r="U31" s="21"/>
+      <c r="V31" s="21"/>
+      <c r="W31" s="21"/>
+      <c r="X31" s="21"/>
+      <c r="Y31" s="21"/>
+      <c r="Z31" s="21"/>
+      <c r="AA31" s="21"/>
+      <c r="AB31" s="21"/>
+      <c r="AC31" s="21"/>
+      <c r="AD31" s="21"/>
+      <c r="AE31" s="21"/>
+      <c r="AF31" s="21"/>
+      <c r="AG31" s="21"/>
+      <c r="AH31" s="21"/>
+      <c r="AI31" s="21"/>
+      <c r="AJ31" s="21"/>
+      <c r="AK31" s="21"/>
+      <c r="AL31" s="21"/>
+      <c r="AM31" s="21"/>
+      <c r="AN31" s="21"/>
+      <c r="AO31" s="21"/>
+      <c r="AP31" s="21"/>
+      <c r="AQ31" s="21"/>
+      <c r="AR31" s="21"/>
+      <c r="AS31" s="21"/>
+      <c r="AT31" s="21"/>
+      <c r="AU31" s="21"/>
+      <c r="AV31" s="21"/>
+      <c r="AW31" s="21"/>
+      <c r="AX31" s="21"/>
+      <c r="AY31" s="21"/>
+      <c r="AZ31" s="21"/>
+      <c r="BA31" s="21"/>
+      <c r="BB31" s="21"/>
+      <c r="BC31" s="21"/>
+      <c r="BD31" s="21"/>
+      <c r="BE31" s="21"/>
+      <c r="BF31" s="21"/>
+      <c r="BG31" s="21"/>
+      <c r="BH31" s="21"/>
+      <c r="BI31" s="21"/>
+      <c r="BJ31" s="21"/>
+      <c r="BK31" s="21"/>
+      <c r="BL31" s="21"/>
+      <c r="BM31" s="21"/>
     </row>
-    <row r="32" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="21" t="s">
-        <v>181</v>
-      </c>
-      <c r="B32" s="21"/>
-      <c r="C32" s="21"/>
-      <c r="D32" s="21"/>
-      <c r="E32" s="21"/>
-      <c r="F32" s="21"/>
-      <c r="G32" s="21"/>
-      <c r="H32" s="21"/>
-      <c r="I32" s="21"/>
-      <c r="J32" s="21"/>
-      <c r="K32" s="21"/>
-      <c r="L32" s="21"/>
-      <c r="M32" s="21"/>
-      <c r="N32" s="21"/>
-      <c r="O32" s="21"/>
-      <c r="P32" s="21"/>
-      <c r="Q32" s="21"/>
-      <c r="R32" s="21"/>
-      <c r="S32" s="21"/>
-      <c r="T32" s="21"/>
-      <c r="U32" s="21"/>
-      <c r="V32" s="21"/>
-      <c r="W32" s="21"/>
-      <c r="X32" s="21"/>
-      <c r="Y32" s="21"/>
-      <c r="Z32" s="21"/>
-      <c r="AA32" s="21"/>
-      <c r="AB32" s="21"/>
-      <c r="AC32" s="21"/>
-      <c r="AD32" s="21"/>
-      <c r="AE32" s="21"/>
-      <c r="AF32" s="21"/>
-      <c r="AG32" s="21"/>
-      <c r="AH32" s="21"/>
-      <c r="AI32" s="21"/>
-      <c r="AJ32" s="21"/>
-      <c r="AK32" s="21"/>
-      <c r="AL32" s="21"/>
-      <c r="AM32" s="21"/>
-      <c r="AN32" s="21"/>
-      <c r="AO32" s="21"/>
-      <c r="AP32" s="21"/>
-      <c r="AQ32" s="21"/>
-      <c r="AR32" s="21"/>
-      <c r="AS32" s="21"/>
-      <c r="AT32" s="21"/>
-      <c r="AU32" s="21"/>
-      <c r="AV32" s="21"/>
-      <c r="AW32" s="21"/>
-      <c r="AX32" s="21"/>
-      <c r="AY32" s="21"/>
-      <c r="AZ32" s="21"/>
-      <c r="BA32" s="21"/>
-      <c r="BB32" s="21"/>
-      <c r="BC32" s="21"/>
-      <c r="BD32" s="21"/>
-      <c r="BE32" s="21"/>
-      <c r="BF32" s="21"/>
-      <c r="BG32" s="21"/>
-      <c r="BH32" s="21"/>
-      <c r="BI32" s="21"/>
-      <c r="BJ32" s="21"/>
-      <c r="BK32" s="21"/>
-      <c r="BL32" s="21"/>
-      <c r="BM32" s="21"/>
+    <row r="32" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+      <c r="K32" s="4"/>
+      <c r="L32" s="4"/>
+      <c r="M32" s="4"/>
+      <c r="N32" s="4"/>
+      <c r="O32" s="4"/>
+      <c r="P32" s="4"/>
+      <c r="Q32" s="4"/>
+      <c r="R32" s="4"/>
+      <c r="S32" s="4"/>
+      <c r="T32" s="4"/>
+      <c r="U32" s="4"/>
+      <c r="V32" s="4"/>
+      <c r="W32" s="4"/>
+      <c r="X32" s="4"/>
+      <c r="Y32" s="4"/>
+      <c r="Z32" s="4"/>
+      <c r="AA32" s="4"/>
+      <c r="AB32" s="4"/>
+      <c r="AC32" s="4"/>
+      <c r="AD32" s="4"/>
+      <c r="AE32" s="4"/>
+      <c r="AF32" s="4"/>
+      <c r="AG32" s="4"/>
+      <c r="AH32" s="4"/>
+      <c r="AI32" s="4"/>
+      <c r="AJ32" s="4"/>
+      <c r="AK32" s="4"/>
+      <c r="AL32" s="4"/>
+      <c r="AM32" s="4"/>
+      <c r="AN32" s="4"/>
+      <c r="AO32" s="4"/>
+      <c r="AP32" s="4"/>
+      <c r="AQ32" s="4"/>
+      <c r="AR32" s="4"/>
+      <c r="AS32" s="4"/>
+      <c r="AT32" s="4"/>
+      <c r="AU32" s="4"/>
+      <c r="AV32" s="4"/>
+      <c r="AW32" s="4"/>
+      <c r="AX32" s="4"/>
+      <c r="AY32" s="4"/>
+      <c r="AZ32" s="4"/>
+      <c r="BA32" s="4"/>
+      <c r="BB32" s="4"/>
+      <c r="BC32" s="4"/>
+      <c r="BD32" s="4"/>
+      <c r="BE32" s="4"/>
+      <c r="BF32" s="4"/>
+      <c r="BG32" s="4"/>
+      <c r="BH32" s="4"/>
+      <c r="BI32" s="4"/>
+      <c r="BJ32" s="4"/>
+      <c r="BK32" s="4"/>
+      <c r="BL32" s="4"/>
+      <c r="BM32" s="4"/>
     </row>
     <row r="33" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>75</v>
+        <v>179</v>
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
@@ -21358,7 +21227,7 @@
     </row>
     <row r="34" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
@@ -21427,7 +21296,7 @@
     </row>
     <row r="35" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
@@ -21496,7 +21365,7 @@
     </row>
     <row r="36" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>184</v>
+        <v>22</v>
       </c>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
@@ -21565,7 +21434,7 @@
     </row>
     <row r="37" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
-        <v>22</v>
+        <v>182</v>
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
@@ -21634,7 +21503,7 @@
     </row>
     <row r="38" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
@@ -21703,7 +21572,7 @@
     </row>
     <row r="39" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
@@ -21772,7 +21641,7 @@
     </row>
     <row r="40" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
@@ -21841,7 +21710,7 @@
     </row>
     <row r="41" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
@@ -21908,77 +21777,8 @@
       <c r="BL41" s="4"/>
       <c r="BM41" s="4"/>
     </row>
-    <row r="42" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="B42" s="4"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="4"/>
-      <c r="E42" s="4"/>
-      <c r="F42" s="4"/>
-      <c r="G42" s="4"/>
-      <c r="H42" s="4"/>
-      <c r="I42" s="4"/>
-      <c r="J42" s="4"/>
-      <c r="K42" s="4"/>
-      <c r="L42" s="4"/>
-      <c r="M42" s="4"/>
-      <c r="N42" s="4"/>
-      <c r="O42" s="4"/>
-      <c r="P42" s="4"/>
-      <c r="Q42" s="4"/>
-      <c r="R42" s="4"/>
-      <c r="S42" s="4"/>
-      <c r="T42" s="4"/>
-      <c r="U42" s="4"/>
-      <c r="V42" s="4"/>
-      <c r="W42" s="4"/>
-      <c r="X42" s="4"/>
-      <c r="Y42" s="4"/>
-      <c r="Z42" s="4"/>
-      <c r="AA42" s="4"/>
-      <c r="AB42" s="4"/>
-      <c r="AC42" s="4"/>
-      <c r="AD42" s="4"/>
-      <c r="AE42" s="4"/>
-      <c r="AF42" s="4"/>
-      <c r="AG42" s="4"/>
-      <c r="AH42" s="4"/>
-      <c r="AI42" s="4"/>
-      <c r="AJ42" s="4"/>
-      <c r="AK42" s="4"/>
-      <c r="AL42" s="4"/>
-      <c r="AM42" s="4"/>
-      <c r="AN42" s="4"/>
-      <c r="AO42" s="4"/>
-      <c r="AP42" s="4"/>
-      <c r="AQ42" s="4"/>
-      <c r="AR42" s="4"/>
-      <c r="AS42" s="4"/>
-      <c r="AT42" s="4"/>
-      <c r="AU42" s="4"/>
-      <c r="AV42" s="4"/>
-      <c r="AW42" s="4"/>
-      <c r="AX42" s="4"/>
-      <c r="AY42" s="4"/>
-      <c r="AZ42" s="4"/>
-      <c r="BA42" s="4"/>
-      <c r="BB42" s="4"/>
-      <c r="BC42" s="4"/>
-      <c r="BD42" s="4"/>
-      <c r="BE42" s="4"/>
-      <c r="BF42" s="4"/>
-      <c r="BG42" s="4"/>
-      <c r="BH42" s="4"/>
-      <c r="BI42" s="4"/>
-      <c r="BJ42" s="4"/>
-      <c r="BK42" s="4"/>
-      <c r="BL42" s="4"/>
-      <c r="BM42" s="4"/>
-    </row>
   </sheetData>
-  <mergeCells count="36">
+  <mergeCells count="35">
     <mergeCell ref="A1:BI1"/>
     <mergeCell ref="BJ1:BM1"/>
     <mergeCell ref="A2:BM2"/>
@@ -22002,8 +21802,8 @@
     <mergeCell ref="B21:E21"/>
     <mergeCell ref="B22:E22"/>
     <mergeCell ref="B23:E23"/>
-    <mergeCell ref="B24:E24"/>
-    <mergeCell ref="A26:V26"/>
+    <mergeCell ref="A25:V25"/>
+    <mergeCell ref="A31:BM31"/>
     <mergeCell ref="A32:BM32"/>
     <mergeCell ref="A33:BM33"/>
     <mergeCell ref="A34:BM34"/>
@@ -22014,7 +21814,6 @@
     <mergeCell ref="A39:BM39"/>
     <mergeCell ref="A40:BM40"/>
     <mergeCell ref="A41:BM41"/>
-    <mergeCell ref="A42:BM42"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>

--- a/tratando_tabelas/finitura/entradas_finitura.xlsx
+++ b/tratando_tabelas/finitura/entradas_finitura.xlsx
@@ -20,12 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1192" uniqueCount="216">
   <si>
     <t xml:space="preserve">Santri ADM 1.1.5.7 R1</t>
   </si>
   <si>
-    <t xml:space="preserve">Emitido em: 10/04/2026 15:09:21</t>
+    <t xml:space="preserve">Emitido em: 14/04/2026 11:16:21</t>
   </si>
   <si>
     <t xml:space="preserve">Relação de entradas - Sintético</t>
@@ -373,39 +373,6 @@
     <t xml:space="preserve">42260486532538003005550010013770411001107072</t>
   </si>
   <si>
-    <t xml:space="preserve">3.101 - INDUSTRIA E COMERCIO DE MOLDURAS SANTA LUZIA LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">139.145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27/03/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.870,46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">396.685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.659 - RODO DANNY TRANSPORTES E LOGISTICAS EIRELI ME</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138,30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260375821546000102550040001391451614982040</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260411389565000200570050003966851001240602</t>
-  </si>
-  <si>
     <t xml:space="preserve">26.123 - RUBINETTOS ACABAMENTOS EXCLUSIVOS LTDA</t>
   </si>
   <si>
@@ -455,6 +422,9 @@
   </si>
   <si>
     <t xml:space="preserve">601.004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">165,44</t>
@@ -524,6 +494,123 @@
   </si>
   <si>
     <t xml:space="preserve">41260417781412000109550010000119661000316126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.891 - STUDIOLUCE ILUMINACAO IMPORTACAO E EXPORTACAO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.899,92</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260410599342000123550020001038851778360240</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.145 - TKS ILUMINACAO E VENTILADORES LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.594,31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260430228132000136550010000088151717974742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">611.130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.910,76</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260475339051000141550080006111301281525751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.923 - NEW LINE ILUMINACAO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">223.491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171,56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260412077181000133550030002234911678252367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">223.474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.085,14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260412077181000133550030002234741265844688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.818,78</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41260417781412000109550010000119691000316152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.941 - AQUECE METAIS FABRICACAO E MANUTENCAO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.418,46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43260427254297000178550010000104561755610073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.143.628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.010,42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002271550010021436281549941562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.829 - STUDIO LAMPLUZ COMERCIO E SERVICOS LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.047,98</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260458339477000186550010000005321000000540</t>
   </si>
   <si>
     <t xml:space="preserve">Total geral</t>
@@ -16769,7 +16856,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BM41"/>
+  <dimension ref="A1:BM49"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="18"/>
@@ -18860,7 +18947,7 @@
     </row>
     <row r="14" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="n">
-        <v>304520</v>
+        <v>304561</v>
       </c>
       <c r="B14" s="9" t="s">
         <v>117</v>
@@ -18872,46 +18959,46 @@
         <v>118</v>
       </c>
       <c r="G14" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="I14" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="H14" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="I14" s="9" t="s">
-        <v>108</v>
-      </c>
       <c r="J14" s="9" t="s">
-        <v>121</v>
+        <v>68</v>
       </c>
       <c r="K14" s="11" t="s">
         <v>69</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>6870.46</v>
+        <v>1446.24</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O14" s="12" t="n">
-        <v>6870.46</v>
+        <v>1446.24</v>
       </c>
       <c r="P14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q14" s="13" t="n">
-        <v>0.04644</v>
+        <v>0.00268</v>
       </c>
       <c r="R14" s="12" t="n">
-        <v>25.27</v>
+        <v>8</v>
       </c>
       <c r="S14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T14" s="14" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="U14" s="15" t="s">
         <v>71</v>
@@ -18923,16 +19010,16 @@
         <v>72</v>
       </c>
       <c r="X14" s="9" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="Y14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z14" s="12" t="n">
-        <v>6870.46</v>
+        <v>1446.24</v>
       </c>
       <c r="AA14" s="12" t="n">
-        <v>480.93</v>
+        <v>101.24</v>
       </c>
       <c r="AB14" s="12" t="n">
         <v>0</v>
@@ -18941,7 +19028,7 @@
         <v>0</v>
       </c>
       <c r="AD14" s="12" t="n">
-        <v>138.3</v>
+        <v>0</v>
       </c>
       <c r="AE14" s="12" t="n">
         <v>0</v>
@@ -19022,25 +19109,25 @@
         <v>74</v>
       </c>
       <c r="BE14" s="14" t="s">
-        <v>123</v>
+        <v>74</v>
       </c>
       <c r="BF14" s="9" t="s">
-        <v>124</v>
+        <v>74</v>
       </c>
       <c r="BG14" s="9" t="s">
-        <v>103</v>
+        <v>77</v>
       </c>
       <c r="BH14" s="14" t="s">
-        <v>125</v>
+        <v>74</v>
       </c>
       <c r="BI14" s="9" t="s">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="BJ14" s="9" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="BK14" s="9" t="s">
-        <v>127</v>
+        <v>74</v>
       </c>
       <c r="BL14" s="9" t="s">
         <v>74</v>
@@ -19051,34 +19138,34 @@
     </row>
     <row r="15" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="n">
-        <v>304561</v>
+        <v>304624</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>128</v>
+        <v>83</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
       <c r="F15" s="9" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>67</v>
+        <v>108</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>68</v>
+        <v>114</v>
       </c>
       <c r="K15" s="11" t="s">
         <v>69</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>1446.24</v>
+        <v>803.16</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>0</v>
@@ -19087,43 +19174,43 @@
         <v>1</v>
       </c>
       <c r="O15" s="12" t="n">
-        <v>1446.24</v>
+        <v>803.16</v>
       </c>
       <c r="P15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q15" s="13" t="n">
-        <v>0.00268</v>
+        <v>0.00374</v>
       </c>
       <c r="R15" s="12" t="n">
-        <v>8</v>
+        <v>0.8</v>
       </c>
       <c r="S15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T15" s="14" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="U15" s="15" t="s">
         <v>71</v>
       </c>
       <c r="V15" s="12" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="W15" s="9" t="s">
         <v>72</v>
       </c>
       <c r="X15" s="9" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="Y15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z15" s="12" t="n">
-        <v>1446.24</v>
+        <v>803.16</v>
       </c>
       <c r="AA15" s="12" t="n">
-        <v>101.24</v>
+        <v>56.22</v>
       </c>
       <c r="AB15" s="12" t="n">
         <v>0</v>
@@ -19228,7 +19315,7 @@
         <v>77</v>
       </c>
       <c r="BJ15" s="9" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="BK15" s="9" t="s">
         <v>74</v>
@@ -19242,7 +19329,7 @@
     </row>
     <row r="16" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="n">
-        <v>304624</v>
+        <v>304629</v>
       </c>
       <c r="B16" s="9" t="s">
         <v>83</v>
@@ -19251,25 +19338,25 @@
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
       <c r="F16" s="9" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="G16" s="10" t="s">
         <v>85</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="K16" s="11" t="s">
         <v>69</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>803.16</v>
+        <v>482.14</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>0</v>
@@ -19278,22 +19365,22 @@
         <v>1</v>
       </c>
       <c r="O16" s="12" t="n">
-        <v>803.16</v>
+        <v>482.14</v>
       </c>
       <c r="P16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q16" s="13" t="n">
-        <v>0.00374</v>
+        <v>0.007527</v>
       </c>
       <c r="R16" s="12" t="n">
-        <v>0.8</v>
+        <v>1.57</v>
       </c>
       <c r="S16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T16" s="14" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="U16" s="15" t="s">
         <v>71</v>
@@ -19305,16 +19392,16 @@
         <v>72</v>
       </c>
       <c r="X16" s="9" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="Y16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z16" s="12" t="n">
-        <v>803.16</v>
+        <v>482.14</v>
       </c>
       <c r="AA16" s="12" t="n">
-        <v>56.22</v>
+        <v>33.75</v>
       </c>
       <c r="AB16" s="12" t="n">
         <v>0</v>
@@ -19419,7 +19506,7 @@
         <v>77</v>
       </c>
       <c r="BJ16" s="9" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="BK16" s="9" t="s">
         <v>74</v>
@@ -19433,7 +19520,7 @@
     </row>
     <row r="17" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="n">
-        <v>304629</v>
+        <v>304690</v>
       </c>
       <c r="B17" s="9" t="s">
         <v>83</v>
@@ -19442,25 +19529,25 @@
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
       <c r="F17" s="9" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="G17" s="10" t="s">
         <v>85</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="I17" s="9" t="s">
         <v>130</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>137</v>
+        <v>77</v>
       </c>
       <c r="K17" s="11" t="s">
         <v>69</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>482.14</v>
+        <v>397.77</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>0</v>
@@ -19469,28 +19556,28 @@
         <v>1</v>
       </c>
       <c r="O17" s="12" t="n">
-        <v>482.14</v>
+        <v>397.77</v>
       </c>
       <c r="P17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q17" s="13" t="n">
-        <v>0.007527</v>
+        <v>0.000557</v>
       </c>
       <c r="R17" s="12" t="n">
-        <v>1.57</v>
+        <v>0.4</v>
       </c>
       <c r="S17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T17" s="14" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="U17" s="15" t="s">
         <v>71</v>
       </c>
       <c r="V17" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W17" s="9" t="s">
         <v>72</v>
@@ -19502,10 +19589,10 @@
         <v>0</v>
       </c>
       <c r="Z17" s="12" t="n">
-        <v>482.14</v>
+        <v>397.77</v>
       </c>
       <c r="AA17" s="12" t="n">
-        <v>33.75</v>
+        <v>27.84</v>
       </c>
       <c r="AB17" s="12" t="n">
         <v>0</v>
@@ -19574,7 +19661,7 @@
         <v>75</v>
       </c>
       <c r="AX17" s="10" t="s">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="AY17" s="14" t="s">
         <v>74</v>
@@ -19610,7 +19697,7 @@
         <v>77</v>
       </c>
       <c r="BJ17" s="9" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="BK17" s="9" t="s">
         <v>74</v>
@@ -19624,7 +19711,7 @@
     </row>
     <row r="18" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="n">
-        <v>304690</v>
+        <v>304691</v>
       </c>
       <c r="B18" s="9" t="s">
         <v>83</v>
@@ -19633,16 +19720,16 @@
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
       <c r="F18" s="9" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="G18" s="10" t="s">
         <v>85</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>90</v>
+        <v>134</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="J18" s="9" t="s">
         <v>77</v>
@@ -19651,7 +19738,7 @@
         <v>69</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>397.77</v>
+        <v>165.44</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>0</v>
@@ -19660,22 +19747,22 @@
         <v>1</v>
       </c>
       <c r="O18" s="12" t="n">
-        <v>397.77</v>
+        <v>165.44</v>
       </c>
       <c r="P18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q18" s="13" t="n">
-        <v>0.000557</v>
+        <v>0.00729</v>
       </c>
       <c r="R18" s="12" t="n">
-        <v>0.4</v>
+        <v>1.03</v>
       </c>
       <c r="S18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T18" s="14" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="U18" s="15" t="s">
         <v>71</v>
@@ -19687,16 +19774,16 @@
         <v>72</v>
       </c>
       <c r="X18" s="9" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="Y18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z18" s="12" t="n">
-        <v>397.77</v>
+        <v>165.44</v>
       </c>
       <c r="AA18" s="12" t="n">
-        <v>27.84</v>
+        <v>11.58</v>
       </c>
       <c r="AB18" s="12" t="n">
         <v>0</v>
@@ -19801,7 +19888,7 @@
         <v>77</v>
       </c>
       <c r="BJ18" s="9" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="BK18" s="9" t="s">
         <v>74</v>
@@ -19815,34 +19902,34 @@
     </row>
     <row r="19" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="n">
-        <v>304691</v>
+        <v>304792</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>83</v>
+        <v>137</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
       <c r="F19" s="9" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>77</v>
+        <v>140</v>
       </c>
       <c r="K19" s="11" t="s">
         <v>69</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>165.44</v>
+        <v>698.84</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>0</v>
@@ -19851,43 +19938,43 @@
         <v>1</v>
       </c>
       <c r="O19" s="12" t="n">
-        <v>165.44</v>
+        <v>698.84</v>
       </c>
       <c r="P19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q19" s="13" t="n">
-        <v>0.00729</v>
+        <v>0.026256</v>
       </c>
       <c r="R19" s="12" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="S19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T19" s="14" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="U19" s="15" t="s">
         <v>71</v>
       </c>
       <c r="V19" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W19" s="9" t="s">
         <v>72</v>
       </c>
       <c r="X19" s="9" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="Y19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z19" s="12" t="n">
-        <v>165.44</v>
+        <v>698.84</v>
       </c>
       <c r="AA19" s="12" t="n">
-        <v>11.58</v>
+        <v>48.92</v>
       </c>
       <c r="AB19" s="12" t="n">
         <v>0</v>
@@ -19956,7 +20043,7 @@
         <v>75</v>
       </c>
       <c r="AX19" s="10" t="s">
-        <v>105</v>
+        <v>76</v>
       </c>
       <c r="AY19" s="14" t="s">
         <v>74</v>
@@ -19992,7 +20079,7 @@
         <v>77</v>
       </c>
       <c r="BJ19" s="9" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="BK19" s="9" t="s">
         <v>74</v>
@@ -20006,34 +20093,34 @@
     </row>
     <row r="20" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="n">
-        <v>304792</v>
+        <v>304801</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
       <c r="F20" s="9" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="G20" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="K20" s="11" t="s">
         <v>69</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>698.84</v>
+        <v>1839.76</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>0</v>
@@ -20042,22 +20129,22 @@
         <v>1</v>
       </c>
       <c r="O20" s="12" t="n">
-        <v>698.84</v>
+        <v>1680.76</v>
       </c>
       <c r="P20" s="12" t="n">
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="Q20" s="13" t="n">
-        <v>0.026256</v>
+        <v>0</v>
       </c>
       <c r="R20" s="12" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="S20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T20" s="14" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="U20" s="15" t="s">
         <v>71</v>
@@ -20069,16 +20156,16 @@
         <v>72</v>
       </c>
       <c r="X20" s="9" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="Y20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z20" s="12" t="n">
-        <v>698.84</v>
+        <v>1839.76</v>
       </c>
       <c r="AA20" s="12" t="n">
-        <v>48.92</v>
+        <v>73.59</v>
       </c>
       <c r="AB20" s="12" t="n">
         <v>0</v>
@@ -20183,7 +20270,7 @@
         <v>77</v>
       </c>
       <c r="BJ20" s="9" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="BK20" s="9" t="s">
         <v>74</v>
@@ -20197,34 +20284,34 @@
     </row>
     <row r="21" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="n">
-        <v>304801</v>
+        <v>304810</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>153</v>
+        <v>83</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
       <c r="F21" s="9" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>141</v>
+        <v>67</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>150</v>
+        <v>77</v>
       </c>
       <c r="K21" s="11" t="s">
         <v>69</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>1839.76</v>
+        <v>8720.4</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>0</v>
@@ -20233,112 +20320,112 @@
         <v>1</v>
       </c>
       <c r="O21" s="12" t="n">
-        <v>1680.76</v>
+        <v>8720.4</v>
       </c>
       <c r="P21" s="12" t="n">
-        <v>159</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="13" t="n">
-        <v>0</v>
+        <v>0.136536</v>
       </c>
       <c r="R21" s="12" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="S21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T21" s="14" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="U21" s="15" t="s">
         <v>71</v>
       </c>
       <c r="V21" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W21" s="9" t="s">
         <v>72</v>
       </c>
       <c r="X21" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="Y21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="12" t="n">
+        <v>8720.4</v>
+      </c>
+      <c r="AA21" s="12" t="n">
+        <v>610.43</v>
+      </c>
+      <c r="AB21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AI21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AK21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AN21" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AO21" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AP21" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AQ21" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR21" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AS21" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AT21" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AU21" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AV21" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AW21" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="Y21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" s="12" t="n">
-        <v>1839.76</v>
-      </c>
-      <c r="AA21" s="12" t="n">
-        <v>73.59</v>
-      </c>
-      <c r="AB21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH21" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AI21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ21" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AK21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM21" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AN21" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AO21" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AP21" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AQ21" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AR21" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AS21" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AT21" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AU21" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AV21" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW21" s="14" t="s">
-        <v>75</v>
-      </c>
       <c r="AX21" s="10" t="s">
-        <v>76</v>
+        <v>150</v>
       </c>
       <c r="AY21" s="14" t="s">
         <v>74</v>
@@ -20374,7 +20461,7 @@
         <v>77</v>
       </c>
       <c r="BJ21" s="9" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="BK21" s="9" t="s">
         <v>74</v>
@@ -20388,148 +20475,148 @@
     </row>
     <row r="22" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="n">
-        <v>304810</v>
+        <v>304880</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>83</v>
+        <v>152</v>
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
       <c r="F22" s="9" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>67</v>
+        <v>108</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="K22" s="11" t="s">
         <v>69</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>8720.4</v>
+        <v>25242</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>0</v>
+        <v>5811.05</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="O22" s="12" t="n">
-        <v>8720.4</v>
+        <v>28810.6</v>
       </c>
       <c r="P22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q22" s="13" t="n">
-        <v>0.136536</v>
+        <v>0</v>
       </c>
       <c r="R22" s="12" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="S22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T22" s="14" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="U22" s="15" t="s">
         <v>71</v>
       </c>
       <c r="V22" s="12" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="W22" s="9" t="s">
         <v>72</v>
       </c>
       <c r="X22" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="Y22" s="12" t="n">
+        <v>2242.45</v>
+      </c>
+      <c r="Z22" s="12" t="n">
+        <v>22999.55</v>
+      </c>
+      <c r="AA22" s="12" t="n">
+        <v>919.96</v>
+      </c>
+      <c r="AB22" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AI22" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ22" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AK22" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL22" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM22" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AN22" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AO22" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AP22" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AQ22" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR22" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AS22" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AT22" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AU22" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AV22" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AW22" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="Y22" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z22" s="12" t="n">
-        <v>8720.4</v>
-      </c>
-      <c r="AA22" s="12" t="n">
-        <v>610.43</v>
-      </c>
-      <c r="AB22" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC22" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD22" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE22" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF22" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG22" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH22" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AI22" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ22" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AK22" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL22" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM22" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AN22" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AO22" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AP22" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AQ22" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AR22" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AS22" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AT22" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AU22" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AV22" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW22" s="14" t="s">
-        <v>159</v>
-      </c>
       <c r="AX22" s="10" t="s">
-        <v>160</v>
+        <v>76</v>
       </c>
       <c r="AY22" s="14" t="s">
         <v>74</v>
@@ -20565,7 +20652,7 @@
         <v>77</v>
       </c>
       <c r="BJ22" s="9" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="BK22" s="9" t="s">
         <v>74</v>
@@ -20579,43 +20666,43 @@
     </row>
     <row r="23" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="n">
-        <v>304880</v>
+        <v>304916</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="9" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>66</v>
+        <v>160</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>108</v>
+        <v>139</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="K23" s="11" t="s">
         <v>69</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>25242</v>
+        <v>2899.92</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>5811.05</v>
+        <v>0</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="O23" s="12" t="n">
-        <v>28810.6</v>
+        <v>2642.3</v>
       </c>
       <c r="P23" s="12" t="n">
         <v>0</v>
@@ -20624,34 +20711,34 @@
         <v>0</v>
       </c>
       <c r="R23" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T23" s="14" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="U23" s="15" t="s">
         <v>71</v>
       </c>
       <c r="V23" s="12" t="n">
-        <v>120</v>
+        <v>28</v>
       </c>
       <c r="W23" s="9" t="s">
         <v>72</v>
       </c>
       <c r="X23" s="9" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="Y23" s="12" t="n">
-        <v>2242.45</v>
+        <v>257.62</v>
       </c>
       <c r="Z23" s="12" t="n">
-        <v>22999.55</v>
+        <v>2642.3</v>
       </c>
       <c r="AA23" s="12" t="n">
-        <v>919.96</v>
+        <v>105.7</v>
       </c>
       <c r="AB23" s="12" t="n">
         <v>0</v>
@@ -20717,7 +20804,7 @@
         <v>73</v>
       </c>
       <c r="AW23" s="14" t="s">
-        <v>159</v>
+        <v>75</v>
       </c>
       <c r="AX23" s="10" t="s">
         <v>76</v>
@@ -20756,7 +20843,7 @@
         <v>77</v>
       </c>
       <c r="BJ23" s="9" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="BK23" s="9" t="s">
         <v>74</v>
@@ -20769,879 +20856,1855 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4"/>
+      <c r="A24" s="8" t="n">
+        <v>304921</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="G24" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="I24" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="J24" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="K24" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="L24" s="12" t="n">
+        <v>3594.31</v>
+      </c>
+      <c r="M24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O24" s="12" t="n">
+        <v>3275</v>
+      </c>
+      <c r="P24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="13" t="n">
+        <v>0.02415</v>
+      </c>
+      <c r="R24" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="S24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="U24" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="V24" s="12" t="n">
+        <v>35.67</v>
+      </c>
+      <c r="W24" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="X24" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="Y24" s="12" t="n">
+        <v>319.31</v>
+      </c>
+      <c r="Z24" s="12" t="n">
+        <v>3275</v>
+      </c>
+      <c r="AA24" s="12" t="n">
+        <v>229.25</v>
+      </c>
+      <c r="AB24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AI24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AK24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM24" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AN24" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AO24" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AP24" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AQ24" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR24" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AS24" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AT24" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AU24" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AV24" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AW24" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AX24" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="AY24" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AZ24" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BA24" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BB24" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BC24" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BD24" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BE24" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BF24" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="BG24" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="BH24" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BI24" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="BJ24" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="BK24" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="BL24" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="BM24" s="16" t="s">
+        <v>79</v>
+      </c>
     </row>
-    <row r="25" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="17" t="s">
-        <v>168</v>
-      </c>
-      <c r="B25" s="17"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="17"/>
-      <c r="H25" s="17"/>
-      <c r="I25" s="17"/>
-      <c r="J25" s="17"/>
-      <c r="K25" s="17"/>
-      <c r="L25" s="17"/>
-      <c r="M25" s="17"/>
-      <c r="N25" s="17"/>
-      <c r="O25" s="17"/>
-      <c r="P25" s="17"/>
-      <c r="Q25" s="17"/>
-      <c r="R25" s="17"/>
-      <c r="S25" s="17"/>
-      <c r="T25" s="17"/>
-      <c r="U25" s="17"/>
-      <c r="V25" s="17"/>
+    <row r="25" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="8" t="n">
+        <v>304929</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="G25" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="I25" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="J25" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="K25" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="L25" s="12" t="n">
+        <v>2910.76</v>
+      </c>
+      <c r="M25" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" s="12" t="n">
+        <v>2910.76</v>
+      </c>
+      <c r="P25" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="13" t="n">
+        <v>0.000864</v>
+      </c>
+      <c r="R25" s="12" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S25" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="U25" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="V25" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="W25" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="X25" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="Y25" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="12" t="n">
+        <v>2910.76</v>
+      </c>
+      <c r="AA25" s="12" t="n">
+        <v>203.75</v>
+      </c>
+      <c r="AB25" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AI25" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ25" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AK25" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL25" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM25" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AN25" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AO25" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AP25" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AQ25" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR25" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AS25" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AT25" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AU25" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AV25" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AW25" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AX25" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="AY25" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AZ25" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BA25" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BB25" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BC25" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BD25" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BE25" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BF25" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="BG25" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="BH25" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BI25" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="BJ25" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="BK25" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="BL25" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="BM25" s="16" t="s">
+        <v>79</v>
+      </c>
     </row>
-    <row r="26" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="18" t="s">
-        <v>169</v>
-      </c>
-      <c r="B26" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C26" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D26" s="18" t="s">
-        <v>170</v>
-      </c>
-      <c r="E26" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F26" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="G26" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="H26" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="I26" s="18" t="s">
-        <v>171</v>
-      </c>
-      <c r="J26" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="K26" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="L26" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="M26" s="18" t="s">
+    <row r="26" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="8" t="n">
+        <v>304934</v>
+      </c>
+      <c r="B26" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="N26" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="O26" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="P26" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q26" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="R26" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="S26" s="18" t="s">
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="T26" s="18" t="s">
+      <c r="G26" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="U26" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="V26" s="18" t="s">
-        <v>37</v>
+      <c r="H26" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="J26" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K26" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="L26" s="12" t="n">
+        <v>171.56</v>
+      </c>
+      <c r="M26" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O26" s="12" t="n">
+        <v>156.32</v>
+      </c>
+      <c r="P26" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="U26" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="V26" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="X26" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="Y26" s="12" t="n">
+        <v>15.24</v>
+      </c>
+      <c r="Z26" s="12" t="n">
+        <v>156.32</v>
+      </c>
+      <c r="AA26" s="12" t="n">
+        <v>10.94</v>
+      </c>
+      <c r="AB26" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AI26" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AK26" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL26" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM26" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AN26" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AO26" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AP26" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AQ26" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR26" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AS26" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AT26" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AU26" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AV26" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AW26" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AX26" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="AY26" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AZ26" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BA26" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BB26" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BC26" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BD26" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BE26" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BF26" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="BG26" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="BH26" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BI26" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="BJ26" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="BK26" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="BL26" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="BM26" s="16" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="19" t="n">
-        <v>19</v>
-      </c>
-      <c r="B27" s="19" t="n">
-        <v>5811.05</v>
-      </c>
-      <c r="C27" s="19" t="n">
-        <v>159</v>
-      </c>
-      <c r="D27" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="19" t="n">
-        <v>2594.24</v>
-      </c>
-      <c r="F27" s="19" t="n">
-        <v>71673.42</v>
-      </c>
-      <c r="G27" s="19" t="n">
-        <v>4152.23</v>
-      </c>
-      <c r="H27" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="19" t="n">
-        <v>138.3</v>
-      </c>
-      <c r="K27" s="19" t="n">
-        <v>74267.66</v>
-      </c>
-      <c r="L27" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" s="20" t="n">
-        <v>0.477439</v>
-      </c>
-      <c r="S27" s="19" t="n">
-        <v>77325.47</v>
-      </c>
-      <c r="T27" s="19" t="n">
-        <v>74267.66</v>
-      </c>
-      <c r="U27" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" s="19" t="n">
-        <v>0</v>
+      <c r="A27" s="8" t="n">
+        <v>304937</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="G27" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="I27" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="J27" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="K27" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="L27" s="12" t="n">
+        <v>2085.14</v>
+      </c>
+      <c r="M27" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O27" s="12" t="n">
+        <v>1899.9</v>
+      </c>
+      <c r="P27" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" s="12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="S27" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="U27" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="V27" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="W27" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="X27" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="Y27" s="12" t="n">
+        <v>185.24</v>
+      </c>
+      <c r="Z27" s="12" t="n">
+        <v>1899.9</v>
+      </c>
+      <c r="AA27" s="12" t="n">
+        <v>132.99</v>
+      </c>
+      <c r="AB27" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AI27" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ27" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AK27" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL27" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM27" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AN27" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AO27" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AP27" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AQ27" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR27" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AS27" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AT27" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AU27" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AV27" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AW27" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AX27" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="AY27" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AZ27" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BA27" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BB27" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BC27" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BD27" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BE27" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BF27" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="BG27" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="BH27" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BI27" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="BJ27" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="BK27" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="BL27" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="BM27" s="16" t="s">
+        <v>79</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="B28" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C28" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="D28" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E28" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="F28" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="G28" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="H28" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="I28" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="J28" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="K28" s="18" t="s">
-        <v>175</v>
-      </c>
-      <c r="L28" s="18" t="s">
-        <v>176</v>
-      </c>
-      <c r="M28" s="18" t="s">
-        <v>177</v>
+    <row r="28" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="8" t="n">
+        <v>304943</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="G28" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H28" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="I28" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="J28" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K28" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="L28" s="12" t="n">
+        <v>1818.78</v>
+      </c>
+      <c r="M28" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O28" s="12" t="n">
+        <v>1657.2</v>
+      </c>
+      <c r="P28" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="U28" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="V28" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="X28" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="Y28" s="12" t="n">
+        <v>161.58</v>
+      </c>
+      <c r="Z28" s="12" t="n">
+        <v>1657.2</v>
+      </c>
+      <c r="AA28" s="12" t="n">
+        <v>66.28</v>
+      </c>
+      <c r="AB28" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AI28" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ28" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AK28" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL28" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AN28" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AO28" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AP28" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AQ28" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR28" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AS28" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AT28" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AU28" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AV28" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AW28" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AX28" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="AY28" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AZ28" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BA28" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BB28" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BC28" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BD28" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BE28" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BF28" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="BG28" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="BH28" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BI28" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="BJ28" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="BK28" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="BL28" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="BM28" s="16" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="19" t="n">
-        <v>121.62</v>
-      </c>
-      <c r="B29" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C29" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" s="19" t="n">
-        <v>61.46</v>
-      </c>
-      <c r="E29" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" s="19" t="n">
-        <v>0</v>
+      <c r="A29" s="8" t="n">
+        <v>304974</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="G29" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="I29" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="J29" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="K29" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="L29" s="12" t="n">
+        <v>5418.46</v>
+      </c>
+      <c r="M29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O29" s="12" t="n">
+        <v>5153.46</v>
+      </c>
+      <c r="P29" s="12" t="n">
+        <v>265</v>
+      </c>
+      <c r="Q29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="U29" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="V29" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="W29" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="X29" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="Y29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="12" t="n">
+        <v>5418.46</v>
+      </c>
+      <c r="AA29" s="12" t="n">
+        <v>379.29</v>
+      </c>
+      <c r="AB29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AI29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ29" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AK29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM29" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AN29" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AO29" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AP29" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AQ29" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR29" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AS29" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AT29" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AU29" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AV29" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AW29" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AX29" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="AY29" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AZ29" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BA29" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BB29" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BC29" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BD29" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BE29" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BF29" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="BG29" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="BH29" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BI29" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="BJ29" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="BK29" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="BL29" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="BM29" s="16" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="4"/>
+      <c r="A30" s="8" t="n">
+        <v>304983</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="G30" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H30" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="I30" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="J30" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="K30" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="L30" s="12" t="n">
+        <v>5010.42</v>
+      </c>
+      <c r="M30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O30" s="12" t="n">
+        <v>5010.42</v>
+      </c>
+      <c r="P30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="13" t="n">
+        <v>0.26199</v>
+      </c>
+      <c r="R30" s="12" t="n">
+        <v>109.24</v>
+      </c>
+      <c r="S30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="U30" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="V30" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="W30" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="X30" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="Y30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="12" t="n">
+        <v>5010.42</v>
+      </c>
+      <c r="AA30" s="12" t="n">
+        <v>350.73</v>
+      </c>
+      <c r="AB30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AI30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ30" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AK30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM30" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AN30" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AO30" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AP30" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AQ30" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR30" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AS30" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AT30" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AU30" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AV30" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AW30" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AX30" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="AY30" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AZ30" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BA30" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BB30" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BC30" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BD30" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BE30" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BF30" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="BG30" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="BH30" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BI30" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="BJ30" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="BK30" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="BL30" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="BM30" s="16" t="s">
+        <v>79</v>
+      </c>
     </row>
-    <row r="31" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="21" t="s">
-        <v>178</v>
-      </c>
-      <c r="B31" s="21"/>
-      <c r="C31" s="21"/>
-      <c r="D31" s="21"/>
-      <c r="E31" s="21"/>
-      <c r="F31" s="21"/>
-      <c r="G31" s="21"/>
-      <c r="H31" s="21"/>
-      <c r="I31" s="21"/>
-      <c r="J31" s="21"/>
-      <c r="K31" s="21"/>
-      <c r="L31" s="21"/>
-      <c r="M31" s="21"/>
-      <c r="N31" s="21"/>
-      <c r="O31" s="21"/>
-      <c r="P31" s="21"/>
-      <c r="Q31" s="21"/>
-      <c r="R31" s="21"/>
-      <c r="S31" s="21"/>
-      <c r="T31" s="21"/>
-      <c r="U31" s="21"/>
-      <c r="V31" s="21"/>
-      <c r="W31" s="21"/>
-      <c r="X31" s="21"/>
-      <c r="Y31" s="21"/>
-      <c r="Z31" s="21"/>
-      <c r="AA31" s="21"/>
-      <c r="AB31" s="21"/>
-      <c r="AC31" s="21"/>
-      <c r="AD31" s="21"/>
-      <c r="AE31" s="21"/>
-      <c r="AF31" s="21"/>
-      <c r="AG31" s="21"/>
-      <c r="AH31" s="21"/>
-      <c r="AI31" s="21"/>
-      <c r="AJ31" s="21"/>
-      <c r="AK31" s="21"/>
-      <c r="AL31" s="21"/>
-      <c r="AM31" s="21"/>
-      <c r="AN31" s="21"/>
-      <c r="AO31" s="21"/>
-      <c r="AP31" s="21"/>
-      <c r="AQ31" s="21"/>
-      <c r="AR31" s="21"/>
-      <c r="AS31" s="21"/>
-      <c r="AT31" s="21"/>
-      <c r="AU31" s="21"/>
-      <c r="AV31" s="21"/>
-      <c r="AW31" s="21"/>
-      <c r="AX31" s="21"/>
-      <c r="AY31" s="21"/>
-      <c r="AZ31" s="21"/>
-      <c r="BA31" s="21"/>
-      <c r="BB31" s="21"/>
-      <c r="BC31" s="21"/>
-      <c r="BD31" s="21"/>
-      <c r="BE31" s="21"/>
-      <c r="BF31" s="21"/>
-      <c r="BG31" s="21"/>
-      <c r="BH31" s="21"/>
-      <c r="BI31" s="21"/>
-      <c r="BJ31" s="21"/>
-      <c r="BK31" s="21"/>
-      <c r="BL31" s="21"/>
-      <c r="BM31" s="21"/>
+    <row r="31" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="8" t="n">
+        <v>304992</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="G31" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H31" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="I31" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="J31" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="K31" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="L31" s="12" t="n">
+        <v>3047.98</v>
+      </c>
+      <c r="M31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O31" s="12" t="n">
+        <v>3047.98</v>
+      </c>
+      <c r="P31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="S31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="U31" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="V31" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="W31" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="X31" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="Y31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="12" t="n">
+        <v>3047.98</v>
+      </c>
+      <c r="AA31" s="12" t="n">
+        <v>92.05</v>
+      </c>
+      <c r="AB31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AI31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ31" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AK31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM31" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AN31" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AO31" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AP31" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AQ31" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR31" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AS31" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AT31" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AU31" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AV31" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AW31" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AX31" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="AY31" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AZ31" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BA31" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BB31" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BC31" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BD31" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BE31" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BF31" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="BG31" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="BH31" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BI31" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="BJ31" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="BK31" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="BL31" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="BM31" s="16" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="4"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="4"/>
-      <c r="I32" s="4"/>
-      <c r="J32" s="4"/>
-      <c r="K32" s="4"/>
-      <c r="L32" s="4"/>
-      <c r="M32" s="4"/>
-      <c r="N32" s="4"/>
-      <c r="O32" s="4"/>
-      <c r="P32" s="4"/>
-      <c r="Q32" s="4"/>
-      <c r="R32" s="4"/>
-      <c r="S32" s="4"/>
-      <c r="T32" s="4"/>
-      <c r="U32" s="4"/>
-      <c r="V32" s="4"/>
-      <c r="W32" s="4"/>
-      <c r="X32" s="4"/>
-      <c r="Y32" s="4"/>
-      <c r="Z32" s="4"/>
-      <c r="AA32" s="4"/>
-      <c r="AB32" s="4"/>
-      <c r="AC32" s="4"/>
-      <c r="AD32" s="4"/>
-      <c r="AE32" s="4"/>
-      <c r="AF32" s="4"/>
-      <c r="AG32" s="4"/>
-      <c r="AH32" s="4"/>
-      <c r="AI32" s="4"/>
-      <c r="AJ32" s="4"/>
-      <c r="AK32" s="4"/>
-      <c r="AL32" s="4"/>
-      <c r="AM32" s="4"/>
-      <c r="AN32" s="4"/>
-      <c r="AO32" s="4"/>
-      <c r="AP32" s="4"/>
-      <c r="AQ32" s="4"/>
-      <c r="AR32" s="4"/>
-      <c r="AS32" s="4"/>
-      <c r="AT32" s="4"/>
-      <c r="AU32" s="4"/>
-      <c r="AV32" s="4"/>
-      <c r="AW32" s="4"/>
-      <c r="AX32" s="4"/>
-      <c r="AY32" s="4"/>
-      <c r="AZ32" s="4"/>
-      <c r="BA32" s="4"/>
-      <c r="BB32" s="4"/>
-      <c r="BC32" s="4"/>
-      <c r="BD32" s="4"/>
-      <c r="BE32" s="4"/>
-      <c r="BF32" s="4"/>
-      <c r="BG32" s="4"/>
-      <c r="BH32" s="4"/>
-      <c r="BI32" s="4"/>
-      <c r="BJ32" s="4"/>
-      <c r="BK32" s="4"/>
-      <c r="BL32" s="4"/>
-      <c r="BM32" s="4"/>
+      <c r="A32" s="4"/>
     </row>
-    <row r="33" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
-      <c r="G33" s="4"/>
-      <c r="H33" s="4"/>
-      <c r="I33" s="4"/>
-      <c r="J33" s="4"/>
-      <c r="K33" s="4"/>
-      <c r="L33" s="4"/>
-      <c r="M33" s="4"/>
-      <c r="N33" s="4"/>
-      <c r="O33" s="4"/>
-      <c r="P33" s="4"/>
-      <c r="Q33" s="4"/>
-      <c r="R33" s="4"/>
-      <c r="S33" s="4"/>
-      <c r="T33" s="4"/>
-      <c r="U33" s="4"/>
-      <c r="V33" s="4"/>
-      <c r="W33" s="4"/>
-      <c r="X33" s="4"/>
-      <c r="Y33" s="4"/>
-      <c r="Z33" s="4"/>
-      <c r="AA33" s="4"/>
-      <c r="AB33" s="4"/>
-      <c r="AC33" s="4"/>
-      <c r="AD33" s="4"/>
-      <c r="AE33" s="4"/>
-      <c r="AF33" s="4"/>
-      <c r="AG33" s="4"/>
-      <c r="AH33" s="4"/>
-      <c r="AI33" s="4"/>
-      <c r="AJ33" s="4"/>
-      <c r="AK33" s="4"/>
-      <c r="AL33" s="4"/>
-      <c r="AM33" s="4"/>
-      <c r="AN33" s="4"/>
-      <c r="AO33" s="4"/>
-      <c r="AP33" s="4"/>
-      <c r="AQ33" s="4"/>
-      <c r="AR33" s="4"/>
-      <c r="AS33" s="4"/>
-      <c r="AT33" s="4"/>
-      <c r="AU33" s="4"/>
-      <c r="AV33" s="4"/>
-      <c r="AW33" s="4"/>
-      <c r="AX33" s="4"/>
-      <c r="AY33" s="4"/>
-      <c r="AZ33" s="4"/>
-      <c r="BA33" s="4"/>
-      <c r="BB33" s="4"/>
-      <c r="BC33" s="4"/>
-      <c r="BD33" s="4"/>
-      <c r="BE33" s="4"/>
-      <c r="BF33" s="4"/>
-      <c r="BG33" s="4"/>
-      <c r="BH33" s="4"/>
-      <c r="BI33" s="4"/>
-      <c r="BJ33" s="4"/>
-      <c r="BK33" s="4"/>
-      <c r="BL33" s="4"/>
-      <c r="BM33" s="4"/>
+    <row r="33" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="17" t="s">
+        <v>197</v>
+      </c>
+      <c r="B33" s="17"/>
+      <c r="C33" s="17"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="17"/>
+      <c r="F33" s="17"/>
+      <c r="G33" s="17"/>
+      <c r="H33" s="17"/>
+      <c r="I33" s="17"/>
+      <c r="J33" s="17"/>
+      <c r="K33" s="17"/>
+      <c r="L33" s="17"/>
+      <c r="M33" s="17"/>
+      <c r="N33" s="17"/>
+      <c r="O33" s="17"/>
+      <c r="P33" s="17"/>
+      <c r="Q33" s="17"/>
+      <c r="R33" s="17"/>
+      <c r="S33" s="17"/>
+      <c r="T33" s="17"/>
+      <c r="U33" s="17"/>
+      <c r="V33" s="17"/>
     </row>
-    <row r="34" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
-      <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
-      <c r="I34" s="4"/>
-      <c r="J34" s="4"/>
-      <c r="K34" s="4"/>
-      <c r="L34" s="4"/>
-      <c r="M34" s="4"/>
-      <c r="N34" s="4"/>
-      <c r="O34" s="4"/>
-      <c r="P34" s="4"/>
-      <c r="Q34" s="4"/>
-      <c r="R34" s="4"/>
-      <c r="S34" s="4"/>
-      <c r="T34" s="4"/>
-      <c r="U34" s="4"/>
-      <c r="V34" s="4"/>
-      <c r="W34" s="4"/>
-      <c r="X34" s="4"/>
-      <c r="Y34" s="4"/>
-      <c r="Z34" s="4"/>
-      <c r="AA34" s="4"/>
-      <c r="AB34" s="4"/>
-      <c r="AC34" s="4"/>
-      <c r="AD34" s="4"/>
-      <c r="AE34" s="4"/>
-      <c r="AF34" s="4"/>
-      <c r="AG34" s="4"/>
-      <c r="AH34" s="4"/>
-      <c r="AI34" s="4"/>
-      <c r="AJ34" s="4"/>
-      <c r="AK34" s="4"/>
-      <c r="AL34" s="4"/>
-      <c r="AM34" s="4"/>
-      <c r="AN34" s="4"/>
-      <c r="AO34" s="4"/>
-      <c r="AP34" s="4"/>
-      <c r="AQ34" s="4"/>
-      <c r="AR34" s="4"/>
-      <c r="AS34" s="4"/>
-      <c r="AT34" s="4"/>
-      <c r="AU34" s="4"/>
-      <c r="AV34" s="4"/>
-      <c r="AW34" s="4"/>
-      <c r="AX34" s="4"/>
-      <c r="AY34" s="4"/>
-      <c r="AZ34" s="4"/>
-      <c r="BA34" s="4"/>
-      <c r="BB34" s="4"/>
-      <c r="BC34" s="4"/>
-      <c r="BD34" s="4"/>
-      <c r="BE34" s="4"/>
-      <c r="BF34" s="4"/>
-      <c r="BG34" s="4"/>
-      <c r="BH34" s="4"/>
-      <c r="BI34" s="4"/>
-      <c r="BJ34" s="4"/>
-      <c r="BK34" s="4"/>
-      <c r="BL34" s="4"/>
-      <c r="BM34" s="4"/>
+    <row r="34" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="18" t="s">
+        <v>198</v>
+      </c>
+      <c r="B34" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C34" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D34" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="E34" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F34" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="G34" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H34" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="I34" s="18" t="s">
+        <v>200</v>
+      </c>
+      <c r="J34" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="K34" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="L34" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="M34" s="18" t="s">
+        <v>201</v>
+      </c>
+      <c r="N34" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="O34" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="P34" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q34" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="R34" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="S34" s="18" t="s">
+        <v>202</v>
+      </c>
+      <c r="T34" s="18" t="s">
+        <v>203</v>
+      </c>
+      <c r="U34" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="V34" s="18" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
-      <c r="I35" s="4"/>
-      <c r="J35" s="4"/>
-      <c r="K35" s="4"/>
-      <c r="L35" s="4"/>
-      <c r="M35" s="4"/>
-      <c r="N35" s="4"/>
-      <c r="O35" s="4"/>
-      <c r="P35" s="4"/>
-      <c r="Q35" s="4"/>
-      <c r="R35" s="4"/>
-      <c r="S35" s="4"/>
-      <c r="T35" s="4"/>
-      <c r="U35" s="4"/>
-      <c r="V35" s="4"/>
-      <c r="W35" s="4"/>
-      <c r="X35" s="4"/>
-      <c r="Y35" s="4"/>
-      <c r="Z35" s="4"/>
-      <c r="AA35" s="4"/>
-      <c r="AB35" s="4"/>
-      <c r="AC35" s="4"/>
-      <c r="AD35" s="4"/>
-      <c r="AE35" s="4"/>
-      <c r="AF35" s="4"/>
-      <c r="AG35" s="4"/>
-      <c r="AH35" s="4"/>
-      <c r="AI35" s="4"/>
-      <c r="AJ35" s="4"/>
-      <c r="AK35" s="4"/>
-      <c r="AL35" s="4"/>
-      <c r="AM35" s="4"/>
-      <c r="AN35" s="4"/>
-      <c r="AO35" s="4"/>
-      <c r="AP35" s="4"/>
-      <c r="AQ35" s="4"/>
-      <c r="AR35" s="4"/>
-      <c r="AS35" s="4"/>
-      <c r="AT35" s="4"/>
-      <c r="AU35" s="4"/>
-      <c r="AV35" s="4"/>
-      <c r="AW35" s="4"/>
-      <c r="AX35" s="4"/>
-      <c r="AY35" s="4"/>
-      <c r="AZ35" s="4"/>
-      <c r="BA35" s="4"/>
-      <c r="BB35" s="4"/>
-      <c r="BC35" s="4"/>
-      <c r="BD35" s="4"/>
-      <c r="BE35" s="4"/>
-      <c r="BF35" s="4"/>
-      <c r="BG35" s="4"/>
-      <c r="BH35" s="4"/>
-      <c r="BI35" s="4"/>
-      <c r="BJ35" s="4"/>
-      <c r="BK35" s="4"/>
-      <c r="BL35" s="4"/>
-      <c r="BM35" s="4"/>
+      <c r="A35" s="19" t="n">
+        <v>27</v>
+      </c>
+      <c r="B35" s="19" t="n">
+        <v>5811.05</v>
+      </c>
+      <c r="C35" s="19" t="n">
+        <v>424</v>
+      </c>
+      <c r="D35" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="19" t="n">
+        <v>3533.23</v>
+      </c>
+      <c r="F35" s="19" t="n">
+        <v>90821.3</v>
+      </c>
+      <c r="G35" s="19" t="n">
+        <v>5242.28</v>
+      </c>
+      <c r="H35" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="19" t="n">
+        <v>94354.53</v>
+      </c>
+      <c r="L35" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" s="20" t="n">
+        <v>0.718003</v>
+      </c>
+      <c r="S35" s="19" t="n">
+        <v>96208.35</v>
+      </c>
+      <c r="T35" s="19" t="n">
+        <v>94354.53</v>
+      </c>
+      <c r="U35" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
-    <row r="36" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
-      <c r="I36" s="4"/>
-      <c r="J36" s="4"/>
-      <c r="K36" s="4"/>
-      <c r="L36" s="4"/>
-      <c r="M36" s="4"/>
-      <c r="N36" s="4"/>
-      <c r="O36" s="4"/>
-      <c r="P36" s="4"/>
-      <c r="Q36" s="4"/>
-      <c r="R36" s="4"/>
-      <c r="S36" s="4"/>
-      <c r="T36" s="4"/>
-      <c r="U36" s="4"/>
-      <c r="V36" s="4"/>
-      <c r="W36" s="4"/>
-      <c r="X36" s="4"/>
-      <c r="Y36" s="4"/>
-      <c r="Z36" s="4"/>
-      <c r="AA36" s="4"/>
-      <c r="AB36" s="4"/>
-      <c r="AC36" s="4"/>
-      <c r="AD36" s="4"/>
-      <c r="AE36" s="4"/>
-      <c r="AF36" s="4"/>
-      <c r="AG36" s="4"/>
-      <c r="AH36" s="4"/>
-      <c r="AI36" s="4"/>
-      <c r="AJ36" s="4"/>
-      <c r="AK36" s="4"/>
-      <c r="AL36" s="4"/>
-      <c r="AM36" s="4"/>
-      <c r="AN36" s="4"/>
-      <c r="AO36" s="4"/>
-      <c r="AP36" s="4"/>
-      <c r="AQ36" s="4"/>
-      <c r="AR36" s="4"/>
-      <c r="AS36" s="4"/>
-      <c r="AT36" s="4"/>
-      <c r="AU36" s="4"/>
-      <c r="AV36" s="4"/>
-      <c r="AW36" s="4"/>
-      <c r="AX36" s="4"/>
-      <c r="AY36" s="4"/>
-      <c r="AZ36" s="4"/>
-      <c r="BA36" s="4"/>
-      <c r="BB36" s="4"/>
-      <c r="BC36" s="4"/>
-      <c r="BD36" s="4"/>
-      <c r="BE36" s="4"/>
-      <c r="BF36" s="4"/>
-      <c r="BG36" s="4"/>
-      <c r="BH36" s="4"/>
-      <c r="BI36" s="4"/>
-      <c r="BJ36" s="4"/>
-      <c r="BK36" s="4"/>
-      <c r="BL36" s="4"/>
-      <c r="BM36" s="4"/>
+    <row r="36" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B36" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C36" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D36" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="E36" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="F36" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="G36" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="H36" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="I36" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="J36" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="K36" s="18" t="s">
+        <v>204</v>
+      </c>
+      <c r="L36" s="18" t="s">
+        <v>205</v>
+      </c>
+      <c r="M36" s="18" t="s">
+        <v>206</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
-      <c r="I37" s="4"/>
-      <c r="J37" s="4"/>
-      <c r="K37" s="4"/>
-      <c r="L37" s="4"/>
-      <c r="M37" s="4"/>
-      <c r="N37" s="4"/>
-      <c r="O37" s="4"/>
-      <c r="P37" s="4"/>
-      <c r="Q37" s="4"/>
-      <c r="R37" s="4"/>
-      <c r="S37" s="4"/>
-      <c r="T37" s="4"/>
-      <c r="U37" s="4"/>
-      <c r="V37" s="4"/>
-      <c r="W37" s="4"/>
-      <c r="X37" s="4"/>
-      <c r="Y37" s="4"/>
-      <c r="Z37" s="4"/>
-      <c r="AA37" s="4"/>
-      <c r="AB37" s="4"/>
-      <c r="AC37" s="4"/>
-      <c r="AD37" s="4"/>
-      <c r="AE37" s="4"/>
-      <c r="AF37" s="4"/>
-      <c r="AG37" s="4"/>
-      <c r="AH37" s="4"/>
-      <c r="AI37" s="4"/>
-      <c r="AJ37" s="4"/>
-      <c r="AK37" s="4"/>
-      <c r="AL37" s="4"/>
-      <c r="AM37" s="4"/>
-      <c r="AN37" s="4"/>
-      <c r="AO37" s="4"/>
-      <c r="AP37" s="4"/>
-      <c r="AQ37" s="4"/>
-      <c r="AR37" s="4"/>
-      <c r="AS37" s="4"/>
-      <c r="AT37" s="4"/>
-      <c r="AU37" s="4"/>
-      <c r="AV37" s="4"/>
-      <c r="AW37" s="4"/>
-      <c r="AX37" s="4"/>
-      <c r="AY37" s="4"/>
-      <c r="AZ37" s="4"/>
-      <c r="BA37" s="4"/>
-      <c r="BB37" s="4"/>
-      <c r="BC37" s="4"/>
-      <c r="BD37" s="4"/>
-      <c r="BE37" s="4"/>
-      <c r="BF37" s="4"/>
-      <c r="BG37" s="4"/>
-      <c r="BH37" s="4"/>
-      <c r="BI37" s="4"/>
-      <c r="BJ37" s="4"/>
-      <c r="BK37" s="4"/>
-      <c r="BL37" s="4"/>
-      <c r="BM37" s="4"/>
+      <c r="A37" s="19" t="n">
+        <v>215.37</v>
+      </c>
+      <c r="B37" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="19" t="n">
+        <v>54.84</v>
+      </c>
+      <c r="E37" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
-      <c r="I38" s="4"/>
-      <c r="J38" s="4"/>
-      <c r="K38" s="4"/>
-      <c r="L38" s="4"/>
-      <c r="M38" s="4"/>
-      <c r="N38" s="4"/>
-      <c r="O38" s="4"/>
-      <c r="P38" s="4"/>
-      <c r="Q38" s="4"/>
-      <c r="R38" s="4"/>
-      <c r="S38" s="4"/>
-      <c r="T38" s="4"/>
-      <c r="U38" s="4"/>
-      <c r="V38" s="4"/>
-      <c r="W38" s="4"/>
-      <c r="X38" s="4"/>
-      <c r="Y38" s="4"/>
-      <c r="Z38" s="4"/>
-      <c r="AA38" s="4"/>
-      <c r="AB38" s="4"/>
-      <c r="AC38" s="4"/>
-      <c r="AD38" s="4"/>
-      <c r="AE38" s="4"/>
-      <c r="AF38" s="4"/>
-      <c r="AG38" s="4"/>
-      <c r="AH38" s="4"/>
-      <c r="AI38" s="4"/>
-      <c r="AJ38" s="4"/>
-      <c r="AK38" s="4"/>
-      <c r="AL38" s="4"/>
-      <c r="AM38" s="4"/>
-      <c r="AN38" s="4"/>
-      <c r="AO38" s="4"/>
-      <c r="AP38" s="4"/>
-      <c r="AQ38" s="4"/>
-      <c r="AR38" s="4"/>
-      <c r="AS38" s="4"/>
-      <c r="AT38" s="4"/>
-      <c r="AU38" s="4"/>
-      <c r="AV38" s="4"/>
-      <c r="AW38" s="4"/>
-      <c r="AX38" s="4"/>
-      <c r="AY38" s="4"/>
-      <c r="AZ38" s="4"/>
-      <c r="BA38" s="4"/>
-      <c r="BB38" s="4"/>
-      <c r="BC38" s="4"/>
-      <c r="BD38" s="4"/>
-      <c r="BE38" s="4"/>
-      <c r="BF38" s="4"/>
-      <c r="BG38" s="4"/>
-      <c r="BH38" s="4"/>
-      <c r="BI38" s="4"/>
-      <c r="BJ38" s="4"/>
-      <c r="BK38" s="4"/>
-      <c r="BL38" s="4"/>
-      <c r="BM38" s="4"/>
+      <c r="A38" s="4"/>
     </row>
-    <row r="39" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
-      <c r="E39" s="4"/>
-      <c r="F39" s="4"/>
-      <c r="G39" s="4"/>
-      <c r="H39" s="4"/>
-      <c r="I39" s="4"/>
-      <c r="J39" s="4"/>
-      <c r="K39" s="4"/>
-      <c r="L39" s="4"/>
-      <c r="M39" s="4"/>
-      <c r="N39" s="4"/>
-      <c r="O39" s="4"/>
-      <c r="P39" s="4"/>
-      <c r="Q39" s="4"/>
-      <c r="R39" s="4"/>
-      <c r="S39" s="4"/>
-      <c r="T39" s="4"/>
-      <c r="U39" s="4"/>
-      <c r="V39" s="4"/>
-      <c r="W39" s="4"/>
-      <c r="X39" s="4"/>
-      <c r="Y39" s="4"/>
-      <c r="Z39" s="4"/>
-      <c r="AA39" s="4"/>
-      <c r="AB39" s="4"/>
-      <c r="AC39" s="4"/>
-      <c r="AD39" s="4"/>
-      <c r="AE39" s="4"/>
-      <c r="AF39" s="4"/>
-      <c r="AG39" s="4"/>
-      <c r="AH39" s="4"/>
-      <c r="AI39" s="4"/>
-      <c r="AJ39" s="4"/>
-      <c r="AK39" s="4"/>
-      <c r="AL39" s="4"/>
-      <c r="AM39" s="4"/>
-      <c r="AN39" s="4"/>
-      <c r="AO39" s="4"/>
-      <c r="AP39" s="4"/>
-      <c r="AQ39" s="4"/>
-      <c r="AR39" s="4"/>
-      <c r="AS39" s="4"/>
-      <c r="AT39" s="4"/>
-      <c r="AU39" s="4"/>
-      <c r="AV39" s="4"/>
-      <c r="AW39" s="4"/>
-      <c r="AX39" s="4"/>
-      <c r="AY39" s="4"/>
-      <c r="AZ39" s="4"/>
-      <c r="BA39" s="4"/>
-      <c r="BB39" s="4"/>
-      <c r="BC39" s="4"/>
-      <c r="BD39" s="4"/>
-      <c r="BE39" s="4"/>
-      <c r="BF39" s="4"/>
-      <c r="BG39" s="4"/>
-      <c r="BH39" s="4"/>
-      <c r="BI39" s="4"/>
-      <c r="BJ39" s="4"/>
-      <c r="BK39" s="4"/>
-      <c r="BL39" s="4"/>
-      <c r="BM39" s="4"/>
+    <row r="39" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="21" t="s">
+        <v>207</v>
+      </c>
+      <c r="B39" s="21"/>
+      <c r="C39" s="21"/>
+      <c r="D39" s="21"/>
+      <c r="E39" s="21"/>
+      <c r="F39" s="21"/>
+      <c r="G39" s="21"/>
+      <c r="H39" s="21"/>
+      <c r="I39" s="21"/>
+      <c r="J39" s="21"/>
+      <c r="K39" s="21"/>
+      <c r="L39" s="21"/>
+      <c r="M39" s="21"/>
+      <c r="N39" s="21"/>
+      <c r="O39" s="21"/>
+      <c r="P39" s="21"/>
+      <c r="Q39" s="21"/>
+      <c r="R39" s="21"/>
+      <c r="S39" s="21"/>
+      <c r="T39" s="21"/>
+      <c r="U39" s="21"/>
+      <c r="V39" s="21"/>
+      <c r="W39" s="21"/>
+      <c r="X39" s="21"/>
+      <c r="Y39" s="21"/>
+      <c r="Z39" s="21"/>
+      <c r="AA39" s="21"/>
+      <c r="AB39" s="21"/>
+      <c r="AC39" s="21"/>
+      <c r="AD39" s="21"/>
+      <c r="AE39" s="21"/>
+      <c r="AF39" s="21"/>
+      <c r="AG39" s="21"/>
+      <c r="AH39" s="21"/>
+      <c r="AI39" s="21"/>
+      <c r="AJ39" s="21"/>
+      <c r="AK39" s="21"/>
+      <c r="AL39" s="21"/>
+      <c r="AM39" s="21"/>
+      <c r="AN39" s="21"/>
+      <c r="AO39" s="21"/>
+      <c r="AP39" s="21"/>
+      <c r="AQ39" s="21"/>
+      <c r="AR39" s="21"/>
+      <c r="AS39" s="21"/>
+      <c r="AT39" s="21"/>
+      <c r="AU39" s="21"/>
+      <c r="AV39" s="21"/>
+      <c r="AW39" s="21"/>
+      <c r="AX39" s="21"/>
+      <c r="AY39" s="21"/>
+      <c r="AZ39" s="21"/>
+      <c r="BA39" s="21"/>
+      <c r="BB39" s="21"/>
+      <c r="BC39" s="21"/>
+      <c r="BD39" s="21"/>
+      <c r="BE39" s="21"/>
+      <c r="BF39" s="21"/>
+      <c r="BG39" s="21"/>
+      <c r="BH39" s="21"/>
+      <c r="BI39" s="21"/>
+      <c r="BJ39" s="21"/>
+      <c r="BK39" s="21"/>
+      <c r="BL39" s="21"/>
+      <c r="BM39" s="21"/>
     </row>
     <row r="40" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="s">
-        <v>185</v>
+        <v>74</v>
       </c>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
@@ -21710,7 +22773,7 @@
     </row>
     <row r="41" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
-        <v>186</v>
+        <v>208</v>
       </c>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
@@ -21777,8 +22840,560 @@
       <c r="BL41" s="4"/>
       <c r="BM41" s="4"/>
     </row>
+    <row r="42" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="B42" s="4"/>
+      <c r="C42" s="4"/>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4"/>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+      <c r="K42" s="4"/>
+      <c r="L42" s="4"/>
+      <c r="M42" s="4"/>
+      <c r="N42" s="4"/>
+      <c r="O42" s="4"/>
+      <c r="P42" s="4"/>
+      <c r="Q42" s="4"/>
+      <c r="R42" s="4"/>
+      <c r="S42" s="4"/>
+      <c r="T42" s="4"/>
+      <c r="U42" s="4"/>
+      <c r="V42" s="4"/>
+      <c r="W42" s="4"/>
+      <c r="X42" s="4"/>
+      <c r="Y42" s="4"/>
+      <c r="Z42" s="4"/>
+      <c r="AA42" s="4"/>
+      <c r="AB42" s="4"/>
+      <c r="AC42" s="4"/>
+      <c r="AD42" s="4"/>
+      <c r="AE42" s="4"/>
+      <c r="AF42" s="4"/>
+      <c r="AG42" s="4"/>
+      <c r="AH42" s="4"/>
+      <c r="AI42" s="4"/>
+      <c r="AJ42" s="4"/>
+      <c r="AK42" s="4"/>
+      <c r="AL42" s="4"/>
+      <c r="AM42" s="4"/>
+      <c r="AN42" s="4"/>
+      <c r="AO42" s="4"/>
+      <c r="AP42" s="4"/>
+      <c r="AQ42" s="4"/>
+      <c r="AR42" s="4"/>
+      <c r="AS42" s="4"/>
+      <c r="AT42" s="4"/>
+      <c r="AU42" s="4"/>
+      <c r="AV42" s="4"/>
+      <c r="AW42" s="4"/>
+      <c r="AX42" s="4"/>
+      <c r="AY42" s="4"/>
+      <c r="AZ42" s="4"/>
+      <c r="BA42" s="4"/>
+      <c r="BB42" s="4"/>
+      <c r="BC42" s="4"/>
+      <c r="BD42" s="4"/>
+      <c r="BE42" s="4"/>
+      <c r="BF42" s="4"/>
+      <c r="BG42" s="4"/>
+      <c r="BH42" s="4"/>
+      <c r="BI42" s="4"/>
+      <c r="BJ42" s="4"/>
+      <c r="BK42" s="4"/>
+      <c r="BL42" s="4"/>
+      <c r="BM42" s="4"/>
+    </row>
+    <row r="43" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="B43" s="4"/>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="K43" s="4"/>
+      <c r="L43" s="4"/>
+      <c r="M43" s="4"/>
+      <c r="N43" s="4"/>
+      <c r="O43" s="4"/>
+      <c r="P43" s="4"/>
+      <c r="Q43" s="4"/>
+      <c r="R43" s="4"/>
+      <c r="S43" s="4"/>
+      <c r="T43" s="4"/>
+      <c r="U43" s="4"/>
+      <c r="V43" s="4"/>
+      <c r="W43" s="4"/>
+      <c r="X43" s="4"/>
+      <c r="Y43" s="4"/>
+      <c r="Z43" s="4"/>
+      <c r="AA43" s="4"/>
+      <c r="AB43" s="4"/>
+      <c r="AC43" s="4"/>
+      <c r="AD43" s="4"/>
+      <c r="AE43" s="4"/>
+      <c r="AF43" s="4"/>
+      <c r="AG43" s="4"/>
+      <c r="AH43" s="4"/>
+      <c r="AI43" s="4"/>
+      <c r="AJ43" s="4"/>
+      <c r="AK43" s="4"/>
+      <c r="AL43" s="4"/>
+      <c r="AM43" s="4"/>
+      <c r="AN43" s="4"/>
+      <c r="AO43" s="4"/>
+      <c r="AP43" s="4"/>
+      <c r="AQ43" s="4"/>
+      <c r="AR43" s="4"/>
+      <c r="AS43" s="4"/>
+      <c r="AT43" s="4"/>
+      <c r="AU43" s="4"/>
+      <c r="AV43" s="4"/>
+      <c r="AW43" s="4"/>
+      <c r="AX43" s="4"/>
+      <c r="AY43" s="4"/>
+      <c r="AZ43" s="4"/>
+      <c r="BA43" s="4"/>
+      <c r="BB43" s="4"/>
+      <c r="BC43" s="4"/>
+      <c r="BD43" s="4"/>
+      <c r="BE43" s="4"/>
+      <c r="BF43" s="4"/>
+      <c r="BG43" s="4"/>
+      <c r="BH43" s="4"/>
+      <c r="BI43" s="4"/>
+      <c r="BJ43" s="4"/>
+      <c r="BK43" s="4"/>
+      <c r="BL43" s="4"/>
+      <c r="BM43" s="4"/>
+    </row>
+    <row r="44" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B44" s="4"/>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="K44" s="4"/>
+      <c r="L44" s="4"/>
+      <c r="M44" s="4"/>
+      <c r="N44" s="4"/>
+      <c r="O44" s="4"/>
+      <c r="P44" s="4"/>
+      <c r="Q44" s="4"/>
+      <c r="R44" s="4"/>
+      <c r="S44" s="4"/>
+      <c r="T44" s="4"/>
+      <c r="U44" s="4"/>
+      <c r="V44" s="4"/>
+      <c r="W44" s="4"/>
+      <c r="X44" s="4"/>
+      <c r="Y44" s="4"/>
+      <c r="Z44" s="4"/>
+      <c r="AA44" s="4"/>
+      <c r="AB44" s="4"/>
+      <c r="AC44" s="4"/>
+      <c r="AD44" s="4"/>
+      <c r="AE44" s="4"/>
+      <c r="AF44" s="4"/>
+      <c r="AG44" s="4"/>
+      <c r="AH44" s="4"/>
+      <c r="AI44" s="4"/>
+      <c r="AJ44" s="4"/>
+      <c r="AK44" s="4"/>
+      <c r="AL44" s="4"/>
+      <c r="AM44" s="4"/>
+      <c r="AN44" s="4"/>
+      <c r="AO44" s="4"/>
+      <c r="AP44" s="4"/>
+      <c r="AQ44" s="4"/>
+      <c r="AR44" s="4"/>
+      <c r="AS44" s="4"/>
+      <c r="AT44" s="4"/>
+      <c r="AU44" s="4"/>
+      <c r="AV44" s="4"/>
+      <c r="AW44" s="4"/>
+      <c r="AX44" s="4"/>
+      <c r="AY44" s="4"/>
+      <c r="AZ44" s="4"/>
+      <c r="BA44" s="4"/>
+      <c r="BB44" s="4"/>
+      <c r="BC44" s="4"/>
+      <c r="BD44" s="4"/>
+      <c r="BE44" s="4"/>
+      <c r="BF44" s="4"/>
+      <c r="BG44" s="4"/>
+      <c r="BH44" s="4"/>
+      <c r="BI44" s="4"/>
+      <c r="BJ44" s="4"/>
+      <c r="BK44" s="4"/>
+      <c r="BL44" s="4"/>
+      <c r="BM44" s="4"/>
+    </row>
+    <row r="45" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="B45" s="4"/>
+      <c r="C45" s="4"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+      <c r="K45" s="4"/>
+      <c r="L45" s="4"/>
+      <c r="M45" s="4"/>
+      <c r="N45" s="4"/>
+      <c r="O45" s="4"/>
+      <c r="P45" s="4"/>
+      <c r="Q45" s="4"/>
+      <c r="R45" s="4"/>
+      <c r="S45" s="4"/>
+      <c r="T45" s="4"/>
+      <c r="U45" s="4"/>
+      <c r="V45" s="4"/>
+      <c r="W45" s="4"/>
+      <c r="X45" s="4"/>
+      <c r="Y45" s="4"/>
+      <c r="Z45" s="4"/>
+      <c r="AA45" s="4"/>
+      <c r="AB45" s="4"/>
+      <c r="AC45" s="4"/>
+      <c r="AD45" s="4"/>
+      <c r="AE45" s="4"/>
+      <c r="AF45" s="4"/>
+      <c r="AG45" s="4"/>
+      <c r="AH45" s="4"/>
+      <c r="AI45" s="4"/>
+      <c r="AJ45" s="4"/>
+      <c r="AK45" s="4"/>
+      <c r="AL45" s="4"/>
+      <c r="AM45" s="4"/>
+      <c r="AN45" s="4"/>
+      <c r="AO45" s="4"/>
+      <c r="AP45" s="4"/>
+      <c r="AQ45" s="4"/>
+      <c r="AR45" s="4"/>
+      <c r="AS45" s="4"/>
+      <c r="AT45" s="4"/>
+      <c r="AU45" s="4"/>
+      <c r="AV45" s="4"/>
+      <c r="AW45" s="4"/>
+      <c r="AX45" s="4"/>
+      <c r="AY45" s="4"/>
+      <c r="AZ45" s="4"/>
+      <c r="BA45" s="4"/>
+      <c r="BB45" s="4"/>
+      <c r="BC45" s="4"/>
+      <c r="BD45" s="4"/>
+      <c r="BE45" s="4"/>
+      <c r="BF45" s="4"/>
+      <c r="BG45" s="4"/>
+      <c r="BH45" s="4"/>
+      <c r="BI45" s="4"/>
+      <c r="BJ45" s="4"/>
+      <c r="BK45" s="4"/>
+      <c r="BL45" s="4"/>
+      <c r="BM45" s="4"/>
+    </row>
+    <row r="46" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="B46" s="4"/>
+      <c r="C46" s="4"/>
+      <c r="D46" s="4"/>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4"/>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+      <c r="K46" s="4"/>
+      <c r="L46" s="4"/>
+      <c r="M46" s="4"/>
+      <c r="N46" s="4"/>
+      <c r="O46" s="4"/>
+      <c r="P46" s="4"/>
+      <c r="Q46" s="4"/>
+      <c r="R46" s="4"/>
+      <c r="S46" s="4"/>
+      <c r="T46" s="4"/>
+      <c r="U46" s="4"/>
+      <c r="V46" s="4"/>
+      <c r="W46" s="4"/>
+      <c r="X46" s="4"/>
+      <c r="Y46" s="4"/>
+      <c r="Z46" s="4"/>
+      <c r="AA46" s="4"/>
+      <c r="AB46" s="4"/>
+      <c r="AC46" s="4"/>
+      <c r="AD46" s="4"/>
+      <c r="AE46" s="4"/>
+      <c r="AF46" s="4"/>
+      <c r="AG46" s="4"/>
+      <c r="AH46" s="4"/>
+      <c r="AI46" s="4"/>
+      <c r="AJ46" s="4"/>
+      <c r="AK46" s="4"/>
+      <c r="AL46" s="4"/>
+      <c r="AM46" s="4"/>
+      <c r="AN46" s="4"/>
+      <c r="AO46" s="4"/>
+      <c r="AP46" s="4"/>
+      <c r="AQ46" s="4"/>
+      <c r="AR46" s="4"/>
+      <c r="AS46" s="4"/>
+      <c r="AT46" s="4"/>
+      <c r="AU46" s="4"/>
+      <c r="AV46" s="4"/>
+      <c r="AW46" s="4"/>
+      <c r="AX46" s="4"/>
+      <c r="AY46" s="4"/>
+      <c r="AZ46" s="4"/>
+      <c r="BA46" s="4"/>
+      <c r="BB46" s="4"/>
+      <c r="BC46" s="4"/>
+      <c r="BD46" s="4"/>
+      <c r="BE46" s="4"/>
+      <c r="BF46" s="4"/>
+      <c r="BG46" s="4"/>
+      <c r="BH46" s="4"/>
+      <c r="BI46" s="4"/>
+      <c r="BJ46" s="4"/>
+      <c r="BK46" s="4"/>
+      <c r="BL46" s="4"/>
+      <c r="BM46" s="4"/>
+    </row>
+    <row r="47" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B47" s="4"/>
+      <c r="C47" s="4"/>
+      <c r="D47" s="4"/>
+      <c r="E47" s="4"/>
+      <c r="F47" s="4"/>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="K47" s="4"/>
+      <c r="L47" s="4"/>
+      <c r="M47" s="4"/>
+      <c r="N47" s="4"/>
+      <c r="O47" s="4"/>
+      <c r="P47" s="4"/>
+      <c r="Q47" s="4"/>
+      <c r="R47" s="4"/>
+      <c r="S47" s="4"/>
+      <c r="T47" s="4"/>
+      <c r="U47" s="4"/>
+      <c r="V47" s="4"/>
+      <c r="W47" s="4"/>
+      <c r="X47" s="4"/>
+      <c r="Y47" s="4"/>
+      <c r="Z47" s="4"/>
+      <c r="AA47" s="4"/>
+      <c r="AB47" s="4"/>
+      <c r="AC47" s="4"/>
+      <c r="AD47" s="4"/>
+      <c r="AE47" s="4"/>
+      <c r="AF47" s="4"/>
+      <c r="AG47" s="4"/>
+      <c r="AH47" s="4"/>
+      <c r="AI47" s="4"/>
+      <c r="AJ47" s="4"/>
+      <c r="AK47" s="4"/>
+      <c r="AL47" s="4"/>
+      <c r="AM47" s="4"/>
+      <c r="AN47" s="4"/>
+      <c r="AO47" s="4"/>
+      <c r="AP47" s="4"/>
+      <c r="AQ47" s="4"/>
+      <c r="AR47" s="4"/>
+      <c r="AS47" s="4"/>
+      <c r="AT47" s="4"/>
+      <c r="AU47" s="4"/>
+      <c r="AV47" s="4"/>
+      <c r="AW47" s="4"/>
+      <c r="AX47" s="4"/>
+      <c r="AY47" s="4"/>
+      <c r="AZ47" s="4"/>
+      <c r="BA47" s="4"/>
+      <c r="BB47" s="4"/>
+      <c r="BC47" s="4"/>
+      <c r="BD47" s="4"/>
+      <c r="BE47" s="4"/>
+      <c r="BF47" s="4"/>
+      <c r="BG47" s="4"/>
+      <c r="BH47" s="4"/>
+      <c r="BI47" s="4"/>
+      <c r="BJ47" s="4"/>
+      <c r="BK47" s="4"/>
+      <c r="BL47" s="4"/>
+      <c r="BM47" s="4"/>
+    </row>
+    <row r="48" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="B48" s="4"/>
+      <c r="C48" s="4"/>
+      <c r="D48" s="4"/>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4"/>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="K48" s="4"/>
+      <c r="L48" s="4"/>
+      <c r="M48" s="4"/>
+      <c r="N48" s="4"/>
+      <c r="O48" s="4"/>
+      <c r="P48" s="4"/>
+      <c r="Q48" s="4"/>
+      <c r="R48" s="4"/>
+      <c r="S48" s="4"/>
+      <c r="T48" s="4"/>
+      <c r="U48" s="4"/>
+      <c r="V48" s="4"/>
+      <c r="W48" s="4"/>
+      <c r="X48" s="4"/>
+      <c r="Y48" s="4"/>
+      <c r="Z48" s="4"/>
+      <c r="AA48" s="4"/>
+      <c r="AB48" s="4"/>
+      <c r="AC48" s="4"/>
+      <c r="AD48" s="4"/>
+      <c r="AE48" s="4"/>
+      <c r="AF48" s="4"/>
+      <c r="AG48" s="4"/>
+      <c r="AH48" s="4"/>
+      <c r="AI48" s="4"/>
+      <c r="AJ48" s="4"/>
+      <c r="AK48" s="4"/>
+      <c r="AL48" s="4"/>
+      <c r="AM48" s="4"/>
+      <c r="AN48" s="4"/>
+      <c r="AO48" s="4"/>
+      <c r="AP48" s="4"/>
+      <c r="AQ48" s="4"/>
+      <c r="AR48" s="4"/>
+      <c r="AS48" s="4"/>
+      <c r="AT48" s="4"/>
+      <c r="AU48" s="4"/>
+      <c r="AV48" s="4"/>
+      <c r="AW48" s="4"/>
+      <c r="AX48" s="4"/>
+      <c r="AY48" s="4"/>
+      <c r="AZ48" s="4"/>
+      <c r="BA48" s="4"/>
+      <c r="BB48" s="4"/>
+      <c r="BC48" s="4"/>
+      <c r="BD48" s="4"/>
+      <c r="BE48" s="4"/>
+      <c r="BF48" s="4"/>
+      <c r="BG48" s="4"/>
+      <c r="BH48" s="4"/>
+      <c r="BI48" s="4"/>
+      <c r="BJ48" s="4"/>
+      <c r="BK48" s="4"/>
+      <c r="BL48" s="4"/>
+      <c r="BM48" s="4"/>
+    </row>
+    <row r="49" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="B49" s="4"/>
+      <c r="C49" s="4"/>
+      <c r="D49" s="4"/>
+      <c r="E49" s="4"/>
+      <c r="F49" s="4"/>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+      <c r="K49" s="4"/>
+      <c r="L49" s="4"/>
+      <c r="M49" s="4"/>
+      <c r="N49" s="4"/>
+      <c r="O49" s="4"/>
+      <c r="P49" s="4"/>
+      <c r="Q49" s="4"/>
+      <c r="R49" s="4"/>
+      <c r="S49" s="4"/>
+      <c r="T49" s="4"/>
+      <c r="U49" s="4"/>
+      <c r="V49" s="4"/>
+      <c r="W49" s="4"/>
+      <c r="X49" s="4"/>
+      <c r="Y49" s="4"/>
+      <c r="Z49" s="4"/>
+      <c r="AA49" s="4"/>
+      <c r="AB49" s="4"/>
+      <c r="AC49" s="4"/>
+      <c r="AD49" s="4"/>
+      <c r="AE49" s="4"/>
+      <c r="AF49" s="4"/>
+      <c r="AG49" s="4"/>
+      <c r="AH49" s="4"/>
+      <c r="AI49" s="4"/>
+      <c r="AJ49" s="4"/>
+      <c r="AK49" s="4"/>
+      <c r="AL49" s="4"/>
+      <c r="AM49" s="4"/>
+      <c r="AN49" s="4"/>
+      <c r="AO49" s="4"/>
+      <c r="AP49" s="4"/>
+      <c r="AQ49" s="4"/>
+      <c r="AR49" s="4"/>
+      <c r="AS49" s="4"/>
+      <c r="AT49" s="4"/>
+      <c r="AU49" s="4"/>
+      <c r="AV49" s="4"/>
+      <c r="AW49" s="4"/>
+      <c r="AX49" s="4"/>
+      <c r="AY49" s="4"/>
+      <c r="AZ49" s="4"/>
+      <c r="BA49" s="4"/>
+      <c r="BB49" s="4"/>
+      <c r="BC49" s="4"/>
+      <c r="BD49" s="4"/>
+      <c r="BE49" s="4"/>
+      <c r="BF49" s="4"/>
+      <c r="BG49" s="4"/>
+      <c r="BH49" s="4"/>
+      <c r="BI49" s="4"/>
+      <c r="BJ49" s="4"/>
+      <c r="BK49" s="4"/>
+      <c r="BL49" s="4"/>
+      <c r="BM49" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="35">
+  <mergeCells count="43">
     <mergeCell ref="A1:BI1"/>
     <mergeCell ref="BJ1:BM1"/>
     <mergeCell ref="A2:BM2"/>
@@ -21802,18 +23417,26 @@
     <mergeCell ref="B21:E21"/>
     <mergeCell ref="B22:E22"/>
     <mergeCell ref="B23:E23"/>
-    <mergeCell ref="A25:V25"/>
-    <mergeCell ref="A31:BM31"/>
-    <mergeCell ref="A32:BM32"/>
-    <mergeCell ref="A33:BM33"/>
-    <mergeCell ref="A34:BM34"/>
-    <mergeCell ref="A35:BM35"/>
-    <mergeCell ref="A36:BM36"/>
-    <mergeCell ref="A37:BM37"/>
-    <mergeCell ref="A38:BM38"/>
+    <mergeCell ref="B24:E24"/>
+    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="B27:E27"/>
+    <mergeCell ref="B28:E28"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="B31:E31"/>
+    <mergeCell ref="A33:V33"/>
     <mergeCell ref="A39:BM39"/>
     <mergeCell ref="A40:BM40"/>
     <mergeCell ref="A41:BM41"/>
+    <mergeCell ref="A42:BM42"/>
+    <mergeCell ref="A43:BM43"/>
+    <mergeCell ref="A44:BM44"/>
+    <mergeCell ref="A45:BM45"/>
+    <mergeCell ref="A46:BM46"/>
+    <mergeCell ref="A47:BM47"/>
+    <mergeCell ref="A48:BM48"/>
+    <mergeCell ref="A49:BM49"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>

--- a/tratando_tabelas/finitura/entradas_finitura.xlsx
+++ b/tratando_tabelas/finitura/entradas_finitura.xlsx
@@ -20,12 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1192" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1072" uniqueCount="202">
   <si>
     <t xml:space="preserve">Santri ADM 1.1.5.7 R1</t>
   </si>
   <si>
-    <t xml:space="preserve">Emitido em: 14/04/2026 11:16:21</t>
+    <t xml:space="preserve">Emitido em: 23/04/2026 10:36:38</t>
   </si>
   <si>
     <t xml:space="preserve">Relação de entradas - Sintético</t>
@@ -214,25 +214,28 @@
     <t xml:space="preserve">Fornecedor substituto tributário</t>
   </si>
   <si>
-    <t xml:space="preserve">1.856 - DEXCO S.A - METAIS</t>
+    <t xml:space="preserve">16.540 - LEXXA METAIS SANITARIOS LTDA</t>
   </si>
   <si>
-    <t xml:space="preserve">5.050.871</t>
+    <t xml:space="preserve">10.764</t>
   </si>
   <si>
     <t xml:space="preserve">1</t>
   </si>
   <si>
-    <t xml:space="preserve">31/03/2026</t>
+    <t xml:space="preserve">08/04/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">28/04/2026</t>
+    <t xml:space="preserve">09/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06/05/2026</t>
   </si>
   <si>
     <t xml:space="preserve">XML</t>
   </si>
   <si>
-    <t xml:space="preserve">746,26</t>
+    <t xml:space="preserve">1.839,76</t>
   </si>
   <si>
     <t xml:space="preserve">Ag. chegada da mercadoria</t>
@@ -256,232 +259,19 @@
     <t xml:space="preserve">          </t>
   </si>
   <si>
-    <t xml:space="preserve">35260397837181002190550010050508711279023491</t>
+    <t xml:space="preserve">42260400700221000253550010000107641845284938</t>
   </si>
   <si>
     <t xml:space="preserve">Não</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.050.848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">738,32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260397837181002190550010050508481585762982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">761 - DOCOL FV IND.E COM. DE METAIS SANITARIOS LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">603.982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.871,53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260375339051000141550080006039821403799739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.759 - SKYLIGHT COMERCIO E IMPORTACAO LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26/03/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.438,46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43260328115088000106550010000115381056280786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.798,08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43260328115088000106550010000115371056119996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">605.165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.288,60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260475339051000141550080006051651507719756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.051.937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">02/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">496,19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050519371840993190</t>
-  </si>
-  <si>
-    <t xml:space="preserve">606.708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">909,41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260475339051000141550080006067081131978522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.925 - MOHAWK REVESTIMENTOS COCAL DO SUL LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.377.041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.314,60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260486532538003005550010013770411001107072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.123 - RUBINETTOS ACABAMENTOS EXCLUSIVOS LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.446,24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43260386895448000136550010000643241113748902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">608.548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">803,16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260475339051000141550080006085481212565914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">609.191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">482,14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260475339051000141550080006091911082827250</t>
-  </si>
-  <si>
-    <t xml:space="preserve">598.984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">397,77</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260375339051000141550080005989841086380358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">601.004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27/03/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">165,44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260375339051000141550080006010041170406590</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.855 - DEXCO S.A - LOUCAS DECA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.141.823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">698,84</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002271550010021418231107341581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.540 - LEXXA METAIS SANITARIOS LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.839,76</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260400700221000253550010000107641845284938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">604.893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.720,40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.910</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260375339051000141550080006048931151164109</t>
   </si>
   <si>
     <t xml:space="preserve">16.059 - JLR COM IMPORT. E EXP. DE MATERIAIS DE CONSTRUCAO LTDA</t>
   </si>
   <si>
     <t xml:space="preserve">11.966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06/04/2026</t>
   </si>
   <si>
     <t xml:space="preserve">10/04/2026</t>
@@ -493,25 +283,10 @@
     <t xml:space="preserve">25.242,00</t>
   </si>
   <si>
-    <t xml:space="preserve">41260417781412000109550010000119661000316126</t>
+    <t xml:space="preserve">S</t>
   </si>
   <si>
-    <t xml:space="preserve">6.891 - STUDIOLUCE ILUMINACAO IMPORTACAO E EXPORTACAO LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.899,92</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260410599342000123550020001038851778360240</t>
+    <t xml:space="preserve">41260417781412000109550010000119661000316126</t>
   </si>
   <si>
     <t xml:space="preserve">24.145 - TKS ILUMINACAO E VENTILADORES LTDA</t>
@@ -529,15 +304,6 @@
     <t xml:space="preserve">35260430228132000136550010000088151717974742</t>
   </si>
   <si>
-    <t xml:space="preserve">611.130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.910,76</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260475339051000141550080006111301281525751</t>
-  </si>
-  <si>
     <t xml:space="preserve">2.923 - NEW LINE ILUMINACAO LTDA</t>
   </si>
   <si>
@@ -550,16 +316,10 @@
     <t xml:space="preserve">171,56</t>
   </si>
   <si>
-    <t xml:space="preserve">35260412077181000133550030002234911678252367</t>
+    <t xml:space="preserve">2.910</t>
   </si>
   <si>
-    <t xml:space="preserve">223.474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.085,14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260412077181000133550030002234741265844688</t>
+    <t xml:space="preserve">35260412077181000133550030002234911678252367</t>
   </si>
   <si>
     <t xml:space="preserve">11.969</t>
@@ -580,22 +340,13 @@
     <t xml:space="preserve">13/04/2026</t>
   </si>
   <si>
+    <t xml:space="preserve">07/05/2026</t>
+  </si>
+  <si>
     <t xml:space="preserve">5.418,46</t>
   </si>
   <si>
     <t xml:space="preserve">43260427254297000178550010000104561755610073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.143.628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.010,42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002271550010021436281549941562</t>
   </si>
   <si>
     <t xml:space="preserve">33.829 - STUDIO LAMPLUZ COMERCIO E SERVICOS LTDA</t>
@@ -611,6 +362,213 @@
   </si>
   <si>
     <t xml:space="preserve">35260458339477000186550010000005321000000540</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.856 - DEXCO S.A - METAIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.064.033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">542,51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050640331969596239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.343 - INTERLIGHT SISTEMAS DE ILUMINACAO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">258.833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.577,37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260458329608000144550010002588331002588349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">761 - DOCOL FV IND.E COM. DE METAIS SANITARIOS LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">613.557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.751,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260475339051000141550080006135571858110937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">613.278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.088,57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260475339051000141550080006132781579863649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">613.230</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.411,71</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260475339051000141550080006132301500422434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">612.943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.612,24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260475339051000141550080006129431856669777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.064.044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">392,71</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050640441827095101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.064.051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163,48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050640511436911789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.065.606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.770,41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050656061898250181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.065.617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">314,65</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050656171723297522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.065.625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.373,30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050656251541669272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">615.999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.568,57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260475339051000141550080006159991401589579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">617.873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.135,16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260475339051000141550080006178731396485917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">617.874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.258,14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260475339051000141550080006178741898295127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">618.318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.879,02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260475339051000141550080006183181995812619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">619.446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.121,47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260475339051000141550080006194461527273470</t>
+  </si>
+  <si>
+    <t xml:space="preserve">619.536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.331,26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260475339051000141550080006195361507400913</t>
   </si>
   <si>
     <t xml:space="preserve">Total geral</t>
@@ -16856,7 +16814,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BM49"/>
+  <dimension ref="A1:BM46"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="18"/>
@@ -17228,7 +17186,7 @@
     </row>
     <row r="5" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="n">
-        <v>304192</v>
+        <v>304801</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>64</v>
@@ -17246,16 +17204,16 @@
         <v>67</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K5" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L5" s="12" t="n">
-        <v>746.26</v>
+        <v>1839.76</v>
       </c>
       <c r="M5" s="12" t="n">
         <v>0</v>
@@ -17264,43 +17222,43 @@
         <v>1</v>
       </c>
       <c r="O5" s="12" t="n">
-        <v>746.26</v>
+        <v>1680.76</v>
       </c>
       <c r="P5" s="12" t="n">
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="Q5" s="13" t="n">
-        <v>0.034224</v>
+        <v>0</v>
       </c>
       <c r="R5" s="12" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="S5" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T5" s="14" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="U5" s="15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V5" s="12" t="n">
         <v>28</v>
       </c>
       <c r="W5" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X5" s="9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Y5" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z5" s="12" t="n">
-        <v>746.26</v>
+        <v>1839.76</v>
       </c>
       <c r="AA5" s="12" t="n">
-        <v>29.85</v>
+        <v>73.59</v>
       </c>
       <c r="AB5" s="12" t="n">
         <v>0</v>
@@ -17321,13 +17279,13 @@
         <v>0</v>
       </c>
       <c r="AH5" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI5" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AJ5" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AK5" s="12" t="n">
         <v>0</v>
@@ -17336,162 +17294,162 @@
         <v>0</v>
       </c>
       <c r="AM5" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AN5" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AO5" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AP5" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AQ5" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AR5" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AS5" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AT5" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AU5" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AV5" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AW5" s="14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AX5" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AY5" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AZ5" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BA5" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BB5" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BC5" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BD5" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BE5" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BF5" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BG5" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BH5" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BI5" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BJ5" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="BK5" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BL5" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BM5" s="16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="n">
-        <v>304216</v>
+        <v>304880</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
       <c r="E6" s="9"/>
       <c r="F6" s="9" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G6" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L6" s="12" t="n">
-        <v>738.32</v>
+        <v>25242</v>
       </c>
       <c r="M6" s="12" t="n">
-        <v>0</v>
+        <v>5811.05</v>
       </c>
       <c r="N6" s="12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="O6" s="12" t="n">
-        <v>693.26</v>
+        <v>28810.6</v>
       </c>
       <c r="P6" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q6" s="13" t="n">
-        <v>0.011556</v>
+        <v>0</v>
       </c>
       <c r="R6" s="12" t="n">
-        <v>1.23</v>
+        <v>6</v>
       </c>
       <c r="S6" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T6" s="14" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="U6" s="15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V6" s="12" t="n">
-        <v>28</v>
+        <v>120</v>
       </c>
       <c r="W6" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X6" s="9" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="Y6" s="12" t="n">
-        <v>45.06</v>
+        <v>2242.45</v>
       </c>
       <c r="Z6" s="12" t="n">
-        <v>693.26</v>
+        <v>22999.55</v>
       </c>
       <c r="AA6" s="12" t="n">
-        <v>48.53</v>
+        <v>919.96</v>
       </c>
       <c r="AB6" s="12" t="n">
         <v>0</v>
@@ -17512,13 +17470,13 @@
         <v>0</v>
       </c>
       <c r="AH6" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI6" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AJ6" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AK6" s="12" t="n">
         <v>0</v>
@@ -17527,162 +17485,162 @@
         <v>0</v>
       </c>
       <c r="AM6" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AN6" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AO6" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AP6" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AQ6" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AR6" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AS6" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AT6" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AU6" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AV6" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AW6" s="14" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="AX6" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AY6" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AZ6" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BA6" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BB6" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BC6" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BD6" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BE6" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BF6" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BG6" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BH6" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BI6" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BJ6" s="9" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="BK6" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BL6" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BM6" s="16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="n">
-        <v>304225</v>
+        <v>304921</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
       <c r="F7" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H7" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="G7" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>67</v>
-      </c>
       <c r="I7" s="9" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="K7" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L7" s="12" t="n">
-        <v>6871.53</v>
+        <v>3594.31</v>
       </c>
       <c r="M7" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N7" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O7" s="12" t="n">
-        <v>6871.53</v>
+        <v>3275</v>
       </c>
       <c r="P7" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q7" s="13" t="n">
-        <v>0.04634</v>
+        <v>0.02415</v>
       </c>
       <c r="R7" s="12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="S7" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T7" s="14" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="U7" s="15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V7" s="12" t="n">
-        <v>28</v>
+        <v>35.67</v>
       </c>
       <c r="W7" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X7" s="9" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="Y7" s="12" t="n">
-        <v>0</v>
+        <v>319.31</v>
       </c>
       <c r="Z7" s="12" t="n">
-        <v>6871.53</v>
+        <v>3275</v>
       </c>
       <c r="AA7" s="12" t="n">
-        <v>481.01</v>
+        <v>229.25</v>
       </c>
       <c r="AB7" s="12" t="n">
         <v>0</v>
@@ -17703,13 +17661,13 @@
         <v>0</v>
       </c>
       <c r="AH7" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI7" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AJ7" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AK7" s="12" t="n">
         <v>0</v>
@@ -17718,117 +17676,117 @@
         <v>0</v>
       </c>
       <c r="AM7" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AN7" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AO7" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AP7" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AQ7" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AR7" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AS7" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AT7" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AU7" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AV7" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AW7" s="14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AX7" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AY7" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AZ7" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BA7" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BB7" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BC7" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BD7" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BE7" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BF7" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BG7" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BH7" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BI7" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BJ7" s="9" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="BK7" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BL7" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BM7" s="16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="n">
-        <v>304260</v>
+        <v>304934</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
       <c r="F8" s="9" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K8" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L8" s="12" t="n">
-        <v>1438.46</v>
+        <v>171.56</v>
       </c>
       <c r="M8" s="12" t="n">
         <v>0</v>
@@ -17837,7 +17795,7 @@
         <v>1</v>
       </c>
       <c r="O8" s="12" t="n">
-        <v>1310.67</v>
+        <v>156.32</v>
       </c>
       <c r="P8" s="12" t="n">
         <v>0</v>
@@ -17852,28 +17810,28 @@
         <v>0</v>
       </c>
       <c r="T8" s="14" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="U8" s="15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V8" s="12" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="W8" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X8" s="9" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="Y8" s="12" t="n">
-        <v>127.79</v>
+        <v>15.24</v>
       </c>
       <c r="Z8" s="12" t="n">
-        <v>1310.67</v>
+        <v>156.32</v>
       </c>
       <c r="AA8" s="12" t="n">
-        <v>52.43</v>
+        <v>10.94</v>
       </c>
       <c r="AB8" s="12" t="n">
         <v>0</v>
@@ -17894,13 +17852,13 @@
         <v>0</v>
       </c>
       <c r="AH8" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AJ8" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AK8" s="12" t="n">
         <v>0</v>
@@ -17909,126 +17867,126 @@
         <v>0</v>
       </c>
       <c r="AM8" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AN8" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AO8" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AP8" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AQ8" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AR8" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AS8" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AT8" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AU8" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AV8" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AW8" s="14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AX8" s="10" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="AY8" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AZ8" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BA8" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BB8" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BC8" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BD8" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BE8" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BF8" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BG8" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BH8" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BI8" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BJ8" s="9" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="BK8" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BL8" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BM8" s="16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="n">
-        <v>304261</v>
+        <v>304943</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="9" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="G9" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K9" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L9" s="12" t="n">
-        <v>1798.08</v>
+        <v>1818.78</v>
       </c>
       <c r="M9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N9" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O9" s="12" t="n">
-        <v>1638.34</v>
+        <v>1657.2</v>
       </c>
       <c r="P9" s="12" t="n">
         <v>0</v>
@@ -18043,28 +18001,28 @@
         <v>0</v>
       </c>
       <c r="T9" s="14" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="U9" s="15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V9" s="12" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="W9" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X9" s="9" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="Y9" s="12" t="n">
-        <v>159.74</v>
+        <v>161.58</v>
       </c>
       <c r="Z9" s="12" t="n">
-        <v>1638.34</v>
+        <v>1657.2</v>
       </c>
       <c r="AA9" s="12" t="n">
-        <v>65.53</v>
+        <v>66.28</v>
       </c>
       <c r="AB9" s="12" t="n">
         <v>0</v>
@@ -18085,13 +18043,13 @@
         <v>0</v>
       </c>
       <c r="AH9" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AJ9" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AK9" s="12" t="n">
         <v>0</v>
@@ -18100,117 +18058,117 @@
         <v>0</v>
       </c>
       <c r="AM9" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AN9" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AO9" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AP9" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AQ9" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AR9" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AS9" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AT9" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AU9" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AV9" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AW9" s="14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AX9" s="10" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="AY9" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AZ9" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BA9" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BB9" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BC9" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BD9" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BE9" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BF9" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BG9" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BH9" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BI9" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BJ9" s="9" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="BK9" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BL9" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BM9" s="16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="n">
-        <v>304343</v>
+        <v>304974</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
       <c r="F10" s="9" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="K10" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L10" s="12" t="n">
-        <v>3288.6</v>
+        <v>5418.46</v>
       </c>
       <c r="M10" s="12" t="n">
         <v>0</v>
@@ -18219,43 +18177,43 @@
         <v>1</v>
       </c>
       <c r="O10" s="12" t="n">
-        <v>3288.6</v>
+        <v>5153.46</v>
       </c>
       <c r="P10" s="12" t="n">
-        <v>0</v>
+        <v>265</v>
       </c>
       <c r="Q10" s="13" t="n">
-        <v>0.049896</v>
+        <v>0</v>
       </c>
       <c r="R10" s="12" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="S10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T10" s="14" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="U10" s="15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V10" s="12" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="W10" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X10" s="9" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="Y10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z10" s="12" t="n">
-        <v>3288.6</v>
+        <v>5418.46</v>
       </c>
       <c r="AA10" s="12" t="n">
-        <v>230.2</v>
+        <v>379.29</v>
       </c>
       <c r="AB10" s="12" t="n">
         <v>0</v>
@@ -18276,13 +18234,13 @@
         <v>0</v>
       </c>
       <c r="AH10" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AJ10" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AK10" s="12" t="n">
         <v>0</v>
@@ -18291,308 +18249,308 @@
         <v>0</v>
       </c>
       <c r="AM10" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AN10" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AO10" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AP10" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AQ10" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AR10" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AS10" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AT10" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AU10" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AV10" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AW10" s="14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AX10" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AY10" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AZ10" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BA10" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BB10" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BC10" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BD10" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BE10" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BF10" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BG10" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BH10" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BI10" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BJ10" s="9" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="BK10" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BL10" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BM10" s="16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="n">
-        <v>304390</v>
+        <v>304992</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>64</v>
+        <v>109</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
       <c r="F11" s="9" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="G11" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="J11" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="K11" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L11" s="12" t="n">
+        <v>3047.98</v>
+      </c>
+      <c r="M11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O11" s="12" t="n">
+        <v>3047.98</v>
+      </c>
+      <c r="P11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="S11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="U11" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V11" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="W11" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X11" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="Y11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="12" t="n">
+        <v>3047.98</v>
+      </c>
+      <c r="AA11" s="12" t="n">
+        <v>92.05</v>
+      </c>
+      <c r="AB11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN11" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO11" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP11" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ11" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR11" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS11" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT11" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU11" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV11" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW11" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX11" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="K11" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="L11" s="12" t="n">
-        <v>496.19</v>
-      </c>
-      <c r="M11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="O11" s="12" t="n">
-        <v>476.99</v>
-      </c>
-      <c r="P11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="13" t="n">
-        <v>0.104397</v>
-      </c>
-      <c r="R11" s="12" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="S11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="U11" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="V11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="X11" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="Y11" s="12" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="Z11" s="12" t="n">
-        <v>476.99</v>
-      </c>
-      <c r="AA11" s="12" t="n">
-        <v>24.54</v>
-      </c>
-      <c r="AB11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH11" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AI11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ11" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AK11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM11" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AN11" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AO11" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AP11" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AQ11" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AR11" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AS11" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AT11" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AU11" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AV11" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW11" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AX11" s="10" t="s">
-        <v>105</v>
-      </c>
       <c r="AY11" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AZ11" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BA11" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BB11" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BC11" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BD11" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BE11" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BF11" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BG11" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BH11" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BI11" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BJ11" s="9" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="BK11" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BL11" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BM11" s="16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="n">
-        <v>304417</v>
+        <v>305175</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
       <c r="F12" s="9" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="K12" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>909.41</v>
+        <v>542.51</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>0</v>
@@ -18601,43 +18559,43 @@
         <v>1</v>
       </c>
       <c r="O12" s="12" t="n">
-        <v>909.41</v>
+        <v>509.4</v>
       </c>
       <c r="P12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" s="13" t="n">
-        <v>0</v>
+        <v>0.002772</v>
       </c>
       <c r="R12" s="12" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="S12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T12" s="14" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="U12" s="15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V12" s="12" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="W12" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X12" s="9" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="Y12" s="12" t="n">
-        <v>0</v>
+        <v>33.11</v>
       </c>
       <c r="Z12" s="12" t="n">
-        <v>909.41</v>
+        <v>509.4</v>
       </c>
       <c r="AA12" s="12" t="n">
-        <v>63.66</v>
+        <v>20.38</v>
       </c>
       <c r="AB12" s="12" t="n">
         <v>0</v>
@@ -18658,13 +18616,13 @@
         <v>0</v>
       </c>
       <c r="AH12" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AJ12" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AK12" s="12" t="n">
         <v>0</v>
@@ -18673,126 +18631,126 @@
         <v>0</v>
       </c>
       <c r="AM12" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AN12" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AO12" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AP12" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AQ12" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AR12" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AS12" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AT12" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AU12" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AV12" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AW12" s="14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AX12" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AY12" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AZ12" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BA12" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BB12" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BC12" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BD12" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BE12" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BF12" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BG12" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BH12" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BI12" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BJ12" s="9" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="BK12" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BL12" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BM12" s="16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="n">
-        <v>304503</v>
+        <v>305206</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
       <c r="F13" s="9" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="G13" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="K13" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>11314.6</v>
+        <v>2577.37</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O13" s="12" t="n">
-        <v>11314.6</v>
+        <v>2348.4</v>
       </c>
       <c r="P13" s="12" t="n">
         <v>0</v>
@@ -18801,34 +18759,34 @@
         <v>0</v>
       </c>
       <c r="R13" s="12" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="S13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T13" s="14" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="U13" s="15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V13" s="12" t="n">
-        <v>42</v>
+        <v>31.19</v>
       </c>
       <c r="W13" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X13" s="9" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="Y13" s="12" t="n">
-        <v>0</v>
+        <v>228.97</v>
       </c>
       <c r="Z13" s="12" t="n">
-        <v>11314.6</v>
+        <v>2348.4</v>
       </c>
       <c r="AA13" s="12" t="n">
-        <v>792.02</v>
+        <v>164.38</v>
       </c>
       <c r="AB13" s="12" t="n">
         <v>0</v>
@@ -18849,13 +18807,13 @@
         <v>0</v>
       </c>
       <c r="AH13" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AJ13" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AK13" s="12" t="n">
         <v>0</v>
@@ -18864,162 +18822,162 @@
         <v>0</v>
       </c>
       <c r="AM13" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AN13" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AO13" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AP13" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AQ13" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AR13" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AS13" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AT13" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AU13" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AV13" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AW13" s="14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AX13" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AY13" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AZ13" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BA13" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BB13" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BC13" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BD13" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BE13" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BF13" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BG13" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BH13" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BI13" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BJ13" s="9" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="BK13" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BL13" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BM13" s="16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="n">
-        <v>304561</v>
+        <v>305238</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
       <c r="F14" s="9" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>66</v>
+        <v>128</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>67</v>
+        <v>122</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>68</v>
+        <v>123</v>
       </c>
       <c r="K14" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>1446.24</v>
+        <v>2751</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O14" s="12" t="n">
-        <v>1446.24</v>
+        <v>2751</v>
       </c>
       <c r="P14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q14" s="13" t="n">
-        <v>0.00268</v>
+        <v>0.011956</v>
       </c>
       <c r="R14" s="12" t="n">
-        <v>8</v>
+        <v>5.06</v>
       </c>
       <c r="S14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T14" s="14" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="U14" s="15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V14" s="12" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="W14" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X14" s="9" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="Y14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z14" s="12" t="n">
-        <v>1446.24</v>
+        <v>2751</v>
       </c>
       <c r="AA14" s="12" t="n">
-        <v>101.24</v>
+        <v>192.57</v>
       </c>
       <c r="AB14" s="12" t="n">
         <v>0</v>
@@ -19040,13 +18998,13 @@
         <v>0</v>
       </c>
       <c r="AH14" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AJ14" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AK14" s="12" t="n">
         <v>0</v>
@@ -19055,117 +19013,117 @@
         <v>0</v>
       </c>
       <c r="AM14" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AN14" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AO14" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AP14" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AQ14" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AR14" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AS14" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AT14" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AU14" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AV14" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AW14" s="14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AX14" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AY14" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AZ14" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BA14" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BB14" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BC14" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BD14" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BE14" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BF14" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BG14" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BH14" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BI14" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BJ14" s="9" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="BK14" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BL14" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BM14" s="16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="n">
-        <v>304624</v>
+        <v>305250</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>83</v>
+        <v>126</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
       <c r="F15" s="9" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>85</v>
+        <v>128</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>108</v>
+        <v>132</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="K15" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>803.16</v>
+        <v>2088.57</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>0</v>
@@ -19174,43 +19132,43 @@
         <v>1</v>
       </c>
       <c r="O15" s="12" t="n">
-        <v>803.16</v>
+        <v>2088.57</v>
       </c>
       <c r="P15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q15" s="13" t="n">
-        <v>0.00374</v>
+        <v>0.005874</v>
       </c>
       <c r="R15" s="12" t="n">
-        <v>0.8</v>
+        <v>1.45</v>
       </c>
       <c r="S15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T15" s="14" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="U15" s="15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V15" s="12" t="n">
         <v>28</v>
       </c>
       <c r="W15" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X15" s="9" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="Y15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z15" s="12" t="n">
-        <v>803.16</v>
+        <v>2088.57</v>
       </c>
       <c r="AA15" s="12" t="n">
-        <v>56.22</v>
+        <v>146.2</v>
       </c>
       <c r="AB15" s="12" t="n">
         <v>0</v>
@@ -19231,13 +19189,13 @@
         <v>0</v>
       </c>
       <c r="AH15" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AJ15" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AK15" s="12" t="n">
         <v>0</v>
@@ -19246,117 +19204,117 @@
         <v>0</v>
       </c>
       <c r="AM15" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AN15" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AO15" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AP15" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AQ15" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AR15" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AS15" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AT15" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AU15" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AV15" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AW15" s="14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AX15" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AY15" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AZ15" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BA15" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BB15" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BC15" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BD15" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BE15" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BF15" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BG15" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BH15" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BI15" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BJ15" s="9" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="BK15" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BL15" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BM15" s="16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="n">
-        <v>304629</v>
+        <v>305251</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>83</v>
+        <v>126</v>
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
       <c r="F16" s="9" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>85</v>
+        <v>128</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="K16" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>482.14</v>
+        <v>1411.71</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>0</v>
@@ -19365,43 +19323,43 @@
         <v>1</v>
       </c>
       <c r="O16" s="12" t="n">
-        <v>482.14</v>
+        <v>1411.71</v>
       </c>
       <c r="P16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q16" s="13" t="n">
-        <v>0.007527</v>
+        <v>0.000432</v>
       </c>
       <c r="R16" s="12" t="n">
-        <v>1.57</v>
+        <v>0.74</v>
       </c>
       <c r="S16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T16" s="14" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="U16" s="15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V16" s="12" t="n">
         <v>28</v>
       </c>
       <c r="W16" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X16" s="9" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="Y16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z16" s="12" t="n">
-        <v>482.14</v>
+        <v>1411.71</v>
       </c>
       <c r="AA16" s="12" t="n">
-        <v>33.75</v>
+        <v>98.82</v>
       </c>
       <c r="AB16" s="12" t="n">
         <v>0</v>
@@ -19422,13 +19380,13 @@
         <v>0</v>
       </c>
       <c r="AH16" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AJ16" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AK16" s="12" t="n">
         <v>0</v>
@@ -19437,117 +19395,117 @@
         <v>0</v>
       </c>
       <c r="AM16" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AN16" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AO16" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AP16" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AQ16" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AR16" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AS16" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AT16" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AU16" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AV16" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AW16" s="14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AX16" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AY16" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AZ16" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BA16" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BB16" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BC16" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BD16" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BE16" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BF16" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BG16" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BH16" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BI16" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BJ16" s="9" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="BK16" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BL16" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BM16" s="16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="n">
-        <v>304690</v>
+        <v>305258</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>83</v>
+        <v>126</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
       <c r="F17" s="9" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>85</v>
+        <v>128</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>90</v>
+        <v>132</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>77</v>
+        <v>133</v>
       </c>
       <c r="K17" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>397.77</v>
+        <v>5612.24</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>0</v>
@@ -19556,43 +19514,43 @@
         <v>1</v>
       </c>
       <c r="O17" s="12" t="n">
-        <v>397.77</v>
+        <v>5612.24</v>
       </c>
       <c r="P17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q17" s="13" t="n">
-        <v>0.000557</v>
+        <v>0.034</v>
       </c>
       <c r="R17" s="12" t="n">
-        <v>0.4</v>
+        <v>10.12</v>
       </c>
       <c r="S17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T17" s="14" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="U17" s="15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V17" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W17" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X17" s="9" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="Y17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z17" s="12" t="n">
-        <v>397.77</v>
+        <v>5612.24</v>
       </c>
       <c r="AA17" s="12" t="n">
-        <v>27.84</v>
+        <v>392.86</v>
       </c>
       <c r="AB17" s="12" t="n">
         <v>0</v>
@@ -19613,13 +19571,13 @@
         <v>0</v>
       </c>
       <c r="AH17" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AJ17" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AK17" s="12" t="n">
         <v>0</v>
@@ -19628,117 +19586,117 @@
         <v>0</v>
       </c>
       <c r="AM17" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AN17" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AO17" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AP17" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AQ17" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AR17" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AS17" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AT17" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AU17" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AV17" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AW17" s="14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AX17" s="10" t="s">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="AY17" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AZ17" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BA17" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BB17" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BC17" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BD17" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BE17" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BF17" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BG17" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BH17" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BI17" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BJ17" s="9" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="BK17" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BL17" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BM17" s="16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="n">
-        <v>304691</v>
+        <v>305419</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
       <c r="F18" s="9" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K18" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>165.44</v>
+        <v>392.71</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>0</v>
@@ -19747,43 +19705,43 @@
         <v>1</v>
       </c>
       <c r="O18" s="12" t="n">
-        <v>165.44</v>
+        <v>368.74</v>
       </c>
       <c r="P18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q18" s="13" t="n">
-        <v>0.00729</v>
+        <v>0.006789</v>
       </c>
       <c r="R18" s="12" t="n">
-        <v>1.03</v>
+        <v>3.81</v>
       </c>
       <c r="S18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T18" s="14" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="U18" s="15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="W18" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X18" s="9" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="Y18" s="12" t="n">
-        <v>0</v>
+        <v>23.97</v>
       </c>
       <c r="Z18" s="12" t="n">
-        <v>165.44</v>
+        <v>368.74</v>
       </c>
       <c r="AA18" s="12" t="n">
-        <v>11.58</v>
+        <v>14.75</v>
       </c>
       <c r="AB18" s="12" t="n">
         <v>0</v>
@@ -19804,13 +19762,13 @@
         <v>0</v>
       </c>
       <c r="AH18" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AJ18" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AK18" s="12" t="n">
         <v>0</v>
@@ -19819,117 +19777,117 @@
         <v>0</v>
       </c>
       <c r="AM18" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AN18" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AO18" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AP18" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AQ18" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AR18" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AS18" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AT18" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AU18" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AV18" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AW18" s="14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AX18" s="10" t="s">
-        <v>105</v>
+        <v>145</v>
       </c>
       <c r="AY18" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AZ18" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BA18" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BB18" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BC18" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BD18" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BE18" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BF18" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BG18" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BH18" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BI18" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BJ18" s="9" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="BK18" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BL18" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BM18" s="16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="n">
-        <v>304792</v>
+        <v>305443</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
       <c r="F19" s="9" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="G19" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="K19" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>698.84</v>
+        <v>163.48</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>0</v>
@@ -19938,43 +19896,43 @@
         <v>1</v>
       </c>
       <c r="O19" s="12" t="n">
-        <v>698.84</v>
+        <v>153.5</v>
       </c>
       <c r="P19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q19" s="13" t="n">
-        <v>0.026256</v>
+        <v>0.003456</v>
       </c>
       <c r="R19" s="12" t="n">
-        <v>5.8</v>
+        <v>0.8</v>
       </c>
       <c r="S19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T19" s="14" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="U19" s="15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V19" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W19" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X19" s="9" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="Y19" s="12" t="n">
-        <v>0</v>
+        <v>9.98</v>
       </c>
       <c r="Z19" s="12" t="n">
-        <v>698.84</v>
+        <v>153.5</v>
       </c>
       <c r="AA19" s="12" t="n">
-        <v>48.92</v>
+        <v>6.14</v>
       </c>
       <c r="AB19" s="12" t="n">
         <v>0</v>
@@ -19995,13 +19953,13 @@
         <v>0</v>
       </c>
       <c r="AH19" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AJ19" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AK19" s="12" t="n">
         <v>0</v>
@@ -20010,353 +19968,353 @@
         <v>0</v>
       </c>
       <c r="AM19" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AN19" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AO19" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AP19" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AQ19" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AR19" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AS19" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AT19" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AU19" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AV19" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AW19" s="14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AX19" s="10" t="s">
-        <v>76</v>
+        <v>145</v>
       </c>
       <c r="AY19" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AZ19" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BA19" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BB19" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BC19" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BD19" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BE19" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BF19" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BG19" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BH19" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BI19" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BJ19" s="9" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="BK19" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BL19" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BM19" s="16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="n">
-        <v>304801</v>
+        <v>305457</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>143</v>
+        <v>114</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
       <c r="F20" s="9" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="G20" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="K20" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>1839.76</v>
+        <v>4770.41</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="O20" s="12" t="n">
-        <v>1680.76</v>
+        <v>4588.46</v>
       </c>
       <c r="P20" s="12" t="n">
-        <v>159</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="13" t="n">
-        <v>0</v>
+        <v>0.231499</v>
       </c>
       <c r="R20" s="12" t="n">
-        <v>0</v>
+        <v>35.08</v>
       </c>
       <c r="S20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T20" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="U20" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X20" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="Y20" s="12" t="n">
+        <v>181.95</v>
+      </c>
+      <c r="Z20" s="12" t="n">
+        <v>4588.46</v>
+      </c>
+      <c r="AA20" s="12" t="n">
+        <v>183.54</v>
+      </c>
+      <c r="AB20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN20" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO20" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP20" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ20" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR20" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS20" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT20" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU20" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV20" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW20" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX20" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="U20" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="V20" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="W20" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="X20" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="Y20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="12" t="n">
-        <v>1839.76</v>
-      </c>
-      <c r="AA20" s="12" t="n">
-        <v>73.59</v>
-      </c>
-      <c r="AB20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH20" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AI20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ20" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AK20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM20" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AN20" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AO20" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AP20" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AQ20" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AR20" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AS20" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AT20" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AU20" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AV20" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW20" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AX20" s="10" t="s">
-        <v>76</v>
-      </c>
       <c r="AY20" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AZ20" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BA20" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BB20" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BC20" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BD20" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BE20" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BF20" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BG20" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BH20" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BI20" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BJ20" s="9" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="BK20" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BL20" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BM20" s="16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="n">
-        <v>304810</v>
+        <v>305470</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
       <c r="F21" s="9" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>67</v>
+        <v>151</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K21" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>8720.4</v>
+        <v>314.65</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O21" s="12" t="n">
-        <v>8720.4</v>
+        <v>295.45</v>
       </c>
       <c r="P21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q21" s="13" t="n">
-        <v>0.136536</v>
+        <v>0.016472</v>
       </c>
       <c r="R21" s="12" t="n">
-        <v>24</v>
+        <v>1.6</v>
       </c>
       <c r="S21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T21" s="14" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="U21" s="15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="W21" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X21" s="9" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="Y21" s="12" t="n">
-        <v>0</v>
+        <v>19.2</v>
       </c>
       <c r="Z21" s="12" t="n">
-        <v>8720.4</v>
+        <v>295.45</v>
       </c>
       <c r="AA21" s="12" t="n">
-        <v>610.43</v>
+        <v>11.81</v>
       </c>
       <c r="AB21" s="12" t="n">
         <v>0</v>
@@ -20377,13 +20335,13 @@
         <v>0</v>
       </c>
       <c r="AH21" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AJ21" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AK21" s="12" t="n">
         <v>0</v>
@@ -20392,162 +20350,162 @@
         <v>0</v>
       </c>
       <c r="AM21" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AN21" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AO21" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AP21" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AQ21" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AR21" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AS21" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AT21" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AU21" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AV21" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AW21" s="14" t="s">
-        <v>149</v>
+        <v>76</v>
       </c>
       <c r="AX21" s="10" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="AY21" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AZ21" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BA21" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BB21" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BC21" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BD21" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BE21" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BF21" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BG21" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BH21" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BI21" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BJ21" s="9" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="BK21" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BL21" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BM21" s="16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="n">
-        <v>304880</v>
+        <v>305480</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>152</v>
+        <v>114</v>
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
       <c r="F22" s="9" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G22" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>108</v>
+        <v>151</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>155</v>
+        <v>78</v>
       </c>
       <c r="K22" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>25242</v>
+        <v>2373.3</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>5811.05</v>
+        <v>0</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="O22" s="12" t="n">
-        <v>28810.6</v>
+        <v>2228.46</v>
       </c>
       <c r="P22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q22" s="13" t="n">
-        <v>0</v>
+        <v>0.017186</v>
       </c>
       <c r="R22" s="12" t="n">
-        <v>6</v>
+        <v>12.33</v>
       </c>
       <c r="S22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T22" s="14" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="U22" s="15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V22" s="12" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="W22" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X22" s="9" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="Y22" s="12" t="n">
-        <v>2242.45</v>
+        <v>144.84</v>
       </c>
       <c r="Z22" s="12" t="n">
-        <v>22999.55</v>
+        <v>2228.46</v>
       </c>
       <c r="AA22" s="12" t="n">
-        <v>919.96</v>
+        <v>89.14</v>
       </c>
       <c r="AB22" s="12" t="n">
         <v>0</v>
@@ -20568,13 +20526,13 @@
         <v>0</v>
       </c>
       <c r="AH22" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AJ22" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AK22" s="12" t="n">
         <v>0</v>
@@ -20583,162 +20541,162 @@
         <v>0</v>
       </c>
       <c r="AM22" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AN22" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AO22" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AP22" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AQ22" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AR22" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AS22" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AT22" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AU22" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AV22" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AW22" s="14" t="s">
-        <v>149</v>
+        <v>76</v>
       </c>
       <c r="AX22" s="10" t="s">
-        <v>76</v>
+        <v>145</v>
       </c>
       <c r="AY22" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AZ22" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BA22" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BB22" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BC22" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BD22" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BE22" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BF22" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BG22" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BH22" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BI22" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BJ22" s="9" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="BK22" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BL22" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BM22" s="16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="n">
-        <v>304916</v>
+        <v>305539</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>158</v>
+        <v>126</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>160</v>
+        <v>128</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K23" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>2899.92</v>
+        <v>1568.57</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O23" s="12" t="n">
-        <v>2642.3</v>
+        <v>1568.57</v>
       </c>
       <c r="P23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q23" s="13" t="n">
-        <v>0</v>
+        <v>0.000432</v>
       </c>
       <c r="R23" s="12" t="n">
-        <v>0</v>
+        <v>0.74</v>
       </c>
       <c r="S23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T23" s="14" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="U23" s="15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V23" s="12" t="n">
         <v>28</v>
       </c>
       <c r="W23" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X23" s="9" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="Y23" s="12" t="n">
-        <v>257.62</v>
+        <v>0</v>
       </c>
       <c r="Z23" s="12" t="n">
-        <v>2642.3</v>
+        <v>1568.57</v>
       </c>
       <c r="AA23" s="12" t="n">
-        <v>105.7</v>
+        <v>109.8</v>
       </c>
       <c r="AB23" s="12" t="n">
         <v>0</v>
@@ -20759,13 +20717,13 @@
         <v>0</v>
       </c>
       <c r="AH23" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AJ23" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AK23" s="12" t="n">
         <v>0</v>
@@ -20774,93 +20732,93 @@
         <v>0</v>
       </c>
       <c r="AM23" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AN23" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AO23" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AP23" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AQ23" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AR23" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AS23" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AT23" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AU23" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AV23" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AW23" s="14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AX23" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AY23" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AZ23" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BA23" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BB23" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BC23" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BD23" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BE23" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BF23" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BG23" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BH23" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BI23" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BJ23" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="BK23" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BL23" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BM23" s="16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="n">
-        <v>304921</v>
+        <v>305553</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>164</v>
+        <v>126</v>
       </c>
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
@@ -20869,40 +20827,40 @@
         <v>165</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>66</v>
+        <v>128</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="J24" s="9" t="s">
         <v>166</v>
       </c>
       <c r="K24" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>3594.31</v>
+        <v>3135.16</v>
       </c>
       <c r="M24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O24" s="12" t="n">
-        <v>3275</v>
+        <v>3135.16</v>
       </c>
       <c r="P24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q24" s="13" t="n">
-        <v>0.02415</v>
+        <v>0.000864</v>
       </c>
       <c r="R24" s="12" t="n">
-        <v>2</v>
+        <v>1.48</v>
       </c>
       <c r="S24" s="12" t="n">
         <v>0</v>
@@ -20911,25 +20869,25 @@
         <v>167</v>
       </c>
       <c r="U24" s="15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V24" s="12" t="n">
-        <v>35.67</v>
+        <v>28</v>
       </c>
       <c r="W24" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X24" s="9" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="Y24" s="12" t="n">
-        <v>319.31</v>
+        <v>0</v>
       </c>
       <c r="Z24" s="12" t="n">
-        <v>3275</v>
+        <v>3135.16</v>
       </c>
       <c r="AA24" s="12" t="n">
-        <v>229.25</v>
+        <v>219.46</v>
       </c>
       <c r="AB24" s="12" t="n">
         <v>0</v>
@@ -20950,13 +20908,13 @@
         <v>0</v>
       </c>
       <c r="AH24" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AJ24" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AK24" s="12" t="n">
         <v>0</v>
@@ -20965,93 +20923,93 @@
         <v>0</v>
       </c>
       <c r="AM24" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AN24" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AO24" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AP24" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AQ24" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AR24" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AS24" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AT24" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AU24" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AV24" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AW24" s="14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AX24" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AY24" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AZ24" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BA24" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BB24" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BC24" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BD24" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BE24" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BF24" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BG24" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BH24" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BI24" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BJ24" s="9" t="s">
         <v>168</v>
       </c>
       <c r="BK24" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BL24" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BM24" s="16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="n">
-        <v>304929</v>
+        <v>305554</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>83</v>
+        <v>126</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
@@ -21060,22 +21018,22 @@
         <v>169</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>85</v>
+        <v>128</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>140</v>
+        <v>166</v>
       </c>
       <c r="K25" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>2910.76</v>
+        <v>3258.14</v>
       </c>
       <c r="M25" s="12" t="n">
         <v>0</v>
@@ -21084,7 +21042,7 @@
         <v>1</v>
       </c>
       <c r="O25" s="12" t="n">
-        <v>2910.76</v>
+        <v>3258.14</v>
       </c>
       <c r="P25" s="12" t="n">
         <v>0</v>
@@ -21102,25 +21060,25 @@
         <v>170</v>
       </c>
       <c r="U25" s="15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V25" s="12" t="n">
         <v>28</v>
       </c>
       <c r="W25" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X25" s="9" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="Y25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z25" s="12" t="n">
-        <v>2910.76</v>
+        <v>3258.14</v>
       </c>
       <c r="AA25" s="12" t="n">
-        <v>203.75</v>
+        <v>228.07</v>
       </c>
       <c r="AB25" s="12" t="n">
         <v>0</v>
@@ -21141,13 +21099,13 @@
         <v>0</v>
       </c>
       <c r="AH25" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AJ25" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AK25" s="12" t="n">
         <v>0</v>
@@ -21156,117 +21114,117 @@
         <v>0</v>
       </c>
       <c r="AM25" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AN25" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AO25" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AP25" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AQ25" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AR25" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AS25" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AT25" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AU25" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AV25" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AW25" s="14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AX25" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AY25" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AZ25" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BA25" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BB25" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BC25" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BD25" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BE25" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BF25" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BG25" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BH25" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BI25" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BJ25" s="9" t="s">
         <v>171</v>
       </c>
       <c r="BK25" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BL25" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BM25" s="16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="n">
-        <v>304934</v>
+        <v>305556</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>172</v>
+        <v>126</v>
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>174</v>
+        <v>128</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="K26" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>171.56</v>
+        <v>5879.02</v>
       </c>
       <c r="M26" s="12" t="n">
         <v>0</v>
@@ -21275,43 +21233,43 @@
         <v>1</v>
       </c>
       <c r="O26" s="12" t="n">
-        <v>156.32</v>
+        <v>5879.02</v>
       </c>
       <c r="P26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q26" s="13" t="n">
-        <v>0</v>
+        <v>0.467698</v>
       </c>
       <c r="R26" s="12" t="n">
-        <v>0</v>
+        <v>31.5</v>
       </c>
       <c r="S26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T26" s="14" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="U26" s="15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V26" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W26" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X26" s="9" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="Y26" s="12" t="n">
-        <v>15.24</v>
+        <v>0</v>
       </c>
       <c r="Z26" s="12" t="n">
-        <v>156.32</v>
+        <v>5879.02</v>
       </c>
       <c r="AA26" s="12" t="n">
-        <v>10.94</v>
+        <v>411.53</v>
       </c>
       <c r="AB26" s="12" t="n">
         <v>0</v>
@@ -21332,13 +21290,13 @@
         <v>0</v>
       </c>
       <c r="AH26" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AJ26" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AK26" s="12" t="n">
         <v>0</v>
@@ -21347,135 +21305,135 @@
         <v>0</v>
       </c>
       <c r="AM26" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AN26" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AO26" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AP26" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AQ26" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AR26" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AS26" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AT26" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AU26" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AV26" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AW26" s="14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AX26" s="10" t="s">
-        <v>150</v>
+        <v>77</v>
       </c>
       <c r="AY26" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AZ26" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BA26" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BB26" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BC26" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BD26" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BE26" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BF26" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BG26" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BH26" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BI26" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BJ26" s="9" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="BK26" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BL26" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BM26" s="16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="n">
-        <v>304937</v>
+        <v>305560</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>172</v>
+        <v>126</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="G27" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="I27" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="J27" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="G27" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="H27" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="I27" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="J27" s="9" t="s">
-        <v>140</v>
-      </c>
       <c r="K27" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>2085.14</v>
+        <v>3121.47</v>
       </c>
       <c r="M27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O27" s="12" t="n">
-        <v>1899.9</v>
+        <v>3121.47</v>
       </c>
       <c r="P27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q27" s="13" t="n">
-        <v>0</v>
+        <v>0.031059</v>
       </c>
       <c r="R27" s="12" t="n">
-        <v>4.3</v>
+        <v>5.54</v>
       </c>
       <c r="S27" s="12" t="n">
         <v>0</v>
@@ -21484,25 +21442,25 @@
         <v>178</v>
       </c>
       <c r="U27" s="15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V27" s="12" t="n">
         <v>28</v>
       </c>
       <c r="W27" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X27" s="9" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="Y27" s="12" t="n">
-        <v>185.24</v>
+        <v>0</v>
       </c>
       <c r="Z27" s="12" t="n">
-        <v>1899.9</v>
+        <v>3121.47</v>
       </c>
       <c r="AA27" s="12" t="n">
-        <v>132.99</v>
+        <v>218.5</v>
       </c>
       <c r="AB27" s="12" t="n">
         <v>0</v>
@@ -21523,13 +21481,13 @@
         <v>0</v>
       </c>
       <c r="AH27" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AJ27" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AK27" s="12" t="n">
         <v>0</v>
@@ -21538,93 +21496,93 @@
         <v>0</v>
       </c>
       <c r="AM27" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AN27" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AO27" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AP27" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AQ27" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AR27" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AS27" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AT27" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AU27" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AV27" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AW27" s="14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AX27" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AY27" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AZ27" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BA27" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BB27" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BC27" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BD27" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BE27" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BF27" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BG27" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BH27" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BI27" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BJ27" s="9" t="s">
         <v>179</v>
       </c>
       <c r="BK27" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BL27" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BM27" s="16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="n">
-        <v>304943</v>
+        <v>305561</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>152</v>
+        <v>126</v>
       </c>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
@@ -21633,40 +21591,40 @@
         <v>180</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>66</v>
+        <v>128</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>108</v>
+        <v>176</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>77</v>
+        <v>177</v>
       </c>
       <c r="K28" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>1818.78</v>
+        <v>5331.26</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O28" s="12" t="n">
-        <v>1657.2</v>
+        <v>5005.88</v>
       </c>
       <c r="P28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q28" s="13" t="n">
-        <v>0</v>
+        <v>0.055816</v>
       </c>
       <c r="R28" s="12" t="n">
-        <v>0</v>
+        <v>7.12</v>
       </c>
       <c r="S28" s="12" t="n">
         <v>0</v>
@@ -21675,25 +21633,25 @@
         <v>181</v>
       </c>
       <c r="U28" s="15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V28" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W28" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X28" s="9" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="Y28" s="12" t="n">
-        <v>161.58</v>
+        <v>325.38</v>
       </c>
       <c r="Z28" s="12" t="n">
-        <v>1657.2</v>
+        <v>5005.88</v>
       </c>
       <c r="AA28" s="12" t="n">
-        <v>66.28</v>
+        <v>350.41</v>
       </c>
       <c r="AB28" s="12" t="n">
         <v>0</v>
@@ -21714,13 +21672,13 @@
         <v>0</v>
       </c>
       <c r="AH28" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AJ28" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AK28" s="12" t="n">
         <v>0</v>
@@ -21729,982 +21687,616 @@
         <v>0</v>
       </c>
       <c r="AM28" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AN28" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AO28" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AP28" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AQ28" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AR28" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AS28" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AT28" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AU28" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AV28" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AW28" s="14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AX28" s="10" t="s">
-        <v>150</v>
+        <v>77</v>
       </c>
       <c r="AY28" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AZ28" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BA28" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BB28" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BC28" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BD28" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BE28" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BF28" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BG28" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BH28" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BI28" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BJ28" s="9" t="s">
         <v>182</v>
       </c>
       <c r="BK28" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BL28" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BM28" s="16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="8" t="n">
-        <v>304974</v>
-      </c>
-      <c r="B29" s="9" t="s">
+      <c r="A29" s="4"/>
+    </row>
+    <row r="30" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="17" t="s">
         <v>183</v>
       </c>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9" t="s">
+      <c r="B30" s="17"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="17"/>
+      <c r="F30" s="17"/>
+      <c r="G30" s="17"/>
+      <c r="H30" s="17"/>
+      <c r="I30" s="17"/>
+      <c r="J30" s="17"/>
+      <c r="K30" s="17"/>
+      <c r="L30" s="17"/>
+      <c r="M30" s="17"/>
+      <c r="N30" s="17"/>
+      <c r="O30" s="17"/>
+      <c r="P30" s="17"/>
+      <c r="Q30" s="17"/>
+      <c r="R30" s="17"/>
+      <c r="S30" s="17"/>
+      <c r="T30" s="17"/>
+      <c r="U30" s="17"/>
+      <c r="V30" s="17"/>
+    </row>
+    <row r="31" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="18" t="s">
         <v>184</v>
       </c>
-      <c r="G29" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="H29" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="I29" s="9" t="s">
+      <c r="B31" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" s="18" t="s">
         <v>185</v>
       </c>
-      <c r="J29" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="K29" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="L29" s="12" t="n">
-        <v>5418.46</v>
-      </c>
-      <c r="M29" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O29" s="12" t="n">
-        <v>5153.46</v>
-      </c>
-      <c r="P29" s="12" t="n">
-        <v>265</v>
-      </c>
-      <c r="Q29" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" s="14" t="s">
+      <c r="E31" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F31" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="G31" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H31" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="I31" s="18" t="s">
         <v>186</v>
       </c>
-      <c r="U29" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="V29" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="W29" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="X29" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="Y29" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z29" s="12" t="n">
-        <v>5418.46</v>
-      </c>
-      <c r="AA29" s="12" t="n">
-        <v>379.29</v>
-      </c>
-      <c r="AB29" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC29" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD29" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE29" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF29" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG29" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH29" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AI29" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ29" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AK29" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL29" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM29" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AN29" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AO29" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AP29" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AQ29" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AR29" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AS29" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AT29" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AU29" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AV29" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW29" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AX29" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="AY29" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AZ29" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BA29" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BB29" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BC29" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BD29" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BE29" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BF29" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="BG29" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="BH29" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BI29" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="BJ29" s="9" t="s">
+      <c r="J31" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="K31" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="L31" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="M31" s="18" t="s">
         <v>187</v>
       </c>
-      <c r="BK29" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="BL29" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="BM29" s="16" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="8" t="n">
-        <v>304983</v>
-      </c>
-      <c r="B30" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9" t="s">
+      <c r="N31" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="O31" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="P31" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q31" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="R31" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="S31" s="18" t="s">
         <v>188</v>
       </c>
-      <c r="G30" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="H30" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="I30" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="J30" s="9" t="s">
+      <c r="T31" s="18" t="s">
         <v>189</v>
       </c>
-      <c r="K30" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="L30" s="12" t="n">
-        <v>5010.42</v>
-      </c>
-      <c r="M30" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O30" s="12" t="n">
-        <v>5010.42</v>
-      </c>
-      <c r="P30" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" s="13" t="n">
-        <v>0.26199</v>
-      </c>
-      <c r="R30" s="12" t="n">
-        <v>109.24</v>
-      </c>
-      <c r="S30" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="U30" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="V30" s="12" t="n">
-        <v>56</v>
-      </c>
-      <c r="W30" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="X30" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="Y30" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z30" s="12" t="n">
-        <v>5010.42</v>
-      </c>
-      <c r="AA30" s="12" t="n">
-        <v>350.73</v>
-      </c>
-      <c r="AB30" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC30" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD30" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE30" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF30" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG30" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH30" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AI30" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ30" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AK30" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL30" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM30" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AN30" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AO30" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AP30" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AQ30" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AR30" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AS30" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AT30" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AU30" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AV30" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW30" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AX30" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="AY30" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AZ30" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BA30" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BB30" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BC30" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BD30" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BE30" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BF30" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="BG30" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="BH30" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BI30" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="BJ30" s="9" t="s">
-        <v>191</v>
-      </c>
-      <c r="BK30" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="BL30" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="BM30" s="16" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="8" t="n">
-        <v>304992</v>
-      </c>
-      <c r="B31" s="9" t="s">
-        <v>192</v>
-      </c>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="G31" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="H31" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="I31" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="J31" s="9" t="s">
-        <v>194</v>
-      </c>
-      <c r="K31" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="L31" s="12" t="n">
-        <v>3047.98</v>
-      </c>
-      <c r="M31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="O31" s="12" t="n">
-        <v>3047.98</v>
-      </c>
-      <c r="P31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="S31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" s="14" t="s">
-        <v>195</v>
-      </c>
-      <c r="U31" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="V31" s="12" t="n">
-        <v>45</v>
-      </c>
-      <c r="W31" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="X31" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="Y31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z31" s="12" t="n">
-        <v>3047.98</v>
-      </c>
-      <c r="AA31" s="12" t="n">
-        <v>92.05</v>
-      </c>
-      <c r="AB31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH31" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AI31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ31" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AK31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM31" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AN31" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AO31" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AP31" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AQ31" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AR31" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AS31" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AT31" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AU31" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AV31" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW31" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AX31" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="AY31" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AZ31" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BA31" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BB31" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BC31" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BD31" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BE31" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BF31" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="BG31" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="BH31" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BI31" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="BJ31" s="9" t="s">
-        <v>196</v>
-      </c>
-      <c r="BK31" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="BL31" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="BM31" s="16" t="s">
-        <v>79</v>
+      <c r="U31" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="V31" s="18" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="4"/>
+      <c r="A32" s="19" t="n">
+        <v>24</v>
+      </c>
+      <c r="B32" s="19" t="n">
+        <v>5811.05</v>
+      </c>
+      <c r="C32" s="19" t="n">
+        <v>424</v>
+      </c>
+      <c r="D32" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="19" t="n">
+        <v>3705.98</v>
+      </c>
+      <c r="F32" s="19" t="n">
+        <v>82718.44</v>
+      </c>
+      <c r="G32" s="19" t="n">
+        <v>4629.72</v>
+      </c>
+      <c r="H32" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="19" t="n">
+        <v>86424.42</v>
+      </c>
+      <c r="L32" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" s="20" t="n">
+        <v>0.911319</v>
+      </c>
+      <c r="S32" s="19" t="n">
+        <v>88105.49</v>
+      </c>
+      <c r="T32" s="19" t="n">
+        <v>86424.42</v>
+      </c>
+      <c r="U32" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="17" t="s">
-        <v>197</v>
-      </c>
-      <c r="B33" s="17"/>
-      <c r="C33" s="17"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="17"/>
-      <c r="G33" s="17"/>
-      <c r="H33" s="17"/>
-      <c r="I33" s="17"/>
-      <c r="J33" s="17"/>
-      <c r="K33" s="17"/>
-      <c r="L33" s="17"/>
-      <c r="M33" s="17"/>
-      <c r="N33" s="17"/>
-      <c r="O33" s="17"/>
-      <c r="P33" s="17"/>
-      <c r="Q33" s="17"/>
-      <c r="R33" s="17"/>
-      <c r="S33" s="17"/>
-      <c r="T33" s="17"/>
-      <c r="U33" s="17"/>
-      <c r="V33" s="17"/>
+      <c r="A33" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B33" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C33" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D33" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="E33" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="F33" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="G33" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="H33" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="I33" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="J33" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="K33" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="L33" s="18" t="s">
+        <v>191</v>
+      </c>
+      <c r="M33" s="18" t="s">
+        <v>192</v>
+      </c>
     </row>
-    <row r="34" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="18" t="s">
-        <v>198</v>
-      </c>
-      <c r="B34" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C34" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D34" s="18" t="s">
-        <v>199</v>
-      </c>
-      <c r="E34" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F34" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="G34" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="H34" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="I34" s="18" t="s">
-        <v>200</v>
-      </c>
-      <c r="J34" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="K34" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="L34" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="M34" s="18" t="s">
-        <v>201</v>
-      </c>
-      <c r="N34" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="O34" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="P34" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q34" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="R34" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="S34" s="18" t="s">
-        <v>202</v>
-      </c>
-      <c r="T34" s="18" t="s">
-        <v>203</v>
-      </c>
-      <c r="U34" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="V34" s="18" t="s">
-        <v>37</v>
+    <row r="34" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="19" t="n">
+        <v>131.77</v>
+      </c>
+      <c r="B34" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="19" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="E34" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="19" t="n">
-        <v>27</v>
-      </c>
-      <c r="B35" s="19" t="n">
-        <v>5811.05</v>
-      </c>
-      <c r="C35" s="19" t="n">
-        <v>424</v>
-      </c>
-      <c r="D35" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" s="19" t="n">
-        <v>3533.23</v>
-      </c>
-      <c r="F35" s="19" t="n">
-        <v>90821.3</v>
-      </c>
-      <c r="G35" s="19" t="n">
-        <v>5242.28</v>
-      </c>
-      <c r="H35" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" s="19" t="n">
-        <v>94354.53</v>
-      </c>
-      <c r="L35" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" s="20" t="n">
-        <v>0.718003</v>
-      </c>
-      <c r="S35" s="19" t="n">
-        <v>96208.35</v>
-      </c>
-      <c r="T35" s="19" t="n">
-        <v>94354.53</v>
-      </c>
-      <c r="U35" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" s="19" t="n">
-        <v>0</v>
-      </c>
+      <c r="A35" s="4"/>
     </row>
     <row r="36" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="B36" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C36" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="D36" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E36" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="F36" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="G36" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="H36" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="I36" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="J36" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="K36" s="18" t="s">
-        <v>204</v>
-      </c>
-      <c r="L36" s="18" t="s">
-        <v>205</v>
-      </c>
-      <c r="M36" s="18" t="s">
-        <v>206</v>
-      </c>
+      <c r="A36" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="B36" s="21"/>
+      <c r="C36" s="21"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="21"/>
+      <c r="F36" s="21"/>
+      <c r="G36" s="21"/>
+      <c r="H36" s="21"/>
+      <c r="I36" s="21"/>
+      <c r="J36" s="21"/>
+      <c r="K36" s="21"/>
+      <c r="L36" s="21"/>
+      <c r="M36" s="21"/>
+      <c r="N36" s="21"/>
+      <c r="O36" s="21"/>
+      <c r="P36" s="21"/>
+      <c r="Q36" s="21"/>
+      <c r="R36" s="21"/>
+      <c r="S36" s="21"/>
+      <c r="T36" s="21"/>
+      <c r="U36" s="21"/>
+      <c r="V36" s="21"/>
+      <c r="W36" s="21"/>
+      <c r="X36" s="21"/>
+      <c r="Y36" s="21"/>
+      <c r="Z36" s="21"/>
+      <c r="AA36" s="21"/>
+      <c r="AB36" s="21"/>
+      <c r="AC36" s="21"/>
+      <c r="AD36" s="21"/>
+      <c r="AE36" s="21"/>
+      <c r="AF36" s="21"/>
+      <c r="AG36" s="21"/>
+      <c r="AH36" s="21"/>
+      <c r="AI36" s="21"/>
+      <c r="AJ36" s="21"/>
+      <c r="AK36" s="21"/>
+      <c r="AL36" s="21"/>
+      <c r="AM36" s="21"/>
+      <c r="AN36" s="21"/>
+      <c r="AO36" s="21"/>
+      <c r="AP36" s="21"/>
+      <c r="AQ36" s="21"/>
+      <c r="AR36" s="21"/>
+      <c r="AS36" s="21"/>
+      <c r="AT36" s="21"/>
+      <c r="AU36" s="21"/>
+      <c r="AV36" s="21"/>
+      <c r="AW36" s="21"/>
+      <c r="AX36" s="21"/>
+      <c r="AY36" s="21"/>
+      <c r="AZ36" s="21"/>
+      <c r="BA36" s="21"/>
+      <c r="BB36" s="21"/>
+      <c r="BC36" s="21"/>
+      <c r="BD36" s="21"/>
+      <c r="BE36" s="21"/>
+      <c r="BF36" s="21"/>
+      <c r="BG36" s="21"/>
+      <c r="BH36" s="21"/>
+      <c r="BI36" s="21"/>
+      <c r="BJ36" s="21"/>
+      <c r="BK36" s="21"/>
+      <c r="BL36" s="21"/>
+      <c r="BM36" s="21"/>
     </row>
     <row r="37" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="19" t="n">
-        <v>215.37</v>
-      </c>
-      <c r="B37" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C37" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" s="19" t="n">
-        <v>54.84</v>
-      </c>
-      <c r="E37" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" s="19" t="n">
-        <v>0</v>
-      </c>
+      <c r="A37" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
+      <c r="K37" s="4"/>
+      <c r="L37" s="4"/>
+      <c r="M37" s="4"/>
+      <c r="N37" s="4"/>
+      <c r="O37" s="4"/>
+      <c r="P37" s="4"/>
+      <c r="Q37" s="4"/>
+      <c r="R37" s="4"/>
+      <c r="S37" s="4"/>
+      <c r="T37" s="4"/>
+      <c r="U37" s="4"/>
+      <c r="V37" s="4"/>
+      <c r="W37" s="4"/>
+      <c r="X37" s="4"/>
+      <c r="Y37" s="4"/>
+      <c r="Z37" s="4"/>
+      <c r="AA37" s="4"/>
+      <c r="AB37" s="4"/>
+      <c r="AC37" s="4"/>
+      <c r="AD37" s="4"/>
+      <c r="AE37" s="4"/>
+      <c r="AF37" s="4"/>
+      <c r="AG37" s="4"/>
+      <c r="AH37" s="4"/>
+      <c r="AI37" s="4"/>
+      <c r="AJ37" s="4"/>
+      <c r="AK37" s="4"/>
+      <c r="AL37" s="4"/>
+      <c r="AM37" s="4"/>
+      <c r="AN37" s="4"/>
+      <c r="AO37" s="4"/>
+      <c r="AP37" s="4"/>
+      <c r="AQ37" s="4"/>
+      <c r="AR37" s="4"/>
+      <c r="AS37" s="4"/>
+      <c r="AT37" s="4"/>
+      <c r="AU37" s="4"/>
+      <c r="AV37" s="4"/>
+      <c r="AW37" s="4"/>
+      <c r="AX37" s="4"/>
+      <c r="AY37" s="4"/>
+      <c r="AZ37" s="4"/>
+      <c r="BA37" s="4"/>
+      <c r="BB37" s="4"/>
+      <c r="BC37" s="4"/>
+      <c r="BD37" s="4"/>
+      <c r="BE37" s="4"/>
+      <c r="BF37" s="4"/>
+      <c r="BG37" s="4"/>
+      <c r="BH37" s="4"/>
+      <c r="BI37" s="4"/>
+      <c r="BJ37" s="4"/>
+      <c r="BK37" s="4"/>
+      <c r="BL37" s="4"/>
+      <c r="BM37" s="4"/>
     </row>
     <row r="38" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="4"/>
+      <c r="A38" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="K38" s="4"/>
+      <c r="L38" s="4"/>
+      <c r="M38" s="4"/>
+      <c r="N38" s="4"/>
+      <c r="O38" s="4"/>
+      <c r="P38" s="4"/>
+      <c r="Q38" s="4"/>
+      <c r="R38" s="4"/>
+      <c r="S38" s="4"/>
+      <c r="T38" s="4"/>
+      <c r="U38" s="4"/>
+      <c r="V38" s="4"/>
+      <c r="W38" s="4"/>
+      <c r="X38" s="4"/>
+      <c r="Y38" s="4"/>
+      <c r="Z38" s="4"/>
+      <c r="AA38" s="4"/>
+      <c r="AB38" s="4"/>
+      <c r="AC38" s="4"/>
+      <c r="AD38" s="4"/>
+      <c r="AE38" s="4"/>
+      <c r="AF38" s="4"/>
+      <c r="AG38" s="4"/>
+      <c r="AH38" s="4"/>
+      <c r="AI38" s="4"/>
+      <c r="AJ38" s="4"/>
+      <c r="AK38" s="4"/>
+      <c r="AL38" s="4"/>
+      <c r="AM38" s="4"/>
+      <c r="AN38" s="4"/>
+      <c r="AO38" s="4"/>
+      <c r="AP38" s="4"/>
+      <c r="AQ38" s="4"/>
+      <c r="AR38" s="4"/>
+      <c r="AS38" s="4"/>
+      <c r="AT38" s="4"/>
+      <c r="AU38" s="4"/>
+      <c r="AV38" s="4"/>
+      <c r="AW38" s="4"/>
+      <c r="AX38" s="4"/>
+      <c r="AY38" s="4"/>
+      <c r="AZ38" s="4"/>
+      <c r="BA38" s="4"/>
+      <c r="BB38" s="4"/>
+      <c r="BC38" s="4"/>
+      <c r="BD38" s="4"/>
+      <c r="BE38" s="4"/>
+      <c r="BF38" s="4"/>
+      <c r="BG38" s="4"/>
+      <c r="BH38" s="4"/>
+      <c r="BI38" s="4"/>
+      <c r="BJ38" s="4"/>
+      <c r="BK38" s="4"/>
+      <c r="BL38" s="4"/>
+      <c r="BM38" s="4"/>
     </row>
-    <row r="39" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="21" t="s">
-        <v>207</v>
-      </c>
-      <c r="B39" s="21"/>
-      <c r="C39" s="21"/>
-      <c r="D39" s="21"/>
-      <c r="E39" s="21"/>
-      <c r="F39" s="21"/>
-      <c r="G39" s="21"/>
-      <c r="H39" s="21"/>
-      <c r="I39" s="21"/>
-      <c r="J39" s="21"/>
-      <c r="K39" s="21"/>
-      <c r="L39" s="21"/>
-      <c r="M39" s="21"/>
-      <c r="N39" s="21"/>
-      <c r="O39" s="21"/>
-      <c r="P39" s="21"/>
-      <c r="Q39" s="21"/>
-      <c r="R39" s="21"/>
-      <c r="S39" s="21"/>
-      <c r="T39" s="21"/>
-      <c r="U39" s="21"/>
-      <c r="V39" s="21"/>
-      <c r="W39" s="21"/>
-      <c r="X39" s="21"/>
-      <c r="Y39" s="21"/>
-      <c r="Z39" s="21"/>
-      <c r="AA39" s="21"/>
-      <c r="AB39" s="21"/>
-      <c r="AC39" s="21"/>
-      <c r="AD39" s="21"/>
-      <c r="AE39" s="21"/>
-      <c r="AF39" s="21"/>
-      <c r="AG39" s="21"/>
-      <c r="AH39" s="21"/>
-      <c r="AI39" s="21"/>
-      <c r="AJ39" s="21"/>
-      <c r="AK39" s="21"/>
-      <c r="AL39" s="21"/>
-      <c r="AM39" s="21"/>
-      <c r="AN39" s="21"/>
-      <c r="AO39" s="21"/>
-      <c r="AP39" s="21"/>
-      <c r="AQ39" s="21"/>
-      <c r="AR39" s="21"/>
-      <c r="AS39" s="21"/>
-      <c r="AT39" s="21"/>
-      <c r="AU39" s="21"/>
-      <c r="AV39" s="21"/>
-      <c r="AW39" s="21"/>
-      <c r="AX39" s="21"/>
-      <c r="AY39" s="21"/>
-      <c r="AZ39" s="21"/>
-      <c r="BA39" s="21"/>
-      <c r="BB39" s="21"/>
-      <c r="BC39" s="21"/>
-      <c r="BD39" s="21"/>
-      <c r="BE39" s="21"/>
-      <c r="BF39" s="21"/>
-      <c r="BG39" s="21"/>
-      <c r="BH39" s="21"/>
-      <c r="BI39" s="21"/>
-      <c r="BJ39" s="21"/>
-      <c r="BK39" s="21"/>
-      <c r="BL39" s="21"/>
-      <c r="BM39" s="21"/>
+    <row r="39" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B39" s="4"/>
+      <c r="C39" s="4"/>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+      <c r="K39" s="4"/>
+      <c r="L39" s="4"/>
+      <c r="M39" s="4"/>
+      <c r="N39" s="4"/>
+      <c r="O39" s="4"/>
+      <c r="P39" s="4"/>
+      <c r="Q39" s="4"/>
+      <c r="R39" s="4"/>
+      <c r="S39" s="4"/>
+      <c r="T39" s="4"/>
+      <c r="U39" s="4"/>
+      <c r="V39" s="4"/>
+      <c r="W39" s="4"/>
+      <c r="X39" s="4"/>
+      <c r="Y39" s="4"/>
+      <c r="Z39" s="4"/>
+      <c r="AA39" s="4"/>
+      <c r="AB39" s="4"/>
+      <c r="AC39" s="4"/>
+      <c r="AD39" s="4"/>
+      <c r="AE39" s="4"/>
+      <c r="AF39" s="4"/>
+      <c r="AG39" s="4"/>
+      <c r="AH39" s="4"/>
+      <c r="AI39" s="4"/>
+      <c r="AJ39" s="4"/>
+      <c r="AK39" s="4"/>
+      <c r="AL39" s="4"/>
+      <c r="AM39" s="4"/>
+      <c r="AN39" s="4"/>
+      <c r="AO39" s="4"/>
+      <c r="AP39" s="4"/>
+      <c r="AQ39" s="4"/>
+      <c r="AR39" s="4"/>
+      <c r="AS39" s="4"/>
+      <c r="AT39" s="4"/>
+      <c r="AU39" s="4"/>
+      <c r="AV39" s="4"/>
+      <c r="AW39" s="4"/>
+      <c r="AX39" s="4"/>
+      <c r="AY39" s="4"/>
+      <c r="AZ39" s="4"/>
+      <c r="BA39" s="4"/>
+      <c r="BB39" s="4"/>
+      <c r="BC39" s="4"/>
+      <c r="BD39" s="4"/>
+      <c r="BE39" s="4"/>
+      <c r="BF39" s="4"/>
+      <c r="BG39" s="4"/>
+      <c r="BH39" s="4"/>
+      <c r="BI39" s="4"/>
+      <c r="BJ39" s="4"/>
+      <c r="BK39" s="4"/>
+      <c r="BL39" s="4"/>
+      <c r="BM39" s="4"/>
     </row>
     <row r="40" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="s">
-        <v>74</v>
+        <v>196</v>
       </c>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
@@ -22773,7 +22365,7 @@
     </row>
     <row r="41" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
-        <v>208</v>
+        <v>22</v>
       </c>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
@@ -22842,7 +22434,7 @@
     </row>
     <row r="42" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
@@ -22911,7 +22503,7 @@
     </row>
     <row r="43" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
@@ -22980,7 +22572,7 @@
     </row>
     <row r="44" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="s">
-        <v>22</v>
+        <v>199</v>
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
@@ -23049,7 +22641,7 @@
     </row>
     <row r="45" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="4" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
@@ -23118,7 +22710,7 @@
     </row>
     <row r="46" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="4" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
@@ -23185,215 +22777,8 @@
       <c r="BL46" s="4"/>
       <c r="BM46" s="4"/>
     </row>
-    <row r="47" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="B47" s="4"/>
-      <c r="C47" s="4"/>
-      <c r="D47" s="4"/>
-      <c r="E47" s="4"/>
-      <c r="F47" s="4"/>
-      <c r="G47" s="4"/>
-      <c r="H47" s="4"/>
-      <c r="I47" s="4"/>
-      <c r="J47" s="4"/>
-      <c r="K47" s="4"/>
-      <c r="L47" s="4"/>
-      <c r="M47" s="4"/>
-      <c r="N47" s="4"/>
-      <c r="O47" s="4"/>
-      <c r="P47" s="4"/>
-      <c r="Q47" s="4"/>
-      <c r="R47" s="4"/>
-      <c r="S47" s="4"/>
-      <c r="T47" s="4"/>
-      <c r="U47" s="4"/>
-      <c r="V47" s="4"/>
-      <c r="W47" s="4"/>
-      <c r="X47" s="4"/>
-      <c r="Y47" s="4"/>
-      <c r="Z47" s="4"/>
-      <c r="AA47" s="4"/>
-      <c r="AB47" s="4"/>
-      <c r="AC47" s="4"/>
-      <c r="AD47" s="4"/>
-      <c r="AE47" s="4"/>
-      <c r="AF47" s="4"/>
-      <c r="AG47" s="4"/>
-      <c r="AH47" s="4"/>
-      <c r="AI47" s="4"/>
-      <c r="AJ47" s="4"/>
-      <c r="AK47" s="4"/>
-      <c r="AL47" s="4"/>
-      <c r="AM47" s="4"/>
-      <c r="AN47" s="4"/>
-      <c r="AO47" s="4"/>
-      <c r="AP47" s="4"/>
-      <c r="AQ47" s="4"/>
-      <c r="AR47" s="4"/>
-      <c r="AS47" s="4"/>
-      <c r="AT47" s="4"/>
-      <c r="AU47" s="4"/>
-      <c r="AV47" s="4"/>
-      <c r="AW47" s="4"/>
-      <c r="AX47" s="4"/>
-      <c r="AY47" s="4"/>
-      <c r="AZ47" s="4"/>
-      <c r="BA47" s="4"/>
-      <c r="BB47" s="4"/>
-      <c r="BC47" s="4"/>
-      <c r="BD47" s="4"/>
-      <c r="BE47" s="4"/>
-      <c r="BF47" s="4"/>
-      <c r="BG47" s="4"/>
-      <c r="BH47" s="4"/>
-      <c r="BI47" s="4"/>
-      <c r="BJ47" s="4"/>
-      <c r="BK47" s="4"/>
-      <c r="BL47" s="4"/>
-      <c r="BM47" s="4"/>
-    </row>
-    <row r="48" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="B48" s="4"/>
-      <c r="C48" s="4"/>
-      <c r="D48" s="4"/>
-      <c r="E48" s="4"/>
-      <c r="F48" s="4"/>
-      <c r="G48" s="4"/>
-      <c r="H48" s="4"/>
-      <c r="I48" s="4"/>
-      <c r="J48" s="4"/>
-      <c r="K48" s="4"/>
-      <c r="L48" s="4"/>
-      <c r="M48" s="4"/>
-      <c r="N48" s="4"/>
-      <c r="O48" s="4"/>
-      <c r="P48" s="4"/>
-      <c r="Q48" s="4"/>
-      <c r="R48" s="4"/>
-      <c r="S48" s="4"/>
-      <c r="T48" s="4"/>
-      <c r="U48" s="4"/>
-      <c r="V48" s="4"/>
-      <c r="W48" s="4"/>
-      <c r="X48" s="4"/>
-      <c r="Y48" s="4"/>
-      <c r="Z48" s="4"/>
-      <c r="AA48" s="4"/>
-      <c r="AB48" s="4"/>
-      <c r="AC48" s="4"/>
-      <c r="AD48" s="4"/>
-      <c r="AE48" s="4"/>
-      <c r="AF48" s="4"/>
-      <c r="AG48" s="4"/>
-      <c r="AH48" s="4"/>
-      <c r="AI48" s="4"/>
-      <c r="AJ48" s="4"/>
-      <c r="AK48" s="4"/>
-      <c r="AL48" s="4"/>
-      <c r="AM48" s="4"/>
-      <c r="AN48" s="4"/>
-      <c r="AO48" s="4"/>
-      <c r="AP48" s="4"/>
-      <c r="AQ48" s="4"/>
-      <c r="AR48" s="4"/>
-      <c r="AS48" s="4"/>
-      <c r="AT48" s="4"/>
-      <c r="AU48" s="4"/>
-      <c r="AV48" s="4"/>
-      <c r="AW48" s="4"/>
-      <c r="AX48" s="4"/>
-      <c r="AY48" s="4"/>
-      <c r="AZ48" s="4"/>
-      <c r="BA48" s="4"/>
-      <c r="BB48" s="4"/>
-      <c r="BC48" s="4"/>
-      <c r="BD48" s="4"/>
-      <c r="BE48" s="4"/>
-      <c r="BF48" s="4"/>
-      <c r="BG48" s="4"/>
-      <c r="BH48" s="4"/>
-      <c r="BI48" s="4"/>
-      <c r="BJ48" s="4"/>
-      <c r="BK48" s="4"/>
-      <c r="BL48" s="4"/>
-      <c r="BM48" s="4"/>
-    </row>
-    <row r="49" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="B49" s="4"/>
-      <c r="C49" s="4"/>
-      <c r="D49" s="4"/>
-      <c r="E49" s="4"/>
-      <c r="F49" s="4"/>
-      <c r="G49" s="4"/>
-      <c r="H49" s="4"/>
-      <c r="I49" s="4"/>
-      <c r="J49" s="4"/>
-      <c r="K49" s="4"/>
-      <c r="L49" s="4"/>
-      <c r="M49" s="4"/>
-      <c r="N49" s="4"/>
-      <c r="O49" s="4"/>
-      <c r="P49" s="4"/>
-      <c r="Q49" s="4"/>
-      <c r="R49" s="4"/>
-      <c r="S49" s="4"/>
-      <c r="T49" s="4"/>
-      <c r="U49" s="4"/>
-      <c r="V49" s="4"/>
-      <c r="W49" s="4"/>
-      <c r="X49" s="4"/>
-      <c r="Y49" s="4"/>
-      <c r="Z49" s="4"/>
-      <c r="AA49" s="4"/>
-      <c r="AB49" s="4"/>
-      <c r="AC49" s="4"/>
-      <c r="AD49" s="4"/>
-      <c r="AE49" s="4"/>
-      <c r="AF49" s="4"/>
-      <c r="AG49" s="4"/>
-      <c r="AH49" s="4"/>
-      <c r="AI49" s="4"/>
-      <c r="AJ49" s="4"/>
-      <c r="AK49" s="4"/>
-      <c r="AL49" s="4"/>
-      <c r="AM49" s="4"/>
-      <c r="AN49" s="4"/>
-      <c r="AO49" s="4"/>
-      <c r="AP49" s="4"/>
-      <c r="AQ49" s="4"/>
-      <c r="AR49" s="4"/>
-      <c r="AS49" s="4"/>
-      <c r="AT49" s="4"/>
-      <c r="AU49" s="4"/>
-      <c r="AV49" s="4"/>
-      <c r="AW49" s="4"/>
-      <c r="AX49" s="4"/>
-      <c r="AY49" s="4"/>
-      <c r="AZ49" s="4"/>
-      <c r="BA49" s="4"/>
-      <c r="BB49" s="4"/>
-      <c r="BC49" s="4"/>
-      <c r="BD49" s="4"/>
-      <c r="BE49" s="4"/>
-      <c r="BF49" s="4"/>
-      <c r="BG49" s="4"/>
-      <c r="BH49" s="4"/>
-      <c r="BI49" s="4"/>
-      <c r="BJ49" s="4"/>
-      <c r="BK49" s="4"/>
-      <c r="BL49" s="4"/>
-      <c r="BM49" s="4"/>
-    </row>
   </sheetData>
-  <mergeCells count="43">
+  <mergeCells count="40">
     <mergeCell ref="A1:BI1"/>
     <mergeCell ref="BJ1:BM1"/>
     <mergeCell ref="A2:BM2"/>
@@ -23422,10 +22807,10 @@
     <mergeCell ref="B26:E26"/>
     <mergeCell ref="B27:E27"/>
     <mergeCell ref="B28:E28"/>
-    <mergeCell ref="B29:E29"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="B31:E31"/>
-    <mergeCell ref="A33:V33"/>
+    <mergeCell ref="A30:V30"/>
+    <mergeCell ref="A36:BM36"/>
+    <mergeCell ref="A37:BM37"/>
+    <mergeCell ref="A38:BM38"/>
     <mergeCell ref="A39:BM39"/>
     <mergeCell ref="A40:BM40"/>
     <mergeCell ref="A41:BM41"/>
@@ -23434,9 +22819,6 @@
     <mergeCell ref="A44:BM44"/>
     <mergeCell ref="A45:BM45"/>
     <mergeCell ref="A46:BM46"/>
-    <mergeCell ref="A47:BM47"/>
-    <mergeCell ref="A48:BM48"/>
-    <mergeCell ref="A49:BM49"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>

--- a/tratando_tabelas/finitura/entradas_finitura.xlsx
+++ b/tratando_tabelas/finitura/entradas_finitura.xlsx
@@ -20,12 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1072" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1192" uniqueCount="212">
   <si>
     <t xml:space="preserve">Santri ADM 1.1.5.7 R1</t>
   </si>
   <si>
-    <t xml:space="preserve">Emitido em: 23/04/2026 10:36:38</t>
+    <t xml:space="preserve">Emitido em: 24/04/2026 09:30:17</t>
   </si>
   <si>
     <t xml:space="preserve">Relação de entradas - Sintético</t>
@@ -304,28 +304,13 @@
     <t xml:space="preserve">35260430228132000136550010000088151717974742</t>
   </si>
   <si>
-    <t xml:space="preserve">2.923 - NEW LINE ILUMINACAO LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">223.491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">171,56</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.910</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260412077181000133550030002234911678252367</t>
-  </si>
-  <si>
     <t xml:space="preserve">11.969</t>
   </si>
   <si>
     <t xml:space="preserve">1.818,78</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.910</t>
   </si>
   <si>
     <t xml:space="preserve">41260417781412000109550010000119691000316152</t>
@@ -347,21 +332,6 @@
   </si>
   <si>
     <t xml:space="preserve">43260427254297000178550010000104561755610073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.829 - STUDIO LAMPLUZ COMERCIO E SERVICOS LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.047,98</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260458339477000186550010000005321000000540</t>
   </si>
   <si>
     <t xml:space="preserve">1.856 - DEXCO S.A - METAIS</t>
@@ -569,6 +539,66 @@
   </si>
   <si>
     <t xml:space="preserve">42260475339051000141550080006195361507400913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">621.751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.945,98</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260475339051000141550080006217511066401195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.664 - STANDARD ILUMINACAO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.563,51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260456365423000160550010000116311171638522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">620.355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.674,18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260475339051000141550080006203551861934770</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.705 - DOKA - INDUSTRIA E COMERCIO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.012,80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260401136190000131550010000613311329572229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.067.220</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.247,73</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050672201050975986</t>
   </si>
   <si>
     <t xml:space="preserve">Total geral</t>
@@ -16814,7 +16844,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BM46"/>
+  <dimension ref="A1:BM49"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="18"/>
@@ -17759,22 +17789,22 @@
     </row>
     <row r="8" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="n">
-        <v>304934</v>
+        <v>304943</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
       <c r="F8" s="9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>96</v>
+        <v>66</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="I8" s="9" t="s">
         <v>84</v>
@@ -17786,16 +17816,16 @@
         <v>70</v>
       </c>
       <c r="L8" s="12" t="n">
-        <v>171.56</v>
+        <v>1818.78</v>
       </c>
       <c r="M8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N8" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O8" s="12" t="n">
-        <v>156.32</v>
+        <v>1657.2</v>
       </c>
       <c r="P8" s="12" t="n">
         <v>0</v>
@@ -17810,7 +17840,7 @@
         <v>0</v>
       </c>
       <c r="T8" s="14" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="U8" s="15" t="s">
         <v>72</v>
@@ -17825,13 +17855,13 @@
         <v>84</v>
       </c>
       <c r="Y8" s="12" t="n">
-        <v>15.24</v>
+        <v>161.58</v>
       </c>
       <c r="Z8" s="12" t="n">
-        <v>156.32</v>
+        <v>1657.2</v>
       </c>
       <c r="AA8" s="12" t="n">
-        <v>10.94</v>
+        <v>66.28</v>
       </c>
       <c r="AB8" s="12" t="n">
         <v>0</v>
@@ -17900,7 +17930,7 @@
         <v>76</v>
       </c>
       <c r="AX8" s="10" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="AY8" s="14" t="s">
         <v>75</v>
@@ -17936,7 +17966,7 @@
         <v>78</v>
       </c>
       <c r="BJ8" s="9" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="BK8" s="9" t="s">
         <v>75</v>
@@ -17950,46 +17980,46 @@
     </row>
     <row r="9" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="n">
-        <v>304943</v>
+        <v>304974</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G9" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="K9" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L9" s="12" t="n">
-        <v>1818.78</v>
+        <v>5418.46</v>
       </c>
       <c r="M9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N9" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O9" s="12" t="n">
-        <v>1657.2</v>
+        <v>5153.46</v>
       </c>
       <c r="P9" s="12" t="n">
-        <v>0</v>
+        <v>265</v>
       </c>
       <c r="Q9" s="13" t="n">
         <v>0</v>
@@ -18001,28 +18031,28 @@
         <v>0</v>
       </c>
       <c r="T9" s="14" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="U9" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V9" s="12" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="W9" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X9" s="9" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="Y9" s="12" t="n">
-        <v>161.58</v>
+        <v>0</v>
       </c>
       <c r="Z9" s="12" t="n">
-        <v>1657.2</v>
+        <v>5418.46</v>
       </c>
       <c r="AA9" s="12" t="n">
-        <v>66.28</v>
+        <v>379.29</v>
       </c>
       <c r="AB9" s="12" t="n">
         <v>0</v>
@@ -18091,7 +18121,7 @@
         <v>76</v>
       </c>
       <c r="AX9" s="10" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="AY9" s="14" t="s">
         <v>75</v>
@@ -18127,7 +18157,7 @@
         <v>78</v>
       </c>
       <c r="BJ9" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="BK9" s="9" t="s">
         <v>75</v>
@@ -18141,34 +18171,34 @@
     </row>
     <row r="10" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="n">
-        <v>304974</v>
+        <v>305175</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
       <c r="F10" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G10" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>68</v>
+        <v>106</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K10" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L10" s="12" t="n">
-        <v>5418.46</v>
+        <v>542.51</v>
       </c>
       <c r="M10" s="12" t="n">
         <v>0</v>
@@ -18177,43 +18207,43 @@
         <v>1</v>
       </c>
       <c r="O10" s="12" t="n">
-        <v>5153.46</v>
+        <v>509.4</v>
       </c>
       <c r="P10" s="12" t="n">
-        <v>265</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="13" t="n">
-        <v>0</v>
+        <v>0.002772</v>
       </c>
       <c r="R10" s="12" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="S10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T10" s="14" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="U10" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V10" s="12" t="n">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="W10" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X10" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Y10" s="12" t="n">
-        <v>0</v>
+        <v>33.11</v>
       </c>
       <c r="Z10" s="12" t="n">
-        <v>5418.46</v>
+        <v>509.4</v>
       </c>
       <c r="AA10" s="12" t="n">
-        <v>379.29</v>
+        <v>20.38</v>
       </c>
       <c r="AB10" s="12" t="n">
         <v>0</v>
@@ -18318,7 +18348,7 @@
         <v>78</v>
       </c>
       <c r="BJ10" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BK10" s="9" t="s">
         <v>75</v>
@@ -18332,34 +18362,34 @@
     </row>
     <row r="11" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="n">
-        <v>304992</v>
+        <v>305206</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
       <c r="F11" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G11" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="K11" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>3047.98</v>
+        <v>2577.37</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>0</v>
@@ -18368,7 +18398,7 @@
         <v>2</v>
       </c>
       <c r="O11" s="12" t="n">
-        <v>3047.98</v>
+        <v>2348.4</v>
       </c>
       <c r="P11" s="12" t="n">
         <v>0</v>
@@ -18377,34 +18407,34 @@
         <v>0</v>
       </c>
       <c r="R11" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T11" s="14" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="U11" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V11" s="12" t="n">
-        <v>45</v>
+        <v>31.19</v>
       </c>
       <c r="W11" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X11" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Y11" s="12" t="n">
-        <v>0</v>
+        <v>228.97</v>
       </c>
       <c r="Z11" s="12" t="n">
-        <v>3047.98</v>
+        <v>2348.4</v>
       </c>
       <c r="AA11" s="12" t="n">
-        <v>92.05</v>
+        <v>164.38</v>
       </c>
       <c r="AB11" s="12" t="n">
         <v>0</v>
@@ -18509,7 +18539,7 @@
         <v>78</v>
       </c>
       <c r="BJ11" s="9" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="BK11" s="9" t="s">
         <v>75</v>
@@ -18523,79 +18553,79 @@
     </row>
     <row r="12" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="n">
-        <v>305175</v>
+        <v>305238</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
       <c r="F12" s="9" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>66</v>
+        <v>118</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="K12" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>542.51</v>
+        <v>2751</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O12" s="12" t="n">
-        <v>509.4</v>
+        <v>2751</v>
       </c>
       <c r="P12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" s="13" t="n">
-        <v>0.002772</v>
+        <v>0.011956</v>
       </c>
       <c r="R12" s="12" t="n">
-        <v>2.92</v>
+        <v>5.06</v>
       </c>
       <c r="S12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T12" s="14" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="U12" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V12" s="12" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="W12" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X12" s="9" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="Y12" s="12" t="n">
-        <v>33.11</v>
+        <v>0</v>
       </c>
       <c r="Z12" s="12" t="n">
-        <v>509.4</v>
+        <v>2751</v>
       </c>
       <c r="AA12" s="12" t="n">
-        <v>20.38</v>
+        <v>192.57</v>
       </c>
       <c r="AB12" s="12" t="n">
         <v>0</v>
@@ -18700,7 +18730,7 @@
         <v>78</v>
       </c>
       <c r="BJ12" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="BK12" s="9" t="s">
         <v>75</v>
@@ -18714,10 +18744,10 @@
     </row>
     <row r="13" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="n">
-        <v>305206</v>
+        <v>305250</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
@@ -18726,13 +18756,13 @@
         <v>121</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>66</v>
+        <v>118</v>
       </c>
       <c r="H13" s="9" t="s">
         <v>122</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="J13" s="9" t="s">
         <v>123</v>
@@ -18741,25 +18771,25 @@
         <v>70</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>2577.37</v>
+        <v>2088.57</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O13" s="12" t="n">
-        <v>2348.4</v>
+        <v>2088.57</v>
       </c>
       <c r="P13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q13" s="13" t="n">
-        <v>0</v>
+        <v>0.005874</v>
       </c>
       <c r="R13" s="12" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S13" s="12" t="n">
         <v>0</v>
@@ -18771,22 +18801,22 @@
         <v>72</v>
       </c>
       <c r="V13" s="12" t="n">
-        <v>31.19</v>
+        <v>28</v>
       </c>
       <c r="W13" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X13" s="9" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="Y13" s="12" t="n">
-        <v>228.97</v>
+        <v>0</v>
       </c>
       <c r="Z13" s="12" t="n">
-        <v>2348.4</v>
+        <v>2088.57</v>
       </c>
       <c r="AA13" s="12" t="n">
-        <v>164.38</v>
+        <v>146.2</v>
       </c>
       <c r="AB13" s="12" t="n">
         <v>0</v>
@@ -18905,25 +18935,25 @@
     </row>
     <row r="14" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="n">
-        <v>305238</v>
+        <v>305251</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
       <c r="F14" s="9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="H14" s="9" t="s">
         <v>122</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="J14" s="9" t="s">
         <v>123</v>
@@ -18932,31 +18962,31 @@
         <v>70</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>2751</v>
+        <v>1411.71</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O14" s="12" t="n">
-        <v>2751</v>
+        <v>1411.71</v>
       </c>
       <c r="P14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q14" s="13" t="n">
-        <v>0.011956</v>
+        <v>0.000432</v>
       </c>
       <c r="R14" s="12" t="n">
-        <v>5.06</v>
+        <v>0.74</v>
       </c>
       <c r="S14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T14" s="14" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="U14" s="15" t="s">
         <v>72</v>
@@ -18968,16 +18998,16 @@
         <v>73</v>
       </c>
       <c r="X14" s="9" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="Y14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z14" s="12" t="n">
-        <v>2751</v>
+        <v>1411.71</v>
       </c>
       <c r="AA14" s="12" t="n">
-        <v>192.57</v>
+        <v>98.82</v>
       </c>
       <c r="AB14" s="12" t="n">
         <v>0</v>
@@ -19082,7 +19112,7 @@
         <v>78</v>
       </c>
       <c r="BJ14" s="9" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="BK14" s="9" t="s">
         <v>75</v>
@@ -19096,34 +19126,34 @@
     </row>
     <row r="15" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="n">
-        <v>305250</v>
+        <v>305258</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
       <c r="F15" s="9" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="K15" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>2088.57</v>
+        <v>5612.24</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>0</v>
@@ -19132,22 +19162,22 @@
         <v>1</v>
       </c>
       <c r="O15" s="12" t="n">
-        <v>2088.57</v>
+        <v>5612.24</v>
       </c>
       <c r="P15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q15" s="13" t="n">
-        <v>0.005874</v>
+        <v>0.034</v>
       </c>
       <c r="R15" s="12" t="n">
-        <v>1.45</v>
+        <v>10.12</v>
       </c>
       <c r="S15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T15" s="14" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="U15" s="15" t="s">
         <v>72</v>
@@ -19159,16 +19189,16 @@
         <v>73</v>
       </c>
       <c r="X15" s="9" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="Y15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z15" s="12" t="n">
-        <v>2088.57</v>
+        <v>5612.24</v>
       </c>
       <c r="AA15" s="12" t="n">
-        <v>146.2</v>
+        <v>392.86</v>
       </c>
       <c r="AB15" s="12" t="n">
         <v>0</v>
@@ -19273,7 +19303,7 @@
         <v>78</v>
       </c>
       <c r="BJ15" s="9" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="BK15" s="9" t="s">
         <v>75</v>
@@ -19287,34 +19317,34 @@
     </row>
     <row r="16" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="n">
-        <v>305251</v>
+        <v>305419</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
       <c r="F16" s="9" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>128</v>
+        <v>66</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="K16" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>1411.71</v>
+        <v>392.71</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>0</v>
@@ -19323,43 +19353,43 @@
         <v>1</v>
       </c>
       <c r="O16" s="12" t="n">
-        <v>1411.71</v>
+        <v>368.74</v>
       </c>
       <c r="P16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q16" s="13" t="n">
-        <v>0.000432</v>
+        <v>0.006789</v>
       </c>
       <c r="R16" s="12" t="n">
-        <v>0.74</v>
+        <v>3.81</v>
       </c>
       <c r="S16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T16" s="14" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="U16" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V16" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W16" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X16" s="9" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="Y16" s="12" t="n">
-        <v>0</v>
+        <v>23.97</v>
       </c>
       <c r="Z16" s="12" t="n">
-        <v>1411.71</v>
+        <v>368.74</v>
       </c>
       <c r="AA16" s="12" t="n">
-        <v>98.82</v>
+        <v>14.75</v>
       </c>
       <c r="AB16" s="12" t="n">
         <v>0</v>
@@ -19428,7 +19458,7 @@
         <v>76</v>
       </c>
       <c r="AX16" s="10" t="s">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="AY16" s="14" t="s">
         <v>75</v>
@@ -19464,7 +19494,7 @@
         <v>78</v>
       </c>
       <c r="BJ16" s="9" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="BK16" s="9" t="s">
         <v>75</v>
@@ -19478,34 +19508,34 @@
     </row>
     <row r="17" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="n">
-        <v>305258</v>
+        <v>305443</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
       <c r="F17" s="9" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>128</v>
+        <v>66</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="K17" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>5612.24</v>
+        <v>163.48</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>0</v>
@@ -19514,43 +19544,43 @@
         <v>1</v>
       </c>
       <c r="O17" s="12" t="n">
-        <v>5612.24</v>
+        <v>153.5</v>
       </c>
       <c r="P17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q17" s="13" t="n">
-        <v>0.034</v>
+        <v>0.003456</v>
       </c>
       <c r="R17" s="12" t="n">
-        <v>10.12</v>
+        <v>0.8</v>
       </c>
       <c r="S17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T17" s="14" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="U17" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V17" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W17" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X17" s="9" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="Y17" s="12" t="n">
-        <v>0</v>
+        <v>9.98</v>
       </c>
       <c r="Z17" s="12" t="n">
-        <v>5612.24</v>
+        <v>153.5</v>
       </c>
       <c r="AA17" s="12" t="n">
-        <v>392.86</v>
+        <v>6.14</v>
       </c>
       <c r="AB17" s="12" t="n">
         <v>0</v>
@@ -19619,7 +19649,7 @@
         <v>76</v>
       </c>
       <c r="AX17" s="10" t="s">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="AY17" s="14" t="s">
         <v>75</v>
@@ -19655,7 +19685,7 @@
         <v>78</v>
       </c>
       <c r="BJ17" s="9" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="BK17" s="9" t="s">
         <v>75</v>
@@ -19669,25 +19699,25 @@
     </row>
     <row r="18" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="n">
-        <v>305419</v>
+        <v>305457</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
       <c r="F18" s="9" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G18" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>116</v>
+        <v>141</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="J18" s="9" t="s">
         <v>78</v>
@@ -19696,31 +19726,31 @@
         <v>70</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>392.71</v>
+        <v>4770.41</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="O18" s="12" t="n">
-        <v>368.74</v>
+        <v>4588.46</v>
       </c>
       <c r="P18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q18" s="13" t="n">
-        <v>0.006789</v>
+        <v>0.231499</v>
       </c>
       <c r="R18" s="12" t="n">
-        <v>3.81</v>
+        <v>35.08</v>
       </c>
       <c r="S18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T18" s="14" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="U18" s="15" t="s">
         <v>72</v>
@@ -19732,16 +19762,16 @@
         <v>73</v>
       </c>
       <c r="X18" s="9" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="Y18" s="12" t="n">
-        <v>23.97</v>
+        <v>181.95</v>
       </c>
       <c r="Z18" s="12" t="n">
-        <v>368.74</v>
+        <v>4588.46</v>
       </c>
       <c r="AA18" s="12" t="n">
-        <v>14.75</v>
+        <v>183.54</v>
       </c>
       <c r="AB18" s="12" t="n">
         <v>0</v>
@@ -19810,7 +19840,7 @@
         <v>76</v>
       </c>
       <c r="AX18" s="10" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="AY18" s="14" t="s">
         <v>75</v>
@@ -19846,7 +19876,7 @@
         <v>78</v>
       </c>
       <c r="BJ18" s="9" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="BK18" s="9" t="s">
         <v>75</v>
@@ -19860,25 +19890,25 @@
     </row>
     <row r="19" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="n">
-        <v>305443</v>
+        <v>305470</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
       <c r="F19" s="9" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="G19" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>116</v>
+        <v>141</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="J19" s="9" t="s">
         <v>78</v>
@@ -19887,31 +19917,31 @@
         <v>70</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>163.48</v>
+        <v>314.65</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O19" s="12" t="n">
-        <v>153.5</v>
+        <v>295.45</v>
       </c>
       <c r="P19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q19" s="13" t="n">
-        <v>0.003456</v>
+        <v>0.016472</v>
       </c>
       <c r="R19" s="12" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="S19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T19" s="14" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="U19" s="15" t="s">
         <v>72</v>
@@ -19923,16 +19953,16 @@
         <v>73</v>
       </c>
       <c r="X19" s="9" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="Y19" s="12" t="n">
-        <v>9.98</v>
+        <v>19.2</v>
       </c>
       <c r="Z19" s="12" t="n">
-        <v>153.5</v>
+        <v>295.45</v>
       </c>
       <c r="AA19" s="12" t="n">
-        <v>6.14</v>
+        <v>11.81</v>
       </c>
       <c r="AB19" s="12" t="n">
         <v>0</v>
@@ -20001,7 +20031,7 @@
         <v>76</v>
       </c>
       <c r="AX19" s="10" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="AY19" s="14" t="s">
         <v>75</v>
@@ -20037,7 +20067,7 @@
         <v>78</v>
       </c>
       <c r="BJ19" s="9" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="BK19" s="9" t="s">
         <v>75</v>
@@ -20051,25 +20081,25 @@
     </row>
     <row r="20" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="n">
-        <v>305457</v>
+        <v>305480</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
       <c r="F20" s="9" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G20" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="J20" s="9" t="s">
         <v>78</v>
@@ -20078,31 +20108,31 @@
         <v>70</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>4770.41</v>
+        <v>2373.3</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="O20" s="12" t="n">
-        <v>4588.46</v>
+        <v>2228.46</v>
       </c>
       <c r="P20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q20" s="13" t="n">
-        <v>0.231499</v>
+        <v>0.017186</v>
       </c>
       <c r="R20" s="12" t="n">
-        <v>35.08</v>
+        <v>12.33</v>
       </c>
       <c r="S20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T20" s="14" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="U20" s="15" t="s">
         <v>72</v>
@@ -20114,16 +20144,16 @@
         <v>73</v>
       </c>
       <c r="X20" s="9" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="Y20" s="12" t="n">
-        <v>181.95</v>
+        <v>144.84</v>
       </c>
       <c r="Z20" s="12" t="n">
-        <v>4588.46</v>
+        <v>2228.46</v>
       </c>
       <c r="AA20" s="12" t="n">
-        <v>183.54</v>
+        <v>89.14</v>
       </c>
       <c r="AB20" s="12" t="n">
         <v>0</v>
@@ -20192,7 +20222,7 @@
         <v>76</v>
       </c>
       <c r="AX20" s="10" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="AY20" s="14" t="s">
         <v>75</v>
@@ -20228,7 +20258,7 @@
         <v>78</v>
       </c>
       <c r="BJ20" s="9" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="BK20" s="9" t="s">
         <v>75</v>
@@ -20242,79 +20272,79 @@
     </row>
     <row r="21" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="n">
-        <v>305470</v>
+        <v>305539</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
       <c r="F21" s="9" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>66</v>
+        <v>118</v>
       </c>
       <c r="H21" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="I21" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="I21" s="9" t="s">
-        <v>143</v>
-      </c>
       <c r="J21" s="9" t="s">
-        <v>78</v>
+        <v>152</v>
       </c>
       <c r="K21" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>314.65</v>
+        <v>1568.57</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O21" s="12" t="n">
-        <v>295.45</v>
+        <v>1568.57</v>
       </c>
       <c r="P21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q21" s="13" t="n">
-        <v>0.016472</v>
+        <v>0.000432</v>
       </c>
       <c r="R21" s="12" t="n">
-        <v>1.6</v>
+        <v>0.74</v>
       </c>
       <c r="S21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T21" s="14" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="U21" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V21" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W21" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X21" s="9" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="Y21" s="12" t="n">
-        <v>19.2</v>
+        <v>0</v>
       </c>
       <c r="Z21" s="12" t="n">
-        <v>295.45</v>
+        <v>1568.57</v>
       </c>
       <c r="AA21" s="12" t="n">
-        <v>11.81</v>
+        <v>109.8</v>
       </c>
       <c r="AB21" s="12" t="n">
         <v>0</v>
@@ -20383,7 +20413,7 @@
         <v>76</v>
       </c>
       <c r="AX21" s="10" t="s">
-        <v>145</v>
+        <v>77</v>
       </c>
       <c r="AY21" s="14" t="s">
         <v>75</v>
@@ -20419,7 +20449,7 @@
         <v>78</v>
       </c>
       <c r="BJ21" s="9" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="BK21" s="9" t="s">
         <v>75</v>
@@ -20433,79 +20463,79 @@
     </row>
     <row r="22" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="n">
-        <v>305480</v>
+        <v>305553</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
       <c r="F22" s="9" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>66</v>
+        <v>118</v>
       </c>
       <c r="H22" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="I22" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="I22" s="9" t="s">
-        <v>143</v>
-      </c>
       <c r="J22" s="9" t="s">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="K22" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>2373.3</v>
+        <v>3135.16</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O22" s="12" t="n">
-        <v>2228.46</v>
+        <v>3135.16</v>
       </c>
       <c r="P22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q22" s="13" t="n">
-        <v>0.017186</v>
+        <v>0.000864</v>
       </c>
       <c r="R22" s="12" t="n">
-        <v>12.33</v>
+        <v>1.48</v>
       </c>
       <c r="S22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T22" s="14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="U22" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V22" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W22" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X22" s="9" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="Y22" s="12" t="n">
-        <v>144.84</v>
+        <v>0</v>
       </c>
       <c r="Z22" s="12" t="n">
-        <v>2228.46</v>
+        <v>3135.16</v>
       </c>
       <c r="AA22" s="12" t="n">
-        <v>89.14</v>
+        <v>219.46</v>
       </c>
       <c r="AB22" s="12" t="n">
         <v>0</v>
@@ -20574,7 +20604,7 @@
         <v>76</v>
       </c>
       <c r="AX22" s="10" t="s">
-        <v>145</v>
+        <v>77</v>
       </c>
       <c r="AY22" s="14" t="s">
         <v>75</v>
@@ -20610,7 +20640,7 @@
         <v>78</v>
       </c>
       <c r="BJ22" s="9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="BK22" s="9" t="s">
         <v>75</v>
@@ -20624,34 +20654,34 @@
     </row>
     <row r="23" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="n">
-        <v>305539</v>
+        <v>305554</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="K23" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>1568.57</v>
+        <v>3258.14</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>0</v>
@@ -20660,22 +20690,22 @@
         <v>1</v>
       </c>
       <c r="O23" s="12" t="n">
-        <v>1568.57</v>
+        <v>3258.14</v>
       </c>
       <c r="P23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q23" s="13" t="n">
-        <v>0.000432</v>
+        <v>0.000864</v>
       </c>
       <c r="R23" s="12" t="n">
-        <v>0.74</v>
+        <v>1.48</v>
       </c>
       <c r="S23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T23" s="14" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="U23" s="15" t="s">
         <v>72</v>
@@ -20687,16 +20717,16 @@
         <v>73</v>
       </c>
       <c r="X23" s="9" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="Y23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z23" s="12" t="n">
-        <v>1568.57</v>
+        <v>3258.14</v>
       </c>
       <c r="AA23" s="12" t="n">
-        <v>109.8</v>
+        <v>228.07</v>
       </c>
       <c r="AB23" s="12" t="n">
         <v>0</v>
@@ -20801,7 +20831,7 @@
         <v>78</v>
       </c>
       <c r="BJ23" s="9" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="BK23" s="9" t="s">
         <v>75</v>
@@ -20815,34 +20845,34 @@
     </row>
     <row r="24" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="n">
-        <v>305553</v>
+        <v>305556</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
       <c r="F24" s="9" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="K24" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>3135.16</v>
+        <v>5879.02</v>
       </c>
       <c r="M24" s="12" t="n">
         <v>0</v>
@@ -20851,22 +20881,22 @@
         <v>1</v>
       </c>
       <c r="O24" s="12" t="n">
-        <v>3135.16</v>
+        <v>5879.02</v>
       </c>
       <c r="P24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q24" s="13" t="n">
-        <v>0.000864</v>
+        <v>0.467698</v>
       </c>
       <c r="R24" s="12" t="n">
-        <v>1.48</v>
+        <v>31.5</v>
       </c>
       <c r="S24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T24" s="14" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="U24" s="15" t="s">
         <v>72</v>
@@ -20878,16 +20908,16 @@
         <v>73</v>
       </c>
       <c r="X24" s="9" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="Y24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z24" s="12" t="n">
-        <v>3135.16</v>
+        <v>5879.02</v>
       </c>
       <c r="AA24" s="12" t="n">
-        <v>219.46</v>
+        <v>411.53</v>
       </c>
       <c r="AB24" s="12" t="n">
         <v>0</v>
@@ -20992,7 +21022,7 @@
         <v>78</v>
       </c>
       <c r="BJ24" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="BK24" s="9" t="s">
         <v>75</v>
@@ -21006,34 +21036,34 @@
     </row>
     <row r="25" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="n">
-        <v>305554</v>
+        <v>305560</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>143</v>
+        <v>166</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K25" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>3258.14</v>
+        <v>3121.47</v>
       </c>
       <c r="M25" s="12" t="n">
         <v>0</v>
@@ -21042,22 +21072,22 @@
         <v>1</v>
       </c>
       <c r="O25" s="12" t="n">
-        <v>3258.14</v>
+        <v>3121.47</v>
       </c>
       <c r="P25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q25" s="13" t="n">
-        <v>0.000864</v>
+        <v>0.031059</v>
       </c>
       <c r="R25" s="12" t="n">
-        <v>1.48</v>
+        <v>5.54</v>
       </c>
       <c r="S25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T25" s="14" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="U25" s="15" t="s">
         <v>72</v>
@@ -21069,16 +21099,16 @@
         <v>73</v>
       </c>
       <c r="X25" s="9" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="Y25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z25" s="12" t="n">
-        <v>3258.14</v>
+        <v>3121.47</v>
       </c>
       <c r="AA25" s="12" t="n">
-        <v>228.07</v>
+        <v>218.5</v>
       </c>
       <c r="AB25" s="12" t="n">
         <v>0</v>
@@ -21183,7 +21213,7 @@
         <v>78</v>
       </c>
       <c r="BJ25" s="9" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="BK25" s="9" t="s">
         <v>75</v>
@@ -21197,34 +21227,34 @@
     </row>
     <row r="26" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="n">
-        <v>305556</v>
+        <v>305561</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>143</v>
+        <v>166</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K26" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>5879.02</v>
+        <v>5331.26</v>
       </c>
       <c r="M26" s="12" t="n">
         <v>0</v>
@@ -21233,22 +21263,22 @@
         <v>1</v>
       </c>
       <c r="O26" s="12" t="n">
-        <v>5879.02</v>
+        <v>5005.88</v>
       </c>
       <c r="P26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q26" s="13" t="n">
-        <v>0.467698</v>
+        <v>0.055816</v>
       </c>
       <c r="R26" s="12" t="n">
-        <v>31.5</v>
+        <v>7.12</v>
       </c>
       <c r="S26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T26" s="14" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="U26" s="15" t="s">
         <v>72</v>
@@ -21260,16 +21290,16 @@
         <v>73</v>
       </c>
       <c r="X26" s="9" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="Y26" s="12" t="n">
-        <v>0</v>
+        <v>325.38</v>
       </c>
       <c r="Z26" s="12" t="n">
-        <v>5879.02</v>
+        <v>5005.88</v>
       </c>
       <c r="AA26" s="12" t="n">
-        <v>411.53</v>
+        <v>350.41</v>
       </c>
       <c r="AB26" s="12" t="n">
         <v>0</v>
@@ -21374,7 +21404,7 @@
         <v>78</v>
       </c>
       <c r="BJ26" s="9" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="BK26" s="9" t="s">
         <v>75</v>
@@ -21388,34 +21418,34 @@
     </row>
     <row r="27" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="n">
-        <v>305560</v>
+        <v>305681</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="G27" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="I27" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="J27" s="9" t="s">
         <v>175</v>
-      </c>
-      <c r="G27" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="H27" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="I27" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="J27" s="9" t="s">
-        <v>177</v>
       </c>
       <c r="K27" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>3121.47</v>
+        <v>1945.98</v>
       </c>
       <c r="M27" s="12" t="n">
         <v>0</v>
@@ -21424,22 +21454,22 @@
         <v>1</v>
       </c>
       <c r="O27" s="12" t="n">
-        <v>3121.47</v>
+        <v>1945.98</v>
       </c>
       <c r="P27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q27" s="13" t="n">
-        <v>0.031059</v>
+        <v>0.004946</v>
       </c>
       <c r="R27" s="12" t="n">
-        <v>5.54</v>
+        <v>1.15</v>
       </c>
       <c r="S27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T27" s="14" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="U27" s="15" t="s">
         <v>72</v>
@@ -21451,16 +21481,16 @@
         <v>73</v>
       </c>
       <c r="X27" s="9" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="Y27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z27" s="12" t="n">
-        <v>3121.47</v>
+        <v>1945.98</v>
       </c>
       <c r="AA27" s="12" t="n">
-        <v>218.5</v>
+        <v>136.22</v>
       </c>
       <c r="AB27" s="12" t="n">
         <v>0</v>
@@ -21565,7 +21595,7 @@
         <v>78</v>
       </c>
       <c r="BJ27" s="9" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="BK27" s="9" t="s">
         <v>75</v>
@@ -21579,79 +21609,79 @@
     </row>
     <row r="28" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="n">
-        <v>305561</v>
+        <v>305691</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>126</v>
+        <v>178</v>
       </c>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>128</v>
+        <v>66</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="K28" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>5331.26</v>
+        <v>3563.51</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O28" s="12" t="n">
-        <v>5005.88</v>
+        <v>3098.7</v>
       </c>
       <c r="P28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q28" s="13" t="n">
-        <v>0.055816</v>
+        <v>0</v>
       </c>
       <c r="R28" s="12" t="n">
-        <v>7.12</v>
+        <v>0</v>
       </c>
       <c r="S28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T28" s="14" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="U28" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V28" s="12" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="W28" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X28" s="9" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="Y28" s="12" t="n">
-        <v>325.38</v>
+        <v>464.81</v>
       </c>
       <c r="Z28" s="12" t="n">
-        <v>5005.88</v>
+        <v>3098.7</v>
       </c>
       <c r="AA28" s="12" t="n">
-        <v>350.41</v>
+        <v>216.91</v>
       </c>
       <c r="AB28" s="12" t="n">
         <v>0</v>
@@ -21756,7 +21786,7 @@
         <v>78</v>
       </c>
       <c r="BJ28" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="BK28" s="9" t="s">
         <v>75</v>
@@ -21769,534 +21799,900 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4"/>
+      <c r="A29" s="8" t="n">
+        <v>305724</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="G29" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="I29" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="J29" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="K29" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L29" s="12" t="n">
+        <v>1674.18</v>
+      </c>
+      <c r="M29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O29" s="12" t="n">
+        <v>1674.18</v>
+      </c>
+      <c r="P29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="13" t="n">
+        <v>0.003916</v>
+      </c>
+      <c r="R29" s="12" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="S29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="U29" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V29" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="W29" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X29" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="12" t="n">
+        <v>1674.18</v>
+      </c>
+      <c r="AA29" s="12" t="n">
+        <v>117.19</v>
+      </c>
+      <c r="AB29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ29" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM29" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN29" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO29" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP29" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ29" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR29" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS29" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT29" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU29" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV29" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW29" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX29" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY29" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ29" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA29" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB29" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC29" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD29" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE29" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF29" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG29" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH29" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI29" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ29" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="BK29" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL29" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM29" s="16" t="s">
+        <v>80</v>
+      </c>
     </row>
-    <row r="30" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="17" t="s">
+    <row r="30" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="8" t="n">
+        <v>305725</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="G30" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H30" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="I30" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="J30" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="B30" s="17"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="17"/>
-      <c r="G30" s="17"/>
-      <c r="H30" s="17"/>
-      <c r="I30" s="17"/>
-      <c r="J30" s="17"/>
-      <c r="K30" s="17"/>
-      <c r="L30" s="17"/>
-      <c r="M30" s="17"/>
-      <c r="N30" s="17"/>
-      <c r="O30" s="17"/>
-      <c r="P30" s="17"/>
-      <c r="Q30" s="17"/>
-      <c r="R30" s="17"/>
-      <c r="S30" s="17"/>
-      <c r="T30" s="17"/>
-      <c r="U30" s="17"/>
-      <c r="V30" s="17"/>
+      <c r="K30" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L30" s="12" t="n">
+        <v>10012.8</v>
+      </c>
+      <c r="M30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O30" s="12" t="n">
+        <v>10012.8</v>
+      </c>
+      <c r="P30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="13" t="n">
+        <v>0.750038</v>
+      </c>
+      <c r="R30" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="S30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="U30" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V30" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="W30" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X30" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="12" t="n">
+        <v>10012.8</v>
+      </c>
+      <c r="AA30" s="12" t="n">
+        <v>400.51</v>
+      </c>
+      <c r="AB30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ30" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM30" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN30" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO30" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP30" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ30" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR30" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS30" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT30" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU30" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV30" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW30" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX30" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY30" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ30" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA30" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB30" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC30" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD30" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE30" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF30" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG30" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH30" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI30" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ30" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="BK30" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL30" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM30" s="16" t="s">
+        <v>80</v>
+      </c>
     </row>
-    <row r="31" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="18" t="s">
-        <v>184</v>
-      </c>
-      <c r="B31" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C31" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D31" s="18" t="s">
-        <v>185</v>
-      </c>
-      <c r="E31" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F31" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="G31" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="H31" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="I31" s="18" t="s">
-        <v>186</v>
-      </c>
-      <c r="J31" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="K31" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="L31" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="M31" s="18" t="s">
-        <v>187</v>
-      </c>
-      <c r="N31" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="O31" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="P31" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q31" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="R31" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="S31" s="18" t="s">
-        <v>188</v>
-      </c>
-      <c r="T31" s="18" t="s">
-        <v>189</v>
-      </c>
-      <c r="U31" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="V31" s="18" t="s">
-        <v>37</v>
+    <row r="31" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="8" t="n">
+        <v>305731</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="G31" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H31" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="I31" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="J31" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="K31" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L31" s="12" t="n">
+        <v>6247.73</v>
+      </c>
+      <c r="M31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O31" s="12" t="n">
+        <v>6247.73</v>
+      </c>
+      <c r="P31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="13" t="n">
+        <v>0.030808</v>
+      </c>
+      <c r="R31" s="12" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="S31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="U31" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V31" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="W31" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X31" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="12" t="n">
+        <v>6247.73</v>
+      </c>
+      <c r="AA31" s="12" t="n">
+        <v>437.34</v>
+      </c>
+      <c r="AB31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ31" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM31" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN31" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO31" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP31" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ31" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR31" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS31" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT31" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU31" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV31" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW31" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX31" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY31" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ31" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA31" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB31" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC31" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD31" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE31" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF31" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG31" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH31" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI31" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ31" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="BK31" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL31" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM31" s="16" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="19" t="n">
-        <v>24</v>
-      </c>
-      <c r="B32" s="19" t="n">
-        <v>5811.05</v>
-      </c>
-      <c r="C32" s="19" t="n">
-        <v>424</v>
-      </c>
-      <c r="D32" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" s="19" t="n">
-        <v>3705.98</v>
-      </c>
-      <c r="F32" s="19" t="n">
-        <v>82718.44</v>
-      </c>
-      <c r="G32" s="19" t="n">
-        <v>4629.72</v>
-      </c>
-      <c r="H32" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" s="19" t="n">
-        <v>86424.42</v>
-      </c>
-      <c r="L32" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" s="20" t="n">
-        <v>0.911319</v>
-      </c>
-      <c r="S32" s="19" t="n">
-        <v>88105.49</v>
-      </c>
-      <c r="T32" s="19" t="n">
-        <v>86424.42</v>
-      </c>
-      <c r="U32" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" s="19" t="n">
-        <v>0</v>
-      </c>
+      <c r="A32" s="4"/>
     </row>
     <row r="33" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="B33" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C33" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="D33" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E33" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="F33" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="G33" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="H33" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="I33" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="J33" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="K33" s="18" t="s">
-        <v>190</v>
-      </c>
-      <c r="L33" s="18" t="s">
-        <v>191</v>
-      </c>
-      <c r="M33" s="18" t="s">
-        <v>192</v>
-      </c>
+      <c r="A33" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="B33" s="17"/>
+      <c r="C33" s="17"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="17"/>
+      <c r="F33" s="17"/>
+      <c r="G33" s="17"/>
+      <c r="H33" s="17"/>
+      <c r="I33" s="17"/>
+      <c r="J33" s="17"/>
+      <c r="K33" s="17"/>
+      <c r="L33" s="17"/>
+      <c r="M33" s="17"/>
+      <c r="N33" s="17"/>
+      <c r="O33" s="17"/>
+      <c r="P33" s="17"/>
+      <c r="Q33" s="17"/>
+      <c r="R33" s="17"/>
+      <c r="S33" s="17"/>
+      <c r="T33" s="17"/>
+      <c r="U33" s="17"/>
+      <c r="V33" s="17"/>
     </row>
-    <row r="34" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="19" t="n">
-        <v>131.77</v>
-      </c>
-      <c r="B34" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C34" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" s="19" t="n">
-        <v>53.7</v>
-      </c>
-      <c r="E34" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" s="19" t="n">
-        <v>0</v>
+    <row r="34" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="B34" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C34" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D34" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="E34" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F34" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="G34" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H34" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="I34" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="J34" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="K34" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="L34" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="M34" s="18" t="s">
+        <v>197</v>
+      </c>
+      <c r="N34" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="O34" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="P34" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q34" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="R34" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="S34" s="18" t="s">
+        <v>198</v>
+      </c>
+      <c r="T34" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="U34" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="V34" s="18" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="4"/>
+      <c r="A35" s="19" t="n">
+        <v>27</v>
+      </c>
+      <c r="B35" s="19" t="n">
+        <v>5811.05</v>
+      </c>
+      <c r="C35" s="19" t="n">
+        <v>424</v>
+      </c>
+      <c r="D35" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="19" t="n">
+        <v>4155.55</v>
+      </c>
+      <c r="F35" s="19" t="n">
+        <v>102493.53</v>
+      </c>
+      <c r="G35" s="19" t="n">
+        <v>5834.9</v>
+      </c>
+      <c r="H35" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="19" t="n">
+        <v>106649.08</v>
+      </c>
+      <c r="L35" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" s="20" t="n">
+        <v>1.701027</v>
+      </c>
+      <c r="S35" s="19" t="n">
+        <v>107880.58</v>
+      </c>
+      <c r="T35" s="19" t="n">
+        <v>106649.08</v>
+      </c>
+      <c r="U35" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="21" t="s">
-        <v>193</v>
-      </c>
-      <c r="B36" s="21"/>
-      <c r="C36" s="21"/>
-      <c r="D36" s="21"/>
-      <c r="E36" s="21"/>
-      <c r="F36" s="21"/>
-      <c r="G36" s="21"/>
-      <c r="H36" s="21"/>
-      <c r="I36" s="21"/>
-      <c r="J36" s="21"/>
-      <c r="K36" s="21"/>
-      <c r="L36" s="21"/>
-      <c r="M36" s="21"/>
-      <c r="N36" s="21"/>
-      <c r="O36" s="21"/>
-      <c r="P36" s="21"/>
-      <c r="Q36" s="21"/>
-      <c r="R36" s="21"/>
-      <c r="S36" s="21"/>
-      <c r="T36" s="21"/>
-      <c r="U36" s="21"/>
-      <c r="V36" s="21"/>
-      <c r="W36" s="21"/>
-      <c r="X36" s="21"/>
-      <c r="Y36" s="21"/>
-      <c r="Z36" s="21"/>
-      <c r="AA36" s="21"/>
-      <c r="AB36" s="21"/>
-      <c r="AC36" s="21"/>
-      <c r="AD36" s="21"/>
-      <c r="AE36" s="21"/>
-      <c r="AF36" s="21"/>
-      <c r="AG36" s="21"/>
-      <c r="AH36" s="21"/>
-      <c r="AI36" s="21"/>
-      <c r="AJ36" s="21"/>
-      <c r="AK36" s="21"/>
-      <c r="AL36" s="21"/>
-      <c r="AM36" s="21"/>
-      <c r="AN36" s="21"/>
-      <c r="AO36" s="21"/>
-      <c r="AP36" s="21"/>
-      <c r="AQ36" s="21"/>
-      <c r="AR36" s="21"/>
-      <c r="AS36" s="21"/>
-      <c r="AT36" s="21"/>
-      <c r="AU36" s="21"/>
-      <c r="AV36" s="21"/>
-      <c r="AW36" s="21"/>
-      <c r="AX36" s="21"/>
-      <c r="AY36" s="21"/>
-      <c r="AZ36" s="21"/>
-      <c r="BA36" s="21"/>
-      <c r="BB36" s="21"/>
-      <c r="BC36" s="21"/>
-      <c r="BD36" s="21"/>
-      <c r="BE36" s="21"/>
-      <c r="BF36" s="21"/>
-      <c r="BG36" s="21"/>
-      <c r="BH36" s="21"/>
-      <c r="BI36" s="21"/>
-      <c r="BJ36" s="21"/>
-      <c r="BK36" s="21"/>
-      <c r="BL36" s="21"/>
-      <c r="BM36" s="21"/>
+      <c r="A36" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B36" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C36" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D36" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="E36" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="F36" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="G36" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="H36" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="I36" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="J36" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="K36" s="18" t="s">
+        <v>200</v>
+      </c>
+      <c r="L36" s="18" t="s">
+        <v>201</v>
+      </c>
+      <c r="M36" s="18" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
-      <c r="I37" s="4"/>
-      <c r="J37" s="4"/>
-      <c r="K37" s="4"/>
-      <c r="L37" s="4"/>
-      <c r="M37" s="4"/>
-      <c r="N37" s="4"/>
-      <c r="O37" s="4"/>
-      <c r="P37" s="4"/>
-      <c r="Q37" s="4"/>
-      <c r="R37" s="4"/>
-      <c r="S37" s="4"/>
-      <c r="T37" s="4"/>
-      <c r="U37" s="4"/>
-      <c r="V37" s="4"/>
-      <c r="W37" s="4"/>
-      <c r="X37" s="4"/>
-      <c r="Y37" s="4"/>
-      <c r="Z37" s="4"/>
-      <c r="AA37" s="4"/>
-      <c r="AB37" s="4"/>
-      <c r="AC37" s="4"/>
-      <c r="AD37" s="4"/>
-      <c r="AE37" s="4"/>
-      <c r="AF37" s="4"/>
-      <c r="AG37" s="4"/>
-      <c r="AH37" s="4"/>
-      <c r="AI37" s="4"/>
-      <c r="AJ37" s="4"/>
-      <c r="AK37" s="4"/>
-      <c r="AL37" s="4"/>
-      <c r="AM37" s="4"/>
-      <c r="AN37" s="4"/>
-      <c r="AO37" s="4"/>
-      <c r="AP37" s="4"/>
-      <c r="AQ37" s="4"/>
-      <c r="AR37" s="4"/>
-      <c r="AS37" s="4"/>
-      <c r="AT37" s="4"/>
-      <c r="AU37" s="4"/>
-      <c r="AV37" s="4"/>
-      <c r="AW37" s="4"/>
-      <c r="AX37" s="4"/>
-      <c r="AY37" s="4"/>
-      <c r="AZ37" s="4"/>
-      <c r="BA37" s="4"/>
-      <c r="BB37" s="4"/>
-      <c r="BC37" s="4"/>
-      <c r="BD37" s="4"/>
-      <c r="BE37" s="4"/>
-      <c r="BF37" s="4"/>
-      <c r="BG37" s="4"/>
-      <c r="BH37" s="4"/>
-      <c r="BI37" s="4"/>
-      <c r="BJ37" s="4"/>
-      <c r="BK37" s="4"/>
-      <c r="BL37" s="4"/>
-      <c r="BM37" s="4"/>
+      <c r="A37" s="19" t="n">
+        <v>175.94</v>
+      </c>
+      <c r="B37" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="19" t="n">
+        <v>48.85</v>
+      </c>
+      <c r="E37" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
-      <c r="I38" s="4"/>
-      <c r="J38" s="4"/>
-      <c r="K38" s="4"/>
-      <c r="L38" s="4"/>
-      <c r="M38" s="4"/>
-      <c r="N38" s="4"/>
-      <c r="O38" s="4"/>
-      <c r="P38" s="4"/>
-      <c r="Q38" s="4"/>
-      <c r="R38" s="4"/>
-      <c r="S38" s="4"/>
-      <c r="T38" s="4"/>
-      <c r="U38" s="4"/>
-      <c r="V38" s="4"/>
-      <c r="W38" s="4"/>
-      <c r="X38" s="4"/>
-      <c r="Y38" s="4"/>
-      <c r="Z38" s="4"/>
-      <c r="AA38" s="4"/>
-      <c r="AB38" s="4"/>
-      <c r="AC38" s="4"/>
-      <c r="AD38" s="4"/>
-      <c r="AE38" s="4"/>
-      <c r="AF38" s="4"/>
-      <c r="AG38" s="4"/>
-      <c r="AH38" s="4"/>
-      <c r="AI38" s="4"/>
-      <c r="AJ38" s="4"/>
-      <c r="AK38" s="4"/>
-      <c r="AL38" s="4"/>
-      <c r="AM38" s="4"/>
-      <c r="AN38" s="4"/>
-      <c r="AO38" s="4"/>
-      <c r="AP38" s="4"/>
-      <c r="AQ38" s="4"/>
-      <c r="AR38" s="4"/>
-      <c r="AS38" s="4"/>
-      <c r="AT38" s="4"/>
-      <c r="AU38" s="4"/>
-      <c r="AV38" s="4"/>
-      <c r="AW38" s="4"/>
-      <c r="AX38" s="4"/>
-      <c r="AY38" s="4"/>
-      <c r="AZ38" s="4"/>
-      <c r="BA38" s="4"/>
-      <c r="BB38" s="4"/>
-      <c r="BC38" s="4"/>
-      <c r="BD38" s="4"/>
-      <c r="BE38" s="4"/>
-      <c r="BF38" s="4"/>
-      <c r="BG38" s="4"/>
-      <c r="BH38" s="4"/>
-      <c r="BI38" s="4"/>
-      <c r="BJ38" s="4"/>
-      <c r="BK38" s="4"/>
-      <c r="BL38" s="4"/>
-      <c r="BM38" s="4"/>
+      <c r="A38" s="4"/>
     </row>
-    <row r="39" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
-      <c r="E39" s="4"/>
-      <c r="F39" s="4"/>
-      <c r="G39" s="4"/>
-      <c r="H39" s="4"/>
-      <c r="I39" s="4"/>
-      <c r="J39" s="4"/>
-      <c r="K39" s="4"/>
-      <c r="L39" s="4"/>
-      <c r="M39" s="4"/>
-      <c r="N39" s="4"/>
-      <c r="O39" s="4"/>
-      <c r="P39" s="4"/>
-      <c r="Q39" s="4"/>
-      <c r="R39" s="4"/>
-      <c r="S39" s="4"/>
-      <c r="T39" s="4"/>
-      <c r="U39" s="4"/>
-      <c r="V39" s="4"/>
-      <c r="W39" s="4"/>
-      <c r="X39" s="4"/>
-      <c r="Y39" s="4"/>
-      <c r="Z39" s="4"/>
-      <c r="AA39" s="4"/>
-      <c r="AB39" s="4"/>
-      <c r="AC39" s="4"/>
-      <c r="AD39" s="4"/>
-      <c r="AE39" s="4"/>
-      <c r="AF39" s="4"/>
-      <c r="AG39" s="4"/>
-      <c r="AH39" s="4"/>
-      <c r="AI39" s="4"/>
-      <c r="AJ39" s="4"/>
-      <c r="AK39" s="4"/>
-      <c r="AL39" s="4"/>
-      <c r="AM39" s="4"/>
-      <c r="AN39" s="4"/>
-      <c r="AO39" s="4"/>
-      <c r="AP39" s="4"/>
-      <c r="AQ39" s="4"/>
-      <c r="AR39" s="4"/>
-      <c r="AS39" s="4"/>
-      <c r="AT39" s="4"/>
-      <c r="AU39" s="4"/>
-      <c r="AV39" s="4"/>
-      <c r="AW39" s="4"/>
-      <c r="AX39" s="4"/>
-      <c r="AY39" s="4"/>
-      <c r="AZ39" s="4"/>
-      <c r="BA39" s="4"/>
-      <c r="BB39" s="4"/>
-      <c r="BC39" s="4"/>
-      <c r="BD39" s="4"/>
-      <c r="BE39" s="4"/>
-      <c r="BF39" s="4"/>
-      <c r="BG39" s="4"/>
-      <c r="BH39" s="4"/>
-      <c r="BI39" s="4"/>
-      <c r="BJ39" s="4"/>
-      <c r="BK39" s="4"/>
-      <c r="BL39" s="4"/>
-      <c r="BM39" s="4"/>
+    <row r="39" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="21" t="s">
+        <v>203</v>
+      </c>
+      <c r="B39" s="21"/>
+      <c r="C39" s="21"/>
+      <c r="D39" s="21"/>
+      <c r="E39" s="21"/>
+      <c r="F39" s="21"/>
+      <c r="G39" s="21"/>
+      <c r="H39" s="21"/>
+      <c r="I39" s="21"/>
+      <c r="J39" s="21"/>
+      <c r="K39" s="21"/>
+      <c r="L39" s="21"/>
+      <c r="M39" s="21"/>
+      <c r="N39" s="21"/>
+      <c r="O39" s="21"/>
+      <c r="P39" s="21"/>
+      <c r="Q39" s="21"/>
+      <c r="R39" s="21"/>
+      <c r="S39" s="21"/>
+      <c r="T39" s="21"/>
+      <c r="U39" s="21"/>
+      <c r="V39" s="21"/>
+      <c r="W39" s="21"/>
+      <c r="X39" s="21"/>
+      <c r="Y39" s="21"/>
+      <c r="Z39" s="21"/>
+      <c r="AA39" s="21"/>
+      <c r="AB39" s="21"/>
+      <c r="AC39" s="21"/>
+      <c r="AD39" s="21"/>
+      <c r="AE39" s="21"/>
+      <c r="AF39" s="21"/>
+      <c r="AG39" s="21"/>
+      <c r="AH39" s="21"/>
+      <c r="AI39" s="21"/>
+      <c r="AJ39" s="21"/>
+      <c r="AK39" s="21"/>
+      <c r="AL39" s="21"/>
+      <c r="AM39" s="21"/>
+      <c r="AN39" s="21"/>
+      <c r="AO39" s="21"/>
+      <c r="AP39" s="21"/>
+      <c r="AQ39" s="21"/>
+      <c r="AR39" s="21"/>
+      <c r="AS39" s="21"/>
+      <c r="AT39" s="21"/>
+      <c r="AU39" s="21"/>
+      <c r="AV39" s="21"/>
+      <c r="AW39" s="21"/>
+      <c r="AX39" s="21"/>
+      <c r="AY39" s="21"/>
+      <c r="AZ39" s="21"/>
+      <c r="BA39" s="21"/>
+      <c r="BB39" s="21"/>
+      <c r="BC39" s="21"/>
+      <c r="BD39" s="21"/>
+      <c r="BE39" s="21"/>
+      <c r="BF39" s="21"/>
+      <c r="BG39" s="21"/>
+      <c r="BH39" s="21"/>
+      <c r="BI39" s="21"/>
+      <c r="BJ39" s="21"/>
+      <c r="BK39" s="21"/>
+      <c r="BL39" s="21"/>
+      <c r="BM39" s="21"/>
     </row>
     <row r="40" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="s">
-        <v>196</v>
+        <v>75</v>
       </c>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
@@ -22365,7 +22761,7 @@
     </row>
     <row r="41" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
-        <v>22</v>
+        <v>204</v>
       </c>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
@@ -22434,7 +22830,7 @@
     </row>
     <row r="42" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
@@ -22503,7 +22899,7 @@
     </row>
     <row r="43" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
@@ -22572,7 +22968,7 @@
     </row>
     <row r="44" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="s">
-        <v>199</v>
+        <v>22</v>
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
@@ -22641,7 +23037,7 @@
     </row>
     <row r="45" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="4" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
@@ -22710,7 +23106,7 @@
     </row>
     <row r="46" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="4" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
@@ -22777,8 +23173,215 @@
       <c r="BL46" s="4"/>
       <c r="BM46" s="4"/>
     </row>
+    <row r="47" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="B47" s="4"/>
+      <c r="C47" s="4"/>
+      <c r="D47" s="4"/>
+      <c r="E47" s="4"/>
+      <c r="F47" s="4"/>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="K47" s="4"/>
+      <c r="L47" s="4"/>
+      <c r="M47" s="4"/>
+      <c r="N47" s="4"/>
+      <c r="O47" s="4"/>
+      <c r="P47" s="4"/>
+      <c r="Q47" s="4"/>
+      <c r="R47" s="4"/>
+      <c r="S47" s="4"/>
+      <c r="T47" s="4"/>
+      <c r="U47" s="4"/>
+      <c r="V47" s="4"/>
+      <c r="W47" s="4"/>
+      <c r="X47" s="4"/>
+      <c r="Y47" s="4"/>
+      <c r="Z47" s="4"/>
+      <c r="AA47" s="4"/>
+      <c r="AB47" s="4"/>
+      <c r="AC47" s="4"/>
+      <c r="AD47" s="4"/>
+      <c r="AE47" s="4"/>
+      <c r="AF47" s="4"/>
+      <c r="AG47" s="4"/>
+      <c r="AH47" s="4"/>
+      <c r="AI47" s="4"/>
+      <c r="AJ47" s="4"/>
+      <c r="AK47" s="4"/>
+      <c r="AL47" s="4"/>
+      <c r="AM47" s="4"/>
+      <c r="AN47" s="4"/>
+      <c r="AO47" s="4"/>
+      <c r="AP47" s="4"/>
+      <c r="AQ47" s="4"/>
+      <c r="AR47" s="4"/>
+      <c r="AS47" s="4"/>
+      <c r="AT47" s="4"/>
+      <c r="AU47" s="4"/>
+      <c r="AV47" s="4"/>
+      <c r="AW47" s="4"/>
+      <c r="AX47" s="4"/>
+      <c r="AY47" s="4"/>
+      <c r="AZ47" s="4"/>
+      <c r="BA47" s="4"/>
+      <c r="BB47" s="4"/>
+      <c r="BC47" s="4"/>
+      <c r="BD47" s="4"/>
+      <c r="BE47" s="4"/>
+      <c r="BF47" s="4"/>
+      <c r="BG47" s="4"/>
+      <c r="BH47" s="4"/>
+      <c r="BI47" s="4"/>
+      <c r="BJ47" s="4"/>
+      <c r="BK47" s="4"/>
+      <c r="BL47" s="4"/>
+      <c r="BM47" s="4"/>
+    </row>
+    <row r="48" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="B48" s="4"/>
+      <c r="C48" s="4"/>
+      <c r="D48" s="4"/>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4"/>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="K48" s="4"/>
+      <c r="L48" s="4"/>
+      <c r="M48" s="4"/>
+      <c r="N48" s="4"/>
+      <c r="O48" s="4"/>
+      <c r="P48" s="4"/>
+      <c r="Q48" s="4"/>
+      <c r="R48" s="4"/>
+      <c r="S48" s="4"/>
+      <c r="T48" s="4"/>
+      <c r="U48" s="4"/>
+      <c r="V48" s="4"/>
+      <c r="W48" s="4"/>
+      <c r="X48" s="4"/>
+      <c r="Y48" s="4"/>
+      <c r="Z48" s="4"/>
+      <c r="AA48" s="4"/>
+      <c r="AB48" s="4"/>
+      <c r="AC48" s="4"/>
+      <c r="AD48" s="4"/>
+      <c r="AE48" s="4"/>
+      <c r="AF48" s="4"/>
+      <c r="AG48" s="4"/>
+      <c r="AH48" s="4"/>
+      <c r="AI48" s="4"/>
+      <c r="AJ48" s="4"/>
+      <c r="AK48" s="4"/>
+      <c r="AL48" s="4"/>
+      <c r="AM48" s="4"/>
+      <c r="AN48" s="4"/>
+      <c r="AO48" s="4"/>
+      <c r="AP48" s="4"/>
+      <c r="AQ48" s="4"/>
+      <c r="AR48" s="4"/>
+      <c r="AS48" s="4"/>
+      <c r="AT48" s="4"/>
+      <c r="AU48" s="4"/>
+      <c r="AV48" s="4"/>
+      <c r="AW48" s="4"/>
+      <c r="AX48" s="4"/>
+      <c r="AY48" s="4"/>
+      <c r="AZ48" s="4"/>
+      <c r="BA48" s="4"/>
+      <c r="BB48" s="4"/>
+      <c r="BC48" s="4"/>
+      <c r="BD48" s="4"/>
+      <c r="BE48" s="4"/>
+      <c r="BF48" s="4"/>
+      <c r="BG48" s="4"/>
+      <c r="BH48" s="4"/>
+      <c r="BI48" s="4"/>
+      <c r="BJ48" s="4"/>
+      <c r="BK48" s="4"/>
+      <c r="BL48" s="4"/>
+      <c r="BM48" s="4"/>
+    </row>
+    <row r="49" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="B49" s="4"/>
+      <c r="C49" s="4"/>
+      <c r="D49" s="4"/>
+      <c r="E49" s="4"/>
+      <c r="F49" s="4"/>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+      <c r="K49" s="4"/>
+      <c r="L49" s="4"/>
+      <c r="M49" s="4"/>
+      <c r="N49" s="4"/>
+      <c r="O49" s="4"/>
+      <c r="P49" s="4"/>
+      <c r="Q49" s="4"/>
+      <c r="R49" s="4"/>
+      <c r="S49" s="4"/>
+      <c r="T49" s="4"/>
+      <c r="U49" s="4"/>
+      <c r="V49" s="4"/>
+      <c r="W49" s="4"/>
+      <c r="X49" s="4"/>
+      <c r="Y49" s="4"/>
+      <c r="Z49" s="4"/>
+      <c r="AA49" s="4"/>
+      <c r="AB49" s="4"/>
+      <c r="AC49" s="4"/>
+      <c r="AD49" s="4"/>
+      <c r="AE49" s="4"/>
+      <c r="AF49" s="4"/>
+      <c r="AG49" s="4"/>
+      <c r="AH49" s="4"/>
+      <c r="AI49" s="4"/>
+      <c r="AJ49" s="4"/>
+      <c r="AK49" s="4"/>
+      <c r="AL49" s="4"/>
+      <c r="AM49" s="4"/>
+      <c r="AN49" s="4"/>
+      <c r="AO49" s="4"/>
+      <c r="AP49" s="4"/>
+      <c r="AQ49" s="4"/>
+      <c r="AR49" s="4"/>
+      <c r="AS49" s="4"/>
+      <c r="AT49" s="4"/>
+      <c r="AU49" s="4"/>
+      <c r="AV49" s="4"/>
+      <c r="AW49" s="4"/>
+      <c r="AX49" s="4"/>
+      <c r="AY49" s="4"/>
+      <c r="AZ49" s="4"/>
+      <c r="BA49" s="4"/>
+      <c r="BB49" s="4"/>
+      <c r="BC49" s="4"/>
+      <c r="BD49" s="4"/>
+      <c r="BE49" s="4"/>
+      <c r="BF49" s="4"/>
+      <c r="BG49" s="4"/>
+      <c r="BH49" s="4"/>
+      <c r="BI49" s="4"/>
+      <c r="BJ49" s="4"/>
+      <c r="BK49" s="4"/>
+      <c r="BL49" s="4"/>
+      <c r="BM49" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="40">
+  <mergeCells count="43">
     <mergeCell ref="A1:BI1"/>
     <mergeCell ref="BJ1:BM1"/>
     <mergeCell ref="A2:BM2"/>
@@ -22807,10 +23410,10 @@
     <mergeCell ref="B26:E26"/>
     <mergeCell ref="B27:E27"/>
     <mergeCell ref="B28:E28"/>
-    <mergeCell ref="A30:V30"/>
-    <mergeCell ref="A36:BM36"/>
-    <mergeCell ref="A37:BM37"/>
-    <mergeCell ref="A38:BM38"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="B31:E31"/>
+    <mergeCell ref="A33:V33"/>
     <mergeCell ref="A39:BM39"/>
     <mergeCell ref="A40:BM40"/>
     <mergeCell ref="A41:BM41"/>
@@ -22819,6 +23422,9 @@
     <mergeCell ref="A44:BM44"/>
     <mergeCell ref="A45:BM45"/>
     <mergeCell ref="A46:BM46"/>
+    <mergeCell ref="A47:BM47"/>
+    <mergeCell ref="A48:BM48"/>
+    <mergeCell ref="A49:BM49"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>

--- a/tratando_tabelas/finitura/entradas_finitura.xlsx
+++ b/tratando_tabelas/finitura/entradas_finitura.xlsx
@@ -20,12 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1192" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1352" uniqueCount="231">
   <si>
     <t xml:space="preserve">Santri ADM 1.1.5.7 R1</t>
   </si>
   <si>
-    <t xml:space="preserve">Emitido em: 24/04/2026 09:30:17</t>
+    <t xml:space="preserve">Emitido em: 27/04/2026 08:59:35</t>
   </si>
   <si>
     <t xml:space="preserve">Relação de entradas - Sintético</t>
@@ -287,21 +287,6 @@
   </si>
   <si>
     <t xml:space="preserve">41260417781412000109550010000119661000316126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.145 - TKS ILUMINACAO E VENTILADORES LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">02/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.594,31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260430228132000136550010000088151717974742</t>
   </si>
   <si>
     <t xml:space="preserve">11.969</t>
@@ -599,6 +584,78 @@
   </si>
   <si>
     <t xml:space="preserve">35260497837181002190550010050672201050975986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.857 - GOLDEN ART INDUSTRIA E COMERCIO LTDA - EPP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">834,78</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260453654471000180550010000536161000320142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.101 - INDUSTRIA E COMERCIO DE MOLDURAS SANTA LUZIA LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139.721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.520,02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">397.763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.659 - RODO DANNY TRANSPORTES E LOGISTICAS EIRELI ME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91,25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260475821546000102550040001397211377780494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260411389565000200570050003977631000839511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">622.732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.462,34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260475339051000141550080006227321190427035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">622.723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.464,23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260475339051000141550080006227231342556046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">622.390</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.019,02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260475339051000141550080006223901051401241</t>
   </si>
   <si>
     <t xml:space="preserve">Total geral</t>
@@ -16844,7 +16901,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BM49"/>
+  <dimension ref="A1:BM53"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="18"/>
@@ -17598,34 +17655,34 @@
     </row>
     <row r="7" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="n">
-        <v>304921</v>
+        <v>304943</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
       <c r="F7" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G7" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>84</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K7" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L7" s="12" t="n">
-        <v>3594.31</v>
+        <v>1818.78</v>
       </c>
       <c r="M7" s="12" t="n">
         <v>0</v>
@@ -17634,28 +17691,28 @@
         <v>2</v>
       </c>
       <c r="O7" s="12" t="n">
-        <v>3275</v>
+        <v>1657.2</v>
       </c>
       <c r="P7" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q7" s="13" t="n">
-        <v>0.02415</v>
+        <v>0</v>
       </c>
       <c r="R7" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S7" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T7" s="14" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="U7" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V7" s="12" t="n">
-        <v>35.67</v>
+        <v>0</v>
       </c>
       <c r="W7" s="9" t="s">
         <v>73</v>
@@ -17664,13 +17721,13 @@
         <v>84</v>
       </c>
       <c r="Y7" s="12" t="n">
-        <v>319.31</v>
+        <v>161.58</v>
       </c>
       <c r="Z7" s="12" t="n">
-        <v>3275</v>
+        <v>1657.2</v>
       </c>
       <c r="AA7" s="12" t="n">
-        <v>229.25</v>
+        <v>66.28</v>
       </c>
       <c r="AB7" s="12" t="n">
         <v>0</v>
@@ -17739,7 +17796,7 @@
         <v>76</v>
       </c>
       <c r="AX7" s="10" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="AY7" s="14" t="s">
         <v>75</v>
@@ -17775,7 +17832,7 @@
         <v>78</v>
       </c>
       <c r="BJ7" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="BK7" s="9" t="s">
         <v>75</v>
@@ -17789,10 +17846,10 @@
     </row>
     <row r="8" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="n">
-        <v>304943</v>
+        <v>304974</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
@@ -17804,31 +17861,31 @@
         <v>66</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="K8" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L8" s="12" t="n">
-        <v>1818.78</v>
+        <v>5418.46</v>
       </c>
       <c r="M8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N8" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O8" s="12" t="n">
-        <v>1657.2</v>
+        <v>5153.46</v>
       </c>
       <c r="P8" s="12" t="n">
-        <v>0</v>
+        <v>265</v>
       </c>
       <c r="Q8" s="13" t="n">
         <v>0</v>
@@ -17840,28 +17897,28 @@
         <v>0</v>
       </c>
       <c r="T8" s="14" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="U8" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V8" s="12" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="W8" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X8" s="9" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="Y8" s="12" t="n">
-        <v>161.58</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="12" t="n">
-        <v>1657.2</v>
+        <v>5418.46</v>
       </c>
       <c r="AA8" s="12" t="n">
-        <v>66.28</v>
+        <v>379.29</v>
       </c>
       <c r="AB8" s="12" t="n">
         <v>0</v>
@@ -17930,7 +17987,7 @@
         <v>76</v>
       </c>
       <c r="AX8" s="10" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="AY8" s="14" t="s">
         <v>75</v>
@@ -17966,7 +18023,7 @@
         <v>78</v>
       </c>
       <c r="BJ8" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="BK8" s="9" t="s">
         <v>75</v>
@@ -17980,34 +18037,34 @@
     </row>
     <row r="9" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="n">
-        <v>304974</v>
+        <v>305175</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G9" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>68</v>
+        <v>101</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K9" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L9" s="12" t="n">
-        <v>5418.46</v>
+        <v>542.51</v>
       </c>
       <c r="M9" s="12" t="n">
         <v>0</v>
@@ -18016,43 +18073,43 @@
         <v>1</v>
       </c>
       <c r="O9" s="12" t="n">
-        <v>5153.46</v>
+        <v>509.4</v>
       </c>
       <c r="P9" s="12" t="n">
-        <v>265</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="13" t="n">
-        <v>0</v>
+        <v>0.002772</v>
       </c>
       <c r="R9" s="12" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="S9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T9" s="14" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="U9" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V9" s="12" t="n">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="W9" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X9" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Y9" s="12" t="n">
-        <v>0</v>
+        <v>33.11</v>
       </c>
       <c r="Z9" s="12" t="n">
-        <v>5418.46</v>
+        <v>509.4</v>
       </c>
       <c r="AA9" s="12" t="n">
-        <v>379.29</v>
+        <v>20.38</v>
       </c>
       <c r="AB9" s="12" t="n">
         <v>0</v>
@@ -18157,7 +18214,7 @@
         <v>78</v>
       </c>
       <c r="BJ9" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BK9" s="9" t="s">
         <v>75</v>
@@ -18171,79 +18228,79 @@
     </row>
     <row r="10" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="n">
-        <v>305175</v>
+        <v>305206</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
       <c r="F10" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G10" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K10" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L10" s="12" t="n">
-        <v>542.51</v>
+        <v>2577.37</v>
       </c>
       <c r="M10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N10" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O10" s="12" t="n">
-        <v>509.4</v>
+        <v>2348.4</v>
       </c>
       <c r="P10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q10" s="13" t="n">
-        <v>0.002772</v>
+        <v>0</v>
       </c>
       <c r="R10" s="12" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="S10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T10" s="14" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="U10" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V10" s="12" t="n">
-        <v>56</v>
+        <v>31.19</v>
       </c>
       <c r="W10" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X10" s="9" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="Y10" s="12" t="n">
-        <v>33.11</v>
+        <v>228.97</v>
       </c>
       <c r="Z10" s="12" t="n">
-        <v>509.4</v>
+        <v>2348.4</v>
       </c>
       <c r="AA10" s="12" t="n">
-        <v>20.38</v>
+        <v>164.38</v>
       </c>
       <c r="AB10" s="12" t="n">
         <v>0</v>
@@ -18348,7 +18405,7 @@
         <v>78</v>
       </c>
       <c r="BJ10" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BK10" s="9" t="s">
         <v>75</v>
@@ -18362,34 +18419,34 @@
     </row>
     <row r="11" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="n">
-        <v>305206</v>
+        <v>305238</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
       <c r="F11" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>66</v>
+        <v>113</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="K11" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>2577.37</v>
+        <v>2751</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>0</v>
@@ -18398,16 +18455,16 @@
         <v>2</v>
       </c>
       <c r="O11" s="12" t="n">
-        <v>2348.4</v>
+        <v>2751</v>
       </c>
       <c r="P11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q11" s="13" t="n">
-        <v>0</v>
+        <v>0.011956</v>
       </c>
       <c r="R11" s="12" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="S11" s="12" t="n">
         <v>0</v>
@@ -18419,22 +18476,22 @@
         <v>72</v>
       </c>
       <c r="V11" s="12" t="n">
-        <v>31.19</v>
+        <v>28</v>
       </c>
       <c r="W11" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X11" s="9" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="Y11" s="12" t="n">
-        <v>228.97</v>
+        <v>0</v>
       </c>
       <c r="Z11" s="12" t="n">
-        <v>2348.4</v>
+        <v>2751</v>
       </c>
       <c r="AA11" s="12" t="n">
-        <v>164.38</v>
+        <v>192.57</v>
       </c>
       <c r="AB11" s="12" t="n">
         <v>0</v>
@@ -18553,52 +18610,52 @@
     </row>
     <row r="12" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="n">
-        <v>305238</v>
+        <v>305250</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
       <c r="F12" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="H12" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="G12" s="10" t="s">
+      <c r="I12" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="J12" s="9" t="s">
         <v>118</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="I12" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="J12" s="9" t="s">
-        <v>113</v>
       </c>
       <c r="K12" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>2751</v>
+        <v>2088.57</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O12" s="12" t="n">
-        <v>2751</v>
+        <v>2088.57</v>
       </c>
       <c r="P12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" s="13" t="n">
-        <v>0.011956</v>
+        <v>0.005874</v>
       </c>
       <c r="R12" s="12" t="n">
-        <v>5.06</v>
+        <v>1.45</v>
       </c>
       <c r="S12" s="12" t="n">
         <v>0</v>
@@ -18616,16 +18673,16 @@
         <v>73</v>
       </c>
       <c r="X12" s="9" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="Y12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z12" s="12" t="n">
-        <v>2751</v>
+        <v>2088.57</v>
       </c>
       <c r="AA12" s="12" t="n">
-        <v>192.57</v>
+        <v>146.2</v>
       </c>
       <c r="AB12" s="12" t="n">
         <v>0</v>
@@ -18744,10 +18801,10 @@
     </row>
     <row r="13" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="n">
-        <v>305250</v>
+        <v>305251</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
@@ -18756,22 +18813,22 @@
         <v>121</v>
       </c>
       <c r="G13" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="J13" s="9" t="s">
         <v>118</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="I13" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="J13" s="9" t="s">
-        <v>123</v>
       </c>
       <c r="K13" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>2088.57</v>
+        <v>1411.71</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>0</v>
@@ -18780,22 +18837,22 @@
         <v>1</v>
       </c>
       <c r="O13" s="12" t="n">
-        <v>2088.57</v>
+        <v>1411.71</v>
       </c>
       <c r="P13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q13" s="13" t="n">
-        <v>0.005874</v>
+        <v>0.000432</v>
       </c>
       <c r="R13" s="12" t="n">
-        <v>1.45</v>
+        <v>0.74</v>
       </c>
       <c r="S13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T13" s="14" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="U13" s="15" t="s">
         <v>72</v>
@@ -18807,16 +18864,16 @@
         <v>73</v>
       </c>
       <c r="X13" s="9" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="Y13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z13" s="12" t="n">
-        <v>2088.57</v>
+        <v>1411.71</v>
       </c>
       <c r="AA13" s="12" t="n">
-        <v>146.2</v>
+        <v>98.82</v>
       </c>
       <c r="AB13" s="12" t="n">
         <v>0</v>
@@ -18921,7 +18978,7 @@
         <v>78</v>
       </c>
       <c r="BJ13" s="9" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="BK13" s="9" t="s">
         <v>75</v>
@@ -18935,34 +18992,34 @@
     </row>
     <row r="14" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="n">
-        <v>305251</v>
+        <v>305258</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
       <c r="F14" s="9" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G14" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="J14" s="9" t="s">
         <v>118</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="I14" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="J14" s="9" t="s">
-        <v>123</v>
       </c>
       <c r="K14" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>1411.71</v>
+        <v>5612.24</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>0</v>
@@ -18971,22 +19028,22 @@
         <v>1</v>
       </c>
       <c r="O14" s="12" t="n">
-        <v>1411.71</v>
+        <v>5612.24</v>
       </c>
       <c r="P14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q14" s="13" t="n">
-        <v>0.000432</v>
+        <v>0.034</v>
       </c>
       <c r="R14" s="12" t="n">
-        <v>0.74</v>
+        <v>10.12</v>
       </c>
       <c r="S14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T14" s="14" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="U14" s="15" t="s">
         <v>72</v>
@@ -18998,16 +19055,16 @@
         <v>73</v>
       </c>
       <c r="X14" s="9" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="Y14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z14" s="12" t="n">
-        <v>1411.71</v>
+        <v>5612.24</v>
       </c>
       <c r="AA14" s="12" t="n">
-        <v>98.82</v>
+        <v>392.86</v>
       </c>
       <c r="AB14" s="12" t="n">
         <v>0</v>
@@ -19112,7 +19169,7 @@
         <v>78</v>
       </c>
       <c r="BJ14" s="9" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="BK14" s="9" t="s">
         <v>75</v>
@@ -19126,34 +19183,34 @@
     </row>
     <row r="15" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="n">
-        <v>305258</v>
+        <v>305419</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
       <c r="F15" s="9" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>118</v>
+        <v>66</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>122</v>
+        <v>101</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>106</v>
+        <v>128</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>123</v>
+        <v>78</v>
       </c>
       <c r="K15" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>5612.24</v>
+        <v>392.71</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>0</v>
@@ -19162,43 +19219,43 @@
         <v>1</v>
       </c>
       <c r="O15" s="12" t="n">
-        <v>5612.24</v>
+        <v>368.74</v>
       </c>
       <c r="P15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q15" s="13" t="n">
-        <v>0.034</v>
+        <v>0.006789</v>
       </c>
       <c r="R15" s="12" t="n">
-        <v>10.12</v>
+        <v>3.81</v>
       </c>
       <c r="S15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T15" s="14" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="U15" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V15" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W15" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X15" s="9" t="s">
-        <v>106</v>
+        <v>128</v>
       </c>
       <c r="Y15" s="12" t="n">
-        <v>0</v>
+        <v>23.97</v>
       </c>
       <c r="Z15" s="12" t="n">
-        <v>5612.24</v>
+        <v>368.74</v>
       </c>
       <c r="AA15" s="12" t="n">
-        <v>392.86</v>
+        <v>14.75</v>
       </c>
       <c r="AB15" s="12" t="n">
         <v>0</v>
@@ -19267,7 +19324,7 @@
         <v>76</v>
       </c>
       <c r="AX15" s="10" t="s">
-        <v>77</v>
+        <v>130</v>
       </c>
       <c r="AY15" s="14" t="s">
         <v>75</v>
@@ -19317,10 +19374,10 @@
     </row>
     <row r="16" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="n">
-        <v>305419</v>
+        <v>305443</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
@@ -19332,10 +19389,10 @@
         <v>66</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="J16" s="9" t="s">
         <v>78</v>
@@ -19344,7 +19401,7 @@
         <v>70</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>392.71</v>
+        <v>163.48</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>0</v>
@@ -19353,22 +19410,22 @@
         <v>1</v>
       </c>
       <c r="O16" s="12" t="n">
-        <v>368.74</v>
+        <v>153.5</v>
       </c>
       <c r="P16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q16" s="13" t="n">
-        <v>0.006789</v>
+        <v>0.003456</v>
       </c>
       <c r="R16" s="12" t="n">
-        <v>3.81</v>
+        <v>0.8</v>
       </c>
       <c r="S16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T16" s="14" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="U16" s="15" t="s">
         <v>72</v>
@@ -19380,16 +19437,16 @@
         <v>73</v>
       </c>
       <c r="X16" s="9" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="Y16" s="12" t="n">
-        <v>23.97</v>
+        <v>9.98</v>
       </c>
       <c r="Z16" s="12" t="n">
-        <v>368.74</v>
+        <v>153.5</v>
       </c>
       <c r="AA16" s="12" t="n">
-        <v>14.75</v>
+        <v>6.14</v>
       </c>
       <c r="AB16" s="12" t="n">
         <v>0</v>
@@ -19458,7 +19515,7 @@
         <v>76</v>
       </c>
       <c r="AX16" s="10" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="AY16" s="14" t="s">
         <v>75</v>
@@ -19494,7 +19551,7 @@
         <v>78</v>
       </c>
       <c r="BJ16" s="9" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="BK16" s="9" t="s">
         <v>75</v>
@@ -19508,25 +19565,25 @@
     </row>
     <row r="17" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="n">
-        <v>305443</v>
+        <v>305457</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
       <c r="F17" s="9" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G17" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>106</v>
+        <v>136</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="J17" s="9" t="s">
         <v>78</v>
@@ -19535,31 +19592,31 @@
         <v>70</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>163.48</v>
+        <v>4770.41</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="O17" s="12" t="n">
-        <v>153.5</v>
+        <v>4588.46</v>
       </c>
       <c r="P17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q17" s="13" t="n">
-        <v>0.003456</v>
+        <v>0.231499</v>
       </c>
       <c r="R17" s="12" t="n">
-        <v>0.8</v>
+        <v>35.08</v>
       </c>
       <c r="S17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T17" s="14" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="U17" s="15" t="s">
         <v>72</v>
@@ -19571,16 +19628,16 @@
         <v>73</v>
       </c>
       <c r="X17" s="9" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="Y17" s="12" t="n">
-        <v>9.98</v>
+        <v>181.95</v>
       </c>
       <c r="Z17" s="12" t="n">
-        <v>153.5</v>
+        <v>4588.46</v>
       </c>
       <c r="AA17" s="12" t="n">
-        <v>6.14</v>
+        <v>183.54</v>
       </c>
       <c r="AB17" s="12" t="n">
         <v>0</v>
@@ -19649,7 +19706,7 @@
         <v>76</v>
       </c>
       <c r="AX17" s="10" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="AY17" s="14" t="s">
         <v>75</v>
@@ -19685,7 +19742,7 @@
         <v>78</v>
       </c>
       <c r="BJ17" s="9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="BK17" s="9" t="s">
         <v>75</v>
@@ -19699,25 +19756,25 @@
     </row>
     <row r="18" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="n">
-        <v>305457</v>
+        <v>305470</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
       <c r="F18" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G18" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="J18" s="9" t="s">
         <v>78</v>
@@ -19726,31 +19783,31 @@
         <v>70</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>4770.41</v>
+        <v>314.65</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="O18" s="12" t="n">
-        <v>4588.46</v>
+        <v>295.45</v>
       </c>
       <c r="P18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q18" s="13" t="n">
-        <v>0.231499</v>
+        <v>0.016472</v>
       </c>
       <c r="R18" s="12" t="n">
-        <v>35.08</v>
+        <v>1.6</v>
       </c>
       <c r="S18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T18" s="14" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="U18" s="15" t="s">
         <v>72</v>
@@ -19762,16 +19819,16 @@
         <v>73</v>
       </c>
       <c r="X18" s="9" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="Y18" s="12" t="n">
-        <v>181.95</v>
+        <v>19.2</v>
       </c>
       <c r="Z18" s="12" t="n">
-        <v>4588.46</v>
+        <v>295.45</v>
       </c>
       <c r="AA18" s="12" t="n">
-        <v>183.54</v>
+        <v>11.81</v>
       </c>
       <c r="AB18" s="12" t="n">
         <v>0</v>
@@ -19840,7 +19897,7 @@
         <v>76</v>
       </c>
       <c r="AX18" s="10" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="AY18" s="14" t="s">
         <v>75</v>
@@ -19876,7 +19933,7 @@
         <v>78</v>
       </c>
       <c r="BJ18" s="9" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="BK18" s="9" t="s">
         <v>75</v>
@@ -19890,25 +19947,25 @@
     </row>
     <row r="19" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="n">
-        <v>305470</v>
+        <v>305480</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
       <c r="F19" s="9" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G19" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="J19" s="9" t="s">
         <v>78</v>
@@ -19917,31 +19974,31 @@
         <v>70</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>314.65</v>
+        <v>2373.3</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O19" s="12" t="n">
-        <v>295.45</v>
+        <v>2228.46</v>
       </c>
       <c r="P19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q19" s="13" t="n">
-        <v>0.016472</v>
+        <v>0.017186</v>
       </c>
       <c r="R19" s="12" t="n">
-        <v>1.6</v>
+        <v>12.33</v>
       </c>
       <c r="S19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T19" s="14" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="U19" s="15" t="s">
         <v>72</v>
@@ -19953,16 +20010,16 @@
         <v>73</v>
       </c>
       <c r="X19" s="9" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="Y19" s="12" t="n">
-        <v>19.2</v>
+        <v>144.84</v>
       </c>
       <c r="Z19" s="12" t="n">
-        <v>295.45</v>
+        <v>2228.46</v>
       </c>
       <c r="AA19" s="12" t="n">
-        <v>11.81</v>
+        <v>89.14</v>
       </c>
       <c r="AB19" s="12" t="n">
         <v>0</v>
@@ -20031,7 +20088,7 @@
         <v>76</v>
       </c>
       <c r="AX19" s="10" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="AY19" s="14" t="s">
         <v>75</v>
@@ -20067,7 +20124,7 @@
         <v>78</v>
       </c>
       <c r="BJ19" s="9" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="BK19" s="9" t="s">
         <v>75</v>
@@ -20081,52 +20138,52 @@
     </row>
     <row r="20" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="n">
-        <v>305480</v>
+        <v>305539</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
       <c r="F20" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="G20" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="I20" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="J20" s="9" t="s">
         <v>147</v>
-      </c>
-      <c r="G20" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="H20" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="I20" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="J20" s="9" t="s">
-        <v>78</v>
       </c>
       <c r="K20" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>2373.3</v>
+        <v>1568.57</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O20" s="12" t="n">
-        <v>2228.46</v>
+        <v>1568.57</v>
       </c>
       <c r="P20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q20" s="13" t="n">
-        <v>0.017186</v>
+        <v>0.000432</v>
       </c>
       <c r="R20" s="12" t="n">
-        <v>12.33</v>
+        <v>0.74</v>
       </c>
       <c r="S20" s="12" t="n">
         <v>0</v>
@@ -20138,22 +20195,22 @@
         <v>72</v>
       </c>
       <c r="V20" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W20" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X20" s="9" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="Y20" s="12" t="n">
-        <v>144.84</v>
+        <v>0</v>
       </c>
       <c r="Z20" s="12" t="n">
-        <v>2228.46</v>
+        <v>1568.57</v>
       </c>
       <c r="AA20" s="12" t="n">
-        <v>89.14</v>
+        <v>109.8</v>
       </c>
       <c r="AB20" s="12" t="n">
         <v>0</v>
@@ -20222,7 +20279,7 @@
         <v>76</v>
       </c>
       <c r="AX20" s="10" t="s">
-        <v>135</v>
+        <v>77</v>
       </c>
       <c r="AY20" s="14" t="s">
         <v>75</v>
@@ -20272,10 +20329,10 @@
     </row>
     <row r="21" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="n">
-        <v>305539</v>
+        <v>305553</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
@@ -20284,22 +20341,22 @@
         <v>150</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>106</v>
+        <v>128</v>
       </c>
       <c r="I21" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="J21" s="9" t="s">
         <v>151</v>
-      </c>
-      <c r="J21" s="9" t="s">
-        <v>152</v>
       </c>
       <c r="K21" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>1568.57</v>
+        <v>3135.16</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>0</v>
@@ -20308,22 +20365,22 @@
         <v>1</v>
       </c>
       <c r="O21" s="12" t="n">
-        <v>1568.57</v>
+        <v>3135.16</v>
       </c>
       <c r="P21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q21" s="13" t="n">
-        <v>0.000432</v>
+        <v>0.000864</v>
       </c>
       <c r="R21" s="12" t="n">
-        <v>0.74</v>
+        <v>1.48</v>
       </c>
       <c r="S21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T21" s="14" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="U21" s="15" t="s">
         <v>72</v>
@@ -20335,16 +20392,16 @@
         <v>73</v>
       </c>
       <c r="X21" s="9" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="Y21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z21" s="12" t="n">
-        <v>1568.57</v>
+        <v>3135.16</v>
       </c>
       <c r="AA21" s="12" t="n">
-        <v>109.8</v>
+        <v>219.46</v>
       </c>
       <c r="AB21" s="12" t="n">
         <v>0</v>
@@ -20449,7 +20506,7 @@
         <v>78</v>
       </c>
       <c r="BJ21" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="BK21" s="9" t="s">
         <v>75</v>
@@ -20463,34 +20520,34 @@
     </row>
     <row r="22" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="n">
-        <v>305553</v>
+        <v>305554</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
       <c r="F22" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="I22" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="J22" s="9" t="s">
         <v>151</v>
-      </c>
-      <c r="J22" s="9" t="s">
-        <v>156</v>
       </c>
       <c r="K22" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>3135.16</v>
+        <v>3258.14</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>0</v>
@@ -20499,7 +20556,7 @@
         <v>1</v>
       </c>
       <c r="O22" s="12" t="n">
-        <v>3135.16</v>
+        <v>3258.14</v>
       </c>
       <c r="P22" s="12" t="n">
         <v>0</v>
@@ -20514,7 +20571,7 @@
         <v>0</v>
       </c>
       <c r="T22" s="14" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="U22" s="15" t="s">
         <v>72</v>
@@ -20526,16 +20583,16 @@
         <v>73</v>
       </c>
       <c r="X22" s="9" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="Y22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z22" s="12" t="n">
-        <v>3135.16</v>
+        <v>3258.14</v>
       </c>
       <c r="AA22" s="12" t="n">
-        <v>219.46</v>
+        <v>228.07</v>
       </c>
       <c r="AB22" s="12" t="n">
         <v>0</v>
@@ -20640,7 +20697,7 @@
         <v>78</v>
       </c>
       <c r="BJ22" s="9" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="BK22" s="9" t="s">
         <v>75</v>
@@ -20654,34 +20711,34 @@
     </row>
     <row r="23" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="n">
-        <v>305554</v>
+        <v>305556</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="9" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="I23" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="J23" s="9" t="s">
         <v>151</v>
-      </c>
-      <c r="J23" s="9" t="s">
-        <v>156</v>
       </c>
       <c r="K23" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>3258.14</v>
+        <v>5879.02</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>0</v>
@@ -20690,22 +20747,22 @@
         <v>1</v>
       </c>
       <c r="O23" s="12" t="n">
-        <v>3258.14</v>
+        <v>5879.02</v>
       </c>
       <c r="P23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q23" s="13" t="n">
-        <v>0.000864</v>
+        <v>0.467698</v>
       </c>
       <c r="R23" s="12" t="n">
-        <v>1.48</v>
+        <v>31.5</v>
       </c>
       <c r="S23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T23" s="14" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="U23" s="15" t="s">
         <v>72</v>
@@ -20717,16 +20774,16 @@
         <v>73</v>
       </c>
       <c r="X23" s="9" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="Y23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z23" s="12" t="n">
-        <v>3258.14</v>
+        <v>5879.02</v>
       </c>
       <c r="AA23" s="12" t="n">
-        <v>228.07</v>
+        <v>411.53</v>
       </c>
       <c r="AB23" s="12" t="n">
         <v>0</v>
@@ -20831,7 +20888,7 @@
         <v>78</v>
       </c>
       <c r="BJ23" s="9" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="BK23" s="9" t="s">
         <v>75</v>
@@ -20845,34 +20902,34 @@
     </row>
     <row r="24" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="n">
-        <v>305556</v>
+        <v>305560</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
       <c r="F24" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="G24" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="I24" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="J24" s="9" t="s">
         <v>162</v>
-      </c>
-      <c r="G24" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="H24" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="I24" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="J24" s="9" t="s">
-        <v>156</v>
       </c>
       <c r="K24" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>5879.02</v>
+        <v>3121.47</v>
       </c>
       <c r="M24" s="12" t="n">
         <v>0</v>
@@ -20881,16 +20938,16 @@
         <v>1</v>
       </c>
       <c r="O24" s="12" t="n">
-        <v>5879.02</v>
+        <v>3121.47</v>
       </c>
       <c r="P24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q24" s="13" t="n">
-        <v>0.467698</v>
+        <v>0.031059</v>
       </c>
       <c r="R24" s="12" t="n">
-        <v>31.5</v>
+        <v>5.54</v>
       </c>
       <c r="S24" s="12" t="n">
         <v>0</v>
@@ -20908,16 +20965,16 @@
         <v>73</v>
       </c>
       <c r="X24" s="9" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="Y24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z24" s="12" t="n">
-        <v>5879.02</v>
+        <v>3121.47</v>
       </c>
       <c r="AA24" s="12" t="n">
-        <v>411.53</v>
+        <v>218.5</v>
       </c>
       <c r="AB24" s="12" t="n">
         <v>0</v>
@@ -21036,10 +21093,10 @@
     </row>
     <row r="25" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="n">
-        <v>305560</v>
+        <v>305561</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
@@ -21048,22 +21105,22 @@
         <v>165</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="K25" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>3121.47</v>
+        <v>5331.26</v>
       </c>
       <c r="M25" s="12" t="n">
         <v>0</v>
@@ -21072,22 +21129,22 @@
         <v>1</v>
       </c>
       <c r="O25" s="12" t="n">
-        <v>3121.47</v>
+        <v>5005.88</v>
       </c>
       <c r="P25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q25" s="13" t="n">
-        <v>0.031059</v>
+        <v>0.055816</v>
       </c>
       <c r="R25" s="12" t="n">
-        <v>5.54</v>
+        <v>7.12</v>
       </c>
       <c r="S25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T25" s="14" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="U25" s="15" t="s">
         <v>72</v>
@@ -21099,16 +21156,16 @@
         <v>73</v>
       </c>
       <c r="X25" s="9" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="Y25" s="12" t="n">
-        <v>0</v>
+        <v>325.38</v>
       </c>
       <c r="Z25" s="12" t="n">
-        <v>3121.47</v>
+        <v>5005.88</v>
       </c>
       <c r="AA25" s="12" t="n">
-        <v>218.5</v>
+        <v>350.41</v>
       </c>
       <c r="AB25" s="12" t="n">
         <v>0</v>
@@ -21213,7 +21270,7 @@
         <v>78</v>
       </c>
       <c r="BJ25" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="BK25" s="9" t="s">
         <v>75</v>
@@ -21227,34 +21284,34 @@
     </row>
     <row r="26" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="n">
-        <v>305561</v>
+        <v>305681</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="G26" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="J26" s="9" t="s">
         <v>170</v>
-      </c>
-      <c r="G26" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="H26" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="I26" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="J26" s="9" t="s">
-        <v>167</v>
       </c>
       <c r="K26" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>5331.26</v>
+        <v>1945.98</v>
       </c>
       <c r="M26" s="12" t="n">
         <v>0</v>
@@ -21263,16 +21320,16 @@
         <v>1</v>
       </c>
       <c r="O26" s="12" t="n">
-        <v>5005.88</v>
+        <v>1945.98</v>
       </c>
       <c r="P26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q26" s="13" t="n">
-        <v>0.055816</v>
+        <v>0.004946</v>
       </c>
       <c r="R26" s="12" t="n">
-        <v>7.12</v>
+        <v>1.15</v>
       </c>
       <c r="S26" s="12" t="n">
         <v>0</v>
@@ -21290,16 +21347,16 @@
         <v>73</v>
       </c>
       <c r="X26" s="9" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="Y26" s="12" t="n">
-        <v>325.38</v>
+        <v>0</v>
       </c>
       <c r="Z26" s="12" t="n">
-        <v>5005.88</v>
+        <v>1945.98</v>
       </c>
       <c r="AA26" s="12" t="n">
-        <v>350.41</v>
+        <v>136.22</v>
       </c>
       <c r="AB26" s="12" t="n">
         <v>0</v>
@@ -21418,79 +21475,79 @@
     </row>
     <row r="27" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="n">
-        <v>305681</v>
+        <v>305691</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>116</v>
+        <v>173</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>118</v>
+        <v>66</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="J27" s="9" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="K27" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>1945.98</v>
+        <v>3563.51</v>
       </c>
       <c r="M27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O27" s="12" t="n">
-        <v>1945.98</v>
+        <v>3098.7</v>
       </c>
       <c r="P27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q27" s="13" t="n">
-        <v>0.004946</v>
+        <v>0</v>
       </c>
       <c r="R27" s="12" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="S27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T27" s="14" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="U27" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V27" s="12" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="W27" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X27" s="9" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="Y27" s="12" t="n">
-        <v>0</v>
+        <v>464.81</v>
       </c>
       <c r="Z27" s="12" t="n">
-        <v>1945.98</v>
+        <v>3098.7</v>
       </c>
       <c r="AA27" s="12" t="n">
-        <v>136.22</v>
+        <v>216.91</v>
       </c>
       <c r="AB27" s="12" t="n">
         <v>0</v>
@@ -21595,7 +21652,7 @@
         <v>78</v>
       </c>
       <c r="BJ27" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="BK27" s="9" t="s">
         <v>75</v>
@@ -21609,79 +21666,79 @@
     </row>
     <row r="28" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="n">
-        <v>305691</v>
+        <v>305724</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>178</v>
+        <v>111</v>
       </c>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>66</v>
+        <v>113</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>174</v>
+        <v>146</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="K28" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>3563.51</v>
+        <v>1674.18</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O28" s="12" t="n">
-        <v>3098.7</v>
+        <v>1674.18</v>
       </c>
       <c r="P28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q28" s="13" t="n">
-        <v>0</v>
+        <v>0.003916</v>
       </c>
       <c r="R28" s="12" t="n">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="S28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T28" s="14" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="U28" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V28" s="12" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="W28" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X28" s="9" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="Y28" s="12" t="n">
-        <v>464.81</v>
+        <v>0</v>
       </c>
       <c r="Z28" s="12" t="n">
-        <v>3098.7</v>
+        <v>1674.18</v>
       </c>
       <c r="AA28" s="12" t="n">
-        <v>216.91</v>
+        <v>117.19</v>
       </c>
       <c r="AB28" s="12" t="n">
         <v>0</v>
@@ -21786,7 +21843,7 @@
         <v>78</v>
       </c>
       <c r="BJ28" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="BK28" s="9" t="s">
         <v>75</v>
@@ -21800,10 +21857,10 @@
     </row>
     <row r="29" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="n">
-        <v>305724</v>
+        <v>305725</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>116</v>
+        <v>181</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
@@ -21812,46 +21869,46 @@
         <v>182</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>118</v>
+        <v>66</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="K29" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>1674.18</v>
+        <v>10012.8</v>
       </c>
       <c r="M29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O29" s="12" t="n">
-        <v>1674.18</v>
+        <v>10012.8</v>
       </c>
       <c r="P29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q29" s="13" t="n">
-        <v>0.003916</v>
+        <v>0.750038</v>
       </c>
       <c r="R29" s="12" t="n">
-        <v>0.97</v>
+        <v>38</v>
       </c>
       <c r="S29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T29" s="14" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="U29" s="15" t="s">
         <v>72</v>
@@ -21863,16 +21920,16 @@
         <v>73</v>
       </c>
       <c r="X29" s="9" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="Y29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z29" s="12" t="n">
-        <v>1674.18</v>
+        <v>10012.8</v>
       </c>
       <c r="AA29" s="12" t="n">
-        <v>117.19</v>
+        <v>400.51</v>
       </c>
       <c r="AB29" s="12" t="n">
         <v>0</v>
@@ -21977,7 +22034,7 @@
         <v>78</v>
       </c>
       <c r="BJ29" s="9" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="BK29" s="9" t="s">
         <v>75</v>
@@ -21991,34 +22048,34 @@
     </row>
     <row r="30" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="n">
-        <v>305725</v>
+        <v>305731</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>186</v>
+        <v>99</v>
       </c>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
       <c r="F30" s="9" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="G30" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="K30" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>10012.8</v>
+        <v>6247.73</v>
       </c>
       <c r="M30" s="12" t="n">
         <v>0</v>
@@ -22027,22 +22084,22 @@
         <v>2</v>
       </c>
       <c r="O30" s="12" t="n">
-        <v>10012.8</v>
+        <v>6247.73</v>
       </c>
       <c r="P30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q30" s="13" t="n">
-        <v>0.750038</v>
+        <v>0.030808</v>
       </c>
       <c r="R30" s="12" t="n">
-        <v>38</v>
+        <v>6.05</v>
       </c>
       <c r="S30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T30" s="14" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="U30" s="15" t="s">
         <v>72</v>
@@ -22054,16 +22111,16 @@
         <v>73</v>
       </c>
       <c r="X30" s="9" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="Y30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z30" s="12" t="n">
-        <v>10012.8</v>
+        <v>6247.73</v>
       </c>
       <c r="AA30" s="12" t="n">
-        <v>400.51</v>
+        <v>437.34</v>
       </c>
       <c r="AB30" s="12" t="n">
         <v>0</v>
@@ -22168,7 +22225,7 @@
         <v>78</v>
       </c>
       <c r="BJ30" s="9" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="BK30" s="9" t="s">
         <v>75</v>
@@ -22182,34 +22239,34 @@
     </row>
     <row r="31" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="n">
-        <v>305731</v>
+        <v>305778</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>104</v>
+        <v>188</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
       <c r="F31" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G31" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="J31" s="9" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="K31" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>6247.73</v>
+        <v>834.78</v>
       </c>
       <c r="M31" s="12" t="n">
         <v>0</v>
@@ -22218,16 +22275,16 @@
         <v>2</v>
       </c>
       <c r="O31" s="12" t="n">
-        <v>6247.73</v>
+        <v>730</v>
       </c>
       <c r="P31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q31" s="13" t="n">
-        <v>0.030808</v>
+        <v>0</v>
       </c>
       <c r="R31" s="12" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="S31" s="12" t="n">
         <v>0</v>
@@ -22239,22 +22296,22 @@
         <v>72</v>
       </c>
       <c r="V31" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="W31" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X31" s="9" t="s">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="Y31" s="12" t="n">
-        <v>0</v>
+        <v>104.78</v>
       </c>
       <c r="Z31" s="12" t="n">
-        <v>6247.73</v>
+        <v>730</v>
       </c>
       <c r="AA31" s="12" t="n">
-        <v>437.34</v>
+        <v>51.1</v>
       </c>
       <c r="AB31" s="12" t="n">
         <v>0</v>
@@ -22320,7 +22377,7 @@
         <v>74</v>
       </c>
       <c r="AW31" s="14" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="AX31" s="10" t="s">
         <v>77</v>
@@ -22372,603 +22429,1091 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="4"/>
+      <c r="A32" s="8" t="n">
+        <v>305787</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="G32" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="H32" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="I32" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="J32" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="K32" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L32" s="12" t="n">
+        <v>4520.02</v>
+      </c>
+      <c r="M32" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="O32" s="12" t="n">
+        <v>4520.02</v>
+      </c>
+      <c r="P32" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="13" t="n">
+        <v>0.004608</v>
+      </c>
+      <c r="R32" s="12" t="n">
+        <v>36.69</v>
+      </c>
+      <c r="S32" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="U32" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V32" s="12" t="n">
+        <v>55.99</v>
+      </c>
+      <c r="W32" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X32" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="Y32" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="12" t="n">
+        <v>4520.02</v>
+      </c>
+      <c r="AA32" s="12" t="n">
+        <v>316.39</v>
+      </c>
+      <c r="AB32" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="12" t="n">
+        <v>91.25</v>
+      </c>
+      <c r="AE32" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI32" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK32" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL32" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM32" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN32" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO32" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP32" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ32" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR32" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS32" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT32" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU32" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV32" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW32" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX32" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY32" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ32" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA32" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB32" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC32" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD32" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE32" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="BF32" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="BG32" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="BH32" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="BI32" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="BJ32" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="BK32" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="BL32" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM32" s="16" t="s">
+        <v>80</v>
+      </c>
     </row>
-    <row r="33" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="17" t="s">
-        <v>193</v>
-      </c>
-      <c r="B33" s="17"/>
-      <c r="C33" s="17"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="17"/>
-      <c r="G33" s="17"/>
-      <c r="H33" s="17"/>
-      <c r="I33" s="17"/>
-      <c r="J33" s="17"/>
-      <c r="K33" s="17"/>
-      <c r="L33" s="17"/>
-      <c r="M33" s="17"/>
-      <c r="N33" s="17"/>
-      <c r="O33" s="17"/>
-      <c r="P33" s="17"/>
-      <c r="Q33" s="17"/>
-      <c r="R33" s="17"/>
-      <c r="S33" s="17"/>
-      <c r="T33" s="17"/>
-      <c r="U33" s="17"/>
-      <c r="V33" s="17"/>
+    <row r="33" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="8" t="n">
+        <v>305821</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="G33" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="H33" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="I33" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="J33" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="K33" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L33" s="12" t="n">
+        <v>4462.34</v>
+      </c>
+      <c r="M33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O33" s="12" t="n">
+        <v>4462.34</v>
+      </c>
+      <c r="P33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="13" t="n">
+        <v>0.010272</v>
+      </c>
+      <c r="R33" s="12" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="S33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" s="14" t="s">
+        <v>204</v>
+      </c>
+      <c r="U33" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V33" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="W33" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X33" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="Y33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="12" t="n">
+        <v>4462.34</v>
+      </c>
+      <c r="AA33" s="12" t="n">
+        <v>312.36</v>
+      </c>
+      <c r="AB33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ33" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM33" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN33" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO33" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP33" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ33" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR33" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS33" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT33" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU33" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV33" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW33" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX33" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY33" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ33" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA33" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB33" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC33" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD33" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE33" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF33" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG33" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH33" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI33" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ33" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="BK33" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL33" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM33" s="16" t="s">
+        <v>80</v>
+      </c>
     </row>
-    <row r="34" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="18" t="s">
-        <v>194</v>
-      </c>
-      <c r="B34" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C34" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D34" s="18" t="s">
-        <v>195</v>
-      </c>
-      <c r="E34" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F34" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="G34" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="H34" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="I34" s="18" t="s">
-        <v>196</v>
-      </c>
-      <c r="J34" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="K34" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="L34" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="M34" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="N34" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="O34" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="P34" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q34" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="R34" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="S34" s="18" t="s">
-        <v>198</v>
-      </c>
-      <c r="T34" s="18" t="s">
-        <v>199</v>
-      </c>
-      <c r="U34" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="V34" s="18" t="s">
-        <v>37</v>
+    <row r="34" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="8" t="n">
+        <v>305822</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="G34" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="H34" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="I34" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="J34" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="K34" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L34" s="12" t="n">
+        <v>1464.23</v>
+      </c>
+      <c r="M34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O34" s="12" t="n">
+        <v>1464.23</v>
+      </c>
+      <c r="P34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="13" t="n">
+        <v>0.002473</v>
+      </c>
+      <c r="R34" s="12" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="S34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="U34" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V34" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="W34" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X34" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="Y34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="12" t="n">
+        <v>1464.23</v>
+      </c>
+      <c r="AA34" s="12" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="AB34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ34" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM34" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN34" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO34" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP34" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ34" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR34" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS34" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT34" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU34" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV34" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW34" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX34" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY34" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ34" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA34" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB34" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC34" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD34" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE34" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF34" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG34" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH34" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI34" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ34" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="BK34" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL34" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM34" s="16" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="19" t="n">
+      <c r="A35" s="8" t="n">
+        <v>305829</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="9"/>
+      <c r="F35" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="G35" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="H35" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="I35" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="J35" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="K35" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L35" s="12" t="n">
+        <v>3019.02</v>
+      </c>
+      <c r="M35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O35" s="12" t="n">
+        <v>3019.02</v>
+      </c>
+      <c r="P35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="13" t="n">
+        <v>0.004946</v>
+      </c>
+      <c r="R35" s="12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="U35" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V35" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="W35" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X35" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="Y35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" s="12" t="n">
+        <v>3019.02</v>
+      </c>
+      <c r="AA35" s="12" t="n">
+        <v>211.33</v>
+      </c>
+      <c r="AB35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ35" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM35" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN35" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO35" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP35" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ35" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR35" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS35" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT35" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU35" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV35" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW35" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX35" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY35" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ35" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA35" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB35" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC35" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD35" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE35" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF35" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG35" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH35" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI35" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ35" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="BK35" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL35" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM35" s="16" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="4"/>
+    </row>
+    <row r="37" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="17" t="s">
+        <v>212</v>
+      </c>
+      <c r="B37" s="17"/>
+      <c r="C37" s="17"/>
+      <c r="D37" s="17"/>
+      <c r="E37" s="17"/>
+      <c r="F37" s="17"/>
+      <c r="G37" s="17"/>
+      <c r="H37" s="17"/>
+      <c r="I37" s="17"/>
+      <c r="J37" s="17"/>
+      <c r="K37" s="17"/>
+      <c r="L37" s="17"/>
+      <c r="M37" s="17"/>
+      <c r="N37" s="17"/>
+      <c r="O37" s="17"/>
+      <c r="P37" s="17"/>
+      <c r="Q37" s="17"/>
+      <c r="R37" s="17"/>
+      <c r="S37" s="17"/>
+      <c r="T37" s="17"/>
+      <c r="U37" s="17"/>
+      <c r="V37" s="17"/>
+    </row>
+    <row r="38" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="18" t="s">
+        <v>213</v>
+      </c>
+      <c r="B38" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C38" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D38" s="18" t="s">
+        <v>214</v>
+      </c>
+      <c r="E38" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F38" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="G38" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H38" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="B35" s="19" t="n">
+      <c r="I38" s="18" t="s">
+        <v>215</v>
+      </c>
+      <c r="J38" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="K38" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="L38" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="M38" s="18" t="s">
+        <v>216</v>
+      </c>
+      <c r="N38" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="O38" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="P38" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q38" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="R38" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="S38" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="T38" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="U38" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="V38" s="18" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="19" t="n">
+        <v>31</v>
+      </c>
+      <c r="B39" s="19" t="n">
         <v>5811.05</v>
       </c>
-      <c r="C35" s="19" t="n">
+      <c r="C39" s="19" t="n">
         <v>424</v>
       </c>
-      <c r="D35" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" s="19" t="n">
-        <v>4155.55</v>
-      </c>
-      <c r="F35" s="19" t="n">
-        <v>102493.53</v>
-      </c>
-      <c r="G35" s="19" t="n">
-        <v>5834.9</v>
-      </c>
-      <c r="H35" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" s="19" t="n">
-        <v>106649.08</v>
-      </c>
-      <c r="L35" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" s="20" t="n">
-        <v>1.701027</v>
-      </c>
-      <c r="S35" s="19" t="n">
-        <v>107880.58</v>
-      </c>
-      <c r="T35" s="19" t="n">
-        <v>106649.08</v>
-      </c>
-      <c r="U35" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" s="19" t="n">
+      <c r="D39" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="19" t="n">
+        <v>3941.02</v>
+      </c>
+      <c r="F39" s="19" t="n">
+        <v>113414.14</v>
+      </c>
+      <c r="G39" s="19" t="n">
+        <v>6599.33</v>
+      </c>
+      <c r="H39" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="19" t="n">
+        <v>91.25</v>
+      </c>
+      <c r="K39" s="19" t="n">
+        <v>117355.16</v>
+      </c>
+      <c r="L39" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" s="20" t="n">
+        <v>1.699176</v>
+      </c>
+      <c r="S39" s="19" t="n">
+        <v>118801.19</v>
+      </c>
+      <c r="T39" s="19" t="n">
+        <v>117355.16</v>
+      </c>
+      <c r="U39" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" s="19" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="18" t="s">
+    <row r="40" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="B36" s="18" t="s">
+      <c r="B40" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="C36" s="18" t="s">
+      <c r="C40" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="D36" s="18" t="s">
+      <c r="D40" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="E36" s="18" t="s">
+      <c r="E40" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="F36" s="18" t="s">
+      <c r="F40" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="G36" s="18" t="s">
+      <c r="G40" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="H36" s="18" t="s">
+      <c r="H40" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="I36" s="18" t="s">
+      <c r="I40" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="J36" s="18" t="s">
+      <c r="J40" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="K36" s="18" t="s">
-        <v>200</v>
-      </c>
-      <c r="L36" s="18" t="s">
-        <v>201</v>
-      </c>
-      <c r="M36" s="18" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="19" t="n">
-        <v>175.94</v>
-      </c>
-      <c r="B37" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C37" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" s="19" t="n">
-        <v>48.85</v>
-      </c>
-      <c r="E37" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" s="19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="4"/>
-    </row>
-    <row r="39" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="21" t="s">
-        <v>203</v>
-      </c>
-      <c r="B39" s="21"/>
-      <c r="C39" s="21"/>
-      <c r="D39" s="21"/>
-      <c r="E39" s="21"/>
-      <c r="F39" s="21"/>
-      <c r="G39" s="21"/>
-      <c r="H39" s="21"/>
-      <c r="I39" s="21"/>
-      <c r="J39" s="21"/>
-      <c r="K39" s="21"/>
-      <c r="L39" s="21"/>
-      <c r="M39" s="21"/>
-      <c r="N39" s="21"/>
-      <c r="O39" s="21"/>
-      <c r="P39" s="21"/>
-      <c r="Q39" s="21"/>
-      <c r="R39" s="21"/>
-      <c r="S39" s="21"/>
-      <c r="T39" s="21"/>
-      <c r="U39" s="21"/>
-      <c r="V39" s="21"/>
-      <c r="W39" s="21"/>
-      <c r="X39" s="21"/>
-      <c r="Y39" s="21"/>
-      <c r="Z39" s="21"/>
-      <c r="AA39" s="21"/>
-      <c r="AB39" s="21"/>
-      <c r="AC39" s="21"/>
-      <c r="AD39" s="21"/>
-      <c r="AE39" s="21"/>
-      <c r="AF39" s="21"/>
-      <c r="AG39" s="21"/>
-      <c r="AH39" s="21"/>
-      <c r="AI39" s="21"/>
-      <c r="AJ39" s="21"/>
-      <c r="AK39" s="21"/>
-      <c r="AL39" s="21"/>
-      <c r="AM39" s="21"/>
-      <c r="AN39" s="21"/>
-      <c r="AO39" s="21"/>
-      <c r="AP39" s="21"/>
-      <c r="AQ39" s="21"/>
-      <c r="AR39" s="21"/>
-      <c r="AS39" s="21"/>
-      <c r="AT39" s="21"/>
-      <c r="AU39" s="21"/>
-      <c r="AV39" s="21"/>
-      <c r="AW39" s="21"/>
-      <c r="AX39" s="21"/>
-      <c r="AY39" s="21"/>
-      <c r="AZ39" s="21"/>
-      <c r="BA39" s="21"/>
-      <c r="BB39" s="21"/>
-      <c r="BC39" s="21"/>
-      <c r="BD39" s="21"/>
-      <c r="BE39" s="21"/>
-      <c r="BF39" s="21"/>
-      <c r="BG39" s="21"/>
-      <c r="BH39" s="21"/>
-      <c r="BI39" s="21"/>
-      <c r="BJ39" s="21"/>
-      <c r="BK39" s="21"/>
-      <c r="BL39" s="21"/>
-      <c r="BM39" s="21"/>
-    </row>
-    <row r="40" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B40" s="4"/>
-      <c r="C40" s="4"/>
-      <c r="D40" s="4"/>
-      <c r="E40" s="4"/>
-      <c r="F40" s="4"/>
-      <c r="G40" s="4"/>
-      <c r="H40" s="4"/>
-      <c r="I40" s="4"/>
-      <c r="J40" s="4"/>
-      <c r="K40" s="4"/>
-      <c r="L40" s="4"/>
-      <c r="M40" s="4"/>
-      <c r="N40" s="4"/>
-      <c r="O40" s="4"/>
-      <c r="P40" s="4"/>
-      <c r="Q40" s="4"/>
-      <c r="R40" s="4"/>
-      <c r="S40" s="4"/>
-      <c r="T40" s="4"/>
-      <c r="U40" s="4"/>
-      <c r="V40" s="4"/>
-      <c r="W40" s="4"/>
-      <c r="X40" s="4"/>
-      <c r="Y40" s="4"/>
-      <c r="Z40" s="4"/>
-      <c r="AA40" s="4"/>
-      <c r="AB40" s="4"/>
-      <c r="AC40" s="4"/>
-      <c r="AD40" s="4"/>
-      <c r="AE40" s="4"/>
-      <c r="AF40" s="4"/>
-      <c r="AG40" s="4"/>
-      <c r="AH40" s="4"/>
-      <c r="AI40" s="4"/>
-      <c r="AJ40" s="4"/>
-      <c r="AK40" s="4"/>
-      <c r="AL40" s="4"/>
-      <c r="AM40" s="4"/>
-      <c r="AN40" s="4"/>
-      <c r="AO40" s="4"/>
-      <c r="AP40" s="4"/>
-      <c r="AQ40" s="4"/>
-      <c r="AR40" s="4"/>
-      <c r="AS40" s="4"/>
-      <c r="AT40" s="4"/>
-      <c r="AU40" s="4"/>
-      <c r="AV40" s="4"/>
-      <c r="AW40" s="4"/>
-      <c r="AX40" s="4"/>
-      <c r="AY40" s="4"/>
-      <c r="AZ40" s="4"/>
-      <c r="BA40" s="4"/>
-      <c r="BB40" s="4"/>
-      <c r="BC40" s="4"/>
-      <c r="BD40" s="4"/>
-      <c r="BE40" s="4"/>
-      <c r="BF40" s="4"/>
-      <c r="BG40" s="4"/>
-      <c r="BH40" s="4"/>
-      <c r="BI40" s="4"/>
-      <c r="BJ40" s="4"/>
-      <c r="BK40" s="4"/>
-      <c r="BL40" s="4"/>
-      <c r="BM40" s="4"/>
+      <c r="K40" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="L40" s="18" t="s">
+        <v>220</v>
+      </c>
+      <c r="M40" s="18" t="s">
+        <v>221</v>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="B41" s="4"/>
-      <c r="C41" s="4"/>
-      <c r="D41" s="4"/>
-      <c r="E41" s="4"/>
-      <c r="F41" s="4"/>
-      <c r="G41" s="4"/>
-      <c r="H41" s="4"/>
-      <c r="I41" s="4"/>
-      <c r="J41" s="4"/>
-      <c r="K41" s="4"/>
-      <c r="L41" s="4"/>
-      <c r="M41" s="4"/>
-      <c r="N41" s="4"/>
-      <c r="O41" s="4"/>
-      <c r="P41" s="4"/>
-      <c r="Q41" s="4"/>
-      <c r="R41" s="4"/>
-      <c r="S41" s="4"/>
-      <c r="T41" s="4"/>
-      <c r="U41" s="4"/>
-      <c r="V41" s="4"/>
-      <c r="W41" s="4"/>
-      <c r="X41" s="4"/>
-      <c r="Y41" s="4"/>
-      <c r="Z41" s="4"/>
-      <c r="AA41" s="4"/>
-      <c r="AB41" s="4"/>
-      <c r="AC41" s="4"/>
-      <c r="AD41" s="4"/>
-      <c r="AE41" s="4"/>
-      <c r="AF41" s="4"/>
-      <c r="AG41" s="4"/>
-      <c r="AH41" s="4"/>
-      <c r="AI41" s="4"/>
-      <c r="AJ41" s="4"/>
-      <c r="AK41" s="4"/>
-      <c r="AL41" s="4"/>
-      <c r="AM41" s="4"/>
-      <c r="AN41" s="4"/>
-      <c r="AO41" s="4"/>
-      <c r="AP41" s="4"/>
-      <c r="AQ41" s="4"/>
-      <c r="AR41" s="4"/>
-      <c r="AS41" s="4"/>
-      <c r="AT41" s="4"/>
-      <c r="AU41" s="4"/>
-      <c r="AV41" s="4"/>
-      <c r="AW41" s="4"/>
-      <c r="AX41" s="4"/>
-      <c r="AY41" s="4"/>
-      <c r="AZ41" s="4"/>
-      <c r="BA41" s="4"/>
-      <c r="BB41" s="4"/>
-      <c r="BC41" s="4"/>
-      <c r="BD41" s="4"/>
-      <c r="BE41" s="4"/>
-      <c r="BF41" s="4"/>
-      <c r="BG41" s="4"/>
-      <c r="BH41" s="4"/>
-      <c r="BI41" s="4"/>
-      <c r="BJ41" s="4"/>
-      <c r="BK41" s="4"/>
-      <c r="BL41" s="4"/>
-      <c r="BM41" s="4"/>
+      <c r="A41" s="19" t="n">
+        <v>216.63</v>
+      </c>
+      <c r="B41" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="19" t="n">
+        <v>47.81</v>
+      </c>
+      <c r="E41" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="B42" s="4"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="4"/>
-      <c r="E42" s="4"/>
-      <c r="F42" s="4"/>
-      <c r="G42" s="4"/>
-      <c r="H42" s="4"/>
-      <c r="I42" s="4"/>
-      <c r="J42" s="4"/>
-      <c r="K42" s="4"/>
-      <c r="L42" s="4"/>
-      <c r="M42" s="4"/>
-      <c r="N42" s="4"/>
-      <c r="O42" s="4"/>
-      <c r="P42" s="4"/>
-      <c r="Q42" s="4"/>
-      <c r="R42" s="4"/>
-      <c r="S42" s="4"/>
-      <c r="T42" s="4"/>
-      <c r="U42" s="4"/>
-      <c r="V42" s="4"/>
-      <c r="W42" s="4"/>
-      <c r="X42" s="4"/>
-      <c r="Y42" s="4"/>
-      <c r="Z42" s="4"/>
-      <c r="AA42" s="4"/>
-      <c r="AB42" s="4"/>
-      <c r="AC42" s="4"/>
-      <c r="AD42" s="4"/>
-      <c r="AE42" s="4"/>
-      <c r="AF42" s="4"/>
-      <c r="AG42" s="4"/>
-      <c r="AH42" s="4"/>
-      <c r="AI42" s="4"/>
-      <c r="AJ42" s="4"/>
-      <c r="AK42" s="4"/>
-      <c r="AL42" s="4"/>
-      <c r="AM42" s="4"/>
-      <c r="AN42" s="4"/>
-      <c r="AO42" s="4"/>
-      <c r="AP42" s="4"/>
-      <c r="AQ42" s="4"/>
-      <c r="AR42" s="4"/>
-      <c r="AS42" s="4"/>
-      <c r="AT42" s="4"/>
-      <c r="AU42" s="4"/>
-      <c r="AV42" s="4"/>
-      <c r="AW42" s="4"/>
-      <c r="AX42" s="4"/>
-      <c r="AY42" s="4"/>
-      <c r="AZ42" s="4"/>
-      <c r="BA42" s="4"/>
-      <c r="BB42" s="4"/>
-      <c r="BC42" s="4"/>
-      <c r="BD42" s="4"/>
-      <c r="BE42" s="4"/>
-      <c r="BF42" s="4"/>
-      <c r="BG42" s="4"/>
-      <c r="BH42" s="4"/>
-      <c r="BI42" s="4"/>
-      <c r="BJ42" s="4"/>
-      <c r="BK42" s="4"/>
-      <c r="BL42" s="4"/>
-      <c r="BM42" s="4"/>
+      <c r="A42" s="4"/>
     </row>
-    <row r="43" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="B43" s="4"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="4"/>
-      <c r="E43" s="4"/>
-      <c r="F43" s="4"/>
-      <c r="G43" s="4"/>
-      <c r="H43" s="4"/>
-      <c r="I43" s="4"/>
-      <c r="J43" s="4"/>
-      <c r="K43" s="4"/>
-      <c r="L43" s="4"/>
-      <c r="M43" s="4"/>
-      <c r="N43" s="4"/>
-      <c r="O43" s="4"/>
-      <c r="P43" s="4"/>
-      <c r="Q43" s="4"/>
-      <c r="R43" s="4"/>
-      <c r="S43" s="4"/>
-      <c r="T43" s="4"/>
-      <c r="U43" s="4"/>
-      <c r="V43" s="4"/>
-      <c r="W43" s="4"/>
-      <c r="X43" s="4"/>
-      <c r="Y43" s="4"/>
-      <c r="Z43" s="4"/>
-      <c r="AA43" s="4"/>
-      <c r="AB43" s="4"/>
-      <c r="AC43" s="4"/>
-      <c r="AD43" s="4"/>
-      <c r="AE43" s="4"/>
-      <c r="AF43" s="4"/>
-      <c r="AG43" s="4"/>
-      <c r="AH43" s="4"/>
-      <c r="AI43" s="4"/>
-      <c r="AJ43" s="4"/>
-      <c r="AK43" s="4"/>
-      <c r="AL43" s="4"/>
-      <c r="AM43" s="4"/>
-      <c r="AN43" s="4"/>
-      <c r="AO43" s="4"/>
-      <c r="AP43" s="4"/>
-      <c r="AQ43" s="4"/>
-      <c r="AR43" s="4"/>
-      <c r="AS43" s="4"/>
-      <c r="AT43" s="4"/>
-      <c r="AU43" s="4"/>
-      <c r="AV43" s="4"/>
-      <c r="AW43" s="4"/>
-      <c r="AX43" s="4"/>
-      <c r="AY43" s="4"/>
-      <c r="AZ43" s="4"/>
-      <c r="BA43" s="4"/>
-      <c r="BB43" s="4"/>
-      <c r="BC43" s="4"/>
-      <c r="BD43" s="4"/>
-      <c r="BE43" s="4"/>
-      <c r="BF43" s="4"/>
-      <c r="BG43" s="4"/>
-      <c r="BH43" s="4"/>
-      <c r="BI43" s="4"/>
-      <c r="BJ43" s="4"/>
-      <c r="BK43" s="4"/>
-      <c r="BL43" s="4"/>
-      <c r="BM43" s="4"/>
+    <row r="43" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="21" t="s">
+        <v>222</v>
+      </c>
+      <c r="B43" s="21"/>
+      <c r="C43" s="21"/>
+      <c r="D43" s="21"/>
+      <c r="E43" s="21"/>
+      <c r="F43" s="21"/>
+      <c r="G43" s="21"/>
+      <c r="H43" s="21"/>
+      <c r="I43" s="21"/>
+      <c r="J43" s="21"/>
+      <c r="K43" s="21"/>
+      <c r="L43" s="21"/>
+      <c r="M43" s="21"/>
+      <c r="N43" s="21"/>
+      <c r="O43" s="21"/>
+      <c r="P43" s="21"/>
+      <c r="Q43" s="21"/>
+      <c r="R43" s="21"/>
+      <c r="S43" s="21"/>
+      <c r="T43" s="21"/>
+      <c r="U43" s="21"/>
+      <c r="V43" s="21"/>
+      <c r="W43" s="21"/>
+      <c r="X43" s="21"/>
+      <c r="Y43" s="21"/>
+      <c r="Z43" s="21"/>
+      <c r="AA43" s="21"/>
+      <c r="AB43" s="21"/>
+      <c r="AC43" s="21"/>
+      <c r="AD43" s="21"/>
+      <c r="AE43" s="21"/>
+      <c r="AF43" s="21"/>
+      <c r="AG43" s="21"/>
+      <c r="AH43" s="21"/>
+      <c r="AI43" s="21"/>
+      <c r="AJ43" s="21"/>
+      <c r="AK43" s="21"/>
+      <c r="AL43" s="21"/>
+      <c r="AM43" s="21"/>
+      <c r="AN43" s="21"/>
+      <c r="AO43" s="21"/>
+      <c r="AP43" s="21"/>
+      <c r="AQ43" s="21"/>
+      <c r="AR43" s="21"/>
+      <c r="AS43" s="21"/>
+      <c r="AT43" s="21"/>
+      <c r="AU43" s="21"/>
+      <c r="AV43" s="21"/>
+      <c r="AW43" s="21"/>
+      <c r="AX43" s="21"/>
+      <c r="AY43" s="21"/>
+      <c r="AZ43" s="21"/>
+      <c r="BA43" s="21"/>
+      <c r="BB43" s="21"/>
+      <c r="BC43" s="21"/>
+      <c r="BD43" s="21"/>
+      <c r="BE43" s="21"/>
+      <c r="BF43" s="21"/>
+      <c r="BG43" s="21"/>
+      <c r="BH43" s="21"/>
+      <c r="BI43" s="21"/>
+      <c r="BJ43" s="21"/>
+      <c r="BK43" s="21"/>
+      <c r="BL43" s="21"/>
+      <c r="BM43" s="21"/>
     </row>
     <row r="44" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="s">
-        <v>22</v>
+        <v>75</v>
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
@@ -23037,7 +23582,7 @@
     </row>
     <row r="45" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="4" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
@@ -23106,7 +23651,7 @@
     </row>
     <row r="46" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="4" t="s">
-        <v>208</v>
+        <v>224</v>
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
@@ -23175,7 +23720,7 @@
     </row>
     <row r="47" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="s">
-        <v>209</v>
+        <v>225</v>
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
@@ -23244,7 +23789,7 @@
     </row>
     <row r="48" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="4" t="s">
-        <v>210</v>
+        <v>22</v>
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
@@ -23313,7 +23858,7 @@
     </row>
     <row r="49" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="4" t="s">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
@@ -23380,8 +23925,284 @@
       <c r="BL49" s="4"/>
       <c r="BM49" s="4"/>
     </row>
+    <row r="50" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B50" s="4"/>
+      <c r="C50" s="4"/>
+      <c r="D50" s="4"/>
+      <c r="E50" s="4"/>
+      <c r="F50" s="4"/>
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="K50" s="4"/>
+      <c r="L50" s="4"/>
+      <c r="M50" s="4"/>
+      <c r="N50" s="4"/>
+      <c r="O50" s="4"/>
+      <c r="P50" s="4"/>
+      <c r="Q50" s="4"/>
+      <c r="R50" s="4"/>
+      <c r="S50" s="4"/>
+      <c r="T50" s="4"/>
+      <c r="U50" s="4"/>
+      <c r="V50" s="4"/>
+      <c r="W50" s="4"/>
+      <c r="X50" s="4"/>
+      <c r="Y50" s="4"/>
+      <c r="Z50" s="4"/>
+      <c r="AA50" s="4"/>
+      <c r="AB50" s="4"/>
+      <c r="AC50" s="4"/>
+      <c r="AD50" s="4"/>
+      <c r="AE50" s="4"/>
+      <c r="AF50" s="4"/>
+      <c r="AG50" s="4"/>
+      <c r="AH50" s="4"/>
+      <c r="AI50" s="4"/>
+      <c r="AJ50" s="4"/>
+      <c r="AK50" s="4"/>
+      <c r="AL50" s="4"/>
+      <c r="AM50" s="4"/>
+      <c r="AN50" s="4"/>
+      <c r="AO50" s="4"/>
+      <c r="AP50" s="4"/>
+      <c r="AQ50" s="4"/>
+      <c r="AR50" s="4"/>
+      <c r="AS50" s="4"/>
+      <c r="AT50" s="4"/>
+      <c r="AU50" s="4"/>
+      <c r="AV50" s="4"/>
+      <c r="AW50" s="4"/>
+      <c r="AX50" s="4"/>
+      <c r="AY50" s="4"/>
+      <c r="AZ50" s="4"/>
+      <c r="BA50" s="4"/>
+      <c r="BB50" s="4"/>
+      <c r="BC50" s="4"/>
+      <c r="BD50" s="4"/>
+      <c r="BE50" s="4"/>
+      <c r="BF50" s="4"/>
+      <c r="BG50" s="4"/>
+      <c r="BH50" s="4"/>
+      <c r="BI50" s="4"/>
+      <c r="BJ50" s="4"/>
+      <c r="BK50" s="4"/>
+      <c r="BL50" s="4"/>
+      <c r="BM50" s="4"/>
+    </row>
+    <row r="51" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="B51" s="4"/>
+      <c r="C51" s="4"/>
+      <c r="D51" s="4"/>
+      <c r="E51" s="4"/>
+      <c r="F51" s="4"/>
+      <c r="G51" s="4"/>
+      <c r="H51" s="4"/>
+      <c r="I51" s="4"/>
+      <c r="J51" s="4"/>
+      <c r="K51" s="4"/>
+      <c r="L51" s="4"/>
+      <c r="M51" s="4"/>
+      <c r="N51" s="4"/>
+      <c r="O51" s="4"/>
+      <c r="P51" s="4"/>
+      <c r="Q51" s="4"/>
+      <c r="R51" s="4"/>
+      <c r="S51" s="4"/>
+      <c r="T51" s="4"/>
+      <c r="U51" s="4"/>
+      <c r="V51" s="4"/>
+      <c r="W51" s="4"/>
+      <c r="X51" s="4"/>
+      <c r="Y51" s="4"/>
+      <c r="Z51" s="4"/>
+      <c r="AA51" s="4"/>
+      <c r="AB51" s="4"/>
+      <c r="AC51" s="4"/>
+      <c r="AD51" s="4"/>
+      <c r="AE51" s="4"/>
+      <c r="AF51" s="4"/>
+      <c r="AG51" s="4"/>
+      <c r="AH51" s="4"/>
+      <c r="AI51" s="4"/>
+      <c r="AJ51" s="4"/>
+      <c r="AK51" s="4"/>
+      <c r="AL51" s="4"/>
+      <c r="AM51" s="4"/>
+      <c r="AN51" s="4"/>
+      <c r="AO51" s="4"/>
+      <c r="AP51" s="4"/>
+      <c r="AQ51" s="4"/>
+      <c r="AR51" s="4"/>
+      <c r="AS51" s="4"/>
+      <c r="AT51" s="4"/>
+      <c r="AU51" s="4"/>
+      <c r="AV51" s="4"/>
+      <c r="AW51" s="4"/>
+      <c r="AX51" s="4"/>
+      <c r="AY51" s="4"/>
+      <c r="AZ51" s="4"/>
+      <c r="BA51" s="4"/>
+      <c r="BB51" s="4"/>
+      <c r="BC51" s="4"/>
+      <c r="BD51" s="4"/>
+      <c r="BE51" s="4"/>
+      <c r="BF51" s="4"/>
+      <c r="BG51" s="4"/>
+      <c r="BH51" s="4"/>
+      <c r="BI51" s="4"/>
+      <c r="BJ51" s="4"/>
+      <c r="BK51" s="4"/>
+      <c r="BL51" s="4"/>
+      <c r="BM51" s="4"/>
+    </row>
+    <row r="52" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="B52" s="4"/>
+      <c r="C52" s="4"/>
+      <c r="D52" s="4"/>
+      <c r="E52" s="4"/>
+      <c r="F52" s="4"/>
+      <c r="G52" s="4"/>
+      <c r="H52" s="4"/>
+      <c r="I52" s="4"/>
+      <c r="J52" s="4"/>
+      <c r="K52" s="4"/>
+      <c r="L52" s="4"/>
+      <c r="M52" s="4"/>
+      <c r="N52" s="4"/>
+      <c r="O52" s="4"/>
+      <c r="P52" s="4"/>
+      <c r="Q52" s="4"/>
+      <c r="R52" s="4"/>
+      <c r="S52" s="4"/>
+      <c r="T52" s="4"/>
+      <c r="U52" s="4"/>
+      <c r="V52" s="4"/>
+      <c r="W52" s="4"/>
+      <c r="X52" s="4"/>
+      <c r="Y52" s="4"/>
+      <c r="Z52" s="4"/>
+      <c r="AA52" s="4"/>
+      <c r="AB52" s="4"/>
+      <c r="AC52" s="4"/>
+      <c r="AD52" s="4"/>
+      <c r="AE52" s="4"/>
+      <c r="AF52" s="4"/>
+      <c r="AG52" s="4"/>
+      <c r="AH52" s="4"/>
+      <c r="AI52" s="4"/>
+      <c r="AJ52" s="4"/>
+      <c r="AK52" s="4"/>
+      <c r="AL52" s="4"/>
+      <c r="AM52" s="4"/>
+      <c r="AN52" s="4"/>
+      <c r="AO52" s="4"/>
+      <c r="AP52" s="4"/>
+      <c r="AQ52" s="4"/>
+      <c r="AR52" s="4"/>
+      <c r="AS52" s="4"/>
+      <c r="AT52" s="4"/>
+      <c r="AU52" s="4"/>
+      <c r="AV52" s="4"/>
+      <c r="AW52" s="4"/>
+      <c r="AX52" s="4"/>
+      <c r="AY52" s="4"/>
+      <c r="AZ52" s="4"/>
+      <c r="BA52" s="4"/>
+      <c r="BB52" s="4"/>
+      <c r="BC52" s="4"/>
+      <c r="BD52" s="4"/>
+      <c r="BE52" s="4"/>
+      <c r="BF52" s="4"/>
+      <c r="BG52" s="4"/>
+      <c r="BH52" s="4"/>
+      <c r="BI52" s="4"/>
+      <c r="BJ52" s="4"/>
+      <c r="BK52" s="4"/>
+      <c r="BL52" s="4"/>
+      <c r="BM52" s="4"/>
+    </row>
+    <row r="53" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="B53" s="4"/>
+      <c r="C53" s="4"/>
+      <c r="D53" s="4"/>
+      <c r="E53" s="4"/>
+      <c r="F53" s="4"/>
+      <c r="G53" s="4"/>
+      <c r="H53" s="4"/>
+      <c r="I53" s="4"/>
+      <c r="J53" s="4"/>
+      <c r="K53" s="4"/>
+      <c r="L53" s="4"/>
+      <c r="M53" s="4"/>
+      <c r="N53" s="4"/>
+      <c r="O53" s="4"/>
+      <c r="P53" s="4"/>
+      <c r="Q53" s="4"/>
+      <c r="R53" s="4"/>
+      <c r="S53" s="4"/>
+      <c r="T53" s="4"/>
+      <c r="U53" s="4"/>
+      <c r="V53" s="4"/>
+      <c r="W53" s="4"/>
+      <c r="X53" s="4"/>
+      <c r="Y53" s="4"/>
+      <c r="Z53" s="4"/>
+      <c r="AA53" s="4"/>
+      <c r="AB53" s="4"/>
+      <c r="AC53" s="4"/>
+      <c r="AD53" s="4"/>
+      <c r="AE53" s="4"/>
+      <c r="AF53" s="4"/>
+      <c r="AG53" s="4"/>
+      <c r="AH53" s="4"/>
+      <c r="AI53" s="4"/>
+      <c r="AJ53" s="4"/>
+      <c r="AK53" s="4"/>
+      <c r="AL53" s="4"/>
+      <c r="AM53" s="4"/>
+      <c r="AN53" s="4"/>
+      <c r="AO53" s="4"/>
+      <c r="AP53" s="4"/>
+      <c r="AQ53" s="4"/>
+      <c r="AR53" s="4"/>
+      <c r="AS53" s="4"/>
+      <c r="AT53" s="4"/>
+      <c r="AU53" s="4"/>
+      <c r="AV53" s="4"/>
+      <c r="AW53" s="4"/>
+      <c r="AX53" s="4"/>
+      <c r="AY53" s="4"/>
+      <c r="AZ53" s="4"/>
+      <c r="BA53" s="4"/>
+      <c r="BB53" s="4"/>
+      <c r="BC53" s="4"/>
+      <c r="BD53" s="4"/>
+      <c r="BE53" s="4"/>
+      <c r="BF53" s="4"/>
+      <c r="BG53" s="4"/>
+      <c r="BH53" s="4"/>
+      <c r="BI53" s="4"/>
+      <c r="BJ53" s="4"/>
+      <c r="BK53" s="4"/>
+      <c r="BL53" s="4"/>
+      <c r="BM53" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="43">
+  <mergeCells count="47">
     <mergeCell ref="A1:BI1"/>
     <mergeCell ref="BJ1:BM1"/>
     <mergeCell ref="A2:BM2"/>
@@ -23413,11 +24234,11 @@
     <mergeCell ref="B29:E29"/>
     <mergeCell ref="B30:E30"/>
     <mergeCell ref="B31:E31"/>
-    <mergeCell ref="A33:V33"/>
-    <mergeCell ref="A39:BM39"/>
-    <mergeCell ref="A40:BM40"/>
-    <mergeCell ref="A41:BM41"/>
-    <mergeCell ref="A42:BM42"/>
+    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="B34:E34"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="A37:V37"/>
     <mergeCell ref="A43:BM43"/>
     <mergeCell ref="A44:BM44"/>
     <mergeCell ref="A45:BM45"/>
@@ -23425,6 +24246,10 @@
     <mergeCell ref="A47:BM47"/>
     <mergeCell ref="A48:BM48"/>
     <mergeCell ref="A49:BM49"/>
+    <mergeCell ref="A50:BM50"/>
+    <mergeCell ref="A51:BM51"/>
+    <mergeCell ref="A52:BM52"/>
+    <mergeCell ref="A53:BM53"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>

--- a/tratando_tabelas/finitura/entradas_finitura.xlsx
+++ b/tratando_tabelas/finitura/entradas_finitura.xlsx
@@ -20,12 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1352" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1392" uniqueCount="227">
   <si>
     <t xml:space="preserve">Santri ADM 1.1.5.7 R1</t>
   </si>
   <si>
-    <t xml:space="preserve">Emitido em: 27/04/2026 08:59:35</t>
+    <t xml:space="preserve">Emitido em: 28/04/2026 05:30:25</t>
   </si>
   <si>
     <t xml:space="preserve">Relação de entradas - Sintético</t>
@@ -214,28 +214,28 @@
     <t xml:space="preserve">Fornecedor substituto tributário</t>
   </si>
   <si>
-    <t xml:space="preserve">16.540 - LEXXA METAIS SANITARIOS LTDA</t>
+    <t xml:space="preserve">16.059 - JLR COM IMPORT. E EXP. DE MATERIAIS DE CONSTRUCAO LTDA</t>
   </si>
   <si>
-    <t xml:space="preserve">10.764</t>
+    <t xml:space="preserve">11.966</t>
   </si>
   <si>
     <t xml:space="preserve">1</t>
   </si>
   <si>
-    <t xml:space="preserve">08/04/2026</t>
+    <t xml:space="preserve">06/04/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">09/04/2026</t>
+    <t xml:space="preserve">10/04/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">06/05/2026</t>
+    <t xml:space="preserve">05/06/2026</t>
   </si>
   <si>
     <t xml:space="preserve">XML</t>
   </si>
   <si>
-    <t xml:space="preserve">1.839,76</t>
+    <t xml:space="preserve">25.242,00</t>
   </si>
   <si>
     <t xml:space="preserve">Ag. chegada da mercadoria</t>
@@ -250,7 +250,7 @@
     <t xml:space="preserve"/>
   </si>
   <si>
-    <t xml:space="preserve">N</t>
+    <t xml:space="preserve">S</t>
   </si>
   <si>
     <t xml:space="preserve">2.102</t>
@@ -259,34 +259,10 @@
     <t xml:space="preserve">          </t>
   </si>
   <si>
-    <t xml:space="preserve">42260400700221000253550010000107641845284938</t>
+    <t xml:space="preserve">41260417781412000109550010000119661000316126</t>
   </si>
   <si>
     <t xml:space="preserve">Não</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.059 - JLR COM IMPORT. E EXP. DE MATERIAIS DE CONSTRUCAO LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.242,00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41260417781412000109550010000119661000316126</t>
   </si>
   <si>
     <t xml:space="preserve">11.969</t>
@@ -295,46 +271,13 @@
     <t xml:space="preserve">1.818,78</t>
   </si>
   <si>
+    <t xml:space="preserve">N</t>
+  </si>
+  <si>
     <t xml:space="preserve">2.910</t>
   </si>
   <si>
     <t xml:space="preserve">41260417781412000109550010000119691000316152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.941 - AQUECE METAIS FABRICACAO E MANUTENCAO LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.418,46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43260427254297000178550010000104561755610073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.856 - DEXCO S.A - METAIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.064.033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">542,51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050640331969596239</t>
   </si>
   <si>
     <t xml:space="preserve">10.343 - INTERLIGHT SISTEMAS DE ILUMINACAO LTDA</t>
@@ -344,6 +287,9 @@
   </si>
   <si>
     <t xml:space="preserve">15/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16/04/2026</t>
   </si>
   <si>
     <t xml:space="preserve">13/05/2026</t>
@@ -401,6 +347,9 @@
   </si>
   <si>
     <t xml:space="preserve">42260475339051000141550080006129431856669777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.856 - DEXCO S.A - METAIS</t>
   </si>
   <si>
     <t xml:space="preserve">5.064.044</t>
@@ -656,6 +605,45 @@
   </si>
   <si>
     <t xml:space="preserve">42260475339051000141550080006223901051401241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.069.526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">366,64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050695261009694039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.069.532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42,44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050695321391333760</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.071.467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126,70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050714671217480571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.071.473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">290,09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050714731527694305</t>
   </si>
   <si>
     <t xml:space="preserve">Total geral</t>
@@ -16901,7 +16889,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BM53"/>
+  <dimension ref="A1:BM54"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="18"/>
@@ -17273,7 +17261,7 @@
     </row>
     <row r="5" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="n">
-        <v>304801</v>
+        <v>304880</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>64</v>
@@ -17300,25 +17288,25 @@
         <v>70</v>
       </c>
       <c r="L5" s="12" t="n">
-        <v>1839.76</v>
+        <v>25242</v>
       </c>
       <c r="M5" s="12" t="n">
-        <v>0</v>
+        <v>5811.05</v>
       </c>
       <c r="N5" s="12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="O5" s="12" t="n">
-        <v>1680.76</v>
+        <v>28810.6</v>
       </c>
       <c r="P5" s="12" t="n">
-        <v>159</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R5" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S5" s="12" t="n">
         <v>0</v>
@@ -17330,7 +17318,7 @@
         <v>72</v>
       </c>
       <c r="V5" s="12" t="n">
-        <v>28</v>
+        <v>120</v>
       </c>
       <c r="W5" s="9" t="s">
         <v>73</v>
@@ -17339,13 +17327,13 @@
         <v>68</v>
       </c>
       <c r="Y5" s="12" t="n">
-        <v>0</v>
+        <v>2242.45</v>
       </c>
       <c r="Z5" s="12" t="n">
-        <v>1839.76</v>
+        <v>22999.55</v>
       </c>
       <c r="AA5" s="12" t="n">
-        <v>73.59</v>
+        <v>919.96</v>
       </c>
       <c r="AB5" s="12" t="n">
         <v>0</v>
@@ -17464,43 +17452,43 @@
     </row>
     <row r="6" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="n">
-        <v>304880</v>
+        <v>304943</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
       <c r="E6" s="9"/>
       <c r="F6" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G6" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="K6" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L6" s="12" t="n">
-        <v>25242</v>
+        <v>1818.78</v>
       </c>
       <c r="M6" s="12" t="n">
-        <v>5811.05</v>
+        <v>0</v>
       </c>
       <c r="N6" s="12" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="O6" s="12" t="n">
-        <v>28810.6</v>
+        <v>1657.2</v>
       </c>
       <c r="P6" s="12" t="n">
         <v>0</v>
@@ -17509,103 +17497,103 @@
         <v>0</v>
       </c>
       <c r="R6" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S6" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T6" s="14" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="U6" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V6" s="12" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="W6" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X6" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y6" s="12" t="n">
+        <v>161.58</v>
+      </c>
+      <c r="Z6" s="12" t="n">
+        <v>1657.2</v>
+      </c>
+      <c r="AA6" s="12" t="n">
+        <v>66.28</v>
+      </c>
+      <c r="AB6" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI6" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK6" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN6" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO6" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP6" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ6" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR6" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS6" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT6" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU6" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV6" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW6" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="AX6" s="10" t="s">
         <v>84</v>
-      </c>
-      <c r="Y6" s="12" t="n">
-        <v>2242.45</v>
-      </c>
-      <c r="Z6" s="12" t="n">
-        <v>22999.55</v>
-      </c>
-      <c r="AA6" s="12" t="n">
-        <v>919.96</v>
-      </c>
-      <c r="AB6" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI6" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ6" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AK6" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AN6" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AO6" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AP6" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ6" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR6" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS6" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT6" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU6" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV6" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW6" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="AX6" s="10" t="s">
-        <v>77</v>
       </c>
       <c r="AY6" s="14" t="s">
         <v>75</v>
@@ -17641,7 +17629,7 @@
         <v>78</v>
       </c>
       <c r="BJ6" s="9" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="BK6" s="9" t="s">
         <v>75</v>
@@ -17655,34 +17643,34 @@
     </row>
     <row r="7" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="n">
-        <v>304943</v>
+        <v>305206</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
       <c r="F7" s="9" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G7" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K7" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L7" s="12" t="n">
-        <v>1818.78</v>
+        <v>2577.37</v>
       </c>
       <c r="M7" s="12" t="n">
         <v>0</v>
@@ -17691,7 +17679,7 @@
         <v>2</v>
       </c>
       <c r="O7" s="12" t="n">
-        <v>1657.2</v>
+        <v>2348.4</v>
       </c>
       <c r="P7" s="12" t="n">
         <v>0</v>
@@ -17706,28 +17694,28 @@
         <v>0</v>
       </c>
       <c r="T7" s="14" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="U7" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V7" s="12" t="n">
-        <v>0</v>
+        <v>31.19</v>
       </c>
       <c r="W7" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X7" s="9" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="Y7" s="12" t="n">
-        <v>161.58</v>
+        <v>228.97</v>
       </c>
       <c r="Z7" s="12" t="n">
-        <v>1657.2</v>
+        <v>2348.4</v>
       </c>
       <c r="AA7" s="12" t="n">
-        <v>66.28</v>
+        <v>164.38</v>
       </c>
       <c r="AB7" s="12" t="n">
         <v>0</v>
@@ -17793,10 +17781,10 @@
         <v>74</v>
       </c>
       <c r="AW7" s="14" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AX7" s="10" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="AY7" s="14" t="s">
         <v>75</v>
@@ -17846,7 +17834,7 @@
     </row>
     <row r="8" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="n">
-        <v>304974</v>
+        <v>305238</v>
       </c>
       <c r="B8" s="9" t="s">
         <v>93</v>
@@ -17858,67 +17846,67 @@
         <v>94</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="K8" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L8" s="12" t="n">
-        <v>5418.46</v>
+        <v>2751</v>
       </c>
       <c r="M8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N8" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O8" s="12" t="n">
-        <v>5153.46</v>
+        <v>2751</v>
       </c>
       <c r="P8" s="12" t="n">
-        <v>265</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="13" t="n">
-        <v>0</v>
+        <v>0.011956</v>
       </c>
       <c r="R8" s="12" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="S8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T8" s="14" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="U8" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V8" s="12" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="W8" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X8" s="9" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="Y8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z8" s="12" t="n">
-        <v>5418.46</v>
+        <v>2751</v>
       </c>
       <c r="AA8" s="12" t="n">
-        <v>379.29</v>
+        <v>192.57</v>
       </c>
       <c r="AB8" s="12" t="n">
         <v>0</v>
@@ -17984,7 +17972,7 @@
         <v>74</v>
       </c>
       <c r="AW8" s="14" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AX8" s="10" t="s">
         <v>77</v>
@@ -18023,7 +18011,7 @@
         <v>78</v>
       </c>
       <c r="BJ8" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="BK8" s="9" t="s">
         <v>75</v>
@@ -18037,34 +18025,34 @@
     </row>
     <row r="9" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="n">
-        <v>305175</v>
+        <v>305250</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="J9" s="9" t="s">
         <v>100</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="J9" s="9" t="s">
-        <v>102</v>
       </c>
       <c r="K9" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L9" s="12" t="n">
-        <v>542.51</v>
+        <v>2088.57</v>
       </c>
       <c r="M9" s="12" t="n">
         <v>0</v>
@@ -18073,43 +18061,43 @@
         <v>1</v>
       </c>
       <c r="O9" s="12" t="n">
-        <v>509.4</v>
+        <v>2088.57</v>
       </c>
       <c r="P9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q9" s="13" t="n">
-        <v>0.002772</v>
+        <v>0.005874</v>
       </c>
       <c r="R9" s="12" t="n">
-        <v>2.92</v>
+        <v>1.45</v>
       </c>
       <c r="S9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T9" s="14" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="U9" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V9" s="12" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="W9" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X9" s="9" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="Y9" s="12" t="n">
-        <v>33.11</v>
+        <v>0</v>
       </c>
       <c r="Z9" s="12" t="n">
-        <v>509.4</v>
+        <v>2088.57</v>
       </c>
       <c r="AA9" s="12" t="n">
-        <v>20.38</v>
+        <v>146.2</v>
       </c>
       <c r="AB9" s="12" t="n">
         <v>0</v>
@@ -18175,7 +18163,7 @@
         <v>74</v>
       </c>
       <c r="AW9" s="14" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AX9" s="10" t="s">
         <v>77</v>
@@ -18214,7 +18202,7 @@
         <v>78</v>
       </c>
       <c r="BJ9" s="9" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="BK9" s="9" t="s">
         <v>75</v>
@@ -18228,79 +18216,79 @@
     </row>
     <row r="10" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="n">
-        <v>305206</v>
+        <v>305251</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
       <c r="F10" s="9" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="K10" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L10" s="12" t="n">
-        <v>2577.37</v>
+        <v>1411.71</v>
       </c>
       <c r="M10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N10" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O10" s="12" t="n">
-        <v>2348.4</v>
+        <v>1411.71</v>
       </c>
       <c r="P10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q10" s="13" t="n">
-        <v>0</v>
+        <v>0.000432</v>
       </c>
       <c r="R10" s="12" t="n">
-        <v>0</v>
+        <v>0.74</v>
       </c>
       <c r="S10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T10" s="14" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="U10" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V10" s="12" t="n">
-        <v>31.19</v>
+        <v>28</v>
       </c>
       <c r="W10" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X10" s="9" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="Y10" s="12" t="n">
-        <v>228.97</v>
+        <v>0</v>
       </c>
       <c r="Z10" s="12" t="n">
-        <v>2348.4</v>
+        <v>1411.71</v>
       </c>
       <c r="AA10" s="12" t="n">
-        <v>164.38</v>
+        <v>98.82</v>
       </c>
       <c r="AB10" s="12" t="n">
         <v>0</v>
@@ -18366,7 +18354,7 @@
         <v>74</v>
       </c>
       <c r="AW10" s="14" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AX10" s="10" t="s">
         <v>77</v>
@@ -18405,7 +18393,7 @@
         <v>78</v>
       </c>
       <c r="BJ10" s="9" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="BK10" s="9" t="s">
         <v>75</v>
@@ -18419,58 +18407,58 @@
     </row>
     <row r="11" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="n">
-        <v>305238</v>
+        <v>305258</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
       <c r="F11" s="9" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="K11" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>2751</v>
+        <v>5612.24</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O11" s="12" t="n">
-        <v>2751</v>
+        <v>5612.24</v>
       </c>
       <c r="P11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q11" s="13" t="n">
-        <v>0.011956</v>
+        <v>0.034</v>
       </c>
       <c r="R11" s="12" t="n">
-        <v>5.06</v>
+        <v>10.12</v>
       </c>
       <c r="S11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T11" s="14" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="U11" s="15" t="s">
         <v>72</v>
@@ -18482,16 +18470,16 @@
         <v>73</v>
       </c>
       <c r="X11" s="9" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="Y11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z11" s="12" t="n">
-        <v>2751</v>
+        <v>5612.24</v>
       </c>
       <c r="AA11" s="12" t="n">
-        <v>192.57</v>
+        <v>392.86</v>
       </c>
       <c r="AB11" s="12" t="n">
         <v>0</v>
@@ -18557,7 +18545,7 @@
         <v>74</v>
       </c>
       <c r="AW11" s="14" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AX11" s="10" t="s">
         <v>77</v>
@@ -18596,7 +18584,7 @@
         <v>78</v>
       </c>
       <c r="BJ11" s="9" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="BK11" s="9" t="s">
         <v>75</v>
@@ -18610,34 +18598,34 @@
     </row>
     <row r="12" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="n">
-        <v>305250</v>
+        <v>305419</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
       <c r="F12" s="9" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>113</v>
+        <v>66</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>117</v>
+        <v>89</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>118</v>
+        <v>78</v>
       </c>
       <c r="K12" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>2088.57</v>
+        <v>392.71</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>0</v>
@@ -18646,43 +18634,43 @@
         <v>1</v>
       </c>
       <c r="O12" s="12" t="n">
-        <v>2088.57</v>
+        <v>368.74</v>
       </c>
       <c r="P12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" s="13" t="n">
-        <v>0.005874</v>
+        <v>0.006789</v>
       </c>
       <c r="R12" s="12" t="n">
-        <v>1.45</v>
+        <v>3.81</v>
       </c>
       <c r="S12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T12" s="14" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="U12" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V12" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W12" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X12" s="9" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="Y12" s="12" t="n">
-        <v>0</v>
+        <v>23.97</v>
       </c>
       <c r="Z12" s="12" t="n">
-        <v>2088.57</v>
+        <v>368.74</v>
       </c>
       <c r="AA12" s="12" t="n">
-        <v>146.2</v>
+        <v>14.75</v>
       </c>
       <c r="AB12" s="12" t="n">
         <v>0</v>
@@ -18748,10 +18736,10 @@
         <v>74</v>
       </c>
       <c r="AW12" s="14" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AX12" s="10" t="s">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AY12" s="14" t="s">
         <v>75</v>
@@ -18787,7 +18775,7 @@
         <v>78</v>
       </c>
       <c r="BJ12" s="9" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="BK12" s="9" t="s">
         <v>75</v>
@@ -18801,34 +18789,34 @@
     </row>
     <row r="13" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="n">
-        <v>305251</v>
+        <v>305443</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
       <c r="F13" s="9" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>113</v>
+        <v>66</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>117</v>
+        <v>89</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>118</v>
+        <v>78</v>
       </c>
       <c r="K13" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>1411.71</v>
+        <v>163.48</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>0</v>
@@ -18837,43 +18825,43 @@
         <v>1</v>
       </c>
       <c r="O13" s="12" t="n">
-        <v>1411.71</v>
+        <v>153.5</v>
       </c>
       <c r="P13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q13" s="13" t="n">
-        <v>0.000432</v>
+        <v>0.003456</v>
       </c>
       <c r="R13" s="12" t="n">
-        <v>0.74</v>
+        <v>0.8</v>
       </c>
       <c r="S13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T13" s="14" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="U13" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V13" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W13" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X13" s="9" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="Y13" s="12" t="n">
-        <v>0</v>
+        <v>9.98</v>
       </c>
       <c r="Z13" s="12" t="n">
-        <v>1411.71</v>
+        <v>153.5</v>
       </c>
       <c r="AA13" s="12" t="n">
-        <v>98.82</v>
+        <v>6.14</v>
       </c>
       <c r="AB13" s="12" t="n">
         <v>0</v>
@@ -18939,10 +18927,10 @@
         <v>74</v>
       </c>
       <c r="AW13" s="14" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AX13" s="10" t="s">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AY13" s="14" t="s">
         <v>75</v>
@@ -18978,7 +18966,7 @@
         <v>78</v>
       </c>
       <c r="BJ13" s="9" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="BK13" s="9" t="s">
         <v>75</v>
@@ -18992,79 +18980,79 @@
     </row>
     <row r="14" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="n">
-        <v>305258</v>
+        <v>305457</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
       <c r="F14" s="9" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>113</v>
+        <v>66</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>118</v>
+        <v>78</v>
       </c>
       <c r="K14" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>5612.24</v>
+        <v>4770.41</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="O14" s="12" t="n">
-        <v>5612.24</v>
+        <v>4588.46</v>
       </c>
       <c r="P14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q14" s="13" t="n">
-        <v>0.034</v>
+        <v>0.231499</v>
       </c>
       <c r="R14" s="12" t="n">
-        <v>10.12</v>
+        <v>35.08</v>
       </c>
       <c r="S14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T14" s="14" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="U14" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V14" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W14" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X14" s="9" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="Y14" s="12" t="n">
-        <v>0</v>
+        <v>181.95</v>
       </c>
       <c r="Z14" s="12" t="n">
-        <v>5612.24</v>
+        <v>4588.46</v>
       </c>
       <c r="AA14" s="12" t="n">
-        <v>392.86</v>
+        <v>183.54</v>
       </c>
       <c r="AB14" s="12" t="n">
         <v>0</v>
@@ -19130,10 +19118,10 @@
         <v>74</v>
       </c>
       <c r="AW14" s="14" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AX14" s="10" t="s">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AY14" s="14" t="s">
         <v>75</v>
@@ -19169,7 +19157,7 @@
         <v>78</v>
       </c>
       <c r="BJ14" s="9" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="BK14" s="9" t="s">
         <v>75</v>
@@ -19183,25 +19171,25 @@
     </row>
     <row r="15" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="n">
-        <v>305419</v>
+        <v>305470</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
       <c r="F15" s="9" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="G15" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="J15" s="9" t="s">
         <v>78</v>
@@ -19210,31 +19198,31 @@
         <v>70</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>392.71</v>
+        <v>314.65</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O15" s="12" t="n">
-        <v>368.74</v>
+        <v>295.45</v>
       </c>
       <c r="P15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q15" s="13" t="n">
-        <v>0.006789</v>
+        <v>0.016472</v>
       </c>
       <c r="R15" s="12" t="n">
-        <v>3.81</v>
+        <v>1.6</v>
       </c>
       <c r="S15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T15" s="14" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="U15" s="15" t="s">
         <v>72</v>
@@ -19246,16 +19234,16 @@
         <v>73</v>
       </c>
       <c r="X15" s="9" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="Y15" s="12" t="n">
-        <v>23.97</v>
+        <v>19.2</v>
       </c>
       <c r="Z15" s="12" t="n">
-        <v>368.74</v>
+        <v>295.45</v>
       </c>
       <c r="AA15" s="12" t="n">
-        <v>14.75</v>
+        <v>11.81</v>
       </c>
       <c r="AB15" s="12" t="n">
         <v>0</v>
@@ -19321,10 +19309,10 @@
         <v>74</v>
       </c>
       <c r="AW15" s="14" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AX15" s="10" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="AY15" s="14" t="s">
         <v>75</v>
@@ -19360,7 +19348,7 @@
         <v>78</v>
       </c>
       <c r="BJ15" s="9" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="BK15" s="9" t="s">
         <v>75</v>
@@ -19374,25 +19362,25 @@
     </row>
     <row r="16" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="n">
-        <v>305443</v>
+        <v>305480</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
       <c r="F16" s="9" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="G16" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="J16" s="9" t="s">
         <v>78</v>
@@ -19401,31 +19389,31 @@
         <v>70</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>163.48</v>
+        <v>2373.3</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O16" s="12" t="n">
-        <v>153.5</v>
+        <v>2228.46</v>
       </c>
       <c r="P16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q16" s="13" t="n">
-        <v>0.003456</v>
+        <v>0.017186</v>
       </c>
       <c r="R16" s="12" t="n">
-        <v>0.8</v>
+        <v>12.33</v>
       </c>
       <c r="S16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T16" s="14" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="U16" s="15" t="s">
         <v>72</v>
@@ -19437,16 +19425,16 @@
         <v>73</v>
       </c>
       <c r="X16" s="9" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="Y16" s="12" t="n">
-        <v>9.98</v>
+        <v>144.84</v>
       </c>
       <c r="Z16" s="12" t="n">
-        <v>153.5</v>
+        <v>2228.46</v>
       </c>
       <c r="AA16" s="12" t="n">
-        <v>6.14</v>
+        <v>89.14</v>
       </c>
       <c r="AB16" s="12" t="n">
         <v>0</v>
@@ -19512,10 +19500,10 @@
         <v>74</v>
       </c>
       <c r="AW16" s="14" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AX16" s="10" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="AY16" s="14" t="s">
         <v>75</v>
@@ -19551,7 +19539,7 @@
         <v>78</v>
       </c>
       <c r="BJ16" s="9" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="BK16" s="9" t="s">
         <v>75</v>
@@ -19565,79 +19553,79 @@
     </row>
     <row r="17" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="n">
-        <v>305457</v>
+        <v>305539</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
       <c r="F17" s="9" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>136</v>
+        <v>89</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>78</v>
+        <v>130</v>
       </c>
       <c r="K17" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>4770.41</v>
+        <v>1568.57</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="O17" s="12" t="n">
-        <v>4588.46</v>
+        <v>1568.57</v>
       </c>
       <c r="P17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q17" s="13" t="n">
-        <v>0.231499</v>
+        <v>0.000432</v>
       </c>
       <c r="R17" s="12" t="n">
-        <v>35.08</v>
+        <v>0.74</v>
       </c>
       <c r="S17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T17" s="14" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="U17" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V17" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W17" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X17" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Y17" s="12" t="n">
-        <v>181.95</v>
+        <v>0</v>
       </c>
       <c r="Z17" s="12" t="n">
-        <v>4588.46</v>
+        <v>1568.57</v>
       </c>
       <c r="AA17" s="12" t="n">
-        <v>183.54</v>
+        <v>109.8</v>
       </c>
       <c r="AB17" s="12" t="n">
         <v>0</v>
@@ -19703,10 +19691,10 @@
         <v>74</v>
       </c>
       <c r="AW17" s="14" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AX17" s="10" t="s">
-        <v>130</v>
+        <v>77</v>
       </c>
       <c r="AY17" s="14" t="s">
         <v>75</v>
@@ -19742,7 +19730,7 @@
         <v>78</v>
       </c>
       <c r="BJ17" s="9" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="BK17" s="9" t="s">
         <v>75</v>
@@ -19756,79 +19744,79 @@
     </row>
     <row r="18" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="n">
-        <v>305470</v>
+        <v>305553</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
       <c r="F18" s="9" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>136</v>
+        <v>111</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="K18" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>314.65</v>
+        <v>3135.16</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O18" s="12" t="n">
-        <v>295.45</v>
+        <v>3135.16</v>
       </c>
       <c r="P18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q18" s="13" t="n">
-        <v>0.016472</v>
+        <v>0.000864</v>
       </c>
       <c r="R18" s="12" t="n">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="S18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T18" s="14" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="U18" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V18" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W18" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X18" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Y18" s="12" t="n">
-        <v>19.2</v>
+        <v>0</v>
       </c>
       <c r="Z18" s="12" t="n">
-        <v>295.45</v>
+        <v>3135.16</v>
       </c>
       <c r="AA18" s="12" t="n">
-        <v>11.81</v>
+        <v>219.46</v>
       </c>
       <c r="AB18" s="12" t="n">
         <v>0</v>
@@ -19894,10 +19882,10 @@
         <v>74</v>
       </c>
       <c r="AW18" s="14" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AX18" s="10" t="s">
-        <v>130</v>
+        <v>77</v>
       </c>
       <c r="AY18" s="14" t="s">
         <v>75</v>
@@ -19933,7 +19921,7 @@
         <v>78</v>
       </c>
       <c r="BJ18" s="9" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="BK18" s="9" t="s">
         <v>75</v>
@@ -19947,79 +19935,79 @@
     </row>
     <row r="19" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="n">
-        <v>305480</v>
+        <v>305554</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
       <c r="F19" s="9" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>136</v>
+        <v>111</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="K19" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>2373.3</v>
+        <v>3258.14</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O19" s="12" t="n">
-        <v>2228.46</v>
+        <v>3258.14</v>
       </c>
       <c r="P19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q19" s="13" t="n">
-        <v>0.017186</v>
+        <v>0.000864</v>
       </c>
       <c r="R19" s="12" t="n">
-        <v>12.33</v>
+        <v>1.48</v>
       </c>
       <c r="S19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T19" s="14" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="U19" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V19" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W19" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X19" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Y19" s="12" t="n">
-        <v>144.84</v>
+        <v>0</v>
       </c>
       <c r="Z19" s="12" t="n">
-        <v>2228.46</v>
+        <v>3258.14</v>
       </c>
       <c r="AA19" s="12" t="n">
-        <v>89.14</v>
+        <v>228.07</v>
       </c>
       <c r="AB19" s="12" t="n">
         <v>0</v>
@@ -20085,10 +20073,10 @@
         <v>74</v>
       </c>
       <c r="AW19" s="14" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AX19" s="10" t="s">
-        <v>130</v>
+        <v>77</v>
       </c>
       <c r="AY19" s="14" t="s">
         <v>75</v>
@@ -20124,7 +20112,7 @@
         <v>78</v>
       </c>
       <c r="BJ19" s="9" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="BK19" s="9" t="s">
         <v>75</v>
@@ -20138,34 +20126,34 @@
     </row>
     <row r="20" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="n">
-        <v>305539</v>
+        <v>305556</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
       <c r="F20" s="9" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="K20" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>1568.57</v>
+        <v>5879.02</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>0</v>
@@ -20174,22 +20162,22 @@
         <v>1</v>
       </c>
       <c r="O20" s="12" t="n">
-        <v>1568.57</v>
+        <v>5879.02</v>
       </c>
       <c r="P20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q20" s="13" t="n">
-        <v>0.000432</v>
+        <v>0.467698</v>
       </c>
       <c r="R20" s="12" t="n">
-        <v>0.74</v>
+        <v>31.5</v>
       </c>
       <c r="S20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T20" s="14" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="U20" s="15" t="s">
         <v>72</v>
@@ -20201,16 +20189,16 @@
         <v>73</v>
       </c>
       <c r="X20" s="9" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="Y20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z20" s="12" t="n">
-        <v>1568.57</v>
+        <v>5879.02</v>
       </c>
       <c r="AA20" s="12" t="n">
-        <v>109.8</v>
+        <v>411.53</v>
       </c>
       <c r="AB20" s="12" t="n">
         <v>0</v>
@@ -20276,7 +20264,7 @@
         <v>74</v>
       </c>
       <c r="AW20" s="14" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AX20" s="10" t="s">
         <v>77</v>
@@ -20315,7 +20303,7 @@
         <v>78</v>
       </c>
       <c r="BJ20" s="9" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="BK20" s="9" t="s">
         <v>75</v>
@@ -20329,34 +20317,34 @@
     </row>
     <row r="21" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="n">
-        <v>305553</v>
+        <v>305560</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
       <c r="F21" s="9" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="K21" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>3135.16</v>
+        <v>3121.47</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>0</v>
@@ -20365,22 +20353,22 @@
         <v>1</v>
       </c>
       <c r="O21" s="12" t="n">
-        <v>3135.16</v>
+        <v>3121.47</v>
       </c>
       <c r="P21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q21" s="13" t="n">
-        <v>0.000864</v>
+        <v>0.031059</v>
       </c>
       <c r="R21" s="12" t="n">
-        <v>1.48</v>
+        <v>5.54</v>
       </c>
       <c r="S21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T21" s="14" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="U21" s="15" t="s">
         <v>72</v>
@@ -20392,16 +20380,16 @@
         <v>73</v>
       </c>
       <c r="X21" s="9" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="Y21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z21" s="12" t="n">
-        <v>3135.16</v>
+        <v>3121.47</v>
       </c>
       <c r="AA21" s="12" t="n">
-        <v>219.46</v>
+        <v>218.5</v>
       </c>
       <c r="AB21" s="12" t="n">
         <v>0</v>
@@ -20467,7 +20455,7 @@
         <v>74</v>
       </c>
       <c r="AW21" s="14" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AX21" s="10" t="s">
         <v>77</v>
@@ -20506,7 +20494,7 @@
         <v>78</v>
       </c>
       <c r="BJ21" s="9" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="BK21" s="9" t="s">
         <v>75</v>
@@ -20520,34 +20508,34 @@
     </row>
     <row r="22" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="n">
-        <v>305554</v>
+        <v>305561</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
       <c r="F22" s="9" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="K22" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>3258.14</v>
+        <v>5331.26</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>0</v>
@@ -20556,22 +20544,22 @@
         <v>1</v>
       </c>
       <c r="O22" s="12" t="n">
-        <v>3258.14</v>
+        <v>5005.88</v>
       </c>
       <c r="P22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q22" s="13" t="n">
-        <v>0.000864</v>
+        <v>0.055816</v>
       </c>
       <c r="R22" s="12" t="n">
-        <v>1.48</v>
+        <v>7.12</v>
       </c>
       <c r="S22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T22" s="14" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="U22" s="15" t="s">
         <v>72</v>
@@ -20583,16 +20571,16 @@
         <v>73</v>
       </c>
       <c r="X22" s="9" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="Y22" s="12" t="n">
-        <v>0</v>
+        <v>325.38</v>
       </c>
       <c r="Z22" s="12" t="n">
-        <v>3258.14</v>
+        <v>5005.88</v>
       </c>
       <c r="AA22" s="12" t="n">
-        <v>228.07</v>
+        <v>350.41</v>
       </c>
       <c r="AB22" s="12" t="n">
         <v>0</v>
@@ -20658,7 +20646,7 @@
         <v>74</v>
       </c>
       <c r="AW22" s="14" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AX22" s="10" t="s">
         <v>77</v>
@@ -20697,7 +20685,7 @@
         <v>78</v>
       </c>
       <c r="BJ22" s="9" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="BK22" s="9" t="s">
         <v>75</v>
@@ -20711,34 +20699,34 @@
     </row>
     <row r="23" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="n">
-        <v>305556</v>
+        <v>305681</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="9" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>128</v>
+        <v>152</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="K23" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>5879.02</v>
+        <v>1945.98</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>0</v>
@@ -20747,22 +20735,22 @@
         <v>1</v>
       </c>
       <c r="O23" s="12" t="n">
-        <v>5879.02</v>
+        <v>1945.98</v>
       </c>
       <c r="P23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q23" s="13" t="n">
-        <v>0.467698</v>
+        <v>0.004946</v>
       </c>
       <c r="R23" s="12" t="n">
-        <v>31.5</v>
+        <v>1.15</v>
       </c>
       <c r="S23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T23" s="14" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="U23" s="15" t="s">
         <v>72</v>
@@ -20774,16 +20762,16 @@
         <v>73</v>
       </c>
       <c r="X23" s="9" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="Y23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z23" s="12" t="n">
-        <v>5879.02</v>
+        <v>1945.98</v>
       </c>
       <c r="AA23" s="12" t="n">
-        <v>411.53</v>
+        <v>136.22</v>
       </c>
       <c r="AB23" s="12" t="n">
         <v>0</v>
@@ -20849,7 +20837,7 @@
         <v>74</v>
       </c>
       <c r="AW23" s="14" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AX23" s="10" t="s">
         <v>77</v>
@@ -20888,7 +20876,7 @@
         <v>78</v>
       </c>
       <c r="BJ23" s="9" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="BK23" s="9" t="s">
         <v>75</v>
@@ -20902,79 +20890,79 @@
     </row>
     <row r="24" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="n">
-        <v>305560</v>
+        <v>305691</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>111</v>
+        <v>156</v>
       </c>
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
       <c r="F24" s="9" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>113</v>
+        <v>66</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="K24" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>3121.47</v>
+        <v>3563.51</v>
       </c>
       <c r="M24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O24" s="12" t="n">
-        <v>3121.47</v>
+        <v>3098.7</v>
       </c>
       <c r="P24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q24" s="13" t="n">
-        <v>0.031059</v>
+        <v>0</v>
       </c>
       <c r="R24" s="12" t="n">
-        <v>5.54</v>
+        <v>0</v>
       </c>
       <c r="S24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T24" s="14" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="U24" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V24" s="12" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="W24" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X24" s="9" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="Y24" s="12" t="n">
-        <v>0</v>
+        <v>464.81</v>
       </c>
       <c r="Z24" s="12" t="n">
-        <v>3121.47</v>
+        <v>3098.7</v>
       </c>
       <c r="AA24" s="12" t="n">
-        <v>218.5</v>
+        <v>216.91</v>
       </c>
       <c r="AB24" s="12" t="n">
         <v>0</v>
@@ -21040,7 +21028,7 @@
         <v>74</v>
       </c>
       <c r="AW24" s="14" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AX24" s="10" t="s">
         <v>77</v>
@@ -21079,7 +21067,7 @@
         <v>78</v>
       </c>
       <c r="BJ24" s="9" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="BK24" s="9" t="s">
         <v>75</v>
@@ -21093,34 +21081,34 @@
     </row>
     <row r="25" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="n">
-        <v>305561</v>
+        <v>305724</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="H25" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="I25" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="J25" s="9" t="s">
         <v>161</v>
-      </c>
-      <c r="I25" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="J25" s="9" t="s">
-        <v>162</v>
       </c>
       <c r="K25" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>5331.26</v>
+        <v>1674.18</v>
       </c>
       <c r="M25" s="12" t="n">
         <v>0</v>
@@ -21129,22 +21117,22 @@
         <v>1</v>
       </c>
       <c r="O25" s="12" t="n">
-        <v>5005.88</v>
+        <v>1674.18</v>
       </c>
       <c r="P25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q25" s="13" t="n">
-        <v>0.055816</v>
+        <v>0.003916</v>
       </c>
       <c r="R25" s="12" t="n">
-        <v>7.12</v>
+        <v>0.97</v>
       </c>
       <c r="S25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T25" s="14" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="U25" s="15" t="s">
         <v>72</v>
@@ -21156,16 +21144,16 @@
         <v>73</v>
       </c>
       <c r="X25" s="9" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="Y25" s="12" t="n">
-        <v>325.38</v>
+        <v>0</v>
       </c>
       <c r="Z25" s="12" t="n">
-        <v>5005.88</v>
+        <v>1674.18</v>
       </c>
       <c r="AA25" s="12" t="n">
-        <v>350.41</v>
+        <v>117.19</v>
       </c>
       <c r="AB25" s="12" t="n">
         <v>0</v>
@@ -21231,7 +21219,7 @@
         <v>74</v>
       </c>
       <c r="AW25" s="14" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AX25" s="10" t="s">
         <v>77</v>
@@ -21270,7 +21258,7 @@
         <v>78</v>
       </c>
       <c r="BJ25" s="9" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="BK25" s="9" t="s">
         <v>75</v>
@@ -21284,58 +21272,58 @@
     </row>
     <row r="26" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="n">
-        <v>305681</v>
+        <v>305725</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>111</v>
+        <v>164</v>
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>113</v>
+        <v>66</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>169</v>
+        <v>129</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="K26" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>1945.98</v>
+        <v>10012.8</v>
       </c>
       <c r="M26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O26" s="12" t="n">
-        <v>1945.98</v>
+        <v>10012.8</v>
       </c>
       <c r="P26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q26" s="13" t="n">
-        <v>0.004946</v>
+        <v>0.750038</v>
       </c>
       <c r="R26" s="12" t="n">
-        <v>1.15</v>
+        <v>38</v>
       </c>
       <c r="S26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T26" s="14" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="U26" s="15" t="s">
         <v>72</v>
@@ -21347,16 +21335,16 @@
         <v>73</v>
       </c>
       <c r="X26" s="9" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="Y26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z26" s="12" t="n">
-        <v>1945.98</v>
+        <v>10012.8</v>
       </c>
       <c r="AA26" s="12" t="n">
-        <v>136.22</v>
+        <v>400.51</v>
       </c>
       <c r="AB26" s="12" t="n">
         <v>0</v>
@@ -21422,7 +21410,7 @@
         <v>74</v>
       </c>
       <c r="AW26" s="14" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AX26" s="10" t="s">
         <v>77</v>
@@ -21461,7 +21449,7 @@
         <v>78</v>
       </c>
       <c r="BJ26" s="9" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="BK26" s="9" t="s">
         <v>75</v>
@@ -21475,34 +21463,34 @@
     </row>
     <row r="27" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="n">
-        <v>305691</v>
+        <v>305731</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>173</v>
+        <v>109</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="G27" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>169</v>
+        <v>129</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="J27" s="9" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="K27" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>3563.51</v>
+        <v>6247.73</v>
       </c>
       <c r="M27" s="12" t="n">
         <v>0</v>
@@ -21511,43 +21499,43 @@
         <v>2</v>
       </c>
       <c r="O27" s="12" t="n">
-        <v>3098.7</v>
+        <v>6247.73</v>
       </c>
       <c r="P27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q27" s="13" t="n">
-        <v>0</v>
+        <v>0.030808</v>
       </c>
       <c r="R27" s="12" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="S27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T27" s="14" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="U27" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V27" s="12" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="W27" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X27" s="9" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="Y27" s="12" t="n">
-        <v>464.81</v>
+        <v>0</v>
       </c>
       <c r="Z27" s="12" t="n">
-        <v>3098.7</v>
+        <v>6247.73</v>
       </c>
       <c r="AA27" s="12" t="n">
-        <v>216.91</v>
+        <v>437.34</v>
       </c>
       <c r="AB27" s="12" t="n">
         <v>0</v>
@@ -21613,7 +21601,7 @@
         <v>74</v>
       </c>
       <c r="AW27" s="14" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AX27" s="10" t="s">
         <v>77</v>
@@ -21652,7 +21640,7 @@
         <v>78</v>
       </c>
       <c r="BJ27" s="9" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="BK27" s="9" t="s">
         <v>75</v>
@@ -21666,79 +21654,79 @@
     </row>
     <row r="28" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="n">
-        <v>305724</v>
+        <v>305778</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>111</v>
+        <v>171</v>
       </c>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>113</v>
+        <v>66</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>178</v>
+        <v>153</v>
       </c>
       <c r="K28" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>1674.18</v>
+        <v>834.78</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O28" s="12" t="n">
-        <v>1674.18</v>
+        <v>730</v>
       </c>
       <c r="P28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q28" s="13" t="n">
-        <v>0.003916</v>
+        <v>0</v>
       </c>
       <c r="R28" s="12" t="n">
-        <v>0.97</v>
+        <v>0</v>
       </c>
       <c r="S28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T28" s="14" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="U28" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V28" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="W28" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X28" s="9" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="Y28" s="12" t="n">
-        <v>0</v>
+        <v>104.78</v>
       </c>
       <c r="Z28" s="12" t="n">
-        <v>1674.18</v>
+        <v>730</v>
       </c>
       <c r="AA28" s="12" t="n">
-        <v>117.19</v>
+        <v>51.1</v>
       </c>
       <c r="AB28" s="12" t="n">
         <v>0</v>
@@ -21843,7 +21831,7 @@
         <v>78</v>
       </c>
       <c r="BJ28" s="9" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="BK28" s="9" t="s">
         <v>75</v>
@@ -21857,79 +21845,79 @@
     </row>
     <row r="29" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="n">
-        <v>305725</v>
+        <v>305787</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
       <c r="F29" s="9" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>66</v>
+        <v>178</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>146</v>
+        <v>89</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>178</v>
+        <v>130</v>
       </c>
       <c r="K29" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>10012.8</v>
+        <v>4520.02</v>
       </c>
       <c r="M29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O29" s="12" t="n">
-        <v>10012.8</v>
+        <v>4520.02</v>
       </c>
       <c r="P29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q29" s="13" t="n">
-        <v>0.750038</v>
+        <v>0.004608</v>
       </c>
       <c r="R29" s="12" t="n">
-        <v>38</v>
+        <v>36.69</v>
       </c>
       <c r="S29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T29" s="14" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="U29" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V29" s="12" t="n">
-        <v>28</v>
+        <v>55.99</v>
       </c>
       <c r="W29" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X29" s="9" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="Y29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z29" s="12" t="n">
-        <v>10012.8</v>
+        <v>4520.02</v>
       </c>
       <c r="AA29" s="12" t="n">
-        <v>400.51</v>
+        <v>316.39</v>
       </c>
       <c r="AB29" s="12" t="n">
         <v>0</v>
@@ -21938,7 +21926,7 @@
         <v>0</v>
       </c>
       <c r="AD29" s="12" t="n">
-        <v>0</v>
+        <v>91.25</v>
       </c>
       <c r="AE29" s="12" t="n">
         <v>0</v>
@@ -21995,7 +21983,7 @@
         <v>74</v>
       </c>
       <c r="AW29" s="14" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AX29" s="10" t="s">
         <v>77</v>
@@ -22019,25 +22007,25 @@
         <v>75</v>
       </c>
       <c r="BE29" s="14" t="s">
-        <v>75</v>
+        <v>180</v>
       </c>
       <c r="BF29" s="9" t="s">
-        <v>75</v>
+        <v>181</v>
       </c>
       <c r="BG29" s="9" t="s">
-        <v>78</v>
+        <v>129</v>
       </c>
       <c r="BH29" s="14" t="s">
-        <v>75</v>
+        <v>182</v>
       </c>
       <c r="BI29" s="9" t="s">
-        <v>78</v>
+        <v>152</v>
       </c>
       <c r="BJ29" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="BK29" s="9" t="s">
         <v>184</v>
-      </c>
-      <c r="BK29" s="9" t="s">
-        <v>75</v>
       </c>
       <c r="BL29" s="9" t="s">
         <v>75</v>
@@ -22048,10 +22036,10 @@
     </row>
     <row r="30" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="n">
-        <v>305731</v>
+        <v>305821</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
@@ -22060,46 +22048,46 @@
         <v>185</v>
       </c>
       <c r="G30" s="10" t="s">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>146</v>
+        <v>173</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="K30" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>6247.73</v>
+        <v>4462.34</v>
       </c>
       <c r="M30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O30" s="12" t="n">
-        <v>6247.73</v>
+        <v>4462.34</v>
       </c>
       <c r="P30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q30" s="13" t="n">
-        <v>0.030808</v>
+        <v>0.010272</v>
       </c>
       <c r="R30" s="12" t="n">
-        <v>6.05</v>
+        <v>3.7</v>
       </c>
       <c r="S30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T30" s="14" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="U30" s="15" t="s">
         <v>72</v>
@@ -22111,16 +22099,16 @@
         <v>73</v>
       </c>
       <c r="X30" s="9" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="Y30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z30" s="12" t="n">
-        <v>6247.73</v>
+        <v>4462.34</v>
       </c>
       <c r="AA30" s="12" t="n">
-        <v>437.34</v>
+        <v>312.36</v>
       </c>
       <c r="AB30" s="12" t="n">
         <v>0</v>
@@ -22186,7 +22174,7 @@
         <v>74</v>
       </c>
       <c r="AW30" s="14" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AX30" s="10" t="s">
         <v>77</v>
@@ -22225,7 +22213,7 @@
         <v>78</v>
       </c>
       <c r="BJ30" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="BK30" s="9" t="s">
         <v>75</v>
@@ -22239,10 +22227,10 @@
     </row>
     <row r="31" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="n">
-        <v>305778</v>
+        <v>305822</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>188</v>
+        <v>93</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
@@ -22251,67 +22239,67 @@
         <v>189</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>190</v>
+        <v>173</v>
       </c>
       <c r="J31" s="9" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="K31" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>834.78</v>
+        <v>1464.23</v>
       </c>
       <c r="M31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O31" s="12" t="n">
-        <v>730</v>
+        <v>1464.23</v>
       </c>
       <c r="P31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q31" s="13" t="n">
-        <v>0</v>
+        <v>0.002473</v>
       </c>
       <c r="R31" s="12" t="n">
-        <v>0</v>
+        <v>0.77</v>
       </c>
       <c r="S31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T31" s="14" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="U31" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V31" s="12" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="W31" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X31" s="9" t="s">
-        <v>190</v>
+        <v>173</v>
       </c>
       <c r="Y31" s="12" t="n">
-        <v>104.78</v>
+        <v>0</v>
       </c>
       <c r="Z31" s="12" t="n">
-        <v>730</v>
+        <v>1464.23</v>
       </c>
       <c r="AA31" s="12" t="n">
-        <v>51.1</v>
+        <v>102.5</v>
       </c>
       <c r="AB31" s="12" t="n">
         <v>0</v>
@@ -22377,7 +22365,7 @@
         <v>74</v>
       </c>
       <c r="AW31" s="14" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="AX31" s="10" t="s">
         <v>77</v>
@@ -22416,7 +22404,7 @@
         <v>78</v>
       </c>
       <c r="BJ31" s="9" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="BK31" s="9" t="s">
         <v>75</v>
@@ -22430,79 +22418,79 @@
     </row>
     <row r="32" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="n">
-        <v>305787</v>
+        <v>305829</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>193</v>
+        <v>93</v>
       </c>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
       <c r="F32" s="9" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G32" s="10" t="s">
-        <v>195</v>
+        <v>95</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>101</v>
+        <v>152</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>190</v>
+        <v>173</v>
       </c>
       <c r="J32" s="9" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="K32" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>4520.02</v>
+        <v>3019.02</v>
       </c>
       <c r="M32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O32" s="12" t="n">
-        <v>4520.02</v>
+        <v>3019.02</v>
       </c>
       <c r="P32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q32" s="13" t="n">
-        <v>0.004608</v>
+        <v>0.004946</v>
       </c>
       <c r="R32" s="12" t="n">
-        <v>36.69</v>
+        <v>1.53</v>
       </c>
       <c r="S32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T32" s="14" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="U32" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V32" s="12" t="n">
-        <v>55.99</v>
+        <v>28</v>
       </c>
       <c r="W32" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X32" s="9" t="s">
-        <v>190</v>
+        <v>173</v>
       </c>
       <c r="Y32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z32" s="12" t="n">
-        <v>4520.02</v>
+        <v>3019.02</v>
       </c>
       <c r="AA32" s="12" t="n">
-        <v>316.39</v>
+        <v>211.33</v>
       </c>
       <c r="AB32" s="12" t="n">
         <v>0</v>
@@ -22511,7 +22499,7 @@
         <v>0</v>
       </c>
       <c r="AD32" s="12" t="n">
-        <v>91.25</v>
+        <v>0</v>
       </c>
       <c r="AE32" s="12" t="n">
         <v>0</v>
@@ -22568,7 +22556,7 @@
         <v>74</v>
       </c>
       <c r="AW32" s="14" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AX32" s="10" t="s">
         <v>77</v>
@@ -22592,25 +22580,25 @@
         <v>75</v>
       </c>
       <c r="BE32" s="14" t="s">
-        <v>197</v>
+        <v>75</v>
       </c>
       <c r="BF32" s="9" t="s">
-        <v>198</v>
+        <v>75</v>
       </c>
       <c r="BG32" s="9" t="s">
-        <v>146</v>
+        <v>78</v>
       </c>
       <c r="BH32" s="14" t="s">
-        <v>199</v>
+        <v>75</v>
       </c>
       <c r="BI32" s="9" t="s">
-        <v>169</v>
+        <v>78</v>
       </c>
       <c r="BJ32" s="9" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="BK32" s="9" t="s">
-        <v>201</v>
+        <v>75</v>
       </c>
       <c r="BL32" s="9" t="s">
         <v>75</v>
@@ -22621,34 +22609,34 @@
     </row>
     <row r="33" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="n">
-        <v>305821</v>
+        <v>305933</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="9"/>
       <c r="E33" s="9"/>
       <c r="F33" s="9" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>113</v>
+        <v>66</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>190</v>
+        <v>152</v>
       </c>
       <c r="I33" s="9" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="J33" s="9" t="s">
-        <v>203</v>
+        <v>78</v>
       </c>
       <c r="K33" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>4462.34</v>
+        <v>366.64</v>
       </c>
       <c r="M33" s="12" t="n">
         <v>0</v>
@@ -22657,43 +22645,43 @@
         <v>1</v>
       </c>
       <c r="O33" s="12" t="n">
-        <v>4462.34</v>
+        <v>344.26</v>
       </c>
       <c r="P33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q33" s="13" t="n">
-        <v>0.010272</v>
+        <v>0.007989</v>
       </c>
       <c r="R33" s="12" t="n">
-        <v>3.7</v>
+        <v>1.76</v>
       </c>
       <c r="S33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T33" s="14" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="U33" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V33" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W33" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X33" s="9" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="Y33" s="12" t="n">
-        <v>0</v>
+        <v>22.38</v>
       </c>
       <c r="Z33" s="12" t="n">
-        <v>4462.34</v>
+        <v>344.26</v>
       </c>
       <c r="AA33" s="12" t="n">
-        <v>312.36</v>
+        <v>13.77</v>
       </c>
       <c r="AB33" s="12" t="n">
         <v>0</v>
@@ -22759,10 +22747,10 @@
         <v>74</v>
       </c>
       <c r="AW33" s="14" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AX33" s="10" t="s">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AY33" s="14" t="s">
         <v>75</v>
@@ -22798,7 +22786,7 @@
         <v>78</v>
       </c>
       <c r="BJ33" s="9" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="BK33" s="9" t="s">
         <v>75</v>
@@ -22812,34 +22800,34 @@
     </row>
     <row r="34" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="n">
-        <v>305822</v>
+        <v>305942</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
       <c r="F34" s="9" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="G34" s="10" t="s">
-        <v>113</v>
+        <v>66</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>190</v>
+        <v>152</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="J34" s="9" t="s">
-        <v>203</v>
+        <v>78</v>
       </c>
       <c r="K34" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>1464.23</v>
+        <v>42.44</v>
       </c>
       <c r="M34" s="12" t="n">
         <v>0</v>
@@ -22848,43 +22836,43 @@
         <v>1</v>
       </c>
       <c r="O34" s="12" t="n">
-        <v>1464.23</v>
+        <v>39.85</v>
       </c>
       <c r="P34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q34" s="13" t="n">
-        <v>0.002473</v>
+        <v>0.002284</v>
       </c>
       <c r="R34" s="12" t="n">
-        <v>0.77</v>
+        <v>0.8</v>
       </c>
       <c r="S34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T34" s="14" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="U34" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V34" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W34" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X34" s="9" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="Y34" s="12" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Z34" s="12" t="n">
-        <v>1464.23</v>
+        <v>39.85</v>
       </c>
       <c r="AA34" s="12" t="n">
-        <v>102.5</v>
+        <v>1.59</v>
       </c>
       <c r="AB34" s="12" t="n">
         <v>0</v>
@@ -22950,10 +22938,10 @@
         <v>74</v>
       </c>
       <c r="AW34" s="14" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AX34" s="10" t="s">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AY34" s="14" t="s">
         <v>75</v>
@@ -22989,7 +22977,7 @@
         <v>78</v>
       </c>
       <c r="BJ34" s="9" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="BK34" s="9" t="s">
         <v>75</v>
@@ -23003,34 +22991,34 @@
     </row>
     <row r="35" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="n">
-        <v>305829</v>
+        <v>305957</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
       <c r="E35" s="9"/>
       <c r="F35" s="9" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>113</v>
+        <v>66</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>169</v>
+        <v>196</v>
       </c>
       <c r="I35" s="9" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="J35" s="9" t="s">
-        <v>170</v>
+        <v>78</v>
       </c>
       <c r="K35" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>3019.02</v>
+        <v>126.7</v>
       </c>
       <c r="M35" s="12" t="n">
         <v>0</v>
@@ -23039,43 +23027,43 @@
         <v>1</v>
       </c>
       <c r="O35" s="12" t="n">
-        <v>3019.02</v>
+        <v>118.97</v>
       </c>
       <c r="P35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q35" s="13" t="n">
-        <v>0.004946</v>
+        <v>0.001512</v>
       </c>
       <c r="R35" s="12" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="S35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T35" s="14" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="U35" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V35" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W35" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X35" s="9" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="Y35" s="12" t="n">
-        <v>0</v>
+        <v>7.73</v>
       </c>
       <c r="Z35" s="12" t="n">
-        <v>3019.02</v>
+        <v>118.97</v>
       </c>
       <c r="AA35" s="12" t="n">
-        <v>211.33</v>
+        <v>4.76</v>
       </c>
       <c r="AB35" s="12" t="n">
         <v>0</v>
@@ -23141,10 +23129,10 @@
         <v>74</v>
       </c>
       <c r="AW35" s="14" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AX35" s="10" t="s">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AY35" s="14" t="s">
         <v>75</v>
@@ -23180,7 +23168,7 @@
         <v>78</v>
       </c>
       <c r="BJ35" s="9" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="BK35" s="9" t="s">
         <v>75</v>
@@ -23193,396 +23181,518 @@
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="4"/>
+      <c r="A36" s="8" t="n">
+        <v>305966</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="G36" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H36" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="I36" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="J36" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K36" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L36" s="12" t="n">
+        <v>290.09</v>
+      </c>
+      <c r="M36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O36" s="12" t="n">
+        <v>272.38</v>
+      </c>
+      <c r="P36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="13" t="n">
+        <v>0.003202</v>
+      </c>
+      <c r="R36" s="12" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="S36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" s="14" t="s">
+        <v>206</v>
+      </c>
+      <c r="U36" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X36" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="Y36" s="12" t="n">
+        <v>17.71</v>
+      </c>
+      <c r="Z36" s="12" t="n">
+        <v>272.38</v>
+      </c>
+      <c r="AA36" s="12" t="n">
+        <v>10.89</v>
+      </c>
+      <c r="AB36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ36" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM36" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN36" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO36" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP36" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ36" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR36" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS36" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT36" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU36" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV36" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW36" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="AX36" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="AY36" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ36" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA36" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB36" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC36" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD36" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE36" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF36" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG36" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH36" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI36" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ36" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="BK36" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL36" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM36" s="16" t="s">
+        <v>80</v>
+      </c>
     </row>
-    <row r="37" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="17" t="s">
-        <v>212</v>
-      </c>
-      <c r="B37" s="17"/>
-      <c r="C37" s="17"/>
-      <c r="D37" s="17"/>
-      <c r="E37" s="17"/>
-      <c r="F37" s="17"/>
-      <c r="G37" s="17"/>
-      <c r="H37" s="17"/>
-      <c r="I37" s="17"/>
-      <c r="J37" s="17"/>
-      <c r="K37" s="17"/>
-      <c r="L37" s="17"/>
-      <c r="M37" s="17"/>
-      <c r="N37" s="17"/>
-      <c r="O37" s="17"/>
-      <c r="P37" s="17"/>
-      <c r="Q37" s="17"/>
-      <c r="R37" s="17"/>
-      <c r="S37" s="17"/>
-      <c r="T37" s="17"/>
-      <c r="U37" s="17"/>
-      <c r="V37" s="17"/>
+    <row r="37" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="4"/>
     </row>
     <row r="38" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="18" t="s">
+      <c r="A38" s="17" t="s">
+        <v>208</v>
+      </c>
+      <c r="B38" s="17"/>
+      <c r="C38" s="17"/>
+      <c r="D38" s="17"/>
+      <c r="E38" s="17"/>
+      <c r="F38" s="17"/>
+      <c r="G38" s="17"/>
+      <c r="H38" s="17"/>
+      <c r="I38" s="17"/>
+      <c r="J38" s="17"/>
+      <c r="K38" s="17"/>
+      <c r="L38" s="17"/>
+      <c r="M38" s="17"/>
+      <c r="N38" s="17"/>
+      <c r="O38" s="17"/>
+      <c r="P38" s="17"/>
+      <c r="Q38" s="17"/>
+      <c r="R38" s="17"/>
+      <c r="S38" s="17"/>
+      <c r="T38" s="17"/>
+      <c r="U38" s="17"/>
+      <c r="V38" s="17"/>
+    </row>
+    <row r="39" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="18" t="s">
+        <v>209</v>
+      </c>
+      <c r="B39" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C39" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" s="18" t="s">
+        <v>210</v>
+      </c>
+      <c r="E39" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F39" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="G39" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H39" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="I39" s="18" t="s">
+        <v>211</v>
+      </c>
+      <c r="J39" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="K39" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="L39" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="M39" s="18" t="s">
+        <v>212</v>
+      </c>
+      <c r="N39" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="O39" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="P39" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q39" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="R39" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="S39" s="18" t="s">
         <v>213</v>
       </c>
-      <c r="B38" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C38" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D38" s="18" t="s">
+      <c r="T39" s="18" t="s">
         <v>214</v>
       </c>
-      <c r="E38" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F38" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="G38" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="H38" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="I38" s="18" t="s">
+      <c r="U39" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="V39" s="18" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="19" t="n">
+        <v>32</v>
+      </c>
+      <c r="B40" s="19" t="n">
+        <v>5811.05</v>
+      </c>
+      <c r="C40" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="19" t="n">
+        <v>3958.32</v>
+      </c>
+      <c r="F40" s="19" t="n">
+        <v>106421.98</v>
+      </c>
+      <c r="G40" s="19" t="n">
+        <v>6157.08</v>
+      </c>
+      <c r="H40" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="19" t="n">
+        <v>91.25</v>
+      </c>
+      <c r="K40" s="19" t="n">
+        <v>110380.3</v>
+      </c>
+      <c r="L40" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" s="20" t="n">
+        <v>1.711391</v>
+      </c>
+      <c r="S40" s="19" t="n">
+        <v>112233.03</v>
+      </c>
+      <c r="T40" s="19" t="n">
+        <v>110380.3</v>
+      </c>
+      <c r="U40" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B41" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C41" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D41" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="E41" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="F41" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="G41" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="H41" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="I41" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="J41" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="K41" s="18" t="s">
         <v>215</v>
       </c>
-      <c r="J38" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="K38" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="L38" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="M38" s="18" t="s">
+      <c r="L41" s="18" t="s">
         <v>216</v>
       </c>
-      <c r="N38" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="O38" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="P38" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q38" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="R38" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="S38" s="18" t="s">
+      <c r="M41" s="18" t="s">
         <v>217</v>
-      </c>
-      <c r="T38" s="18" t="s">
-        <v>218</v>
-      </c>
-      <c r="U38" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="V38" s="18" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="19" t="n">
-        <v>31</v>
-      </c>
-      <c r="B39" s="19" t="n">
-        <v>5811.05</v>
-      </c>
-      <c r="C39" s="19" t="n">
-        <v>424</v>
-      </c>
-      <c r="D39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" s="19" t="n">
-        <v>3941.02</v>
-      </c>
-      <c r="F39" s="19" t="n">
-        <v>113414.14</v>
-      </c>
-      <c r="G39" s="19" t="n">
-        <v>6599.33</v>
-      </c>
-      <c r="H39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" s="19" t="n">
-        <v>91.25</v>
-      </c>
-      <c r="K39" s="19" t="n">
-        <v>117355.16</v>
-      </c>
-      <c r="L39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" s="20" t="n">
-        <v>1.699176</v>
-      </c>
-      <c r="S39" s="19" t="n">
-        <v>118801.19</v>
-      </c>
-      <c r="T39" s="19" t="n">
-        <v>117355.16</v>
-      </c>
-      <c r="U39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" s="19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="B40" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C40" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="D40" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E40" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="F40" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="G40" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="H40" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="I40" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="J40" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="K40" s="18" t="s">
-        <v>219</v>
-      </c>
-      <c r="L40" s="18" t="s">
-        <v>220</v>
-      </c>
-      <c r="M40" s="18" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="19" t="n">
-        <v>216.63</v>
-      </c>
-      <c r="B41" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C41" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" s="19" t="n">
-        <v>47.81</v>
-      </c>
-      <c r="E41" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" s="19" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="4"/>
+      <c r="A42" s="19" t="n">
+        <v>219.77</v>
+      </c>
+      <c r="B42" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="19" t="n">
+        <v>48.02</v>
+      </c>
+      <c r="E42" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="21" t="s">
-        <v>222</v>
-      </c>
-      <c r="B43" s="21"/>
-      <c r="C43" s="21"/>
-      <c r="D43" s="21"/>
-      <c r="E43" s="21"/>
-      <c r="F43" s="21"/>
-      <c r="G43" s="21"/>
-      <c r="H43" s="21"/>
-      <c r="I43" s="21"/>
-      <c r="J43" s="21"/>
-      <c r="K43" s="21"/>
-      <c r="L43" s="21"/>
-      <c r="M43" s="21"/>
-      <c r="N43" s="21"/>
-      <c r="O43" s="21"/>
-      <c r="P43" s="21"/>
-      <c r="Q43" s="21"/>
-      <c r="R43" s="21"/>
-      <c r="S43" s="21"/>
-      <c r="T43" s="21"/>
-      <c r="U43" s="21"/>
-      <c r="V43" s="21"/>
-      <c r="W43" s="21"/>
-      <c r="X43" s="21"/>
-      <c r="Y43" s="21"/>
-      <c r="Z43" s="21"/>
-      <c r="AA43" s="21"/>
-      <c r="AB43" s="21"/>
-      <c r="AC43" s="21"/>
-      <c r="AD43" s="21"/>
-      <c r="AE43" s="21"/>
-      <c r="AF43" s="21"/>
-      <c r="AG43" s="21"/>
-      <c r="AH43" s="21"/>
-      <c r="AI43" s="21"/>
-      <c r="AJ43" s="21"/>
-      <c r="AK43" s="21"/>
-      <c r="AL43" s="21"/>
-      <c r="AM43" s="21"/>
-      <c r="AN43" s="21"/>
-      <c r="AO43" s="21"/>
-      <c r="AP43" s="21"/>
-      <c r="AQ43" s="21"/>
-      <c r="AR43" s="21"/>
-      <c r="AS43" s="21"/>
-      <c r="AT43" s="21"/>
-      <c r="AU43" s="21"/>
-      <c r="AV43" s="21"/>
-      <c r="AW43" s="21"/>
-      <c r="AX43" s="21"/>
-      <c r="AY43" s="21"/>
-      <c r="AZ43" s="21"/>
-      <c r="BA43" s="21"/>
-      <c r="BB43" s="21"/>
-      <c r="BC43" s="21"/>
-      <c r="BD43" s="21"/>
-      <c r="BE43" s="21"/>
-      <c r="BF43" s="21"/>
-      <c r="BG43" s="21"/>
-      <c r="BH43" s="21"/>
-      <c r="BI43" s="21"/>
-      <c r="BJ43" s="21"/>
-      <c r="BK43" s="21"/>
-      <c r="BL43" s="21"/>
-      <c r="BM43" s="21"/>
+    <row r="43" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="4"/>
     </row>
-    <row r="44" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B44" s="4"/>
-      <c r="C44" s="4"/>
-      <c r="D44" s="4"/>
-      <c r="E44" s="4"/>
-      <c r="F44" s="4"/>
-      <c r="G44" s="4"/>
-      <c r="H44" s="4"/>
-      <c r="I44" s="4"/>
-      <c r="J44" s="4"/>
-      <c r="K44" s="4"/>
-      <c r="L44" s="4"/>
-      <c r="M44" s="4"/>
-      <c r="N44" s="4"/>
-      <c r="O44" s="4"/>
-      <c r="P44" s="4"/>
-      <c r="Q44" s="4"/>
-      <c r="R44" s="4"/>
-      <c r="S44" s="4"/>
-      <c r="T44" s="4"/>
-      <c r="U44" s="4"/>
-      <c r="V44" s="4"/>
-      <c r="W44" s="4"/>
-      <c r="X44" s="4"/>
-      <c r="Y44" s="4"/>
-      <c r="Z44" s="4"/>
-      <c r="AA44" s="4"/>
-      <c r="AB44" s="4"/>
-      <c r="AC44" s="4"/>
-      <c r="AD44" s="4"/>
-      <c r="AE44" s="4"/>
-      <c r="AF44" s="4"/>
-      <c r="AG44" s="4"/>
-      <c r="AH44" s="4"/>
-      <c r="AI44" s="4"/>
-      <c r="AJ44" s="4"/>
-      <c r="AK44" s="4"/>
-      <c r="AL44" s="4"/>
-      <c r="AM44" s="4"/>
-      <c r="AN44" s="4"/>
-      <c r="AO44" s="4"/>
-      <c r="AP44" s="4"/>
-      <c r="AQ44" s="4"/>
-      <c r="AR44" s="4"/>
-      <c r="AS44" s="4"/>
-      <c r="AT44" s="4"/>
-      <c r="AU44" s="4"/>
-      <c r="AV44" s="4"/>
-      <c r="AW44" s="4"/>
-      <c r="AX44" s="4"/>
-      <c r="AY44" s="4"/>
-      <c r="AZ44" s="4"/>
-      <c r="BA44" s="4"/>
-      <c r="BB44" s="4"/>
-      <c r="BC44" s="4"/>
-      <c r="BD44" s="4"/>
-      <c r="BE44" s="4"/>
-      <c r="BF44" s="4"/>
-      <c r="BG44" s="4"/>
-      <c r="BH44" s="4"/>
-      <c r="BI44" s="4"/>
-      <c r="BJ44" s="4"/>
-      <c r="BK44" s="4"/>
-      <c r="BL44" s="4"/>
-      <c r="BM44" s="4"/>
+    <row r="44" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="21" t="s">
+        <v>218</v>
+      </c>
+      <c r="B44" s="21"/>
+      <c r="C44" s="21"/>
+      <c r="D44" s="21"/>
+      <c r="E44" s="21"/>
+      <c r="F44" s="21"/>
+      <c r="G44" s="21"/>
+      <c r="H44" s="21"/>
+      <c r="I44" s="21"/>
+      <c r="J44" s="21"/>
+      <c r="K44" s="21"/>
+      <c r="L44" s="21"/>
+      <c r="M44" s="21"/>
+      <c r="N44" s="21"/>
+      <c r="O44" s="21"/>
+      <c r="P44" s="21"/>
+      <c r="Q44" s="21"/>
+      <c r="R44" s="21"/>
+      <c r="S44" s="21"/>
+      <c r="T44" s="21"/>
+      <c r="U44" s="21"/>
+      <c r="V44" s="21"/>
+      <c r="W44" s="21"/>
+      <c r="X44" s="21"/>
+      <c r="Y44" s="21"/>
+      <c r="Z44" s="21"/>
+      <c r="AA44" s="21"/>
+      <c r="AB44" s="21"/>
+      <c r="AC44" s="21"/>
+      <c r="AD44" s="21"/>
+      <c r="AE44" s="21"/>
+      <c r="AF44" s="21"/>
+      <c r="AG44" s="21"/>
+      <c r="AH44" s="21"/>
+      <c r="AI44" s="21"/>
+      <c r="AJ44" s="21"/>
+      <c r="AK44" s="21"/>
+      <c r="AL44" s="21"/>
+      <c r="AM44" s="21"/>
+      <c r="AN44" s="21"/>
+      <c r="AO44" s="21"/>
+      <c r="AP44" s="21"/>
+      <c r="AQ44" s="21"/>
+      <c r="AR44" s="21"/>
+      <c r="AS44" s="21"/>
+      <c r="AT44" s="21"/>
+      <c r="AU44" s="21"/>
+      <c r="AV44" s="21"/>
+      <c r="AW44" s="21"/>
+      <c r="AX44" s="21"/>
+      <c r="AY44" s="21"/>
+      <c r="AZ44" s="21"/>
+      <c r="BA44" s="21"/>
+      <c r="BB44" s="21"/>
+      <c r="BC44" s="21"/>
+      <c r="BD44" s="21"/>
+      <c r="BE44" s="21"/>
+      <c r="BF44" s="21"/>
+      <c r="BG44" s="21"/>
+      <c r="BH44" s="21"/>
+      <c r="BI44" s="21"/>
+      <c r="BJ44" s="21"/>
+      <c r="BK44" s="21"/>
+      <c r="BL44" s="21"/>
+      <c r="BM44" s="21"/>
     </row>
     <row r="45" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="4" t="s">
-        <v>223</v>
+        <v>75</v>
       </c>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
@@ -23651,7 +23761,7 @@
     </row>
     <row r="46" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="4" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
@@ -23720,7 +23830,7 @@
     </row>
     <row r="47" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
@@ -23789,7 +23899,7 @@
     </row>
     <row r="48" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="4" t="s">
-        <v>22</v>
+        <v>221</v>
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
@@ -23858,7 +23968,7 @@
     </row>
     <row r="49" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="4" t="s">
-        <v>226</v>
+        <v>22</v>
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
@@ -23927,7 +24037,7 @@
     </row>
     <row r="50" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="4" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
@@ -23996,7 +24106,7 @@
     </row>
     <row r="51" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="4" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
@@ -24065,7 +24175,7 @@
     </row>
     <row r="52" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="4" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
@@ -24134,7 +24244,7 @@
     </row>
     <row r="53" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="4" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
@@ -24201,8 +24311,77 @@
       <c r="BL53" s="4"/>
       <c r="BM53" s="4"/>
     </row>
+    <row r="54" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="B54" s="4"/>
+      <c r="C54" s="4"/>
+      <c r="D54" s="4"/>
+      <c r="E54" s="4"/>
+      <c r="F54" s="4"/>
+      <c r="G54" s="4"/>
+      <c r="H54" s="4"/>
+      <c r="I54" s="4"/>
+      <c r="J54" s="4"/>
+      <c r="K54" s="4"/>
+      <c r="L54" s="4"/>
+      <c r="M54" s="4"/>
+      <c r="N54" s="4"/>
+      <c r="O54" s="4"/>
+      <c r="P54" s="4"/>
+      <c r="Q54" s="4"/>
+      <c r="R54" s="4"/>
+      <c r="S54" s="4"/>
+      <c r="T54" s="4"/>
+      <c r="U54" s="4"/>
+      <c r="V54" s="4"/>
+      <c r="W54" s="4"/>
+      <c r="X54" s="4"/>
+      <c r="Y54" s="4"/>
+      <c r="Z54" s="4"/>
+      <c r="AA54" s="4"/>
+      <c r="AB54" s="4"/>
+      <c r="AC54" s="4"/>
+      <c r="AD54" s="4"/>
+      <c r="AE54" s="4"/>
+      <c r="AF54" s="4"/>
+      <c r="AG54" s="4"/>
+      <c r="AH54" s="4"/>
+      <c r="AI54" s="4"/>
+      <c r="AJ54" s="4"/>
+      <c r="AK54" s="4"/>
+      <c r="AL54" s="4"/>
+      <c r="AM54" s="4"/>
+      <c r="AN54" s="4"/>
+      <c r="AO54" s="4"/>
+      <c r="AP54" s="4"/>
+      <c r="AQ54" s="4"/>
+      <c r="AR54" s="4"/>
+      <c r="AS54" s="4"/>
+      <c r="AT54" s="4"/>
+      <c r="AU54" s="4"/>
+      <c r="AV54" s="4"/>
+      <c r="AW54" s="4"/>
+      <c r="AX54" s="4"/>
+      <c r="AY54" s="4"/>
+      <c r="AZ54" s="4"/>
+      <c r="BA54" s="4"/>
+      <c r="BB54" s="4"/>
+      <c r="BC54" s="4"/>
+      <c r="BD54" s="4"/>
+      <c r="BE54" s="4"/>
+      <c r="BF54" s="4"/>
+      <c r="BG54" s="4"/>
+      <c r="BH54" s="4"/>
+      <c r="BI54" s="4"/>
+      <c r="BJ54" s="4"/>
+      <c r="BK54" s="4"/>
+      <c r="BL54" s="4"/>
+      <c r="BM54" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="47">
+  <mergeCells count="48">
     <mergeCell ref="A1:BI1"/>
     <mergeCell ref="BJ1:BM1"/>
     <mergeCell ref="A2:BM2"/>
@@ -24238,8 +24417,8 @@
     <mergeCell ref="B33:E33"/>
     <mergeCell ref="B34:E34"/>
     <mergeCell ref="B35:E35"/>
-    <mergeCell ref="A37:V37"/>
-    <mergeCell ref="A43:BM43"/>
+    <mergeCell ref="B36:E36"/>
+    <mergeCell ref="A38:V38"/>
     <mergeCell ref="A44:BM44"/>
     <mergeCell ref="A45:BM45"/>
     <mergeCell ref="A46:BM46"/>
@@ -24250,6 +24429,7 @@
     <mergeCell ref="A51:BM51"/>
     <mergeCell ref="A52:BM52"/>
     <mergeCell ref="A53:BM53"/>
+    <mergeCell ref="A54:BM54"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>

--- a/tratando_tabelas/finitura/entradas_finitura.xlsx
+++ b/tratando_tabelas/finitura/entradas_finitura.xlsx
@@ -20,12 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1392" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1352" uniqueCount="235">
   <si>
     <t xml:space="preserve">Santri ADM 1.1.5.7 R1</t>
   </si>
   <si>
-    <t xml:space="preserve">Emitido em: 28/04/2026 05:30:25</t>
+    <t xml:space="preserve">Emitido em: 29/04/2026 05:30:28</t>
   </si>
   <si>
     <t xml:space="preserve">Relação de entradas - Sintético</t>
@@ -316,64 +316,7 @@
     <t xml:space="preserve">42260475339051000141550080006135571858110937</t>
   </si>
   <si>
-    <t xml:space="preserve">613.278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.088,57</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260475339051000141550080006132781579863649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">613.230</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.411,71</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260475339051000141550080006132301500422434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">612.943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.612,24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260475339051000141550080006129431856669777</t>
-  </si>
-  <si>
     <t xml:space="preserve">1.856 - DEXCO S.A - METAIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.064.044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">392,71</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050640441827095101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.064.051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163,48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050640511436911789</t>
   </si>
   <si>
     <t xml:space="preserve">5.065.606</t>
@@ -382,7 +325,13 @@
     <t xml:space="preserve">17/04/2026</t>
   </si>
   <si>
+    <t xml:space="preserve">20/04/2026</t>
+  </si>
+  <si>
     <t xml:space="preserve">4.770,41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.949</t>
   </si>
   <si>
     <t xml:space="preserve">35260497837181002190550010050656061898250181</t>
@@ -406,43 +355,13 @@
     <t xml:space="preserve">35260497837181002190550010050656251541669272</t>
   </si>
   <si>
-    <t xml:space="preserve">615.999</t>
+    <t xml:space="preserve">618.318</t>
   </si>
   <si>
     <t xml:space="preserve">22/04/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">14/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.568,57</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260475339051000141550080006159991401589579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">617.873</t>
-  </si>
-  <si>
     <t xml:space="preserve">18/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.135,16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260475339051000141550080006178731396485917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">617.874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.258,14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260475339051000141550080006178741898295127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">618.318</t>
   </si>
   <si>
     <t xml:space="preserve">5.879,02</t>
@@ -559,6 +478,9 @@
     <t xml:space="preserve">4</t>
   </si>
   <si>
+    <t xml:space="preserve">14/05/2026</t>
+  </si>
+  <si>
     <t xml:space="preserve">4.520,02</t>
   </si>
   <si>
@@ -644,6 +566,108 @@
   </si>
   <si>
     <t xml:space="preserve">35260497837181002190550010050714731527694305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">622.321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.583,52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260475339051000141550080006223211866017660</t>
+  </si>
+  <si>
+    <t xml:space="preserve">623.684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.181,41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260475339051000141550080006236841835737409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.855 - DEXCO S.A - LOUCAS DECA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.146.188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">861,88</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002271550010021461881648923974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.923 - NEW LINE ILUMINACAO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">224.086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.390,44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">397.948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89,72</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260412077181000133550030002240861005369088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260411389565000200570050003979481000841502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.134 - L.MARTINKOSKI &amp; CIA LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.260</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.070,21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41260408028676000103550010000562601004422817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.718 - STELLA IMPORTACAO E EXPORTACAO DE LUMINARIAS LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">291.625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.204,49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260410691158000370550010002916251859632469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.730,39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41260408028676000103550010000562311004422203</t>
   </si>
   <si>
     <t xml:space="preserve">Total geral</t>
@@ -16889,7 +16913,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BM54"/>
+  <dimension ref="A1:BM53"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="18"/>
@@ -18025,79 +18049,79 @@
     </row>
     <row r="9" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="n">
-        <v>305250</v>
+        <v>305457</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="K9" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L9" s="12" t="n">
-        <v>2088.57</v>
+        <v>4770.41</v>
       </c>
       <c r="M9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N9" s="12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="O9" s="12" t="n">
-        <v>2088.57</v>
+        <v>4588.46</v>
       </c>
       <c r="P9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q9" s="13" t="n">
-        <v>0.005874</v>
+        <v>0.231499</v>
       </c>
       <c r="R9" s="12" t="n">
-        <v>1.45</v>
+        <v>35.08</v>
       </c>
       <c r="S9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T9" s="14" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="U9" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V9" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W9" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X9" s="9" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="Y9" s="12" t="n">
-        <v>0</v>
+        <v>181.95</v>
       </c>
       <c r="Z9" s="12" t="n">
-        <v>2088.57</v>
+        <v>4588.46</v>
       </c>
       <c r="AA9" s="12" t="n">
-        <v>146.2</v>
+        <v>183.54</v>
       </c>
       <c r="AB9" s="12" t="n">
         <v>0</v>
@@ -18166,7 +18190,7 @@
         <v>83</v>
       </c>
       <c r="AX9" s="10" t="s">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="AY9" s="14" t="s">
         <v>75</v>
@@ -18202,7 +18226,7 @@
         <v>78</v>
       </c>
       <c r="BJ9" s="9" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="BK9" s="9" t="s">
         <v>75</v>
@@ -18216,79 +18240,79 @@
     </row>
     <row r="10" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="n">
-        <v>305251</v>
+        <v>305470</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
       <c r="F10" s="9" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="K10" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L10" s="12" t="n">
-        <v>1411.71</v>
+        <v>314.65</v>
       </c>
       <c r="M10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N10" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O10" s="12" t="n">
-        <v>1411.71</v>
+        <v>295.45</v>
       </c>
       <c r="P10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q10" s="13" t="n">
-        <v>0.000432</v>
+        <v>0.016472</v>
       </c>
       <c r="R10" s="12" t="n">
-        <v>0.74</v>
+        <v>1.6</v>
       </c>
       <c r="S10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T10" s="14" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="U10" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V10" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W10" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X10" s="9" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="Y10" s="12" t="n">
-        <v>0</v>
+        <v>19.2</v>
       </c>
       <c r="Z10" s="12" t="n">
-        <v>1411.71</v>
+        <v>295.45</v>
       </c>
       <c r="AA10" s="12" t="n">
-        <v>98.82</v>
+        <v>11.81</v>
       </c>
       <c r="AB10" s="12" t="n">
         <v>0</v>
@@ -18357,7 +18381,7 @@
         <v>83</v>
       </c>
       <c r="AX10" s="10" t="s">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="AY10" s="14" t="s">
         <v>75</v>
@@ -18393,7 +18417,7 @@
         <v>78</v>
       </c>
       <c r="BJ10" s="9" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="BK10" s="9" t="s">
         <v>75</v>
@@ -18407,79 +18431,79 @@
     </row>
     <row r="11" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="n">
-        <v>305258</v>
+        <v>305480</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
       <c r="F11" s="9" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="K11" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>5612.24</v>
+        <v>2373.3</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O11" s="12" t="n">
-        <v>5612.24</v>
+        <v>2228.46</v>
       </c>
       <c r="P11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q11" s="13" t="n">
-        <v>0.034</v>
+        <v>0.017186</v>
       </c>
       <c r="R11" s="12" t="n">
-        <v>10.12</v>
+        <v>12.33</v>
       </c>
       <c r="S11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T11" s="14" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="U11" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V11" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W11" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X11" s="9" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="Y11" s="12" t="n">
-        <v>0</v>
+        <v>144.84</v>
       </c>
       <c r="Z11" s="12" t="n">
-        <v>5612.24</v>
+        <v>2228.46</v>
       </c>
       <c r="AA11" s="12" t="n">
-        <v>392.86</v>
+        <v>89.14</v>
       </c>
       <c r="AB11" s="12" t="n">
         <v>0</v>
@@ -18548,7 +18572,7 @@
         <v>83</v>
       </c>
       <c r="AX11" s="10" t="s">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="AY11" s="14" t="s">
         <v>75</v>
@@ -18584,7 +18608,7 @@
         <v>78</v>
       </c>
       <c r="BJ11" s="9" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="BK11" s="9" t="s">
         <v>75</v>
@@ -18598,34 +18622,34 @@
     </row>
     <row r="12" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="n">
-        <v>305419</v>
+        <v>305556</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
       <c r="F12" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="K12" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>392.71</v>
+        <v>5879.02</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>0</v>
@@ -18634,43 +18658,43 @@
         <v>1</v>
       </c>
       <c r="O12" s="12" t="n">
-        <v>368.74</v>
+        <v>5879.02</v>
       </c>
       <c r="P12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" s="13" t="n">
-        <v>0.006789</v>
+        <v>0.467698</v>
       </c>
       <c r="R12" s="12" t="n">
-        <v>3.81</v>
+        <v>31.5</v>
       </c>
       <c r="S12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T12" s="14" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="U12" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V12" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W12" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X12" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Y12" s="12" t="n">
-        <v>23.97</v>
+        <v>0</v>
       </c>
       <c r="Z12" s="12" t="n">
-        <v>368.74</v>
+        <v>5879.02</v>
       </c>
       <c r="AA12" s="12" t="n">
-        <v>14.75</v>
+        <v>411.53</v>
       </c>
       <c r="AB12" s="12" t="n">
         <v>0</v>
@@ -18739,7 +18763,7 @@
         <v>83</v>
       </c>
       <c r="AX12" s="10" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="AY12" s="14" t="s">
         <v>75</v>
@@ -18775,7 +18799,7 @@
         <v>78</v>
       </c>
       <c r="BJ12" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="BK12" s="9" t="s">
         <v>75</v>
@@ -18789,34 +18813,34 @@
     </row>
     <row r="13" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="n">
-        <v>305443</v>
+        <v>305560</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
       <c r="F13" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>89</v>
+        <v>117</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="K13" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>163.48</v>
+        <v>3121.47</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>0</v>
@@ -18825,43 +18849,43 @@
         <v>1</v>
       </c>
       <c r="O13" s="12" t="n">
-        <v>153.5</v>
+        <v>3121.47</v>
       </c>
       <c r="P13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q13" s="13" t="n">
-        <v>0.003456</v>
+        <v>0.031059</v>
       </c>
       <c r="R13" s="12" t="n">
-        <v>0.8</v>
+        <v>5.54</v>
       </c>
       <c r="S13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T13" s="14" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="U13" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V13" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W13" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X13" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Y13" s="12" t="n">
-        <v>9.98</v>
+        <v>0</v>
       </c>
       <c r="Z13" s="12" t="n">
-        <v>153.5</v>
+        <v>3121.47</v>
       </c>
       <c r="AA13" s="12" t="n">
-        <v>6.14</v>
+        <v>218.5</v>
       </c>
       <c r="AB13" s="12" t="n">
         <v>0</v>
@@ -18930,7 +18954,7 @@
         <v>83</v>
       </c>
       <c r="AX13" s="10" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="AY13" s="14" t="s">
         <v>75</v>
@@ -18966,7 +18990,7 @@
         <v>78</v>
       </c>
       <c r="BJ13" s="9" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="BK13" s="9" t="s">
         <v>75</v>
@@ -18980,79 +19004,79 @@
     </row>
     <row r="14" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="n">
-        <v>305457</v>
+        <v>305561</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
       <c r="F14" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="J14" s="9" t="s">
         <v>118</v>
-      </c>
-      <c r="G14" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="I14" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="J14" s="9" t="s">
-        <v>78</v>
       </c>
       <c r="K14" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>4770.41</v>
+        <v>5331.26</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="O14" s="12" t="n">
-        <v>4588.46</v>
+        <v>5005.88</v>
       </c>
       <c r="P14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q14" s="13" t="n">
-        <v>0.231499</v>
+        <v>0.055816</v>
       </c>
       <c r="R14" s="12" t="n">
-        <v>35.08</v>
+        <v>7.12</v>
       </c>
       <c r="S14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T14" s="14" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="U14" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V14" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W14" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X14" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Y14" s="12" t="n">
-        <v>181.95</v>
+        <v>325.38</v>
       </c>
       <c r="Z14" s="12" t="n">
-        <v>4588.46</v>
+        <v>5005.88</v>
       </c>
       <c r="AA14" s="12" t="n">
-        <v>183.54</v>
+        <v>350.41</v>
       </c>
       <c r="AB14" s="12" t="n">
         <v>0</v>
@@ -19121,7 +19145,7 @@
         <v>83</v>
       </c>
       <c r="AX14" s="10" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="AY14" s="14" t="s">
         <v>75</v>
@@ -19157,7 +19181,7 @@
         <v>78</v>
       </c>
       <c r="BJ14" s="9" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="BK14" s="9" t="s">
         <v>75</v>
@@ -19171,79 +19195,79 @@
     </row>
     <row r="15" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="n">
-        <v>305470</v>
+        <v>305681</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
       <c r="F15" s="9" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>78</v>
+        <v>126</v>
       </c>
       <c r="K15" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>314.65</v>
+        <v>1945.98</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O15" s="12" t="n">
-        <v>295.45</v>
+        <v>1945.98</v>
       </c>
       <c r="P15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q15" s="13" t="n">
-        <v>0.016472</v>
+        <v>0.004946</v>
       </c>
       <c r="R15" s="12" t="n">
-        <v>1.6</v>
+        <v>1.15</v>
       </c>
       <c r="S15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T15" s="14" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="U15" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V15" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W15" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X15" s="9" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="Y15" s="12" t="n">
-        <v>19.2</v>
+        <v>0</v>
       </c>
       <c r="Z15" s="12" t="n">
-        <v>295.45</v>
+        <v>1945.98</v>
       </c>
       <c r="AA15" s="12" t="n">
-        <v>11.81</v>
+        <v>136.22</v>
       </c>
       <c r="AB15" s="12" t="n">
         <v>0</v>
@@ -19312,7 +19336,7 @@
         <v>83</v>
       </c>
       <c r="AX15" s="10" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="AY15" s="14" t="s">
         <v>75</v>
@@ -19348,7 +19372,7 @@
         <v>78</v>
       </c>
       <c r="BJ15" s="9" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="BK15" s="9" t="s">
         <v>75</v>
@@ -19362,79 +19386,79 @@
     </row>
     <row r="16" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="n">
-        <v>305480</v>
+        <v>305691</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
       <c r="F16" s="9" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="G16" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>78</v>
+        <v>126</v>
       </c>
       <c r="K16" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>2373.3</v>
+        <v>3563.51</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O16" s="12" t="n">
-        <v>2228.46</v>
+        <v>3098.7</v>
       </c>
       <c r="P16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q16" s="13" t="n">
-        <v>0.017186</v>
+        <v>0</v>
       </c>
       <c r="R16" s="12" t="n">
-        <v>12.33</v>
+        <v>0</v>
       </c>
       <c r="S16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T16" s="14" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="U16" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V16" s="12" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="W16" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X16" s="9" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="Y16" s="12" t="n">
-        <v>144.84</v>
+        <v>464.81</v>
       </c>
       <c r="Z16" s="12" t="n">
-        <v>2228.46</v>
+        <v>3098.7</v>
       </c>
       <c r="AA16" s="12" t="n">
-        <v>89.14</v>
+        <v>216.91</v>
       </c>
       <c r="AB16" s="12" t="n">
         <v>0</v>
@@ -19503,7 +19527,7 @@
         <v>83</v>
       </c>
       <c r="AX16" s="10" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="AY16" s="14" t="s">
         <v>75</v>
@@ -19539,7 +19563,7 @@
         <v>78</v>
       </c>
       <c r="BJ16" s="9" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="BK16" s="9" t="s">
         <v>75</v>
@@ -19553,7 +19577,7 @@
     </row>
     <row r="17" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="n">
-        <v>305539</v>
+        <v>305724</v>
       </c>
       <c r="B17" s="9" t="s">
         <v>93</v>
@@ -19562,25 +19586,25 @@
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
       <c r="F17" s="9" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="G17" s="10" t="s">
         <v>95</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="K17" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>1568.57</v>
+        <v>1674.18</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>0</v>
@@ -19589,22 +19613,22 @@
         <v>1</v>
       </c>
       <c r="O17" s="12" t="n">
-        <v>1568.57</v>
+        <v>1674.18</v>
       </c>
       <c r="P17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q17" s="13" t="n">
-        <v>0.000432</v>
+        <v>0.003916</v>
       </c>
       <c r="R17" s="12" t="n">
-        <v>0.74</v>
+        <v>0.97</v>
       </c>
       <c r="S17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T17" s="14" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="U17" s="15" t="s">
         <v>72</v>
@@ -19616,16 +19640,16 @@
         <v>73</v>
       </c>
       <c r="X17" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="Y17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z17" s="12" t="n">
-        <v>1568.57</v>
+        <v>1674.18</v>
       </c>
       <c r="AA17" s="12" t="n">
-        <v>109.8</v>
+        <v>117.19</v>
       </c>
       <c r="AB17" s="12" t="n">
         <v>0</v>
@@ -19730,7 +19754,7 @@
         <v>78</v>
       </c>
       <c r="BJ17" s="9" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="BK17" s="9" t="s">
         <v>75</v>
@@ -19744,25 +19768,25 @@
     </row>
     <row r="18" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="n">
-        <v>305553</v>
+        <v>305725</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>93</v>
+        <v>137</v>
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
       <c r="F18" s="9" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="J18" s="9" t="s">
         <v>134</v>
@@ -19771,31 +19795,31 @@
         <v>70</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>3135.16</v>
+        <v>10012.8</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O18" s="12" t="n">
-        <v>3135.16</v>
+        <v>10012.8</v>
       </c>
       <c r="P18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q18" s="13" t="n">
-        <v>0.000864</v>
+        <v>0.750038</v>
       </c>
       <c r="R18" s="12" t="n">
-        <v>1.48</v>
+        <v>38</v>
       </c>
       <c r="S18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T18" s="14" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="U18" s="15" t="s">
         <v>72</v>
@@ -19807,16 +19831,16 @@
         <v>73</v>
       </c>
       <c r="X18" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="Y18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z18" s="12" t="n">
-        <v>3135.16</v>
+        <v>10012.8</v>
       </c>
       <c r="AA18" s="12" t="n">
-        <v>219.46</v>
+        <v>400.51</v>
       </c>
       <c r="AB18" s="12" t="n">
         <v>0</v>
@@ -19921,7 +19945,7 @@
         <v>78</v>
       </c>
       <c r="BJ18" s="9" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="BK18" s="9" t="s">
         <v>75</v>
@@ -19935,25 +19959,25 @@
     </row>
     <row r="19" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="n">
-        <v>305554</v>
+        <v>305731</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
       <c r="F19" s="9" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="J19" s="9" t="s">
         <v>134</v>
@@ -19962,31 +19986,31 @@
         <v>70</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>3258.14</v>
+        <v>6247.73</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O19" s="12" t="n">
-        <v>3258.14</v>
+        <v>6247.73</v>
       </c>
       <c r="P19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q19" s="13" t="n">
-        <v>0.000864</v>
+        <v>0.030808</v>
       </c>
       <c r="R19" s="12" t="n">
-        <v>1.48</v>
+        <v>6.05</v>
       </c>
       <c r="S19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T19" s="14" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="U19" s="15" t="s">
         <v>72</v>
@@ -19998,16 +20022,16 @@
         <v>73</v>
       </c>
       <c r="X19" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="Y19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z19" s="12" t="n">
-        <v>3258.14</v>
+        <v>6247.73</v>
       </c>
       <c r="AA19" s="12" t="n">
-        <v>228.07</v>
+        <v>437.34</v>
       </c>
       <c r="AB19" s="12" t="n">
         <v>0</v>
@@ -20112,7 +20136,7 @@
         <v>78</v>
       </c>
       <c r="BJ19" s="9" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="BK19" s="9" t="s">
         <v>75</v>
@@ -20126,79 +20150,79 @@
     </row>
     <row r="20" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="n">
-        <v>305556</v>
+        <v>305778</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>93</v>
+        <v>144</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
       <c r="F20" s="9" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="K20" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>5879.02</v>
+        <v>834.78</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O20" s="12" t="n">
-        <v>5879.02</v>
+        <v>730</v>
       </c>
       <c r="P20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q20" s="13" t="n">
-        <v>0.467698</v>
+        <v>0</v>
       </c>
       <c r="R20" s="12" t="n">
-        <v>31.5</v>
+        <v>0</v>
       </c>
       <c r="S20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T20" s="14" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="U20" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V20" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="W20" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X20" s="9" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="Y20" s="12" t="n">
-        <v>0</v>
+        <v>104.78</v>
       </c>
       <c r="Z20" s="12" t="n">
-        <v>5879.02</v>
+        <v>730</v>
       </c>
       <c r="AA20" s="12" t="n">
-        <v>411.53</v>
+        <v>51.1</v>
       </c>
       <c r="AB20" s="12" t="n">
         <v>0</v>
@@ -20264,7 +20288,7 @@
         <v>74</v>
       </c>
       <c r="AW20" s="14" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AX20" s="10" t="s">
         <v>77</v>
@@ -20303,7 +20327,7 @@
         <v>78</v>
       </c>
       <c r="BJ20" s="9" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="BK20" s="9" t="s">
         <v>75</v>
@@ -20317,79 +20341,79 @@
     </row>
     <row r="21" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="n">
-        <v>305560</v>
+        <v>305787</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>93</v>
+        <v>149</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
       <c r="F21" s="9" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>95</v>
+        <v>151</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>144</v>
+        <v>89</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="K21" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>3121.47</v>
+        <v>4520.02</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O21" s="12" t="n">
-        <v>3121.47</v>
+        <v>4520.02</v>
       </c>
       <c r="P21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q21" s="13" t="n">
-        <v>0.031059</v>
+        <v>0.004608</v>
       </c>
       <c r="R21" s="12" t="n">
-        <v>5.54</v>
+        <v>36.69</v>
       </c>
       <c r="S21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T21" s="14" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="U21" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V21" s="12" t="n">
-        <v>28</v>
+        <v>55.99</v>
       </c>
       <c r="W21" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X21" s="9" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="Y21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z21" s="12" t="n">
-        <v>3121.47</v>
+        <v>4520.02</v>
       </c>
       <c r="AA21" s="12" t="n">
-        <v>218.5</v>
+        <v>316.39</v>
       </c>
       <c r="AB21" s="12" t="n">
         <v>0</v>
@@ -20398,7 +20422,7 @@
         <v>0</v>
       </c>
       <c r="AD21" s="12" t="n">
-        <v>0</v>
+        <v>91.25</v>
       </c>
       <c r="AE21" s="12" t="n">
         <v>0</v>
@@ -20479,25 +20503,25 @@
         <v>75</v>
       </c>
       <c r="BE21" s="14" t="s">
-        <v>75</v>
+        <v>154</v>
       </c>
       <c r="BF21" s="9" t="s">
-        <v>75</v>
+        <v>155</v>
       </c>
       <c r="BG21" s="9" t="s">
-        <v>78</v>
+        <v>112</v>
       </c>
       <c r="BH21" s="14" t="s">
-        <v>75</v>
+        <v>156</v>
       </c>
       <c r="BI21" s="9" t="s">
-        <v>78</v>
+        <v>125</v>
       </c>
       <c r="BJ21" s="9" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="BK21" s="9" t="s">
-        <v>75</v>
+        <v>158</v>
       </c>
       <c r="BL21" s="9" t="s">
         <v>75</v>
@@ -20508,7 +20532,7 @@
     </row>
     <row r="22" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="n">
-        <v>305561</v>
+        <v>305821</v>
       </c>
       <c r="B22" s="9" t="s">
         <v>93</v>
@@ -20517,25 +20541,25 @@
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
       <c r="F22" s="9" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="G22" s="10" t="s">
         <v>95</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="K22" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>5331.26</v>
+        <v>4462.34</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>0</v>
@@ -20544,22 +20568,22 @@
         <v>1</v>
       </c>
       <c r="O22" s="12" t="n">
-        <v>5005.88</v>
+        <v>4462.34</v>
       </c>
       <c r="P22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q22" s="13" t="n">
-        <v>0.055816</v>
+        <v>0.010272</v>
       </c>
       <c r="R22" s="12" t="n">
-        <v>7.12</v>
+        <v>3.7</v>
       </c>
       <c r="S22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T22" s="14" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="U22" s="15" t="s">
         <v>72</v>
@@ -20571,16 +20595,16 @@
         <v>73</v>
       </c>
       <c r="X22" s="9" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="Y22" s="12" t="n">
-        <v>325.38</v>
+        <v>0</v>
       </c>
       <c r="Z22" s="12" t="n">
-        <v>5005.88</v>
+        <v>4462.34</v>
       </c>
       <c r="AA22" s="12" t="n">
-        <v>350.41</v>
+        <v>312.36</v>
       </c>
       <c r="AB22" s="12" t="n">
         <v>0</v>
@@ -20685,7 +20709,7 @@
         <v>78</v>
       </c>
       <c r="BJ22" s="9" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="BK22" s="9" t="s">
         <v>75</v>
@@ -20699,7 +20723,7 @@
     </row>
     <row r="23" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="n">
-        <v>305681</v>
+        <v>305822</v>
       </c>
       <c r="B23" s="9" t="s">
         <v>93</v>
@@ -20708,25 +20732,25 @@
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="9" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="G23" s="10" t="s">
         <v>95</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="K23" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>1945.98</v>
+        <v>1464.23</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>0</v>
@@ -20735,22 +20759,22 @@
         <v>1</v>
       </c>
       <c r="O23" s="12" t="n">
-        <v>1945.98</v>
+        <v>1464.23</v>
       </c>
       <c r="P23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q23" s="13" t="n">
-        <v>0.004946</v>
+        <v>0.002473</v>
       </c>
       <c r="R23" s="12" t="n">
-        <v>1.15</v>
+        <v>0.77</v>
       </c>
       <c r="S23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T23" s="14" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="U23" s="15" t="s">
         <v>72</v>
@@ -20762,16 +20786,16 @@
         <v>73</v>
       </c>
       <c r="X23" s="9" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="Y23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z23" s="12" t="n">
-        <v>1945.98</v>
+        <v>1464.23</v>
       </c>
       <c r="AA23" s="12" t="n">
-        <v>136.22</v>
+        <v>102.5</v>
       </c>
       <c r="AB23" s="12" t="n">
         <v>0</v>
@@ -20876,7 +20900,7 @@
         <v>78</v>
       </c>
       <c r="BJ23" s="9" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="BK23" s="9" t="s">
         <v>75</v>
@@ -20890,79 +20914,79 @@
     </row>
     <row r="24" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="n">
-        <v>305691</v>
+        <v>305829</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>156</v>
+        <v>93</v>
       </c>
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
       <c r="F24" s="9" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>152</v>
+        <v>125</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>153</v>
+        <v>126</v>
       </c>
       <c r="K24" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>3563.51</v>
+        <v>3019.02</v>
       </c>
       <c r="M24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O24" s="12" t="n">
-        <v>3098.7</v>
+        <v>3019.02</v>
       </c>
       <c r="P24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q24" s="13" t="n">
-        <v>0</v>
+        <v>0.004946</v>
       </c>
       <c r="R24" s="12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T24" s="14" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="U24" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V24" s="12" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="W24" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X24" s="9" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="Y24" s="12" t="n">
-        <v>464.81</v>
+        <v>0</v>
       </c>
       <c r="Z24" s="12" t="n">
-        <v>3098.7</v>
+        <v>3019.02</v>
       </c>
       <c r="AA24" s="12" t="n">
-        <v>216.91</v>
+        <v>211.33</v>
       </c>
       <c r="AB24" s="12" t="n">
         <v>0</v>
@@ -21067,7 +21091,7 @@
         <v>78</v>
       </c>
       <c r="BJ24" s="9" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="BK24" s="9" t="s">
         <v>75</v>
@@ -21081,34 +21105,34 @@
     </row>
     <row r="25" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="n">
-        <v>305724</v>
+        <v>305933</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>161</v>
+        <v>78</v>
       </c>
       <c r="K25" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>1674.18</v>
+        <v>366.64</v>
       </c>
       <c r="M25" s="12" t="n">
         <v>0</v>
@@ -21117,43 +21141,43 @@
         <v>1</v>
       </c>
       <c r="O25" s="12" t="n">
-        <v>1674.18</v>
+        <v>344.26</v>
       </c>
       <c r="P25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q25" s="13" t="n">
-        <v>0.003916</v>
+        <v>0.007989</v>
       </c>
       <c r="R25" s="12" t="n">
-        <v>0.97</v>
+        <v>1.76</v>
       </c>
       <c r="S25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T25" s="14" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="U25" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V25" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W25" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X25" s="9" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="Y25" s="12" t="n">
-        <v>0</v>
+        <v>22.38</v>
       </c>
       <c r="Z25" s="12" t="n">
-        <v>1674.18</v>
+        <v>344.26</v>
       </c>
       <c r="AA25" s="12" t="n">
-        <v>117.19</v>
+        <v>13.77</v>
       </c>
       <c r="AB25" s="12" t="n">
         <v>0</v>
@@ -21222,7 +21246,7 @@
         <v>83</v>
       </c>
       <c r="AX25" s="10" t="s">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="AY25" s="14" t="s">
         <v>75</v>
@@ -21258,7 +21282,7 @@
         <v>78</v>
       </c>
       <c r="BJ25" s="9" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="BK25" s="9" t="s">
         <v>75</v>
@@ -21272,79 +21296,79 @@
     </row>
     <row r="26" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="n">
-        <v>305725</v>
+        <v>305942</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>164</v>
+        <v>98</v>
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="G26" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>161</v>
+        <v>78</v>
       </c>
       <c r="K26" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>10012.8</v>
+        <v>42.44</v>
       </c>
       <c r="M26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O26" s="12" t="n">
-        <v>10012.8</v>
+        <v>39.85</v>
       </c>
       <c r="P26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q26" s="13" t="n">
-        <v>0.750038</v>
+        <v>0.002284</v>
       </c>
       <c r="R26" s="12" t="n">
-        <v>38</v>
+        <v>0.8</v>
       </c>
       <c r="S26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T26" s="14" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="U26" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V26" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W26" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X26" s="9" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="Y26" s="12" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Z26" s="12" t="n">
-        <v>10012.8</v>
+        <v>39.85</v>
       </c>
       <c r="AA26" s="12" t="n">
-        <v>400.51</v>
+        <v>1.59</v>
       </c>
       <c r="AB26" s="12" t="n">
         <v>0</v>
@@ -21413,7 +21437,7 @@
         <v>83</v>
       </c>
       <c r="AX26" s="10" t="s">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="AY26" s="14" t="s">
         <v>75</v>
@@ -21449,7 +21473,7 @@
         <v>78</v>
       </c>
       <c r="BJ26" s="9" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="BK26" s="9" t="s">
         <v>75</v>
@@ -21463,79 +21487,79 @@
     </row>
     <row r="27" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="n">
-        <v>305731</v>
+        <v>305957</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="G27" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>129</v>
+        <v>170</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="J27" s="9" t="s">
-        <v>161</v>
+        <v>78</v>
       </c>
       <c r="K27" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>6247.73</v>
+        <v>126.7</v>
       </c>
       <c r="M27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O27" s="12" t="n">
-        <v>6247.73</v>
+        <v>118.97</v>
       </c>
       <c r="P27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q27" s="13" t="n">
-        <v>0.030808</v>
+        <v>0.001512</v>
       </c>
       <c r="R27" s="12" t="n">
-        <v>6.05</v>
+        <v>1.58</v>
       </c>
       <c r="S27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T27" s="14" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="U27" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V27" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W27" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X27" s="9" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="Y27" s="12" t="n">
-        <v>0</v>
+        <v>7.73</v>
       </c>
       <c r="Z27" s="12" t="n">
-        <v>6247.73</v>
+        <v>118.97</v>
       </c>
       <c r="AA27" s="12" t="n">
-        <v>437.34</v>
+        <v>4.76</v>
       </c>
       <c r="AB27" s="12" t="n">
         <v>0</v>
@@ -21604,7 +21628,7 @@
         <v>83</v>
       </c>
       <c r="AX27" s="10" t="s">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="AY27" s="14" t="s">
         <v>75</v>
@@ -21640,7 +21664,7 @@
         <v>78</v>
       </c>
       <c r="BJ27" s="9" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="BK27" s="9" t="s">
         <v>75</v>
@@ -21654,34 +21678,34 @@
     </row>
     <row r="28" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="n">
-        <v>305778</v>
+        <v>305966</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>171</v>
+        <v>98</v>
       </c>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="G28" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>144</v>
+        <v>170</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="K28" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>834.78</v>
+        <v>290.09</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>0</v>
@@ -21690,43 +21714,43 @@
         <v>2</v>
       </c>
       <c r="O28" s="12" t="n">
-        <v>730</v>
+        <v>272.38</v>
       </c>
       <c r="P28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q28" s="13" t="n">
-        <v>0</v>
+        <v>0.003202</v>
       </c>
       <c r="R28" s="12" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T28" s="14" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="U28" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V28" s="12" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="W28" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X28" s="9" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="Y28" s="12" t="n">
-        <v>104.78</v>
+        <v>17.71</v>
       </c>
       <c r="Z28" s="12" t="n">
-        <v>730</v>
+        <v>272.38</v>
       </c>
       <c r="AA28" s="12" t="n">
-        <v>51.1</v>
+        <v>10.89</v>
       </c>
       <c r="AB28" s="12" t="n">
         <v>0</v>
@@ -21792,10 +21816,10 @@
         <v>74</v>
       </c>
       <c r="AW28" s="14" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AX28" s="10" t="s">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="AY28" s="14" t="s">
         <v>75</v>
@@ -21831,7 +21855,7 @@
         <v>78</v>
       </c>
       <c r="BJ28" s="9" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="BK28" s="9" t="s">
         <v>75</v>
@@ -21845,79 +21869,79 @@
     </row>
     <row r="29" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="n">
-        <v>305787</v>
+        <v>305994</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>176</v>
+        <v>93</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
       <c r="F29" s="9" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>178</v>
+        <v>95</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>89</v>
+        <v>125</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="K29" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>4520.02</v>
+        <v>2583.52</v>
       </c>
       <c r="M29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O29" s="12" t="n">
-        <v>4520.02</v>
+        <v>2583.52</v>
       </c>
       <c r="P29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q29" s="13" t="n">
-        <v>0.004608</v>
+        <v>0.007527</v>
       </c>
       <c r="R29" s="12" t="n">
-        <v>36.69</v>
+        <v>1.95</v>
       </c>
       <c r="S29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T29" s="14" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="U29" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V29" s="12" t="n">
-        <v>55.99</v>
+        <v>28</v>
       </c>
       <c r="W29" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X29" s="9" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="Y29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z29" s="12" t="n">
-        <v>4520.02</v>
+        <v>2583.52</v>
       </c>
       <c r="AA29" s="12" t="n">
-        <v>316.39</v>
+        <v>180.85</v>
       </c>
       <c r="AB29" s="12" t="n">
         <v>0</v>
@@ -21926,7 +21950,7 @@
         <v>0</v>
       </c>
       <c r="AD29" s="12" t="n">
-        <v>91.25</v>
+        <v>0</v>
       </c>
       <c r="AE29" s="12" t="n">
         <v>0</v>
@@ -22007,25 +22031,25 @@
         <v>75</v>
       </c>
       <c r="BE29" s="14" t="s">
-        <v>180</v>
+        <v>75</v>
       </c>
       <c r="BF29" s="9" t="s">
-        <v>181</v>
+        <v>75</v>
       </c>
       <c r="BG29" s="9" t="s">
-        <v>129</v>
+        <v>78</v>
       </c>
       <c r="BH29" s="14" t="s">
-        <v>182</v>
+        <v>75</v>
       </c>
       <c r="BI29" s="9" t="s">
-        <v>152</v>
+        <v>78</v>
       </c>
       <c r="BJ29" s="9" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="BK29" s="9" t="s">
-        <v>184</v>
+        <v>75</v>
       </c>
       <c r="BL29" s="9" t="s">
         <v>75</v>
@@ -22036,7 +22060,7 @@
     </row>
     <row r="30" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="n">
-        <v>305821</v>
+        <v>306001</v>
       </c>
       <c r="B30" s="9" t="s">
         <v>93</v>
@@ -22045,25 +22069,25 @@
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
       <c r="F30" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G30" s="10" t="s">
         <v>95</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="K30" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>4462.34</v>
+        <v>1181.41</v>
       </c>
       <c r="M30" s="12" t="n">
         <v>0</v>
@@ -22072,22 +22096,22 @@
         <v>1</v>
       </c>
       <c r="O30" s="12" t="n">
-        <v>4462.34</v>
+        <v>1181.41</v>
       </c>
       <c r="P30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q30" s="13" t="n">
-        <v>0.010272</v>
+        <v>0.000412</v>
       </c>
       <c r="R30" s="12" t="n">
-        <v>3.7</v>
+        <v>0.71</v>
       </c>
       <c r="S30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T30" s="14" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="U30" s="15" t="s">
         <v>72</v>
@@ -22099,16 +22123,16 @@
         <v>73</v>
       </c>
       <c r="X30" s="9" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="Y30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z30" s="12" t="n">
-        <v>4462.34</v>
+        <v>1181.41</v>
       </c>
       <c r="AA30" s="12" t="n">
-        <v>312.36</v>
+        <v>82.7</v>
       </c>
       <c r="AB30" s="12" t="n">
         <v>0</v>
@@ -22213,7 +22237,7 @@
         <v>78</v>
       </c>
       <c r="BJ30" s="9" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="BK30" s="9" t="s">
         <v>75</v>
@@ -22227,34 +22251,34 @@
     </row>
     <row r="31" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="n">
-        <v>305822</v>
+        <v>306005</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>93</v>
+        <v>191</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
       <c r="F31" s="9" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>173</v>
+        <v>146</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="J31" s="9" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="K31" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>1464.23</v>
+        <v>861.88</v>
       </c>
       <c r="M31" s="12" t="n">
         <v>0</v>
@@ -22263,43 +22287,43 @@
         <v>1</v>
       </c>
       <c r="O31" s="12" t="n">
-        <v>1464.23</v>
+        <v>861.88</v>
       </c>
       <c r="P31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q31" s="13" t="n">
-        <v>0.002473</v>
+        <v>0.073796</v>
       </c>
       <c r="R31" s="12" t="n">
-        <v>0.77</v>
+        <v>43.13</v>
       </c>
       <c r="S31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T31" s="14" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="U31" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V31" s="12" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="W31" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X31" s="9" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="Y31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z31" s="12" t="n">
-        <v>1464.23</v>
+        <v>861.88</v>
       </c>
       <c r="AA31" s="12" t="n">
-        <v>102.5</v>
+        <v>60.33</v>
       </c>
       <c r="AB31" s="12" t="n">
         <v>0</v>
@@ -22404,7 +22428,7 @@
         <v>78</v>
       </c>
       <c r="BJ31" s="9" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="BK31" s="9" t="s">
         <v>75</v>
@@ -22418,58 +22442,58 @@
     </row>
     <row r="32" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="n">
-        <v>305829</v>
+        <v>306127</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>93</v>
+        <v>196</v>
       </c>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
       <c r="F32" s="9" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="G32" s="10" t="s">
-        <v>95</v>
+        <v>198</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>152</v>
+        <v>125</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="J32" s="9" t="s">
-        <v>153</v>
+        <v>126</v>
       </c>
       <c r="K32" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>3019.02</v>
+        <v>4390.44</v>
       </c>
       <c r="M32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O32" s="12" t="n">
-        <v>3019.02</v>
+        <v>4000.4</v>
       </c>
       <c r="P32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q32" s="13" t="n">
-        <v>0.004946</v>
+        <v>0</v>
       </c>
       <c r="R32" s="12" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T32" s="14" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="U32" s="15" t="s">
         <v>72</v>
@@ -22481,16 +22505,16 @@
         <v>73</v>
       </c>
       <c r="X32" s="9" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="Y32" s="12" t="n">
-        <v>0</v>
+        <v>390.04</v>
       </c>
       <c r="Z32" s="12" t="n">
-        <v>3019.02</v>
+        <v>4000.4</v>
       </c>
       <c r="AA32" s="12" t="n">
-        <v>211.33</v>
+        <v>280.03</v>
       </c>
       <c r="AB32" s="12" t="n">
         <v>0</v>
@@ -22499,7 +22523,7 @@
         <v>0</v>
       </c>
       <c r="AD32" s="12" t="n">
-        <v>0</v>
+        <v>89.72</v>
       </c>
       <c r="AE32" s="12" t="n">
         <v>0</v>
@@ -22580,25 +22604,25 @@
         <v>75</v>
       </c>
       <c r="BE32" s="14" t="s">
-        <v>75</v>
+        <v>200</v>
       </c>
       <c r="BF32" s="9" t="s">
-        <v>75</v>
+        <v>155</v>
       </c>
       <c r="BG32" s="9" t="s">
-        <v>78</v>
+        <v>146</v>
       </c>
       <c r="BH32" s="14" t="s">
-        <v>75</v>
+        <v>201</v>
       </c>
       <c r="BI32" s="9" t="s">
-        <v>78</v>
+        <v>146</v>
       </c>
       <c r="BJ32" s="9" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="BK32" s="9" t="s">
-        <v>75</v>
+        <v>203</v>
       </c>
       <c r="BL32" s="9" t="s">
         <v>75</v>
@@ -22609,79 +22633,79 @@
     </row>
     <row r="33" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="n">
-        <v>305933</v>
+        <v>306150</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>109</v>
+        <v>204</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="9"/>
       <c r="E33" s="9"/>
       <c r="F33" s="9" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="G33" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="I33" s="9" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="J33" s="9" t="s">
-        <v>78</v>
+        <v>206</v>
       </c>
       <c r="K33" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>366.64</v>
+        <v>2070.21</v>
       </c>
       <c r="M33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O33" s="12" t="n">
-        <v>344.26</v>
+        <v>1970.21</v>
       </c>
       <c r="P33" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q33" s="13" t="n">
-        <v>0.007989</v>
+        <v>0</v>
       </c>
       <c r="R33" s="12" t="n">
-        <v>1.76</v>
+        <v>4.15</v>
       </c>
       <c r="S33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T33" s="14" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="U33" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V33" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W33" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X33" s="9" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="Y33" s="12" t="n">
-        <v>22.38</v>
+        <v>0</v>
       </c>
       <c r="Z33" s="12" t="n">
-        <v>344.26</v>
+        <v>2070.21</v>
       </c>
       <c r="AA33" s="12" t="n">
-        <v>13.77</v>
+        <v>144.92</v>
       </c>
       <c r="AB33" s="12" t="n">
         <v>0</v>
@@ -22750,7 +22774,7 @@
         <v>83</v>
       </c>
       <c r="AX33" s="10" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="AY33" s="14" t="s">
         <v>75</v>
@@ -22786,7 +22810,7 @@
         <v>78</v>
       </c>
       <c r="BJ33" s="9" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="BK33" s="9" t="s">
         <v>75</v>
@@ -22800,79 +22824,79 @@
     </row>
     <row r="34" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="n">
-        <v>305942</v>
+        <v>306157</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>109</v>
+        <v>209</v>
       </c>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
       <c r="F34" s="9" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="G34" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>152</v>
+        <v>125</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="J34" s="9" t="s">
-        <v>78</v>
+        <v>126</v>
       </c>
       <c r="K34" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>42.44</v>
+        <v>11204.49</v>
       </c>
       <c r="M34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O34" s="12" t="n">
-        <v>39.85</v>
+        <v>10131.65</v>
       </c>
       <c r="P34" s="12" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="Q34" s="13" t="n">
-        <v>0.002284</v>
+        <v>0.02398</v>
       </c>
       <c r="R34" s="12" t="n">
-        <v>0.8</v>
+        <v>14.4</v>
       </c>
       <c r="S34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T34" s="14" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="U34" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V34" s="12" t="n">
-        <v>0</v>
+        <v>55.79</v>
       </c>
       <c r="W34" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X34" s="9" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="Y34" s="12" t="n">
-        <v>2.59</v>
+        <v>987.84</v>
       </c>
       <c r="Z34" s="12" t="n">
-        <v>39.85</v>
+        <v>10216.65</v>
       </c>
       <c r="AA34" s="12" t="n">
-        <v>1.59</v>
+        <v>408.68</v>
       </c>
       <c r="AB34" s="12" t="n">
         <v>0</v>
@@ -22941,7 +22965,7 @@
         <v>83</v>
       </c>
       <c r="AX34" s="10" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="AY34" s="14" t="s">
         <v>75</v>
@@ -22977,7 +23001,7 @@
         <v>78</v>
       </c>
       <c r="BJ34" s="9" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="BK34" s="9" t="s">
         <v>75</v>
@@ -22991,79 +23015,79 @@
     </row>
     <row r="35" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="n">
-        <v>305957</v>
+        <v>306173</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>109</v>
+        <v>204</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
       <c r="E35" s="9"/>
       <c r="F35" s="9" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="G35" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>196</v>
+        <v>170</v>
       </c>
       <c r="I35" s="9" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="J35" s="9" t="s">
-        <v>78</v>
+        <v>206</v>
       </c>
       <c r="K35" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>126.7</v>
+        <v>3730.39</v>
       </c>
       <c r="M35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O35" s="12" t="n">
-        <v>118.97</v>
+        <v>3730.39</v>
       </c>
       <c r="P35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q35" s="13" t="n">
-        <v>0.001512</v>
+        <v>0</v>
       </c>
       <c r="R35" s="12" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="S35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T35" s="14" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="U35" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V35" s="12" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="W35" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X35" s="9" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="Y35" s="12" t="n">
-        <v>7.73</v>
+        <v>0</v>
       </c>
       <c r="Z35" s="12" t="n">
-        <v>118.97</v>
+        <v>3730.39</v>
       </c>
       <c r="AA35" s="12" t="n">
-        <v>4.76</v>
+        <v>261.14</v>
       </c>
       <c r="AB35" s="12" t="n">
         <v>0</v>
@@ -23132,7 +23156,7 @@
         <v>83</v>
       </c>
       <c r="AX35" s="10" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="AY35" s="14" t="s">
         <v>75</v>
@@ -23168,7 +23192,7 @@
         <v>78</v>
       </c>
       <c r="BJ35" s="9" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="BK35" s="9" t="s">
         <v>75</v>
@@ -23181,518 +23205,396 @@
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="8" t="n">
-        <v>305966</v>
-      </c>
-      <c r="B36" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="9" t="s">
-        <v>205</v>
-      </c>
-      <c r="G36" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="H36" s="9" t="s">
-        <v>196</v>
-      </c>
-      <c r="I36" s="9" t="s">
-        <v>196</v>
-      </c>
-      <c r="J36" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="K36" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="L36" s="12" t="n">
-        <v>290.09</v>
-      </c>
-      <c r="M36" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="O36" s="12" t="n">
-        <v>272.38</v>
-      </c>
-      <c r="P36" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" s="13" t="n">
-        <v>0.003202</v>
-      </c>
-      <c r="R36" s="12" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="S36" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" s="14" t="s">
-        <v>206</v>
-      </c>
-      <c r="U36" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="V36" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W36" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="X36" s="9" t="s">
-        <v>196</v>
-      </c>
-      <c r="Y36" s="12" t="n">
-        <v>17.71</v>
-      </c>
-      <c r="Z36" s="12" t="n">
-        <v>272.38</v>
-      </c>
-      <c r="AA36" s="12" t="n">
-        <v>10.89</v>
-      </c>
-      <c r="AB36" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC36" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD36" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE36" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF36" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG36" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH36" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI36" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ36" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AK36" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL36" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM36" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AN36" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AO36" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AP36" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ36" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR36" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS36" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT36" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU36" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV36" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW36" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="AX36" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="AY36" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ36" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA36" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB36" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BC36" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD36" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE36" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BF36" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BG36" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="BH36" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BI36" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="BJ36" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="BK36" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BL36" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BM36" s="16" t="s">
-        <v>80</v>
-      </c>
+      <c r="A36" s="4"/>
     </row>
-    <row r="37" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="4"/>
+    <row r="37" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="B37" s="17"/>
+      <c r="C37" s="17"/>
+      <c r="D37" s="17"/>
+      <c r="E37" s="17"/>
+      <c r="F37" s="17"/>
+      <c r="G37" s="17"/>
+      <c r="H37" s="17"/>
+      <c r="I37" s="17"/>
+      <c r="J37" s="17"/>
+      <c r="K37" s="17"/>
+      <c r="L37" s="17"/>
+      <c r="M37" s="17"/>
+      <c r="N37" s="17"/>
+      <c r="O37" s="17"/>
+      <c r="P37" s="17"/>
+      <c r="Q37" s="17"/>
+      <c r="R37" s="17"/>
+      <c r="S37" s="17"/>
+      <c r="T37" s="17"/>
+      <c r="U37" s="17"/>
+      <c r="V37" s="17"/>
     </row>
     <row r="38" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="17" t="s">
-        <v>208</v>
-      </c>
-      <c r="B38" s="17"/>
-      <c r="C38" s="17"/>
-      <c r="D38" s="17"/>
-      <c r="E38" s="17"/>
-      <c r="F38" s="17"/>
-      <c r="G38" s="17"/>
-      <c r="H38" s="17"/>
-      <c r="I38" s="17"/>
-      <c r="J38" s="17"/>
-      <c r="K38" s="17"/>
-      <c r="L38" s="17"/>
-      <c r="M38" s="17"/>
-      <c r="N38" s="17"/>
-      <c r="O38" s="17"/>
-      <c r="P38" s="17"/>
-      <c r="Q38" s="17"/>
-      <c r="R38" s="17"/>
-      <c r="S38" s="17"/>
-      <c r="T38" s="17"/>
-      <c r="U38" s="17"/>
-      <c r="V38" s="17"/>
+      <c r="A38" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="B38" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C38" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D38" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="E38" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F38" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="G38" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H38" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="I38" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="J38" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="K38" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="L38" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="M38" s="18" t="s">
+        <v>220</v>
+      </c>
+      <c r="N38" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="O38" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="P38" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q38" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="R38" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="S38" s="18" t="s">
+        <v>221</v>
+      </c>
+      <c r="T38" s="18" t="s">
+        <v>222</v>
+      </c>
+      <c r="U38" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="V38" s="18" t="s">
+        <v>37</v>
+      </c>
     </row>
-    <row r="39" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="18" t="s">
-        <v>209</v>
-      </c>
-      <c r="B39" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C39" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D39" s="18" t="s">
-        <v>210</v>
-      </c>
-      <c r="E39" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F39" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="G39" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="H39" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="I39" s="18" t="s">
-        <v>211</v>
-      </c>
-      <c r="J39" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="K39" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="L39" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="M39" s="18" t="s">
-        <v>212</v>
-      </c>
-      <c r="N39" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="O39" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="P39" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q39" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="R39" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="S39" s="18" t="s">
-        <v>213</v>
-      </c>
-      <c r="T39" s="18" t="s">
-        <v>214</v>
-      </c>
-      <c r="U39" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="V39" s="18" t="s">
-        <v>37</v>
+    <row r="39" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="19" t="n">
+        <v>31</v>
+      </c>
+      <c r="B39" s="19" t="n">
+        <v>5811.05</v>
+      </c>
+      <c r="C39" s="19" t="n">
+        <v>185</v>
+      </c>
+      <c r="D39" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="19" t="n">
+        <v>5302.25</v>
+      </c>
+      <c r="F39" s="19" t="n">
+        <v>113469.81</v>
+      </c>
+      <c r="G39" s="19" t="n">
+        <v>6359.63</v>
+      </c>
+      <c r="H39" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="19" t="n">
+        <v>180.97</v>
+      </c>
+      <c r="K39" s="19" t="n">
+        <v>118772.06</v>
+      </c>
+      <c r="L39" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" s="20" t="n">
+        <v>1.764395</v>
+      </c>
+      <c r="S39" s="19" t="n">
+        <v>119095.86</v>
+      </c>
+      <c r="T39" s="19" t="n">
+        <v>118772.06</v>
+      </c>
+      <c r="U39" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" s="19" t="n">
+        <v>0</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="19" t="n">
-        <v>32</v>
-      </c>
-      <c r="B40" s="19" t="n">
-        <v>5811.05</v>
-      </c>
-      <c r="C40" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" s="19" t="n">
-        <v>3958.32</v>
-      </c>
-      <c r="F40" s="19" t="n">
-        <v>106421.98</v>
-      </c>
-      <c r="G40" s="19" t="n">
-        <v>6157.08</v>
-      </c>
-      <c r="H40" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="19" t="n">
-        <v>91.25</v>
-      </c>
-      <c r="K40" s="19" t="n">
-        <v>110380.3</v>
-      </c>
-      <c r="L40" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" s="20" t="n">
-        <v>1.711391</v>
-      </c>
-      <c r="S40" s="19" t="n">
-        <v>112233.03</v>
-      </c>
-      <c r="T40" s="19" t="n">
-        <v>110380.3</v>
-      </c>
-      <c r="U40" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" s="19" t="n">
-        <v>0</v>
+    <row r="40" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B40" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C40" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D40" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="E40" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="F40" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="G40" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="H40" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="I40" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="J40" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="K40" s="18" t="s">
+        <v>223</v>
+      </c>
+      <c r="L40" s="18" t="s">
+        <v>224</v>
+      </c>
+      <c r="M40" s="18" t="s">
+        <v>225</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="B41" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C41" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="D41" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E41" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="F41" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="G41" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="H41" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="I41" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="J41" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="K41" s="18" t="s">
-        <v>215</v>
-      </c>
-      <c r="L41" s="18" t="s">
-        <v>216</v>
-      </c>
-      <c r="M41" s="18" t="s">
-        <v>217</v>
+    <row r="41" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="19" t="n">
+        <v>263.49</v>
+      </c>
+      <c r="B41" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="19" t="n">
+        <v>50.44</v>
+      </c>
+      <c r="E41" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" s="19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="19" t="n">
-        <v>219.77</v>
-      </c>
-      <c r="B42" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C42" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D42" s="19" t="n">
-        <v>48.02</v>
-      </c>
-      <c r="E42" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M42" s="19" t="n">
-        <v>0</v>
-      </c>
+      <c r="A42" s="4"/>
     </row>
-    <row r="43" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="4"/>
+    <row r="43" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="21" t="s">
+        <v>226</v>
+      </c>
+      <c r="B43" s="21"/>
+      <c r="C43" s="21"/>
+      <c r="D43" s="21"/>
+      <c r="E43" s="21"/>
+      <c r="F43" s="21"/>
+      <c r="G43" s="21"/>
+      <c r="H43" s="21"/>
+      <c r="I43" s="21"/>
+      <c r="J43" s="21"/>
+      <c r="K43" s="21"/>
+      <c r="L43" s="21"/>
+      <c r="M43" s="21"/>
+      <c r="N43" s="21"/>
+      <c r="O43" s="21"/>
+      <c r="P43" s="21"/>
+      <c r="Q43" s="21"/>
+      <c r="R43" s="21"/>
+      <c r="S43" s="21"/>
+      <c r="T43" s="21"/>
+      <c r="U43" s="21"/>
+      <c r="V43" s="21"/>
+      <c r="W43" s="21"/>
+      <c r="X43" s="21"/>
+      <c r="Y43" s="21"/>
+      <c r="Z43" s="21"/>
+      <c r="AA43" s="21"/>
+      <c r="AB43" s="21"/>
+      <c r="AC43" s="21"/>
+      <c r="AD43" s="21"/>
+      <c r="AE43" s="21"/>
+      <c r="AF43" s="21"/>
+      <c r="AG43" s="21"/>
+      <c r="AH43" s="21"/>
+      <c r="AI43" s="21"/>
+      <c r="AJ43" s="21"/>
+      <c r="AK43" s="21"/>
+      <c r="AL43" s="21"/>
+      <c r="AM43" s="21"/>
+      <c r="AN43" s="21"/>
+      <c r="AO43" s="21"/>
+      <c r="AP43" s="21"/>
+      <c r="AQ43" s="21"/>
+      <c r="AR43" s="21"/>
+      <c r="AS43" s="21"/>
+      <c r="AT43" s="21"/>
+      <c r="AU43" s="21"/>
+      <c r="AV43" s="21"/>
+      <c r="AW43" s="21"/>
+      <c r="AX43" s="21"/>
+      <c r="AY43" s="21"/>
+      <c r="AZ43" s="21"/>
+      <c r="BA43" s="21"/>
+      <c r="BB43" s="21"/>
+      <c r="BC43" s="21"/>
+      <c r="BD43" s="21"/>
+      <c r="BE43" s="21"/>
+      <c r="BF43" s="21"/>
+      <c r="BG43" s="21"/>
+      <c r="BH43" s="21"/>
+      <c r="BI43" s="21"/>
+      <c r="BJ43" s="21"/>
+      <c r="BK43" s="21"/>
+      <c r="BL43" s="21"/>
+      <c r="BM43" s="21"/>
     </row>
-    <row r="44" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="21" t="s">
-        <v>218</v>
-      </c>
-      <c r="B44" s="21"/>
-      <c r="C44" s="21"/>
-      <c r="D44" s="21"/>
-      <c r="E44" s="21"/>
-      <c r="F44" s="21"/>
-      <c r="G44" s="21"/>
-      <c r="H44" s="21"/>
-      <c r="I44" s="21"/>
-      <c r="J44" s="21"/>
-      <c r="K44" s="21"/>
-      <c r="L44" s="21"/>
-      <c r="M44" s="21"/>
-      <c r="N44" s="21"/>
-      <c r="O44" s="21"/>
-      <c r="P44" s="21"/>
-      <c r="Q44" s="21"/>
-      <c r="R44" s="21"/>
-      <c r="S44" s="21"/>
-      <c r="T44" s="21"/>
-      <c r="U44" s="21"/>
-      <c r="V44" s="21"/>
-      <c r="W44" s="21"/>
-      <c r="X44" s="21"/>
-      <c r="Y44" s="21"/>
-      <c r="Z44" s="21"/>
-      <c r="AA44" s="21"/>
-      <c r="AB44" s="21"/>
-      <c r="AC44" s="21"/>
-      <c r="AD44" s="21"/>
-      <c r="AE44" s="21"/>
-      <c r="AF44" s="21"/>
-      <c r="AG44" s="21"/>
-      <c r="AH44" s="21"/>
-      <c r="AI44" s="21"/>
-      <c r="AJ44" s="21"/>
-      <c r="AK44" s="21"/>
-      <c r="AL44" s="21"/>
-      <c r="AM44" s="21"/>
-      <c r="AN44" s="21"/>
-      <c r="AO44" s="21"/>
-      <c r="AP44" s="21"/>
-      <c r="AQ44" s="21"/>
-      <c r="AR44" s="21"/>
-      <c r="AS44" s="21"/>
-      <c r="AT44" s="21"/>
-      <c r="AU44" s="21"/>
-      <c r="AV44" s="21"/>
-      <c r="AW44" s="21"/>
-      <c r="AX44" s="21"/>
-      <c r="AY44" s="21"/>
-      <c r="AZ44" s="21"/>
-      <c r="BA44" s="21"/>
-      <c r="BB44" s="21"/>
-      <c r="BC44" s="21"/>
-      <c r="BD44" s="21"/>
-      <c r="BE44" s="21"/>
-      <c r="BF44" s="21"/>
-      <c r="BG44" s="21"/>
-      <c r="BH44" s="21"/>
-      <c r="BI44" s="21"/>
-      <c r="BJ44" s="21"/>
-      <c r="BK44" s="21"/>
-      <c r="BL44" s="21"/>
-      <c r="BM44" s="21"/>
+    <row r="44" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B44" s="4"/>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="K44" s="4"/>
+      <c r="L44" s="4"/>
+      <c r="M44" s="4"/>
+      <c r="N44" s="4"/>
+      <c r="O44" s="4"/>
+      <c r="P44" s="4"/>
+      <c r="Q44" s="4"/>
+      <c r="R44" s="4"/>
+      <c r="S44" s="4"/>
+      <c r="T44" s="4"/>
+      <c r="U44" s="4"/>
+      <c r="V44" s="4"/>
+      <c r="W44" s="4"/>
+      <c r="X44" s="4"/>
+      <c r="Y44" s="4"/>
+      <c r="Z44" s="4"/>
+      <c r="AA44" s="4"/>
+      <c r="AB44" s="4"/>
+      <c r="AC44" s="4"/>
+      <c r="AD44" s="4"/>
+      <c r="AE44" s="4"/>
+      <c r="AF44" s="4"/>
+      <c r="AG44" s="4"/>
+      <c r="AH44" s="4"/>
+      <c r="AI44" s="4"/>
+      <c r="AJ44" s="4"/>
+      <c r="AK44" s="4"/>
+      <c r="AL44" s="4"/>
+      <c r="AM44" s="4"/>
+      <c r="AN44" s="4"/>
+      <c r="AO44" s="4"/>
+      <c r="AP44" s="4"/>
+      <c r="AQ44" s="4"/>
+      <c r="AR44" s="4"/>
+      <c r="AS44" s="4"/>
+      <c r="AT44" s="4"/>
+      <c r="AU44" s="4"/>
+      <c r="AV44" s="4"/>
+      <c r="AW44" s="4"/>
+      <c r="AX44" s="4"/>
+      <c r="AY44" s="4"/>
+      <c r="AZ44" s="4"/>
+      <c r="BA44" s="4"/>
+      <c r="BB44" s="4"/>
+      <c r="BC44" s="4"/>
+      <c r="BD44" s="4"/>
+      <c r="BE44" s="4"/>
+      <c r="BF44" s="4"/>
+      <c r="BG44" s="4"/>
+      <c r="BH44" s="4"/>
+      <c r="BI44" s="4"/>
+      <c r="BJ44" s="4"/>
+      <c r="BK44" s="4"/>
+      <c r="BL44" s="4"/>
+      <c r="BM44" s="4"/>
     </row>
     <row r="45" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="4" t="s">
-        <v>75</v>
+        <v>227</v>
       </c>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
@@ -23761,7 +23663,7 @@
     </row>
     <row r="46" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="4" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
@@ -23830,7 +23732,7 @@
     </row>
     <row r="47" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
@@ -23899,7 +23801,7 @@
     </row>
     <row r="48" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="4" t="s">
-        <v>221</v>
+        <v>22</v>
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
@@ -23968,7 +23870,7 @@
     </row>
     <row r="49" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="4" t="s">
-        <v>22</v>
+        <v>230</v>
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
@@ -24037,7 +23939,7 @@
     </row>
     <row r="50" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="4" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
@@ -24106,7 +24008,7 @@
     </row>
     <row r="51" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="4" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
@@ -24175,7 +24077,7 @@
     </row>
     <row r="52" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="4" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
@@ -24244,7 +24146,7 @@
     </row>
     <row r="53" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="4" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
@@ -24311,77 +24213,8 @@
       <c r="BL53" s="4"/>
       <c r="BM53" s="4"/>
     </row>
-    <row r="54" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="B54" s="4"/>
-      <c r="C54" s="4"/>
-      <c r="D54" s="4"/>
-      <c r="E54" s="4"/>
-      <c r="F54" s="4"/>
-      <c r="G54" s="4"/>
-      <c r="H54" s="4"/>
-      <c r="I54" s="4"/>
-      <c r="J54" s="4"/>
-      <c r="K54" s="4"/>
-      <c r="L54" s="4"/>
-      <c r="M54" s="4"/>
-      <c r="N54" s="4"/>
-      <c r="O54" s="4"/>
-      <c r="P54" s="4"/>
-      <c r="Q54" s="4"/>
-      <c r="R54" s="4"/>
-      <c r="S54" s="4"/>
-      <c r="T54" s="4"/>
-      <c r="U54" s="4"/>
-      <c r="V54" s="4"/>
-      <c r="W54" s="4"/>
-      <c r="X54" s="4"/>
-      <c r="Y54" s="4"/>
-      <c r="Z54" s="4"/>
-      <c r="AA54" s="4"/>
-      <c r="AB54" s="4"/>
-      <c r="AC54" s="4"/>
-      <c r="AD54" s="4"/>
-      <c r="AE54" s="4"/>
-      <c r="AF54" s="4"/>
-      <c r="AG54" s="4"/>
-      <c r="AH54" s="4"/>
-      <c r="AI54" s="4"/>
-      <c r="AJ54" s="4"/>
-      <c r="AK54" s="4"/>
-      <c r="AL54" s="4"/>
-      <c r="AM54" s="4"/>
-      <c r="AN54" s="4"/>
-      <c r="AO54" s="4"/>
-      <c r="AP54" s="4"/>
-      <c r="AQ54" s="4"/>
-      <c r="AR54" s="4"/>
-      <c r="AS54" s="4"/>
-      <c r="AT54" s="4"/>
-      <c r="AU54" s="4"/>
-      <c r="AV54" s="4"/>
-      <c r="AW54" s="4"/>
-      <c r="AX54" s="4"/>
-      <c r="AY54" s="4"/>
-      <c r="AZ54" s="4"/>
-      <c r="BA54" s="4"/>
-      <c r="BB54" s="4"/>
-      <c r="BC54" s="4"/>
-      <c r="BD54" s="4"/>
-      <c r="BE54" s="4"/>
-      <c r="BF54" s="4"/>
-      <c r="BG54" s="4"/>
-      <c r="BH54" s="4"/>
-      <c r="BI54" s="4"/>
-      <c r="BJ54" s="4"/>
-      <c r="BK54" s="4"/>
-      <c r="BL54" s="4"/>
-      <c r="BM54" s="4"/>
-    </row>
   </sheetData>
-  <mergeCells count="48">
+  <mergeCells count="47">
     <mergeCell ref="A1:BI1"/>
     <mergeCell ref="BJ1:BM1"/>
     <mergeCell ref="A2:BM2"/>
@@ -24417,8 +24250,8 @@
     <mergeCell ref="B33:E33"/>
     <mergeCell ref="B34:E34"/>
     <mergeCell ref="B35:E35"/>
-    <mergeCell ref="B36:E36"/>
-    <mergeCell ref="A38:V38"/>
+    <mergeCell ref="A37:V37"/>
+    <mergeCell ref="A43:BM43"/>
     <mergeCell ref="A44:BM44"/>
     <mergeCell ref="A45:BM45"/>
     <mergeCell ref="A46:BM46"/>
@@ -24429,7 +24262,6 @@
     <mergeCell ref="A51:BM51"/>
     <mergeCell ref="A52:BM52"/>
     <mergeCell ref="A53:BM53"/>
-    <mergeCell ref="A54:BM54"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>

--- a/tratando_tabelas/finitura/entradas_finitura.xlsx
+++ b/tratando_tabelas/finitura/entradas_finitura.xlsx
@@ -20,12 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1352" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1152" uniqueCount="206">
   <si>
     <t xml:space="preserve">Santri ADM 1.1.5.7 R1</t>
   </si>
   <si>
-    <t xml:space="preserve">Emitido em: 29/04/2026 05:30:28</t>
+    <t xml:space="preserve">Emitido em: 30/04/2026 05:30:25</t>
   </si>
   <si>
     <t xml:space="preserve">Relação de entradas - Sintético</t>
@@ -280,10 +280,13 @@
     <t xml:space="preserve">41260417781412000109550010000119691000316152</t>
   </si>
   <si>
-    <t xml:space="preserve">10.343 - INTERLIGHT SISTEMAS DE ILUMINACAO LTDA</t>
+    <t xml:space="preserve">761 - DOCOL FV IND.E COM. DE METAIS SANITARIOS LTDA</t>
   </si>
   <si>
-    <t xml:space="preserve">258.833</t>
+    <t xml:space="preserve">613.557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8</t>
   </si>
   <si>
     <t xml:space="preserve">15/04/2026</t>
@@ -293,21 +296,6 @@
   </si>
   <si>
     <t xml:space="preserve">13/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.577,37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260458329608000144550010002588331002588349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">761 - DOCOL FV IND.E COM. DE METAIS SANITARIOS LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">613.557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8</t>
   </si>
   <si>
     <t xml:space="preserve">2.751,00</t>
@@ -409,18 +397,6 @@
     <t xml:space="preserve">42260475339051000141550080006217511066401195</t>
   </si>
   <si>
-    <t xml:space="preserve">32.664 - STANDARD ILUMINACAO LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.563,51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260456365423000160550010000116311171638522</t>
-  </si>
-  <si>
     <t xml:space="preserve">620.355</t>
   </si>
   <si>
@@ -469,36 +445,6 @@
     <t xml:space="preserve">35260453654471000180550010000536161000320142</t>
   </si>
   <si>
-    <t xml:space="preserve">3.101 - INDUSTRIA E COMERCIO DE MOLDURAS SANTA LUZIA LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">139.721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.520,02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">397.763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.659 - RODO DANNY TRANSPORTES E LOGISTICAS EIRELI ME</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91,25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260475821546000102550040001397211377780494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260411389565000200570050003977631000839511</t>
-  </si>
-  <si>
     <t xml:space="preserve">622.732</t>
   </si>
   <si>
@@ -529,19 +475,10 @@
     <t xml:space="preserve">42260475339051000141550080006223901051401241</t>
   </si>
   <si>
-    <t xml:space="preserve">5.069.526</t>
+    <t xml:space="preserve">5.069.532</t>
   </si>
   <si>
     <t xml:space="preserve">27/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">366,64</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050695261009694039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.069.532</t>
   </si>
   <si>
     <t xml:space="preserve">42,44</t>
@@ -608,30 +545,6 @@
   </si>
   <si>
     <t xml:space="preserve">35260497837181002271550010021461881648923974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.923 - NEW LINE ILUMINACAO LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">224.086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.390,44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">397.948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89,72</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260412077181000133550030002240861005369088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260411389565000200570050003979481000841502</t>
   </si>
   <si>
     <t xml:space="preserve">9.134 - L.MARTINKOSKI &amp; CIA LTDA</t>
@@ -16913,7 +16826,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BM53"/>
+  <dimension ref="A1:BM48"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="18"/>
@@ -17667,7 +17580,7 @@
     </row>
     <row r="7" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="n">
-        <v>305206</v>
+        <v>305238</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>86</v>
@@ -17679,22 +17592,22 @@
         <v>87</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K7" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L7" s="12" t="n">
-        <v>2577.37</v>
+        <v>2751</v>
       </c>
       <c r="M7" s="12" t="n">
         <v>0</v>
@@ -17703,43 +17616,43 @@
         <v>2</v>
       </c>
       <c r="O7" s="12" t="n">
-        <v>2348.4</v>
+        <v>2751</v>
       </c>
       <c r="P7" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q7" s="13" t="n">
-        <v>0</v>
+        <v>0.011956</v>
       </c>
       <c r="R7" s="12" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="S7" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T7" s="14" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="U7" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V7" s="12" t="n">
-        <v>31.19</v>
+        <v>28</v>
       </c>
       <c r="W7" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X7" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Y7" s="12" t="n">
-        <v>228.97</v>
+        <v>0</v>
       </c>
       <c r="Z7" s="12" t="n">
-        <v>2348.4</v>
+        <v>2751</v>
       </c>
       <c r="AA7" s="12" t="n">
-        <v>164.38</v>
+        <v>192.57</v>
       </c>
       <c r="AB7" s="12" t="n">
         <v>0</v>
@@ -17844,7 +17757,7 @@
         <v>78</v>
       </c>
       <c r="BJ7" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="BK7" s="9" t="s">
         <v>75</v>
@@ -17858,79 +17771,79 @@
     </row>
     <row r="8" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="n">
-        <v>305238</v>
+        <v>305457</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
       <c r="F8" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K8" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L8" s="12" t="n">
-        <v>2751</v>
+        <v>4770.41</v>
       </c>
       <c r="M8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N8" s="12" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="O8" s="12" t="n">
-        <v>2751</v>
+        <v>4588.46</v>
       </c>
       <c r="P8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q8" s="13" t="n">
-        <v>0.011956</v>
+        <v>0.231499</v>
       </c>
       <c r="R8" s="12" t="n">
-        <v>5.06</v>
+        <v>35.08</v>
       </c>
       <c r="S8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T8" s="14" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="U8" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V8" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W8" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X8" s="9" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="Y8" s="12" t="n">
-        <v>0</v>
+        <v>181.95</v>
       </c>
       <c r="Z8" s="12" t="n">
-        <v>2751</v>
+        <v>4588.46</v>
       </c>
       <c r="AA8" s="12" t="n">
-        <v>192.57</v>
+        <v>183.54</v>
       </c>
       <c r="AB8" s="12" t="n">
         <v>0</v>
@@ -17999,7 +17912,7 @@
         <v>83</v>
       </c>
       <c r="AX8" s="10" t="s">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AY8" s="14" t="s">
         <v>75</v>
@@ -18035,7 +17948,7 @@
         <v>78</v>
       </c>
       <c r="BJ8" s="9" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="BK8" s="9" t="s">
         <v>75</v>
@@ -18049,25 +17962,25 @@
     </row>
     <row r="9" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="n">
-        <v>305457</v>
+        <v>305470</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G9" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="J9" s="9" t="s">
         <v>78</v>
@@ -18076,25 +17989,25 @@
         <v>70</v>
       </c>
       <c r="L9" s="12" t="n">
-        <v>4770.41</v>
+        <v>314.65</v>
       </c>
       <c r="M9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N9" s="12" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="O9" s="12" t="n">
-        <v>4588.46</v>
+        <v>295.45</v>
       </c>
       <c r="P9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q9" s="13" t="n">
-        <v>0.231499</v>
+        <v>0.016472</v>
       </c>
       <c r="R9" s="12" t="n">
-        <v>35.08</v>
+        <v>1.6</v>
       </c>
       <c r="S9" s="12" t="n">
         <v>0</v>
@@ -18112,16 +18025,16 @@
         <v>73</v>
       </c>
       <c r="X9" s="9" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="Y9" s="12" t="n">
-        <v>181.95</v>
+        <v>19.2</v>
       </c>
       <c r="Z9" s="12" t="n">
-        <v>4588.46</v>
+        <v>295.45</v>
       </c>
       <c r="AA9" s="12" t="n">
-        <v>183.54</v>
+        <v>11.81</v>
       </c>
       <c r="AB9" s="12" t="n">
         <v>0</v>
@@ -18190,7 +18103,7 @@
         <v>83</v>
       </c>
       <c r="AX9" s="10" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="AY9" s="14" t="s">
         <v>75</v>
@@ -18226,7 +18139,7 @@
         <v>78</v>
       </c>
       <c r="BJ9" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="BK9" s="9" t="s">
         <v>75</v>
@@ -18240,25 +18153,25 @@
     </row>
     <row r="10" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="n">
-        <v>305470</v>
+        <v>305480</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
       <c r="F10" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G10" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="J10" s="9" t="s">
         <v>78</v>
@@ -18267,31 +18180,31 @@
         <v>70</v>
       </c>
       <c r="L10" s="12" t="n">
-        <v>314.65</v>
+        <v>2373.3</v>
       </c>
       <c r="M10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N10" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O10" s="12" t="n">
-        <v>295.45</v>
+        <v>2228.46</v>
       </c>
       <c r="P10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q10" s="13" t="n">
-        <v>0.016472</v>
+        <v>0.017186</v>
       </c>
       <c r="R10" s="12" t="n">
-        <v>1.6</v>
+        <v>12.33</v>
       </c>
       <c r="S10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T10" s="14" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="U10" s="15" t="s">
         <v>72</v>
@@ -18303,16 +18216,16 @@
         <v>73</v>
       </c>
       <c r="X10" s="9" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="Y10" s="12" t="n">
-        <v>19.2</v>
+        <v>144.84</v>
       </c>
       <c r="Z10" s="12" t="n">
-        <v>295.45</v>
+        <v>2228.46</v>
       </c>
       <c r="AA10" s="12" t="n">
-        <v>11.81</v>
+        <v>89.14</v>
       </c>
       <c r="AB10" s="12" t="n">
         <v>0</v>
@@ -18381,7 +18294,7 @@
         <v>83</v>
       </c>
       <c r="AX10" s="10" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="AY10" s="14" t="s">
         <v>75</v>
@@ -18417,7 +18330,7 @@
         <v>78</v>
       </c>
       <c r="BJ10" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="BK10" s="9" t="s">
         <v>75</v>
@@ -18431,79 +18344,79 @@
     </row>
     <row r="11" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="n">
-        <v>305480</v>
+        <v>305556</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
       <c r="F11" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="I11" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="G11" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>101</v>
-      </c>
       <c r="J11" s="9" t="s">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="K11" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>2373.3</v>
+        <v>5879.02</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O11" s="12" t="n">
-        <v>2228.46</v>
+        <v>5879.02</v>
       </c>
       <c r="P11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q11" s="13" t="n">
-        <v>0.017186</v>
+        <v>0.467698</v>
       </c>
       <c r="R11" s="12" t="n">
-        <v>12.33</v>
+        <v>31.5</v>
       </c>
       <c r="S11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T11" s="14" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="U11" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V11" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W11" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X11" s="9" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="Y11" s="12" t="n">
-        <v>144.84</v>
+        <v>0</v>
       </c>
       <c r="Z11" s="12" t="n">
-        <v>2228.46</v>
+        <v>5879.02</v>
       </c>
       <c r="AA11" s="12" t="n">
-        <v>89.14</v>
+        <v>411.53</v>
       </c>
       <c r="AB11" s="12" t="n">
         <v>0</v>
@@ -18572,7 +18485,7 @@
         <v>83</v>
       </c>
       <c r="AX11" s="10" t="s">
-        <v>103</v>
+        <v>77</v>
       </c>
       <c r="AY11" s="14" t="s">
         <v>75</v>
@@ -18608,7 +18521,7 @@
         <v>78</v>
       </c>
       <c r="BJ11" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="BK11" s="9" t="s">
         <v>75</v>
@@ -18622,34 +18535,34 @@
     </row>
     <row r="12" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="n">
-        <v>305556</v>
+        <v>305560</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
       <c r="F12" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K12" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>5879.02</v>
+        <v>3121.47</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>0</v>
@@ -18658,22 +18571,22 @@
         <v>1</v>
       </c>
       <c r="O12" s="12" t="n">
-        <v>5879.02</v>
+        <v>3121.47</v>
       </c>
       <c r="P12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" s="13" t="n">
-        <v>0.467698</v>
+        <v>0.031059</v>
       </c>
       <c r="R12" s="12" t="n">
-        <v>31.5</v>
+        <v>5.54</v>
       </c>
       <c r="S12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T12" s="14" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="U12" s="15" t="s">
         <v>72</v>
@@ -18685,16 +18598,16 @@
         <v>73</v>
       </c>
       <c r="X12" s="9" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="Y12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z12" s="12" t="n">
-        <v>5879.02</v>
+        <v>3121.47</v>
       </c>
       <c r="AA12" s="12" t="n">
-        <v>411.53</v>
+        <v>218.5</v>
       </c>
       <c r="AB12" s="12" t="n">
         <v>0</v>
@@ -18799,7 +18712,7 @@
         <v>78</v>
       </c>
       <c r="BJ12" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="BK12" s="9" t="s">
         <v>75</v>
@@ -18813,34 +18726,34 @@
     </row>
     <row r="13" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="n">
-        <v>305560</v>
+        <v>305561</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
       <c r="F13" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="K13" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>3121.47</v>
+        <v>5331.26</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>0</v>
@@ -18849,22 +18762,22 @@
         <v>1</v>
       </c>
       <c r="O13" s="12" t="n">
-        <v>3121.47</v>
+        <v>5005.88</v>
       </c>
       <c r="P13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q13" s="13" t="n">
-        <v>0.031059</v>
+        <v>0.055816</v>
       </c>
       <c r="R13" s="12" t="n">
-        <v>5.54</v>
+        <v>7.12</v>
       </c>
       <c r="S13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T13" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="U13" s="15" t="s">
         <v>72</v>
@@ -18876,16 +18789,16 @@
         <v>73</v>
       </c>
       <c r="X13" s="9" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="Y13" s="12" t="n">
-        <v>0</v>
+        <v>325.38</v>
       </c>
       <c r="Z13" s="12" t="n">
-        <v>3121.47</v>
+        <v>5005.88</v>
       </c>
       <c r="AA13" s="12" t="n">
-        <v>218.5</v>
+        <v>350.41</v>
       </c>
       <c r="AB13" s="12" t="n">
         <v>0</v>
@@ -18990,7 +18903,7 @@
         <v>78</v>
       </c>
       <c r="BJ13" s="9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="BK13" s="9" t="s">
         <v>75</v>
@@ -19004,34 +18917,34 @@
     </row>
     <row r="14" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="n">
-        <v>305561</v>
+        <v>305681</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
       <c r="F14" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="H14" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="G14" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>117</v>
-      </c>
       <c r="I14" s="9" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="K14" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>5331.26</v>
+        <v>1945.98</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>0</v>
@@ -19040,22 +18953,22 @@
         <v>1</v>
       </c>
       <c r="O14" s="12" t="n">
-        <v>5005.88</v>
+        <v>1945.98</v>
       </c>
       <c r="P14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q14" s="13" t="n">
-        <v>0.055816</v>
+        <v>0.004946</v>
       </c>
       <c r="R14" s="12" t="n">
-        <v>7.12</v>
+        <v>1.15</v>
       </c>
       <c r="S14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T14" s="14" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="U14" s="15" t="s">
         <v>72</v>
@@ -19067,16 +18980,16 @@
         <v>73</v>
       </c>
       <c r="X14" s="9" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="Y14" s="12" t="n">
-        <v>325.38</v>
+        <v>0</v>
       </c>
       <c r="Z14" s="12" t="n">
-        <v>5005.88</v>
+        <v>1945.98</v>
       </c>
       <c r="AA14" s="12" t="n">
-        <v>350.41</v>
+        <v>136.22</v>
       </c>
       <c r="AB14" s="12" t="n">
         <v>0</v>
@@ -19181,7 +19094,7 @@
         <v>78</v>
       </c>
       <c r="BJ14" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="BK14" s="9" t="s">
         <v>75</v>
@@ -19195,25 +19108,25 @@
     </row>
     <row r="15" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="n">
-        <v>305681</v>
+        <v>305724</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
       <c r="F15" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>125</v>
+        <v>108</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="J15" s="9" t="s">
         <v>126</v>
@@ -19222,7 +19135,7 @@
         <v>70</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>1945.98</v>
+        <v>1674.18</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>0</v>
@@ -19231,16 +19144,16 @@
         <v>1</v>
       </c>
       <c r="O15" s="12" t="n">
-        <v>1945.98</v>
+        <v>1674.18</v>
       </c>
       <c r="P15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q15" s="13" t="n">
-        <v>0.004946</v>
+        <v>0.003916</v>
       </c>
       <c r="R15" s="12" t="n">
-        <v>1.15</v>
+        <v>0.97</v>
       </c>
       <c r="S15" s="12" t="n">
         <v>0</v>
@@ -19258,16 +19171,16 @@
         <v>73</v>
       </c>
       <c r="X15" s="9" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="Y15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z15" s="12" t="n">
-        <v>1945.98</v>
+        <v>1674.18</v>
       </c>
       <c r="AA15" s="12" t="n">
-        <v>136.22</v>
+        <v>117.19</v>
       </c>
       <c r="AB15" s="12" t="n">
         <v>0</v>
@@ -19386,7 +19299,7 @@
     </row>
     <row r="16" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="n">
-        <v>305691</v>
+        <v>305725</v>
       </c>
       <c r="B16" s="9" t="s">
         <v>129</v>
@@ -19401,10 +19314,10 @@
         <v>66</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>125</v>
+        <v>108</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="J16" s="9" t="s">
         <v>126</v>
@@ -19413,7 +19326,7 @@
         <v>70</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>3563.51</v>
+        <v>10012.8</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>0</v>
@@ -19422,16 +19335,16 @@
         <v>2</v>
       </c>
       <c r="O16" s="12" t="n">
-        <v>3098.7</v>
+        <v>10012.8</v>
       </c>
       <c r="P16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q16" s="13" t="n">
-        <v>0</v>
+        <v>0.750038</v>
       </c>
       <c r="R16" s="12" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="S16" s="12" t="n">
         <v>0</v>
@@ -19443,22 +19356,22 @@
         <v>72</v>
       </c>
       <c r="V16" s="12" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="W16" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X16" s="9" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="Y16" s="12" t="n">
-        <v>464.81</v>
+        <v>0</v>
       </c>
       <c r="Z16" s="12" t="n">
-        <v>3098.7</v>
+        <v>10012.8</v>
       </c>
       <c r="AA16" s="12" t="n">
-        <v>216.91</v>
+        <v>400.51</v>
       </c>
       <c r="AB16" s="12" t="n">
         <v>0</v>
@@ -19577,10 +19490,10 @@
     </row>
     <row r="17" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="n">
-        <v>305724</v>
+        <v>305731</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
@@ -19589,46 +19502,46 @@
         <v>133</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="K17" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>1674.18</v>
+        <v>6247.73</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O17" s="12" t="n">
-        <v>1674.18</v>
+        <v>6247.73</v>
       </c>
       <c r="P17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q17" s="13" t="n">
-        <v>0.003916</v>
+        <v>0.030808</v>
       </c>
       <c r="R17" s="12" t="n">
-        <v>0.97</v>
+        <v>6.05</v>
       </c>
       <c r="S17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T17" s="14" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="U17" s="15" t="s">
         <v>72</v>
@@ -19640,16 +19553,16 @@
         <v>73</v>
       </c>
       <c r="X17" s="9" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="Y17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z17" s="12" t="n">
-        <v>1674.18</v>
+        <v>6247.73</v>
       </c>
       <c r="AA17" s="12" t="n">
-        <v>117.19</v>
+        <v>437.34</v>
       </c>
       <c r="AB17" s="12" t="n">
         <v>0</v>
@@ -19754,7 +19667,7 @@
         <v>78</v>
       </c>
       <c r="BJ17" s="9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="BK17" s="9" t="s">
         <v>75</v>
@@ -19768,34 +19681,34 @@
     </row>
     <row r="18" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="n">
-        <v>305725</v>
+        <v>305778</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
       <c r="F18" s="9" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G18" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="K18" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>10012.8</v>
+        <v>834.78</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>0</v>
@@ -19804,16 +19717,16 @@
         <v>2</v>
       </c>
       <c r="O18" s="12" t="n">
-        <v>10012.8</v>
+        <v>730</v>
       </c>
       <c r="P18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q18" s="13" t="n">
-        <v>0.750038</v>
+        <v>0</v>
       </c>
       <c r="R18" s="12" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="S18" s="12" t="n">
         <v>0</v>
@@ -19825,22 +19738,22 @@
         <v>72</v>
       </c>
       <c r="V18" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="W18" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X18" s="9" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="Y18" s="12" t="n">
-        <v>0</v>
+        <v>104.78</v>
       </c>
       <c r="Z18" s="12" t="n">
-        <v>10012.8</v>
+        <v>730</v>
       </c>
       <c r="AA18" s="12" t="n">
-        <v>400.51</v>
+        <v>51.1</v>
       </c>
       <c r="AB18" s="12" t="n">
         <v>0</v>
@@ -19906,7 +19819,7 @@
         <v>74</v>
       </c>
       <c r="AW18" s="14" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AX18" s="10" t="s">
         <v>77</v>
@@ -19959,10 +19872,10 @@
     </row>
     <row r="19" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="n">
-        <v>305731</v>
+        <v>305821</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
@@ -19971,46 +19884,46 @@
         <v>141</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>112</v>
+        <v>138</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="K19" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>6247.73</v>
+        <v>4462.34</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O19" s="12" t="n">
-        <v>6247.73</v>
+        <v>4462.34</v>
       </c>
       <c r="P19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q19" s="13" t="n">
-        <v>0.030808</v>
+        <v>0.010272</v>
       </c>
       <c r="R19" s="12" t="n">
-        <v>6.05</v>
+        <v>3.7</v>
       </c>
       <c r="S19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T19" s="14" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="U19" s="15" t="s">
         <v>72</v>
@@ -20022,16 +19935,16 @@
         <v>73</v>
       </c>
       <c r="X19" s="9" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="Y19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z19" s="12" t="n">
-        <v>6247.73</v>
+        <v>4462.34</v>
       </c>
       <c r="AA19" s="12" t="n">
-        <v>437.34</v>
+        <v>312.36</v>
       </c>
       <c r="AB19" s="12" t="n">
         <v>0</v>
@@ -20136,7 +20049,7 @@
         <v>78</v>
       </c>
       <c r="BJ19" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="BK19" s="9" t="s">
         <v>75</v>
@@ -20150,10 +20063,10 @@
     </row>
     <row r="20" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="n">
-        <v>305778</v>
+        <v>305822</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>144</v>
+        <v>86</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
@@ -20162,67 +20075,67 @@
         <v>145</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="K20" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>834.78</v>
+        <v>1464.23</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O20" s="12" t="n">
-        <v>730</v>
+        <v>1464.23</v>
       </c>
       <c r="P20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q20" s="13" t="n">
-        <v>0</v>
+        <v>0.002473</v>
       </c>
       <c r="R20" s="12" t="n">
-        <v>0</v>
+        <v>0.77</v>
       </c>
       <c r="S20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T20" s="14" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="U20" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V20" s="12" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="W20" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X20" s="9" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="Y20" s="12" t="n">
-        <v>104.78</v>
+        <v>0</v>
       </c>
       <c r="Z20" s="12" t="n">
-        <v>730</v>
+        <v>1464.23</v>
       </c>
       <c r="AA20" s="12" t="n">
-        <v>51.1</v>
+        <v>102.5</v>
       </c>
       <c r="AB20" s="12" t="n">
         <v>0</v>
@@ -20288,7 +20201,7 @@
         <v>74</v>
       </c>
       <c r="AW20" s="14" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AX20" s="10" t="s">
         <v>77</v>
@@ -20327,7 +20240,7 @@
         <v>78</v>
       </c>
       <c r="BJ20" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="BK20" s="9" t="s">
         <v>75</v>
@@ -20341,79 +20254,79 @@
     </row>
     <row r="21" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="n">
-        <v>305787</v>
+        <v>305829</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>149</v>
+        <v>86</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
       <c r="F21" s="9" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>151</v>
+        <v>88</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>89</v>
+        <v>121</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>152</v>
+        <v>122</v>
       </c>
       <c r="K21" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>4520.02</v>
+        <v>3019.02</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O21" s="12" t="n">
-        <v>4520.02</v>
+        <v>3019.02</v>
       </c>
       <c r="P21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q21" s="13" t="n">
-        <v>0.004608</v>
+        <v>0.004946</v>
       </c>
       <c r="R21" s="12" t="n">
-        <v>36.69</v>
+        <v>1.53</v>
       </c>
       <c r="S21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T21" s="14" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="U21" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V21" s="12" t="n">
-        <v>55.99</v>
+        <v>28</v>
       </c>
       <c r="W21" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X21" s="9" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="Y21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z21" s="12" t="n">
-        <v>4520.02</v>
+        <v>3019.02</v>
       </c>
       <c r="AA21" s="12" t="n">
-        <v>316.39</v>
+        <v>211.33</v>
       </c>
       <c r="AB21" s="12" t="n">
         <v>0</v>
@@ -20422,7 +20335,7 @@
         <v>0</v>
       </c>
       <c r="AD21" s="12" t="n">
-        <v>91.25</v>
+        <v>0</v>
       </c>
       <c r="AE21" s="12" t="n">
         <v>0</v>
@@ -20503,25 +20416,25 @@
         <v>75</v>
       </c>
       <c r="BE21" s="14" t="s">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="BF21" s="9" t="s">
-        <v>155</v>
+        <v>75</v>
       </c>
       <c r="BG21" s="9" t="s">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="BH21" s="14" t="s">
-        <v>156</v>
+        <v>75</v>
       </c>
       <c r="BI21" s="9" t="s">
-        <v>125</v>
+        <v>78</v>
       </c>
       <c r="BJ21" s="9" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="BK21" s="9" t="s">
-        <v>158</v>
+        <v>75</v>
       </c>
       <c r="BL21" s="9" t="s">
         <v>75</v>
@@ -20532,34 +20445,34 @@
     </row>
     <row r="22" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="n">
-        <v>305821</v>
+        <v>305942</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
       <c r="F22" s="9" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>146</v>
+        <v>121</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>160</v>
+        <v>78</v>
       </c>
       <c r="K22" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>4462.34</v>
+        <v>42.44</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>0</v>
@@ -20568,43 +20481,43 @@
         <v>1</v>
       </c>
       <c r="O22" s="12" t="n">
-        <v>4462.34</v>
+        <v>39.85</v>
       </c>
       <c r="P22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q22" s="13" t="n">
-        <v>0.010272</v>
+        <v>0.002284</v>
       </c>
       <c r="R22" s="12" t="n">
-        <v>3.7</v>
+        <v>0.8</v>
       </c>
       <c r="S22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T22" s="14" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="U22" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V22" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W22" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X22" s="9" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="Y22" s="12" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Z22" s="12" t="n">
-        <v>4462.34</v>
+        <v>39.85</v>
       </c>
       <c r="AA22" s="12" t="n">
-        <v>312.36</v>
+        <v>1.59</v>
       </c>
       <c r="AB22" s="12" t="n">
         <v>0</v>
@@ -20673,7 +20586,7 @@
         <v>83</v>
       </c>
       <c r="AX22" s="10" t="s">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AY22" s="14" t="s">
         <v>75</v>
@@ -20709,7 +20622,7 @@
         <v>78</v>
       </c>
       <c r="BJ22" s="9" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="BK22" s="9" t="s">
         <v>75</v>
@@ -20723,34 +20636,34 @@
     </row>
     <row r="23" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="n">
-        <v>305822</v>
+        <v>305957</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="9" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>160</v>
+        <v>78</v>
       </c>
       <c r="K23" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>1464.23</v>
+        <v>126.7</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>0</v>
@@ -20759,43 +20672,43 @@
         <v>1</v>
       </c>
       <c r="O23" s="12" t="n">
-        <v>1464.23</v>
+        <v>118.97</v>
       </c>
       <c r="P23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q23" s="13" t="n">
-        <v>0.002473</v>
+        <v>0.001512</v>
       </c>
       <c r="R23" s="12" t="n">
-        <v>0.77</v>
+        <v>1.58</v>
       </c>
       <c r="S23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T23" s="14" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="U23" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V23" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W23" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X23" s="9" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="Y23" s="12" t="n">
-        <v>0</v>
+        <v>7.73</v>
       </c>
       <c r="Z23" s="12" t="n">
-        <v>1464.23</v>
+        <v>118.97</v>
       </c>
       <c r="AA23" s="12" t="n">
-        <v>102.5</v>
+        <v>4.76</v>
       </c>
       <c r="AB23" s="12" t="n">
         <v>0</v>
@@ -20864,7 +20777,7 @@
         <v>83</v>
       </c>
       <c r="AX23" s="10" t="s">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AY23" s="14" t="s">
         <v>75</v>
@@ -20900,7 +20813,7 @@
         <v>78</v>
       </c>
       <c r="BJ23" s="9" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="BK23" s="9" t="s">
         <v>75</v>
@@ -20914,79 +20827,79 @@
     </row>
     <row r="24" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="n">
-        <v>305829</v>
+        <v>305966</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
       <c r="F24" s="9" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>125</v>
+        <v>152</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>126</v>
+        <v>78</v>
       </c>
       <c r="K24" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>3019.02</v>
+        <v>290.09</v>
       </c>
       <c r="M24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O24" s="12" t="n">
-        <v>3019.02</v>
+        <v>272.38</v>
       </c>
       <c r="P24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q24" s="13" t="n">
-        <v>0.004946</v>
+        <v>0.003202</v>
       </c>
       <c r="R24" s="12" t="n">
-        <v>1.53</v>
+        <v>1.93</v>
       </c>
       <c r="S24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T24" s="14" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="U24" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V24" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W24" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X24" s="9" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="Y24" s="12" t="n">
-        <v>0</v>
+        <v>17.71</v>
       </c>
       <c r="Z24" s="12" t="n">
-        <v>3019.02</v>
+        <v>272.38</v>
       </c>
       <c r="AA24" s="12" t="n">
-        <v>211.33</v>
+        <v>10.89</v>
       </c>
       <c r="AB24" s="12" t="n">
         <v>0</v>
@@ -21055,7 +20968,7 @@
         <v>83</v>
       </c>
       <c r="AX24" s="10" t="s">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AY24" s="14" t="s">
         <v>75</v>
@@ -21091,7 +21004,7 @@
         <v>78</v>
       </c>
       <c r="BJ24" s="9" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="BK24" s="9" t="s">
         <v>75</v>
@@ -21105,34 +21018,34 @@
     </row>
     <row r="25" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="n">
-        <v>305933</v>
+        <v>305994</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>78</v>
+        <v>122</v>
       </c>
       <c r="K25" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>366.64</v>
+        <v>2583.52</v>
       </c>
       <c r="M25" s="12" t="n">
         <v>0</v>
@@ -21141,43 +21054,43 @@
         <v>1</v>
       </c>
       <c r="O25" s="12" t="n">
-        <v>344.26</v>
+        <v>2583.52</v>
       </c>
       <c r="P25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q25" s="13" t="n">
-        <v>0.007989</v>
+        <v>0.007527</v>
       </c>
       <c r="R25" s="12" t="n">
-        <v>1.76</v>
+        <v>1.95</v>
       </c>
       <c r="S25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T25" s="14" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="U25" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V25" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W25" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X25" s="9" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="Y25" s="12" t="n">
-        <v>22.38</v>
+        <v>0</v>
       </c>
       <c r="Z25" s="12" t="n">
-        <v>344.26</v>
+        <v>2583.52</v>
       </c>
       <c r="AA25" s="12" t="n">
-        <v>13.77</v>
+        <v>180.85</v>
       </c>
       <c r="AB25" s="12" t="n">
         <v>0</v>
@@ -21246,7 +21159,7 @@
         <v>83</v>
       </c>
       <c r="AX25" s="10" t="s">
-        <v>103</v>
+        <v>77</v>
       </c>
       <c r="AY25" s="14" t="s">
         <v>75</v>
@@ -21282,7 +21195,7 @@
         <v>78</v>
       </c>
       <c r="BJ25" s="9" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="BK25" s="9" t="s">
         <v>75</v>
@@ -21296,34 +21209,34 @@
     </row>
     <row r="26" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="n">
-        <v>305942</v>
+        <v>306001</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>125</v>
+        <v>166</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>78</v>
+        <v>167</v>
       </c>
       <c r="K26" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>42.44</v>
+        <v>1181.41</v>
       </c>
       <c r="M26" s="12" t="n">
         <v>0</v>
@@ -21332,43 +21245,43 @@
         <v>1</v>
       </c>
       <c r="O26" s="12" t="n">
-        <v>39.85</v>
+        <v>1181.41</v>
       </c>
       <c r="P26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q26" s="13" t="n">
-        <v>0.002284</v>
+        <v>0.000412</v>
       </c>
       <c r="R26" s="12" t="n">
-        <v>0.8</v>
+        <v>0.71</v>
       </c>
       <c r="S26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T26" s="14" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="U26" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V26" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W26" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X26" s="9" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="Y26" s="12" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Z26" s="12" t="n">
-        <v>39.85</v>
+        <v>1181.41</v>
       </c>
       <c r="AA26" s="12" t="n">
-        <v>1.59</v>
+        <v>82.7</v>
       </c>
       <c r="AB26" s="12" t="n">
         <v>0</v>
@@ -21437,7 +21350,7 @@
         <v>83</v>
       </c>
       <c r="AX26" s="10" t="s">
-        <v>103</v>
+        <v>77</v>
       </c>
       <c r="AY26" s="14" t="s">
         <v>75</v>
@@ -21473,7 +21386,7 @@
         <v>78</v>
       </c>
       <c r="BJ26" s="9" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="BK26" s="9" t="s">
         <v>75</v>
@@ -21487,34 +21400,34 @@
     </row>
     <row r="27" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="n">
-        <v>305957</v>
+        <v>306005</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>98</v>
+        <v>170</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="G27" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>170</v>
+        <v>138</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="J27" s="9" t="s">
-        <v>78</v>
+        <v>172</v>
       </c>
       <c r="K27" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>126.7</v>
+        <v>861.88</v>
       </c>
       <c r="M27" s="12" t="n">
         <v>0</v>
@@ -21523,43 +21436,43 @@
         <v>1</v>
       </c>
       <c r="O27" s="12" t="n">
-        <v>118.97</v>
+        <v>861.88</v>
       </c>
       <c r="P27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q27" s="13" t="n">
-        <v>0.001512</v>
+        <v>0.073796</v>
       </c>
       <c r="R27" s="12" t="n">
-        <v>1.58</v>
+        <v>43.13</v>
       </c>
       <c r="S27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T27" s="14" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="U27" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V27" s="12" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="W27" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X27" s="9" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="Y27" s="12" t="n">
-        <v>7.73</v>
+        <v>0</v>
       </c>
       <c r="Z27" s="12" t="n">
-        <v>118.97</v>
+        <v>861.88</v>
       </c>
       <c r="AA27" s="12" t="n">
-        <v>4.76</v>
+        <v>60.33</v>
       </c>
       <c r="AB27" s="12" t="n">
         <v>0</v>
@@ -21628,7 +21541,7 @@
         <v>83</v>
       </c>
       <c r="AX27" s="10" t="s">
-        <v>103</v>
+        <v>77</v>
       </c>
       <c r="AY27" s="14" t="s">
         <v>75</v>
@@ -21664,7 +21577,7 @@
         <v>78</v>
       </c>
       <c r="BJ27" s="9" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="BK27" s="9" t="s">
         <v>75</v>
@@ -21678,34 +21591,34 @@
     </row>
     <row r="28" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="n">
-        <v>305966</v>
+        <v>306150</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>98</v>
+        <v>175</v>
       </c>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G28" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>78</v>
+        <v>177</v>
       </c>
       <c r="K28" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>290.09</v>
+        <v>2070.21</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>0</v>
@@ -21714,43 +21627,43 @@
         <v>2</v>
       </c>
       <c r="O28" s="12" t="n">
-        <v>272.38</v>
+        <v>1970.21</v>
       </c>
       <c r="P28" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q28" s="13" t="n">
-        <v>0.003202</v>
+        <v>0</v>
       </c>
       <c r="R28" s="12" t="n">
-        <v>1.93</v>
+        <v>4.15</v>
       </c>
       <c r="S28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T28" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="U28" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V28" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W28" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X28" s="9" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="Y28" s="12" t="n">
-        <v>17.71</v>
+        <v>0</v>
       </c>
       <c r="Z28" s="12" t="n">
-        <v>272.38</v>
+        <v>2070.21</v>
       </c>
       <c r="AA28" s="12" t="n">
-        <v>10.89</v>
+        <v>144.92</v>
       </c>
       <c r="AB28" s="12" t="n">
         <v>0</v>
@@ -21819,7 +21732,7 @@
         <v>83</v>
       </c>
       <c r="AX28" s="10" t="s">
-        <v>103</v>
+        <v>77</v>
       </c>
       <c r="AY28" s="14" t="s">
         <v>75</v>
@@ -21855,7 +21768,7 @@
         <v>78</v>
       </c>
       <c r="BJ28" s="9" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="BK28" s="9" t="s">
         <v>75</v>
@@ -21869,79 +21782,79 @@
     </row>
     <row r="29" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="n">
-        <v>305994</v>
+        <v>306157</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>93</v>
+        <v>180</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
       <c r="F29" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>183</v>
+        <v>162</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="K29" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>2583.52</v>
+        <v>11204.49</v>
       </c>
       <c r="M29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O29" s="12" t="n">
-        <v>2583.52</v>
+        <v>10131.65</v>
       </c>
       <c r="P29" s="12" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="Q29" s="13" t="n">
-        <v>0.007527</v>
+        <v>0.02398</v>
       </c>
       <c r="R29" s="12" t="n">
-        <v>1.95</v>
+        <v>14.4</v>
       </c>
       <c r="S29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T29" s="14" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="U29" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V29" s="12" t="n">
-        <v>28</v>
+        <v>55.79</v>
       </c>
       <c r="W29" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X29" s="9" t="s">
-        <v>183</v>
+        <v>162</v>
       </c>
       <c r="Y29" s="12" t="n">
-        <v>0</v>
+        <v>987.84</v>
       </c>
       <c r="Z29" s="12" t="n">
-        <v>2583.52</v>
+        <v>10216.65</v>
       </c>
       <c r="AA29" s="12" t="n">
-        <v>180.85</v>
+        <v>408.68</v>
       </c>
       <c r="AB29" s="12" t="n">
         <v>0</v>
@@ -22046,7 +21959,7 @@
         <v>78</v>
       </c>
       <c r="BJ29" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="BK29" s="9" t="s">
         <v>75</v>
@@ -22060,79 +21973,79 @@
     </row>
     <row r="30" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="n">
-        <v>306001</v>
+        <v>306173</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>93</v>
+        <v>175</v>
       </c>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
       <c r="F30" s="9" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G30" s="10" t="s">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>187</v>
+        <v>152</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>183</v>
+        <v>162</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="K30" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>1181.41</v>
+        <v>3730.39</v>
       </c>
       <c r="M30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O30" s="12" t="n">
-        <v>1181.41</v>
+        <v>3730.39</v>
       </c>
       <c r="P30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q30" s="13" t="n">
-        <v>0.000412</v>
+        <v>0</v>
       </c>
       <c r="R30" s="12" t="n">
-        <v>0.71</v>
+        <v>0</v>
       </c>
       <c r="S30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T30" s="14" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="U30" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V30" s="12" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="W30" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X30" s="9" t="s">
-        <v>183</v>
+        <v>162</v>
       </c>
       <c r="Y30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z30" s="12" t="n">
-        <v>1181.41</v>
+        <v>3730.39</v>
       </c>
       <c r="AA30" s="12" t="n">
-        <v>82.7</v>
+        <v>261.14</v>
       </c>
       <c r="AB30" s="12" t="n">
         <v>0</v>
@@ -22237,7 +22150,7 @@
         <v>78</v>
       </c>
       <c r="BJ30" s="9" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="BK30" s="9" t="s">
         <v>75</v>
@@ -22250,1282 +22163,672 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="8" t="n">
-        <v>306005</v>
-      </c>
-      <c r="B31" s="9" t="s">
+      <c r="A31" s="4"/>
+    </row>
+    <row r="32" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="17" t="s">
+        <v>187</v>
+      </c>
+      <c r="B32" s="17"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="17"/>
+      <c r="G32" s="17"/>
+      <c r="H32" s="17"/>
+      <c r="I32" s="17"/>
+      <c r="J32" s="17"/>
+      <c r="K32" s="17"/>
+      <c r="L32" s="17"/>
+      <c r="M32" s="17"/>
+      <c r="N32" s="17"/>
+      <c r="O32" s="17"/>
+      <c r="P32" s="17"/>
+      <c r="Q32" s="17"/>
+      <c r="R32" s="17"/>
+      <c r="S32" s="17"/>
+      <c r="T32" s="17"/>
+      <c r="U32" s="17"/>
+      <c r="V32" s="17"/>
+    </row>
+    <row r="33" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="18" t="s">
+        <v>188</v>
+      </c>
+      <c r="B33" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C33" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" s="18" t="s">
+        <v>189</v>
+      </c>
+      <c r="E33" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F33" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="G33" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H33" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="I33" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="J33" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="K33" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="L33" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="M33" s="18" t="s">
         <v>191</v>
       </c>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9" t="s">
+      <c r="N33" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="O33" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="P33" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q33" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="R33" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="S33" s="18" t="s">
         <v>192</v>
       </c>
-      <c r="G31" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="H31" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="I31" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="J31" s="9" t="s">
+      <c r="T33" s="18" t="s">
         <v>193</v>
       </c>
-      <c r="K31" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="L31" s="12" t="n">
-        <v>861.88</v>
-      </c>
-      <c r="M31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O31" s="12" t="n">
-        <v>861.88</v>
-      </c>
-      <c r="P31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="13" t="n">
-        <v>0.073796</v>
-      </c>
-      <c r="R31" s="12" t="n">
-        <v>43.13</v>
-      </c>
-      <c r="S31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" s="14" t="s">
-        <v>194</v>
-      </c>
-      <c r="U31" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="V31" s="12" t="n">
-        <v>56</v>
-      </c>
-      <c r="W31" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="X31" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="Y31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z31" s="12" t="n">
-        <v>861.88</v>
-      </c>
-      <c r="AA31" s="12" t="n">
-        <v>60.33</v>
-      </c>
-      <c r="AB31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH31" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ31" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AK31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM31" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AN31" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AO31" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AP31" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ31" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR31" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS31" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT31" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU31" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV31" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW31" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="AX31" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="AY31" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ31" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA31" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB31" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BC31" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD31" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE31" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BF31" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BG31" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="BH31" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BI31" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="BJ31" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="BK31" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BL31" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BM31" s="16" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="8" t="n">
-        <v>306127</v>
-      </c>
-      <c r="B32" s="9" t="s">
-        <v>196</v>
-      </c>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9" t="s">
-        <v>197</v>
-      </c>
-      <c r="G32" s="10" t="s">
-        <v>198</v>
-      </c>
-      <c r="H32" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="I32" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="J32" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="K32" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="L32" s="12" t="n">
-        <v>4390.44</v>
-      </c>
-      <c r="M32" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="O32" s="12" t="n">
-        <v>4000.4</v>
-      </c>
-      <c r="P32" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="U32" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="V32" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="W32" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="X32" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="Y32" s="12" t="n">
-        <v>390.04</v>
-      </c>
-      <c r="Z32" s="12" t="n">
-        <v>4000.4</v>
-      </c>
-      <c r="AA32" s="12" t="n">
-        <v>280.03</v>
-      </c>
-      <c r="AB32" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC32" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD32" s="12" t="n">
-        <v>89.72</v>
-      </c>
-      <c r="AE32" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF32" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG32" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH32" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI32" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ32" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AK32" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL32" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM32" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AN32" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AO32" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AP32" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ32" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR32" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS32" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT32" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU32" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV32" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW32" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="AX32" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="AY32" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ32" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA32" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB32" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BC32" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD32" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE32" s="14" t="s">
-        <v>200</v>
-      </c>
-      <c r="BF32" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="BG32" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="BH32" s="14" t="s">
-        <v>201</v>
-      </c>
-      <c r="BI32" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="BJ32" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="BK32" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="BL32" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BM32" s="16" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="8" t="n">
-        <v>306150</v>
-      </c>
-      <c r="B33" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9" t="s">
-        <v>205</v>
-      </c>
-      <c r="G33" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="H33" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="I33" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="J33" s="9" t="s">
-        <v>206</v>
-      </c>
-      <c r="K33" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="L33" s="12" t="n">
-        <v>2070.21</v>
-      </c>
-      <c r="M33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="O33" s="12" t="n">
-        <v>1970.21</v>
-      </c>
-      <c r="P33" s="12" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q33" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" s="12" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="S33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" s="14" t="s">
-        <v>207</v>
-      </c>
-      <c r="U33" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="V33" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="W33" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="X33" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="Y33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z33" s="12" t="n">
-        <v>2070.21</v>
-      </c>
-      <c r="AA33" s="12" t="n">
-        <v>144.92</v>
-      </c>
-      <c r="AB33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH33" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ33" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AK33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM33" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AN33" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AO33" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AP33" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ33" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR33" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS33" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT33" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU33" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV33" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW33" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="AX33" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="AY33" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ33" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA33" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB33" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BC33" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD33" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE33" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BF33" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BG33" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="BH33" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BI33" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="BJ33" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="BK33" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BL33" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BM33" s="16" t="s">
-        <v>80</v>
+      <c r="U33" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="V33" s="18" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="8" t="n">
-        <v>306157</v>
-      </c>
-      <c r="B34" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="G34" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="H34" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="I34" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="J34" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="K34" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="L34" s="12" t="n">
-        <v>11204.49</v>
-      </c>
-      <c r="M34" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="O34" s="12" t="n">
-        <v>10131.65</v>
-      </c>
-      <c r="P34" s="12" t="n">
-        <v>85</v>
-      </c>
-      <c r="Q34" s="13" t="n">
-        <v>0.02398</v>
-      </c>
-      <c r="R34" s="12" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="S34" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" s="14" t="s">
-        <v>211</v>
-      </c>
-      <c r="U34" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="V34" s="12" t="n">
-        <v>55.79</v>
-      </c>
-      <c r="W34" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="X34" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="Y34" s="12" t="n">
-        <v>987.84</v>
-      </c>
-      <c r="Z34" s="12" t="n">
-        <v>10216.65</v>
-      </c>
-      <c r="AA34" s="12" t="n">
-        <v>408.68</v>
-      </c>
-      <c r="AB34" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC34" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD34" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE34" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF34" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG34" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH34" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI34" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ34" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AK34" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL34" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM34" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AN34" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AO34" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AP34" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ34" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR34" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS34" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT34" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU34" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV34" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW34" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="AX34" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="AY34" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ34" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA34" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB34" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BC34" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD34" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE34" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BF34" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BG34" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="BH34" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BI34" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="BJ34" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="BK34" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BL34" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BM34" s="16" t="s">
-        <v>80</v>
+      <c r="A34" s="19" t="n">
+        <v>26</v>
+      </c>
+      <c r="B34" s="19" t="n">
+        <v>5811.05</v>
+      </c>
+      <c r="C34" s="19" t="n">
+        <v>185</v>
+      </c>
+      <c r="D34" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="19" t="n">
+        <v>4196.05</v>
+      </c>
+      <c r="F34" s="19" t="n">
+        <v>99158.03</v>
+      </c>
+      <c r="G34" s="19" t="n">
+        <v>5368.15</v>
+      </c>
+      <c r="H34" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="19" t="n">
+        <v>103354.08</v>
+      </c>
+      <c r="L34" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" s="20" t="n">
+        <v>1.751798</v>
+      </c>
+      <c r="S34" s="19" t="n">
+        <v>104784.08</v>
+      </c>
+      <c r="T34" s="19" t="n">
+        <v>103354.08</v>
+      </c>
+      <c r="U34" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" s="19" t="n">
+        <v>0</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="8" t="n">
-        <v>306173</v>
-      </c>
-      <c r="B35" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9" t="s">
-        <v>213</v>
-      </c>
-      <c r="G35" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="H35" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="I35" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="J35" s="9" t="s">
-        <v>206</v>
-      </c>
-      <c r="K35" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="L35" s="12" t="n">
-        <v>3730.39</v>
-      </c>
-      <c r="M35" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="O35" s="12" t="n">
-        <v>3730.39</v>
-      </c>
-      <c r="P35" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" s="14" t="s">
-        <v>214</v>
-      </c>
-      <c r="U35" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="V35" s="12" t="n">
-        <v>56</v>
-      </c>
-      <c r="W35" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="X35" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="Y35" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z35" s="12" t="n">
-        <v>3730.39</v>
-      </c>
-      <c r="AA35" s="12" t="n">
-        <v>261.14</v>
-      </c>
-      <c r="AB35" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC35" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD35" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE35" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF35" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG35" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH35" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI35" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ35" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AK35" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL35" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM35" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AN35" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AO35" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AP35" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ35" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR35" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS35" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT35" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU35" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV35" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW35" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="AX35" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="AY35" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ35" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA35" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB35" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BC35" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD35" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE35" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BF35" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BG35" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="BH35" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BI35" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="BJ35" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="BK35" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BL35" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BM35" s="16" t="s">
-        <v>80</v>
+    <row r="35" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B35" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C35" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D35" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="E35" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="F35" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="G35" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="H35" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="I35" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="J35" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="K35" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="L35" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="M35" s="18" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="4"/>
+      <c r="A36" s="19" t="n">
+        <v>225.05</v>
+      </c>
+      <c r="B36" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="19" t="n">
+        <v>52.1</v>
+      </c>
+      <c r="E36" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
-    <row r="37" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="17" t="s">
-        <v>216</v>
-      </c>
-      <c r="B37" s="17"/>
-      <c r="C37" s="17"/>
-      <c r="D37" s="17"/>
-      <c r="E37" s="17"/>
-      <c r="F37" s="17"/>
-      <c r="G37" s="17"/>
-      <c r="H37" s="17"/>
-      <c r="I37" s="17"/>
-      <c r="J37" s="17"/>
-      <c r="K37" s="17"/>
-      <c r="L37" s="17"/>
-      <c r="M37" s="17"/>
-      <c r="N37" s="17"/>
-      <c r="O37" s="17"/>
-      <c r="P37" s="17"/>
-      <c r="Q37" s="17"/>
-      <c r="R37" s="17"/>
-      <c r="S37" s="17"/>
-      <c r="T37" s="17"/>
-      <c r="U37" s="17"/>
-      <c r="V37" s="17"/>
+    <row r="37" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="4"/>
     </row>
     <row r="38" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="18" t="s">
-        <v>217</v>
-      </c>
-      <c r="B38" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C38" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D38" s="18" t="s">
-        <v>218</v>
-      </c>
-      <c r="E38" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F38" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="G38" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="H38" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="I38" s="18" t="s">
-        <v>219</v>
-      </c>
-      <c r="J38" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="K38" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="L38" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="M38" s="18" t="s">
-        <v>220</v>
-      </c>
-      <c r="N38" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="O38" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="P38" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q38" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="R38" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="S38" s="18" t="s">
-        <v>221</v>
-      </c>
-      <c r="T38" s="18" t="s">
-        <v>222</v>
-      </c>
-      <c r="U38" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="V38" s="18" t="s">
-        <v>37</v>
-      </c>
+      <c r="A38" s="21" t="s">
+        <v>197</v>
+      </c>
+      <c r="B38" s="21"/>
+      <c r="C38" s="21"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="21"/>
+      <c r="F38" s="21"/>
+      <c r="G38" s="21"/>
+      <c r="H38" s="21"/>
+      <c r="I38" s="21"/>
+      <c r="J38" s="21"/>
+      <c r="K38" s="21"/>
+      <c r="L38" s="21"/>
+      <c r="M38" s="21"/>
+      <c r="N38" s="21"/>
+      <c r="O38" s="21"/>
+      <c r="P38" s="21"/>
+      <c r="Q38" s="21"/>
+      <c r="R38" s="21"/>
+      <c r="S38" s="21"/>
+      <c r="T38" s="21"/>
+      <c r="U38" s="21"/>
+      <c r="V38" s="21"/>
+      <c r="W38" s="21"/>
+      <c r="X38" s="21"/>
+      <c r="Y38" s="21"/>
+      <c r="Z38" s="21"/>
+      <c r="AA38" s="21"/>
+      <c r="AB38" s="21"/>
+      <c r="AC38" s="21"/>
+      <c r="AD38" s="21"/>
+      <c r="AE38" s="21"/>
+      <c r="AF38" s="21"/>
+      <c r="AG38" s="21"/>
+      <c r="AH38" s="21"/>
+      <c r="AI38" s="21"/>
+      <c r="AJ38" s="21"/>
+      <c r="AK38" s="21"/>
+      <c r="AL38" s="21"/>
+      <c r="AM38" s="21"/>
+      <c r="AN38" s="21"/>
+      <c r="AO38" s="21"/>
+      <c r="AP38" s="21"/>
+      <c r="AQ38" s="21"/>
+      <c r="AR38" s="21"/>
+      <c r="AS38" s="21"/>
+      <c r="AT38" s="21"/>
+      <c r="AU38" s="21"/>
+      <c r="AV38" s="21"/>
+      <c r="AW38" s="21"/>
+      <c r="AX38" s="21"/>
+      <c r="AY38" s="21"/>
+      <c r="AZ38" s="21"/>
+      <c r="BA38" s="21"/>
+      <c r="BB38" s="21"/>
+      <c r="BC38" s="21"/>
+      <c r="BD38" s="21"/>
+      <c r="BE38" s="21"/>
+      <c r="BF38" s="21"/>
+      <c r="BG38" s="21"/>
+      <c r="BH38" s="21"/>
+      <c r="BI38" s="21"/>
+      <c r="BJ38" s="21"/>
+      <c r="BK38" s="21"/>
+      <c r="BL38" s="21"/>
+      <c r="BM38" s="21"/>
     </row>
     <row r="39" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="19" t="n">
-        <v>31</v>
-      </c>
-      <c r="B39" s="19" t="n">
-        <v>5811.05</v>
-      </c>
-      <c r="C39" s="19" t="n">
-        <v>185</v>
-      </c>
-      <c r="D39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" s="19" t="n">
-        <v>5302.25</v>
-      </c>
-      <c r="F39" s="19" t="n">
-        <v>113469.81</v>
-      </c>
-      <c r="G39" s="19" t="n">
-        <v>6359.63</v>
-      </c>
-      <c r="H39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" s="19" t="n">
-        <v>180.97</v>
-      </c>
-      <c r="K39" s="19" t="n">
-        <v>118772.06</v>
-      </c>
-      <c r="L39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" s="20" t="n">
-        <v>1.764395</v>
-      </c>
-      <c r="S39" s="19" t="n">
-        <v>119095.86</v>
-      </c>
-      <c r="T39" s="19" t="n">
-        <v>118772.06</v>
-      </c>
-      <c r="U39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" s="19" t="n">
-        <v>0</v>
-      </c>
+      <c r="A39" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B39" s="4"/>
+      <c r="C39" s="4"/>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+      <c r="K39" s="4"/>
+      <c r="L39" s="4"/>
+      <c r="M39" s="4"/>
+      <c r="N39" s="4"/>
+      <c r="O39" s="4"/>
+      <c r="P39" s="4"/>
+      <c r="Q39" s="4"/>
+      <c r="R39" s="4"/>
+      <c r="S39" s="4"/>
+      <c r="T39" s="4"/>
+      <c r="U39" s="4"/>
+      <c r="V39" s="4"/>
+      <c r="W39" s="4"/>
+      <c r="X39" s="4"/>
+      <c r="Y39" s="4"/>
+      <c r="Z39" s="4"/>
+      <c r="AA39" s="4"/>
+      <c r="AB39" s="4"/>
+      <c r="AC39" s="4"/>
+      <c r="AD39" s="4"/>
+      <c r="AE39" s="4"/>
+      <c r="AF39" s="4"/>
+      <c r="AG39" s="4"/>
+      <c r="AH39" s="4"/>
+      <c r="AI39" s="4"/>
+      <c r="AJ39" s="4"/>
+      <c r="AK39" s="4"/>
+      <c r="AL39" s="4"/>
+      <c r="AM39" s="4"/>
+      <c r="AN39" s="4"/>
+      <c r="AO39" s="4"/>
+      <c r="AP39" s="4"/>
+      <c r="AQ39" s="4"/>
+      <c r="AR39" s="4"/>
+      <c r="AS39" s="4"/>
+      <c r="AT39" s="4"/>
+      <c r="AU39" s="4"/>
+      <c r="AV39" s="4"/>
+      <c r="AW39" s="4"/>
+      <c r="AX39" s="4"/>
+      <c r="AY39" s="4"/>
+      <c r="AZ39" s="4"/>
+      <c r="BA39" s="4"/>
+      <c r="BB39" s="4"/>
+      <c r="BC39" s="4"/>
+      <c r="BD39" s="4"/>
+      <c r="BE39" s="4"/>
+      <c r="BF39" s="4"/>
+      <c r="BG39" s="4"/>
+      <c r="BH39" s="4"/>
+      <c r="BI39" s="4"/>
+      <c r="BJ39" s="4"/>
+      <c r="BK39" s="4"/>
+      <c r="BL39" s="4"/>
+      <c r="BM39" s="4"/>
     </row>
-    <row r="40" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="B40" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C40" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="D40" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E40" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="F40" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="G40" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="H40" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="I40" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="J40" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="K40" s="18" t="s">
-        <v>223</v>
-      </c>
-      <c r="L40" s="18" t="s">
-        <v>224</v>
-      </c>
-      <c r="M40" s="18" t="s">
-        <v>225</v>
-      </c>
+    <row r="40" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="K40" s="4"/>
+      <c r="L40" s="4"/>
+      <c r="M40" s="4"/>
+      <c r="N40" s="4"/>
+      <c r="O40" s="4"/>
+      <c r="P40" s="4"/>
+      <c r="Q40" s="4"/>
+      <c r="R40" s="4"/>
+      <c r="S40" s="4"/>
+      <c r="T40" s="4"/>
+      <c r="U40" s="4"/>
+      <c r="V40" s="4"/>
+      <c r="W40" s="4"/>
+      <c r="X40" s="4"/>
+      <c r="Y40" s="4"/>
+      <c r="Z40" s="4"/>
+      <c r="AA40" s="4"/>
+      <c r="AB40" s="4"/>
+      <c r="AC40" s="4"/>
+      <c r="AD40" s="4"/>
+      <c r="AE40" s="4"/>
+      <c r="AF40" s="4"/>
+      <c r="AG40" s="4"/>
+      <c r="AH40" s="4"/>
+      <c r="AI40" s="4"/>
+      <c r="AJ40" s="4"/>
+      <c r="AK40" s="4"/>
+      <c r="AL40" s="4"/>
+      <c r="AM40" s="4"/>
+      <c r="AN40" s="4"/>
+      <c r="AO40" s="4"/>
+      <c r="AP40" s="4"/>
+      <c r="AQ40" s="4"/>
+      <c r="AR40" s="4"/>
+      <c r="AS40" s="4"/>
+      <c r="AT40" s="4"/>
+      <c r="AU40" s="4"/>
+      <c r="AV40" s="4"/>
+      <c r="AW40" s="4"/>
+      <c r="AX40" s="4"/>
+      <c r="AY40" s="4"/>
+      <c r="AZ40" s="4"/>
+      <c r="BA40" s="4"/>
+      <c r="BB40" s="4"/>
+      <c r="BC40" s="4"/>
+      <c r="BD40" s="4"/>
+      <c r="BE40" s="4"/>
+      <c r="BF40" s="4"/>
+      <c r="BG40" s="4"/>
+      <c r="BH40" s="4"/>
+      <c r="BI40" s="4"/>
+      <c r="BJ40" s="4"/>
+      <c r="BK40" s="4"/>
+      <c r="BL40" s="4"/>
+      <c r="BM40" s="4"/>
     </row>
     <row r="41" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="19" t="n">
-        <v>263.49</v>
-      </c>
-      <c r="B41" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C41" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" s="19" t="n">
-        <v>50.44</v>
-      </c>
-      <c r="E41" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" s="19" t="n">
-        <v>0</v>
-      </c>
+      <c r="A41" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="K41" s="4"/>
+      <c r="L41" s="4"/>
+      <c r="M41" s="4"/>
+      <c r="N41" s="4"/>
+      <c r="O41" s="4"/>
+      <c r="P41" s="4"/>
+      <c r="Q41" s="4"/>
+      <c r="R41" s="4"/>
+      <c r="S41" s="4"/>
+      <c r="T41" s="4"/>
+      <c r="U41" s="4"/>
+      <c r="V41" s="4"/>
+      <c r="W41" s="4"/>
+      <c r="X41" s="4"/>
+      <c r="Y41" s="4"/>
+      <c r="Z41" s="4"/>
+      <c r="AA41" s="4"/>
+      <c r="AB41" s="4"/>
+      <c r="AC41" s="4"/>
+      <c r="AD41" s="4"/>
+      <c r="AE41" s="4"/>
+      <c r="AF41" s="4"/>
+      <c r="AG41" s="4"/>
+      <c r="AH41" s="4"/>
+      <c r="AI41" s="4"/>
+      <c r="AJ41" s="4"/>
+      <c r="AK41" s="4"/>
+      <c r="AL41" s="4"/>
+      <c r="AM41" s="4"/>
+      <c r="AN41" s="4"/>
+      <c r="AO41" s="4"/>
+      <c r="AP41" s="4"/>
+      <c r="AQ41" s="4"/>
+      <c r="AR41" s="4"/>
+      <c r="AS41" s="4"/>
+      <c r="AT41" s="4"/>
+      <c r="AU41" s="4"/>
+      <c r="AV41" s="4"/>
+      <c r="AW41" s="4"/>
+      <c r="AX41" s="4"/>
+      <c r="AY41" s="4"/>
+      <c r="AZ41" s="4"/>
+      <c r="BA41" s="4"/>
+      <c r="BB41" s="4"/>
+      <c r="BC41" s="4"/>
+      <c r="BD41" s="4"/>
+      <c r="BE41" s="4"/>
+      <c r="BF41" s="4"/>
+      <c r="BG41" s="4"/>
+      <c r="BH41" s="4"/>
+      <c r="BI41" s="4"/>
+      <c r="BJ41" s="4"/>
+      <c r="BK41" s="4"/>
+      <c r="BL41" s="4"/>
+      <c r="BM41" s="4"/>
     </row>
     <row r="42" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="4"/>
+      <c r="A42" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="B42" s="4"/>
+      <c r="C42" s="4"/>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4"/>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+      <c r="K42" s="4"/>
+      <c r="L42" s="4"/>
+      <c r="M42" s="4"/>
+      <c r="N42" s="4"/>
+      <c r="O42" s="4"/>
+      <c r="P42" s="4"/>
+      <c r="Q42" s="4"/>
+      <c r="R42" s="4"/>
+      <c r="S42" s="4"/>
+      <c r="T42" s="4"/>
+      <c r="U42" s="4"/>
+      <c r="V42" s="4"/>
+      <c r="W42" s="4"/>
+      <c r="X42" s="4"/>
+      <c r="Y42" s="4"/>
+      <c r="Z42" s="4"/>
+      <c r="AA42" s="4"/>
+      <c r="AB42" s="4"/>
+      <c r="AC42" s="4"/>
+      <c r="AD42" s="4"/>
+      <c r="AE42" s="4"/>
+      <c r="AF42" s="4"/>
+      <c r="AG42" s="4"/>
+      <c r="AH42" s="4"/>
+      <c r="AI42" s="4"/>
+      <c r="AJ42" s="4"/>
+      <c r="AK42" s="4"/>
+      <c r="AL42" s="4"/>
+      <c r="AM42" s="4"/>
+      <c r="AN42" s="4"/>
+      <c r="AO42" s="4"/>
+      <c r="AP42" s="4"/>
+      <c r="AQ42" s="4"/>
+      <c r="AR42" s="4"/>
+      <c r="AS42" s="4"/>
+      <c r="AT42" s="4"/>
+      <c r="AU42" s="4"/>
+      <c r="AV42" s="4"/>
+      <c r="AW42" s="4"/>
+      <c r="AX42" s="4"/>
+      <c r="AY42" s="4"/>
+      <c r="AZ42" s="4"/>
+      <c r="BA42" s="4"/>
+      <c r="BB42" s="4"/>
+      <c r="BC42" s="4"/>
+      <c r="BD42" s="4"/>
+      <c r="BE42" s="4"/>
+      <c r="BF42" s="4"/>
+      <c r="BG42" s="4"/>
+      <c r="BH42" s="4"/>
+      <c r="BI42" s="4"/>
+      <c r="BJ42" s="4"/>
+      <c r="BK42" s="4"/>
+      <c r="BL42" s="4"/>
+      <c r="BM42" s="4"/>
     </row>
-    <row r="43" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="21" t="s">
-        <v>226</v>
-      </c>
-      <c r="B43" s="21"/>
-      <c r="C43" s="21"/>
-      <c r="D43" s="21"/>
-      <c r="E43" s="21"/>
-      <c r="F43" s="21"/>
-      <c r="G43" s="21"/>
-      <c r="H43" s="21"/>
-      <c r="I43" s="21"/>
-      <c r="J43" s="21"/>
-      <c r="K43" s="21"/>
-      <c r="L43" s="21"/>
-      <c r="M43" s="21"/>
-      <c r="N43" s="21"/>
-      <c r="O43" s="21"/>
-      <c r="P43" s="21"/>
-      <c r="Q43" s="21"/>
-      <c r="R43" s="21"/>
-      <c r="S43" s="21"/>
-      <c r="T43" s="21"/>
-      <c r="U43" s="21"/>
-      <c r="V43" s="21"/>
-      <c r="W43" s="21"/>
-      <c r="X43" s="21"/>
-      <c r="Y43" s="21"/>
-      <c r="Z43" s="21"/>
-      <c r="AA43" s="21"/>
-      <c r="AB43" s="21"/>
-      <c r="AC43" s="21"/>
-      <c r="AD43" s="21"/>
-      <c r="AE43" s="21"/>
-      <c r="AF43" s="21"/>
-      <c r="AG43" s="21"/>
-      <c r="AH43" s="21"/>
-      <c r="AI43" s="21"/>
-      <c r="AJ43" s="21"/>
-      <c r="AK43" s="21"/>
-      <c r="AL43" s="21"/>
-      <c r="AM43" s="21"/>
-      <c r="AN43" s="21"/>
-      <c r="AO43" s="21"/>
-      <c r="AP43" s="21"/>
-      <c r="AQ43" s="21"/>
-      <c r="AR43" s="21"/>
-      <c r="AS43" s="21"/>
-      <c r="AT43" s="21"/>
-      <c r="AU43" s="21"/>
-      <c r="AV43" s="21"/>
-      <c r="AW43" s="21"/>
-      <c r="AX43" s="21"/>
-      <c r="AY43" s="21"/>
-      <c r="AZ43" s="21"/>
-      <c r="BA43" s="21"/>
-      <c r="BB43" s="21"/>
-      <c r="BC43" s="21"/>
-      <c r="BD43" s="21"/>
-      <c r="BE43" s="21"/>
-      <c r="BF43" s="21"/>
-      <c r="BG43" s="21"/>
-      <c r="BH43" s="21"/>
-      <c r="BI43" s="21"/>
-      <c r="BJ43" s="21"/>
-      <c r="BK43" s="21"/>
-      <c r="BL43" s="21"/>
-      <c r="BM43" s="21"/>
+    <row r="43" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B43" s="4"/>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="K43" s="4"/>
+      <c r="L43" s="4"/>
+      <c r="M43" s="4"/>
+      <c r="N43" s="4"/>
+      <c r="O43" s="4"/>
+      <c r="P43" s="4"/>
+      <c r="Q43" s="4"/>
+      <c r="R43" s="4"/>
+      <c r="S43" s="4"/>
+      <c r="T43" s="4"/>
+      <c r="U43" s="4"/>
+      <c r="V43" s="4"/>
+      <c r="W43" s="4"/>
+      <c r="X43" s="4"/>
+      <c r="Y43" s="4"/>
+      <c r="Z43" s="4"/>
+      <c r="AA43" s="4"/>
+      <c r="AB43" s="4"/>
+      <c r="AC43" s="4"/>
+      <c r="AD43" s="4"/>
+      <c r="AE43" s="4"/>
+      <c r="AF43" s="4"/>
+      <c r="AG43" s="4"/>
+      <c r="AH43" s="4"/>
+      <c r="AI43" s="4"/>
+      <c r="AJ43" s="4"/>
+      <c r="AK43" s="4"/>
+      <c r="AL43" s="4"/>
+      <c r="AM43" s="4"/>
+      <c r="AN43" s="4"/>
+      <c r="AO43" s="4"/>
+      <c r="AP43" s="4"/>
+      <c r="AQ43" s="4"/>
+      <c r="AR43" s="4"/>
+      <c r="AS43" s="4"/>
+      <c r="AT43" s="4"/>
+      <c r="AU43" s="4"/>
+      <c r="AV43" s="4"/>
+      <c r="AW43" s="4"/>
+      <c r="AX43" s="4"/>
+      <c r="AY43" s="4"/>
+      <c r="AZ43" s="4"/>
+      <c r="BA43" s="4"/>
+      <c r="BB43" s="4"/>
+      <c r="BC43" s="4"/>
+      <c r="BD43" s="4"/>
+      <c r="BE43" s="4"/>
+      <c r="BF43" s="4"/>
+      <c r="BG43" s="4"/>
+      <c r="BH43" s="4"/>
+      <c r="BI43" s="4"/>
+      <c r="BJ43" s="4"/>
+      <c r="BK43" s="4"/>
+      <c r="BL43" s="4"/>
+      <c r="BM43" s="4"/>
     </row>
     <row r="44" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="s">
-        <v>75</v>
+        <v>201</v>
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
@@ -23594,7 +22897,7 @@
     </row>
     <row r="45" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="4" t="s">
-        <v>227</v>
+        <v>202</v>
       </c>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
@@ -23663,7 +22966,7 @@
     </row>
     <row r="46" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="4" t="s">
-        <v>228</v>
+        <v>203</v>
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
@@ -23732,7 +23035,7 @@
     </row>
     <row r="47" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="s">
-        <v>229</v>
+        <v>204</v>
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
@@ -23801,7 +23104,7 @@
     </row>
     <row r="48" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="4" t="s">
-        <v>22</v>
+        <v>205</v>
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
@@ -23868,353 +23171,8 @@
       <c r="BL48" s="4"/>
       <c r="BM48" s="4"/>
     </row>
-    <row r="49" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="B49" s="4"/>
-      <c r="C49" s="4"/>
-      <c r="D49" s="4"/>
-      <c r="E49" s="4"/>
-      <c r="F49" s="4"/>
-      <c r="G49" s="4"/>
-      <c r="H49" s="4"/>
-      <c r="I49" s="4"/>
-      <c r="J49" s="4"/>
-      <c r="K49" s="4"/>
-      <c r="L49" s="4"/>
-      <c r="M49" s="4"/>
-      <c r="N49" s="4"/>
-      <c r="O49" s="4"/>
-      <c r="P49" s="4"/>
-      <c r="Q49" s="4"/>
-      <c r="R49" s="4"/>
-      <c r="S49" s="4"/>
-      <c r="T49" s="4"/>
-      <c r="U49" s="4"/>
-      <c r="V49" s="4"/>
-      <c r="W49" s="4"/>
-      <c r="X49" s="4"/>
-      <c r="Y49" s="4"/>
-      <c r="Z49" s="4"/>
-      <c r="AA49" s="4"/>
-      <c r="AB49" s="4"/>
-      <c r="AC49" s="4"/>
-      <c r="AD49" s="4"/>
-      <c r="AE49" s="4"/>
-      <c r="AF49" s="4"/>
-      <c r="AG49" s="4"/>
-      <c r="AH49" s="4"/>
-      <c r="AI49" s="4"/>
-      <c r="AJ49" s="4"/>
-      <c r="AK49" s="4"/>
-      <c r="AL49" s="4"/>
-      <c r="AM49" s="4"/>
-      <c r="AN49" s="4"/>
-      <c r="AO49" s="4"/>
-      <c r="AP49" s="4"/>
-      <c r="AQ49" s="4"/>
-      <c r="AR49" s="4"/>
-      <c r="AS49" s="4"/>
-      <c r="AT49" s="4"/>
-      <c r="AU49" s="4"/>
-      <c r="AV49" s="4"/>
-      <c r="AW49" s="4"/>
-      <c r="AX49" s="4"/>
-      <c r="AY49" s="4"/>
-      <c r="AZ49" s="4"/>
-      <c r="BA49" s="4"/>
-      <c r="BB49" s="4"/>
-      <c r="BC49" s="4"/>
-      <c r="BD49" s="4"/>
-      <c r="BE49" s="4"/>
-      <c r="BF49" s="4"/>
-      <c r="BG49" s="4"/>
-      <c r="BH49" s="4"/>
-      <c r="BI49" s="4"/>
-      <c r="BJ49" s="4"/>
-      <c r="BK49" s="4"/>
-      <c r="BL49" s="4"/>
-      <c r="BM49" s="4"/>
-    </row>
-    <row r="50" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="B50" s="4"/>
-      <c r="C50" s="4"/>
-      <c r="D50" s="4"/>
-      <c r="E50" s="4"/>
-      <c r="F50" s="4"/>
-      <c r="G50" s="4"/>
-      <c r="H50" s="4"/>
-      <c r="I50" s="4"/>
-      <c r="J50" s="4"/>
-      <c r="K50" s="4"/>
-      <c r="L50" s="4"/>
-      <c r="M50" s="4"/>
-      <c r="N50" s="4"/>
-      <c r="O50" s="4"/>
-      <c r="P50" s="4"/>
-      <c r="Q50" s="4"/>
-      <c r="R50" s="4"/>
-      <c r="S50" s="4"/>
-      <c r="T50" s="4"/>
-      <c r="U50" s="4"/>
-      <c r="V50" s="4"/>
-      <c r="W50" s="4"/>
-      <c r="X50" s="4"/>
-      <c r="Y50" s="4"/>
-      <c r="Z50" s="4"/>
-      <c r="AA50" s="4"/>
-      <c r="AB50" s="4"/>
-      <c r="AC50" s="4"/>
-      <c r="AD50" s="4"/>
-      <c r="AE50" s="4"/>
-      <c r="AF50" s="4"/>
-      <c r="AG50" s="4"/>
-      <c r="AH50" s="4"/>
-      <c r="AI50" s="4"/>
-      <c r="AJ50" s="4"/>
-      <c r="AK50" s="4"/>
-      <c r="AL50" s="4"/>
-      <c r="AM50" s="4"/>
-      <c r="AN50" s="4"/>
-      <c r="AO50" s="4"/>
-      <c r="AP50" s="4"/>
-      <c r="AQ50" s="4"/>
-      <c r="AR50" s="4"/>
-      <c r="AS50" s="4"/>
-      <c r="AT50" s="4"/>
-      <c r="AU50" s="4"/>
-      <c r="AV50" s="4"/>
-      <c r="AW50" s="4"/>
-      <c r="AX50" s="4"/>
-      <c r="AY50" s="4"/>
-      <c r="AZ50" s="4"/>
-      <c r="BA50" s="4"/>
-      <c r="BB50" s="4"/>
-      <c r="BC50" s="4"/>
-      <c r="BD50" s="4"/>
-      <c r="BE50" s="4"/>
-      <c r="BF50" s="4"/>
-      <c r="BG50" s="4"/>
-      <c r="BH50" s="4"/>
-      <c r="BI50" s="4"/>
-      <c r="BJ50" s="4"/>
-      <c r="BK50" s="4"/>
-      <c r="BL50" s="4"/>
-      <c r="BM50" s="4"/>
-    </row>
-    <row r="51" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="B51" s="4"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="4"/>
-      <c r="E51" s="4"/>
-      <c r="F51" s="4"/>
-      <c r="G51" s="4"/>
-      <c r="H51" s="4"/>
-      <c r="I51" s="4"/>
-      <c r="J51" s="4"/>
-      <c r="K51" s="4"/>
-      <c r="L51" s="4"/>
-      <c r="M51" s="4"/>
-      <c r="N51" s="4"/>
-      <c r="O51" s="4"/>
-      <c r="P51" s="4"/>
-      <c r="Q51" s="4"/>
-      <c r="R51" s="4"/>
-      <c r="S51" s="4"/>
-      <c r="T51" s="4"/>
-      <c r="U51" s="4"/>
-      <c r="V51" s="4"/>
-      <c r="W51" s="4"/>
-      <c r="X51" s="4"/>
-      <c r="Y51" s="4"/>
-      <c r="Z51" s="4"/>
-      <c r="AA51" s="4"/>
-      <c r="AB51" s="4"/>
-      <c r="AC51" s="4"/>
-      <c r="AD51" s="4"/>
-      <c r="AE51" s="4"/>
-      <c r="AF51" s="4"/>
-      <c r="AG51" s="4"/>
-      <c r="AH51" s="4"/>
-      <c r="AI51" s="4"/>
-      <c r="AJ51" s="4"/>
-      <c r="AK51" s="4"/>
-      <c r="AL51" s="4"/>
-      <c r="AM51" s="4"/>
-      <c r="AN51" s="4"/>
-      <c r="AO51" s="4"/>
-      <c r="AP51" s="4"/>
-      <c r="AQ51" s="4"/>
-      <c r="AR51" s="4"/>
-      <c r="AS51" s="4"/>
-      <c r="AT51" s="4"/>
-      <c r="AU51" s="4"/>
-      <c r="AV51" s="4"/>
-      <c r="AW51" s="4"/>
-      <c r="AX51" s="4"/>
-      <c r="AY51" s="4"/>
-      <c r="AZ51" s="4"/>
-      <c r="BA51" s="4"/>
-      <c r="BB51" s="4"/>
-      <c r="BC51" s="4"/>
-      <c r="BD51" s="4"/>
-      <c r="BE51" s="4"/>
-      <c r="BF51" s="4"/>
-      <c r="BG51" s="4"/>
-      <c r="BH51" s="4"/>
-      <c r="BI51" s="4"/>
-      <c r="BJ51" s="4"/>
-      <c r="BK51" s="4"/>
-      <c r="BL51" s="4"/>
-      <c r="BM51" s="4"/>
-    </row>
-    <row r="52" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="B52" s="4"/>
-      <c r="C52" s="4"/>
-      <c r="D52" s="4"/>
-      <c r="E52" s="4"/>
-      <c r="F52" s="4"/>
-      <c r="G52" s="4"/>
-      <c r="H52" s="4"/>
-      <c r="I52" s="4"/>
-      <c r="J52" s="4"/>
-      <c r="K52" s="4"/>
-      <c r="L52" s="4"/>
-      <c r="M52" s="4"/>
-      <c r="N52" s="4"/>
-      <c r="O52" s="4"/>
-      <c r="P52" s="4"/>
-      <c r="Q52" s="4"/>
-      <c r="R52" s="4"/>
-      <c r="S52" s="4"/>
-      <c r="T52" s="4"/>
-      <c r="U52" s="4"/>
-      <c r="V52" s="4"/>
-      <c r="W52" s="4"/>
-      <c r="X52" s="4"/>
-      <c r="Y52" s="4"/>
-      <c r="Z52" s="4"/>
-      <c r="AA52" s="4"/>
-      <c r="AB52" s="4"/>
-      <c r="AC52" s="4"/>
-      <c r="AD52" s="4"/>
-      <c r="AE52" s="4"/>
-      <c r="AF52" s="4"/>
-      <c r="AG52" s="4"/>
-      <c r="AH52" s="4"/>
-      <c r="AI52" s="4"/>
-      <c r="AJ52" s="4"/>
-      <c r="AK52" s="4"/>
-      <c r="AL52" s="4"/>
-      <c r="AM52" s="4"/>
-      <c r="AN52" s="4"/>
-      <c r="AO52" s="4"/>
-      <c r="AP52" s="4"/>
-      <c r="AQ52" s="4"/>
-      <c r="AR52" s="4"/>
-      <c r="AS52" s="4"/>
-      <c r="AT52" s="4"/>
-      <c r="AU52" s="4"/>
-      <c r="AV52" s="4"/>
-      <c r="AW52" s="4"/>
-      <c r="AX52" s="4"/>
-      <c r="AY52" s="4"/>
-      <c r="AZ52" s="4"/>
-      <c r="BA52" s="4"/>
-      <c r="BB52" s="4"/>
-      <c r="BC52" s="4"/>
-      <c r="BD52" s="4"/>
-      <c r="BE52" s="4"/>
-      <c r="BF52" s="4"/>
-      <c r="BG52" s="4"/>
-      <c r="BH52" s="4"/>
-      <c r="BI52" s="4"/>
-      <c r="BJ52" s="4"/>
-      <c r="BK52" s="4"/>
-      <c r="BL52" s="4"/>
-      <c r="BM52" s="4"/>
-    </row>
-    <row r="53" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="B53" s="4"/>
-      <c r="C53" s="4"/>
-      <c r="D53" s="4"/>
-      <c r="E53" s="4"/>
-      <c r="F53" s="4"/>
-      <c r="G53" s="4"/>
-      <c r="H53" s="4"/>
-      <c r="I53" s="4"/>
-      <c r="J53" s="4"/>
-      <c r="K53" s="4"/>
-      <c r="L53" s="4"/>
-      <c r="M53" s="4"/>
-      <c r="N53" s="4"/>
-      <c r="O53" s="4"/>
-      <c r="P53" s="4"/>
-      <c r="Q53" s="4"/>
-      <c r="R53" s="4"/>
-      <c r="S53" s="4"/>
-      <c r="T53" s="4"/>
-      <c r="U53" s="4"/>
-      <c r="V53" s="4"/>
-      <c r="W53" s="4"/>
-      <c r="X53" s="4"/>
-      <c r="Y53" s="4"/>
-      <c r="Z53" s="4"/>
-      <c r="AA53" s="4"/>
-      <c r="AB53" s="4"/>
-      <c r="AC53" s="4"/>
-      <c r="AD53" s="4"/>
-      <c r="AE53" s="4"/>
-      <c r="AF53" s="4"/>
-      <c r="AG53" s="4"/>
-      <c r="AH53" s="4"/>
-      <c r="AI53" s="4"/>
-      <c r="AJ53" s="4"/>
-      <c r="AK53" s="4"/>
-      <c r="AL53" s="4"/>
-      <c r="AM53" s="4"/>
-      <c r="AN53" s="4"/>
-      <c r="AO53" s="4"/>
-      <c r="AP53" s="4"/>
-      <c r="AQ53" s="4"/>
-      <c r="AR53" s="4"/>
-      <c r="AS53" s="4"/>
-      <c r="AT53" s="4"/>
-      <c r="AU53" s="4"/>
-      <c r="AV53" s="4"/>
-      <c r="AW53" s="4"/>
-      <c r="AX53" s="4"/>
-      <c r="AY53" s="4"/>
-      <c r="AZ53" s="4"/>
-      <c r="BA53" s="4"/>
-      <c r="BB53" s="4"/>
-      <c r="BC53" s="4"/>
-      <c r="BD53" s="4"/>
-      <c r="BE53" s="4"/>
-      <c r="BF53" s="4"/>
-      <c r="BG53" s="4"/>
-      <c r="BH53" s="4"/>
-      <c r="BI53" s="4"/>
-      <c r="BJ53" s="4"/>
-      <c r="BK53" s="4"/>
-      <c r="BL53" s="4"/>
-      <c r="BM53" s="4"/>
-    </row>
   </sheetData>
-  <mergeCells count="47">
+  <mergeCells count="42">
     <mergeCell ref="A1:BI1"/>
     <mergeCell ref="BJ1:BM1"/>
     <mergeCell ref="A2:BM2"/>
@@ -24245,23 +23203,18 @@
     <mergeCell ref="B28:E28"/>
     <mergeCell ref="B29:E29"/>
     <mergeCell ref="B30:E30"/>
-    <mergeCell ref="B31:E31"/>
-    <mergeCell ref="B32:E32"/>
-    <mergeCell ref="B33:E33"/>
-    <mergeCell ref="B34:E34"/>
-    <mergeCell ref="B35:E35"/>
-    <mergeCell ref="A37:V37"/>
+    <mergeCell ref="A32:V32"/>
+    <mergeCell ref="A38:BM38"/>
+    <mergeCell ref="A39:BM39"/>
+    <mergeCell ref="A40:BM40"/>
+    <mergeCell ref="A41:BM41"/>
+    <mergeCell ref="A42:BM42"/>
     <mergeCell ref="A43:BM43"/>
     <mergeCell ref="A44:BM44"/>
     <mergeCell ref="A45:BM45"/>
     <mergeCell ref="A46:BM46"/>
     <mergeCell ref="A47:BM47"/>
     <mergeCell ref="A48:BM48"/>
-    <mergeCell ref="A49:BM49"/>
-    <mergeCell ref="A50:BM50"/>
-    <mergeCell ref="A51:BM51"/>
-    <mergeCell ref="A52:BM52"/>
-    <mergeCell ref="A53:BM53"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>

--- a/tratando_tabelas/finitura/entradas_finitura.xlsx
+++ b/tratando_tabelas/finitura/entradas_finitura.xlsx
@@ -20,12 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1152" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1272" uniqueCount="218">
   <si>
     <t xml:space="preserve">Santri ADM 1.1.5.7 R1</t>
   </si>
   <si>
-    <t xml:space="preserve">Emitido em: 30/04/2026 05:30:25</t>
+    <t xml:space="preserve">Emitido em: 04/05/2026 07:42:43</t>
   </si>
   <si>
     <t xml:space="preserve">Relação de entradas - Sintético</t>
@@ -214,72 +214,6 @@
     <t xml:space="preserve">Fornecedor substituto tributário</t>
   </si>
   <si>
-    <t xml:space="preserve">16.059 - JLR COM IMPORT. E EXP. DE MATERIAIS DE CONSTRUCAO LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">XML</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.242,00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ag. chegada da mercadoria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - OBJETIVA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0,00</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">          </t>
-  </si>
-  <si>
-    <t xml:space="preserve">41260417781412000109550010000119661000316126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Não</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.818,78</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.910</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41260417781412000109550010000119691000316152</t>
-  </si>
-  <si>
     <t xml:space="preserve">761 - DOCOL FV IND.E COM. DE METAIS SANITARIOS LTDA</t>
   </si>
   <si>
@@ -298,16 +232,46 @@
     <t xml:space="preserve">13/05/2026</t>
   </si>
   <si>
+    <t xml:space="preserve">XML</t>
+  </si>
+  <si>
     <t xml:space="preserve">2.751,00</t>
   </si>
   <si>
+    <t xml:space="preserve">Ag. chegada da mercadoria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - OBJETIVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">          </t>
+  </si>
+  <si>
     <t xml:space="preserve">42260475339051000141550080006135571858110937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Não</t>
   </si>
   <si>
     <t xml:space="preserve">1.856 - DEXCO S.A - METAIS</t>
   </si>
   <si>
     <t xml:space="preserve">5.065.606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
   </si>
   <si>
     <t xml:space="preserve">17/04/2026</t>
@@ -440,6 +404,9 @@
   </si>
   <si>
     <t xml:space="preserve">834,78</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S</t>
   </si>
   <si>
     <t xml:space="preserve">35260453654471000180550010000536161000320142</t>
@@ -581,6 +548,75 @@
   </si>
   <si>
     <t xml:space="preserve">41260408028676000103550010000562311004422203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.059 - JLR COM IMPORT. E EXP. DE MATERIAIS DE CONSTRUCAO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.916,19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41260417781412000109550010000120381000336730</t>
+  </si>
+  <si>
+    <t xml:space="preserve">628.023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.714,13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260475339051000141550080006280231262652897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">628.271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">891,38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260475339051000141550080006282711217572128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">629.065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.593,54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260475339051000141550080006290651791456700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.576 - GRUPO METAL DESIGN LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">900,38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.910</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260486895448000560550010000006961367561442</t>
   </si>
   <si>
     <t xml:space="preserve">Total geral</t>
@@ -16826,7 +16862,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BM48"/>
+  <dimension ref="A1:BM51"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="18"/>
@@ -17198,7 +17234,7 @@
     </row>
     <row r="5" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="n">
-        <v>304880</v>
+        <v>305238</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>64</v>
@@ -17225,25 +17261,25 @@
         <v>70</v>
       </c>
       <c r="L5" s="12" t="n">
-        <v>25242</v>
+        <v>2751</v>
       </c>
       <c r="M5" s="12" t="n">
-        <v>5811.05</v>
+        <v>0</v>
       </c>
       <c r="N5" s="12" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="O5" s="12" t="n">
-        <v>28810.6</v>
+        <v>2751</v>
       </c>
       <c r="P5" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q5" s="13" t="n">
-        <v>0</v>
+        <v>0.011956</v>
       </c>
       <c r="R5" s="12" t="n">
-        <v>6</v>
+        <v>5.06</v>
       </c>
       <c r="S5" s="12" t="n">
         <v>0</v>
@@ -17255,7 +17291,7 @@
         <v>72</v>
       </c>
       <c r="V5" s="12" t="n">
-        <v>120</v>
+        <v>28</v>
       </c>
       <c r="W5" s="9" t="s">
         <v>73</v>
@@ -17264,13 +17300,13 @@
         <v>68</v>
       </c>
       <c r="Y5" s="12" t="n">
-        <v>2242.45</v>
+        <v>0</v>
       </c>
       <c r="Z5" s="12" t="n">
-        <v>22999.55</v>
+        <v>2751</v>
       </c>
       <c r="AA5" s="12" t="n">
-        <v>919.96</v>
+        <v>192.57</v>
       </c>
       <c r="AB5" s="12" t="n">
         <v>0</v>
@@ -17389,25 +17425,25 @@
     </row>
     <row r="6" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="n">
-        <v>304943</v>
+        <v>305457</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
       <c r="E6" s="9"/>
       <c r="F6" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="J6" s="9" t="s">
         <v>78</v>
@@ -17416,31 +17452,31 @@
         <v>70</v>
       </c>
       <c r="L6" s="12" t="n">
-        <v>1818.78</v>
+        <v>4770.41</v>
       </c>
       <c r="M6" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N6" s="12" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="O6" s="12" t="n">
-        <v>1657.2</v>
+        <v>4588.46</v>
       </c>
       <c r="P6" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q6" s="13" t="n">
-        <v>0</v>
+        <v>0.231499</v>
       </c>
       <c r="R6" s="12" t="n">
-        <v>0</v>
+        <v>35.08</v>
       </c>
       <c r="S6" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T6" s="14" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="U6" s="15" t="s">
         <v>72</v>
@@ -17452,16 +17488,16 @@
         <v>73</v>
       </c>
       <c r="X6" s="9" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="Y6" s="12" t="n">
-        <v>161.58</v>
+        <v>181.95</v>
       </c>
       <c r="Z6" s="12" t="n">
-        <v>1657.2</v>
+        <v>4588.46</v>
       </c>
       <c r="AA6" s="12" t="n">
-        <v>66.28</v>
+        <v>183.54</v>
       </c>
       <c r="AB6" s="12" t="n">
         <v>0</v>
@@ -17527,10 +17563,10 @@
         <v>74</v>
       </c>
       <c r="AW6" s="14" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AX6" s="10" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="AY6" s="14" t="s">
         <v>75</v>
@@ -17566,7 +17602,7 @@
         <v>78</v>
       </c>
       <c r="BJ6" s="9" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="BK6" s="9" t="s">
         <v>75</v>
@@ -17580,34 +17616,34 @@
     </row>
     <row r="7" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="n">
-        <v>305238</v>
+        <v>305470</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
       <c r="F7" s="9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K7" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L7" s="12" t="n">
-        <v>2751</v>
+        <v>314.65</v>
       </c>
       <c r="M7" s="12" t="n">
         <v>0</v>
@@ -17616,43 +17652,43 @@
         <v>2</v>
       </c>
       <c r="O7" s="12" t="n">
-        <v>2751</v>
+        <v>295.45</v>
       </c>
       <c r="P7" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q7" s="13" t="n">
-        <v>0.011956</v>
+        <v>0.016472</v>
       </c>
       <c r="R7" s="12" t="n">
-        <v>5.06</v>
+        <v>1.6</v>
       </c>
       <c r="S7" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T7" s="14" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="U7" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V7" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W7" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X7" s="9" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="Y7" s="12" t="n">
-        <v>0</v>
+        <v>19.2</v>
       </c>
       <c r="Z7" s="12" t="n">
-        <v>2751</v>
+        <v>295.45</v>
       </c>
       <c r="AA7" s="12" t="n">
-        <v>192.57</v>
+        <v>11.81</v>
       </c>
       <c r="AB7" s="12" t="n">
         <v>0</v>
@@ -17718,10 +17754,10 @@
         <v>74</v>
       </c>
       <c r="AW7" s="14" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AX7" s="10" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AY7" s="14" t="s">
         <v>75</v>
@@ -17757,7 +17793,7 @@
         <v>78</v>
       </c>
       <c r="BJ7" s="9" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="BK7" s="9" t="s">
         <v>75</v>
@@ -17771,25 +17807,25 @@
     </row>
     <row r="8" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="n">
-        <v>305457</v>
+        <v>305480</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
       <c r="F8" s="9" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="J8" s="9" t="s">
         <v>78</v>
@@ -17798,31 +17834,31 @@
         <v>70</v>
       </c>
       <c r="L8" s="12" t="n">
-        <v>4770.41</v>
+        <v>2373.3</v>
       </c>
       <c r="M8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N8" s="12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="O8" s="12" t="n">
-        <v>4588.46</v>
+        <v>2228.46</v>
       </c>
       <c r="P8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q8" s="13" t="n">
-        <v>0.231499</v>
+        <v>0.017186</v>
       </c>
       <c r="R8" s="12" t="n">
-        <v>35.08</v>
+        <v>12.33</v>
       </c>
       <c r="S8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T8" s="14" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="U8" s="15" t="s">
         <v>72</v>
@@ -17834,16 +17870,16 @@
         <v>73</v>
       </c>
       <c r="X8" s="9" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="Y8" s="12" t="n">
-        <v>181.95</v>
+        <v>144.84</v>
       </c>
       <c r="Z8" s="12" t="n">
-        <v>4588.46</v>
+        <v>2228.46</v>
       </c>
       <c r="AA8" s="12" t="n">
-        <v>183.54</v>
+        <v>89.14</v>
       </c>
       <c r="AB8" s="12" t="n">
         <v>0</v>
@@ -17909,10 +17945,10 @@
         <v>74</v>
       </c>
       <c r="AW8" s="14" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AX8" s="10" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="AY8" s="14" t="s">
         <v>75</v>
@@ -17948,7 +17984,7 @@
         <v>78</v>
       </c>
       <c r="BJ8" s="9" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="BK8" s="9" t="s">
         <v>75</v>
@@ -17962,79 +17998,79 @@
     </row>
     <row r="9" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="n">
-        <v>305470</v>
+        <v>305556</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>94</v>
+        <v>64</v>
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="9" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="G9" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H9" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="I9" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I9" s="9" t="s">
+      <c r="J9" s="9" t="s">
         <v>97</v>
-      </c>
-      <c r="J9" s="9" t="s">
-        <v>78</v>
       </c>
       <c r="K9" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L9" s="12" t="n">
-        <v>314.65</v>
+        <v>5879.02</v>
       </c>
       <c r="M9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N9" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O9" s="12" t="n">
-        <v>295.45</v>
+        <v>5879.02</v>
       </c>
       <c r="P9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q9" s="13" t="n">
-        <v>0.016472</v>
+        <v>0.467698</v>
       </c>
       <c r="R9" s="12" t="n">
-        <v>1.6</v>
+        <v>31.5</v>
       </c>
       <c r="S9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T9" s="14" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="U9" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V9" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W9" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X9" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Y9" s="12" t="n">
-        <v>19.2</v>
+        <v>0</v>
       </c>
       <c r="Z9" s="12" t="n">
-        <v>295.45</v>
+        <v>5879.02</v>
       </c>
       <c r="AA9" s="12" t="n">
-        <v>11.81</v>
+        <v>411.53</v>
       </c>
       <c r="AB9" s="12" t="n">
         <v>0</v>
@@ -18100,10 +18136,10 @@
         <v>74</v>
       </c>
       <c r="AW9" s="14" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AX9" s="10" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AY9" s="14" t="s">
         <v>75</v>
@@ -18139,7 +18175,7 @@
         <v>78</v>
       </c>
       <c r="BJ9" s="9" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="BK9" s="9" t="s">
         <v>75</v>
@@ -18153,79 +18189,79 @@
     </row>
     <row r="10" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="n">
-        <v>305480</v>
+        <v>305560</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>94</v>
+        <v>64</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
       <c r="F10" s="9" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G10" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H10" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="I10" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I10" s="9" t="s">
-        <v>97</v>
-      </c>
       <c r="J10" s="9" t="s">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="K10" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L10" s="12" t="n">
-        <v>2373.3</v>
+        <v>3121.47</v>
       </c>
       <c r="M10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N10" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O10" s="12" t="n">
-        <v>2228.46</v>
+        <v>3121.47</v>
       </c>
       <c r="P10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q10" s="13" t="n">
-        <v>0.017186</v>
+        <v>0.031059</v>
       </c>
       <c r="R10" s="12" t="n">
-        <v>12.33</v>
+        <v>5.54</v>
       </c>
       <c r="S10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T10" s="14" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="U10" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V10" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W10" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X10" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Y10" s="12" t="n">
-        <v>144.84</v>
+        <v>0</v>
       </c>
       <c r="Z10" s="12" t="n">
-        <v>2228.46</v>
+        <v>3121.47</v>
       </c>
       <c r="AA10" s="12" t="n">
-        <v>89.14</v>
+        <v>218.5</v>
       </c>
       <c r="AB10" s="12" t="n">
         <v>0</v>
@@ -18291,10 +18327,10 @@
         <v>74</v>
       </c>
       <c r="AW10" s="14" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AX10" s="10" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AY10" s="14" t="s">
         <v>75</v>
@@ -18330,7 +18366,7 @@
         <v>78</v>
       </c>
       <c r="BJ10" s="9" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="BK10" s="9" t="s">
         <v>75</v>
@@ -18344,34 +18380,34 @@
     </row>
     <row r="11" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="n">
-        <v>305556</v>
+        <v>305561</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
       <c r="F11" s="9" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="K11" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>5879.02</v>
+        <v>5331.26</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>0</v>
@@ -18380,22 +18416,22 @@
         <v>1</v>
       </c>
       <c r="O11" s="12" t="n">
-        <v>5879.02</v>
+        <v>5005.88</v>
       </c>
       <c r="P11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q11" s="13" t="n">
-        <v>0.467698</v>
+        <v>0.055816</v>
       </c>
       <c r="R11" s="12" t="n">
-        <v>31.5</v>
+        <v>7.12</v>
       </c>
       <c r="S11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T11" s="14" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="U11" s="15" t="s">
         <v>72</v>
@@ -18407,16 +18443,16 @@
         <v>73</v>
       </c>
       <c r="X11" s="9" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="Y11" s="12" t="n">
-        <v>0</v>
+        <v>325.38</v>
       </c>
       <c r="Z11" s="12" t="n">
-        <v>5879.02</v>
+        <v>5005.88</v>
       </c>
       <c r="AA11" s="12" t="n">
-        <v>411.53</v>
+        <v>350.41</v>
       </c>
       <c r="AB11" s="12" t="n">
         <v>0</v>
@@ -18482,7 +18518,7 @@
         <v>74</v>
       </c>
       <c r="AW11" s="14" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AX11" s="10" t="s">
         <v>77</v>
@@ -18521,7 +18557,7 @@
         <v>78</v>
       </c>
       <c r="BJ11" s="9" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="BK11" s="9" t="s">
         <v>75</v>
@@ -18535,34 +18571,34 @@
     </row>
     <row r="12" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="n">
-        <v>305560</v>
+        <v>305681</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
       <c r="F12" s="9" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="K12" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>3121.47</v>
+        <v>1945.98</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>0</v>
@@ -18571,22 +18607,22 @@
         <v>1</v>
       </c>
       <c r="O12" s="12" t="n">
-        <v>3121.47</v>
+        <v>1945.98</v>
       </c>
       <c r="P12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" s="13" t="n">
-        <v>0.031059</v>
+        <v>0.004946</v>
       </c>
       <c r="R12" s="12" t="n">
-        <v>5.54</v>
+        <v>1.15</v>
       </c>
       <c r="S12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T12" s="14" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="U12" s="15" t="s">
         <v>72</v>
@@ -18598,16 +18634,16 @@
         <v>73</v>
       </c>
       <c r="X12" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Y12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z12" s="12" t="n">
-        <v>3121.47</v>
+        <v>1945.98</v>
       </c>
       <c r="AA12" s="12" t="n">
-        <v>218.5</v>
+        <v>136.22</v>
       </c>
       <c r="AB12" s="12" t="n">
         <v>0</v>
@@ -18673,7 +18709,7 @@
         <v>74</v>
       </c>
       <c r="AW12" s="14" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AX12" s="10" t="s">
         <v>77</v>
@@ -18712,7 +18748,7 @@
         <v>78</v>
       </c>
       <c r="BJ12" s="9" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="BK12" s="9" t="s">
         <v>75</v>
@@ -18726,25 +18762,25 @@
     </row>
     <row r="13" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="n">
-        <v>305561</v>
+        <v>305724</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
       <c r="F13" s="9" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J13" s="9" t="s">
         <v>114</v>
@@ -18753,7 +18789,7 @@
         <v>70</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>5331.26</v>
+        <v>1674.18</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>0</v>
@@ -18762,22 +18798,22 @@
         <v>1</v>
       </c>
       <c r="O13" s="12" t="n">
-        <v>5005.88</v>
+        <v>1674.18</v>
       </c>
       <c r="P13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q13" s="13" t="n">
-        <v>0.055816</v>
+        <v>0.003916</v>
       </c>
       <c r="R13" s="12" t="n">
-        <v>7.12</v>
+        <v>0.97</v>
       </c>
       <c r="S13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T13" s="14" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="U13" s="15" t="s">
         <v>72</v>
@@ -18789,16 +18825,16 @@
         <v>73</v>
       </c>
       <c r="X13" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Y13" s="12" t="n">
-        <v>325.38</v>
+        <v>0</v>
       </c>
       <c r="Z13" s="12" t="n">
-        <v>5005.88</v>
+        <v>1674.18</v>
       </c>
       <c r="AA13" s="12" t="n">
-        <v>350.41</v>
+        <v>117.19</v>
       </c>
       <c r="AB13" s="12" t="n">
         <v>0</v>
@@ -18864,7 +18900,7 @@
         <v>74</v>
       </c>
       <c r="AW13" s="14" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AX13" s="10" t="s">
         <v>77</v>
@@ -18903,7 +18939,7 @@
         <v>78</v>
       </c>
       <c r="BJ13" s="9" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="BK13" s="9" t="s">
         <v>75</v>
@@ -18917,58 +18953,58 @@
     </row>
     <row r="14" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="n">
-        <v>305681</v>
+        <v>305725</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>86</v>
+        <v>117</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
       <c r="F14" s="9" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>121</v>
+        <v>96</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="K14" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>1945.98</v>
+        <v>10012.8</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O14" s="12" t="n">
-        <v>1945.98</v>
+        <v>10012.8</v>
       </c>
       <c r="P14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q14" s="13" t="n">
-        <v>0.004946</v>
+        <v>0.750038</v>
       </c>
       <c r="R14" s="12" t="n">
-        <v>1.15</v>
+        <v>38</v>
       </c>
       <c r="S14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T14" s="14" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="U14" s="15" t="s">
         <v>72</v>
@@ -18980,16 +19016,16 @@
         <v>73</v>
       </c>
       <c r="X14" s="9" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="Y14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z14" s="12" t="n">
-        <v>1945.98</v>
+        <v>10012.8</v>
       </c>
       <c r="AA14" s="12" t="n">
-        <v>136.22</v>
+        <v>400.51</v>
       </c>
       <c r="AB14" s="12" t="n">
         <v>0</v>
@@ -19055,7 +19091,7 @@
         <v>74</v>
       </c>
       <c r="AW14" s="14" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AX14" s="10" t="s">
         <v>77</v>
@@ -19094,7 +19130,7 @@
         <v>78</v>
       </c>
       <c r="BJ14" s="9" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="BK14" s="9" t="s">
         <v>75</v>
@@ -19108,58 +19144,58 @@
     </row>
     <row r="15" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="n">
-        <v>305724</v>
+        <v>305731</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
       <c r="F15" s="9" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="K15" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>1674.18</v>
+        <v>6247.73</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O15" s="12" t="n">
-        <v>1674.18</v>
+        <v>6247.73</v>
       </c>
       <c r="P15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q15" s="13" t="n">
-        <v>0.003916</v>
+        <v>0.030808</v>
       </c>
       <c r="R15" s="12" t="n">
-        <v>0.97</v>
+        <v>6.05</v>
       </c>
       <c r="S15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T15" s="14" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="U15" s="15" t="s">
         <v>72</v>
@@ -19171,16 +19207,16 @@
         <v>73</v>
       </c>
       <c r="X15" s="9" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="Y15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z15" s="12" t="n">
-        <v>1674.18</v>
+        <v>6247.73</v>
       </c>
       <c r="AA15" s="12" t="n">
-        <v>117.19</v>
+        <v>437.34</v>
       </c>
       <c r="AB15" s="12" t="n">
         <v>0</v>
@@ -19246,7 +19282,7 @@
         <v>74</v>
       </c>
       <c r="AW15" s="14" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AX15" s="10" t="s">
         <v>77</v>
@@ -19285,7 +19321,7 @@
         <v>78</v>
       </c>
       <c r="BJ15" s="9" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="BK15" s="9" t="s">
         <v>75</v>
@@ -19299,34 +19335,34 @@
     </row>
     <row r="16" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="n">
-        <v>305725</v>
+        <v>305778</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
       <c r="F16" s="9" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="K16" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>10012.8</v>
+        <v>834.78</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>0</v>
@@ -19335,43 +19371,43 @@
         <v>2</v>
       </c>
       <c r="O16" s="12" t="n">
-        <v>10012.8</v>
+        <v>730</v>
       </c>
       <c r="P16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q16" s="13" t="n">
-        <v>0.750038</v>
+        <v>0</v>
       </c>
       <c r="R16" s="12" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="S16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T16" s="14" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="U16" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V16" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="W16" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X16" s="9" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="Y16" s="12" t="n">
-        <v>0</v>
+        <v>104.78</v>
       </c>
       <c r="Z16" s="12" t="n">
-        <v>10012.8</v>
+        <v>730</v>
       </c>
       <c r="AA16" s="12" t="n">
-        <v>400.51</v>
+        <v>51.1</v>
       </c>
       <c r="AB16" s="12" t="n">
         <v>0</v>
@@ -19437,7 +19473,7 @@
         <v>74</v>
       </c>
       <c r="AW16" s="14" t="s">
-        <v>83</v>
+        <v>128</v>
       </c>
       <c r="AX16" s="10" t="s">
         <v>77</v>
@@ -19476,7 +19512,7 @@
         <v>78</v>
       </c>
       <c r="BJ16" s="9" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="BK16" s="9" t="s">
         <v>75</v>
@@ -19490,58 +19526,58 @@
     </row>
     <row r="17" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="n">
-        <v>305731</v>
+        <v>305821</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>94</v>
+        <v>64</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
       <c r="F17" s="9" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="G17" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="K17" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>6247.73</v>
+        <v>4462.34</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O17" s="12" t="n">
-        <v>6247.73</v>
+        <v>4462.34</v>
       </c>
       <c r="P17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q17" s="13" t="n">
-        <v>0.030808</v>
+        <v>0.010272</v>
       </c>
       <c r="R17" s="12" t="n">
-        <v>6.05</v>
+        <v>3.7</v>
       </c>
       <c r="S17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T17" s="14" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="U17" s="15" t="s">
         <v>72</v>
@@ -19553,16 +19589,16 @@
         <v>73</v>
       </c>
       <c r="X17" s="9" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="Y17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z17" s="12" t="n">
-        <v>6247.73</v>
+        <v>4462.34</v>
       </c>
       <c r="AA17" s="12" t="n">
-        <v>437.34</v>
+        <v>312.36</v>
       </c>
       <c r="AB17" s="12" t="n">
         <v>0</v>
@@ -19628,7 +19664,7 @@
         <v>74</v>
       </c>
       <c r="AW17" s="14" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AX17" s="10" t="s">
         <v>77</v>
@@ -19667,7 +19703,7 @@
         <v>78</v>
       </c>
       <c r="BJ17" s="9" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="BK17" s="9" t="s">
         <v>75</v>
@@ -19681,79 +19717,79 @@
     </row>
     <row r="18" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="n">
-        <v>305778</v>
+        <v>305822</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>136</v>
+        <v>64</v>
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
       <c r="F18" s="9" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="G18" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="K18" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>834.78</v>
+        <v>1464.23</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O18" s="12" t="n">
-        <v>730</v>
+        <v>1464.23</v>
       </c>
       <c r="P18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q18" s="13" t="n">
-        <v>0</v>
+        <v>0.002473</v>
       </c>
       <c r="R18" s="12" t="n">
-        <v>0</v>
+        <v>0.77</v>
       </c>
       <c r="S18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T18" s="14" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="U18" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V18" s="12" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="W18" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X18" s="9" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="Y18" s="12" t="n">
-        <v>104.78</v>
+        <v>0</v>
       </c>
       <c r="Z18" s="12" t="n">
-        <v>730</v>
+        <v>1464.23</v>
       </c>
       <c r="AA18" s="12" t="n">
-        <v>51.1</v>
+        <v>102.5</v>
       </c>
       <c r="AB18" s="12" t="n">
         <v>0</v>
@@ -19858,7 +19894,7 @@
         <v>78</v>
       </c>
       <c r="BJ18" s="9" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="BK18" s="9" t="s">
         <v>75</v>
@@ -19872,34 +19908,34 @@
     </row>
     <row r="19" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="n">
-        <v>305821</v>
+        <v>305829</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
       <c r="F19" s="9" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>138</v>
+        <v>109</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>142</v>
+        <v>110</v>
       </c>
       <c r="K19" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>4462.34</v>
+        <v>3019.02</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>0</v>
@@ -19908,22 +19944,22 @@
         <v>1</v>
       </c>
       <c r="O19" s="12" t="n">
-        <v>4462.34</v>
+        <v>3019.02</v>
       </c>
       <c r="P19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q19" s="13" t="n">
-        <v>0.010272</v>
+        <v>0.004946</v>
       </c>
       <c r="R19" s="12" t="n">
-        <v>3.7</v>
+        <v>1.53</v>
       </c>
       <c r="S19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T19" s="14" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="U19" s="15" t="s">
         <v>72</v>
@@ -19935,16 +19971,16 @@
         <v>73</v>
       </c>
       <c r="X19" s="9" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="Y19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z19" s="12" t="n">
-        <v>4462.34</v>
+        <v>3019.02</v>
       </c>
       <c r="AA19" s="12" t="n">
-        <v>312.36</v>
+        <v>211.33</v>
       </c>
       <c r="AB19" s="12" t="n">
         <v>0</v>
@@ -20010,7 +20046,7 @@
         <v>74</v>
       </c>
       <c r="AW19" s="14" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AX19" s="10" t="s">
         <v>77</v>
@@ -20049,7 +20085,7 @@
         <v>78</v>
       </c>
       <c r="BJ19" s="9" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="BK19" s="9" t="s">
         <v>75</v>
@@ -20063,34 +20099,34 @@
     </row>
     <row r="20" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="n">
-        <v>305822</v>
+        <v>305942</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
       <c r="F20" s="9" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>138</v>
+        <v>109</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>142</v>
+        <v>78</v>
       </c>
       <c r="K20" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>1464.23</v>
+        <v>42.44</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>0</v>
@@ -20099,43 +20135,43 @@
         <v>1</v>
       </c>
       <c r="O20" s="12" t="n">
-        <v>1464.23</v>
+        <v>39.85</v>
       </c>
       <c r="P20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q20" s="13" t="n">
-        <v>0.002473</v>
+        <v>0.002284</v>
       </c>
       <c r="R20" s="12" t="n">
-        <v>0.77</v>
+        <v>0.8</v>
       </c>
       <c r="S20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T20" s="14" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="U20" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V20" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W20" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X20" s="9" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="Y20" s="12" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Z20" s="12" t="n">
-        <v>1464.23</v>
+        <v>39.85</v>
       </c>
       <c r="AA20" s="12" t="n">
-        <v>102.5</v>
+        <v>1.59</v>
       </c>
       <c r="AB20" s="12" t="n">
         <v>0</v>
@@ -20201,10 +20237,10 @@
         <v>74</v>
       </c>
       <c r="AW20" s="14" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AX20" s="10" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AY20" s="14" t="s">
         <v>75</v>
@@ -20240,7 +20276,7 @@
         <v>78</v>
       </c>
       <c r="BJ20" s="9" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="BK20" s="9" t="s">
         <v>75</v>
@@ -20254,34 +20290,34 @@
     </row>
     <row r="21" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="n">
-        <v>305829</v>
+        <v>305957</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
       <c r="F21" s="9" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>122</v>
+        <v>78</v>
       </c>
       <c r="K21" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>3019.02</v>
+        <v>126.7</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>0</v>
@@ -20290,43 +20326,43 @@
         <v>1</v>
       </c>
       <c r="O21" s="12" t="n">
-        <v>3019.02</v>
+        <v>118.97</v>
       </c>
       <c r="P21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q21" s="13" t="n">
-        <v>0.004946</v>
+        <v>0.001512</v>
       </c>
       <c r="R21" s="12" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="S21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T21" s="14" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="U21" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V21" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W21" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X21" s="9" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="Y21" s="12" t="n">
-        <v>0</v>
+        <v>7.73</v>
       </c>
       <c r="Z21" s="12" t="n">
-        <v>3019.02</v>
+        <v>118.97</v>
       </c>
       <c r="AA21" s="12" t="n">
-        <v>211.33</v>
+        <v>4.76</v>
       </c>
       <c r="AB21" s="12" t="n">
         <v>0</v>
@@ -20392,10 +20428,10 @@
         <v>74</v>
       </c>
       <c r="AW21" s="14" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AX21" s="10" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AY21" s="14" t="s">
         <v>75</v>
@@ -20431,7 +20467,7 @@
         <v>78</v>
       </c>
       <c r="BJ21" s="9" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="BK21" s="9" t="s">
         <v>75</v>
@@ -20445,25 +20481,25 @@
     </row>
     <row r="22" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="n">
-        <v>305942</v>
+        <v>305966</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
       <c r="F22" s="9" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="J22" s="9" t="s">
         <v>78</v>
@@ -20472,31 +20508,31 @@
         <v>70</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>42.44</v>
+        <v>290.09</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O22" s="12" t="n">
-        <v>39.85</v>
+        <v>272.38</v>
       </c>
       <c r="P22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q22" s="13" t="n">
-        <v>0.002284</v>
+        <v>0.003202</v>
       </c>
       <c r="R22" s="12" t="n">
-        <v>0.8</v>
+        <v>1.93</v>
       </c>
       <c r="S22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T22" s="14" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="U22" s="15" t="s">
         <v>72</v>
@@ -20508,16 +20544,16 @@
         <v>73</v>
       </c>
       <c r="X22" s="9" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="Y22" s="12" t="n">
-        <v>2.59</v>
+        <v>17.71</v>
       </c>
       <c r="Z22" s="12" t="n">
-        <v>39.85</v>
+        <v>272.38</v>
       </c>
       <c r="AA22" s="12" t="n">
-        <v>1.59</v>
+        <v>10.89</v>
       </c>
       <c r="AB22" s="12" t="n">
         <v>0</v>
@@ -20583,10 +20619,10 @@
         <v>74</v>
       </c>
       <c r="AW22" s="14" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AX22" s="10" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="AY22" s="14" t="s">
         <v>75</v>
@@ -20622,7 +20658,7 @@
         <v>78</v>
       </c>
       <c r="BJ22" s="9" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="BK22" s="9" t="s">
         <v>75</v>
@@ -20636,34 +20672,34 @@
     </row>
     <row r="23" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="n">
-        <v>305957</v>
+        <v>305994</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>94</v>
+        <v>64</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="9" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="G23" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>152</v>
+        <v>109</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="K23" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>126.7</v>
+        <v>2583.52</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>0</v>
@@ -20672,43 +20708,43 @@
         <v>1</v>
       </c>
       <c r="O23" s="12" t="n">
-        <v>118.97</v>
+        <v>2583.52</v>
       </c>
       <c r="P23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q23" s="13" t="n">
-        <v>0.001512</v>
+        <v>0.007527</v>
       </c>
       <c r="R23" s="12" t="n">
-        <v>1.58</v>
+        <v>1.95</v>
       </c>
       <c r="S23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T23" s="14" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="U23" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V23" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W23" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X23" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Y23" s="12" t="n">
-        <v>7.73</v>
+        <v>0</v>
       </c>
       <c r="Z23" s="12" t="n">
-        <v>118.97</v>
+        <v>2583.52</v>
       </c>
       <c r="AA23" s="12" t="n">
-        <v>4.76</v>
+        <v>180.85</v>
       </c>
       <c r="AB23" s="12" t="n">
         <v>0</v>
@@ -20774,10 +20810,10 @@
         <v>74</v>
       </c>
       <c r="AW23" s="14" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AX23" s="10" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AY23" s="14" t="s">
         <v>75</v>
@@ -20813,7 +20849,7 @@
         <v>78</v>
       </c>
       <c r="BJ23" s="9" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="BK23" s="9" t="s">
         <v>75</v>
@@ -20827,79 +20863,79 @@
     </row>
     <row r="24" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="n">
-        <v>305966</v>
+        <v>306001</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>94</v>
+        <v>64</v>
       </c>
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
       <c r="F24" s="9" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="G24" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="K24" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>290.09</v>
+        <v>1181.41</v>
       </c>
       <c r="M24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O24" s="12" t="n">
-        <v>272.38</v>
+        <v>1181.41</v>
       </c>
       <c r="P24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q24" s="13" t="n">
-        <v>0.003202</v>
+        <v>0.000412</v>
       </c>
       <c r="R24" s="12" t="n">
-        <v>1.93</v>
+        <v>0.71</v>
       </c>
       <c r="S24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T24" s="14" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="U24" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V24" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W24" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X24" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Y24" s="12" t="n">
-        <v>17.71</v>
+        <v>0</v>
       </c>
       <c r="Z24" s="12" t="n">
-        <v>272.38</v>
+        <v>1181.41</v>
       </c>
       <c r="AA24" s="12" t="n">
-        <v>10.89</v>
+        <v>82.7</v>
       </c>
       <c r="AB24" s="12" t="n">
         <v>0</v>
@@ -20965,10 +21001,10 @@
         <v>74</v>
       </c>
       <c r="AW24" s="14" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AX24" s="10" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AY24" s="14" t="s">
         <v>75</v>
@@ -21004,7 +21040,7 @@
         <v>78</v>
       </c>
       <c r="BJ24" s="9" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="BK24" s="9" t="s">
         <v>75</v>
@@ -21018,34 +21054,34 @@
     </row>
     <row r="25" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="n">
-        <v>305994</v>
+        <v>306005</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>86</v>
+        <v>159</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="G25" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="I25" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="J25" s="9" t="s">
         <v>161</v>
-      </c>
-      <c r="G25" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="H25" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="I25" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="J25" s="9" t="s">
-        <v>122</v>
       </c>
       <c r="K25" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>2583.52</v>
+        <v>861.88</v>
       </c>
       <c r="M25" s="12" t="n">
         <v>0</v>
@@ -21054,43 +21090,43 @@
         <v>1</v>
       </c>
       <c r="O25" s="12" t="n">
-        <v>2583.52</v>
+        <v>861.88</v>
       </c>
       <c r="P25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q25" s="13" t="n">
-        <v>0.007527</v>
+        <v>0.073796</v>
       </c>
       <c r="R25" s="12" t="n">
-        <v>1.95</v>
+        <v>43.13</v>
       </c>
       <c r="S25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T25" s="14" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="U25" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V25" s="12" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="W25" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X25" s="9" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="Y25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z25" s="12" t="n">
-        <v>2583.52</v>
+        <v>861.88</v>
       </c>
       <c r="AA25" s="12" t="n">
-        <v>180.85</v>
+        <v>60.33</v>
       </c>
       <c r="AB25" s="12" t="n">
         <v>0</v>
@@ -21156,7 +21192,7 @@
         <v>74</v>
       </c>
       <c r="AW25" s="14" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AX25" s="10" t="s">
         <v>77</v>
@@ -21195,7 +21231,7 @@
         <v>78</v>
       </c>
       <c r="BJ25" s="9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="BK25" s="9" t="s">
         <v>75</v>
@@ -21209,10 +21245,10 @@
     </row>
     <row r="26" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="n">
-        <v>306001</v>
+        <v>306150</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>86</v>
+        <v>164</v>
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
@@ -21221,46 +21257,46 @@
         <v>165</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H26" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="J26" s="9" t="s">
         <v>166</v>
-      </c>
-      <c r="I26" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="J26" s="9" t="s">
-        <v>167</v>
       </c>
       <c r="K26" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>1181.41</v>
+        <v>2070.21</v>
       </c>
       <c r="M26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O26" s="12" t="n">
-        <v>1181.41</v>
+        <v>1970.21</v>
       </c>
       <c r="P26" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q26" s="13" t="n">
-        <v>0.000412</v>
+        <v>0</v>
       </c>
       <c r="R26" s="12" t="n">
-        <v>0.71</v>
+        <v>4.15</v>
       </c>
       <c r="S26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T26" s="14" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="U26" s="15" t="s">
         <v>72</v>
@@ -21272,16 +21308,16 @@
         <v>73</v>
       </c>
       <c r="X26" s="9" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="Y26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z26" s="12" t="n">
-        <v>1181.41</v>
+        <v>2070.21</v>
       </c>
       <c r="AA26" s="12" t="n">
-        <v>82.7</v>
+        <v>144.92</v>
       </c>
       <c r="AB26" s="12" t="n">
         <v>0</v>
@@ -21347,7 +21383,7 @@
         <v>74</v>
       </c>
       <c r="AW26" s="14" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AX26" s="10" t="s">
         <v>77</v>
@@ -21386,7 +21422,7 @@
         <v>78</v>
       </c>
       <c r="BJ26" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="BK26" s="9" t="s">
         <v>75</v>
@@ -21400,79 +21436,79 @@
     </row>
     <row r="27" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="n">
-        <v>306005</v>
+        <v>306157</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>138</v>
+        <v>109</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="J27" s="9" t="s">
-        <v>172</v>
+        <v>110</v>
       </c>
       <c r="K27" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>861.88</v>
+        <v>11204.49</v>
       </c>
       <c r="M27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O27" s="12" t="n">
-        <v>861.88</v>
+        <v>10131.65</v>
       </c>
       <c r="P27" s="12" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="Q27" s="13" t="n">
-        <v>0.073796</v>
+        <v>0.02398</v>
       </c>
       <c r="R27" s="12" t="n">
-        <v>43.13</v>
+        <v>14.4</v>
       </c>
       <c r="S27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T27" s="14" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="U27" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V27" s="12" t="n">
-        <v>56</v>
+        <v>55.79</v>
       </c>
       <c r="W27" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X27" s="9" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="Y27" s="12" t="n">
-        <v>0</v>
+        <v>987.84</v>
       </c>
       <c r="Z27" s="12" t="n">
-        <v>861.88</v>
+        <v>10216.65</v>
       </c>
       <c r="AA27" s="12" t="n">
-        <v>60.33</v>
+        <v>408.68</v>
       </c>
       <c r="AB27" s="12" t="n">
         <v>0</v>
@@ -21538,7 +21574,7 @@
         <v>74</v>
       </c>
       <c r="AW27" s="14" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AX27" s="10" t="s">
         <v>77</v>
@@ -21577,7 +21613,7 @@
         <v>78</v>
       </c>
       <c r="BJ27" s="9" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="BK27" s="9" t="s">
         <v>75</v>
@@ -21591,79 +21627,79 @@
     </row>
     <row r="28" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="n">
-        <v>306150</v>
+        <v>306173</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="K28" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>2070.21</v>
+        <v>3730.39</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O28" s="12" t="n">
-        <v>1970.21</v>
+        <v>3730.39</v>
       </c>
       <c r="P28" s="12" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q28" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R28" s="12" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="S28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T28" s="14" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="U28" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V28" s="12" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="W28" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X28" s="9" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="Y28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z28" s="12" t="n">
-        <v>2070.21</v>
+        <v>3730.39</v>
       </c>
       <c r="AA28" s="12" t="n">
-        <v>144.92</v>
+        <v>261.14</v>
       </c>
       <c r="AB28" s="12" t="n">
         <v>0</v>
@@ -21729,7 +21765,7 @@
         <v>74</v>
       </c>
       <c r="AW28" s="14" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AX28" s="10" t="s">
         <v>77</v>
@@ -21768,7 +21804,7 @@
         <v>78</v>
       </c>
       <c r="BJ28" s="9" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="BK28" s="9" t="s">
         <v>75</v>
@@ -21782,79 +21818,79 @@
     </row>
     <row r="29" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="n">
-        <v>306157</v>
+        <v>306272</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
       <c r="F29" s="9" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>121</v>
+        <v>178</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>122</v>
+        <v>180</v>
       </c>
       <c r="K29" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>11204.49</v>
+        <v>14916.19</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>0</v>
+        <v>3433.93</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O29" s="12" t="n">
-        <v>10131.65</v>
+        <v>17025</v>
       </c>
       <c r="P29" s="12" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="Q29" s="13" t="n">
-        <v>0.02398</v>
+        <v>0</v>
       </c>
       <c r="R29" s="12" t="n">
-        <v>14.4</v>
+        <v>0</v>
       </c>
       <c r="S29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T29" s="14" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="U29" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V29" s="12" t="n">
-        <v>55.79</v>
+        <v>82</v>
       </c>
       <c r="W29" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X29" s="9" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="Y29" s="12" t="n">
-        <v>987.84</v>
+        <v>1325.12</v>
       </c>
       <c r="Z29" s="12" t="n">
-        <v>10216.65</v>
+        <v>13591.07</v>
       </c>
       <c r="AA29" s="12" t="n">
-        <v>408.68</v>
+        <v>543.65</v>
       </c>
       <c r="AB29" s="12" t="n">
         <v>0</v>
@@ -21920,7 +21956,7 @@
         <v>74</v>
       </c>
       <c r="AW29" s="14" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AX29" s="10" t="s">
         <v>77</v>
@@ -21959,7 +21995,7 @@
         <v>78</v>
       </c>
       <c r="BJ29" s="9" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="BK29" s="9" t="s">
         <v>75</v>
@@ -21973,52 +22009,52 @@
     </row>
     <row r="30" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="n">
-        <v>306173</v>
+        <v>306327</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>175</v>
+        <v>64</v>
       </c>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
       <c r="F30" s="9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G30" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="K30" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>3730.39</v>
+        <v>10714.13</v>
       </c>
       <c r="M30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O30" s="12" t="n">
-        <v>3730.39</v>
+        <v>10714.13</v>
       </c>
       <c r="P30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q30" s="13" t="n">
-        <v>0</v>
+        <v>0.020976</v>
       </c>
       <c r="R30" s="12" t="n">
-        <v>0</v>
+        <v>6.72</v>
       </c>
       <c r="S30" s="12" t="n">
         <v>0</v>
@@ -22030,22 +22066,22 @@
         <v>72</v>
       </c>
       <c r="V30" s="12" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="W30" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X30" s="9" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="Y30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z30" s="12" t="n">
-        <v>3730.39</v>
+        <v>10714.13</v>
       </c>
       <c r="AA30" s="12" t="n">
-        <v>261.14</v>
+        <v>749.99</v>
       </c>
       <c r="AB30" s="12" t="n">
         <v>0</v>
@@ -22111,7 +22147,7 @@
         <v>74</v>
       </c>
       <c r="AW30" s="14" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AX30" s="10" t="s">
         <v>77</v>
@@ -22163,534 +22199,900 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="4"/>
+      <c r="A31" s="8" t="n">
+        <v>306329</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="G31" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H31" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="I31" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="J31" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="K31" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L31" s="12" t="n">
+        <v>891.38</v>
+      </c>
+      <c r="M31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O31" s="12" t="n">
+        <v>891.38</v>
+      </c>
+      <c r="P31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="13" t="n">
+        <v>0.003922</v>
+      </c>
+      <c r="R31" s="12" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="S31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="U31" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V31" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="W31" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X31" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="Y31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="12" t="n">
+        <v>891.38</v>
+      </c>
+      <c r="AA31" s="12" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="AB31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ31" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM31" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN31" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO31" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP31" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ31" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR31" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS31" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT31" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU31" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV31" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW31" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX31" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY31" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ31" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA31" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB31" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC31" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD31" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE31" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF31" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG31" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH31" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI31" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ31" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="BK31" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL31" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM31" s="16" t="s">
+        <v>80</v>
+      </c>
     </row>
-    <row r="32" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="17" t="s">
-        <v>187</v>
-      </c>
-      <c r="B32" s="17"/>
-      <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
-      <c r="G32" s="17"/>
-      <c r="H32" s="17"/>
-      <c r="I32" s="17"/>
-      <c r="J32" s="17"/>
-      <c r="K32" s="17"/>
-      <c r="L32" s="17"/>
-      <c r="M32" s="17"/>
-      <c r="N32" s="17"/>
-      <c r="O32" s="17"/>
-      <c r="P32" s="17"/>
-      <c r="Q32" s="17"/>
-      <c r="R32" s="17"/>
-      <c r="S32" s="17"/>
-      <c r="T32" s="17"/>
-      <c r="U32" s="17"/>
-      <c r="V32" s="17"/>
+    <row r="32" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="8" t="n">
+        <v>306335</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="G32" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H32" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="I32" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="J32" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="K32" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L32" s="12" t="n">
+        <v>1593.54</v>
+      </c>
+      <c r="M32" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O32" s="12" t="n">
+        <v>1593.54</v>
+      </c>
+      <c r="P32" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="13" t="n">
+        <v>0.005136</v>
+      </c>
+      <c r="R32" s="12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S32" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="U32" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V32" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="W32" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X32" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="Y32" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="12" t="n">
+        <v>1593.54</v>
+      </c>
+      <c r="AA32" s="12" t="n">
+        <v>111.55</v>
+      </c>
+      <c r="AB32" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI32" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK32" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL32" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM32" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN32" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO32" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP32" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ32" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR32" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS32" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT32" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU32" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV32" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW32" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX32" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY32" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ32" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA32" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB32" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC32" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD32" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE32" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF32" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG32" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH32" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI32" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ32" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="BK32" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL32" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM32" s="16" t="s">
+        <v>80</v>
+      </c>
     </row>
-    <row r="33" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="18" t="s">
-        <v>188</v>
-      </c>
-      <c r="B33" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C33" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D33" s="18" t="s">
-        <v>189</v>
-      </c>
-      <c r="E33" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F33" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="G33" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="H33" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="I33" s="18" t="s">
-        <v>190</v>
-      </c>
-      <c r="J33" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="K33" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="L33" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="M33" s="18" t="s">
-        <v>191</v>
-      </c>
-      <c r="N33" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="O33" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="P33" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q33" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="R33" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="S33" s="18" t="s">
-        <v>192</v>
-      </c>
-      <c r="T33" s="18" t="s">
-        <v>193</v>
-      </c>
-      <c r="U33" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="V33" s="18" t="s">
-        <v>37</v>
+    <row r="33" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="8" t="n">
+        <v>306338</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="G33" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="H33" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="I33" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="J33" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K33" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L33" s="12" t="n">
+        <v>900.38</v>
+      </c>
+      <c r="M33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="O33" s="12" t="n">
+        <v>900.38</v>
+      </c>
+      <c r="P33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="U33" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X33" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="Y33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="12" t="n">
+        <v>900.38</v>
+      </c>
+      <c r="AA33" s="12" t="n">
+        <v>36.02</v>
+      </c>
+      <c r="AB33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ33" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM33" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN33" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO33" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP33" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ33" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR33" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS33" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT33" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU33" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV33" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW33" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX33" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="AY33" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ33" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA33" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB33" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC33" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD33" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE33" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF33" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG33" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH33" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI33" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ33" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="BK33" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL33" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM33" s="16" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="19" t="n">
-        <v>26</v>
-      </c>
-      <c r="B34" s="19" t="n">
-        <v>5811.05</v>
-      </c>
-      <c r="C34" s="19" t="n">
-        <v>185</v>
-      </c>
-      <c r="D34" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" s="19" t="n">
-        <v>4196.05</v>
-      </c>
-      <c r="F34" s="19" t="n">
-        <v>99158.03</v>
-      </c>
-      <c r="G34" s="19" t="n">
-        <v>5368.15</v>
-      </c>
-      <c r="H34" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" s="19" t="n">
-        <v>103354.08</v>
-      </c>
-      <c r="L34" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" s="20" t="n">
-        <v>1.751798</v>
-      </c>
-      <c r="S34" s="19" t="n">
-        <v>104784.08</v>
-      </c>
-      <c r="T34" s="19" t="n">
-        <v>103354.08</v>
-      </c>
-      <c r="U34" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" s="19" t="n">
-        <v>0</v>
-      </c>
+      <c r="A34" s="4"/>
     </row>
     <row r="35" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="B35" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C35" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="D35" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E35" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="F35" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="G35" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="H35" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="I35" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="J35" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="K35" s="18" t="s">
-        <v>194</v>
-      </c>
-      <c r="L35" s="18" t="s">
-        <v>195</v>
-      </c>
-      <c r="M35" s="18" t="s">
-        <v>196</v>
-      </c>
+      <c r="A35" s="17" t="s">
+        <v>199</v>
+      </c>
+      <c r="B35" s="17"/>
+      <c r="C35" s="17"/>
+      <c r="D35" s="17"/>
+      <c r="E35" s="17"/>
+      <c r="F35" s="17"/>
+      <c r="G35" s="17"/>
+      <c r="H35" s="17"/>
+      <c r="I35" s="17"/>
+      <c r="J35" s="17"/>
+      <c r="K35" s="17"/>
+      <c r="L35" s="17"/>
+      <c r="M35" s="17"/>
+      <c r="N35" s="17"/>
+      <c r="O35" s="17"/>
+      <c r="P35" s="17"/>
+      <c r="Q35" s="17"/>
+      <c r="R35" s="17"/>
+      <c r="S35" s="17"/>
+      <c r="T35" s="17"/>
+      <c r="U35" s="17"/>
+      <c r="V35" s="17"/>
     </row>
-    <row r="36" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="19" t="n">
-        <v>225.05</v>
-      </c>
-      <c r="B36" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C36" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" s="19" t="n">
-        <v>52.1</v>
-      </c>
-      <c r="E36" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" s="19" t="n">
-        <v>0</v>
+    <row r="36" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="18" t="s">
+        <v>200</v>
+      </c>
+      <c r="B36" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C36" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D36" s="18" t="s">
+        <v>201</v>
+      </c>
+      <c r="E36" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F36" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="G36" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H36" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="I36" s="18" t="s">
+        <v>202</v>
+      </c>
+      <c r="J36" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="K36" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="L36" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="M36" s="18" t="s">
+        <v>203</v>
+      </c>
+      <c r="N36" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="O36" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="P36" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q36" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="R36" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="S36" s="18" t="s">
+        <v>204</v>
+      </c>
+      <c r="T36" s="18" t="s">
+        <v>205</v>
+      </c>
+      <c r="U36" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="V36" s="18" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="4"/>
+      <c r="A37" s="19" t="n">
+        <v>29</v>
+      </c>
+      <c r="B37" s="19" t="n">
+        <v>3433.93</v>
+      </c>
+      <c r="C37" s="19" t="n">
+        <v>185</v>
+      </c>
+      <c r="D37" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="19" t="n">
+        <v>3117.14</v>
+      </c>
+      <c r="F37" s="19" t="n">
+        <v>102191.78</v>
+      </c>
+      <c r="G37" s="19" t="n">
+        <v>5885.52</v>
+      </c>
+      <c r="H37" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="19" t="n">
+        <v>105308.92</v>
+      </c>
+      <c r="L37" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" s="20" t="n">
+        <v>1.781832</v>
+      </c>
+      <c r="S37" s="19" t="n">
+        <v>105440.71</v>
+      </c>
+      <c r="T37" s="19" t="n">
+        <v>105308.92</v>
+      </c>
+      <c r="U37" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="21" t="s">
-        <v>197</v>
-      </c>
-      <c r="B38" s="21"/>
-      <c r="C38" s="21"/>
-      <c r="D38" s="21"/>
-      <c r="E38" s="21"/>
-      <c r="F38" s="21"/>
-      <c r="G38" s="21"/>
-      <c r="H38" s="21"/>
-      <c r="I38" s="21"/>
-      <c r="J38" s="21"/>
-      <c r="K38" s="21"/>
-      <c r="L38" s="21"/>
-      <c r="M38" s="21"/>
-      <c r="N38" s="21"/>
-      <c r="O38" s="21"/>
-      <c r="P38" s="21"/>
-      <c r="Q38" s="21"/>
-      <c r="R38" s="21"/>
-      <c r="S38" s="21"/>
-      <c r="T38" s="21"/>
-      <c r="U38" s="21"/>
-      <c r="V38" s="21"/>
-      <c r="W38" s="21"/>
-      <c r="X38" s="21"/>
-      <c r="Y38" s="21"/>
-      <c r="Z38" s="21"/>
-      <c r="AA38" s="21"/>
-      <c r="AB38" s="21"/>
-      <c r="AC38" s="21"/>
-      <c r="AD38" s="21"/>
-      <c r="AE38" s="21"/>
-      <c r="AF38" s="21"/>
-      <c r="AG38" s="21"/>
-      <c r="AH38" s="21"/>
-      <c r="AI38" s="21"/>
-      <c r="AJ38" s="21"/>
-      <c r="AK38" s="21"/>
-      <c r="AL38" s="21"/>
-      <c r="AM38" s="21"/>
-      <c r="AN38" s="21"/>
-      <c r="AO38" s="21"/>
-      <c r="AP38" s="21"/>
-      <c r="AQ38" s="21"/>
-      <c r="AR38" s="21"/>
-      <c r="AS38" s="21"/>
-      <c r="AT38" s="21"/>
-      <c r="AU38" s="21"/>
-      <c r="AV38" s="21"/>
-      <c r="AW38" s="21"/>
-      <c r="AX38" s="21"/>
-      <c r="AY38" s="21"/>
-      <c r="AZ38" s="21"/>
-      <c r="BA38" s="21"/>
-      <c r="BB38" s="21"/>
-      <c r="BC38" s="21"/>
-      <c r="BD38" s="21"/>
-      <c r="BE38" s="21"/>
-      <c r="BF38" s="21"/>
-      <c r="BG38" s="21"/>
-      <c r="BH38" s="21"/>
-      <c r="BI38" s="21"/>
-      <c r="BJ38" s="21"/>
-      <c r="BK38" s="21"/>
-      <c r="BL38" s="21"/>
-      <c r="BM38" s="21"/>
+      <c r="A38" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B38" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C38" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D38" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="E38" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="F38" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="G38" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="H38" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="I38" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="J38" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="K38" s="18" t="s">
+        <v>206</v>
+      </c>
+      <c r="L38" s="18" t="s">
+        <v>207</v>
+      </c>
+      <c r="M38" s="18" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
-      <c r="E39" s="4"/>
-      <c r="F39" s="4"/>
-      <c r="G39" s="4"/>
-      <c r="H39" s="4"/>
-      <c r="I39" s="4"/>
-      <c r="J39" s="4"/>
-      <c r="K39" s="4"/>
-      <c r="L39" s="4"/>
-      <c r="M39" s="4"/>
-      <c r="N39" s="4"/>
-      <c r="O39" s="4"/>
-      <c r="P39" s="4"/>
-      <c r="Q39" s="4"/>
-      <c r="R39" s="4"/>
-      <c r="S39" s="4"/>
-      <c r="T39" s="4"/>
-      <c r="U39" s="4"/>
-      <c r="V39" s="4"/>
-      <c r="W39" s="4"/>
-      <c r="X39" s="4"/>
-      <c r="Y39" s="4"/>
-      <c r="Z39" s="4"/>
-      <c r="AA39" s="4"/>
-      <c r="AB39" s="4"/>
-      <c r="AC39" s="4"/>
-      <c r="AD39" s="4"/>
-      <c r="AE39" s="4"/>
-      <c r="AF39" s="4"/>
-      <c r="AG39" s="4"/>
-      <c r="AH39" s="4"/>
-      <c r="AI39" s="4"/>
-      <c r="AJ39" s="4"/>
-      <c r="AK39" s="4"/>
-      <c r="AL39" s="4"/>
-      <c r="AM39" s="4"/>
-      <c r="AN39" s="4"/>
-      <c r="AO39" s="4"/>
-      <c r="AP39" s="4"/>
-      <c r="AQ39" s="4"/>
-      <c r="AR39" s="4"/>
-      <c r="AS39" s="4"/>
-      <c r="AT39" s="4"/>
-      <c r="AU39" s="4"/>
-      <c r="AV39" s="4"/>
-      <c r="AW39" s="4"/>
-      <c r="AX39" s="4"/>
-      <c r="AY39" s="4"/>
-      <c r="AZ39" s="4"/>
-      <c r="BA39" s="4"/>
-      <c r="BB39" s="4"/>
-      <c r="BC39" s="4"/>
-      <c r="BD39" s="4"/>
-      <c r="BE39" s="4"/>
-      <c r="BF39" s="4"/>
-      <c r="BG39" s="4"/>
-      <c r="BH39" s="4"/>
-      <c r="BI39" s="4"/>
-      <c r="BJ39" s="4"/>
-      <c r="BK39" s="4"/>
-      <c r="BL39" s="4"/>
-      <c r="BM39" s="4"/>
+      <c r="A39" s="19" t="n">
+        <v>228.27</v>
+      </c>
+      <c r="B39" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="19" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="E39" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="B40" s="4"/>
-      <c r="C40" s="4"/>
-      <c r="D40" s="4"/>
-      <c r="E40" s="4"/>
-      <c r="F40" s="4"/>
-      <c r="G40" s="4"/>
-      <c r="H40" s="4"/>
-      <c r="I40" s="4"/>
-      <c r="J40" s="4"/>
-      <c r="K40" s="4"/>
-      <c r="L40" s="4"/>
-      <c r="M40" s="4"/>
-      <c r="N40" s="4"/>
-      <c r="O40" s="4"/>
-      <c r="P40" s="4"/>
-      <c r="Q40" s="4"/>
-      <c r="R40" s="4"/>
-      <c r="S40" s="4"/>
-      <c r="T40" s="4"/>
-      <c r="U40" s="4"/>
-      <c r="V40" s="4"/>
-      <c r="W40" s="4"/>
-      <c r="X40" s="4"/>
-      <c r="Y40" s="4"/>
-      <c r="Z40" s="4"/>
-      <c r="AA40" s="4"/>
-      <c r="AB40" s="4"/>
-      <c r="AC40" s="4"/>
-      <c r="AD40" s="4"/>
-      <c r="AE40" s="4"/>
-      <c r="AF40" s="4"/>
-      <c r="AG40" s="4"/>
-      <c r="AH40" s="4"/>
-      <c r="AI40" s="4"/>
-      <c r="AJ40" s="4"/>
-      <c r="AK40" s="4"/>
-      <c r="AL40" s="4"/>
-      <c r="AM40" s="4"/>
-      <c r="AN40" s="4"/>
-      <c r="AO40" s="4"/>
-      <c r="AP40" s="4"/>
-      <c r="AQ40" s="4"/>
-      <c r="AR40" s="4"/>
-      <c r="AS40" s="4"/>
-      <c r="AT40" s="4"/>
-      <c r="AU40" s="4"/>
-      <c r="AV40" s="4"/>
-      <c r="AW40" s="4"/>
-      <c r="AX40" s="4"/>
-      <c r="AY40" s="4"/>
-      <c r="AZ40" s="4"/>
-      <c r="BA40" s="4"/>
-      <c r="BB40" s="4"/>
-      <c r="BC40" s="4"/>
-      <c r="BD40" s="4"/>
-      <c r="BE40" s="4"/>
-      <c r="BF40" s="4"/>
-      <c r="BG40" s="4"/>
-      <c r="BH40" s="4"/>
-      <c r="BI40" s="4"/>
-      <c r="BJ40" s="4"/>
-      <c r="BK40" s="4"/>
-      <c r="BL40" s="4"/>
-      <c r="BM40" s="4"/>
+      <c r="A40" s="4"/>
     </row>
-    <row r="41" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="B41" s="4"/>
-      <c r="C41" s="4"/>
-      <c r="D41" s="4"/>
-      <c r="E41" s="4"/>
-      <c r="F41" s="4"/>
-      <c r="G41" s="4"/>
-      <c r="H41" s="4"/>
-      <c r="I41" s="4"/>
-      <c r="J41" s="4"/>
-      <c r="K41" s="4"/>
-      <c r="L41" s="4"/>
-      <c r="M41" s="4"/>
-      <c r="N41" s="4"/>
-      <c r="O41" s="4"/>
-      <c r="P41" s="4"/>
-      <c r="Q41" s="4"/>
-      <c r="R41" s="4"/>
-      <c r="S41" s="4"/>
-      <c r="T41" s="4"/>
-      <c r="U41" s="4"/>
-      <c r="V41" s="4"/>
-      <c r="W41" s="4"/>
-      <c r="X41" s="4"/>
-      <c r="Y41" s="4"/>
-      <c r="Z41" s="4"/>
-      <c r="AA41" s="4"/>
-      <c r="AB41" s="4"/>
-      <c r="AC41" s="4"/>
-      <c r="AD41" s="4"/>
-      <c r="AE41" s="4"/>
-      <c r="AF41" s="4"/>
-      <c r="AG41" s="4"/>
-      <c r="AH41" s="4"/>
-      <c r="AI41" s="4"/>
-      <c r="AJ41" s="4"/>
-      <c r="AK41" s="4"/>
-      <c r="AL41" s="4"/>
-      <c r="AM41" s="4"/>
-      <c r="AN41" s="4"/>
-      <c r="AO41" s="4"/>
-      <c r="AP41" s="4"/>
-      <c r="AQ41" s="4"/>
-      <c r="AR41" s="4"/>
-      <c r="AS41" s="4"/>
-      <c r="AT41" s="4"/>
-      <c r="AU41" s="4"/>
-      <c r="AV41" s="4"/>
-      <c r="AW41" s="4"/>
-      <c r="AX41" s="4"/>
-      <c r="AY41" s="4"/>
-      <c r="AZ41" s="4"/>
-      <c r="BA41" s="4"/>
-      <c r="BB41" s="4"/>
-      <c r="BC41" s="4"/>
-      <c r="BD41" s="4"/>
-      <c r="BE41" s="4"/>
-      <c r="BF41" s="4"/>
-      <c r="BG41" s="4"/>
-      <c r="BH41" s="4"/>
-      <c r="BI41" s="4"/>
-      <c r="BJ41" s="4"/>
-      <c r="BK41" s="4"/>
-      <c r="BL41" s="4"/>
-      <c r="BM41" s="4"/>
+    <row r="41" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="21" t="s">
+        <v>209</v>
+      </c>
+      <c r="B41" s="21"/>
+      <c r="C41" s="21"/>
+      <c r="D41" s="21"/>
+      <c r="E41" s="21"/>
+      <c r="F41" s="21"/>
+      <c r="G41" s="21"/>
+      <c r="H41" s="21"/>
+      <c r="I41" s="21"/>
+      <c r="J41" s="21"/>
+      <c r="K41" s="21"/>
+      <c r="L41" s="21"/>
+      <c r="M41" s="21"/>
+      <c r="N41" s="21"/>
+      <c r="O41" s="21"/>
+      <c r="P41" s="21"/>
+      <c r="Q41" s="21"/>
+      <c r="R41" s="21"/>
+      <c r="S41" s="21"/>
+      <c r="T41" s="21"/>
+      <c r="U41" s="21"/>
+      <c r="V41" s="21"/>
+      <c r="W41" s="21"/>
+      <c r="X41" s="21"/>
+      <c r="Y41" s="21"/>
+      <c r="Z41" s="21"/>
+      <c r="AA41" s="21"/>
+      <c r="AB41" s="21"/>
+      <c r="AC41" s="21"/>
+      <c r="AD41" s="21"/>
+      <c r="AE41" s="21"/>
+      <c r="AF41" s="21"/>
+      <c r="AG41" s="21"/>
+      <c r="AH41" s="21"/>
+      <c r="AI41" s="21"/>
+      <c r="AJ41" s="21"/>
+      <c r="AK41" s="21"/>
+      <c r="AL41" s="21"/>
+      <c r="AM41" s="21"/>
+      <c r="AN41" s="21"/>
+      <c r="AO41" s="21"/>
+      <c r="AP41" s="21"/>
+      <c r="AQ41" s="21"/>
+      <c r="AR41" s="21"/>
+      <c r="AS41" s="21"/>
+      <c r="AT41" s="21"/>
+      <c r="AU41" s="21"/>
+      <c r="AV41" s="21"/>
+      <c r="AW41" s="21"/>
+      <c r="AX41" s="21"/>
+      <c r="AY41" s="21"/>
+      <c r="AZ41" s="21"/>
+      <c r="BA41" s="21"/>
+      <c r="BB41" s="21"/>
+      <c r="BC41" s="21"/>
+      <c r="BD41" s="21"/>
+      <c r="BE41" s="21"/>
+      <c r="BF41" s="21"/>
+      <c r="BG41" s="21"/>
+      <c r="BH41" s="21"/>
+      <c r="BI41" s="21"/>
+      <c r="BJ41" s="21"/>
+      <c r="BK41" s="21"/>
+      <c r="BL41" s="21"/>
+      <c r="BM41" s="21"/>
     </row>
     <row r="42" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="s">
-        <v>200</v>
+        <v>75</v>
       </c>
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
@@ -22759,7 +23161,7 @@
     </row>
     <row r="43" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="s">
-        <v>22</v>
+        <v>210</v>
       </c>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
@@ -22828,7 +23230,7 @@
     </row>
     <row r="44" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
@@ -22897,7 +23299,7 @@
     </row>
     <row r="45" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="4" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
@@ -22966,7 +23368,7 @@
     </row>
     <row r="46" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="4" t="s">
-        <v>203</v>
+        <v>22</v>
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
@@ -23035,7 +23437,7 @@
     </row>
     <row r="47" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
@@ -23104,7 +23506,7 @@
     </row>
     <row r="48" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="4" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
@@ -23171,8 +23573,215 @@
       <c r="BL48" s="4"/>
       <c r="BM48" s="4"/>
     </row>
+    <row r="49" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="B49" s="4"/>
+      <c r="C49" s="4"/>
+      <c r="D49" s="4"/>
+      <c r="E49" s="4"/>
+      <c r="F49" s="4"/>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+      <c r="K49" s="4"/>
+      <c r="L49" s="4"/>
+      <c r="M49" s="4"/>
+      <c r="N49" s="4"/>
+      <c r="O49" s="4"/>
+      <c r="P49" s="4"/>
+      <c r="Q49" s="4"/>
+      <c r="R49" s="4"/>
+      <c r="S49" s="4"/>
+      <c r="T49" s="4"/>
+      <c r="U49" s="4"/>
+      <c r="V49" s="4"/>
+      <c r="W49" s="4"/>
+      <c r="X49" s="4"/>
+      <c r="Y49" s="4"/>
+      <c r="Z49" s="4"/>
+      <c r="AA49" s="4"/>
+      <c r="AB49" s="4"/>
+      <c r="AC49" s="4"/>
+      <c r="AD49" s="4"/>
+      <c r="AE49" s="4"/>
+      <c r="AF49" s="4"/>
+      <c r="AG49" s="4"/>
+      <c r="AH49" s="4"/>
+      <c r="AI49" s="4"/>
+      <c r="AJ49" s="4"/>
+      <c r="AK49" s="4"/>
+      <c r="AL49" s="4"/>
+      <c r="AM49" s="4"/>
+      <c r="AN49" s="4"/>
+      <c r="AO49" s="4"/>
+      <c r="AP49" s="4"/>
+      <c r="AQ49" s="4"/>
+      <c r="AR49" s="4"/>
+      <c r="AS49" s="4"/>
+      <c r="AT49" s="4"/>
+      <c r="AU49" s="4"/>
+      <c r="AV49" s="4"/>
+      <c r="AW49" s="4"/>
+      <c r="AX49" s="4"/>
+      <c r="AY49" s="4"/>
+      <c r="AZ49" s="4"/>
+      <c r="BA49" s="4"/>
+      <c r="BB49" s="4"/>
+      <c r="BC49" s="4"/>
+      <c r="BD49" s="4"/>
+      <c r="BE49" s="4"/>
+      <c r="BF49" s="4"/>
+      <c r="BG49" s="4"/>
+      <c r="BH49" s="4"/>
+      <c r="BI49" s="4"/>
+      <c r="BJ49" s="4"/>
+      <c r="BK49" s="4"/>
+      <c r="BL49" s="4"/>
+      <c r="BM49" s="4"/>
+    </row>
+    <row r="50" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="B50" s="4"/>
+      <c r="C50" s="4"/>
+      <c r="D50" s="4"/>
+      <c r="E50" s="4"/>
+      <c r="F50" s="4"/>
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="K50" s="4"/>
+      <c r="L50" s="4"/>
+      <c r="M50" s="4"/>
+      <c r="N50" s="4"/>
+      <c r="O50" s="4"/>
+      <c r="P50" s="4"/>
+      <c r="Q50" s="4"/>
+      <c r="R50" s="4"/>
+      <c r="S50" s="4"/>
+      <c r="T50" s="4"/>
+      <c r="U50" s="4"/>
+      <c r="V50" s="4"/>
+      <c r="W50" s="4"/>
+      <c r="X50" s="4"/>
+      <c r="Y50" s="4"/>
+      <c r="Z50" s="4"/>
+      <c r="AA50" s="4"/>
+      <c r="AB50" s="4"/>
+      <c r="AC50" s="4"/>
+      <c r="AD50" s="4"/>
+      <c r="AE50" s="4"/>
+      <c r="AF50" s="4"/>
+      <c r="AG50" s="4"/>
+      <c r="AH50" s="4"/>
+      <c r="AI50" s="4"/>
+      <c r="AJ50" s="4"/>
+      <c r="AK50" s="4"/>
+      <c r="AL50" s="4"/>
+      <c r="AM50" s="4"/>
+      <c r="AN50" s="4"/>
+      <c r="AO50" s="4"/>
+      <c r="AP50" s="4"/>
+      <c r="AQ50" s="4"/>
+      <c r="AR50" s="4"/>
+      <c r="AS50" s="4"/>
+      <c r="AT50" s="4"/>
+      <c r="AU50" s="4"/>
+      <c r="AV50" s="4"/>
+      <c r="AW50" s="4"/>
+      <c r="AX50" s="4"/>
+      <c r="AY50" s="4"/>
+      <c r="AZ50" s="4"/>
+      <c r="BA50" s="4"/>
+      <c r="BB50" s="4"/>
+      <c r="BC50" s="4"/>
+      <c r="BD50" s="4"/>
+      <c r="BE50" s="4"/>
+      <c r="BF50" s="4"/>
+      <c r="BG50" s="4"/>
+      <c r="BH50" s="4"/>
+      <c r="BI50" s="4"/>
+      <c r="BJ50" s="4"/>
+      <c r="BK50" s="4"/>
+      <c r="BL50" s="4"/>
+      <c r="BM50" s="4"/>
+    </row>
+    <row r="51" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="B51" s="4"/>
+      <c r="C51" s="4"/>
+      <c r="D51" s="4"/>
+      <c r="E51" s="4"/>
+      <c r="F51" s="4"/>
+      <c r="G51" s="4"/>
+      <c r="H51" s="4"/>
+      <c r="I51" s="4"/>
+      <c r="J51" s="4"/>
+      <c r="K51" s="4"/>
+      <c r="L51" s="4"/>
+      <c r="M51" s="4"/>
+      <c r="N51" s="4"/>
+      <c r="O51" s="4"/>
+      <c r="P51" s="4"/>
+      <c r="Q51" s="4"/>
+      <c r="R51" s="4"/>
+      <c r="S51" s="4"/>
+      <c r="T51" s="4"/>
+      <c r="U51" s="4"/>
+      <c r="V51" s="4"/>
+      <c r="W51" s="4"/>
+      <c r="X51" s="4"/>
+      <c r="Y51" s="4"/>
+      <c r="Z51" s="4"/>
+      <c r="AA51" s="4"/>
+      <c r="AB51" s="4"/>
+      <c r="AC51" s="4"/>
+      <c r="AD51" s="4"/>
+      <c r="AE51" s="4"/>
+      <c r="AF51" s="4"/>
+      <c r="AG51" s="4"/>
+      <c r="AH51" s="4"/>
+      <c r="AI51" s="4"/>
+      <c r="AJ51" s="4"/>
+      <c r="AK51" s="4"/>
+      <c r="AL51" s="4"/>
+      <c r="AM51" s="4"/>
+      <c r="AN51" s="4"/>
+      <c r="AO51" s="4"/>
+      <c r="AP51" s="4"/>
+      <c r="AQ51" s="4"/>
+      <c r="AR51" s="4"/>
+      <c r="AS51" s="4"/>
+      <c r="AT51" s="4"/>
+      <c r="AU51" s="4"/>
+      <c r="AV51" s="4"/>
+      <c r="AW51" s="4"/>
+      <c r="AX51" s="4"/>
+      <c r="AY51" s="4"/>
+      <c r="AZ51" s="4"/>
+      <c r="BA51" s="4"/>
+      <c r="BB51" s="4"/>
+      <c r="BC51" s="4"/>
+      <c r="BD51" s="4"/>
+      <c r="BE51" s="4"/>
+      <c r="BF51" s="4"/>
+      <c r="BG51" s="4"/>
+      <c r="BH51" s="4"/>
+      <c r="BI51" s="4"/>
+      <c r="BJ51" s="4"/>
+      <c r="BK51" s="4"/>
+      <c r="BL51" s="4"/>
+      <c r="BM51" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="42">
+  <mergeCells count="45">
     <mergeCell ref="A1:BI1"/>
     <mergeCell ref="BJ1:BM1"/>
     <mergeCell ref="A2:BM2"/>
@@ -23203,10 +23812,10 @@
     <mergeCell ref="B28:E28"/>
     <mergeCell ref="B29:E29"/>
     <mergeCell ref="B30:E30"/>
-    <mergeCell ref="A32:V32"/>
-    <mergeCell ref="A38:BM38"/>
-    <mergeCell ref="A39:BM39"/>
-    <mergeCell ref="A40:BM40"/>
+    <mergeCell ref="B31:E31"/>
+    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="A35:V35"/>
     <mergeCell ref="A41:BM41"/>
     <mergeCell ref="A42:BM42"/>
     <mergeCell ref="A43:BM43"/>
@@ -23215,6 +23824,9 @@
     <mergeCell ref="A46:BM46"/>
     <mergeCell ref="A47:BM47"/>
     <mergeCell ref="A48:BM48"/>
+    <mergeCell ref="A49:BM49"/>
+    <mergeCell ref="A50:BM50"/>
+    <mergeCell ref="A51:BM51"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>

--- a/tratando_tabelas/finitura/entradas_finitura.xlsx
+++ b/tratando_tabelas/finitura/entradas_finitura.xlsx
@@ -20,12 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1272" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1312" uniqueCount="225">
   <si>
     <t xml:space="preserve">Santri ADM 1.1.5.7 R1</t>
   </si>
   <si>
-    <t xml:space="preserve">Emitido em: 04/05/2026 07:42:43</t>
+    <t xml:space="preserve">Emitido em: 05/05/2026 07:39:20</t>
   </si>
   <si>
     <t xml:space="preserve">Relação de entradas - Sintético</t>
@@ -307,76 +307,19 @@
     <t xml:space="preserve">35260497837181002190550010050656251541669272</t>
   </si>
   <si>
-    <t xml:space="preserve">618.318</t>
+    <t xml:space="preserve">27.705 - DOKA - INDUSTRIA E COMERCIO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.331</t>
   </si>
   <si>
     <t xml:space="preserve">22/04/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">18/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.879,02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260475339051000141550080006183181995812619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">619.446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.121,47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260475339051000141550080006194461527273470</t>
-  </si>
-  <si>
-    <t xml:space="preserve">619.536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.331,26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260475339051000141550080006195361507400913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">621.751</t>
-  </si>
-  <si>
     <t xml:space="preserve">23/04/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">21/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.945,98</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260475339051000141550080006217511066401195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">620.355</t>
-  </si>
-  <si>
     <t xml:space="preserve">20/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.674,18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260475339051000141550080006203551861934770</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.705 - DOKA - INDUSTRIA E COMERCIO LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.331</t>
   </si>
   <si>
     <t xml:space="preserve">10.012,80</t>
@@ -400,7 +343,13 @@
     <t xml:space="preserve">53.616</t>
   </si>
   <si>
+    <t xml:space="preserve">21/04/2026</t>
+  </si>
+  <si>
     <t xml:space="preserve">24/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21/05/2026</t>
   </si>
   <si>
     <t xml:space="preserve">834,78</t>
@@ -433,15 +382,6 @@
     <t xml:space="preserve">42260475339051000141550080006227231342556046</t>
   </si>
   <si>
-    <t xml:space="preserve">622.390</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.019,02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260475339051000141550080006223901051401241</t>
-  </si>
-  <si>
     <t xml:space="preserve">5.069.532</t>
   </si>
   <si>
@@ -472,22 +412,13 @@
     <t xml:space="preserve">35260497837181002190550010050714731527694305</t>
   </si>
   <si>
-    <t xml:space="preserve">622.321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.583,52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260475339051000141550080006223211866017660</t>
-  </si>
-  <si>
     <t xml:space="preserve">623.684</t>
   </si>
   <si>
     <t xml:space="preserve">25/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28/04/2026</t>
   </si>
   <si>
     <t xml:space="preserve">23/05/2026</t>
@@ -527,18 +458,6 @@
   </si>
   <si>
     <t xml:space="preserve">41260408028676000103550010000562601004422817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.718 - STELLA IMPORTACAO E EXPORTACAO DE LUMINARIAS LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">291.625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.204,49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260410691158000370550010002916251859632469</t>
   </si>
   <si>
     <t xml:space="preserve">56.231</t>
@@ -617,6 +536,108 @@
   </si>
   <si>
     <t xml:space="preserve">42260486895448000560550010000006961367561442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.419 - METALDOMADO METALURGICA LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.167,76</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260400516639000124550010000274181095610391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.075.259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.108,72</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050752591800655701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">630.877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.876,80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260475339051000141550080006308771523531623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">547 - LORENZETTI S/A INDU.BRASILEIRAS ELETROMETALURGICAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.972.380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.384,20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260461413282000143550010029723801722131595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.638,26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41260417781412000109550010000120391000336745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.171,52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260486895448000560550010000006981526909671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260486895448000560550010000007001016408174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96,50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260486895448000560550010000007011864484685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.540 - LEXXA METAIS SANITARIOS LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.038,11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260400700221000253550010000108841638050409</t>
   </si>
   <si>
     <t xml:space="preserve">Total geral</t>
@@ -16862,7 +16883,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BM51"/>
+  <dimension ref="A1:BM52"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="18"/>
@@ -17998,58 +18019,58 @@
     </row>
     <row r="9" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="n">
-        <v>305556</v>
+        <v>305725</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="K9" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L9" s="12" t="n">
-        <v>5879.02</v>
+        <v>10012.8</v>
       </c>
       <c r="M9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N9" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O9" s="12" t="n">
-        <v>5879.02</v>
+        <v>10012.8</v>
       </c>
       <c r="P9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q9" s="13" t="n">
-        <v>0.467698</v>
+        <v>0.750038</v>
       </c>
       <c r="R9" s="12" t="n">
-        <v>31.5</v>
+        <v>38</v>
       </c>
       <c r="S9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T9" s="14" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="U9" s="15" t="s">
         <v>72</v>
@@ -18061,16 +18082,16 @@
         <v>73</v>
       </c>
       <c r="X9" s="9" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Y9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z9" s="12" t="n">
-        <v>5879.02</v>
+        <v>10012.8</v>
       </c>
       <c r="AA9" s="12" t="n">
-        <v>411.53</v>
+        <v>400.51</v>
       </c>
       <c r="AB9" s="12" t="n">
         <v>0</v>
@@ -18175,7 +18196,7 @@
         <v>78</v>
       </c>
       <c r="BJ9" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="BK9" s="9" t="s">
         <v>75</v>
@@ -18189,52 +18210,52 @@
     </row>
     <row r="10" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="n">
-        <v>305560</v>
+        <v>305731</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
       <c r="F10" s="9" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="K10" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L10" s="12" t="n">
-        <v>3121.47</v>
+        <v>6247.73</v>
       </c>
       <c r="M10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N10" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O10" s="12" t="n">
-        <v>3121.47</v>
+        <v>6247.73</v>
       </c>
       <c r="P10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q10" s="13" t="n">
-        <v>0.031059</v>
+        <v>0.030808</v>
       </c>
       <c r="R10" s="12" t="n">
-        <v>5.54</v>
+        <v>6.05</v>
       </c>
       <c r="S10" s="12" t="n">
         <v>0</v>
@@ -18252,16 +18273,16 @@
         <v>73</v>
       </c>
       <c r="X10" s="9" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Y10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z10" s="12" t="n">
-        <v>3121.47</v>
+        <v>6247.73</v>
       </c>
       <c r="AA10" s="12" t="n">
-        <v>218.5</v>
+        <v>437.34</v>
       </c>
       <c r="AB10" s="12" t="n">
         <v>0</v>
@@ -18380,79 +18401,79 @@
     </row>
     <row r="11" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="n">
-        <v>305561</v>
+        <v>305778</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>64</v>
+        <v>105</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
       <c r="F11" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="K11" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>5331.26</v>
+        <v>834.78</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O11" s="12" t="n">
-        <v>5005.88</v>
+        <v>730</v>
       </c>
       <c r="P11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q11" s="13" t="n">
-        <v>0.055816</v>
+        <v>0</v>
       </c>
       <c r="R11" s="12" t="n">
-        <v>7.12</v>
+        <v>0</v>
       </c>
       <c r="S11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T11" s="14" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="U11" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V11" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="W11" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X11" s="9" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="Y11" s="12" t="n">
-        <v>325.38</v>
+        <v>104.78</v>
       </c>
       <c r="Z11" s="12" t="n">
-        <v>5005.88</v>
+        <v>730</v>
       </c>
       <c r="AA11" s="12" t="n">
-        <v>350.41</v>
+        <v>51.1</v>
       </c>
       <c r="AB11" s="12" t="n">
         <v>0</v>
@@ -18518,7 +18539,7 @@
         <v>74</v>
       </c>
       <c r="AW11" s="14" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="AX11" s="10" t="s">
         <v>77</v>
@@ -18557,7 +18578,7 @@
         <v>78</v>
       </c>
       <c r="BJ11" s="9" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="BK11" s="9" t="s">
         <v>75</v>
@@ -18571,7 +18592,7 @@
     </row>
     <row r="12" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="n">
-        <v>305681</v>
+        <v>305821</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>64</v>
@@ -18580,25 +18601,25 @@
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
       <c r="F12" s="9" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="G12" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="K12" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>1945.98</v>
+        <v>4462.34</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>0</v>
@@ -18607,22 +18628,22 @@
         <v>1</v>
       </c>
       <c r="O12" s="12" t="n">
-        <v>1945.98</v>
+        <v>4462.34</v>
       </c>
       <c r="P12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" s="13" t="n">
-        <v>0.004946</v>
+        <v>0.010272</v>
       </c>
       <c r="R12" s="12" t="n">
-        <v>1.15</v>
+        <v>3.7</v>
       </c>
       <c r="S12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T12" s="14" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="U12" s="15" t="s">
         <v>72</v>
@@ -18634,16 +18655,16 @@
         <v>73</v>
       </c>
       <c r="X12" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Y12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z12" s="12" t="n">
-        <v>1945.98</v>
+        <v>4462.34</v>
       </c>
       <c r="AA12" s="12" t="n">
-        <v>136.22</v>
+        <v>312.36</v>
       </c>
       <c r="AB12" s="12" t="n">
         <v>0</v>
@@ -18748,7 +18769,7 @@
         <v>78</v>
       </c>
       <c r="BJ12" s="9" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="BK12" s="9" t="s">
         <v>75</v>
@@ -18762,7 +18783,7 @@
     </row>
     <row r="13" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="n">
-        <v>305724</v>
+        <v>305822</v>
       </c>
       <c r="B13" s="9" t="s">
         <v>64</v>
@@ -18771,16 +18792,16 @@
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
       <c r="F13" s="9" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="G13" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J13" s="9" t="s">
         <v>114</v>
@@ -18789,7 +18810,7 @@
         <v>70</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>1674.18</v>
+        <v>1464.23</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>0</v>
@@ -18798,22 +18819,22 @@
         <v>1</v>
       </c>
       <c r="O13" s="12" t="n">
-        <v>1674.18</v>
+        <v>1464.23</v>
       </c>
       <c r="P13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q13" s="13" t="n">
-        <v>0.003916</v>
+        <v>0.002473</v>
       </c>
       <c r="R13" s="12" t="n">
-        <v>0.97</v>
+        <v>0.77</v>
       </c>
       <c r="S13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T13" s="14" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="U13" s="15" t="s">
         <v>72</v>
@@ -18825,16 +18846,16 @@
         <v>73</v>
       </c>
       <c r="X13" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Y13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z13" s="12" t="n">
-        <v>1674.18</v>
+        <v>1464.23</v>
       </c>
       <c r="AA13" s="12" t="n">
-        <v>117.19</v>
+        <v>102.5</v>
       </c>
       <c r="AB13" s="12" t="n">
         <v>0</v>
@@ -18939,7 +18960,7 @@
         <v>78</v>
       </c>
       <c r="BJ13" s="9" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="BK13" s="9" t="s">
         <v>75</v>
@@ -18953,79 +18974,79 @@
     </row>
     <row r="14" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="n">
-        <v>305725</v>
+        <v>305942</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
       <c r="F14" s="9" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G14" s="10" t="s">
         <v>83</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="K14" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>10012.8</v>
+        <v>42.44</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O14" s="12" t="n">
-        <v>10012.8</v>
+        <v>39.85</v>
       </c>
       <c r="P14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q14" s="13" t="n">
-        <v>0.750038</v>
+        <v>0.002284</v>
       </c>
       <c r="R14" s="12" t="n">
-        <v>38</v>
+        <v>0.8</v>
       </c>
       <c r="S14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T14" s="14" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="U14" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V14" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W14" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X14" s="9" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="Y14" s="12" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Z14" s="12" t="n">
-        <v>10012.8</v>
+        <v>39.85</v>
       </c>
       <c r="AA14" s="12" t="n">
-        <v>400.51</v>
+        <v>1.59</v>
       </c>
       <c r="AB14" s="12" t="n">
         <v>0</v>
@@ -19094,7 +19115,7 @@
         <v>76</v>
       </c>
       <c r="AX14" s="10" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AY14" s="14" t="s">
         <v>75</v>
@@ -19130,7 +19151,7 @@
         <v>78</v>
       </c>
       <c r="BJ14" s="9" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="BK14" s="9" t="s">
         <v>75</v>
@@ -19144,7 +19165,7 @@
     </row>
     <row r="15" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="n">
-        <v>305731</v>
+        <v>305957</v>
       </c>
       <c r="B15" s="9" t="s">
         <v>81</v>
@@ -19153,70 +19174,70 @@
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
       <c r="F15" s="9" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G15" s="10" t="s">
         <v>83</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="K15" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>6247.73</v>
+        <v>126.7</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O15" s="12" t="n">
-        <v>6247.73</v>
+        <v>118.97</v>
       </c>
       <c r="P15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q15" s="13" t="n">
-        <v>0.030808</v>
+        <v>0.001512</v>
       </c>
       <c r="R15" s="12" t="n">
-        <v>6.05</v>
+        <v>1.58</v>
       </c>
       <c r="S15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T15" s="14" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="U15" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V15" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W15" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X15" s="9" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="Y15" s="12" t="n">
-        <v>0</v>
+        <v>7.73</v>
       </c>
       <c r="Z15" s="12" t="n">
-        <v>6247.73</v>
+        <v>118.97</v>
       </c>
       <c r="AA15" s="12" t="n">
-        <v>437.34</v>
+        <v>4.76</v>
       </c>
       <c r="AB15" s="12" t="n">
         <v>0</v>
@@ -19285,7 +19306,7 @@
         <v>76</v>
       </c>
       <c r="AX15" s="10" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AY15" s="14" t="s">
         <v>75</v>
@@ -19321,7 +19342,7 @@
         <v>78</v>
       </c>
       <c r="BJ15" s="9" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="BK15" s="9" t="s">
         <v>75</v>
@@ -19335,34 +19356,34 @@
     </row>
     <row r="16" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="n">
-        <v>305778</v>
+        <v>305966</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>124</v>
+        <v>81</v>
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
       <c r="F16" s="9" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G16" s="10" t="s">
         <v>83</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="K16" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>834.78</v>
+        <v>290.09</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>0</v>
@@ -19371,43 +19392,43 @@
         <v>2</v>
       </c>
       <c r="O16" s="12" t="n">
-        <v>730</v>
+        <v>272.38</v>
       </c>
       <c r="P16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q16" s="13" t="n">
-        <v>0</v>
+        <v>0.003202</v>
       </c>
       <c r="R16" s="12" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T16" s="14" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="U16" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V16" s="12" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="W16" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X16" s="9" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="Y16" s="12" t="n">
-        <v>104.78</v>
+        <v>17.71</v>
       </c>
       <c r="Z16" s="12" t="n">
-        <v>730</v>
+        <v>272.38</v>
       </c>
       <c r="AA16" s="12" t="n">
-        <v>51.1</v>
+        <v>10.89</v>
       </c>
       <c r="AB16" s="12" t="n">
         <v>0</v>
@@ -19473,10 +19494,10 @@
         <v>74</v>
       </c>
       <c r="AW16" s="14" t="s">
-        <v>128</v>
+        <v>76</v>
       </c>
       <c r="AX16" s="10" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AY16" s="14" t="s">
         <v>75</v>
@@ -19526,7 +19547,7 @@
     </row>
     <row r="17" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="n">
-        <v>305821</v>
+        <v>306001</v>
       </c>
       <c r="B17" s="9" t="s">
         <v>64</v>
@@ -19541,19 +19562,19 @@
         <v>66</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="K17" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>4462.34</v>
+        <v>1181.41</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>0</v>
@@ -19562,22 +19583,22 @@
         <v>1</v>
       </c>
       <c r="O17" s="12" t="n">
-        <v>4462.34</v>
+        <v>1181.41</v>
       </c>
       <c r="P17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q17" s="13" t="n">
-        <v>0.010272</v>
+        <v>0.000412</v>
       </c>
       <c r="R17" s="12" t="n">
-        <v>3.7</v>
+        <v>0.71</v>
       </c>
       <c r="S17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T17" s="14" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="U17" s="15" t="s">
         <v>72</v>
@@ -19589,16 +19610,16 @@
         <v>73</v>
       </c>
       <c r="X17" s="9" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="Y17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z17" s="12" t="n">
-        <v>4462.34</v>
+        <v>1181.41</v>
       </c>
       <c r="AA17" s="12" t="n">
-        <v>312.36</v>
+        <v>82.7</v>
       </c>
       <c r="AB17" s="12" t="n">
         <v>0</v>
@@ -19703,7 +19724,7 @@
         <v>78</v>
       </c>
       <c r="BJ17" s="9" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="BK17" s="9" t="s">
         <v>75</v>
@@ -19717,34 +19738,34 @@
     </row>
     <row r="18" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="n">
-        <v>305822</v>
+        <v>306005</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>64</v>
+        <v>136</v>
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
       <c r="F18" s="9" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="K18" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>1464.23</v>
+        <v>861.88</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>0</v>
@@ -19753,43 +19774,43 @@
         <v>1</v>
       </c>
       <c r="O18" s="12" t="n">
-        <v>1464.23</v>
+        <v>861.88</v>
       </c>
       <c r="P18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q18" s="13" t="n">
-        <v>0.002473</v>
+        <v>0.073796</v>
       </c>
       <c r="R18" s="12" t="n">
-        <v>0.77</v>
+        <v>43.13</v>
       </c>
       <c r="S18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T18" s="14" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="U18" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V18" s="12" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="W18" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X18" s="9" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="Y18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z18" s="12" t="n">
-        <v>1464.23</v>
+        <v>861.88</v>
       </c>
       <c r="AA18" s="12" t="n">
-        <v>102.5</v>
+        <v>60.33</v>
       </c>
       <c r="AB18" s="12" t="n">
         <v>0</v>
@@ -19894,7 +19915,7 @@
         <v>78</v>
       </c>
       <c r="BJ18" s="9" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="BK18" s="9" t="s">
         <v>75</v>
@@ -19908,58 +19929,58 @@
     </row>
     <row r="19" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="n">
-        <v>305829</v>
+        <v>306150</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>64</v>
+        <v>141</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
       <c r="F19" s="9" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>110</v>
+        <v>143</v>
       </c>
       <c r="K19" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>3019.02</v>
+        <v>2070.21</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O19" s="12" t="n">
-        <v>3019.02</v>
+        <v>1970.21</v>
       </c>
       <c r="P19" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q19" s="13" t="n">
-        <v>0.004946</v>
+        <v>0</v>
       </c>
       <c r="R19" s="12" t="n">
-        <v>1.53</v>
+        <v>4.15</v>
       </c>
       <c r="S19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T19" s="14" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="U19" s="15" t="s">
         <v>72</v>
@@ -19971,16 +19992,16 @@
         <v>73</v>
       </c>
       <c r="X19" s="9" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="Y19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z19" s="12" t="n">
-        <v>3019.02</v>
+        <v>2070.21</v>
       </c>
       <c r="AA19" s="12" t="n">
-        <v>211.33</v>
+        <v>144.92</v>
       </c>
       <c r="AB19" s="12" t="n">
         <v>0</v>
@@ -20085,7 +20106,7 @@
         <v>78</v>
       </c>
       <c r="BJ19" s="9" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="BK19" s="9" t="s">
         <v>75</v>
@@ -20099,79 +20120,79 @@
     </row>
     <row r="20" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="n">
-        <v>305942</v>
+        <v>306173</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>81</v>
+        <v>141</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
       <c r="F20" s="9" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="G20" s="10" t="s">
         <v>83</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>78</v>
+        <v>143</v>
       </c>
       <c r="K20" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>42.44</v>
+        <v>3730.39</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O20" s="12" t="n">
-        <v>39.85</v>
+        <v>3730.39</v>
       </c>
       <c r="P20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q20" s="13" t="n">
-        <v>0.002284</v>
+        <v>0</v>
       </c>
       <c r="R20" s="12" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="S20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T20" s="14" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="U20" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V20" s="12" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="W20" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X20" s="9" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="Y20" s="12" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Z20" s="12" t="n">
-        <v>39.85</v>
+        <v>3730.39</v>
       </c>
       <c r="AA20" s="12" t="n">
-        <v>1.59</v>
+        <v>261.14</v>
       </c>
       <c r="AB20" s="12" t="n">
         <v>0</v>
@@ -20240,7 +20261,7 @@
         <v>76</v>
       </c>
       <c r="AX20" s="10" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AY20" s="14" t="s">
         <v>75</v>
@@ -20276,7 +20297,7 @@
         <v>78</v>
       </c>
       <c r="BJ20" s="9" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="BK20" s="9" t="s">
         <v>75</v>
@@ -20290,79 +20311,79 @@
     </row>
     <row r="21" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="n">
-        <v>305957</v>
+        <v>306272</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>81</v>
+        <v>149</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
       <c r="F21" s="9" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="G21" s="10" t="s">
         <v>83</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="K21" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>126.7</v>
+        <v>14916.19</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>0</v>
+        <v>3433.93</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O21" s="12" t="n">
-        <v>118.97</v>
+        <v>17025</v>
       </c>
       <c r="P21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q21" s="13" t="n">
-        <v>0.001512</v>
+        <v>0</v>
       </c>
       <c r="R21" s="12" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="S21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T21" s="14" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="U21" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V21" s="12" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="W21" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X21" s="9" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="Y21" s="12" t="n">
-        <v>7.73</v>
+        <v>1325.12</v>
       </c>
       <c r="Z21" s="12" t="n">
-        <v>118.97</v>
+        <v>13591.07</v>
       </c>
       <c r="AA21" s="12" t="n">
-        <v>4.76</v>
+        <v>543.65</v>
       </c>
       <c r="AB21" s="12" t="n">
         <v>0</v>
@@ -20431,7 +20452,7 @@
         <v>76</v>
       </c>
       <c r="AX21" s="10" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AY21" s="14" t="s">
         <v>75</v>
@@ -20467,7 +20488,7 @@
         <v>78</v>
       </c>
       <c r="BJ21" s="9" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="BK21" s="9" t="s">
         <v>75</v>
@@ -20481,34 +20502,34 @@
     </row>
     <row r="22" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="n">
-        <v>305966</v>
+        <v>306327</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
       <c r="F22" s="9" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>78</v>
+        <v>157</v>
       </c>
       <c r="K22" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>290.09</v>
+        <v>10714.13</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>0</v>
@@ -20517,43 +20538,43 @@
         <v>2</v>
       </c>
       <c r="O22" s="12" t="n">
-        <v>272.38</v>
+        <v>10714.13</v>
       </c>
       <c r="P22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q22" s="13" t="n">
-        <v>0.003202</v>
+        <v>0.020976</v>
       </c>
       <c r="R22" s="12" t="n">
-        <v>1.93</v>
+        <v>6.72</v>
       </c>
       <c r="S22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T22" s="14" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="U22" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V22" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W22" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X22" s="9" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="Y22" s="12" t="n">
-        <v>17.71</v>
+        <v>0</v>
       </c>
       <c r="Z22" s="12" t="n">
-        <v>272.38</v>
+        <v>10714.13</v>
       </c>
       <c r="AA22" s="12" t="n">
-        <v>10.89</v>
+        <v>749.99</v>
       </c>
       <c r="AB22" s="12" t="n">
         <v>0</v>
@@ -20622,7 +20643,7 @@
         <v>76</v>
       </c>
       <c r="AX22" s="10" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AY22" s="14" t="s">
         <v>75</v>
@@ -20658,7 +20679,7 @@
         <v>78</v>
       </c>
       <c r="BJ22" s="9" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="BK22" s="9" t="s">
         <v>75</v>
@@ -20672,7 +20693,7 @@
     </row>
     <row r="23" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="n">
-        <v>305994</v>
+        <v>306329</v>
       </c>
       <c r="B23" s="9" t="s">
         <v>64</v>
@@ -20681,25 +20702,25 @@
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="9" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="G23" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>109</v>
+        <v>151</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="K23" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>2583.52</v>
+        <v>891.38</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>0</v>
@@ -20708,22 +20729,22 @@
         <v>1</v>
       </c>
       <c r="O23" s="12" t="n">
-        <v>2583.52</v>
+        <v>891.38</v>
       </c>
       <c r="P23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q23" s="13" t="n">
-        <v>0.007527</v>
+        <v>0.003922</v>
       </c>
       <c r="R23" s="12" t="n">
-        <v>1.95</v>
+        <v>0.41</v>
       </c>
       <c r="S23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T23" s="14" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="U23" s="15" t="s">
         <v>72</v>
@@ -20735,16 +20756,16 @@
         <v>73</v>
       </c>
       <c r="X23" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Y23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z23" s="12" t="n">
-        <v>2583.52</v>
+        <v>891.38</v>
       </c>
       <c r="AA23" s="12" t="n">
-        <v>180.85</v>
+        <v>62.4</v>
       </c>
       <c r="AB23" s="12" t="n">
         <v>0</v>
@@ -20849,7 +20870,7 @@
         <v>78</v>
       </c>
       <c r="BJ23" s="9" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="BK23" s="9" t="s">
         <v>75</v>
@@ -20863,7 +20884,7 @@
     </row>
     <row r="24" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="n">
-        <v>306001</v>
+        <v>306335</v>
       </c>
       <c r="B24" s="9" t="s">
         <v>64</v>
@@ -20872,25 +20893,25 @@
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
       <c r="F24" s="9" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="G24" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="K24" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>1181.41</v>
+        <v>1593.54</v>
       </c>
       <c r="M24" s="12" t="n">
         <v>0</v>
@@ -20899,22 +20920,22 @@
         <v>1</v>
       </c>
       <c r="O24" s="12" t="n">
-        <v>1181.41</v>
+        <v>1593.54</v>
       </c>
       <c r="P24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q24" s="13" t="n">
-        <v>0.000412</v>
+        <v>0.005136</v>
       </c>
       <c r="R24" s="12" t="n">
-        <v>0.71</v>
+        <v>2.1</v>
       </c>
       <c r="S24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T24" s="14" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="U24" s="15" t="s">
         <v>72</v>
@@ -20926,16 +20947,16 @@
         <v>73</v>
       </c>
       <c r="X24" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Y24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z24" s="12" t="n">
-        <v>1181.41</v>
+        <v>1593.54</v>
       </c>
       <c r="AA24" s="12" t="n">
-        <v>82.7</v>
+        <v>111.55</v>
       </c>
       <c r="AB24" s="12" t="n">
         <v>0</v>
@@ -21040,7 +21061,7 @@
         <v>78</v>
       </c>
       <c r="BJ24" s="9" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="BK24" s="9" t="s">
         <v>75</v>
@@ -21054,79 +21075,79 @@
     </row>
     <row r="25" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="n">
-        <v>306005</v>
+        <v>306338</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="G25" s="10" t="s">
         <v>83</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>126</v>
+        <v>151</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>161</v>
+        <v>78</v>
       </c>
       <c r="K25" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>861.88</v>
+        <v>900.38</v>
       </c>
       <c r="M25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O25" s="12" t="n">
-        <v>861.88</v>
+        <v>900.38</v>
       </c>
       <c r="P25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q25" s="13" t="n">
-        <v>0.073796</v>
+        <v>0</v>
       </c>
       <c r="R25" s="12" t="n">
-        <v>43.13</v>
+        <v>0</v>
       </c>
       <c r="S25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T25" s="14" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="U25" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V25" s="12" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="W25" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X25" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Y25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z25" s="12" t="n">
-        <v>861.88</v>
+        <v>900.38</v>
       </c>
       <c r="AA25" s="12" t="n">
-        <v>60.33</v>
+        <v>36.02</v>
       </c>
       <c r="AB25" s="12" t="n">
         <v>0</v>
@@ -21195,7 +21216,7 @@
         <v>76</v>
       </c>
       <c r="AX25" s="10" t="s">
-        <v>77</v>
+        <v>170</v>
       </c>
       <c r="AY25" s="14" t="s">
         <v>75</v>
@@ -21231,7 +21252,7 @@
         <v>78</v>
       </c>
       <c r="BJ25" s="9" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="BK25" s="9" t="s">
         <v>75</v>
@@ -21245,79 +21266,79 @@
     </row>
     <row r="26" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="n">
-        <v>306150</v>
+        <v>306454</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="G26" s="10" t="s">
         <v>83</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>151</v>
+        <v>174</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="K26" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>2070.21</v>
+        <v>3167.76</v>
       </c>
       <c r="M26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O26" s="12" t="n">
-        <v>1970.21</v>
+        <v>3167.76</v>
       </c>
       <c r="P26" s="12" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q26" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R26" s="12" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="S26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T26" s="14" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="U26" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V26" s="12" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="W26" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X26" s="9" t="s">
-        <v>151</v>
+        <v>174</v>
       </c>
       <c r="Y26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z26" s="12" t="n">
-        <v>2070.21</v>
+        <v>3167.76</v>
       </c>
       <c r="AA26" s="12" t="n">
-        <v>144.92</v>
+        <v>117.52</v>
       </c>
       <c r="AB26" s="12" t="n">
         <v>0</v>
@@ -21422,7 +21443,7 @@
         <v>78</v>
       </c>
       <c r="BJ26" s="9" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="BK26" s="9" t="s">
         <v>75</v>
@@ -21436,79 +21457,79 @@
     </row>
     <row r="27" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="n">
-        <v>306157</v>
+        <v>306477</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>169</v>
+        <v>81</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="G27" s="10" t="s">
         <v>83</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>109</v>
+        <v>152</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>151</v>
+        <v>174</v>
       </c>
       <c r="J27" s="9" t="s">
-        <v>110</v>
+        <v>179</v>
       </c>
       <c r="K27" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>11204.49</v>
+        <v>3108.72</v>
       </c>
       <c r="M27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="O27" s="12" t="n">
-        <v>10131.65</v>
+        <v>3108.72</v>
       </c>
       <c r="P27" s="12" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="Q27" s="13" t="n">
-        <v>0.02398</v>
+        <v>0.001598</v>
       </c>
       <c r="R27" s="12" t="n">
-        <v>14.4</v>
+        <v>2.6</v>
       </c>
       <c r="S27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T27" s="14" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="U27" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V27" s="12" t="n">
-        <v>55.79</v>
+        <v>28</v>
       </c>
       <c r="W27" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X27" s="9" t="s">
-        <v>151</v>
+        <v>174</v>
       </c>
       <c r="Y27" s="12" t="n">
-        <v>987.84</v>
+        <v>0</v>
       </c>
       <c r="Z27" s="12" t="n">
-        <v>10216.65</v>
+        <v>3108.72</v>
       </c>
       <c r="AA27" s="12" t="n">
-        <v>408.68</v>
+        <v>217.61</v>
       </c>
       <c r="AB27" s="12" t="n">
         <v>0</v>
@@ -21613,7 +21634,7 @@
         <v>78</v>
       </c>
       <c r="BJ27" s="9" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="BK27" s="9" t="s">
         <v>75</v>
@@ -21627,79 +21648,79 @@
     </row>
     <row r="28" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="n">
-        <v>306173</v>
+        <v>306493</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>164</v>
+        <v>64</v>
       </c>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>151</v>
+        <v>174</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="K28" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>3730.39</v>
+        <v>2876.8</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O28" s="12" t="n">
-        <v>3730.39</v>
+        <v>2701.22</v>
       </c>
       <c r="P28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q28" s="13" t="n">
-        <v>0</v>
+        <v>0.027908</v>
       </c>
       <c r="R28" s="12" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="S28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T28" s="14" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="U28" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V28" s="12" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="W28" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X28" s="9" t="s">
-        <v>151</v>
+        <v>174</v>
       </c>
       <c r="Y28" s="12" t="n">
-        <v>0</v>
+        <v>175.58</v>
       </c>
       <c r="Z28" s="12" t="n">
-        <v>3730.39</v>
+        <v>2701.22</v>
       </c>
       <c r="AA28" s="12" t="n">
-        <v>261.14</v>
+        <v>189.09</v>
       </c>
       <c r="AB28" s="12" t="n">
         <v>0</v>
@@ -21804,7 +21825,7 @@
         <v>78</v>
       </c>
       <c r="BJ28" s="9" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="BK28" s="9" t="s">
         <v>75</v>
@@ -21818,79 +21839,79 @@
     </row>
     <row r="29" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="n">
-        <v>306272</v>
+        <v>306535</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
       <c r="F29" s="9" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="G29" s="10" t="s">
         <v>83</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>178</v>
+        <v>152</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>180</v>
+        <v>78</v>
       </c>
       <c r="K29" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>14916.19</v>
+        <v>5384.2</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>3433.93</v>
+        <v>0</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>6</v>
       </c>
       <c r="O29" s="12" t="n">
-        <v>17025</v>
+        <v>5384.2</v>
       </c>
       <c r="P29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q29" s="13" t="n">
-        <v>0</v>
+        <v>0.023054</v>
       </c>
       <c r="R29" s="12" t="n">
-        <v>0</v>
+        <v>28.62</v>
       </c>
       <c r="S29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T29" s="14" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="U29" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V29" s="12" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="W29" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X29" s="9" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="Y29" s="12" t="n">
-        <v>1325.12</v>
+        <v>0</v>
       </c>
       <c r="Z29" s="12" t="n">
-        <v>13591.07</v>
+        <v>0</v>
       </c>
       <c r="AA29" s="12" t="n">
-        <v>543.65</v>
+        <v>0</v>
       </c>
       <c r="AB29" s="12" t="n">
         <v>0</v>
@@ -21959,7 +21980,7 @@
         <v>76</v>
       </c>
       <c r="AX29" s="10" t="s">
-        <v>77</v>
+        <v>170</v>
       </c>
       <c r="AY29" s="14" t="s">
         <v>75</v>
@@ -21995,7 +22016,7 @@
         <v>78</v>
       </c>
       <c r="BJ29" s="9" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="BK29" s="9" t="s">
         <v>75</v>
@@ -22009,79 +22030,79 @@
     </row>
     <row r="30" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="n">
-        <v>306327</v>
+        <v>306540</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>64</v>
+        <v>149</v>
       </c>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
       <c r="F30" s="9" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="G30" s="10" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="H30" s="9" t="s">
         <v>151</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="K30" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>10714.13</v>
+        <v>6638.26</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>0</v>
+        <v>1067.38</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O30" s="12" t="n">
-        <v>10714.13</v>
+        <v>7115.9</v>
       </c>
       <c r="P30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q30" s="13" t="n">
-        <v>0.020976</v>
+        <v>0</v>
       </c>
       <c r="R30" s="12" t="n">
-        <v>6.72</v>
+        <v>0</v>
       </c>
       <c r="S30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T30" s="14" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="U30" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V30" s="12" t="n">
-        <v>28</v>
+        <v>105</v>
       </c>
       <c r="W30" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X30" s="9" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="Y30" s="12" t="n">
-        <v>0</v>
+        <v>589.74</v>
       </c>
       <c r="Z30" s="12" t="n">
-        <v>10714.13</v>
+        <v>6048.52</v>
       </c>
       <c r="AA30" s="12" t="n">
-        <v>749.99</v>
+        <v>241.94</v>
       </c>
       <c r="AB30" s="12" t="n">
         <v>0</v>
@@ -22186,7 +22207,7 @@
         <v>78</v>
       </c>
       <c r="BJ30" s="9" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="BK30" s="9" t="s">
         <v>75</v>
@@ -22200,79 +22221,79 @@
     </row>
     <row r="31" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="n">
-        <v>306329</v>
+        <v>306545</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>64</v>
+        <v>167</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
       <c r="F31" s="9" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>178</v>
+        <v>151</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="J31" s="9" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="K31" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>891.38</v>
+        <v>7171.52</v>
       </c>
       <c r="M31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O31" s="12" t="n">
-        <v>891.38</v>
+        <v>7171.52</v>
       </c>
       <c r="P31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q31" s="13" t="n">
-        <v>0.003922</v>
+        <v>0</v>
       </c>
       <c r="R31" s="12" t="n">
-        <v>0.41</v>
+        <v>0</v>
       </c>
       <c r="S31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T31" s="14" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="U31" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V31" s="12" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="W31" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X31" s="9" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="Y31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z31" s="12" t="n">
-        <v>891.38</v>
+        <v>7171.52</v>
       </c>
       <c r="AA31" s="12" t="n">
-        <v>62.4</v>
+        <v>286.86</v>
       </c>
       <c r="AB31" s="12" t="n">
         <v>0</v>
@@ -22377,7 +22398,7 @@
         <v>78</v>
       </c>
       <c r="BJ31" s="9" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="BK31" s="9" t="s">
         <v>75</v>
@@ -22391,79 +22412,79 @@
     </row>
     <row r="32" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="n">
-        <v>306335</v>
+        <v>306579</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>64</v>
+        <v>167</v>
       </c>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
       <c r="F32" s="9" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="G32" s="10" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>178</v>
+        <v>151</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="J32" s="9" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="K32" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>1593.54</v>
+        <v>7171.52</v>
       </c>
       <c r="M32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O32" s="12" t="n">
-        <v>1593.54</v>
+        <v>7171.52</v>
       </c>
       <c r="P32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q32" s="13" t="n">
-        <v>0.005136</v>
+        <v>0</v>
       </c>
       <c r="R32" s="12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T32" s="14" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="U32" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V32" s="12" t="n">
-        <v>28</v>
+        <v>61.66</v>
       </c>
       <c r="W32" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X32" s="9" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="Y32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z32" s="12" t="n">
-        <v>1593.54</v>
+        <v>7171.52</v>
       </c>
       <c r="AA32" s="12" t="n">
-        <v>111.55</v>
+        <v>286.86</v>
       </c>
       <c r="AB32" s="12" t="n">
         <v>0</v>
@@ -22529,7 +22550,7 @@
         <v>74</v>
       </c>
       <c r="AW32" s="14" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="AX32" s="10" t="s">
         <v>77</v>
@@ -22568,7 +22589,7 @@
         <v>78</v>
       </c>
       <c r="BJ32" s="9" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="BK32" s="9" t="s">
         <v>75</v>
@@ -22582,25 +22603,25 @@
     </row>
     <row r="33" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="n">
-        <v>306338</v>
+        <v>306581</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>194</v>
+        <v>167</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="9"/>
       <c r="E33" s="9"/>
       <c r="F33" s="9" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="G33" s="10" t="s">
         <v>83</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>178</v>
+        <v>151</v>
       </c>
       <c r="I33" s="9" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="J33" s="9" t="s">
         <v>78</v>
@@ -22609,16 +22630,16 @@
         <v>70</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>900.38</v>
+        <v>96.5</v>
       </c>
       <c r="M33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O33" s="12" t="n">
-        <v>900.38</v>
+        <v>96.5</v>
       </c>
       <c r="P33" s="12" t="n">
         <v>0</v>
@@ -22633,7 +22654,7 @@
         <v>0</v>
       </c>
       <c r="T33" s="14" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="U33" s="15" t="s">
         <v>72</v>
@@ -22645,16 +22666,16 @@
         <v>73</v>
       </c>
       <c r="X33" s="9" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="Y33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z33" s="12" t="n">
-        <v>900.38</v>
+        <v>96.5</v>
       </c>
       <c r="AA33" s="12" t="n">
-        <v>36.02</v>
+        <v>3.86</v>
       </c>
       <c r="AB33" s="12" t="n">
         <v>0</v>
@@ -22720,10 +22741,10 @@
         <v>74</v>
       </c>
       <c r="AW33" s="14" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="AX33" s="10" t="s">
-        <v>197</v>
+        <v>170</v>
       </c>
       <c r="AY33" s="14" t="s">
         <v>75</v>
@@ -22759,7 +22780,7 @@
         <v>78</v>
       </c>
       <c r="BJ33" s="9" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="BK33" s="9" t="s">
         <v>75</v>
@@ -22772,396 +22793,518 @@
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="4"/>
+      <c r="A34" s="8" t="n">
+        <v>306585</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="G34" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="H34" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="I34" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="J34" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="K34" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L34" s="12" t="n">
+        <v>24038.11</v>
+      </c>
+      <c r="M34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="O34" s="12" t="n">
+        <v>22949.18</v>
+      </c>
+      <c r="P34" s="12" t="n">
+        <v>659</v>
+      </c>
+      <c r="Q34" s="13" t="n">
+        <v>0.022336</v>
+      </c>
+      <c r="R34" s="12" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="S34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" s="14" t="s">
+        <v>204</v>
+      </c>
+      <c r="U34" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V34" s="12" t="n">
+        <v>82.46</v>
+      </c>
+      <c r="W34" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X34" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y34" s="12" t="n">
+        <v>429.93</v>
+      </c>
+      <c r="Z34" s="12" t="n">
+        <v>23608.18</v>
+      </c>
+      <c r="AA34" s="12" t="n">
+        <v>944.32</v>
+      </c>
+      <c r="AB34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ34" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM34" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN34" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO34" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP34" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ34" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR34" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS34" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT34" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU34" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV34" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW34" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX34" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY34" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ34" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA34" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB34" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC34" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD34" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE34" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF34" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG34" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH34" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI34" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ34" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="BK34" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL34" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM34" s="16" t="s">
+        <v>80</v>
+      </c>
     </row>
-    <row r="35" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="17" t="s">
-        <v>199</v>
-      </c>
-      <c r="B35" s="17"/>
-      <c r="C35" s="17"/>
-      <c r="D35" s="17"/>
-      <c r="E35" s="17"/>
-      <c r="F35" s="17"/>
-      <c r="G35" s="17"/>
-      <c r="H35" s="17"/>
-      <c r="I35" s="17"/>
-      <c r="J35" s="17"/>
-      <c r="K35" s="17"/>
-      <c r="L35" s="17"/>
-      <c r="M35" s="17"/>
-      <c r="N35" s="17"/>
-      <c r="O35" s="17"/>
-      <c r="P35" s="17"/>
-      <c r="Q35" s="17"/>
-      <c r="R35" s="17"/>
-      <c r="S35" s="17"/>
-      <c r="T35" s="17"/>
-      <c r="U35" s="17"/>
-      <c r="V35" s="17"/>
+    <row r="35" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="4"/>
     </row>
     <row r="36" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="18" t="s">
-        <v>200</v>
-      </c>
-      <c r="B36" s="18" t="s">
+      <c r="A36" s="17" t="s">
+        <v>206</v>
+      </c>
+      <c r="B36" s="17"/>
+      <c r="C36" s="17"/>
+      <c r="D36" s="17"/>
+      <c r="E36" s="17"/>
+      <c r="F36" s="17"/>
+      <c r="G36" s="17"/>
+      <c r="H36" s="17"/>
+      <c r="I36" s="17"/>
+      <c r="J36" s="17"/>
+      <c r="K36" s="17"/>
+      <c r="L36" s="17"/>
+      <c r="M36" s="17"/>
+      <c r="N36" s="17"/>
+      <c r="O36" s="17"/>
+      <c r="P36" s="17"/>
+      <c r="Q36" s="17"/>
+      <c r="R36" s="17"/>
+      <c r="S36" s="17"/>
+      <c r="T36" s="17"/>
+      <c r="U36" s="17"/>
+      <c r="V36" s="17"/>
+    </row>
+    <row r="37" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="18" t="s">
+        <v>207</v>
+      </c>
+      <c r="B37" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C36" s="18" t="s">
+      <c r="C37" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D36" s="18" t="s">
-        <v>201</v>
-      </c>
-      <c r="E36" s="18" t="s">
+      <c r="D37" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="E37" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="F36" s="18" t="s">
+      <c r="F37" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="G36" s="18" t="s">
+      <c r="G37" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="H36" s="18" t="s">
+      <c r="H37" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="I36" s="18" t="s">
-        <v>202</v>
-      </c>
-      <c r="J36" s="18" t="s">
+      <c r="I37" s="18" t="s">
+        <v>209</v>
+      </c>
+      <c r="J37" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="K36" s="18" t="s">
+      <c r="K37" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="L36" s="18" t="s">
+      <c r="L37" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="M36" s="18" t="s">
-        <v>203</v>
-      </c>
-      <c r="N36" s="18" t="s">
+      <c r="M37" s="18" t="s">
+        <v>210</v>
+      </c>
+      <c r="N37" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="O36" s="18" t="s">
+      <c r="O37" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P36" s="18" t="s">
+      <c r="P37" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="Q36" s="18" t="s">
+      <c r="Q37" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="R36" s="18" t="s">
+      <c r="R37" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="S36" s="18" t="s">
-        <v>204</v>
-      </c>
-      <c r="T36" s="18" t="s">
-        <v>205</v>
-      </c>
-      <c r="U36" s="18" t="s">
+      <c r="S37" s="18" t="s">
+        <v>211</v>
+      </c>
+      <c r="T37" s="18" t="s">
+        <v>212</v>
+      </c>
+      <c r="U37" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="V36" s="18" t="s">
+      <c r="V37" s="18" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="19" t="n">
-        <v>29</v>
-      </c>
-      <c r="B37" s="19" t="n">
-        <v>3433.93</v>
-      </c>
-      <c r="C37" s="19" t="n">
-        <v>185</v>
-      </c>
-      <c r="D37" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" s="19" t="n">
-        <v>3117.14</v>
-      </c>
-      <c r="F37" s="19" t="n">
-        <v>102191.78</v>
-      </c>
-      <c r="G37" s="19" t="n">
-        <v>5885.52</v>
-      </c>
-      <c r="H37" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" s="19" t="n">
-        <v>105308.92</v>
-      </c>
-      <c r="L37" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" s="20" t="n">
-        <v>1.781832</v>
-      </c>
-      <c r="S37" s="19" t="n">
-        <v>105440.71</v>
-      </c>
-      <c r="T37" s="19" t="n">
-        <v>105308.92</v>
-      </c>
-      <c r="U37" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V37" s="19" t="n">
+    <row r="38" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="B38" s="19" t="n">
+        <v>4501.31</v>
+      </c>
+      <c r="C38" s="19" t="n">
+        <v>759</v>
+      </c>
+      <c r="D38" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="19" t="n">
+        <v>2999.17</v>
+      </c>
+      <c r="F38" s="19" t="n">
+        <v>121820</v>
+      </c>
+      <c r="G38" s="19" t="n">
+        <v>6138.87</v>
+      </c>
+      <c r="H38" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="19" t="n">
+        <v>130203.37</v>
+      </c>
+      <c r="L38" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" s="20" t="n">
+        <v>1.25684</v>
+      </c>
+      <c r="S38" s="19" t="n">
+        <v>130946.51</v>
+      </c>
+      <c r="T38" s="19" t="n">
+        <v>130203.37</v>
+      </c>
+      <c r="U38" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" s="19" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="18" t="s">
+    <row r="39" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="B38" s="18" t="s">
+      <c r="B39" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="C38" s="18" t="s">
+      <c r="C39" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="D38" s="18" t="s">
+      <c r="D39" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="E38" s="18" t="s">
+      <c r="E39" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="F38" s="18" t="s">
+      <c r="F39" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="G38" s="18" t="s">
+      <c r="G39" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="H38" s="18" t="s">
+      <c r="H39" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="I38" s="18" t="s">
+      <c r="I39" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="J38" s="18" t="s">
+      <c r="J39" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="K38" s="18" t="s">
-        <v>206</v>
-      </c>
-      <c r="L38" s="18" t="s">
-        <v>207</v>
-      </c>
-      <c r="M38" s="18" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="19" t="n">
-        <v>228.27</v>
-      </c>
-      <c r="B39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" s="19" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="E39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" s="19" t="n">
-        <v>0</v>
+      <c r="K39" s="18" t="s">
+        <v>213</v>
+      </c>
+      <c r="L39" s="18" t="s">
+        <v>214</v>
+      </c>
+      <c r="M39" s="18" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="4"/>
+      <c r="A40" s="19" t="n">
+        <v>204.85</v>
+      </c>
+      <c r="B40" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="19" t="n">
+        <v>48.07</v>
+      </c>
+      <c r="E40" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
-    <row r="41" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="21" t="s">
-        <v>209</v>
-      </c>
-      <c r="B41" s="21"/>
-      <c r="C41" s="21"/>
-      <c r="D41" s="21"/>
-      <c r="E41" s="21"/>
-      <c r="F41" s="21"/>
-      <c r="G41" s="21"/>
-      <c r="H41" s="21"/>
-      <c r="I41" s="21"/>
-      <c r="J41" s="21"/>
-      <c r="K41" s="21"/>
-      <c r="L41" s="21"/>
-      <c r="M41" s="21"/>
-      <c r="N41" s="21"/>
-      <c r="O41" s="21"/>
-      <c r="P41" s="21"/>
-      <c r="Q41" s="21"/>
-      <c r="R41" s="21"/>
-      <c r="S41" s="21"/>
-      <c r="T41" s="21"/>
-      <c r="U41" s="21"/>
-      <c r="V41" s="21"/>
-      <c r="W41" s="21"/>
-      <c r="X41" s="21"/>
-      <c r="Y41" s="21"/>
-      <c r="Z41" s="21"/>
-      <c r="AA41" s="21"/>
-      <c r="AB41" s="21"/>
-      <c r="AC41" s="21"/>
-      <c r="AD41" s="21"/>
-      <c r="AE41" s="21"/>
-      <c r="AF41" s="21"/>
-      <c r="AG41" s="21"/>
-      <c r="AH41" s="21"/>
-      <c r="AI41" s="21"/>
-      <c r="AJ41" s="21"/>
-      <c r="AK41" s="21"/>
-      <c r="AL41" s="21"/>
-      <c r="AM41" s="21"/>
-      <c r="AN41" s="21"/>
-      <c r="AO41" s="21"/>
-      <c r="AP41" s="21"/>
-      <c r="AQ41" s="21"/>
-      <c r="AR41" s="21"/>
-      <c r="AS41" s="21"/>
-      <c r="AT41" s="21"/>
-      <c r="AU41" s="21"/>
-      <c r="AV41" s="21"/>
-      <c r="AW41" s="21"/>
-      <c r="AX41" s="21"/>
-      <c r="AY41" s="21"/>
-      <c r="AZ41" s="21"/>
-      <c r="BA41" s="21"/>
-      <c r="BB41" s="21"/>
-      <c r="BC41" s="21"/>
-      <c r="BD41" s="21"/>
-      <c r="BE41" s="21"/>
-      <c r="BF41" s="21"/>
-      <c r="BG41" s="21"/>
-      <c r="BH41" s="21"/>
-      <c r="BI41" s="21"/>
-      <c r="BJ41" s="21"/>
-      <c r="BK41" s="21"/>
-      <c r="BL41" s="21"/>
-      <c r="BM41" s="21"/>
+    <row r="41" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="4"/>
     </row>
-    <row r="42" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B42" s="4"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="4"/>
-      <c r="E42" s="4"/>
-      <c r="F42" s="4"/>
-      <c r="G42" s="4"/>
-      <c r="H42" s="4"/>
-      <c r="I42" s="4"/>
-      <c r="J42" s="4"/>
-      <c r="K42" s="4"/>
-      <c r="L42" s="4"/>
-      <c r="M42" s="4"/>
-      <c r="N42" s="4"/>
-      <c r="O42" s="4"/>
-      <c r="P42" s="4"/>
-      <c r="Q42" s="4"/>
-      <c r="R42" s="4"/>
-      <c r="S42" s="4"/>
-      <c r="T42" s="4"/>
-      <c r="U42" s="4"/>
-      <c r="V42" s="4"/>
-      <c r="W42" s="4"/>
-      <c r="X42" s="4"/>
-      <c r="Y42" s="4"/>
-      <c r="Z42" s="4"/>
-      <c r="AA42" s="4"/>
-      <c r="AB42" s="4"/>
-      <c r="AC42" s="4"/>
-      <c r="AD42" s="4"/>
-      <c r="AE42" s="4"/>
-      <c r="AF42" s="4"/>
-      <c r="AG42" s="4"/>
-      <c r="AH42" s="4"/>
-      <c r="AI42" s="4"/>
-      <c r="AJ42" s="4"/>
-      <c r="AK42" s="4"/>
-      <c r="AL42" s="4"/>
-      <c r="AM42" s="4"/>
-      <c r="AN42" s="4"/>
-      <c r="AO42" s="4"/>
-      <c r="AP42" s="4"/>
-      <c r="AQ42" s="4"/>
-      <c r="AR42" s="4"/>
-      <c r="AS42" s="4"/>
-      <c r="AT42" s="4"/>
-      <c r="AU42" s="4"/>
-      <c r="AV42" s="4"/>
-      <c r="AW42" s="4"/>
-      <c r="AX42" s="4"/>
-      <c r="AY42" s="4"/>
-      <c r="AZ42" s="4"/>
-      <c r="BA42" s="4"/>
-      <c r="BB42" s="4"/>
-      <c r="BC42" s="4"/>
-      <c r="BD42" s="4"/>
-      <c r="BE42" s="4"/>
-      <c r="BF42" s="4"/>
-      <c r="BG42" s="4"/>
-      <c r="BH42" s="4"/>
-      <c r="BI42" s="4"/>
-      <c r="BJ42" s="4"/>
-      <c r="BK42" s="4"/>
-      <c r="BL42" s="4"/>
-      <c r="BM42" s="4"/>
+    <row r="42" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="21" t="s">
+        <v>216</v>
+      </c>
+      <c r="B42" s="21"/>
+      <c r="C42" s="21"/>
+      <c r="D42" s="21"/>
+      <c r="E42" s="21"/>
+      <c r="F42" s="21"/>
+      <c r="G42" s="21"/>
+      <c r="H42" s="21"/>
+      <c r="I42" s="21"/>
+      <c r="J42" s="21"/>
+      <c r="K42" s="21"/>
+      <c r="L42" s="21"/>
+      <c r="M42" s="21"/>
+      <c r="N42" s="21"/>
+      <c r="O42" s="21"/>
+      <c r="P42" s="21"/>
+      <c r="Q42" s="21"/>
+      <c r="R42" s="21"/>
+      <c r="S42" s="21"/>
+      <c r="T42" s="21"/>
+      <c r="U42" s="21"/>
+      <c r="V42" s="21"/>
+      <c r="W42" s="21"/>
+      <c r="X42" s="21"/>
+      <c r="Y42" s="21"/>
+      <c r="Z42" s="21"/>
+      <c r="AA42" s="21"/>
+      <c r="AB42" s="21"/>
+      <c r="AC42" s="21"/>
+      <c r="AD42" s="21"/>
+      <c r="AE42" s="21"/>
+      <c r="AF42" s="21"/>
+      <c r="AG42" s="21"/>
+      <c r="AH42" s="21"/>
+      <c r="AI42" s="21"/>
+      <c r="AJ42" s="21"/>
+      <c r="AK42" s="21"/>
+      <c r="AL42" s="21"/>
+      <c r="AM42" s="21"/>
+      <c r="AN42" s="21"/>
+      <c r="AO42" s="21"/>
+      <c r="AP42" s="21"/>
+      <c r="AQ42" s="21"/>
+      <c r="AR42" s="21"/>
+      <c r="AS42" s="21"/>
+      <c r="AT42" s="21"/>
+      <c r="AU42" s="21"/>
+      <c r="AV42" s="21"/>
+      <c r="AW42" s="21"/>
+      <c r="AX42" s="21"/>
+      <c r="AY42" s="21"/>
+      <c r="AZ42" s="21"/>
+      <c r="BA42" s="21"/>
+      <c r="BB42" s="21"/>
+      <c r="BC42" s="21"/>
+      <c r="BD42" s="21"/>
+      <c r="BE42" s="21"/>
+      <c r="BF42" s="21"/>
+      <c r="BG42" s="21"/>
+      <c r="BH42" s="21"/>
+      <c r="BI42" s="21"/>
+      <c r="BJ42" s="21"/>
+      <c r="BK42" s="21"/>
+      <c r="BL42" s="21"/>
+      <c r="BM42" s="21"/>
     </row>
     <row r="43" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="s">
-        <v>210</v>
+        <v>75</v>
       </c>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
@@ -23230,7 +23373,7 @@
     </row>
     <row r="44" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
@@ -23299,7 +23442,7 @@
     </row>
     <row r="45" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="4" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
@@ -23368,7 +23511,7 @@
     </row>
     <row r="46" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="4" t="s">
-        <v>22</v>
+        <v>219</v>
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
@@ -23437,7 +23580,7 @@
     </row>
     <row r="47" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="s">
-        <v>213</v>
+        <v>22</v>
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
@@ -23506,7 +23649,7 @@
     </row>
     <row r="48" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="4" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
@@ -23575,7 +23718,7 @@
     </row>
     <row r="49" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="4" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
@@ -23644,7 +23787,7 @@
     </row>
     <row r="50" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="4" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
@@ -23713,7 +23856,7 @@
     </row>
     <row r="51" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="4" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
@@ -23780,8 +23923,77 @@
       <c r="BL51" s="4"/>
       <c r="BM51" s="4"/>
     </row>
+    <row r="52" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="B52" s="4"/>
+      <c r="C52" s="4"/>
+      <c r="D52" s="4"/>
+      <c r="E52" s="4"/>
+      <c r="F52" s="4"/>
+      <c r="G52" s="4"/>
+      <c r="H52" s="4"/>
+      <c r="I52" s="4"/>
+      <c r="J52" s="4"/>
+      <c r="K52" s="4"/>
+      <c r="L52" s="4"/>
+      <c r="M52" s="4"/>
+      <c r="N52" s="4"/>
+      <c r="O52" s="4"/>
+      <c r="P52" s="4"/>
+      <c r="Q52" s="4"/>
+      <c r="R52" s="4"/>
+      <c r="S52" s="4"/>
+      <c r="T52" s="4"/>
+      <c r="U52" s="4"/>
+      <c r="V52" s="4"/>
+      <c r="W52" s="4"/>
+      <c r="X52" s="4"/>
+      <c r="Y52" s="4"/>
+      <c r="Z52" s="4"/>
+      <c r="AA52" s="4"/>
+      <c r="AB52" s="4"/>
+      <c r="AC52" s="4"/>
+      <c r="AD52" s="4"/>
+      <c r="AE52" s="4"/>
+      <c r="AF52" s="4"/>
+      <c r="AG52" s="4"/>
+      <c r="AH52" s="4"/>
+      <c r="AI52" s="4"/>
+      <c r="AJ52" s="4"/>
+      <c r="AK52" s="4"/>
+      <c r="AL52" s="4"/>
+      <c r="AM52" s="4"/>
+      <c r="AN52" s="4"/>
+      <c r="AO52" s="4"/>
+      <c r="AP52" s="4"/>
+      <c r="AQ52" s="4"/>
+      <c r="AR52" s="4"/>
+      <c r="AS52" s="4"/>
+      <c r="AT52" s="4"/>
+      <c r="AU52" s="4"/>
+      <c r="AV52" s="4"/>
+      <c r="AW52" s="4"/>
+      <c r="AX52" s="4"/>
+      <c r="AY52" s="4"/>
+      <c r="AZ52" s="4"/>
+      <c r="BA52" s="4"/>
+      <c r="BB52" s="4"/>
+      <c r="BC52" s="4"/>
+      <c r="BD52" s="4"/>
+      <c r="BE52" s="4"/>
+      <c r="BF52" s="4"/>
+      <c r="BG52" s="4"/>
+      <c r="BH52" s="4"/>
+      <c r="BI52" s="4"/>
+      <c r="BJ52" s="4"/>
+      <c r="BK52" s="4"/>
+      <c r="BL52" s="4"/>
+      <c r="BM52" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="45">
+  <mergeCells count="46">
     <mergeCell ref="A1:BI1"/>
     <mergeCell ref="BJ1:BM1"/>
     <mergeCell ref="A2:BM2"/>
@@ -23815,8 +24027,8 @@
     <mergeCell ref="B31:E31"/>
     <mergeCell ref="B32:E32"/>
     <mergeCell ref="B33:E33"/>
-    <mergeCell ref="A35:V35"/>
-    <mergeCell ref="A41:BM41"/>
+    <mergeCell ref="B34:E34"/>
+    <mergeCell ref="A36:V36"/>
     <mergeCell ref="A42:BM42"/>
     <mergeCell ref="A43:BM43"/>
     <mergeCell ref="A44:BM44"/>
@@ -23827,6 +24039,7 @@
     <mergeCell ref="A49:BM49"/>
     <mergeCell ref="A50:BM50"/>
     <mergeCell ref="A51:BM51"/>
+    <mergeCell ref="A52:BM52"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>

--- a/tratando_tabelas/finitura/entradas_finitura.xlsx
+++ b/tratando_tabelas/finitura/entradas_finitura.xlsx
@@ -25,7 +25,7 @@
     <t xml:space="preserve">Santri ADM 1.1.5.7 R1</t>
   </si>
   <si>
-    <t xml:space="preserve">Emitido em: 05/05/2026 07:39:20</t>
+    <t xml:space="preserve">Emitido em: 05/05/2026 10:35:14</t>
   </si>
   <si>
     <t xml:space="preserve">Relação de entradas - Sintético</t>

--- a/tratando_tabelas/finitura/entradas_finitura.xlsx
+++ b/tratando_tabelas/finitura/entradas_finitura.xlsx
@@ -20,12 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1312" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1472" uniqueCount="241">
   <si>
     <t xml:space="preserve">Santri ADM 1.1.5.7 R1</t>
   </si>
   <si>
-    <t xml:space="preserve">Emitido em: 05/05/2026 10:35:14</t>
+    <t xml:space="preserve">Emitido em: 06/05/2026 08:38:37</t>
   </si>
   <si>
     <t xml:space="preserve">Relação de entradas - Sintético</t>
@@ -638,6 +638,54 @@
   </si>
   <si>
     <t xml:space="preserve">42260400700221000253550010000108841638050409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">632.793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.116,85</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006327931688529359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.715 - LUMIERE COMERCIO INTERNACIONAL LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.485,60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260424855633000140550010000763681140081427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.850 - DEXCO S.A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">976,79</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260497837181005378550010001611641514144027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">632.423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">846,74</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006324231892898250</t>
   </si>
   <si>
     <t xml:space="preserve">Total geral</t>
@@ -16883,7 +16931,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BM52"/>
+  <dimension ref="A1:BM56"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="18"/>
@@ -22984,603 +23032,1091 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="4"/>
+      <c r="A35" s="8" t="n">
+        <v>306675</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="9"/>
+      <c r="F35" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="G35" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H35" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="I35" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="J35" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="K35" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L35" s="12" t="n">
+        <v>3116.85</v>
+      </c>
+      <c r="M35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O35" s="12" t="n">
+        <v>3116.85</v>
+      </c>
+      <c r="P35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="13" t="n">
+        <v>0.011766</v>
+      </c>
+      <c r="R35" s="12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" s="14" t="s">
+        <v>209</v>
+      </c>
+      <c r="U35" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V35" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="W35" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X35" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="Y35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" s="12" t="n">
+        <v>3116.85</v>
+      </c>
+      <c r="AA35" s="12" t="n">
+        <v>218.18</v>
+      </c>
+      <c r="AB35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ35" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM35" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN35" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO35" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP35" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ35" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR35" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS35" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT35" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU35" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV35" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW35" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX35" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY35" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ35" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA35" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB35" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC35" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD35" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE35" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF35" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG35" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH35" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI35" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ35" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="BK35" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL35" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM35" s="16" t="s">
+        <v>80</v>
+      </c>
     </row>
-    <row r="36" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="17" t="s">
-        <v>206</v>
-      </c>
-      <c r="B36" s="17"/>
-      <c r="C36" s="17"/>
-      <c r="D36" s="17"/>
-      <c r="E36" s="17"/>
-      <c r="F36" s="17"/>
-      <c r="G36" s="17"/>
-      <c r="H36" s="17"/>
-      <c r="I36" s="17"/>
-      <c r="J36" s="17"/>
-      <c r="K36" s="17"/>
-      <c r="L36" s="17"/>
-      <c r="M36" s="17"/>
-      <c r="N36" s="17"/>
-      <c r="O36" s="17"/>
-      <c r="P36" s="17"/>
-      <c r="Q36" s="17"/>
-      <c r="R36" s="17"/>
-      <c r="S36" s="17"/>
-      <c r="T36" s="17"/>
-      <c r="U36" s="17"/>
-      <c r="V36" s="17"/>
+    <row r="36" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="8" t="n">
+        <v>306713</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="G36" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="H36" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="I36" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="J36" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="K36" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L36" s="12" t="n">
+        <v>3485.6</v>
+      </c>
+      <c r="M36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O36" s="12" t="n">
+        <v>3288.3</v>
+      </c>
+      <c r="P36" s="12" t="n">
+        <v>197.3</v>
+      </c>
+      <c r="Q36" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="S36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="U36" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V36" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="W36" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X36" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="Y36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" s="12" t="n">
+        <v>3485.6</v>
+      </c>
+      <c r="AA36" s="12" t="n">
+        <v>139.42</v>
+      </c>
+      <c r="AB36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ36" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM36" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN36" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO36" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP36" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ36" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR36" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS36" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT36" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU36" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV36" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW36" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX36" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY36" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ36" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA36" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB36" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC36" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD36" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE36" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF36" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG36" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH36" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI36" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ36" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="BK36" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL36" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM36" s="16" t="s">
+        <v>80</v>
+      </c>
     </row>
-    <row r="37" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="18" t="s">
+    <row r="37" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="8" t="n">
+        <v>306724</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="G37" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="H37" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="I37" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="B37" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C37" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D37" s="18" t="s">
-        <v>208</v>
-      </c>
-      <c r="E37" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F37" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="G37" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="H37" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="I37" s="18" t="s">
-        <v>209</v>
-      </c>
-      <c r="J37" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="K37" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="L37" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="M37" s="18" t="s">
-        <v>210</v>
-      </c>
-      <c r="N37" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="O37" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="P37" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q37" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="R37" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="S37" s="18" t="s">
-        <v>211</v>
-      </c>
-      <c r="T37" s="18" t="s">
-        <v>212</v>
-      </c>
-      <c r="U37" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="V37" s="18" t="s">
-        <v>37</v>
+      <c r="J37" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K37" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L37" s="12" t="n">
+        <v>976.79</v>
+      </c>
+      <c r="M37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="O37" s="12" t="n">
+        <v>970.48</v>
+      </c>
+      <c r="P37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" s="14" t="s">
+        <v>217</v>
+      </c>
+      <c r="U37" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X37" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="Y37" s="12" t="n">
+        <v>6.31</v>
+      </c>
+      <c r="Z37" s="12" t="n">
+        <v>976.79</v>
+      </c>
+      <c r="AA37" s="12" t="n">
+        <v>68.38</v>
+      </c>
+      <c r="AB37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ37" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM37" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN37" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO37" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP37" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ37" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR37" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS37" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT37" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU37" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV37" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW37" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX37" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="AY37" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ37" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA37" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB37" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC37" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD37" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE37" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF37" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG37" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH37" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI37" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ37" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="BK37" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL37" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM37" s="16" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="19" t="n">
+      <c r="A38" s="8" t="n">
+        <v>306726</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C38" s="9"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="9"/>
+      <c r="F38" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="G38" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H38" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="I38" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="J38" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="K38" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L38" s="12" t="n">
+        <v>846.74</v>
+      </c>
+      <c r="M38" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O38" s="12" t="n">
+        <v>846.74</v>
+      </c>
+      <c r="P38" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" s="12" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="S38" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="U38" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V38" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="W38" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X38" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="Y38" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" s="12" t="n">
+        <v>846.74</v>
+      </c>
+      <c r="AA38" s="12" t="n">
+        <v>59.27</v>
+      </c>
+      <c r="AB38" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI38" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ38" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK38" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL38" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM38" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN38" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO38" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP38" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ38" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR38" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS38" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT38" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU38" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV38" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW38" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX38" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY38" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ38" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA38" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB38" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC38" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD38" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE38" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF38" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG38" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH38" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI38" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ38" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="BK38" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL38" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM38" s="16" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="4"/>
+    </row>
+    <row r="40" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="17" t="s">
+        <v>222</v>
+      </c>
+      <c r="B40" s="17"/>
+      <c r="C40" s="17"/>
+      <c r="D40" s="17"/>
+      <c r="E40" s="17"/>
+      <c r="F40" s="17"/>
+      <c r="G40" s="17"/>
+      <c r="H40" s="17"/>
+      <c r="I40" s="17"/>
+      <c r="J40" s="17"/>
+      <c r="K40" s="17"/>
+      <c r="L40" s="17"/>
+      <c r="M40" s="17"/>
+      <c r="N40" s="17"/>
+      <c r="O40" s="17"/>
+      <c r="P40" s="17"/>
+      <c r="Q40" s="17"/>
+      <c r="R40" s="17"/>
+      <c r="S40" s="17"/>
+      <c r="T40" s="17"/>
+      <c r="U40" s="17"/>
+      <c r="V40" s="17"/>
+    </row>
+    <row r="41" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="18" t="s">
+        <v>223</v>
+      </c>
+      <c r="B41" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C41" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D41" s="18" t="s">
+        <v>224</v>
+      </c>
+      <c r="E41" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F41" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="G41" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H41" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="I41" s="18" t="s">
+        <v>225</v>
+      </c>
+      <c r="J41" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="K41" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="L41" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="B38" s="19" t="n">
+      <c r="M41" s="18" t="s">
+        <v>226</v>
+      </c>
+      <c r="N41" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="O41" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="P41" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q41" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="R41" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="S41" s="18" t="s">
+        <v>227</v>
+      </c>
+      <c r="T41" s="18" t="s">
+        <v>228</v>
+      </c>
+      <c r="U41" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="V41" s="18" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="19" t="n">
+        <v>34</v>
+      </c>
+      <c r="B42" s="19" t="n">
         <v>4501.31</v>
       </c>
-      <c r="C38" s="19" t="n">
-        <v>759</v>
-      </c>
-      <c r="D38" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" s="19" t="n">
-        <v>2999.17</v>
-      </c>
-      <c r="F38" s="19" t="n">
-        <v>121820</v>
-      </c>
-      <c r="G38" s="19" t="n">
-        <v>6138.87</v>
-      </c>
-      <c r="H38" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" s="19" t="n">
-        <v>130203.37</v>
-      </c>
-      <c r="L38" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" s="20" t="n">
-        <v>1.25684</v>
-      </c>
-      <c r="S38" s="19" t="n">
-        <v>130946.51</v>
-      </c>
-      <c r="T38" s="19" t="n">
-        <v>130203.37</v>
-      </c>
-      <c r="U38" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" s="19" t="n">
+      <c r="C42" s="19" t="n">
+        <v>956.3</v>
+      </c>
+      <c r="D42" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="19" t="n">
+        <v>3005.48</v>
+      </c>
+      <c r="F42" s="19" t="n">
+        <v>130245.98</v>
+      </c>
+      <c r="G42" s="19" t="n">
+        <v>6624.12</v>
+      </c>
+      <c r="H42" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" s="19" t="n">
+        <v>138629.35</v>
+      </c>
+      <c r="L42" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" s="20" t="n">
+        <v>1.268606</v>
+      </c>
+      <c r="S42" s="19" t="n">
+        <v>139168.88</v>
+      </c>
+      <c r="T42" s="19" t="n">
+        <v>138629.35</v>
+      </c>
+      <c r="U42" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" s="19" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="18" t="s">
+    <row r="43" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="B39" s="18" t="s">
+      <c r="B43" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="C39" s="18" t="s">
+      <c r="C43" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="D39" s="18" t="s">
+      <c r="D43" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="E39" s="18" t="s">
+      <c r="E43" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="F39" s="18" t="s">
+      <c r="F43" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="G39" s="18" t="s">
+      <c r="G43" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="H39" s="18" t="s">
+      <c r="H43" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="I39" s="18" t="s">
+      <c r="I43" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="J39" s="18" t="s">
+      <c r="J43" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="K39" s="18" t="s">
-        <v>213</v>
-      </c>
-      <c r="L39" s="18" t="s">
-        <v>214</v>
-      </c>
-      <c r="M39" s="18" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="19" t="n">
-        <v>204.85</v>
-      </c>
-      <c r="B40" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C40" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" s="19" t="n">
-        <v>48.07</v>
-      </c>
-      <c r="E40" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" s="19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="4"/>
-    </row>
-    <row r="42" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="21" t="s">
-        <v>216</v>
-      </c>
-      <c r="B42" s="21"/>
-      <c r="C42" s="21"/>
-      <c r="D42" s="21"/>
-      <c r="E42" s="21"/>
-      <c r="F42" s="21"/>
-      <c r="G42" s="21"/>
-      <c r="H42" s="21"/>
-      <c r="I42" s="21"/>
-      <c r="J42" s="21"/>
-      <c r="K42" s="21"/>
-      <c r="L42" s="21"/>
-      <c r="M42" s="21"/>
-      <c r="N42" s="21"/>
-      <c r="O42" s="21"/>
-      <c r="P42" s="21"/>
-      <c r="Q42" s="21"/>
-      <c r="R42" s="21"/>
-      <c r="S42" s="21"/>
-      <c r="T42" s="21"/>
-      <c r="U42" s="21"/>
-      <c r="V42" s="21"/>
-      <c r="W42" s="21"/>
-      <c r="X42" s="21"/>
-      <c r="Y42" s="21"/>
-      <c r="Z42" s="21"/>
-      <c r="AA42" s="21"/>
-      <c r="AB42" s="21"/>
-      <c r="AC42" s="21"/>
-      <c r="AD42" s="21"/>
-      <c r="AE42" s="21"/>
-      <c r="AF42" s="21"/>
-      <c r="AG42" s="21"/>
-      <c r="AH42" s="21"/>
-      <c r="AI42" s="21"/>
-      <c r="AJ42" s="21"/>
-      <c r="AK42" s="21"/>
-      <c r="AL42" s="21"/>
-      <c r="AM42" s="21"/>
-      <c r="AN42" s="21"/>
-      <c r="AO42" s="21"/>
-      <c r="AP42" s="21"/>
-      <c r="AQ42" s="21"/>
-      <c r="AR42" s="21"/>
-      <c r="AS42" s="21"/>
-      <c r="AT42" s="21"/>
-      <c r="AU42" s="21"/>
-      <c r="AV42" s="21"/>
-      <c r="AW42" s="21"/>
-      <c r="AX42" s="21"/>
-      <c r="AY42" s="21"/>
-      <c r="AZ42" s="21"/>
-      <c r="BA42" s="21"/>
-      <c r="BB42" s="21"/>
-      <c r="BC42" s="21"/>
-      <c r="BD42" s="21"/>
-      <c r="BE42" s="21"/>
-      <c r="BF42" s="21"/>
-      <c r="BG42" s="21"/>
-      <c r="BH42" s="21"/>
-      <c r="BI42" s="21"/>
-      <c r="BJ42" s="21"/>
-      <c r="BK42" s="21"/>
-      <c r="BL42" s="21"/>
-      <c r="BM42" s="21"/>
-    </row>
-    <row r="43" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B43" s="4"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="4"/>
-      <c r="E43" s="4"/>
-      <c r="F43" s="4"/>
-      <c r="G43" s="4"/>
-      <c r="H43" s="4"/>
-      <c r="I43" s="4"/>
-      <c r="J43" s="4"/>
-      <c r="K43" s="4"/>
-      <c r="L43" s="4"/>
-      <c r="M43" s="4"/>
-      <c r="N43" s="4"/>
-      <c r="O43" s="4"/>
-      <c r="P43" s="4"/>
-      <c r="Q43" s="4"/>
-      <c r="R43" s="4"/>
-      <c r="S43" s="4"/>
-      <c r="T43" s="4"/>
-      <c r="U43" s="4"/>
-      <c r="V43" s="4"/>
-      <c r="W43" s="4"/>
-      <c r="X43" s="4"/>
-      <c r="Y43" s="4"/>
-      <c r="Z43" s="4"/>
-      <c r="AA43" s="4"/>
-      <c r="AB43" s="4"/>
-      <c r="AC43" s="4"/>
-      <c r="AD43" s="4"/>
-      <c r="AE43" s="4"/>
-      <c r="AF43" s="4"/>
-      <c r="AG43" s="4"/>
-      <c r="AH43" s="4"/>
-      <c r="AI43" s="4"/>
-      <c r="AJ43" s="4"/>
-      <c r="AK43" s="4"/>
-      <c r="AL43" s="4"/>
-      <c r="AM43" s="4"/>
-      <c r="AN43" s="4"/>
-      <c r="AO43" s="4"/>
-      <c r="AP43" s="4"/>
-      <c r="AQ43" s="4"/>
-      <c r="AR43" s="4"/>
-      <c r="AS43" s="4"/>
-      <c r="AT43" s="4"/>
-      <c r="AU43" s="4"/>
-      <c r="AV43" s="4"/>
-      <c r="AW43" s="4"/>
-      <c r="AX43" s="4"/>
-      <c r="AY43" s="4"/>
-      <c r="AZ43" s="4"/>
-      <c r="BA43" s="4"/>
-      <c r="BB43" s="4"/>
-      <c r="BC43" s="4"/>
-      <c r="BD43" s="4"/>
-      <c r="BE43" s="4"/>
-      <c r="BF43" s="4"/>
-      <c r="BG43" s="4"/>
-      <c r="BH43" s="4"/>
-      <c r="BI43" s="4"/>
-      <c r="BJ43" s="4"/>
-      <c r="BK43" s="4"/>
-      <c r="BL43" s="4"/>
-      <c r="BM43" s="4"/>
+      <c r="K43" s="18" t="s">
+        <v>229</v>
+      </c>
+      <c r="L43" s="18" t="s">
+        <v>230</v>
+      </c>
+      <c r="M43" s="18" t="s">
+        <v>231</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="B44" s="4"/>
-      <c r="C44" s="4"/>
-      <c r="D44" s="4"/>
-      <c r="E44" s="4"/>
-      <c r="F44" s="4"/>
-      <c r="G44" s="4"/>
-      <c r="H44" s="4"/>
-      <c r="I44" s="4"/>
-      <c r="J44" s="4"/>
-      <c r="K44" s="4"/>
-      <c r="L44" s="4"/>
-      <c r="M44" s="4"/>
-      <c r="N44" s="4"/>
-      <c r="O44" s="4"/>
-      <c r="P44" s="4"/>
-      <c r="Q44" s="4"/>
-      <c r="R44" s="4"/>
-      <c r="S44" s="4"/>
-      <c r="T44" s="4"/>
-      <c r="U44" s="4"/>
-      <c r="V44" s="4"/>
-      <c r="W44" s="4"/>
-      <c r="X44" s="4"/>
-      <c r="Y44" s="4"/>
-      <c r="Z44" s="4"/>
-      <c r="AA44" s="4"/>
-      <c r="AB44" s="4"/>
-      <c r="AC44" s="4"/>
-      <c r="AD44" s="4"/>
-      <c r="AE44" s="4"/>
-      <c r="AF44" s="4"/>
-      <c r="AG44" s="4"/>
-      <c r="AH44" s="4"/>
-      <c r="AI44" s="4"/>
-      <c r="AJ44" s="4"/>
-      <c r="AK44" s="4"/>
-      <c r="AL44" s="4"/>
-      <c r="AM44" s="4"/>
-      <c r="AN44" s="4"/>
-      <c r="AO44" s="4"/>
-      <c r="AP44" s="4"/>
-      <c r="AQ44" s="4"/>
-      <c r="AR44" s="4"/>
-      <c r="AS44" s="4"/>
-      <c r="AT44" s="4"/>
-      <c r="AU44" s="4"/>
-      <c r="AV44" s="4"/>
-      <c r="AW44" s="4"/>
-      <c r="AX44" s="4"/>
-      <c r="AY44" s="4"/>
-      <c r="AZ44" s="4"/>
-      <c r="BA44" s="4"/>
-      <c r="BB44" s="4"/>
-      <c r="BC44" s="4"/>
-      <c r="BD44" s="4"/>
-      <c r="BE44" s="4"/>
-      <c r="BF44" s="4"/>
-      <c r="BG44" s="4"/>
-      <c r="BH44" s="4"/>
-      <c r="BI44" s="4"/>
-      <c r="BJ44" s="4"/>
-      <c r="BK44" s="4"/>
-      <c r="BL44" s="4"/>
-      <c r="BM44" s="4"/>
+      <c r="A44" s="19" t="n">
+        <v>223.38</v>
+      </c>
+      <c r="B44" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="19" t="n">
+        <v>46.67</v>
+      </c>
+      <c r="E44" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="B45" s="4"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="4"/>
-      <c r="E45" s="4"/>
-      <c r="F45" s="4"/>
-      <c r="G45" s="4"/>
-      <c r="H45" s="4"/>
-      <c r="I45" s="4"/>
-      <c r="J45" s="4"/>
-      <c r="K45" s="4"/>
-      <c r="L45" s="4"/>
-      <c r="M45" s="4"/>
-      <c r="N45" s="4"/>
-      <c r="O45" s="4"/>
-      <c r="P45" s="4"/>
-      <c r="Q45" s="4"/>
-      <c r="R45" s="4"/>
-      <c r="S45" s="4"/>
-      <c r="T45" s="4"/>
-      <c r="U45" s="4"/>
-      <c r="V45" s="4"/>
-      <c r="W45" s="4"/>
-      <c r="X45" s="4"/>
-      <c r="Y45" s="4"/>
-      <c r="Z45" s="4"/>
-      <c r="AA45" s="4"/>
-      <c r="AB45" s="4"/>
-      <c r="AC45" s="4"/>
-      <c r="AD45" s="4"/>
-      <c r="AE45" s="4"/>
-      <c r="AF45" s="4"/>
-      <c r="AG45" s="4"/>
-      <c r="AH45" s="4"/>
-      <c r="AI45" s="4"/>
-      <c r="AJ45" s="4"/>
-      <c r="AK45" s="4"/>
-      <c r="AL45" s="4"/>
-      <c r="AM45" s="4"/>
-      <c r="AN45" s="4"/>
-      <c r="AO45" s="4"/>
-      <c r="AP45" s="4"/>
-      <c r="AQ45" s="4"/>
-      <c r="AR45" s="4"/>
-      <c r="AS45" s="4"/>
-      <c r="AT45" s="4"/>
-      <c r="AU45" s="4"/>
-      <c r="AV45" s="4"/>
-      <c r="AW45" s="4"/>
-      <c r="AX45" s="4"/>
-      <c r="AY45" s="4"/>
-      <c r="AZ45" s="4"/>
-      <c r="BA45" s="4"/>
-      <c r="BB45" s="4"/>
-      <c r="BC45" s="4"/>
-      <c r="BD45" s="4"/>
-      <c r="BE45" s="4"/>
-      <c r="BF45" s="4"/>
-      <c r="BG45" s="4"/>
-      <c r="BH45" s="4"/>
-      <c r="BI45" s="4"/>
-      <c r="BJ45" s="4"/>
-      <c r="BK45" s="4"/>
-      <c r="BL45" s="4"/>
-      <c r="BM45" s="4"/>
+      <c r="A45" s="4"/>
     </row>
-    <row r="46" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="B46" s="4"/>
-      <c r="C46" s="4"/>
-      <c r="D46" s="4"/>
-      <c r="E46" s="4"/>
-      <c r="F46" s="4"/>
-      <c r="G46" s="4"/>
-      <c r="H46" s="4"/>
-      <c r="I46" s="4"/>
-      <c r="J46" s="4"/>
-      <c r="K46" s="4"/>
-      <c r="L46" s="4"/>
-      <c r="M46" s="4"/>
-      <c r="N46" s="4"/>
-      <c r="O46" s="4"/>
-      <c r="P46" s="4"/>
-      <c r="Q46" s="4"/>
-      <c r="R46" s="4"/>
-      <c r="S46" s="4"/>
-      <c r="T46" s="4"/>
-      <c r="U46" s="4"/>
-      <c r="V46" s="4"/>
-      <c r="W46" s="4"/>
-      <c r="X46" s="4"/>
-      <c r="Y46" s="4"/>
-      <c r="Z46" s="4"/>
-      <c r="AA46" s="4"/>
-      <c r="AB46" s="4"/>
-      <c r="AC46" s="4"/>
-      <c r="AD46" s="4"/>
-      <c r="AE46" s="4"/>
-      <c r="AF46" s="4"/>
-      <c r="AG46" s="4"/>
-      <c r="AH46" s="4"/>
-      <c r="AI46" s="4"/>
-      <c r="AJ46" s="4"/>
-      <c r="AK46" s="4"/>
-      <c r="AL46" s="4"/>
-      <c r="AM46" s="4"/>
-      <c r="AN46" s="4"/>
-      <c r="AO46" s="4"/>
-      <c r="AP46" s="4"/>
-      <c r="AQ46" s="4"/>
-      <c r="AR46" s="4"/>
-      <c r="AS46" s="4"/>
-      <c r="AT46" s="4"/>
-      <c r="AU46" s="4"/>
-      <c r="AV46" s="4"/>
-      <c r="AW46" s="4"/>
-      <c r="AX46" s="4"/>
-      <c r="AY46" s="4"/>
-      <c r="AZ46" s="4"/>
-      <c r="BA46" s="4"/>
-      <c r="BB46" s="4"/>
-      <c r="BC46" s="4"/>
-      <c r="BD46" s="4"/>
-      <c r="BE46" s="4"/>
-      <c r="BF46" s="4"/>
-      <c r="BG46" s="4"/>
-      <c r="BH46" s="4"/>
-      <c r="BI46" s="4"/>
-      <c r="BJ46" s="4"/>
-      <c r="BK46" s="4"/>
-      <c r="BL46" s="4"/>
-      <c r="BM46" s="4"/>
+    <row r="46" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="21" t="s">
+        <v>232</v>
+      </c>
+      <c r="B46" s="21"/>
+      <c r="C46" s="21"/>
+      <c r="D46" s="21"/>
+      <c r="E46" s="21"/>
+      <c r="F46" s="21"/>
+      <c r="G46" s="21"/>
+      <c r="H46" s="21"/>
+      <c r="I46" s="21"/>
+      <c r="J46" s="21"/>
+      <c r="K46" s="21"/>
+      <c r="L46" s="21"/>
+      <c r="M46" s="21"/>
+      <c r="N46" s="21"/>
+      <c r="O46" s="21"/>
+      <c r="P46" s="21"/>
+      <c r="Q46" s="21"/>
+      <c r="R46" s="21"/>
+      <c r="S46" s="21"/>
+      <c r="T46" s="21"/>
+      <c r="U46" s="21"/>
+      <c r="V46" s="21"/>
+      <c r="W46" s="21"/>
+      <c r="X46" s="21"/>
+      <c r="Y46" s="21"/>
+      <c r="Z46" s="21"/>
+      <c r="AA46" s="21"/>
+      <c r="AB46" s="21"/>
+      <c r="AC46" s="21"/>
+      <c r="AD46" s="21"/>
+      <c r="AE46" s="21"/>
+      <c r="AF46" s="21"/>
+      <c r="AG46" s="21"/>
+      <c r="AH46" s="21"/>
+      <c r="AI46" s="21"/>
+      <c r="AJ46" s="21"/>
+      <c r="AK46" s="21"/>
+      <c r="AL46" s="21"/>
+      <c r="AM46" s="21"/>
+      <c r="AN46" s="21"/>
+      <c r="AO46" s="21"/>
+      <c r="AP46" s="21"/>
+      <c r="AQ46" s="21"/>
+      <c r="AR46" s="21"/>
+      <c r="AS46" s="21"/>
+      <c r="AT46" s="21"/>
+      <c r="AU46" s="21"/>
+      <c r="AV46" s="21"/>
+      <c r="AW46" s="21"/>
+      <c r="AX46" s="21"/>
+      <c r="AY46" s="21"/>
+      <c r="AZ46" s="21"/>
+      <c r="BA46" s="21"/>
+      <c r="BB46" s="21"/>
+      <c r="BC46" s="21"/>
+      <c r="BD46" s="21"/>
+      <c r="BE46" s="21"/>
+      <c r="BF46" s="21"/>
+      <c r="BG46" s="21"/>
+      <c r="BH46" s="21"/>
+      <c r="BI46" s="21"/>
+      <c r="BJ46" s="21"/>
+      <c r="BK46" s="21"/>
+      <c r="BL46" s="21"/>
+      <c r="BM46" s="21"/>
     </row>
     <row r="47" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="s">
-        <v>22</v>
+        <v>75</v>
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
@@ -23649,7 +24185,7 @@
     </row>
     <row r="48" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="4" t="s">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
@@ -23718,7 +24254,7 @@
     </row>
     <row r="49" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="4" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
@@ -23787,7 +24323,7 @@
     </row>
     <row r="50" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="4" t="s">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
@@ -23856,7 +24392,7 @@
     </row>
     <row r="51" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="4" t="s">
-        <v>223</v>
+        <v>22</v>
       </c>
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
@@ -23925,7 +24461,7 @@
     </row>
     <row r="52" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="4" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
@@ -23992,8 +24528,284 @@
       <c r="BL52" s="4"/>
       <c r="BM52" s="4"/>
     </row>
+    <row r="53" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="B53" s="4"/>
+      <c r="C53" s="4"/>
+      <c r="D53" s="4"/>
+      <c r="E53" s="4"/>
+      <c r="F53" s="4"/>
+      <c r="G53" s="4"/>
+      <c r="H53" s="4"/>
+      <c r="I53" s="4"/>
+      <c r="J53" s="4"/>
+      <c r="K53" s="4"/>
+      <c r="L53" s="4"/>
+      <c r="M53" s="4"/>
+      <c r="N53" s="4"/>
+      <c r="O53" s="4"/>
+      <c r="P53" s="4"/>
+      <c r="Q53" s="4"/>
+      <c r="R53" s="4"/>
+      <c r="S53" s="4"/>
+      <c r="T53" s="4"/>
+      <c r="U53" s="4"/>
+      <c r="V53" s="4"/>
+      <c r="W53" s="4"/>
+      <c r="X53" s="4"/>
+      <c r="Y53" s="4"/>
+      <c r="Z53" s="4"/>
+      <c r="AA53" s="4"/>
+      <c r="AB53" s="4"/>
+      <c r="AC53" s="4"/>
+      <c r="AD53" s="4"/>
+      <c r="AE53" s="4"/>
+      <c r="AF53" s="4"/>
+      <c r="AG53" s="4"/>
+      <c r="AH53" s="4"/>
+      <c r="AI53" s="4"/>
+      <c r="AJ53" s="4"/>
+      <c r="AK53" s="4"/>
+      <c r="AL53" s="4"/>
+      <c r="AM53" s="4"/>
+      <c r="AN53" s="4"/>
+      <c r="AO53" s="4"/>
+      <c r="AP53" s="4"/>
+      <c r="AQ53" s="4"/>
+      <c r="AR53" s="4"/>
+      <c r="AS53" s="4"/>
+      <c r="AT53" s="4"/>
+      <c r="AU53" s="4"/>
+      <c r="AV53" s="4"/>
+      <c r="AW53" s="4"/>
+      <c r="AX53" s="4"/>
+      <c r="AY53" s="4"/>
+      <c r="AZ53" s="4"/>
+      <c r="BA53" s="4"/>
+      <c r="BB53" s="4"/>
+      <c r="BC53" s="4"/>
+      <c r="BD53" s="4"/>
+      <c r="BE53" s="4"/>
+      <c r="BF53" s="4"/>
+      <c r="BG53" s="4"/>
+      <c r="BH53" s="4"/>
+      <c r="BI53" s="4"/>
+      <c r="BJ53" s="4"/>
+      <c r="BK53" s="4"/>
+      <c r="BL53" s="4"/>
+      <c r="BM53" s="4"/>
+    </row>
+    <row r="54" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="B54" s="4"/>
+      <c r="C54" s="4"/>
+      <c r="D54" s="4"/>
+      <c r="E54" s="4"/>
+      <c r="F54" s="4"/>
+      <c r="G54" s="4"/>
+      <c r="H54" s="4"/>
+      <c r="I54" s="4"/>
+      <c r="J54" s="4"/>
+      <c r="K54" s="4"/>
+      <c r="L54" s="4"/>
+      <c r="M54" s="4"/>
+      <c r="N54" s="4"/>
+      <c r="O54" s="4"/>
+      <c r="P54" s="4"/>
+      <c r="Q54" s="4"/>
+      <c r="R54" s="4"/>
+      <c r="S54" s="4"/>
+      <c r="T54" s="4"/>
+      <c r="U54" s="4"/>
+      <c r="V54" s="4"/>
+      <c r="W54" s="4"/>
+      <c r="X54" s="4"/>
+      <c r="Y54" s="4"/>
+      <c r="Z54" s="4"/>
+      <c r="AA54" s="4"/>
+      <c r="AB54" s="4"/>
+      <c r="AC54" s="4"/>
+      <c r="AD54" s="4"/>
+      <c r="AE54" s="4"/>
+      <c r="AF54" s="4"/>
+      <c r="AG54" s="4"/>
+      <c r="AH54" s="4"/>
+      <c r="AI54" s="4"/>
+      <c r="AJ54" s="4"/>
+      <c r="AK54" s="4"/>
+      <c r="AL54" s="4"/>
+      <c r="AM54" s="4"/>
+      <c r="AN54" s="4"/>
+      <c r="AO54" s="4"/>
+      <c r="AP54" s="4"/>
+      <c r="AQ54" s="4"/>
+      <c r="AR54" s="4"/>
+      <c r="AS54" s="4"/>
+      <c r="AT54" s="4"/>
+      <c r="AU54" s="4"/>
+      <c r="AV54" s="4"/>
+      <c r="AW54" s="4"/>
+      <c r="AX54" s="4"/>
+      <c r="AY54" s="4"/>
+      <c r="AZ54" s="4"/>
+      <c r="BA54" s="4"/>
+      <c r="BB54" s="4"/>
+      <c r="BC54" s="4"/>
+      <c r="BD54" s="4"/>
+      <c r="BE54" s="4"/>
+      <c r="BF54" s="4"/>
+      <c r="BG54" s="4"/>
+      <c r="BH54" s="4"/>
+      <c r="BI54" s="4"/>
+      <c r="BJ54" s="4"/>
+      <c r="BK54" s="4"/>
+      <c r="BL54" s="4"/>
+      <c r="BM54" s="4"/>
+    </row>
+    <row r="55" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="B55" s="4"/>
+      <c r="C55" s="4"/>
+      <c r="D55" s="4"/>
+      <c r="E55" s="4"/>
+      <c r="F55" s="4"/>
+      <c r="G55" s="4"/>
+      <c r="H55" s="4"/>
+      <c r="I55" s="4"/>
+      <c r="J55" s="4"/>
+      <c r="K55" s="4"/>
+      <c r="L55" s="4"/>
+      <c r="M55" s="4"/>
+      <c r="N55" s="4"/>
+      <c r="O55" s="4"/>
+      <c r="P55" s="4"/>
+      <c r="Q55" s="4"/>
+      <c r="R55" s="4"/>
+      <c r="S55" s="4"/>
+      <c r="T55" s="4"/>
+      <c r="U55" s="4"/>
+      <c r="V55" s="4"/>
+      <c r="W55" s="4"/>
+      <c r="X55" s="4"/>
+      <c r="Y55" s="4"/>
+      <c r="Z55" s="4"/>
+      <c r="AA55" s="4"/>
+      <c r="AB55" s="4"/>
+      <c r="AC55" s="4"/>
+      <c r="AD55" s="4"/>
+      <c r="AE55" s="4"/>
+      <c r="AF55" s="4"/>
+      <c r="AG55" s="4"/>
+      <c r="AH55" s="4"/>
+      <c r="AI55" s="4"/>
+      <c r="AJ55" s="4"/>
+      <c r="AK55" s="4"/>
+      <c r="AL55" s="4"/>
+      <c r="AM55" s="4"/>
+      <c r="AN55" s="4"/>
+      <c r="AO55" s="4"/>
+      <c r="AP55" s="4"/>
+      <c r="AQ55" s="4"/>
+      <c r="AR55" s="4"/>
+      <c r="AS55" s="4"/>
+      <c r="AT55" s="4"/>
+      <c r="AU55" s="4"/>
+      <c r="AV55" s="4"/>
+      <c r="AW55" s="4"/>
+      <c r="AX55" s="4"/>
+      <c r="AY55" s="4"/>
+      <c r="AZ55" s="4"/>
+      <c r="BA55" s="4"/>
+      <c r="BB55" s="4"/>
+      <c r="BC55" s="4"/>
+      <c r="BD55" s="4"/>
+      <c r="BE55" s="4"/>
+      <c r="BF55" s="4"/>
+      <c r="BG55" s="4"/>
+      <c r="BH55" s="4"/>
+      <c r="BI55" s="4"/>
+      <c r="BJ55" s="4"/>
+      <c r="BK55" s="4"/>
+      <c r="BL55" s="4"/>
+      <c r="BM55" s="4"/>
+    </row>
+    <row r="56" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="B56" s="4"/>
+      <c r="C56" s="4"/>
+      <c r="D56" s="4"/>
+      <c r="E56" s="4"/>
+      <c r="F56" s="4"/>
+      <c r="G56" s="4"/>
+      <c r="H56" s="4"/>
+      <c r="I56" s="4"/>
+      <c r="J56" s="4"/>
+      <c r="K56" s="4"/>
+      <c r="L56" s="4"/>
+      <c r="M56" s="4"/>
+      <c r="N56" s="4"/>
+      <c r="O56" s="4"/>
+      <c r="P56" s="4"/>
+      <c r="Q56" s="4"/>
+      <c r="R56" s="4"/>
+      <c r="S56" s="4"/>
+      <c r="T56" s="4"/>
+      <c r="U56" s="4"/>
+      <c r="V56" s="4"/>
+      <c r="W56" s="4"/>
+      <c r="X56" s="4"/>
+      <c r="Y56" s="4"/>
+      <c r="Z56" s="4"/>
+      <c r="AA56" s="4"/>
+      <c r="AB56" s="4"/>
+      <c r="AC56" s="4"/>
+      <c r="AD56" s="4"/>
+      <c r="AE56" s="4"/>
+      <c r="AF56" s="4"/>
+      <c r="AG56" s="4"/>
+      <c r="AH56" s="4"/>
+      <c r="AI56" s="4"/>
+      <c r="AJ56" s="4"/>
+      <c r="AK56" s="4"/>
+      <c r="AL56" s="4"/>
+      <c r="AM56" s="4"/>
+      <c r="AN56" s="4"/>
+      <c r="AO56" s="4"/>
+      <c r="AP56" s="4"/>
+      <c r="AQ56" s="4"/>
+      <c r="AR56" s="4"/>
+      <c r="AS56" s="4"/>
+      <c r="AT56" s="4"/>
+      <c r="AU56" s="4"/>
+      <c r="AV56" s="4"/>
+      <c r="AW56" s="4"/>
+      <c r="AX56" s="4"/>
+      <c r="AY56" s="4"/>
+      <c r="AZ56" s="4"/>
+      <c r="BA56" s="4"/>
+      <c r="BB56" s="4"/>
+      <c r="BC56" s="4"/>
+      <c r="BD56" s="4"/>
+      <c r="BE56" s="4"/>
+      <c r="BF56" s="4"/>
+      <c r="BG56" s="4"/>
+      <c r="BH56" s="4"/>
+      <c r="BI56" s="4"/>
+      <c r="BJ56" s="4"/>
+      <c r="BK56" s="4"/>
+      <c r="BL56" s="4"/>
+      <c r="BM56" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="46">
+  <mergeCells count="50">
     <mergeCell ref="A1:BI1"/>
     <mergeCell ref="BJ1:BM1"/>
     <mergeCell ref="A2:BM2"/>
@@ -24028,11 +24840,11 @@
     <mergeCell ref="B32:E32"/>
     <mergeCell ref="B33:E33"/>
     <mergeCell ref="B34:E34"/>
-    <mergeCell ref="A36:V36"/>
-    <mergeCell ref="A42:BM42"/>
-    <mergeCell ref="A43:BM43"/>
-    <mergeCell ref="A44:BM44"/>
-    <mergeCell ref="A45:BM45"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="B36:E36"/>
+    <mergeCell ref="B37:E37"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="A40:V40"/>
     <mergeCell ref="A46:BM46"/>
     <mergeCell ref="A47:BM47"/>
     <mergeCell ref="A48:BM48"/>
@@ -24040,6 +24852,10 @@
     <mergeCell ref="A50:BM50"/>
     <mergeCell ref="A51:BM51"/>
     <mergeCell ref="A52:BM52"/>
+    <mergeCell ref="A53:BM53"/>
+    <mergeCell ref="A54:BM54"/>
+    <mergeCell ref="A55:BM55"/>
+    <mergeCell ref="A56:BM56"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>

--- a/tratando_tabelas/finitura/entradas_finitura.xlsx
+++ b/tratando_tabelas/finitura/entradas_finitura.xlsx
@@ -20,12 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1472" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1352" uniqueCount="232">
   <si>
     <t xml:space="preserve">Santri ADM 1.1.5.7 R1</t>
   </si>
   <si>
-    <t xml:space="preserve">Emitido em: 06/05/2026 08:38:37</t>
+    <t xml:space="preserve">Emitido em: 07/05/2026 05:30:39</t>
   </si>
   <si>
     <t xml:space="preserve">Relação de entradas - Sintético</t>
@@ -265,52 +265,13 @@
     <t xml:space="preserve">Não</t>
   </si>
   <si>
-    <t xml:space="preserve">1.856 - DEXCO S.A - METAIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.065.606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.770,41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050656061898250181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.065.617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">314,65</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050656171723297522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.065.625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.373,30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050656251541669272</t>
-  </si>
-  <si>
     <t xml:space="preserve">27.705 - DOKA - INDUSTRIA E COMERCIO LTDA</t>
   </si>
   <si>
     <t xml:space="preserve">61.331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
   </si>
   <si>
     <t xml:space="preserve">22/04/2026</t>
@@ -328,40 +289,10 @@
     <t xml:space="preserve">42260401136190000131550010000613311329572229</t>
   </si>
   <si>
-    <t xml:space="preserve">5.067.220</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.247,73</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050672201050975986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.857 - GOLDEN ART INDUSTRIA E COMERCIO LTDA - EPP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21/04/2026</t>
+    <t xml:space="preserve">622.732</t>
   </si>
   <si>
     <t xml:space="preserve">24/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">834,78</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260453654471000180550010000536161000320142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">622.732</t>
   </si>
   <si>
     <t xml:space="preserve">22/05/2026</t>
@@ -382,6 +313,9 @@
     <t xml:space="preserve">42260475339051000141550080006227231342556046</t>
   </si>
   <si>
+    <t xml:space="preserve">1.856 - DEXCO S.A - METAIS</t>
+  </si>
+  <si>
     <t xml:space="preserve">5.069.532</t>
   </si>
   <si>
@@ -389,6 +323,9 @@
   </si>
   <si>
     <t xml:space="preserve">42,44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.949</t>
   </si>
   <si>
     <t xml:space="preserve">35260497837181002190550010050695321391333760</t>
@@ -469,28 +406,10 @@
     <t xml:space="preserve">41260408028676000103550010000562311004422203</t>
   </si>
   <si>
-    <t xml:space="preserve">16.059 - JLR COM IMPORT. E EXP. DE MATERIAIS DE CONSTRUCAO LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29/04/2026</t>
+    <t xml:space="preserve">628.023</t>
   </si>
   <si>
     <t xml:space="preserve">30/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.916,19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41260417781412000109550010000120381000336730</t>
-  </si>
-  <si>
-    <t xml:space="preserve">628.023</t>
   </si>
   <si>
     <t xml:space="preserve">26/05/2026</t>
@@ -503,6 +422,9 @@
   </si>
   <si>
     <t xml:space="preserve">628.271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29/04/2026</t>
   </si>
   <si>
     <t xml:space="preserve">27/05/2026</t>
@@ -589,6 +511,9 @@
     <t xml:space="preserve">35260461413282000143550010029723801722131595</t>
   </si>
   <si>
+    <t xml:space="preserve">16.059 - JLR COM IMPORT. E EXP. DE MATERIAIS DE CONSTRUCAO LTDA</t>
+  </si>
+  <si>
     <t xml:space="preserve">12.039</t>
   </si>
   <si>
@@ -614,6 +539,9 @@
   </si>
   <si>
     <t xml:space="preserve">700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S</t>
   </si>
   <si>
     <t xml:space="preserve">42260486895448000560550010000007001016408174</t>
@@ -686,6 +614,51 @@
   </si>
   <si>
     <t xml:space="preserve">42260575339051000141550080006324231892898250</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.100 - DMFLEX IND E COMERCIO DE METAIS SANITARIOS LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">218.907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">515,80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260509270215000105550060002189071824131540</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.941 - AQUECE METAIS FABRICACAO E MANUTENCAO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.775,71</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43260527254297000178550010000105291836436270</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.123 - RUBINETTOS ACABAMENTOS EXCLUSIVOS LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">935,55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43260586895448000136550010000648961248387979</t>
   </si>
   <si>
     <t xml:space="preserve">Total geral</t>
@@ -16931,7 +16904,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BM56"/>
+  <dimension ref="A1:BM53"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="18"/>
@@ -17494,7 +17467,7 @@
     </row>
     <row r="6" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="n">
-        <v>305457</v>
+        <v>305725</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>81</v>
@@ -17515,43 +17488,43 @@
         <v>85</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="K6" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L6" s="12" t="n">
-        <v>4770.41</v>
+        <v>10012.8</v>
       </c>
       <c r="M6" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N6" s="12" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="O6" s="12" t="n">
-        <v>4588.46</v>
+        <v>10012.8</v>
       </c>
       <c r="P6" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q6" s="13" t="n">
-        <v>0.231499</v>
+        <v>0.750038</v>
       </c>
       <c r="R6" s="12" t="n">
-        <v>35.08</v>
+        <v>38</v>
       </c>
       <c r="S6" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T6" s="14" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="U6" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V6" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W6" s="9" t="s">
         <v>73</v>
@@ -17560,13 +17533,13 @@
         <v>85</v>
       </c>
       <c r="Y6" s="12" t="n">
-        <v>181.95</v>
+        <v>0</v>
       </c>
       <c r="Z6" s="12" t="n">
-        <v>4588.46</v>
+        <v>10012.8</v>
       </c>
       <c r="AA6" s="12" t="n">
-        <v>183.54</v>
+        <v>400.51</v>
       </c>
       <c r="AB6" s="12" t="n">
         <v>0</v>
@@ -17635,7 +17608,7 @@
         <v>76</v>
       </c>
       <c r="AX6" s="10" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AY6" s="14" t="s">
         <v>75</v>
@@ -17685,10 +17658,10 @@
     </row>
     <row r="7" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="n">
-        <v>305470</v>
+        <v>305821</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
@@ -17697,67 +17670,67 @@
         <v>89</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K7" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L7" s="12" t="n">
-        <v>314.65</v>
+        <v>4462.34</v>
       </c>
       <c r="M7" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N7" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O7" s="12" t="n">
-        <v>295.45</v>
+        <v>4462.34</v>
       </c>
       <c r="P7" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q7" s="13" t="n">
-        <v>0.016472</v>
+        <v>0.010272</v>
       </c>
       <c r="R7" s="12" t="n">
-        <v>1.6</v>
+        <v>3.7</v>
       </c>
       <c r="S7" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T7" s="14" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="U7" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V7" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W7" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X7" s="9" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="Y7" s="12" t="n">
-        <v>19.2</v>
+        <v>0</v>
       </c>
       <c r="Z7" s="12" t="n">
-        <v>295.45</v>
+        <v>4462.34</v>
       </c>
       <c r="AA7" s="12" t="n">
-        <v>11.81</v>
+        <v>312.36</v>
       </c>
       <c r="AB7" s="12" t="n">
         <v>0</v>
@@ -17826,7 +17799,7 @@
         <v>76</v>
       </c>
       <c r="AX7" s="10" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AY7" s="14" t="s">
         <v>75</v>
@@ -17862,7 +17835,7 @@
         <v>78</v>
       </c>
       <c r="BJ7" s="9" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="BK7" s="9" t="s">
         <v>75</v>
@@ -17876,79 +17849,79 @@
     </row>
     <row r="8" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="n">
-        <v>305480</v>
+        <v>305822</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
       <c r="F8" s="9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K8" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L8" s="12" t="n">
-        <v>2373.3</v>
+        <v>1464.23</v>
       </c>
       <c r="M8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N8" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O8" s="12" t="n">
-        <v>2228.46</v>
+        <v>1464.23</v>
       </c>
       <c r="P8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q8" s="13" t="n">
-        <v>0.017186</v>
+        <v>0.002473</v>
       </c>
       <c r="R8" s="12" t="n">
-        <v>12.33</v>
+        <v>0.77</v>
       </c>
       <c r="S8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T8" s="14" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="U8" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V8" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W8" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X8" s="9" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="Y8" s="12" t="n">
-        <v>144.84</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="12" t="n">
-        <v>2228.46</v>
+        <v>1464.23</v>
       </c>
       <c r="AA8" s="12" t="n">
-        <v>89.14</v>
+        <v>102.5</v>
       </c>
       <c r="AB8" s="12" t="n">
         <v>0</v>
@@ -18017,7 +17990,7 @@
         <v>76</v>
       </c>
       <c r="AX8" s="10" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AY8" s="14" t="s">
         <v>75</v>
@@ -18053,7 +18026,7 @@
         <v>78</v>
       </c>
       <c r="BJ8" s="9" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="BK8" s="9" t="s">
         <v>75</v>
@@ -18067,52 +18040,52 @@
     </row>
     <row r="9" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="n">
-        <v>305725</v>
+        <v>305942</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="9" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G9" s="10" t="s">
         <v>83</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="K9" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L9" s="12" t="n">
-        <v>10012.8</v>
+        <v>42.44</v>
       </c>
       <c r="M9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N9" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O9" s="12" t="n">
-        <v>10012.8</v>
+        <v>39.85</v>
       </c>
       <c r="P9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q9" s="13" t="n">
-        <v>0.750038</v>
+        <v>0.002284</v>
       </c>
       <c r="R9" s="12" t="n">
-        <v>38</v>
+        <v>0.8</v>
       </c>
       <c r="S9" s="12" t="n">
         <v>0</v>
@@ -18124,22 +18097,22 @@
         <v>72</v>
       </c>
       <c r="V9" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W9" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X9" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Y9" s="12" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Z9" s="12" t="n">
-        <v>10012.8</v>
+        <v>39.85</v>
       </c>
       <c r="AA9" s="12" t="n">
-        <v>400.51</v>
+        <v>1.59</v>
       </c>
       <c r="AB9" s="12" t="n">
         <v>0</v>
@@ -18208,7 +18181,7 @@
         <v>76</v>
       </c>
       <c r="AX9" s="10" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AY9" s="14" t="s">
         <v>75</v>
@@ -18244,7 +18217,7 @@
         <v>78</v>
       </c>
       <c r="BJ9" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="BK9" s="9" t="s">
         <v>75</v>
@@ -18258,79 +18231,79 @@
     </row>
     <row r="10" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="n">
-        <v>305731</v>
+        <v>305957</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
       <c r="F10" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G10" s="10" t="s">
         <v>83</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="K10" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L10" s="12" t="n">
-        <v>6247.73</v>
+        <v>126.7</v>
       </c>
       <c r="M10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N10" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O10" s="12" t="n">
-        <v>6247.73</v>
+        <v>118.97</v>
       </c>
       <c r="P10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q10" s="13" t="n">
-        <v>0.030808</v>
+        <v>0.001512</v>
       </c>
       <c r="R10" s="12" t="n">
-        <v>6.05</v>
+        <v>1.58</v>
       </c>
       <c r="S10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T10" s="14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="U10" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V10" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W10" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X10" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Y10" s="12" t="n">
-        <v>0</v>
+        <v>7.73</v>
       </c>
       <c r="Z10" s="12" t="n">
-        <v>6247.73</v>
+        <v>118.97</v>
       </c>
       <c r="AA10" s="12" t="n">
-        <v>437.34</v>
+        <v>4.76</v>
       </c>
       <c r="AB10" s="12" t="n">
         <v>0</v>
@@ -18399,7 +18372,7 @@
         <v>76</v>
       </c>
       <c r="AX10" s="10" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AY10" s="14" t="s">
         <v>75</v>
@@ -18435,7 +18408,7 @@
         <v>78</v>
       </c>
       <c r="BJ10" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="BK10" s="9" t="s">
         <v>75</v>
@@ -18449,10 +18422,10 @@
     </row>
     <row r="11" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="n">
-        <v>305778</v>
+        <v>305966</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
@@ -18464,19 +18437,19 @@
         <v>83</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="K11" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>834.78</v>
+        <v>290.09</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>0</v>
@@ -18485,43 +18458,43 @@
         <v>2</v>
       </c>
       <c r="O11" s="12" t="n">
-        <v>730</v>
+        <v>272.38</v>
       </c>
       <c r="P11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q11" s="13" t="n">
-        <v>0</v>
+        <v>0.003202</v>
       </c>
       <c r="R11" s="12" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T11" s="14" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="U11" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V11" s="12" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="W11" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X11" s="9" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="Y11" s="12" t="n">
-        <v>104.78</v>
+        <v>17.71</v>
       </c>
       <c r="Z11" s="12" t="n">
-        <v>730</v>
+        <v>272.38</v>
       </c>
       <c r="AA11" s="12" t="n">
-        <v>51.1</v>
+        <v>10.89</v>
       </c>
       <c r="AB11" s="12" t="n">
         <v>0</v>
@@ -18587,10 +18560,10 @@
         <v>74</v>
       </c>
       <c r="AW11" s="14" t="s">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="AX11" s="10" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AY11" s="14" t="s">
         <v>75</v>
@@ -18626,7 +18599,7 @@
         <v>78</v>
       </c>
       <c r="BJ11" s="9" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="BK11" s="9" t="s">
         <v>75</v>
@@ -18640,7 +18613,7 @@
     </row>
     <row r="12" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="n">
-        <v>305821</v>
+        <v>306001</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>64</v>
@@ -18649,25 +18622,25 @@
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
       <c r="F12" s="9" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="G12" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="K12" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>4462.34</v>
+        <v>1181.41</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>0</v>
@@ -18676,22 +18649,22 @@
         <v>1</v>
       </c>
       <c r="O12" s="12" t="n">
-        <v>4462.34</v>
+        <v>1181.41</v>
       </c>
       <c r="P12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" s="13" t="n">
-        <v>0.010272</v>
+        <v>0.000412</v>
       </c>
       <c r="R12" s="12" t="n">
-        <v>3.7</v>
+        <v>0.71</v>
       </c>
       <c r="S12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T12" s="14" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="U12" s="15" t="s">
         <v>72</v>
@@ -18703,16 +18676,16 @@
         <v>73</v>
       </c>
       <c r="X12" s="9" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="Y12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z12" s="12" t="n">
-        <v>4462.34</v>
+        <v>1181.41</v>
       </c>
       <c r="AA12" s="12" t="n">
-        <v>312.36</v>
+        <v>82.7</v>
       </c>
       <c r="AB12" s="12" t="n">
         <v>0</v>
@@ -18817,7 +18790,7 @@
         <v>78</v>
       </c>
       <c r="BJ12" s="9" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="BK12" s="9" t="s">
         <v>75</v>
@@ -18831,34 +18804,34 @@
     </row>
     <row r="13" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="n">
-        <v>305822</v>
+        <v>306005</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>64</v>
+        <v>115</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
       <c r="F13" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="J13" s="9" t="s">
         <v>117</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="I13" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="J13" s="9" t="s">
-        <v>114</v>
       </c>
       <c r="K13" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>1464.23</v>
+        <v>861.88</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>0</v>
@@ -18867,16 +18840,16 @@
         <v>1</v>
       </c>
       <c r="O13" s="12" t="n">
-        <v>1464.23</v>
+        <v>861.88</v>
       </c>
       <c r="P13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q13" s="13" t="n">
-        <v>0.002473</v>
+        <v>0.073796</v>
       </c>
       <c r="R13" s="12" t="n">
-        <v>0.77</v>
+        <v>43.13</v>
       </c>
       <c r="S13" s="12" t="n">
         <v>0</v>
@@ -18888,22 +18861,22 @@
         <v>72</v>
       </c>
       <c r="V13" s="12" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="W13" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X13" s="9" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="Y13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z13" s="12" t="n">
-        <v>1464.23</v>
+        <v>861.88</v>
       </c>
       <c r="AA13" s="12" t="n">
-        <v>102.5</v>
+        <v>60.33</v>
       </c>
       <c r="AB13" s="12" t="n">
         <v>0</v>
@@ -19022,79 +18995,79 @@
     </row>
     <row r="14" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="n">
-        <v>305942</v>
+        <v>306150</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>81</v>
+        <v>120</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
       <c r="F14" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G14" s="10" t="s">
         <v>83</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>78</v>
+        <v>122</v>
       </c>
       <c r="K14" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>42.44</v>
+        <v>2070.21</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O14" s="12" t="n">
-        <v>39.85</v>
+        <v>1970.21</v>
       </c>
       <c r="P14" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q14" s="13" t="n">
-        <v>0.002284</v>
+        <v>0</v>
       </c>
       <c r="R14" s="12" t="n">
-        <v>0.8</v>
+        <v>4.15</v>
       </c>
       <c r="S14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T14" s="14" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="U14" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V14" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W14" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X14" s="9" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="Y14" s="12" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Z14" s="12" t="n">
-        <v>39.85</v>
+        <v>2070.21</v>
       </c>
       <c r="AA14" s="12" t="n">
-        <v>1.59</v>
+        <v>144.92</v>
       </c>
       <c r="AB14" s="12" t="n">
         <v>0</v>
@@ -19163,7 +19136,7 @@
         <v>76</v>
       </c>
       <c r="AX14" s="10" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AY14" s="14" t="s">
         <v>75</v>
@@ -19199,7 +19172,7 @@
         <v>78</v>
       </c>
       <c r="BJ14" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="BK14" s="9" t="s">
         <v>75</v>
@@ -19213,79 +19186,79 @@
     </row>
     <row r="15" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="n">
-        <v>305957</v>
+        <v>306173</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>81</v>
+        <v>120</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
       <c r="F15" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G15" s="10" t="s">
         <v>83</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>78</v>
+        <v>122</v>
       </c>
       <c r="K15" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>126.7</v>
+        <v>3730.39</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O15" s="12" t="n">
-        <v>118.97</v>
+        <v>3730.39</v>
       </c>
       <c r="P15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q15" s="13" t="n">
-        <v>0.001512</v>
+        <v>0</v>
       </c>
       <c r="R15" s="12" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="S15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T15" s="14" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="U15" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V15" s="12" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="W15" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X15" s="9" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="Y15" s="12" t="n">
-        <v>7.73</v>
+        <v>0</v>
       </c>
       <c r="Z15" s="12" t="n">
-        <v>118.97</v>
+        <v>3730.39</v>
       </c>
       <c r="AA15" s="12" t="n">
-        <v>4.76</v>
+        <v>261.14</v>
       </c>
       <c r="AB15" s="12" t="n">
         <v>0</v>
@@ -19354,7 +19327,7 @@
         <v>76</v>
       </c>
       <c r="AX15" s="10" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AY15" s="14" t="s">
         <v>75</v>
@@ -19390,7 +19363,7 @@
         <v>78</v>
       </c>
       <c r="BJ15" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BK15" s="9" t="s">
         <v>75</v>
@@ -19404,34 +19377,34 @@
     </row>
     <row r="16" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="n">
-        <v>305966</v>
+        <v>306327</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
       <c r="F16" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>78</v>
+        <v>130</v>
       </c>
       <c r="K16" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>290.09</v>
+        <v>10714.13</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>0</v>
@@ -19440,43 +19413,43 @@
         <v>2</v>
       </c>
       <c r="O16" s="12" t="n">
-        <v>272.38</v>
+        <v>10714.13</v>
       </c>
       <c r="P16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q16" s="13" t="n">
-        <v>0.003202</v>
+        <v>0.020976</v>
       </c>
       <c r="R16" s="12" t="n">
-        <v>1.93</v>
+        <v>6.72</v>
       </c>
       <c r="S16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T16" s="14" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="U16" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V16" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W16" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X16" s="9" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="Y16" s="12" t="n">
-        <v>17.71</v>
+        <v>0</v>
       </c>
       <c r="Z16" s="12" t="n">
-        <v>272.38</v>
+        <v>10714.13</v>
       </c>
       <c r="AA16" s="12" t="n">
-        <v>10.89</v>
+        <v>749.99</v>
       </c>
       <c r="AB16" s="12" t="n">
         <v>0</v>
@@ -19545,7 +19518,7 @@
         <v>76</v>
       </c>
       <c r="AX16" s="10" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AY16" s="14" t="s">
         <v>75</v>
@@ -19581,7 +19554,7 @@
         <v>78</v>
       </c>
       <c r="BJ16" s="9" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="BK16" s="9" t="s">
         <v>75</v>
@@ -19595,7 +19568,7 @@
     </row>
     <row r="17" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="n">
-        <v>306001</v>
+        <v>306329</v>
       </c>
       <c r="B17" s="9" t="s">
         <v>64</v>
@@ -19604,25 +19577,25 @@
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
       <c r="F17" s="9" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="G17" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="K17" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>1181.41</v>
+        <v>891.38</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>0</v>
@@ -19631,22 +19604,22 @@
         <v>1</v>
       </c>
       <c r="O17" s="12" t="n">
-        <v>1181.41</v>
+        <v>891.38</v>
       </c>
       <c r="P17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q17" s="13" t="n">
-        <v>0.000412</v>
+        <v>0.003922</v>
       </c>
       <c r="R17" s="12" t="n">
-        <v>0.71</v>
+        <v>0.41</v>
       </c>
       <c r="S17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T17" s="14" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="U17" s="15" t="s">
         <v>72</v>
@@ -19658,16 +19631,16 @@
         <v>73</v>
       </c>
       <c r="X17" s="9" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="Y17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z17" s="12" t="n">
-        <v>1181.41</v>
+        <v>891.38</v>
       </c>
       <c r="AA17" s="12" t="n">
-        <v>82.7</v>
+        <v>62.4</v>
       </c>
       <c r="AB17" s="12" t="n">
         <v>0</v>
@@ -19772,7 +19745,7 @@
         <v>78</v>
       </c>
       <c r="BJ17" s="9" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="BK17" s="9" t="s">
         <v>75</v>
@@ -19786,34 +19759,34 @@
     </row>
     <row r="18" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="n">
-        <v>306005</v>
+        <v>306335</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>136</v>
+        <v>64</v>
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
       <c r="F18" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>108</v>
+        <v>134</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="K18" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>861.88</v>
+        <v>1593.54</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>0</v>
@@ -19822,16 +19795,16 @@
         <v>1</v>
       </c>
       <c r="O18" s="12" t="n">
-        <v>861.88</v>
+        <v>1593.54</v>
       </c>
       <c r="P18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q18" s="13" t="n">
-        <v>0.073796</v>
+        <v>0.005136</v>
       </c>
       <c r="R18" s="12" t="n">
-        <v>43.13</v>
+        <v>2.1</v>
       </c>
       <c r="S18" s="12" t="n">
         <v>0</v>
@@ -19843,22 +19816,22 @@
         <v>72</v>
       </c>
       <c r="V18" s="12" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="W18" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X18" s="9" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="Y18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z18" s="12" t="n">
-        <v>861.88</v>
+        <v>1593.54</v>
       </c>
       <c r="AA18" s="12" t="n">
-        <v>60.33</v>
+        <v>111.55</v>
       </c>
       <c r="AB18" s="12" t="n">
         <v>0</v>
@@ -19977,7 +19950,7 @@
     </row>
     <row r="19" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="n">
-        <v>306150</v>
+        <v>306338</v>
       </c>
       <c r="B19" s="9" t="s">
         <v>141</v>
@@ -19992,64 +19965,64 @@
         <v>83</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>143</v>
+        <v>78</v>
       </c>
       <c r="K19" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>2070.21</v>
+        <v>900.38</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O19" s="12" t="n">
-        <v>1970.21</v>
+        <v>900.38</v>
       </c>
       <c r="P19" s="12" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q19" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R19" s="12" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="S19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T19" s="14" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="U19" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V19" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W19" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X19" s="9" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="Y19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z19" s="12" t="n">
-        <v>2070.21</v>
+        <v>900.38</v>
       </c>
       <c r="AA19" s="12" t="n">
-        <v>144.92</v>
+        <v>36.02</v>
       </c>
       <c r="AB19" s="12" t="n">
         <v>0</v>
@@ -20118,7 +20091,7 @@
         <v>76</v>
       </c>
       <c r="AX19" s="10" t="s">
-        <v>77</v>
+        <v>144</v>
       </c>
       <c r="AY19" s="14" t="s">
         <v>75</v>
@@ -20168,43 +20141,43 @@
     </row>
     <row r="20" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="n">
-        <v>306173</v>
+        <v>306454</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
       <c r="F20" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G20" s="10" t="s">
         <v>83</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="K20" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>3730.39</v>
+        <v>3167.76</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O20" s="12" t="n">
-        <v>3730.39</v>
+        <v>3167.76</v>
       </c>
       <c r="P20" s="12" t="n">
         <v>0</v>
@@ -20219,28 +20192,28 @@
         <v>0</v>
       </c>
       <c r="T20" s="14" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="U20" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V20" s="12" t="n">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="W20" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X20" s="9" t="s">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="Y20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z20" s="12" t="n">
-        <v>3730.39</v>
+        <v>3167.76</v>
       </c>
       <c r="AA20" s="12" t="n">
-        <v>261.14</v>
+        <v>117.52</v>
       </c>
       <c r="AB20" s="12" t="n">
         <v>0</v>
@@ -20345,7 +20318,7 @@
         <v>78</v>
       </c>
       <c r="BJ20" s="9" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="BK20" s="9" t="s">
         <v>75</v>
@@ -20359,25 +20332,25 @@
     </row>
     <row r="21" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="n">
-        <v>306272</v>
+        <v>306477</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>149</v>
+        <v>97</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
       <c r="F21" s="9" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="G21" s="10" t="s">
         <v>83</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>151</v>
+        <v>129</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="J21" s="9" t="s">
         <v>153</v>
@@ -20386,25 +20359,25 @@
         <v>70</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>14916.19</v>
+        <v>3108.72</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>3433.93</v>
+        <v>0</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O21" s="12" t="n">
-        <v>17025</v>
+        <v>3108.72</v>
       </c>
       <c r="P21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q21" s="13" t="n">
-        <v>0</v>
+        <v>0.001598</v>
       </c>
       <c r="R21" s="12" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S21" s="12" t="n">
         <v>0</v>
@@ -20416,22 +20389,22 @@
         <v>72</v>
       </c>
       <c r="V21" s="12" t="n">
-        <v>82</v>
+        <v>28</v>
       </c>
       <c r="W21" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X21" s="9" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="Y21" s="12" t="n">
-        <v>1325.12</v>
+        <v>0</v>
       </c>
       <c r="Z21" s="12" t="n">
-        <v>13591.07</v>
+        <v>3108.72</v>
       </c>
       <c r="AA21" s="12" t="n">
-        <v>543.65</v>
+        <v>217.61</v>
       </c>
       <c r="AB21" s="12" t="n">
         <v>0</v>
@@ -20550,7 +20523,7 @@
     </row>
     <row r="22" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="n">
-        <v>306327</v>
+        <v>306493</v>
       </c>
       <c r="B22" s="9" t="s">
         <v>64</v>
@@ -20565,43 +20538,43 @@
         <v>66</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="K22" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>10714.13</v>
+        <v>2876.8</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O22" s="12" t="n">
-        <v>10714.13</v>
+        <v>2701.22</v>
       </c>
       <c r="P22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q22" s="13" t="n">
-        <v>0.020976</v>
+        <v>0.027908</v>
       </c>
       <c r="R22" s="12" t="n">
-        <v>6.72</v>
+        <v>3.56</v>
       </c>
       <c r="S22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T22" s="14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="U22" s="15" t="s">
         <v>72</v>
@@ -20613,16 +20586,16 @@
         <v>73</v>
       </c>
       <c r="X22" s="9" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="Y22" s="12" t="n">
-        <v>0</v>
+        <v>175.58</v>
       </c>
       <c r="Z22" s="12" t="n">
-        <v>10714.13</v>
+        <v>2701.22</v>
       </c>
       <c r="AA22" s="12" t="n">
-        <v>749.99</v>
+        <v>189.09</v>
       </c>
       <c r="AB22" s="12" t="n">
         <v>0</v>
@@ -20727,7 +20700,7 @@
         <v>78</v>
       </c>
       <c r="BJ22" s="9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="BK22" s="9" t="s">
         <v>75</v>
@@ -20741,10 +20714,10 @@
     </row>
     <row r="23" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="n">
-        <v>306329</v>
+        <v>306535</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>64</v>
+        <v>159</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
@@ -20753,67 +20726,67 @@
         <v>160</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>151</v>
+        <v>129</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>161</v>
+        <v>78</v>
       </c>
       <c r="K23" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>891.38</v>
+        <v>5384.2</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O23" s="12" t="n">
-        <v>891.38</v>
+        <v>5384.2</v>
       </c>
       <c r="P23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q23" s="13" t="n">
-        <v>0.003922</v>
+        <v>0.023054</v>
       </c>
       <c r="R23" s="12" t="n">
-        <v>0.41</v>
+        <v>28.62</v>
       </c>
       <c r="S23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T23" s="14" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="U23" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V23" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W23" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X23" s="9" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="Y23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z23" s="12" t="n">
-        <v>891.38</v>
+        <v>0</v>
       </c>
       <c r="AA23" s="12" t="n">
-        <v>62.4</v>
+        <v>0</v>
       </c>
       <c r="AB23" s="12" t="n">
         <v>0</v>
@@ -20882,7 +20855,7 @@
         <v>76</v>
       </c>
       <c r="AX23" s="10" t="s">
-        <v>77</v>
+        <v>144</v>
       </c>
       <c r="AY23" s="14" t="s">
         <v>75</v>
@@ -20918,7 +20891,7 @@
         <v>78</v>
       </c>
       <c r="BJ23" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="BK23" s="9" t="s">
         <v>75</v>
@@ -20932,10 +20905,10 @@
     </row>
     <row r="24" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="n">
-        <v>306335</v>
+        <v>306540</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>64</v>
+        <v>163</v>
       </c>
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
@@ -20944,67 +20917,67 @@
         <v>164</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>151</v>
+        <v>134</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="K24" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>1593.54</v>
+        <v>6638.26</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>0</v>
+        <v>1067.38</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O24" s="12" t="n">
-        <v>1593.54</v>
+        <v>7115.9</v>
       </c>
       <c r="P24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q24" s="13" t="n">
-        <v>0.005136</v>
+        <v>0</v>
       </c>
       <c r="R24" s="12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T24" s="14" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="U24" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V24" s="12" t="n">
-        <v>28</v>
+        <v>105</v>
       </c>
       <c r="W24" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X24" s="9" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="Y24" s="12" t="n">
-        <v>0</v>
+        <v>589.74</v>
       </c>
       <c r="Z24" s="12" t="n">
-        <v>1593.54</v>
+        <v>6048.52</v>
       </c>
       <c r="AA24" s="12" t="n">
-        <v>111.55</v>
+        <v>241.94</v>
       </c>
       <c r="AB24" s="12" t="n">
         <v>0</v>
@@ -21109,7 +21082,7 @@
         <v>78</v>
       </c>
       <c r="BJ24" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="BK24" s="9" t="s">
         <v>75</v>
@@ -21123,10 +21096,10 @@
     </row>
     <row r="25" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="n">
-        <v>306338</v>
+        <v>306545</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>167</v>
+        <v>141</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
@@ -21138,19 +21111,19 @@
         <v>83</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>151</v>
+        <v>134</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>78</v>
+        <v>169</v>
       </c>
       <c r="K25" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>900.38</v>
+        <v>7171.52</v>
       </c>
       <c r="M25" s="12" t="n">
         <v>0</v>
@@ -21159,7 +21132,7 @@
         <v>3</v>
       </c>
       <c r="O25" s="12" t="n">
-        <v>900.38</v>
+        <v>7171.52</v>
       </c>
       <c r="P25" s="12" t="n">
         <v>0</v>
@@ -21174,28 +21147,28 @@
         <v>0</v>
       </c>
       <c r="T25" s="14" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="U25" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V25" s="12" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="W25" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X25" s="9" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="Y25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z25" s="12" t="n">
-        <v>900.38</v>
+        <v>7171.52</v>
       </c>
       <c r="AA25" s="12" t="n">
-        <v>36.02</v>
+        <v>286.86</v>
       </c>
       <c r="AB25" s="12" t="n">
         <v>0</v>
@@ -21264,7 +21237,7 @@
         <v>76</v>
       </c>
       <c r="AX25" s="10" t="s">
-        <v>170</v>
+        <v>77</v>
       </c>
       <c r="AY25" s="14" t="s">
         <v>75</v>
@@ -21314,43 +21287,43 @@
     </row>
     <row r="26" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="n">
-        <v>306454</v>
+        <v>306579</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>172</v>
+        <v>141</v>
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G26" s="10" t="s">
         <v>83</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>174</v>
+        <v>148</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="K26" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>3167.76</v>
+        <v>7171.52</v>
       </c>
       <c r="M26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O26" s="12" t="n">
-        <v>3167.76</v>
+        <v>7171.52</v>
       </c>
       <c r="P26" s="12" t="n">
         <v>0</v>
@@ -21365,28 +21338,28 @@
         <v>0</v>
       </c>
       <c r="T26" s="14" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="U26" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V26" s="12" t="n">
-        <v>8</v>
+        <v>61.66</v>
       </c>
       <c r="W26" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X26" s="9" t="s">
-        <v>174</v>
+        <v>148</v>
       </c>
       <c r="Y26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z26" s="12" t="n">
-        <v>3167.76</v>
+        <v>7171.52</v>
       </c>
       <c r="AA26" s="12" t="n">
-        <v>117.52</v>
+        <v>286.86</v>
       </c>
       <c r="AB26" s="12" t="n">
         <v>0</v>
@@ -21452,7 +21425,7 @@
         <v>74</v>
       </c>
       <c r="AW26" s="14" t="s">
-        <v>76</v>
+        <v>173</v>
       </c>
       <c r="AX26" s="10" t="s">
         <v>77</v>
@@ -21491,7 +21464,7 @@
         <v>78</v>
       </c>
       <c r="BJ26" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="BK26" s="9" t="s">
         <v>75</v>
@@ -21505,79 +21478,79 @@
     </row>
     <row r="27" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="n">
-        <v>306477</v>
+        <v>306581</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>81</v>
+        <v>141</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G27" s="10" t="s">
         <v>83</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>174</v>
+        <v>148</v>
       </c>
       <c r="J27" s="9" t="s">
-        <v>179</v>
+        <v>78</v>
       </c>
       <c r="K27" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>3108.72</v>
+        <v>96.5</v>
       </c>
       <c r="M27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O27" s="12" t="n">
-        <v>3108.72</v>
+        <v>96.5</v>
       </c>
       <c r="P27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q27" s="13" t="n">
-        <v>0.001598</v>
+        <v>0</v>
       </c>
       <c r="R27" s="12" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T27" s="14" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="U27" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V27" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W27" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X27" s="9" t="s">
-        <v>174</v>
+        <v>148</v>
       </c>
       <c r="Y27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z27" s="12" t="n">
-        <v>3108.72</v>
+        <v>96.5</v>
       </c>
       <c r="AA27" s="12" t="n">
-        <v>217.61</v>
+        <v>3.86</v>
       </c>
       <c r="AB27" s="12" t="n">
         <v>0</v>
@@ -21643,10 +21616,10 @@
         <v>74</v>
       </c>
       <c r="AW27" s="14" t="s">
-        <v>76</v>
+        <v>173</v>
       </c>
       <c r="AX27" s="10" t="s">
-        <v>77</v>
+        <v>144</v>
       </c>
       <c r="AY27" s="14" t="s">
         <v>75</v>
@@ -21682,7 +21655,7 @@
         <v>78</v>
       </c>
       <c r="BJ27" s="9" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="BK27" s="9" t="s">
         <v>75</v>
@@ -21696,79 +21669,79 @@
     </row>
     <row r="28" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="n">
-        <v>306493</v>
+        <v>306585</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>64</v>
+        <v>178</v>
       </c>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>152</v>
+        <v>111</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>174</v>
+        <v>148</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>179</v>
+        <v>130</v>
       </c>
       <c r="K28" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>2876.8</v>
+        <v>24038.11</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="O28" s="12" t="n">
-        <v>2701.22</v>
+        <v>22949.18</v>
       </c>
       <c r="P28" s="12" t="n">
-        <v>0</v>
+        <v>659</v>
       </c>
       <c r="Q28" s="13" t="n">
-        <v>0.027908</v>
+        <v>0.022336</v>
       </c>
       <c r="R28" s="12" t="n">
-        <v>3.56</v>
+        <v>5.96</v>
       </c>
       <c r="S28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T28" s="14" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="U28" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V28" s="12" t="n">
-        <v>28</v>
+        <v>82.46</v>
       </c>
       <c r="W28" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X28" s="9" t="s">
-        <v>174</v>
+        <v>148</v>
       </c>
       <c r="Y28" s="12" t="n">
-        <v>175.58</v>
+        <v>429.93</v>
       </c>
       <c r="Z28" s="12" t="n">
-        <v>2701.22</v>
+        <v>23608.18</v>
       </c>
       <c r="AA28" s="12" t="n">
-        <v>189.09</v>
+        <v>944.32</v>
       </c>
       <c r="AB28" s="12" t="n">
         <v>0</v>
@@ -21873,7 +21846,7 @@
         <v>78</v>
       </c>
       <c r="BJ28" s="9" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="BK28" s="9" t="s">
         <v>75</v>
@@ -21887,79 +21860,79 @@
     </row>
     <row r="29" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="n">
-        <v>306535</v>
+        <v>306675</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>185</v>
+        <v>64</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
       <c r="F29" s="9" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>78</v>
+        <v>184</v>
       </c>
       <c r="K29" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>5384.2</v>
+        <v>3116.85</v>
       </c>
       <c r="M29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O29" s="12" t="n">
-        <v>5384.2</v>
+        <v>3116.85</v>
       </c>
       <c r="P29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q29" s="13" t="n">
-        <v>0.023054</v>
+        <v>0.011766</v>
       </c>
       <c r="R29" s="12" t="n">
-        <v>28.62</v>
+        <v>2.1</v>
       </c>
       <c r="S29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T29" s="14" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="U29" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V29" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W29" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X29" s="9" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="Y29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z29" s="12" t="n">
-        <v>0</v>
+        <v>3116.85</v>
       </c>
       <c r="AA29" s="12" t="n">
-        <v>0</v>
+        <v>218.18</v>
       </c>
       <c r="AB29" s="12" t="n">
         <v>0</v>
@@ -22028,7 +22001,7 @@
         <v>76</v>
       </c>
       <c r="AX29" s="10" t="s">
-        <v>170</v>
+        <v>77</v>
       </c>
       <c r="AY29" s="14" t="s">
         <v>75</v>
@@ -22064,7 +22037,7 @@
         <v>78</v>
       </c>
       <c r="BJ29" s="9" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="BK29" s="9" t="s">
         <v>75</v>
@@ -22078,79 +22051,79 @@
     </row>
     <row r="30" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="n">
-        <v>306540</v>
+        <v>306713</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>149</v>
+        <v>187</v>
       </c>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
       <c r="F30" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G30" s="10" t="s">
         <v>83</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>151</v>
+        <v>111</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>190</v>
+        <v>135</v>
       </c>
       <c r="K30" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>6638.26</v>
+        <v>3485.6</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>1067.38</v>
+        <v>0</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O30" s="12" t="n">
-        <v>7115.9</v>
+        <v>3288.3</v>
       </c>
       <c r="P30" s="12" t="n">
-        <v>0</v>
+        <v>197.3</v>
       </c>
       <c r="Q30" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R30" s="12" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="S30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T30" s="14" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="U30" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V30" s="12" t="n">
-        <v>105</v>
+        <v>29</v>
       </c>
       <c r="W30" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X30" s="9" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="Y30" s="12" t="n">
-        <v>589.74</v>
+        <v>0</v>
       </c>
       <c r="Z30" s="12" t="n">
-        <v>6048.52</v>
+        <v>3485.6</v>
       </c>
       <c r="AA30" s="12" t="n">
-        <v>241.94</v>
+        <v>139.42</v>
       </c>
       <c r="AB30" s="12" t="n">
         <v>0</v>
@@ -22255,7 +22228,7 @@
         <v>78</v>
       </c>
       <c r="BJ30" s="9" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="BK30" s="9" t="s">
         <v>75</v>
@@ -22269,43 +22242,43 @@
     </row>
     <row r="31" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="n">
-        <v>306545</v>
+        <v>306724</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>167</v>
+        <v>191</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
       <c r="F31" s="9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G31" s="10" t="s">
         <v>83</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>151</v>
+        <v>129</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="J31" s="9" t="s">
-        <v>194</v>
+        <v>78</v>
       </c>
       <c r="K31" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>7171.52</v>
+        <v>976.79</v>
       </c>
       <c r="M31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O31" s="12" t="n">
-        <v>7171.52</v>
+        <v>970.48</v>
       </c>
       <c r="P31" s="12" t="n">
         <v>0</v>
@@ -22320,28 +22293,28 @@
         <v>0</v>
       </c>
       <c r="T31" s="14" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="U31" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V31" s="12" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="W31" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X31" s="9" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="Y31" s="12" t="n">
-        <v>0</v>
+        <v>6.31</v>
       </c>
       <c r="Z31" s="12" t="n">
-        <v>7171.52</v>
+        <v>976.79</v>
       </c>
       <c r="AA31" s="12" t="n">
-        <v>286.86</v>
+        <v>68.38</v>
       </c>
       <c r="AB31" s="12" t="n">
         <v>0</v>
@@ -22410,7 +22383,7 @@
         <v>76</v>
       </c>
       <c r="AX31" s="10" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AY31" s="14" t="s">
         <v>75</v>
@@ -22446,7 +22419,7 @@
         <v>78</v>
       </c>
       <c r="BJ31" s="9" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="BK31" s="9" t="s">
         <v>75</v>
@@ -22460,43 +22433,43 @@
     </row>
     <row r="32" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="n">
-        <v>306579</v>
+        <v>306726</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>167</v>
+        <v>64</v>
       </c>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
       <c r="F32" s="9" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="G32" s="10" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="J32" s="9" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="K32" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>7171.52</v>
+        <v>846.74</v>
       </c>
       <c r="M32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O32" s="12" t="n">
-        <v>7171.52</v>
+        <v>846.74</v>
       </c>
       <c r="P32" s="12" t="n">
         <v>0</v>
@@ -22505,34 +22478,34 @@
         <v>0</v>
       </c>
       <c r="R32" s="12" t="n">
-        <v>0</v>
+        <v>0.43</v>
       </c>
       <c r="S32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T32" s="14" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="U32" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V32" s="12" t="n">
-        <v>61.66</v>
+        <v>28</v>
       </c>
       <c r="W32" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X32" s="9" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="Y32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z32" s="12" t="n">
-        <v>7171.52</v>
+        <v>846.74</v>
       </c>
       <c r="AA32" s="12" t="n">
-        <v>286.86</v>
+        <v>59.27</v>
       </c>
       <c r="AB32" s="12" t="n">
         <v>0</v>
@@ -22598,7 +22571,7 @@
         <v>74</v>
       </c>
       <c r="AW32" s="14" t="s">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="AX32" s="10" t="s">
         <v>77</v>
@@ -22637,7 +22610,7 @@
         <v>78</v>
       </c>
       <c r="BJ32" s="9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="BK32" s="9" t="s">
         <v>75</v>
@@ -22651,10 +22624,10 @@
     </row>
     <row r="33" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="n">
-        <v>306581</v>
+        <v>306799</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="9"/>
@@ -22663,22 +22636,22 @@
         <v>199</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>83</v>
+        <v>200</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="I33" s="9" t="s">
-        <v>174</v>
+        <v>149</v>
       </c>
       <c r="J33" s="9" t="s">
-        <v>78</v>
+        <v>122</v>
       </c>
       <c r="K33" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>96.5</v>
+        <v>515.8</v>
       </c>
       <c r="M33" s="12" t="n">
         <v>0</v>
@@ -22687,43 +22660,43 @@
         <v>1</v>
       </c>
       <c r="O33" s="12" t="n">
-        <v>96.5</v>
+        <v>499.56</v>
       </c>
       <c r="P33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q33" s="13" t="n">
-        <v>0</v>
+        <v>0.004176</v>
       </c>
       <c r="R33" s="12" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="S33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T33" s="14" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="U33" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V33" s="12" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="W33" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X33" s="9" t="s">
-        <v>174</v>
+        <v>149</v>
       </c>
       <c r="Y33" s="12" t="n">
-        <v>0</v>
+        <v>16.24</v>
       </c>
       <c r="Z33" s="12" t="n">
-        <v>96.5</v>
+        <v>499.56</v>
       </c>
       <c r="AA33" s="12" t="n">
-        <v>3.86</v>
+        <v>34.97</v>
       </c>
       <c r="AB33" s="12" t="n">
         <v>0</v>
@@ -22789,10 +22762,10 @@
         <v>74</v>
       </c>
       <c r="AW33" s="14" t="s">
-        <v>111</v>
+        <v>173</v>
       </c>
       <c r="AX33" s="10" t="s">
-        <v>170</v>
+        <v>77</v>
       </c>
       <c r="AY33" s="14" t="s">
         <v>75</v>
@@ -22828,7 +22801,7 @@
         <v>78</v>
       </c>
       <c r="BJ33" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="BK33" s="9" t="s">
         <v>75</v>
@@ -22842,79 +22815,79 @@
     </row>
     <row r="34" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="n">
-        <v>306585</v>
+        <v>306823</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
       <c r="F34" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G34" s="10" t="s">
         <v>83</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>132</v>
+        <v>183</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>174</v>
+        <v>149</v>
       </c>
       <c r="J34" s="9" t="s">
-        <v>157</v>
+        <v>205</v>
       </c>
       <c r="K34" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>24038.11</v>
+        <v>5775.71</v>
       </c>
       <c r="M34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="O34" s="12" t="n">
-        <v>22949.18</v>
+        <v>5510.71</v>
       </c>
       <c r="P34" s="12" t="n">
-        <v>659</v>
+        <v>265</v>
       </c>
       <c r="Q34" s="13" t="n">
-        <v>0.022336</v>
+        <v>0</v>
       </c>
       <c r="R34" s="12" t="n">
-        <v>5.96</v>
+        <v>3.5</v>
       </c>
       <c r="S34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T34" s="14" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="U34" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V34" s="12" t="n">
-        <v>82.46</v>
+        <v>42</v>
       </c>
       <c r="W34" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X34" s="9" t="s">
-        <v>174</v>
+        <v>149</v>
       </c>
       <c r="Y34" s="12" t="n">
-        <v>429.93</v>
+        <v>0</v>
       </c>
       <c r="Z34" s="12" t="n">
-        <v>23608.18</v>
+        <v>5775.71</v>
       </c>
       <c r="AA34" s="12" t="n">
-        <v>944.32</v>
+        <v>404.3</v>
       </c>
       <c r="AB34" s="12" t="n">
         <v>0</v>
@@ -23019,7 +22992,7 @@
         <v>78</v>
       </c>
       <c r="BJ34" s="9" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="BK34" s="9" t="s">
         <v>75</v>
@@ -23033,34 +23006,34 @@
     </row>
     <row r="35" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="n">
-        <v>306675</v>
+        <v>306845</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>64</v>
+        <v>208</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
       <c r="E35" s="9"/>
       <c r="F35" s="9" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>174</v>
+        <v>149</v>
       </c>
       <c r="I35" s="9" t="s">
-        <v>207</v>
+        <v>149</v>
       </c>
       <c r="J35" s="9" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="K35" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>3116.85</v>
+        <v>935.55</v>
       </c>
       <c r="M35" s="12" t="n">
         <v>0</v>
@@ -23069,22 +23042,22 @@
         <v>1</v>
       </c>
       <c r="O35" s="12" t="n">
-        <v>3116.85</v>
+        <v>935.55</v>
       </c>
       <c r="P35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q35" s="13" t="n">
-        <v>0.011766</v>
+        <v>0</v>
       </c>
       <c r="R35" s="12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T35" s="14" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="U35" s="15" t="s">
         <v>72</v>
@@ -23096,16 +23069,16 @@
         <v>73</v>
       </c>
       <c r="X35" s="9" t="s">
-        <v>207</v>
+        <v>149</v>
       </c>
       <c r="Y35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z35" s="12" t="n">
-        <v>3116.85</v>
+        <v>935.55</v>
       </c>
       <c r="AA35" s="12" t="n">
-        <v>218.18</v>
+        <v>65.49</v>
       </c>
       <c r="AB35" s="12" t="n">
         <v>0</v>
@@ -23210,7 +23183,7 @@
         <v>78</v>
       </c>
       <c r="BJ35" s="9" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="BK35" s="9" t="s">
         <v>75</v>
@@ -23223,900 +23196,534 @@
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="8" t="n">
-        <v>306713</v>
-      </c>
-      <c r="B36" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="G36" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="H36" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="I36" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="J36" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="K36" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="L36" s="12" t="n">
-        <v>3485.6</v>
-      </c>
-      <c r="M36" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O36" s="12" t="n">
-        <v>3288.3</v>
-      </c>
-      <c r="P36" s="12" t="n">
-        <v>197.3</v>
-      </c>
-      <c r="Q36" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" s="12" t="n">
+      <c r="A36" s="4"/>
+    </row>
+    <row r="37" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="17" t="s">
+        <v>213</v>
+      </c>
+      <c r="B37" s="17"/>
+      <c r="C37" s="17"/>
+      <c r="D37" s="17"/>
+      <c r="E37" s="17"/>
+      <c r="F37" s="17"/>
+      <c r="G37" s="17"/>
+      <c r="H37" s="17"/>
+      <c r="I37" s="17"/>
+      <c r="J37" s="17"/>
+      <c r="K37" s="17"/>
+      <c r="L37" s="17"/>
+      <c r="M37" s="17"/>
+      <c r="N37" s="17"/>
+      <c r="O37" s="17"/>
+      <c r="P37" s="17"/>
+      <c r="Q37" s="17"/>
+      <c r="R37" s="17"/>
+      <c r="S37" s="17"/>
+      <c r="T37" s="17"/>
+      <c r="U37" s="17"/>
+      <c r="V37" s="17"/>
+    </row>
+    <row r="38" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="18" t="s">
+        <v>214</v>
+      </c>
+      <c r="B38" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C38" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D38" s="18" t="s">
+        <v>215</v>
+      </c>
+      <c r="E38" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F38" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="G38" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H38" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="I38" s="18" t="s">
+        <v>216</v>
+      </c>
+      <c r="J38" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="K38" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="L38" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="M38" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="N38" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="O38" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="P38" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q38" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="R38" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="S36" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" s="14" t="s">
-        <v>213</v>
-      </c>
-      <c r="U36" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="V36" s="12" t="n">
-        <v>29</v>
-      </c>
-      <c r="W36" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="X36" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="Y36" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z36" s="12" t="n">
-        <v>3485.6</v>
-      </c>
-      <c r="AA36" s="12" t="n">
-        <v>139.42</v>
-      </c>
-      <c r="AB36" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC36" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD36" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE36" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF36" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG36" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH36" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI36" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ36" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AK36" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL36" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM36" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AN36" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AO36" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AP36" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ36" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR36" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS36" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT36" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU36" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV36" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW36" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="AX36" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="AY36" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ36" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA36" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB36" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BC36" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD36" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE36" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BF36" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BG36" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="BH36" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BI36" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="BJ36" s="9" t="s">
-        <v>214</v>
-      </c>
-      <c r="BK36" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BL36" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BM36" s="16" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="8" t="n">
-        <v>306724</v>
-      </c>
-      <c r="B37" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="G37" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="H37" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="I37" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="J37" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="K37" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="L37" s="12" t="n">
-        <v>976.79</v>
-      </c>
-      <c r="M37" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="O37" s="12" t="n">
-        <v>970.48</v>
-      </c>
-      <c r="P37" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" s="14" t="s">
-        <v>217</v>
-      </c>
-      <c r="U37" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="V37" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W37" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="X37" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="Y37" s="12" t="n">
-        <v>6.31</v>
-      </c>
-      <c r="Z37" s="12" t="n">
-        <v>976.79</v>
-      </c>
-      <c r="AA37" s="12" t="n">
-        <v>68.38</v>
-      </c>
-      <c r="AB37" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC37" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD37" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE37" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF37" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG37" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH37" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI37" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ37" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AK37" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL37" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM37" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AN37" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AO37" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AP37" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ37" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR37" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS37" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT37" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU37" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV37" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW37" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="AX37" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="AY37" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ37" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA37" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB37" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BC37" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD37" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE37" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BF37" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BG37" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="BH37" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BI37" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="BJ37" s="9" t="s">
+      <c r="S38" s="18" t="s">
         <v>218</v>
       </c>
-      <c r="BK37" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BL37" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BM37" s="16" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="8" t="n">
-        <v>306726</v>
-      </c>
-      <c r="B38" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C38" s="9"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="9"/>
-      <c r="F38" s="9" t="s">
+      <c r="T38" s="18" t="s">
         <v>219</v>
       </c>
-      <c r="G38" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="H38" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="I38" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="J38" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="K38" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="L38" s="12" t="n">
-        <v>846.74</v>
-      </c>
-      <c r="M38" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O38" s="12" t="n">
-        <v>846.74</v>
-      </c>
-      <c r="P38" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" s="12" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="S38" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" s="14" t="s">
-        <v>220</v>
-      </c>
-      <c r="U38" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="V38" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="W38" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="X38" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="Y38" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z38" s="12" t="n">
-        <v>846.74</v>
-      </c>
-      <c r="AA38" s="12" t="n">
-        <v>59.27</v>
-      </c>
-      <c r="AB38" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC38" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD38" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE38" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF38" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG38" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH38" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI38" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ38" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AK38" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL38" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM38" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AN38" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AO38" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AP38" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ38" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR38" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS38" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT38" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU38" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV38" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW38" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="AX38" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="AY38" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ38" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA38" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB38" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BC38" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD38" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE38" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BF38" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BG38" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="BH38" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BI38" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="BJ38" s="9" t="s">
-        <v>221</v>
-      </c>
-      <c r="BK38" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BL38" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BM38" s="16" t="s">
-        <v>80</v>
+      <c r="U38" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="V38" s="18" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="4"/>
+      <c r="A39" s="19" t="n">
+        <v>31</v>
+      </c>
+      <c r="B39" s="19" t="n">
+        <v>1067.38</v>
+      </c>
+      <c r="C39" s="19" t="n">
+        <v>1221.3</v>
+      </c>
+      <c r="D39" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="19" t="n">
+        <v>1245.83</v>
+      </c>
+      <c r="F39" s="19" t="n">
+        <v>109775.63</v>
+      </c>
+      <c r="G39" s="19" t="n">
+        <v>5812.3</v>
+      </c>
+      <c r="H39" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" s="19" t="n">
+        <v>116399.35</v>
+      </c>
+      <c r="L39" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" s="20" t="n">
+        <v>0.976817</v>
+      </c>
+      <c r="S39" s="19" t="n">
+        <v>114999.6</v>
+      </c>
+      <c r="T39" s="19" t="n">
+        <v>116399.35</v>
+      </c>
+      <c r="U39" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="17" t="s">
+      <c r="A40" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B40" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C40" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D40" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="E40" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="F40" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="G40" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="H40" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="I40" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="J40" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="K40" s="18" t="s">
+        <v>220</v>
+      </c>
+      <c r="L40" s="18" t="s">
+        <v>221</v>
+      </c>
+      <c r="M40" s="18" t="s">
         <v>222</v>
       </c>
-      <c r="B40" s="17"/>
-      <c r="C40" s="17"/>
-      <c r="D40" s="17"/>
-      <c r="E40" s="17"/>
-      <c r="F40" s="17"/>
-      <c r="G40" s="17"/>
-      <c r="H40" s="17"/>
-      <c r="I40" s="17"/>
-      <c r="J40" s="17"/>
-      <c r="K40" s="17"/>
-      <c r="L40" s="17"/>
-      <c r="M40" s="17"/>
-      <c r="N40" s="17"/>
-      <c r="O40" s="17"/>
-      <c r="P40" s="17"/>
-      <c r="Q40" s="17"/>
-      <c r="R40" s="17"/>
-      <c r="S40" s="17"/>
-      <c r="T40" s="17"/>
-      <c r="U40" s="17"/>
-      <c r="V40" s="17"/>
     </row>
-    <row r="41" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="18" t="s">
-        <v>223</v>
-      </c>
-      <c r="B41" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C41" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D41" s="18" t="s">
-        <v>224</v>
-      </c>
-      <c r="E41" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F41" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="G41" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="H41" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="I41" s="18" t="s">
-        <v>225</v>
-      </c>
-      <c r="J41" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="K41" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="L41" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="M41" s="18" t="s">
-        <v>226</v>
-      </c>
-      <c r="N41" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="O41" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="P41" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q41" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="R41" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="S41" s="18" t="s">
-        <v>227</v>
-      </c>
-      <c r="T41" s="18" t="s">
-        <v>228</v>
-      </c>
-      <c r="U41" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="V41" s="18" t="s">
-        <v>37</v>
+    <row r="41" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="19" t="n">
+        <v>172.53</v>
+      </c>
+      <c r="B41" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="19" t="n">
+        <v>45.76</v>
+      </c>
+      <c r="E41" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" s="19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="19" t="n">
-        <v>34</v>
-      </c>
-      <c r="B42" s="19" t="n">
-        <v>4501.31</v>
-      </c>
-      <c r="C42" s="19" t="n">
-        <v>956.3</v>
-      </c>
-      <c r="D42" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" s="19" t="n">
-        <v>3005.48</v>
-      </c>
-      <c r="F42" s="19" t="n">
-        <v>130245.98</v>
-      </c>
-      <c r="G42" s="19" t="n">
-        <v>6624.12</v>
-      </c>
-      <c r="H42" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" s="19" t="n">
-        <v>138629.35</v>
-      </c>
-      <c r="L42" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M42" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R42" s="20" t="n">
-        <v>1.268606</v>
-      </c>
-      <c r="S42" s="19" t="n">
-        <v>139168.88</v>
-      </c>
-      <c r="T42" s="19" t="n">
-        <v>138629.35</v>
-      </c>
-      <c r="U42" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V42" s="19" t="n">
-        <v>0</v>
-      </c>
+      <c r="A42" s="4"/>
     </row>
     <row r="43" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="B43" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C43" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="D43" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E43" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="F43" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="G43" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="H43" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="I43" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="J43" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="K43" s="18" t="s">
-        <v>229</v>
-      </c>
-      <c r="L43" s="18" t="s">
-        <v>230</v>
-      </c>
-      <c r="M43" s="18" t="s">
-        <v>231</v>
-      </c>
+      <c r="A43" s="21" t="s">
+        <v>223</v>
+      </c>
+      <c r="B43" s="21"/>
+      <c r="C43" s="21"/>
+      <c r="D43" s="21"/>
+      <c r="E43" s="21"/>
+      <c r="F43" s="21"/>
+      <c r="G43" s="21"/>
+      <c r="H43" s="21"/>
+      <c r="I43" s="21"/>
+      <c r="J43" s="21"/>
+      <c r="K43" s="21"/>
+      <c r="L43" s="21"/>
+      <c r="M43" s="21"/>
+      <c r="N43" s="21"/>
+      <c r="O43" s="21"/>
+      <c r="P43" s="21"/>
+      <c r="Q43" s="21"/>
+      <c r="R43" s="21"/>
+      <c r="S43" s="21"/>
+      <c r="T43" s="21"/>
+      <c r="U43" s="21"/>
+      <c r="V43" s="21"/>
+      <c r="W43" s="21"/>
+      <c r="X43" s="21"/>
+      <c r="Y43" s="21"/>
+      <c r="Z43" s="21"/>
+      <c r="AA43" s="21"/>
+      <c r="AB43" s="21"/>
+      <c r="AC43" s="21"/>
+      <c r="AD43" s="21"/>
+      <c r="AE43" s="21"/>
+      <c r="AF43" s="21"/>
+      <c r="AG43" s="21"/>
+      <c r="AH43" s="21"/>
+      <c r="AI43" s="21"/>
+      <c r="AJ43" s="21"/>
+      <c r="AK43" s="21"/>
+      <c r="AL43" s="21"/>
+      <c r="AM43" s="21"/>
+      <c r="AN43" s="21"/>
+      <c r="AO43" s="21"/>
+      <c r="AP43" s="21"/>
+      <c r="AQ43" s="21"/>
+      <c r="AR43" s="21"/>
+      <c r="AS43" s="21"/>
+      <c r="AT43" s="21"/>
+      <c r="AU43" s="21"/>
+      <c r="AV43" s="21"/>
+      <c r="AW43" s="21"/>
+      <c r="AX43" s="21"/>
+      <c r="AY43" s="21"/>
+      <c r="AZ43" s="21"/>
+      <c r="BA43" s="21"/>
+      <c r="BB43" s="21"/>
+      <c r="BC43" s="21"/>
+      <c r="BD43" s="21"/>
+      <c r="BE43" s="21"/>
+      <c r="BF43" s="21"/>
+      <c r="BG43" s="21"/>
+      <c r="BH43" s="21"/>
+      <c r="BI43" s="21"/>
+      <c r="BJ43" s="21"/>
+      <c r="BK43" s="21"/>
+      <c r="BL43" s="21"/>
+      <c r="BM43" s="21"/>
     </row>
     <row r="44" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="19" t="n">
-        <v>223.38</v>
-      </c>
-      <c r="B44" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C44" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D44" s="19" t="n">
-        <v>46.67</v>
-      </c>
-      <c r="E44" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" s="19" t="n">
-        <v>0</v>
-      </c>
+      <c r="A44" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B44" s="4"/>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="K44" s="4"/>
+      <c r="L44" s="4"/>
+      <c r="M44" s="4"/>
+      <c r="N44" s="4"/>
+      <c r="O44" s="4"/>
+      <c r="P44" s="4"/>
+      <c r="Q44" s="4"/>
+      <c r="R44" s="4"/>
+      <c r="S44" s="4"/>
+      <c r="T44" s="4"/>
+      <c r="U44" s="4"/>
+      <c r="V44" s="4"/>
+      <c r="W44" s="4"/>
+      <c r="X44" s="4"/>
+      <c r="Y44" s="4"/>
+      <c r="Z44" s="4"/>
+      <c r="AA44" s="4"/>
+      <c r="AB44" s="4"/>
+      <c r="AC44" s="4"/>
+      <c r="AD44" s="4"/>
+      <c r="AE44" s="4"/>
+      <c r="AF44" s="4"/>
+      <c r="AG44" s="4"/>
+      <c r="AH44" s="4"/>
+      <c r="AI44" s="4"/>
+      <c r="AJ44" s="4"/>
+      <c r="AK44" s="4"/>
+      <c r="AL44" s="4"/>
+      <c r="AM44" s="4"/>
+      <c r="AN44" s="4"/>
+      <c r="AO44" s="4"/>
+      <c r="AP44" s="4"/>
+      <c r="AQ44" s="4"/>
+      <c r="AR44" s="4"/>
+      <c r="AS44" s="4"/>
+      <c r="AT44" s="4"/>
+      <c r="AU44" s="4"/>
+      <c r="AV44" s="4"/>
+      <c r="AW44" s="4"/>
+      <c r="AX44" s="4"/>
+      <c r="AY44" s="4"/>
+      <c r="AZ44" s="4"/>
+      <c r="BA44" s="4"/>
+      <c r="BB44" s="4"/>
+      <c r="BC44" s="4"/>
+      <c r="BD44" s="4"/>
+      <c r="BE44" s="4"/>
+      <c r="BF44" s="4"/>
+      <c r="BG44" s="4"/>
+      <c r="BH44" s="4"/>
+      <c r="BI44" s="4"/>
+      <c r="BJ44" s="4"/>
+      <c r="BK44" s="4"/>
+      <c r="BL44" s="4"/>
+      <c r="BM44" s="4"/>
     </row>
     <row r="45" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="4"/>
+      <c r="A45" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="B45" s="4"/>
+      <c r="C45" s="4"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+      <c r="K45" s="4"/>
+      <c r="L45" s="4"/>
+      <c r="M45" s="4"/>
+      <c r="N45" s="4"/>
+      <c r="O45" s="4"/>
+      <c r="P45" s="4"/>
+      <c r="Q45" s="4"/>
+      <c r="R45" s="4"/>
+      <c r="S45" s="4"/>
+      <c r="T45" s="4"/>
+      <c r="U45" s="4"/>
+      <c r="V45" s="4"/>
+      <c r="W45" s="4"/>
+      <c r="X45" s="4"/>
+      <c r="Y45" s="4"/>
+      <c r="Z45" s="4"/>
+      <c r="AA45" s="4"/>
+      <c r="AB45" s="4"/>
+      <c r="AC45" s="4"/>
+      <c r="AD45" s="4"/>
+      <c r="AE45" s="4"/>
+      <c r="AF45" s="4"/>
+      <c r="AG45" s="4"/>
+      <c r="AH45" s="4"/>
+      <c r="AI45" s="4"/>
+      <c r="AJ45" s="4"/>
+      <c r="AK45" s="4"/>
+      <c r="AL45" s="4"/>
+      <c r="AM45" s="4"/>
+      <c r="AN45" s="4"/>
+      <c r="AO45" s="4"/>
+      <c r="AP45" s="4"/>
+      <c r="AQ45" s="4"/>
+      <c r="AR45" s="4"/>
+      <c r="AS45" s="4"/>
+      <c r="AT45" s="4"/>
+      <c r="AU45" s="4"/>
+      <c r="AV45" s="4"/>
+      <c r="AW45" s="4"/>
+      <c r="AX45" s="4"/>
+      <c r="AY45" s="4"/>
+      <c r="AZ45" s="4"/>
+      <c r="BA45" s="4"/>
+      <c r="BB45" s="4"/>
+      <c r="BC45" s="4"/>
+      <c r="BD45" s="4"/>
+      <c r="BE45" s="4"/>
+      <c r="BF45" s="4"/>
+      <c r="BG45" s="4"/>
+      <c r="BH45" s="4"/>
+      <c r="BI45" s="4"/>
+      <c r="BJ45" s="4"/>
+      <c r="BK45" s="4"/>
+      <c r="BL45" s="4"/>
+      <c r="BM45" s="4"/>
     </row>
-    <row r="46" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="21" t="s">
-        <v>232</v>
-      </c>
-      <c r="B46" s="21"/>
-      <c r="C46" s="21"/>
-      <c r="D46" s="21"/>
-      <c r="E46" s="21"/>
-      <c r="F46" s="21"/>
-      <c r="G46" s="21"/>
-      <c r="H46" s="21"/>
-      <c r="I46" s="21"/>
-      <c r="J46" s="21"/>
-      <c r="K46" s="21"/>
-      <c r="L46" s="21"/>
-      <c r="M46" s="21"/>
-      <c r="N46" s="21"/>
-      <c r="O46" s="21"/>
-      <c r="P46" s="21"/>
-      <c r="Q46" s="21"/>
-      <c r="R46" s="21"/>
-      <c r="S46" s="21"/>
-      <c r="T46" s="21"/>
-      <c r="U46" s="21"/>
-      <c r="V46" s="21"/>
-      <c r="W46" s="21"/>
-      <c r="X46" s="21"/>
-      <c r="Y46" s="21"/>
-      <c r="Z46" s="21"/>
-      <c r="AA46" s="21"/>
-      <c r="AB46" s="21"/>
-      <c r="AC46" s="21"/>
-      <c r="AD46" s="21"/>
-      <c r="AE46" s="21"/>
-      <c r="AF46" s="21"/>
-      <c r="AG46" s="21"/>
-      <c r="AH46" s="21"/>
-      <c r="AI46" s="21"/>
-      <c r="AJ46" s="21"/>
-      <c r="AK46" s="21"/>
-      <c r="AL46" s="21"/>
-      <c r="AM46" s="21"/>
-      <c r="AN46" s="21"/>
-      <c r="AO46" s="21"/>
-      <c r="AP46" s="21"/>
-      <c r="AQ46" s="21"/>
-      <c r="AR46" s="21"/>
-      <c r="AS46" s="21"/>
-      <c r="AT46" s="21"/>
-      <c r="AU46" s="21"/>
-      <c r="AV46" s="21"/>
-      <c r="AW46" s="21"/>
-      <c r="AX46" s="21"/>
-      <c r="AY46" s="21"/>
-      <c r="AZ46" s="21"/>
-      <c r="BA46" s="21"/>
-      <c r="BB46" s="21"/>
-      <c r="BC46" s="21"/>
-      <c r="BD46" s="21"/>
-      <c r="BE46" s="21"/>
-      <c r="BF46" s="21"/>
-      <c r="BG46" s="21"/>
-      <c r="BH46" s="21"/>
-      <c r="BI46" s="21"/>
-      <c r="BJ46" s="21"/>
-      <c r="BK46" s="21"/>
-      <c r="BL46" s="21"/>
-      <c r="BM46" s="21"/>
+    <row r="46" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="B46" s="4"/>
+      <c r="C46" s="4"/>
+      <c r="D46" s="4"/>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4"/>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+      <c r="K46" s="4"/>
+      <c r="L46" s="4"/>
+      <c r="M46" s="4"/>
+      <c r="N46" s="4"/>
+      <c r="O46" s="4"/>
+      <c r="P46" s="4"/>
+      <c r="Q46" s="4"/>
+      <c r="R46" s="4"/>
+      <c r="S46" s="4"/>
+      <c r="T46" s="4"/>
+      <c r="U46" s="4"/>
+      <c r="V46" s="4"/>
+      <c r="W46" s="4"/>
+      <c r="X46" s="4"/>
+      <c r="Y46" s="4"/>
+      <c r="Z46" s="4"/>
+      <c r="AA46" s="4"/>
+      <c r="AB46" s="4"/>
+      <c r="AC46" s="4"/>
+      <c r="AD46" s="4"/>
+      <c r="AE46" s="4"/>
+      <c r="AF46" s="4"/>
+      <c r="AG46" s="4"/>
+      <c r="AH46" s="4"/>
+      <c r="AI46" s="4"/>
+      <c r="AJ46" s="4"/>
+      <c r="AK46" s="4"/>
+      <c r="AL46" s="4"/>
+      <c r="AM46" s="4"/>
+      <c r="AN46" s="4"/>
+      <c r="AO46" s="4"/>
+      <c r="AP46" s="4"/>
+      <c r="AQ46" s="4"/>
+      <c r="AR46" s="4"/>
+      <c r="AS46" s="4"/>
+      <c r="AT46" s="4"/>
+      <c r="AU46" s="4"/>
+      <c r="AV46" s="4"/>
+      <c r="AW46" s="4"/>
+      <c r="AX46" s="4"/>
+      <c r="AY46" s="4"/>
+      <c r="AZ46" s="4"/>
+      <c r="BA46" s="4"/>
+      <c r="BB46" s="4"/>
+      <c r="BC46" s="4"/>
+      <c r="BD46" s="4"/>
+      <c r="BE46" s="4"/>
+      <c r="BF46" s="4"/>
+      <c r="BG46" s="4"/>
+      <c r="BH46" s="4"/>
+      <c r="BI46" s="4"/>
+      <c r="BJ46" s="4"/>
+      <c r="BK46" s="4"/>
+      <c r="BL46" s="4"/>
+      <c r="BM46" s="4"/>
     </row>
     <row r="47" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="s">
-        <v>75</v>
+        <v>226</v>
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
@@ -24185,7 +23792,7 @@
     </row>
     <row r="48" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="4" t="s">
-        <v>233</v>
+        <v>22</v>
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
@@ -24254,7 +23861,7 @@
     </row>
     <row r="49" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="4" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
@@ -24323,7 +23930,7 @@
     </row>
     <row r="50" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="4" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
@@ -24392,7 +23999,7 @@
     </row>
     <row r="51" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="4" t="s">
-        <v>22</v>
+        <v>229</v>
       </c>
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
@@ -24461,7 +24068,7 @@
     </row>
     <row r="52" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="4" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
@@ -24530,7 +24137,7 @@
     </row>
     <row r="53" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="4" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
@@ -24597,215 +24204,8 @@
       <c r="BL53" s="4"/>
       <c r="BM53" s="4"/>
     </row>
-    <row r="54" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="B54" s="4"/>
-      <c r="C54" s="4"/>
-      <c r="D54" s="4"/>
-      <c r="E54" s="4"/>
-      <c r="F54" s="4"/>
-      <c r="G54" s="4"/>
-      <c r="H54" s="4"/>
-      <c r="I54" s="4"/>
-      <c r="J54" s="4"/>
-      <c r="K54" s="4"/>
-      <c r="L54" s="4"/>
-      <c r="M54" s="4"/>
-      <c r="N54" s="4"/>
-      <c r="O54" s="4"/>
-      <c r="P54" s="4"/>
-      <c r="Q54" s="4"/>
-      <c r="R54" s="4"/>
-      <c r="S54" s="4"/>
-      <c r="T54" s="4"/>
-      <c r="U54" s="4"/>
-      <c r="V54" s="4"/>
-      <c r="W54" s="4"/>
-      <c r="X54" s="4"/>
-      <c r="Y54" s="4"/>
-      <c r="Z54" s="4"/>
-      <c r="AA54" s="4"/>
-      <c r="AB54" s="4"/>
-      <c r="AC54" s="4"/>
-      <c r="AD54" s="4"/>
-      <c r="AE54" s="4"/>
-      <c r="AF54" s="4"/>
-      <c r="AG54" s="4"/>
-      <c r="AH54" s="4"/>
-      <c r="AI54" s="4"/>
-      <c r="AJ54" s="4"/>
-      <c r="AK54" s="4"/>
-      <c r="AL54" s="4"/>
-      <c r="AM54" s="4"/>
-      <c r="AN54" s="4"/>
-      <c r="AO54" s="4"/>
-      <c r="AP54" s="4"/>
-      <c r="AQ54" s="4"/>
-      <c r="AR54" s="4"/>
-      <c r="AS54" s="4"/>
-      <c r="AT54" s="4"/>
-      <c r="AU54" s="4"/>
-      <c r="AV54" s="4"/>
-      <c r="AW54" s="4"/>
-      <c r="AX54" s="4"/>
-      <c r="AY54" s="4"/>
-      <c r="AZ54" s="4"/>
-      <c r="BA54" s="4"/>
-      <c r="BB54" s="4"/>
-      <c r="BC54" s="4"/>
-      <c r="BD54" s="4"/>
-      <c r="BE54" s="4"/>
-      <c r="BF54" s="4"/>
-      <c r="BG54" s="4"/>
-      <c r="BH54" s="4"/>
-      <c r="BI54" s="4"/>
-      <c r="BJ54" s="4"/>
-      <c r="BK54" s="4"/>
-      <c r="BL54" s="4"/>
-      <c r="BM54" s="4"/>
-    </row>
-    <row r="55" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="B55" s="4"/>
-      <c r="C55" s="4"/>
-      <c r="D55" s="4"/>
-      <c r="E55" s="4"/>
-      <c r="F55" s="4"/>
-      <c r="G55" s="4"/>
-      <c r="H55" s="4"/>
-      <c r="I55" s="4"/>
-      <c r="J55" s="4"/>
-      <c r="K55" s="4"/>
-      <c r="L55" s="4"/>
-      <c r="M55" s="4"/>
-      <c r="N55" s="4"/>
-      <c r="O55" s="4"/>
-      <c r="P55" s="4"/>
-      <c r="Q55" s="4"/>
-      <c r="R55" s="4"/>
-      <c r="S55" s="4"/>
-      <c r="T55" s="4"/>
-      <c r="U55" s="4"/>
-      <c r="V55" s="4"/>
-      <c r="W55" s="4"/>
-      <c r="X55" s="4"/>
-      <c r="Y55" s="4"/>
-      <c r="Z55" s="4"/>
-      <c r="AA55" s="4"/>
-      <c r="AB55" s="4"/>
-      <c r="AC55" s="4"/>
-      <c r="AD55" s="4"/>
-      <c r="AE55" s="4"/>
-      <c r="AF55" s="4"/>
-      <c r="AG55" s="4"/>
-      <c r="AH55" s="4"/>
-      <c r="AI55" s="4"/>
-      <c r="AJ55" s="4"/>
-      <c r="AK55" s="4"/>
-      <c r="AL55" s="4"/>
-      <c r="AM55" s="4"/>
-      <c r="AN55" s="4"/>
-      <c r="AO55" s="4"/>
-      <c r="AP55" s="4"/>
-      <c r="AQ55" s="4"/>
-      <c r="AR55" s="4"/>
-      <c r="AS55" s="4"/>
-      <c r="AT55" s="4"/>
-      <c r="AU55" s="4"/>
-      <c r="AV55" s="4"/>
-      <c r="AW55" s="4"/>
-      <c r="AX55" s="4"/>
-      <c r="AY55" s="4"/>
-      <c r="AZ55" s="4"/>
-      <c r="BA55" s="4"/>
-      <c r="BB55" s="4"/>
-      <c r="BC55" s="4"/>
-      <c r="BD55" s="4"/>
-      <c r="BE55" s="4"/>
-      <c r="BF55" s="4"/>
-      <c r="BG55" s="4"/>
-      <c r="BH55" s="4"/>
-      <c r="BI55" s="4"/>
-      <c r="BJ55" s="4"/>
-      <c r="BK55" s="4"/>
-      <c r="BL55" s="4"/>
-      <c r="BM55" s="4"/>
-    </row>
-    <row r="56" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="B56" s="4"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="4"/>
-      <c r="E56" s="4"/>
-      <c r="F56" s="4"/>
-      <c r="G56" s="4"/>
-      <c r="H56" s="4"/>
-      <c r="I56" s="4"/>
-      <c r="J56" s="4"/>
-      <c r="K56" s="4"/>
-      <c r="L56" s="4"/>
-      <c r="M56" s="4"/>
-      <c r="N56" s="4"/>
-      <c r="O56" s="4"/>
-      <c r="P56" s="4"/>
-      <c r="Q56" s="4"/>
-      <c r="R56" s="4"/>
-      <c r="S56" s="4"/>
-      <c r="T56" s="4"/>
-      <c r="U56" s="4"/>
-      <c r="V56" s="4"/>
-      <c r="W56" s="4"/>
-      <c r="X56" s="4"/>
-      <c r="Y56" s="4"/>
-      <c r="Z56" s="4"/>
-      <c r="AA56" s="4"/>
-      <c r="AB56" s="4"/>
-      <c r="AC56" s="4"/>
-      <c r="AD56" s="4"/>
-      <c r="AE56" s="4"/>
-      <c r="AF56" s="4"/>
-      <c r="AG56" s="4"/>
-      <c r="AH56" s="4"/>
-      <c r="AI56" s="4"/>
-      <c r="AJ56" s="4"/>
-      <c r="AK56" s="4"/>
-      <c r="AL56" s="4"/>
-      <c r="AM56" s="4"/>
-      <c r="AN56" s="4"/>
-      <c r="AO56" s="4"/>
-      <c r="AP56" s="4"/>
-      <c r="AQ56" s="4"/>
-      <c r="AR56" s="4"/>
-      <c r="AS56" s="4"/>
-      <c r="AT56" s="4"/>
-      <c r="AU56" s="4"/>
-      <c r="AV56" s="4"/>
-      <c r="AW56" s="4"/>
-      <c r="AX56" s="4"/>
-      <c r="AY56" s="4"/>
-      <c r="AZ56" s="4"/>
-      <c r="BA56" s="4"/>
-      <c r="BB56" s="4"/>
-      <c r="BC56" s="4"/>
-      <c r="BD56" s="4"/>
-      <c r="BE56" s="4"/>
-      <c r="BF56" s="4"/>
-      <c r="BG56" s="4"/>
-      <c r="BH56" s="4"/>
-      <c r="BI56" s="4"/>
-      <c r="BJ56" s="4"/>
-      <c r="BK56" s="4"/>
-      <c r="BL56" s="4"/>
-      <c r="BM56" s="4"/>
-    </row>
   </sheetData>
-  <mergeCells count="50">
+  <mergeCells count="47">
     <mergeCell ref="A1:BI1"/>
     <mergeCell ref="BJ1:BM1"/>
     <mergeCell ref="A2:BM2"/>
@@ -24841,10 +24241,10 @@
     <mergeCell ref="B33:E33"/>
     <mergeCell ref="B34:E34"/>
     <mergeCell ref="B35:E35"/>
-    <mergeCell ref="B36:E36"/>
-    <mergeCell ref="B37:E37"/>
-    <mergeCell ref="B38:E38"/>
-    <mergeCell ref="A40:V40"/>
+    <mergeCell ref="A37:V37"/>
+    <mergeCell ref="A43:BM43"/>
+    <mergeCell ref="A44:BM44"/>
+    <mergeCell ref="A45:BM45"/>
     <mergeCell ref="A46:BM46"/>
     <mergeCell ref="A47:BM47"/>
     <mergeCell ref="A48:BM48"/>
@@ -24853,9 +24253,6 @@
     <mergeCell ref="A51:BM51"/>
     <mergeCell ref="A52:BM52"/>
     <mergeCell ref="A53:BM53"/>
-    <mergeCell ref="A54:BM54"/>
-    <mergeCell ref="A55:BM55"/>
-    <mergeCell ref="A56:BM56"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>

--- a/tratando_tabelas/finitura/entradas_finitura.xlsx
+++ b/tratando_tabelas/finitura/entradas_finitura.xlsx
@@ -20,12 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1352" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1672" uniqueCount="254">
   <si>
     <t xml:space="preserve">Santri ADM 1.1.5.7 R1</t>
   </si>
   <si>
-    <t xml:space="preserve">Emitido em: 07/05/2026 05:30:39</t>
+    <t xml:space="preserve">Emitido em: 11/05/2026 07:42:26</t>
   </si>
   <si>
     <t xml:space="preserve">Relação de entradas - Sintético</t>
@@ -265,30 +265,6 @@
     <t xml:space="preserve">Não</t>
   </si>
   <si>
-    <t xml:space="preserve">27.705 - DOKA - INDUSTRIA E COMERCIO LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.012,80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260401136190000131550010000613311329572229</t>
-  </si>
-  <si>
     <t xml:space="preserve">622.732</t>
   </si>
   <si>
@@ -316,25 +292,19 @@
     <t xml:space="preserve">1.856 - DEXCO S.A - METAIS</t>
   </si>
   <si>
-    <t xml:space="preserve">5.069.532</t>
+    <t xml:space="preserve">5.071.467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
   </si>
   <si>
     <t xml:space="preserve">27/04/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">42,44</t>
+    <t xml:space="preserve">126,70</t>
   </si>
   <si>
     <t xml:space="preserve">2.949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050695321391333760</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.071.467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126,70</t>
   </si>
   <si>
     <t xml:space="preserve">35260497837181002190550010050714671217480571</t>
@@ -349,13 +319,22 @@
     <t xml:space="preserve">35260497837181002190550010050714731527694305</t>
   </si>
   <si>
+    <t xml:space="preserve">623.380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.387,71</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260475339051000141550080006233801549441662</t>
+  </si>
+  <si>
     <t xml:space="preserve">623.684</t>
   </si>
   <si>
     <t xml:space="preserve">25/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28/04/2026</t>
   </si>
   <si>
     <t xml:space="preserve">23/05/2026</t>
@@ -365,21 +344,6 @@
   </si>
   <si>
     <t xml:space="preserve">42260475339051000141550080006236841835737409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.855 - DEXCO S.A - LOUCAS DECA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.146.188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">861,88</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002271550010021461881648923974</t>
   </si>
   <si>
     <t xml:space="preserve">9.134 - L.MARTINKOSKI &amp; CIA LTDA</t>
@@ -616,21 +580,6 @@
     <t xml:space="preserve">42260575339051000141550080006324231892898250</t>
   </si>
   <si>
-    <t xml:space="preserve">2.100 - DMFLEX IND E COMERCIO DE METAIS SANITARIOS LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">218.907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">515,80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260509270215000105550060002189071824131540</t>
-  </si>
-  <si>
     <t xml:space="preserve">25.941 - AQUECE METAIS FABRICACAO E MANUTENCAO LTDA</t>
   </si>
   <si>
@@ -659,6 +608,123 @@
   </si>
   <si>
     <t xml:space="preserve">43260586895448000136550010000648961248387979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.978,02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43260586895448000136550010000648951883526940</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">569,02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43260586895448000136550010000648971591022939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.954,76</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43260586895448000136550010000648981605277600</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.271,36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43260586895448000136550010000649011440833070</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.900</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.436,26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43260586895448000136550010000649001101985597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.157,12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43260586895448000136550010000648991337116425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.923 - NEW LINE ILUMINACAO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">224.569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39,50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260512077181000133550030002245691053712641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.619 - DICAN COMERCIO EXTERIOR LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.625,80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260505761373000107550010001200771315409772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">985,72</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43260586895448000136550010000649141474712664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.478,58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43260586895448000136550010000649121041239909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43260586895448000136550010000649111298829132</t>
   </si>
   <si>
     <t xml:space="preserve">Total geral</t>
@@ -16904,7 +16970,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BM53"/>
+  <dimension ref="A1:BM61"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="18"/>
@@ -17467,58 +17533,58 @@
     </row>
     <row r="6" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="n">
-        <v>305725</v>
+        <v>305821</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
       <c r="E6" s="9"/>
       <c r="F6" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H6" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="G6" s="10" t="s">
+      <c r="I6" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="J6" s="9" t="s">
         <v>83</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="I6" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="J6" s="9" t="s">
-        <v>86</v>
       </c>
       <c r="K6" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L6" s="12" t="n">
-        <v>10012.8</v>
+        <v>4462.34</v>
       </c>
       <c r="M6" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N6" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O6" s="12" t="n">
-        <v>10012.8</v>
+        <v>4462.34</v>
       </c>
       <c r="P6" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q6" s="13" t="n">
-        <v>0.750038</v>
+        <v>0.010272</v>
       </c>
       <c r="R6" s="12" t="n">
-        <v>38</v>
+        <v>3.7</v>
       </c>
       <c r="S6" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T6" s="14" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="U6" s="15" t="s">
         <v>72</v>
@@ -17530,16 +17596,16 @@
         <v>73</v>
       </c>
       <c r="X6" s="9" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="Y6" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z6" s="12" t="n">
-        <v>10012.8</v>
+        <v>4462.34</v>
       </c>
       <c r="AA6" s="12" t="n">
-        <v>400.51</v>
+        <v>312.36</v>
       </c>
       <c r="AB6" s="12" t="n">
         <v>0</v>
@@ -17644,7 +17710,7 @@
         <v>78</v>
       </c>
       <c r="BJ6" s="9" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="BK6" s="9" t="s">
         <v>75</v>
@@ -17658,7 +17724,7 @@
     </row>
     <row r="7" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="n">
-        <v>305821</v>
+        <v>305822</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>64</v>
@@ -17667,25 +17733,25 @@
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
       <c r="F7" s="9" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G7" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="K7" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L7" s="12" t="n">
-        <v>4462.34</v>
+        <v>1464.23</v>
       </c>
       <c r="M7" s="12" t="n">
         <v>0</v>
@@ -17694,22 +17760,22 @@
         <v>1</v>
       </c>
       <c r="O7" s="12" t="n">
-        <v>4462.34</v>
+        <v>1464.23</v>
       </c>
       <c r="P7" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q7" s="13" t="n">
-        <v>0.010272</v>
+        <v>0.002473</v>
       </c>
       <c r="R7" s="12" t="n">
-        <v>3.7</v>
+        <v>0.77</v>
       </c>
       <c r="S7" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T7" s="14" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="U7" s="15" t="s">
         <v>72</v>
@@ -17721,16 +17787,16 @@
         <v>73</v>
       </c>
       <c r="X7" s="9" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="Y7" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z7" s="12" t="n">
-        <v>4462.34</v>
+        <v>1464.23</v>
       </c>
       <c r="AA7" s="12" t="n">
-        <v>312.36</v>
+        <v>102.5</v>
       </c>
       <c r="AB7" s="12" t="n">
         <v>0</v>
@@ -17835,7 +17901,7 @@
         <v>78</v>
       </c>
       <c r="BJ7" s="9" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="BK7" s="9" t="s">
         <v>75</v>
@@ -17849,34 +17915,34 @@
     </row>
     <row r="8" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="n">
-        <v>305822</v>
+        <v>305957</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>64</v>
+        <v>89</v>
       </c>
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
       <c r="F8" s="9" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K8" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L8" s="12" t="n">
-        <v>1464.23</v>
+        <v>126.7</v>
       </c>
       <c r="M8" s="12" t="n">
         <v>0</v>
@@ -17885,43 +17951,43 @@
         <v>1</v>
       </c>
       <c r="O8" s="12" t="n">
-        <v>1464.23</v>
+        <v>118.97</v>
       </c>
       <c r="P8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q8" s="13" t="n">
-        <v>0.002473</v>
+        <v>0.001512</v>
       </c>
       <c r="R8" s="12" t="n">
-        <v>0.77</v>
+        <v>1.58</v>
       </c>
       <c r="S8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T8" s="14" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="U8" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V8" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W8" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X8" s="9" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="Y8" s="12" t="n">
-        <v>0</v>
+        <v>7.73</v>
       </c>
       <c r="Z8" s="12" t="n">
-        <v>1464.23</v>
+        <v>118.97</v>
       </c>
       <c r="AA8" s="12" t="n">
-        <v>102.5</v>
+        <v>4.76</v>
       </c>
       <c r="AB8" s="12" t="n">
         <v>0</v>
@@ -17990,7 +18056,7 @@
         <v>76</v>
       </c>
       <c r="AX8" s="10" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="AY8" s="14" t="s">
         <v>75</v>
@@ -18026,7 +18092,7 @@
         <v>78</v>
       </c>
       <c r="BJ8" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="BK8" s="9" t="s">
         <v>75</v>
@@ -18040,25 +18106,25 @@
     </row>
     <row r="9" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="n">
-        <v>305942</v>
+        <v>305966</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="9" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="J9" s="9" t="s">
         <v>78</v>
@@ -18067,31 +18133,31 @@
         <v>70</v>
       </c>
       <c r="L9" s="12" t="n">
-        <v>42.44</v>
+        <v>290.09</v>
       </c>
       <c r="M9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N9" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O9" s="12" t="n">
-        <v>39.85</v>
+        <v>272.38</v>
       </c>
       <c r="P9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q9" s="13" t="n">
-        <v>0.002284</v>
+        <v>0.003202</v>
       </c>
       <c r="R9" s="12" t="n">
-        <v>0.8</v>
+        <v>1.93</v>
       </c>
       <c r="S9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T9" s="14" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="U9" s="15" t="s">
         <v>72</v>
@@ -18103,16 +18169,16 @@
         <v>73</v>
       </c>
       <c r="X9" s="9" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="Y9" s="12" t="n">
-        <v>2.59</v>
+        <v>17.71</v>
       </c>
       <c r="Z9" s="12" t="n">
-        <v>39.85</v>
+        <v>272.38</v>
       </c>
       <c r="AA9" s="12" t="n">
-        <v>1.59</v>
+        <v>10.89</v>
       </c>
       <c r="AB9" s="12" t="n">
         <v>0</v>
@@ -18181,7 +18247,7 @@
         <v>76</v>
       </c>
       <c r="AX9" s="10" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="AY9" s="14" t="s">
         <v>75</v>
@@ -18217,7 +18283,7 @@
         <v>78</v>
       </c>
       <c r="BJ9" s="9" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="BK9" s="9" t="s">
         <v>75</v>
@@ -18231,34 +18297,34 @@
     </row>
     <row r="10" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="n">
-        <v>305957</v>
+        <v>306000</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>97</v>
+        <v>64</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
       <c r="F10" s="9" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="G10" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="J10" s="9" t="s">
         <v>83</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="J10" s="9" t="s">
-        <v>78</v>
       </c>
       <c r="K10" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L10" s="12" t="n">
-        <v>126.7</v>
+        <v>1387.71</v>
       </c>
       <c r="M10" s="12" t="n">
         <v>0</v>
@@ -18267,43 +18333,43 @@
         <v>1</v>
       </c>
       <c r="O10" s="12" t="n">
-        <v>118.97</v>
+        <v>1387.71</v>
       </c>
       <c r="P10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q10" s="13" t="n">
-        <v>0.001512</v>
+        <v>0.005525</v>
       </c>
       <c r="R10" s="12" t="n">
-        <v>1.58</v>
+        <v>2.87</v>
       </c>
       <c r="S10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T10" s="14" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="U10" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V10" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W10" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X10" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Y10" s="12" t="n">
-        <v>7.73</v>
+        <v>0</v>
       </c>
       <c r="Z10" s="12" t="n">
-        <v>118.97</v>
+        <v>1387.71</v>
       </c>
       <c r="AA10" s="12" t="n">
-        <v>4.76</v>
+        <v>97.14</v>
       </c>
       <c r="AB10" s="12" t="n">
         <v>0</v>
@@ -18372,7 +18438,7 @@
         <v>76</v>
       </c>
       <c r="AX10" s="10" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AY10" s="14" t="s">
         <v>75</v>
@@ -18408,7 +18474,7 @@
         <v>78</v>
       </c>
       <c r="BJ10" s="9" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="BK10" s="9" t="s">
         <v>75</v>
@@ -18422,79 +18488,79 @@
     </row>
     <row r="11" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="n">
-        <v>305966</v>
+        <v>306001</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>97</v>
+        <v>64</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
       <c r="F11" s="9" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>78</v>
+        <v>105</v>
       </c>
       <c r="K11" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>290.09</v>
+        <v>1181.41</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O11" s="12" t="n">
-        <v>272.38</v>
+        <v>1181.41</v>
       </c>
       <c r="P11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q11" s="13" t="n">
-        <v>0.003202</v>
+        <v>0.000412</v>
       </c>
       <c r="R11" s="12" t="n">
-        <v>1.93</v>
+        <v>0.71</v>
       </c>
       <c r="S11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T11" s="14" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="U11" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V11" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W11" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X11" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Y11" s="12" t="n">
-        <v>17.71</v>
+        <v>0</v>
       </c>
       <c r="Z11" s="12" t="n">
-        <v>272.38</v>
+        <v>1181.41</v>
       </c>
       <c r="AA11" s="12" t="n">
-        <v>10.89</v>
+        <v>82.7</v>
       </c>
       <c r="AB11" s="12" t="n">
         <v>0</v>
@@ -18563,7 +18629,7 @@
         <v>76</v>
       </c>
       <c r="AX11" s="10" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AY11" s="14" t="s">
         <v>75</v>
@@ -18599,7 +18665,7 @@
         <v>78</v>
       </c>
       <c r="BJ11" s="9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="BK11" s="9" t="s">
         <v>75</v>
@@ -18613,10 +18679,10 @@
     </row>
     <row r="12" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="n">
-        <v>306001</v>
+        <v>306150</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>64</v>
+        <v>108</v>
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
@@ -18625,46 +18691,46 @@
         <v>109</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="H12" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="J12" s="9" t="s">
         <v>110</v>
-      </c>
-      <c r="I12" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="J12" s="9" t="s">
-        <v>112</v>
       </c>
       <c r="K12" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>1181.41</v>
+        <v>2070.21</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O12" s="12" t="n">
-        <v>1181.41</v>
+        <v>1970.21</v>
       </c>
       <c r="P12" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q12" s="13" t="n">
-        <v>0.000412</v>
+        <v>0</v>
       </c>
       <c r="R12" s="12" t="n">
-        <v>0.71</v>
+        <v>4.15</v>
       </c>
       <c r="S12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T12" s="14" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="U12" s="15" t="s">
         <v>72</v>
@@ -18676,16 +18742,16 @@
         <v>73</v>
       </c>
       <c r="X12" s="9" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="Y12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z12" s="12" t="n">
-        <v>1181.41</v>
+        <v>2070.21</v>
       </c>
       <c r="AA12" s="12" t="n">
-        <v>82.7</v>
+        <v>144.92</v>
       </c>
       <c r="AB12" s="12" t="n">
         <v>0</v>
@@ -18790,7 +18856,7 @@
         <v>78</v>
       </c>
       <c r="BJ12" s="9" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="BK12" s="9" t="s">
         <v>75</v>
@@ -18804,58 +18870,58 @@
     </row>
     <row r="13" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="n">
-        <v>306005</v>
+        <v>306173</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
       <c r="F13" s="9" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="K13" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>861.88</v>
+        <v>3730.39</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O13" s="12" t="n">
-        <v>861.88</v>
+        <v>3730.39</v>
       </c>
       <c r="P13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q13" s="13" t="n">
-        <v>0.073796</v>
+        <v>0</v>
       </c>
       <c r="R13" s="12" t="n">
-        <v>43.13</v>
+        <v>0</v>
       </c>
       <c r="S13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T13" s="14" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="U13" s="15" t="s">
         <v>72</v>
@@ -18867,16 +18933,16 @@
         <v>73</v>
       </c>
       <c r="X13" s="9" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="Y13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z13" s="12" t="n">
-        <v>861.88</v>
+        <v>3730.39</v>
       </c>
       <c r="AA13" s="12" t="n">
-        <v>60.33</v>
+        <v>261.14</v>
       </c>
       <c r="AB13" s="12" t="n">
         <v>0</v>
@@ -18981,7 +19047,7 @@
         <v>78</v>
       </c>
       <c r="BJ13" s="9" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="BK13" s="9" t="s">
         <v>75</v>
@@ -18995,34 +19061,34 @@
     </row>
     <row r="14" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="n">
-        <v>306150</v>
+        <v>306327</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>120</v>
+        <v>64</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
       <c r="F14" s="9" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="K14" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>2070.21</v>
+        <v>10714.13</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>0</v>
@@ -19031,22 +19097,22 @@
         <v>2</v>
       </c>
       <c r="O14" s="12" t="n">
-        <v>1970.21</v>
+        <v>10714.13</v>
       </c>
       <c r="P14" s="12" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q14" s="13" t="n">
-        <v>0</v>
+        <v>0.020976</v>
       </c>
       <c r="R14" s="12" t="n">
-        <v>4.15</v>
+        <v>6.72</v>
       </c>
       <c r="S14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T14" s="14" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="U14" s="15" t="s">
         <v>72</v>
@@ -19058,16 +19124,16 @@
         <v>73</v>
       </c>
       <c r="X14" s="9" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="Y14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z14" s="12" t="n">
-        <v>2070.21</v>
+        <v>10714.13</v>
       </c>
       <c r="AA14" s="12" t="n">
-        <v>144.92</v>
+        <v>749.99</v>
       </c>
       <c r="AB14" s="12" t="n">
         <v>0</v>
@@ -19172,7 +19238,7 @@
         <v>78</v>
       </c>
       <c r="BJ14" s="9" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="BK14" s="9" t="s">
         <v>75</v>
@@ -19186,79 +19252,79 @@
     </row>
     <row r="15" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="n">
-        <v>306173</v>
+        <v>306329</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>120</v>
+        <v>64</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
       <c r="F15" s="9" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>99</v>
+        <v>122</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K15" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>3730.39</v>
+        <v>891.38</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O15" s="12" t="n">
-        <v>3730.39</v>
+        <v>891.38</v>
       </c>
       <c r="P15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q15" s="13" t="n">
-        <v>0</v>
+        <v>0.003922</v>
       </c>
       <c r="R15" s="12" t="n">
-        <v>0</v>
+        <v>0.41</v>
       </c>
       <c r="S15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T15" s="14" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="U15" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V15" s="12" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="W15" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X15" s="9" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="Y15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z15" s="12" t="n">
-        <v>3730.39</v>
+        <v>891.38</v>
       </c>
       <c r="AA15" s="12" t="n">
-        <v>261.14</v>
+        <v>62.4</v>
       </c>
       <c r="AB15" s="12" t="n">
         <v>0</v>
@@ -19363,7 +19429,7 @@
         <v>78</v>
       </c>
       <c r="BJ15" s="9" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="BK15" s="9" t="s">
         <v>75</v>
@@ -19377,7 +19443,7 @@
     </row>
     <row r="16" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="n">
-        <v>306327</v>
+        <v>306335</v>
       </c>
       <c r="B16" s="9" t="s">
         <v>64</v>
@@ -19386,49 +19452,49 @@
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
       <c r="F16" s="9" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G16" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="K16" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>10714.13</v>
+        <v>1593.54</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O16" s="12" t="n">
-        <v>10714.13</v>
+        <v>1593.54</v>
       </c>
       <c r="P16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q16" s="13" t="n">
-        <v>0.020976</v>
+        <v>0.005136</v>
       </c>
       <c r="R16" s="12" t="n">
-        <v>6.72</v>
+        <v>2.1</v>
       </c>
       <c r="S16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T16" s="14" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="U16" s="15" t="s">
         <v>72</v>
@@ -19440,16 +19506,16 @@
         <v>73</v>
       </c>
       <c r="X16" s="9" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="Y16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z16" s="12" t="n">
-        <v>10714.13</v>
+        <v>1593.54</v>
       </c>
       <c r="AA16" s="12" t="n">
-        <v>749.99</v>
+        <v>111.55</v>
       </c>
       <c r="AB16" s="12" t="n">
         <v>0</v>
@@ -19554,7 +19620,7 @@
         <v>78</v>
       </c>
       <c r="BJ16" s="9" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="BK16" s="9" t="s">
         <v>75</v>
@@ -19568,79 +19634,79 @@
     </row>
     <row r="17" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="n">
-        <v>306329</v>
+        <v>306338</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>64</v>
+        <v>129</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
       <c r="F17" s="9" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>135</v>
+        <v>78</v>
       </c>
       <c r="K17" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>891.38</v>
+        <v>900.38</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O17" s="12" t="n">
-        <v>891.38</v>
+        <v>900.38</v>
       </c>
       <c r="P17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q17" s="13" t="n">
-        <v>0.003922</v>
+        <v>0</v>
       </c>
       <c r="R17" s="12" t="n">
-        <v>0.41</v>
+        <v>0</v>
       </c>
       <c r="S17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T17" s="14" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="U17" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V17" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W17" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X17" s="9" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="Y17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z17" s="12" t="n">
-        <v>891.38</v>
+        <v>900.38</v>
       </c>
       <c r="AA17" s="12" t="n">
-        <v>62.4</v>
+        <v>36.02</v>
       </c>
       <c r="AB17" s="12" t="n">
         <v>0</v>
@@ -19709,7 +19775,7 @@
         <v>76</v>
       </c>
       <c r="AX17" s="10" t="s">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="AY17" s="14" t="s">
         <v>75</v>
@@ -19745,7 +19811,7 @@
         <v>78</v>
       </c>
       <c r="BJ17" s="9" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="BK17" s="9" t="s">
         <v>75</v>
@@ -19759,79 +19825,79 @@
     </row>
     <row r="18" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="n">
-        <v>306335</v>
+        <v>306454</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>64</v>
+        <v>134</v>
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
       <c r="F18" s="9" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>134</v>
+        <v>100</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="K18" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>1593.54</v>
+        <v>3167.76</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O18" s="12" t="n">
-        <v>1593.54</v>
+        <v>3167.76</v>
       </c>
       <c r="P18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q18" s="13" t="n">
-        <v>0.005136</v>
+        <v>0</v>
       </c>
       <c r="R18" s="12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T18" s="14" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="U18" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V18" s="12" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="W18" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X18" s="9" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="Y18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z18" s="12" t="n">
-        <v>1593.54</v>
+        <v>3167.76</v>
       </c>
       <c r="AA18" s="12" t="n">
-        <v>111.55</v>
+        <v>117.52</v>
       </c>
       <c r="AB18" s="12" t="n">
         <v>0</v>
@@ -19936,7 +20002,7 @@
         <v>78</v>
       </c>
       <c r="BJ18" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="BK18" s="9" t="s">
         <v>75</v>
@@ -19950,79 +20016,79 @@
     </row>
     <row r="19" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="n">
-        <v>306338</v>
+        <v>306477</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>141</v>
+        <v>89</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
       <c r="F19" s="9" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>78</v>
+        <v>141</v>
       </c>
       <c r="K19" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>900.38</v>
+        <v>3108.72</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O19" s="12" t="n">
-        <v>900.38</v>
+        <v>3108.72</v>
       </c>
       <c r="P19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q19" s="13" t="n">
-        <v>0</v>
+        <v>0.001598</v>
       </c>
       <c r="R19" s="12" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T19" s="14" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="U19" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V19" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W19" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X19" s="9" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="Y19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z19" s="12" t="n">
-        <v>900.38</v>
+        <v>3108.72</v>
       </c>
       <c r="AA19" s="12" t="n">
-        <v>36.02</v>
+        <v>217.61</v>
       </c>
       <c r="AB19" s="12" t="n">
         <v>0</v>
@@ -20091,7 +20157,7 @@
         <v>76</v>
       </c>
       <c r="AX19" s="10" t="s">
-        <v>144</v>
+        <v>77</v>
       </c>
       <c r="AY19" s="14" t="s">
         <v>75</v>
@@ -20127,7 +20193,7 @@
         <v>78</v>
       </c>
       <c r="BJ19" s="9" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="BK19" s="9" t="s">
         <v>75</v>
@@ -20141,79 +20207,79 @@
     </row>
     <row r="20" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="n">
-        <v>306454</v>
+        <v>306493</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>146</v>
+        <v>64</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
       <c r="F20" s="9" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="K20" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>3167.76</v>
+        <v>2876.8</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O20" s="12" t="n">
-        <v>3167.76</v>
+        <v>2701.22</v>
       </c>
       <c r="P20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q20" s="13" t="n">
-        <v>0</v>
+        <v>0.027908</v>
       </c>
       <c r="R20" s="12" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="S20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T20" s="14" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="U20" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V20" s="12" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="W20" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X20" s="9" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="Y20" s="12" t="n">
-        <v>0</v>
+        <v>175.58</v>
       </c>
       <c r="Z20" s="12" t="n">
-        <v>3167.76</v>
+        <v>2701.22</v>
       </c>
       <c r="AA20" s="12" t="n">
-        <v>117.52</v>
+        <v>189.09</v>
       </c>
       <c r="AB20" s="12" t="n">
         <v>0</v>
@@ -20318,7 +20384,7 @@
         <v>78</v>
       </c>
       <c r="BJ20" s="9" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="BK20" s="9" t="s">
         <v>75</v>
@@ -20332,79 +20398,79 @@
     </row>
     <row r="21" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="n">
-        <v>306477</v>
+        <v>306535</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>97</v>
+        <v>147</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
       <c r="F21" s="9" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="K21" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>3108.72</v>
+        <v>5384.2</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O21" s="12" t="n">
-        <v>3108.72</v>
+        <v>5384.2</v>
       </c>
       <c r="P21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q21" s="13" t="n">
-        <v>0.001598</v>
+        <v>0.023054</v>
       </c>
       <c r="R21" s="12" t="n">
-        <v>2.6</v>
+        <v>28.62</v>
       </c>
       <c r="S21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T21" s="14" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="U21" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V21" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W21" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X21" s="9" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="Y21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z21" s="12" t="n">
-        <v>3108.72</v>
+        <v>0</v>
       </c>
       <c r="AA21" s="12" t="n">
-        <v>217.61</v>
+        <v>0</v>
       </c>
       <c r="AB21" s="12" t="n">
         <v>0</v>
@@ -20473,7 +20539,7 @@
         <v>76</v>
       </c>
       <c r="AX21" s="10" t="s">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="AY21" s="14" t="s">
         <v>75</v>
@@ -20509,7 +20575,7 @@
         <v>78</v>
       </c>
       <c r="BJ21" s="9" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="BK21" s="9" t="s">
         <v>75</v>
@@ -20523,25 +20589,25 @@
     </row>
     <row r="22" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="n">
-        <v>306493</v>
+        <v>306540</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>64</v>
+        <v>151</v>
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
       <c r="F22" s="9" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="J22" s="9" t="s">
         <v>153</v>
@@ -20550,52 +20616,52 @@
         <v>70</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>2876.8</v>
+        <v>6638.26</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>0</v>
+        <v>1067.38</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O22" s="12" t="n">
-        <v>2701.22</v>
+        <v>7115.9</v>
       </c>
       <c r="P22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q22" s="13" t="n">
-        <v>0.027908</v>
+        <v>0</v>
       </c>
       <c r="R22" s="12" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="S22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T22" s="14" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="U22" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V22" s="12" t="n">
-        <v>28</v>
+        <v>105</v>
       </c>
       <c r="W22" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X22" s="9" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="Y22" s="12" t="n">
-        <v>175.58</v>
+        <v>589.74</v>
       </c>
       <c r="Z22" s="12" t="n">
-        <v>2701.22</v>
+        <v>6048.52</v>
       </c>
       <c r="AA22" s="12" t="n">
-        <v>189.09</v>
+        <v>241.94</v>
       </c>
       <c r="AB22" s="12" t="n">
         <v>0</v>
@@ -20700,7 +20766,7 @@
         <v>78</v>
       </c>
       <c r="BJ22" s="9" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="BK22" s="9" t="s">
         <v>75</v>
@@ -20714,79 +20780,79 @@
     </row>
     <row r="23" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="n">
-        <v>306535</v>
+        <v>306545</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>159</v>
+        <v>129</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="9" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>78</v>
+        <v>157</v>
       </c>
       <c r="K23" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>5384.2</v>
+        <v>7171.52</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O23" s="12" t="n">
-        <v>5384.2</v>
+        <v>7171.52</v>
       </c>
       <c r="P23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q23" s="13" t="n">
-        <v>0.023054</v>
+        <v>0</v>
       </c>
       <c r="R23" s="12" t="n">
-        <v>28.62</v>
+        <v>0</v>
       </c>
       <c r="S23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T23" s="14" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="U23" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V23" s="12" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="W23" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X23" s="9" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="Y23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z23" s="12" t="n">
-        <v>0</v>
+        <v>7171.52</v>
       </c>
       <c r="AA23" s="12" t="n">
-        <v>0</v>
+        <v>286.86</v>
       </c>
       <c r="AB23" s="12" t="n">
         <v>0</v>
@@ -20855,7 +20921,7 @@
         <v>76</v>
       </c>
       <c r="AX23" s="10" t="s">
-        <v>144</v>
+        <v>77</v>
       </c>
       <c r="AY23" s="14" t="s">
         <v>75</v>
@@ -20891,7 +20957,7 @@
         <v>78</v>
       </c>
       <c r="BJ23" s="9" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="BK23" s="9" t="s">
         <v>75</v>
@@ -20905,43 +20971,43 @@
     </row>
     <row r="24" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="n">
-        <v>306540</v>
+        <v>306579</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>163</v>
+        <v>129</v>
       </c>
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
       <c r="F24" s="9" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="K24" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>6638.26</v>
+        <v>7171.52</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>1067.38</v>
+        <v>0</v>
       </c>
       <c r="N24" s="12" t="n">
         <v>3</v>
       </c>
       <c r="O24" s="12" t="n">
-        <v>7115.9</v>
+        <v>7171.52</v>
       </c>
       <c r="P24" s="12" t="n">
         <v>0</v>
@@ -20956,28 +21022,28 @@
         <v>0</v>
       </c>
       <c r="T24" s="14" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="U24" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V24" s="12" t="n">
-        <v>105</v>
+        <v>61.66</v>
       </c>
       <c r="W24" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X24" s="9" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="Y24" s="12" t="n">
-        <v>589.74</v>
+        <v>0</v>
       </c>
       <c r="Z24" s="12" t="n">
-        <v>6048.52</v>
+        <v>7171.52</v>
       </c>
       <c r="AA24" s="12" t="n">
-        <v>241.94</v>
+        <v>286.86</v>
       </c>
       <c r="AB24" s="12" t="n">
         <v>0</v>
@@ -21043,7 +21109,7 @@
         <v>74</v>
       </c>
       <c r="AW24" s="14" t="s">
-        <v>76</v>
+        <v>161</v>
       </c>
       <c r="AX24" s="10" t="s">
         <v>77</v>
@@ -21082,7 +21148,7 @@
         <v>78</v>
       </c>
       <c r="BJ24" s="9" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="BK24" s="9" t="s">
         <v>75</v>
@@ -21096,43 +21162,43 @@
     </row>
     <row r="25" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="n">
-        <v>306545</v>
+        <v>306581</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>169</v>
+        <v>78</v>
       </c>
       <c r="K25" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>7171.52</v>
+        <v>96.5</v>
       </c>
       <c r="M25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O25" s="12" t="n">
-        <v>7171.52</v>
+        <v>96.5</v>
       </c>
       <c r="P25" s="12" t="n">
         <v>0</v>
@@ -21147,28 +21213,28 @@
         <v>0</v>
       </c>
       <c r="T25" s="14" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="U25" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V25" s="12" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="W25" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X25" s="9" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="Y25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z25" s="12" t="n">
-        <v>7171.52</v>
+        <v>96.5</v>
       </c>
       <c r="AA25" s="12" t="n">
-        <v>286.86</v>
+        <v>3.86</v>
       </c>
       <c r="AB25" s="12" t="n">
         <v>0</v>
@@ -21234,10 +21300,10 @@
         <v>74</v>
       </c>
       <c r="AW25" s="14" t="s">
-        <v>76</v>
+        <v>161</v>
       </c>
       <c r="AX25" s="10" t="s">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="AY25" s="14" t="s">
         <v>75</v>
@@ -21273,7 +21339,7 @@
         <v>78</v>
       </c>
       <c r="BJ25" s="9" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="BK25" s="9" t="s">
         <v>75</v>
@@ -21287,79 +21353,79 @@
     </row>
     <row r="26" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="n">
-        <v>306579</v>
+        <v>306585</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>134</v>
+        <v>100</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="K26" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>7171.52</v>
+        <v>24038.11</v>
       </c>
       <c r="M26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="O26" s="12" t="n">
-        <v>7171.52</v>
+        <v>22949.18</v>
       </c>
       <c r="P26" s="12" t="n">
-        <v>0</v>
+        <v>659</v>
       </c>
       <c r="Q26" s="13" t="n">
-        <v>0</v>
+        <v>0.022336</v>
       </c>
       <c r="R26" s="12" t="n">
-        <v>0</v>
+        <v>5.96</v>
       </c>
       <c r="S26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T26" s="14" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="U26" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V26" s="12" t="n">
-        <v>61.66</v>
+        <v>82.46</v>
       </c>
       <c r="W26" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X26" s="9" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="Y26" s="12" t="n">
-        <v>0</v>
+        <v>429.93</v>
       </c>
       <c r="Z26" s="12" t="n">
-        <v>7171.52</v>
+        <v>23608.18</v>
       </c>
       <c r="AA26" s="12" t="n">
-        <v>286.86</v>
+        <v>944.32</v>
       </c>
       <c r="AB26" s="12" t="n">
         <v>0</v>
@@ -21425,7 +21491,7 @@
         <v>74</v>
       </c>
       <c r="AW26" s="14" t="s">
-        <v>173</v>
+        <v>76</v>
       </c>
       <c r="AX26" s="10" t="s">
         <v>77</v>
@@ -21464,7 +21530,7 @@
         <v>78</v>
       </c>
       <c r="BJ26" s="9" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="BK26" s="9" t="s">
         <v>75</v>
@@ -21478,34 +21544,34 @@
     </row>
     <row r="27" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="n">
-        <v>306581</v>
+        <v>306675</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>141</v>
+        <v>64</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>148</v>
+        <v>171</v>
       </c>
       <c r="J27" s="9" t="s">
-        <v>78</v>
+        <v>172</v>
       </c>
       <c r="K27" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>96.5</v>
+        <v>3116.85</v>
       </c>
       <c r="M27" s="12" t="n">
         <v>0</v>
@@ -21514,43 +21580,43 @@
         <v>1</v>
       </c>
       <c r="O27" s="12" t="n">
-        <v>96.5</v>
+        <v>3116.85</v>
       </c>
       <c r="P27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q27" s="13" t="n">
-        <v>0</v>
+        <v>0.011766</v>
       </c>
       <c r="R27" s="12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T27" s="14" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="U27" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V27" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W27" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X27" s="9" t="s">
-        <v>148</v>
+        <v>171</v>
       </c>
       <c r="Y27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z27" s="12" t="n">
-        <v>96.5</v>
+        <v>3116.85</v>
       </c>
       <c r="AA27" s="12" t="n">
-        <v>3.86</v>
+        <v>218.18</v>
       </c>
       <c r="AB27" s="12" t="n">
         <v>0</v>
@@ -21616,10 +21682,10 @@
         <v>74</v>
       </c>
       <c r="AW27" s="14" t="s">
-        <v>173</v>
+        <v>76</v>
       </c>
       <c r="AX27" s="10" t="s">
-        <v>144</v>
+        <v>77</v>
       </c>
       <c r="AY27" s="14" t="s">
         <v>75</v>
@@ -21655,7 +21721,7 @@
         <v>78</v>
       </c>
       <c r="BJ27" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="BK27" s="9" t="s">
         <v>75</v>
@@ -21669,79 +21735,79 @@
     </row>
     <row r="28" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="n">
-        <v>306585</v>
+        <v>306713</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>148</v>
+        <v>171</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="K28" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>24038.11</v>
+        <v>3485.6</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="O28" s="12" t="n">
-        <v>22949.18</v>
+        <v>3288.3</v>
       </c>
       <c r="P28" s="12" t="n">
-        <v>659</v>
+        <v>197.3</v>
       </c>
       <c r="Q28" s="13" t="n">
-        <v>0.022336</v>
+        <v>0</v>
       </c>
       <c r="R28" s="12" t="n">
-        <v>5.96</v>
+        <v>16</v>
       </c>
       <c r="S28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T28" s="14" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="U28" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V28" s="12" t="n">
-        <v>82.46</v>
+        <v>29</v>
       </c>
       <c r="W28" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X28" s="9" t="s">
-        <v>148</v>
+        <v>171</v>
       </c>
       <c r="Y28" s="12" t="n">
-        <v>429.93</v>
+        <v>0</v>
       </c>
       <c r="Z28" s="12" t="n">
-        <v>23608.18</v>
+        <v>3485.6</v>
       </c>
       <c r="AA28" s="12" t="n">
-        <v>944.32</v>
+        <v>139.42</v>
       </c>
       <c r="AB28" s="12" t="n">
         <v>0</v>
@@ -21846,7 +21912,7 @@
         <v>78</v>
       </c>
       <c r="BJ28" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="BK28" s="9" t="s">
         <v>75</v>
@@ -21860,79 +21926,79 @@
     </row>
     <row r="29" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="n">
-        <v>306675</v>
+        <v>306724</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>64</v>
+        <v>179</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
       <c r="F29" s="9" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>148</v>
+        <v>117</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>184</v>
+        <v>78</v>
       </c>
       <c r="K29" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>3116.85</v>
+        <v>976.79</v>
       </c>
       <c r="M29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O29" s="12" t="n">
-        <v>3116.85</v>
+        <v>970.48</v>
       </c>
       <c r="P29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q29" s="13" t="n">
-        <v>0.011766</v>
+        <v>0</v>
       </c>
       <c r="R29" s="12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T29" s="14" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="U29" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V29" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W29" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X29" s="9" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="Y29" s="12" t="n">
-        <v>0</v>
+        <v>6.31</v>
       </c>
       <c r="Z29" s="12" t="n">
-        <v>3116.85</v>
+        <v>976.79</v>
       </c>
       <c r="AA29" s="12" t="n">
-        <v>218.18</v>
+        <v>68.38</v>
       </c>
       <c r="AB29" s="12" t="n">
         <v>0</v>
@@ -22001,7 +22067,7 @@
         <v>76</v>
       </c>
       <c r="AX29" s="10" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="AY29" s="14" t="s">
         <v>75</v>
@@ -22037,7 +22103,7 @@
         <v>78</v>
       </c>
       <c r="BJ29" s="9" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="BK29" s="9" t="s">
         <v>75</v>
@@ -22051,34 +22117,34 @@
     </row>
     <row r="30" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="n">
-        <v>306713</v>
+        <v>306726</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>187</v>
+        <v>64</v>
       </c>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
       <c r="F30" s="9" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="G30" s="10" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>111</v>
+        <v>136</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>135</v>
+        <v>172</v>
       </c>
       <c r="K30" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>3485.6</v>
+        <v>846.74</v>
       </c>
       <c r="M30" s="12" t="n">
         <v>0</v>
@@ -22087,43 +22153,43 @@
         <v>1</v>
       </c>
       <c r="O30" s="12" t="n">
-        <v>3288.3</v>
+        <v>846.74</v>
       </c>
       <c r="P30" s="12" t="n">
-        <v>197.3</v>
+        <v>0</v>
       </c>
       <c r="Q30" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R30" s="12" t="n">
-        <v>16</v>
+        <v>0.43</v>
       </c>
       <c r="S30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T30" s="14" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="U30" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V30" s="12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="W30" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X30" s="9" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="Y30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z30" s="12" t="n">
-        <v>3485.6</v>
+        <v>846.74</v>
       </c>
       <c r="AA30" s="12" t="n">
-        <v>139.42</v>
+        <v>59.27</v>
       </c>
       <c r="AB30" s="12" t="n">
         <v>0</v>
@@ -22228,7 +22294,7 @@
         <v>78</v>
       </c>
       <c r="BJ30" s="9" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="BK30" s="9" t="s">
         <v>75</v>
@@ -22242,79 +22308,79 @@
     </row>
     <row r="31" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="n">
-        <v>306724</v>
+        <v>306823</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
       <c r="F31" s="9" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>129</v>
+        <v>171</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>183</v>
+        <v>137</v>
       </c>
       <c r="J31" s="9" t="s">
-        <v>78</v>
+        <v>188</v>
       </c>
       <c r="K31" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>976.79</v>
+        <v>5775.71</v>
       </c>
       <c r="M31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O31" s="12" t="n">
-        <v>970.48</v>
+        <v>5510.71</v>
       </c>
       <c r="P31" s="12" t="n">
-        <v>0</v>
+        <v>265</v>
       </c>
       <c r="Q31" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R31" s="12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="S31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T31" s="14" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="U31" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V31" s="12" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="W31" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X31" s="9" t="s">
-        <v>183</v>
+        <v>137</v>
       </c>
       <c r="Y31" s="12" t="n">
-        <v>6.31</v>
+        <v>0</v>
       </c>
       <c r="Z31" s="12" t="n">
-        <v>976.79</v>
+        <v>5775.71</v>
       </c>
       <c r="AA31" s="12" t="n">
-        <v>68.38</v>
+        <v>404.3</v>
       </c>
       <c r="AB31" s="12" t="n">
         <v>0</v>
@@ -22383,7 +22449,7 @@
         <v>76</v>
       </c>
       <c r="AX31" s="10" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AY31" s="14" t="s">
         <v>75</v>
@@ -22419,7 +22485,7 @@
         <v>78</v>
       </c>
       <c r="BJ31" s="9" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="BK31" s="9" t="s">
         <v>75</v>
@@ -22433,34 +22499,34 @@
     </row>
     <row r="32" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="n">
-        <v>306726</v>
+        <v>306845</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>64</v>
+        <v>191</v>
       </c>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
       <c r="F32" s="9" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="G32" s="10" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>183</v>
+        <v>137</v>
       </c>
       <c r="J32" s="9" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="K32" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>846.74</v>
+        <v>935.55</v>
       </c>
       <c r="M32" s="12" t="n">
         <v>0</v>
@@ -22469,7 +22535,7 @@
         <v>1</v>
       </c>
       <c r="O32" s="12" t="n">
-        <v>846.74</v>
+        <v>935.55</v>
       </c>
       <c r="P32" s="12" t="n">
         <v>0</v>
@@ -22478,13 +22544,13 @@
         <v>0</v>
       </c>
       <c r="R32" s="12" t="n">
-        <v>0.43</v>
+        <v>0</v>
       </c>
       <c r="S32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T32" s="14" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="U32" s="15" t="s">
         <v>72</v>
@@ -22496,16 +22562,16 @@
         <v>73</v>
       </c>
       <c r="X32" s="9" t="s">
-        <v>183</v>
+        <v>137</v>
       </c>
       <c r="Y32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z32" s="12" t="n">
-        <v>846.74</v>
+        <v>935.55</v>
       </c>
       <c r="AA32" s="12" t="n">
-        <v>59.27</v>
+        <v>65.49</v>
       </c>
       <c r="AB32" s="12" t="n">
         <v>0</v>
@@ -22610,7 +22676,7 @@
         <v>78</v>
       </c>
       <c r="BJ32" s="9" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="BK32" s="9" t="s">
         <v>75</v>
@@ -22624,34 +22690,34 @@
     </row>
     <row r="33" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="n">
-        <v>306799</v>
+        <v>306871</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="9"/>
       <c r="E33" s="9"/>
       <c r="F33" s="9" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>200</v>
+        <v>91</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="I33" s="9" t="s">
-        <v>149</v>
+        <v>197</v>
       </c>
       <c r="J33" s="9" t="s">
-        <v>122</v>
+        <v>193</v>
       </c>
       <c r="K33" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>515.8</v>
+        <v>1978.02</v>
       </c>
       <c r="M33" s="12" t="n">
         <v>0</v>
@@ -22660,43 +22726,43 @@
         <v>1</v>
       </c>
       <c r="O33" s="12" t="n">
-        <v>499.56</v>
+        <v>1978.02</v>
       </c>
       <c r="P33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q33" s="13" t="n">
-        <v>0.004176</v>
+        <v>0</v>
       </c>
       <c r="R33" s="12" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="S33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T33" s="14" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="U33" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V33" s="12" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="W33" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X33" s="9" t="s">
-        <v>149</v>
+        <v>197</v>
       </c>
       <c r="Y33" s="12" t="n">
-        <v>16.24</v>
+        <v>0</v>
       </c>
       <c r="Z33" s="12" t="n">
-        <v>499.56</v>
+        <v>1978.02</v>
       </c>
       <c r="AA33" s="12" t="n">
-        <v>34.97</v>
+        <v>138.46</v>
       </c>
       <c r="AB33" s="12" t="n">
         <v>0</v>
@@ -22762,7 +22828,7 @@
         <v>74</v>
       </c>
       <c r="AW33" s="14" t="s">
-        <v>173</v>
+        <v>76</v>
       </c>
       <c r="AX33" s="10" t="s">
         <v>77</v>
@@ -22801,7 +22867,7 @@
         <v>78</v>
       </c>
       <c r="BJ33" s="9" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="BK33" s="9" t="s">
         <v>75</v>
@@ -22815,79 +22881,79 @@
     </row>
     <row r="34" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="n">
-        <v>306823</v>
+        <v>306872</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
       <c r="F34" s="9" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="G34" s="10" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>183</v>
+        <v>137</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>149</v>
+        <v>197</v>
       </c>
       <c r="J34" s="9" t="s">
-        <v>205</v>
+        <v>78</v>
       </c>
       <c r="K34" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>5775.71</v>
+        <v>569.02</v>
       </c>
       <c r="M34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O34" s="12" t="n">
-        <v>5510.71</v>
+        <v>569.02</v>
       </c>
       <c r="P34" s="12" t="n">
-        <v>265</v>
+        <v>0</v>
       </c>
       <c r="Q34" s="13" t="n">
-        <v>0</v>
+        <v>0.003038</v>
       </c>
       <c r="R34" s="12" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="S34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T34" s="14" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="U34" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V34" s="12" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="W34" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X34" s="9" t="s">
-        <v>149</v>
+        <v>197</v>
       </c>
       <c r="Y34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z34" s="12" t="n">
-        <v>5775.71</v>
+        <v>569.02</v>
       </c>
       <c r="AA34" s="12" t="n">
-        <v>404.3</v>
+        <v>39.83</v>
       </c>
       <c r="AB34" s="12" t="n">
         <v>0</v>
@@ -22956,7 +23022,7 @@
         <v>76</v>
       </c>
       <c r="AX34" s="10" t="s">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="AY34" s="14" t="s">
         <v>75</v>
@@ -22992,7 +23058,7 @@
         <v>78</v>
       </c>
       <c r="BJ34" s="9" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="BK34" s="9" t="s">
         <v>75</v>
@@ -23006,79 +23072,79 @@
     </row>
     <row r="35" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="n">
-        <v>306845</v>
+        <v>306873</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
       <c r="E35" s="9"/>
       <c r="F35" s="9" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="I35" s="9" t="s">
-        <v>149</v>
+        <v>197</v>
       </c>
       <c r="J35" s="9" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="K35" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>935.55</v>
+        <v>2954.76</v>
       </c>
       <c r="M35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O35" s="12" t="n">
-        <v>935.55</v>
+        <v>2954.76</v>
       </c>
       <c r="P35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q35" s="13" t="n">
-        <v>0</v>
+        <v>0.00726</v>
       </c>
       <c r="R35" s="12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="S35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T35" s="14" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="U35" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V35" s="12" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="W35" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X35" s="9" t="s">
-        <v>149</v>
+        <v>197</v>
       </c>
       <c r="Y35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z35" s="12" t="n">
-        <v>935.55</v>
+        <v>2954.76</v>
       </c>
       <c r="AA35" s="12" t="n">
-        <v>65.49</v>
+        <v>206.83</v>
       </c>
       <c r="AB35" s="12" t="n">
         <v>0</v>
@@ -23183,7 +23249,7 @@
         <v>78</v>
       </c>
       <c r="BJ35" s="9" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="BK35" s="9" t="s">
         <v>75</v>
@@ -23196,879 +23262,1855 @@
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="4"/>
+      <c r="A36" s="8" t="n">
+        <v>306874</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="G36" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="H36" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="I36" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="J36" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="K36" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L36" s="12" t="n">
+        <v>2271.36</v>
+      </c>
+      <c r="M36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="O36" s="12" t="n">
+        <v>2271.36</v>
+      </c>
+      <c r="P36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="13" t="n">
+        <v>0.011638</v>
+      </c>
+      <c r="R36" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="S36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="U36" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V36" s="12" t="n">
+        <v>41.99</v>
+      </c>
+      <c r="W36" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X36" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="Y36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" s="12" t="n">
+        <v>2271.36</v>
+      </c>
+      <c r="AA36" s="12" t="n">
+        <v>159</v>
+      </c>
+      <c r="AB36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ36" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM36" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN36" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO36" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP36" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ36" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR36" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS36" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT36" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU36" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV36" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW36" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX36" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY36" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ36" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA36" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB36" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC36" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD36" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE36" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF36" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG36" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH36" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI36" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ36" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="BK36" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL36" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM36" s="16" t="s">
+        <v>80</v>
+      </c>
     </row>
-    <row r="37" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="17" t="s">
+    <row r="37" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="8" t="n">
+        <v>306875</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="G37" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="H37" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="I37" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="J37" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="K37" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L37" s="12" t="n">
+        <v>5436.26</v>
+      </c>
+      <c r="M37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="O37" s="12" t="n">
+        <v>5436.26</v>
+      </c>
+      <c r="P37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="13" t="n">
+        <v>0.022294</v>
+      </c>
+      <c r="R37" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="S37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="U37" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V37" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="W37" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X37" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="Y37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" s="12" t="n">
+        <v>5436.26</v>
+      </c>
+      <c r="AA37" s="12" t="n">
+        <v>380.54</v>
+      </c>
+      <c r="AB37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ37" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM37" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN37" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO37" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP37" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ37" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR37" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS37" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT37" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU37" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV37" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW37" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX37" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY37" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ37" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA37" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB37" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC37" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD37" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE37" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF37" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG37" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH37" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI37" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ37" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="BK37" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL37" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM37" s="16" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="8" t="n">
+        <v>306876</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="C38" s="9"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="9"/>
+      <c r="F38" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="G38" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="H38" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="I38" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="J38" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="K38" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L38" s="12" t="n">
+        <v>6157.12</v>
+      </c>
+      <c r="M38" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="O38" s="12" t="n">
+        <v>6157.12</v>
+      </c>
+      <c r="P38" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="13" t="n">
+        <v>0.030068</v>
+      </c>
+      <c r="R38" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="S38" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" s="14" t="s">
         <v>213</v>
       </c>
-      <c r="B37" s="17"/>
-      <c r="C37" s="17"/>
-      <c r="D37" s="17"/>
-      <c r="E37" s="17"/>
-      <c r="F37" s="17"/>
-      <c r="G37" s="17"/>
-      <c r="H37" s="17"/>
-      <c r="I37" s="17"/>
-      <c r="J37" s="17"/>
-      <c r="K37" s="17"/>
-      <c r="L37" s="17"/>
-      <c r="M37" s="17"/>
-      <c r="N37" s="17"/>
-      <c r="O37" s="17"/>
-      <c r="P37" s="17"/>
-      <c r="Q37" s="17"/>
-      <c r="R37" s="17"/>
-      <c r="S37" s="17"/>
-      <c r="T37" s="17"/>
-      <c r="U37" s="17"/>
-      <c r="V37" s="17"/>
-    </row>
-    <row r="38" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="18" t="s">
+      <c r="U38" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V38" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="W38" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X38" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="Y38" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" s="12" t="n">
+        <v>6157.12</v>
+      </c>
+      <c r="AA38" s="12" t="n">
+        <v>431</v>
+      </c>
+      <c r="AB38" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI38" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ38" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK38" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL38" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM38" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN38" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO38" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP38" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ38" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR38" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS38" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT38" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU38" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV38" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW38" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX38" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY38" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ38" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA38" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB38" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC38" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD38" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE38" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF38" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG38" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH38" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI38" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ38" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="B38" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C38" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D38" s="18" t="s">
-        <v>215</v>
-      </c>
-      <c r="E38" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F38" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="G38" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="H38" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="I38" s="18" t="s">
-        <v>216</v>
-      </c>
-      <c r="J38" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="K38" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="L38" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="M38" s="18" t="s">
-        <v>217</v>
-      </c>
-      <c r="N38" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="O38" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="P38" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q38" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="R38" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="S38" s="18" t="s">
-        <v>218</v>
-      </c>
-      <c r="T38" s="18" t="s">
-        <v>219</v>
-      </c>
-      <c r="U38" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="V38" s="18" t="s">
-        <v>37</v>
+      <c r="BK38" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL38" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM38" s="16" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="19" t="n">
-        <v>31</v>
-      </c>
-      <c r="B39" s="19" t="n">
-        <v>1067.38</v>
-      </c>
-      <c r="C39" s="19" t="n">
-        <v>1221.3</v>
-      </c>
-      <c r="D39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" s="19" t="n">
-        <v>1245.83</v>
-      </c>
-      <c r="F39" s="19" t="n">
-        <v>109775.63</v>
-      </c>
-      <c r="G39" s="19" t="n">
-        <v>5812.3</v>
-      </c>
-      <c r="H39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" s="19" t="n">
-        <v>116399.35</v>
-      </c>
-      <c r="L39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" s="20" t="n">
-        <v>0.976817</v>
-      </c>
-      <c r="S39" s="19" t="n">
-        <v>114999.6</v>
-      </c>
-      <c r="T39" s="19" t="n">
-        <v>116399.35</v>
-      </c>
-      <c r="U39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" s="19" t="n">
-        <v>0</v>
+      <c r="A39" s="8" t="n">
+        <v>306880</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="C39" s="9"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="9"/>
+      <c r="F39" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="G39" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="H39" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="I39" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="J39" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K39" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L39" s="12" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="M39" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O39" s="12" t="n">
+        <v>35.99</v>
+      </c>
+      <c r="P39" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="U39" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V39" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X39" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="Y39" s="12" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="Z39" s="12" t="n">
+        <v>35.99</v>
+      </c>
+      <c r="AA39" s="12" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AB39" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD39" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF39" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG39" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI39" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ39" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK39" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL39" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM39" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN39" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO39" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP39" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ39" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR39" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS39" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT39" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU39" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV39" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW39" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX39" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="AY39" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ39" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA39" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB39" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC39" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD39" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE39" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF39" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG39" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH39" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI39" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ39" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="BK39" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL39" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM39" s="16" t="s">
+        <v>80</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="B40" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C40" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="D40" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E40" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="F40" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="G40" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="H40" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="I40" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="J40" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="K40" s="18" t="s">
+    <row r="40" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="8" t="n">
+        <v>306969</v>
+      </c>
+      <c r="B40" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="L40" s="18" t="s">
+      <c r="C40" s="9"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="9"/>
+      <c r="F40" s="9" t="s">
         <v>221</v>
       </c>
-      <c r="M40" s="18" t="s">
+      <c r="G40" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="H40" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="I40" s="9" t="s">
         <v>222</v>
+      </c>
+      <c r="J40" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="K40" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L40" s="12" t="n">
+        <v>3625.8</v>
+      </c>
+      <c r="M40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="O40" s="12" t="n">
+        <v>3315.52</v>
+      </c>
+      <c r="P40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" s="14" t="s">
+        <v>224</v>
+      </c>
+      <c r="U40" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V40" s="12" t="n">
+        <v>60.33</v>
+      </c>
+      <c r="W40" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X40" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="Y40" s="12" t="n">
+        <v>310.28</v>
+      </c>
+      <c r="Z40" s="12" t="n">
+        <v>3315.52</v>
+      </c>
+      <c r="AA40" s="12" t="n">
+        <v>132.63</v>
+      </c>
+      <c r="AB40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH40" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ40" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM40" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN40" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO40" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP40" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ40" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR40" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS40" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT40" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU40" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV40" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW40" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX40" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY40" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ40" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA40" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB40" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC40" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD40" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE40" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF40" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG40" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH40" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI40" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ40" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="BK40" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL40" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM40" s="16" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="19" t="n">
-        <v>172.53</v>
-      </c>
-      <c r="B41" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C41" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" s="19" t="n">
-        <v>45.76</v>
-      </c>
-      <c r="E41" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" s="19" t="n">
-        <v>0</v>
+      <c r="A41" s="8" t="n">
+        <v>306975</v>
+      </c>
+      <c r="B41" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="9"/>
+      <c r="F41" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="G41" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="H41" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="I41" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="J41" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="K41" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L41" s="12" t="n">
+        <v>985.72</v>
+      </c>
+      <c r="M41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O41" s="12" t="n">
+        <v>985.72</v>
+      </c>
+      <c r="P41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="13" t="n">
+        <v>0.002368</v>
+      </c>
+      <c r="R41" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="S41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="U41" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V41" s="12" t="n">
+        <v>41.98</v>
+      </c>
+      <c r="W41" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X41" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="Y41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z41" s="12" t="n">
+        <v>985.72</v>
+      </c>
+      <c r="AA41" s="12" t="n">
+        <v>69</v>
+      </c>
+      <c r="AB41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH41" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ41" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM41" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN41" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO41" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP41" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ41" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR41" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS41" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT41" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU41" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV41" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW41" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX41" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY41" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ41" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA41" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB41" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC41" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD41" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE41" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF41" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG41" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH41" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI41" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ41" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="BK41" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL41" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM41" s="16" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="4"/>
+      <c r="A42" s="8" t="n">
+        <v>306976</v>
+      </c>
+      <c r="B42" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="C42" s="9"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="9"/>
+      <c r="F42" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="G42" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="H42" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="I42" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="J42" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="K42" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L42" s="12" t="n">
+        <v>1478.58</v>
+      </c>
+      <c r="M42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O42" s="12" t="n">
+        <v>1478.58</v>
+      </c>
+      <c r="P42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="13" t="n">
+        <v>0.007104</v>
+      </c>
+      <c r="R42" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="S42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="U42" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V42" s="12" t="n">
+        <v>41.99</v>
+      </c>
+      <c r="W42" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X42" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="Y42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="12" t="n">
+        <v>1478.58</v>
+      </c>
+      <c r="AA42" s="12" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="AB42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ42" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM42" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN42" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO42" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP42" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ42" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR42" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS42" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT42" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU42" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV42" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW42" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX42" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY42" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ42" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA42" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB42" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC42" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD42" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE42" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF42" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG42" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH42" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI42" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ42" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="BK42" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL42" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM42" s="16" t="s">
+        <v>80</v>
+      </c>
     </row>
-    <row r="43" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="21" t="s">
-        <v>223</v>
-      </c>
-      <c r="B43" s="21"/>
-      <c r="C43" s="21"/>
-      <c r="D43" s="21"/>
-      <c r="E43" s="21"/>
-      <c r="F43" s="21"/>
-      <c r="G43" s="21"/>
-      <c r="H43" s="21"/>
-      <c r="I43" s="21"/>
-      <c r="J43" s="21"/>
-      <c r="K43" s="21"/>
-      <c r="L43" s="21"/>
-      <c r="M43" s="21"/>
-      <c r="N43" s="21"/>
-      <c r="O43" s="21"/>
-      <c r="P43" s="21"/>
-      <c r="Q43" s="21"/>
-      <c r="R43" s="21"/>
-      <c r="S43" s="21"/>
-      <c r="T43" s="21"/>
-      <c r="U43" s="21"/>
-      <c r="V43" s="21"/>
-      <c r="W43" s="21"/>
-      <c r="X43" s="21"/>
-      <c r="Y43" s="21"/>
-      <c r="Z43" s="21"/>
-      <c r="AA43" s="21"/>
-      <c r="AB43" s="21"/>
-      <c r="AC43" s="21"/>
-      <c r="AD43" s="21"/>
-      <c r="AE43" s="21"/>
-      <c r="AF43" s="21"/>
-      <c r="AG43" s="21"/>
-      <c r="AH43" s="21"/>
-      <c r="AI43" s="21"/>
-      <c r="AJ43" s="21"/>
-      <c r="AK43" s="21"/>
-      <c r="AL43" s="21"/>
-      <c r="AM43" s="21"/>
-      <c r="AN43" s="21"/>
-      <c r="AO43" s="21"/>
-      <c r="AP43" s="21"/>
-      <c r="AQ43" s="21"/>
-      <c r="AR43" s="21"/>
-      <c r="AS43" s="21"/>
-      <c r="AT43" s="21"/>
-      <c r="AU43" s="21"/>
-      <c r="AV43" s="21"/>
-      <c r="AW43" s="21"/>
-      <c r="AX43" s="21"/>
-      <c r="AY43" s="21"/>
-      <c r="AZ43" s="21"/>
-      <c r="BA43" s="21"/>
-      <c r="BB43" s="21"/>
-      <c r="BC43" s="21"/>
-      <c r="BD43" s="21"/>
-      <c r="BE43" s="21"/>
-      <c r="BF43" s="21"/>
-      <c r="BG43" s="21"/>
-      <c r="BH43" s="21"/>
-      <c r="BI43" s="21"/>
-      <c r="BJ43" s="21"/>
-      <c r="BK43" s="21"/>
-      <c r="BL43" s="21"/>
-      <c r="BM43" s="21"/>
+    <row r="43" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="8" t="n">
+        <v>306977</v>
+      </c>
+      <c r="B43" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="C43" s="9"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="9"/>
+      <c r="F43" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="G43" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="H43" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="I43" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="J43" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="K43" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L43" s="12" t="n">
+        <v>1478.58</v>
+      </c>
+      <c r="M43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O43" s="12" t="n">
+        <v>1478.58</v>
+      </c>
+      <c r="P43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="13" t="n">
+        <v>0.007104</v>
+      </c>
+      <c r="R43" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="S43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="U43" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V43" s="12" t="n">
+        <v>41.99</v>
+      </c>
+      <c r="W43" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X43" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="Y43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z43" s="12" t="n">
+        <v>1478.58</v>
+      </c>
+      <c r="AA43" s="12" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="AB43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH43" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ43" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM43" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN43" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO43" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP43" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ43" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR43" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS43" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT43" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU43" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV43" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW43" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX43" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY43" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ43" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA43" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB43" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC43" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD43" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE43" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF43" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG43" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH43" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI43" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ43" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="BK43" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL43" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM43" s="16" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B44" s="4"/>
-      <c r="C44" s="4"/>
-      <c r="D44" s="4"/>
-      <c r="E44" s="4"/>
-      <c r="F44" s="4"/>
-      <c r="G44" s="4"/>
-      <c r="H44" s="4"/>
-      <c r="I44" s="4"/>
-      <c r="J44" s="4"/>
-      <c r="K44" s="4"/>
-      <c r="L44" s="4"/>
-      <c r="M44" s="4"/>
-      <c r="N44" s="4"/>
-      <c r="O44" s="4"/>
-      <c r="P44" s="4"/>
-      <c r="Q44" s="4"/>
-      <c r="R44" s="4"/>
-      <c r="S44" s="4"/>
-      <c r="T44" s="4"/>
-      <c r="U44" s="4"/>
-      <c r="V44" s="4"/>
-      <c r="W44" s="4"/>
-      <c r="X44" s="4"/>
-      <c r="Y44" s="4"/>
-      <c r="Z44" s="4"/>
-      <c r="AA44" s="4"/>
-      <c r="AB44" s="4"/>
-      <c r="AC44" s="4"/>
-      <c r="AD44" s="4"/>
-      <c r="AE44" s="4"/>
-      <c r="AF44" s="4"/>
-      <c r="AG44" s="4"/>
-      <c r="AH44" s="4"/>
-      <c r="AI44" s="4"/>
-      <c r="AJ44" s="4"/>
-      <c r="AK44" s="4"/>
-      <c r="AL44" s="4"/>
-      <c r="AM44" s="4"/>
-      <c r="AN44" s="4"/>
-      <c r="AO44" s="4"/>
-      <c r="AP44" s="4"/>
-      <c r="AQ44" s="4"/>
-      <c r="AR44" s="4"/>
-      <c r="AS44" s="4"/>
-      <c r="AT44" s="4"/>
-      <c r="AU44" s="4"/>
-      <c r="AV44" s="4"/>
-      <c r="AW44" s="4"/>
-      <c r="AX44" s="4"/>
-      <c r="AY44" s="4"/>
-      <c r="AZ44" s="4"/>
-      <c r="BA44" s="4"/>
-      <c r="BB44" s="4"/>
-      <c r="BC44" s="4"/>
-      <c r="BD44" s="4"/>
-      <c r="BE44" s="4"/>
-      <c r="BF44" s="4"/>
-      <c r="BG44" s="4"/>
-      <c r="BH44" s="4"/>
-      <c r="BI44" s="4"/>
-      <c r="BJ44" s="4"/>
-      <c r="BK44" s="4"/>
-      <c r="BL44" s="4"/>
-      <c r="BM44" s="4"/>
+      <c r="A44" s="4"/>
     </row>
-    <row r="45" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="B45" s="4"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="4"/>
-      <c r="E45" s="4"/>
-      <c r="F45" s="4"/>
-      <c r="G45" s="4"/>
-      <c r="H45" s="4"/>
-      <c r="I45" s="4"/>
-      <c r="J45" s="4"/>
-      <c r="K45" s="4"/>
-      <c r="L45" s="4"/>
-      <c r="M45" s="4"/>
-      <c r="N45" s="4"/>
-      <c r="O45" s="4"/>
-      <c r="P45" s="4"/>
-      <c r="Q45" s="4"/>
-      <c r="R45" s="4"/>
-      <c r="S45" s="4"/>
-      <c r="T45" s="4"/>
-      <c r="U45" s="4"/>
-      <c r="V45" s="4"/>
-      <c r="W45" s="4"/>
-      <c r="X45" s="4"/>
-      <c r="Y45" s="4"/>
-      <c r="Z45" s="4"/>
-      <c r="AA45" s="4"/>
-      <c r="AB45" s="4"/>
-      <c r="AC45" s="4"/>
-      <c r="AD45" s="4"/>
-      <c r="AE45" s="4"/>
-      <c r="AF45" s="4"/>
-      <c r="AG45" s="4"/>
-      <c r="AH45" s="4"/>
-      <c r="AI45" s="4"/>
-      <c r="AJ45" s="4"/>
-      <c r="AK45" s="4"/>
-      <c r="AL45" s="4"/>
-      <c r="AM45" s="4"/>
-      <c r="AN45" s="4"/>
-      <c r="AO45" s="4"/>
-      <c r="AP45" s="4"/>
-      <c r="AQ45" s="4"/>
-      <c r="AR45" s="4"/>
-      <c r="AS45" s="4"/>
-      <c r="AT45" s="4"/>
-      <c r="AU45" s="4"/>
-      <c r="AV45" s="4"/>
-      <c r="AW45" s="4"/>
-      <c r="AX45" s="4"/>
-      <c r="AY45" s="4"/>
-      <c r="AZ45" s="4"/>
-      <c r="BA45" s="4"/>
-      <c r="BB45" s="4"/>
-      <c r="BC45" s="4"/>
-      <c r="BD45" s="4"/>
-      <c r="BE45" s="4"/>
-      <c r="BF45" s="4"/>
-      <c r="BG45" s="4"/>
-      <c r="BH45" s="4"/>
-      <c r="BI45" s="4"/>
-      <c r="BJ45" s="4"/>
-      <c r="BK45" s="4"/>
-      <c r="BL45" s="4"/>
-      <c r="BM45" s="4"/>
+    <row r="45" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="17" t="s">
+        <v>235</v>
+      </c>
+      <c r="B45" s="17"/>
+      <c r="C45" s="17"/>
+      <c r="D45" s="17"/>
+      <c r="E45" s="17"/>
+      <c r="F45" s="17"/>
+      <c r="G45" s="17"/>
+      <c r="H45" s="17"/>
+      <c r="I45" s="17"/>
+      <c r="J45" s="17"/>
+      <c r="K45" s="17"/>
+      <c r="L45" s="17"/>
+      <c r="M45" s="17"/>
+      <c r="N45" s="17"/>
+      <c r="O45" s="17"/>
+      <c r="P45" s="17"/>
+      <c r="Q45" s="17"/>
+      <c r="R45" s="17"/>
+      <c r="S45" s="17"/>
+      <c r="T45" s="17"/>
+      <c r="U45" s="17"/>
+      <c r="V45" s="17"/>
     </row>
-    <row r="46" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="B46" s="4"/>
-      <c r="C46" s="4"/>
-      <c r="D46" s="4"/>
-      <c r="E46" s="4"/>
-      <c r="F46" s="4"/>
-      <c r="G46" s="4"/>
-      <c r="H46" s="4"/>
-      <c r="I46" s="4"/>
-      <c r="J46" s="4"/>
-      <c r="K46" s="4"/>
-      <c r="L46" s="4"/>
-      <c r="M46" s="4"/>
-      <c r="N46" s="4"/>
-      <c r="O46" s="4"/>
-      <c r="P46" s="4"/>
-      <c r="Q46" s="4"/>
-      <c r="R46" s="4"/>
-      <c r="S46" s="4"/>
-      <c r="T46" s="4"/>
-      <c r="U46" s="4"/>
-      <c r="V46" s="4"/>
-      <c r="W46" s="4"/>
-      <c r="X46" s="4"/>
-      <c r="Y46" s="4"/>
-      <c r="Z46" s="4"/>
-      <c r="AA46" s="4"/>
-      <c r="AB46" s="4"/>
-      <c r="AC46" s="4"/>
-      <c r="AD46" s="4"/>
-      <c r="AE46" s="4"/>
-      <c r="AF46" s="4"/>
-      <c r="AG46" s="4"/>
-      <c r="AH46" s="4"/>
-      <c r="AI46" s="4"/>
-      <c r="AJ46" s="4"/>
-      <c r="AK46" s="4"/>
-      <c r="AL46" s="4"/>
-      <c r="AM46" s="4"/>
-      <c r="AN46" s="4"/>
-      <c r="AO46" s="4"/>
-      <c r="AP46" s="4"/>
-      <c r="AQ46" s="4"/>
-      <c r="AR46" s="4"/>
-      <c r="AS46" s="4"/>
-      <c r="AT46" s="4"/>
-      <c r="AU46" s="4"/>
-      <c r="AV46" s="4"/>
-      <c r="AW46" s="4"/>
-      <c r="AX46" s="4"/>
-      <c r="AY46" s="4"/>
-      <c r="AZ46" s="4"/>
-      <c r="BA46" s="4"/>
-      <c r="BB46" s="4"/>
-      <c r="BC46" s="4"/>
-      <c r="BD46" s="4"/>
-      <c r="BE46" s="4"/>
-      <c r="BF46" s="4"/>
-      <c r="BG46" s="4"/>
-      <c r="BH46" s="4"/>
-      <c r="BI46" s="4"/>
-      <c r="BJ46" s="4"/>
-      <c r="BK46" s="4"/>
-      <c r="BL46" s="4"/>
-      <c r="BM46" s="4"/>
+    <row r="46" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="18" t="s">
+        <v>236</v>
+      </c>
+      <c r="B46" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C46" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D46" s="18" t="s">
+        <v>237</v>
+      </c>
+      <c r="E46" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F46" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="G46" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H46" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="I46" s="18" t="s">
+        <v>238</v>
+      </c>
+      <c r="J46" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="K46" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="L46" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="M46" s="18" t="s">
+        <v>239</v>
+      </c>
+      <c r="N46" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="O46" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="P46" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q46" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="R46" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="S46" s="18" t="s">
+        <v>240</v>
+      </c>
+      <c r="T46" s="18" t="s">
+        <v>241</v>
+      </c>
+      <c r="U46" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="V46" s="18" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="B47" s="4"/>
-      <c r="C47" s="4"/>
-      <c r="D47" s="4"/>
-      <c r="E47" s="4"/>
-      <c r="F47" s="4"/>
-      <c r="G47" s="4"/>
-      <c r="H47" s="4"/>
-      <c r="I47" s="4"/>
-      <c r="J47" s="4"/>
-      <c r="K47" s="4"/>
-      <c r="L47" s="4"/>
-      <c r="M47" s="4"/>
-      <c r="N47" s="4"/>
-      <c r="O47" s="4"/>
-      <c r="P47" s="4"/>
-      <c r="Q47" s="4"/>
-      <c r="R47" s="4"/>
-      <c r="S47" s="4"/>
-      <c r="T47" s="4"/>
-      <c r="U47" s="4"/>
-      <c r="V47" s="4"/>
-      <c r="W47" s="4"/>
-      <c r="X47" s="4"/>
-      <c r="Y47" s="4"/>
-      <c r="Z47" s="4"/>
-      <c r="AA47" s="4"/>
-      <c r="AB47" s="4"/>
-      <c r="AC47" s="4"/>
-      <c r="AD47" s="4"/>
-      <c r="AE47" s="4"/>
-      <c r="AF47" s="4"/>
-      <c r="AG47" s="4"/>
-      <c r="AH47" s="4"/>
-      <c r="AI47" s="4"/>
-      <c r="AJ47" s="4"/>
-      <c r="AK47" s="4"/>
-      <c r="AL47" s="4"/>
-      <c r="AM47" s="4"/>
-      <c r="AN47" s="4"/>
-      <c r="AO47" s="4"/>
-      <c r="AP47" s="4"/>
-      <c r="AQ47" s="4"/>
-      <c r="AR47" s="4"/>
-      <c r="AS47" s="4"/>
-      <c r="AT47" s="4"/>
-      <c r="AU47" s="4"/>
-      <c r="AV47" s="4"/>
-      <c r="AW47" s="4"/>
-      <c r="AX47" s="4"/>
-      <c r="AY47" s="4"/>
-      <c r="AZ47" s="4"/>
-      <c r="BA47" s="4"/>
-      <c r="BB47" s="4"/>
-      <c r="BC47" s="4"/>
-      <c r="BD47" s="4"/>
-      <c r="BE47" s="4"/>
-      <c r="BF47" s="4"/>
-      <c r="BG47" s="4"/>
-      <c r="BH47" s="4"/>
-      <c r="BI47" s="4"/>
-      <c r="BJ47" s="4"/>
-      <c r="BK47" s="4"/>
-      <c r="BL47" s="4"/>
-      <c r="BM47" s="4"/>
+      <c r="A47" s="19" t="n">
+        <v>39</v>
+      </c>
+      <c r="B47" s="19" t="n">
+        <v>1067.38</v>
+      </c>
+      <c r="C47" s="19" t="n">
+        <v>1221.3</v>
+      </c>
+      <c r="D47" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="19" t="n">
+        <v>1540.79</v>
+      </c>
+      <c r="F47" s="19" t="n">
+        <v>126410.18</v>
+      </c>
+      <c r="G47" s="19" t="n">
+        <v>7178.85</v>
+      </c>
+      <c r="H47" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" s="19" t="n">
+        <v>133328.86</v>
+      </c>
+      <c r="L47" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" s="20" t="n">
+        <v>0.242922</v>
+      </c>
+      <c r="S47" s="19" t="n">
+        <v>131634.15</v>
+      </c>
+      <c r="T47" s="19" t="n">
+        <v>133328.86</v>
+      </c>
+      <c r="U47" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B48" s="4"/>
-      <c r="C48" s="4"/>
-      <c r="D48" s="4"/>
-      <c r="E48" s="4"/>
-      <c r="F48" s="4"/>
-      <c r="G48" s="4"/>
-      <c r="H48" s="4"/>
-      <c r="I48" s="4"/>
-      <c r="J48" s="4"/>
-      <c r="K48" s="4"/>
-      <c r="L48" s="4"/>
-      <c r="M48" s="4"/>
-      <c r="N48" s="4"/>
-      <c r="O48" s="4"/>
-      <c r="P48" s="4"/>
-      <c r="Q48" s="4"/>
-      <c r="R48" s="4"/>
-      <c r="S48" s="4"/>
-      <c r="T48" s="4"/>
-      <c r="U48" s="4"/>
-      <c r="V48" s="4"/>
-      <c r="W48" s="4"/>
-      <c r="X48" s="4"/>
-      <c r="Y48" s="4"/>
-      <c r="Z48" s="4"/>
-      <c r="AA48" s="4"/>
-      <c r="AB48" s="4"/>
-      <c r="AC48" s="4"/>
-      <c r="AD48" s="4"/>
-      <c r="AE48" s="4"/>
-      <c r="AF48" s="4"/>
-      <c r="AG48" s="4"/>
-      <c r="AH48" s="4"/>
-      <c r="AI48" s="4"/>
-      <c r="AJ48" s="4"/>
-      <c r="AK48" s="4"/>
-      <c r="AL48" s="4"/>
-      <c r="AM48" s="4"/>
-      <c r="AN48" s="4"/>
-      <c r="AO48" s="4"/>
-      <c r="AP48" s="4"/>
-      <c r="AQ48" s="4"/>
-      <c r="AR48" s="4"/>
-      <c r="AS48" s="4"/>
-      <c r="AT48" s="4"/>
-      <c r="AU48" s="4"/>
-      <c r="AV48" s="4"/>
-      <c r="AW48" s="4"/>
-      <c r="AX48" s="4"/>
-      <c r="AY48" s="4"/>
-      <c r="AZ48" s="4"/>
-      <c r="BA48" s="4"/>
-      <c r="BB48" s="4"/>
-      <c r="BC48" s="4"/>
-      <c r="BD48" s="4"/>
-      <c r="BE48" s="4"/>
-      <c r="BF48" s="4"/>
-      <c r="BG48" s="4"/>
-      <c r="BH48" s="4"/>
-      <c r="BI48" s="4"/>
-      <c r="BJ48" s="4"/>
-      <c r="BK48" s="4"/>
-      <c r="BL48" s="4"/>
-      <c r="BM48" s="4"/>
+    <row r="48" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B48" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C48" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D48" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="E48" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="F48" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="G48" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="H48" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="I48" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="J48" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="K48" s="18" t="s">
+        <v>242</v>
+      </c>
+      <c r="L48" s="18" t="s">
+        <v>243</v>
+      </c>
+      <c r="M48" s="18" t="s">
+        <v>244</v>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="B49" s="4"/>
-      <c r="C49" s="4"/>
-      <c r="D49" s="4"/>
-      <c r="E49" s="4"/>
-      <c r="F49" s="4"/>
-      <c r="G49" s="4"/>
-      <c r="H49" s="4"/>
-      <c r="I49" s="4"/>
-      <c r="J49" s="4"/>
-      <c r="K49" s="4"/>
-      <c r="L49" s="4"/>
-      <c r="M49" s="4"/>
-      <c r="N49" s="4"/>
-      <c r="O49" s="4"/>
-      <c r="P49" s="4"/>
-      <c r="Q49" s="4"/>
-      <c r="R49" s="4"/>
-      <c r="S49" s="4"/>
-      <c r="T49" s="4"/>
-      <c r="U49" s="4"/>
-      <c r="V49" s="4"/>
-      <c r="W49" s="4"/>
-      <c r="X49" s="4"/>
-      <c r="Y49" s="4"/>
-      <c r="Z49" s="4"/>
-      <c r="AA49" s="4"/>
-      <c r="AB49" s="4"/>
-      <c r="AC49" s="4"/>
-      <c r="AD49" s="4"/>
-      <c r="AE49" s="4"/>
-      <c r="AF49" s="4"/>
-      <c r="AG49" s="4"/>
-      <c r="AH49" s="4"/>
-      <c r="AI49" s="4"/>
-      <c r="AJ49" s="4"/>
-      <c r="AK49" s="4"/>
-      <c r="AL49" s="4"/>
-      <c r="AM49" s="4"/>
-      <c r="AN49" s="4"/>
-      <c r="AO49" s="4"/>
-      <c r="AP49" s="4"/>
-      <c r="AQ49" s="4"/>
-      <c r="AR49" s="4"/>
-      <c r="AS49" s="4"/>
-      <c r="AT49" s="4"/>
-      <c r="AU49" s="4"/>
-      <c r="AV49" s="4"/>
-      <c r="AW49" s="4"/>
-      <c r="AX49" s="4"/>
-      <c r="AY49" s="4"/>
-      <c r="AZ49" s="4"/>
-      <c r="BA49" s="4"/>
-      <c r="BB49" s="4"/>
-      <c r="BC49" s="4"/>
-      <c r="BD49" s="4"/>
-      <c r="BE49" s="4"/>
-      <c r="BF49" s="4"/>
-      <c r="BG49" s="4"/>
-      <c r="BH49" s="4"/>
-      <c r="BI49" s="4"/>
-      <c r="BJ49" s="4"/>
-      <c r="BK49" s="4"/>
-      <c r="BL49" s="4"/>
-      <c r="BM49" s="4"/>
+      <c r="A49" s="19" t="n">
+        <v>196.76</v>
+      </c>
+      <c r="B49" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" s="19" t="n">
+        <v>46.29</v>
+      </c>
+      <c r="E49" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="B50" s="4"/>
-      <c r="C50" s="4"/>
-      <c r="D50" s="4"/>
-      <c r="E50" s="4"/>
-      <c r="F50" s="4"/>
-      <c r="G50" s="4"/>
-      <c r="H50" s="4"/>
-      <c r="I50" s="4"/>
-      <c r="J50" s="4"/>
-      <c r="K50" s="4"/>
-      <c r="L50" s="4"/>
-      <c r="M50" s="4"/>
-      <c r="N50" s="4"/>
-      <c r="O50" s="4"/>
-      <c r="P50" s="4"/>
-      <c r="Q50" s="4"/>
-      <c r="R50" s="4"/>
-      <c r="S50" s="4"/>
-      <c r="T50" s="4"/>
-      <c r="U50" s="4"/>
-      <c r="V50" s="4"/>
-      <c r="W50" s="4"/>
-      <c r="X50" s="4"/>
-      <c r="Y50" s="4"/>
-      <c r="Z50" s="4"/>
-      <c r="AA50" s="4"/>
-      <c r="AB50" s="4"/>
-      <c r="AC50" s="4"/>
-      <c r="AD50" s="4"/>
-      <c r="AE50" s="4"/>
-      <c r="AF50" s="4"/>
-      <c r="AG50" s="4"/>
-      <c r="AH50" s="4"/>
-      <c r="AI50" s="4"/>
-      <c r="AJ50" s="4"/>
-      <c r="AK50" s="4"/>
-      <c r="AL50" s="4"/>
-      <c r="AM50" s="4"/>
-      <c r="AN50" s="4"/>
-      <c r="AO50" s="4"/>
-      <c r="AP50" s="4"/>
-      <c r="AQ50" s="4"/>
-      <c r="AR50" s="4"/>
-      <c r="AS50" s="4"/>
-      <c r="AT50" s="4"/>
-      <c r="AU50" s="4"/>
-      <c r="AV50" s="4"/>
-      <c r="AW50" s="4"/>
-      <c r="AX50" s="4"/>
-      <c r="AY50" s="4"/>
-      <c r="AZ50" s="4"/>
-      <c r="BA50" s="4"/>
-      <c r="BB50" s="4"/>
-      <c r="BC50" s="4"/>
-      <c r="BD50" s="4"/>
-      <c r="BE50" s="4"/>
-      <c r="BF50" s="4"/>
-      <c r="BG50" s="4"/>
-      <c r="BH50" s="4"/>
-      <c r="BI50" s="4"/>
-      <c r="BJ50" s="4"/>
-      <c r="BK50" s="4"/>
-      <c r="BL50" s="4"/>
-      <c r="BM50" s="4"/>
+      <c r="A50" s="4"/>
     </row>
-    <row r="51" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="B51" s="4"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="4"/>
-      <c r="E51" s="4"/>
-      <c r="F51" s="4"/>
-      <c r="G51" s="4"/>
-      <c r="H51" s="4"/>
-      <c r="I51" s="4"/>
-      <c r="J51" s="4"/>
-      <c r="K51" s="4"/>
-      <c r="L51" s="4"/>
-      <c r="M51" s="4"/>
-      <c r="N51" s="4"/>
-      <c r="O51" s="4"/>
-      <c r="P51" s="4"/>
-      <c r="Q51" s="4"/>
-      <c r="R51" s="4"/>
-      <c r="S51" s="4"/>
-      <c r="T51" s="4"/>
-      <c r="U51" s="4"/>
-      <c r="V51" s="4"/>
-      <c r="W51" s="4"/>
-      <c r="X51" s="4"/>
-      <c r="Y51" s="4"/>
-      <c r="Z51" s="4"/>
-      <c r="AA51" s="4"/>
-      <c r="AB51" s="4"/>
-      <c r="AC51" s="4"/>
-      <c r="AD51" s="4"/>
-      <c r="AE51" s="4"/>
-      <c r="AF51" s="4"/>
-      <c r="AG51" s="4"/>
-      <c r="AH51" s="4"/>
-      <c r="AI51" s="4"/>
-      <c r="AJ51" s="4"/>
-      <c r="AK51" s="4"/>
-      <c r="AL51" s="4"/>
-      <c r="AM51" s="4"/>
-      <c r="AN51" s="4"/>
-      <c r="AO51" s="4"/>
-      <c r="AP51" s="4"/>
-      <c r="AQ51" s="4"/>
-      <c r="AR51" s="4"/>
-      <c r="AS51" s="4"/>
-      <c r="AT51" s="4"/>
-      <c r="AU51" s="4"/>
-      <c r="AV51" s="4"/>
-      <c r="AW51" s="4"/>
-      <c r="AX51" s="4"/>
-      <c r="AY51" s="4"/>
-      <c r="AZ51" s="4"/>
-      <c r="BA51" s="4"/>
-      <c r="BB51" s="4"/>
-      <c r="BC51" s="4"/>
-      <c r="BD51" s="4"/>
-      <c r="BE51" s="4"/>
-      <c r="BF51" s="4"/>
-      <c r="BG51" s="4"/>
-      <c r="BH51" s="4"/>
-      <c r="BI51" s="4"/>
-      <c r="BJ51" s="4"/>
-      <c r="BK51" s="4"/>
-      <c r="BL51" s="4"/>
-      <c r="BM51" s="4"/>
+    <row r="51" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="21" t="s">
+        <v>245</v>
+      </c>
+      <c r="B51" s="21"/>
+      <c r="C51" s="21"/>
+      <c r="D51" s="21"/>
+      <c r="E51" s="21"/>
+      <c r="F51" s="21"/>
+      <c r="G51" s="21"/>
+      <c r="H51" s="21"/>
+      <c r="I51" s="21"/>
+      <c r="J51" s="21"/>
+      <c r="K51" s="21"/>
+      <c r="L51" s="21"/>
+      <c r="M51" s="21"/>
+      <c r="N51" s="21"/>
+      <c r="O51" s="21"/>
+      <c r="P51" s="21"/>
+      <c r="Q51" s="21"/>
+      <c r="R51" s="21"/>
+      <c r="S51" s="21"/>
+      <c r="T51" s="21"/>
+      <c r="U51" s="21"/>
+      <c r="V51" s="21"/>
+      <c r="W51" s="21"/>
+      <c r="X51" s="21"/>
+      <c r="Y51" s="21"/>
+      <c r="Z51" s="21"/>
+      <c r="AA51" s="21"/>
+      <c r="AB51" s="21"/>
+      <c r="AC51" s="21"/>
+      <c r="AD51" s="21"/>
+      <c r="AE51" s="21"/>
+      <c r="AF51" s="21"/>
+      <c r="AG51" s="21"/>
+      <c r="AH51" s="21"/>
+      <c r="AI51" s="21"/>
+      <c r="AJ51" s="21"/>
+      <c r="AK51" s="21"/>
+      <c r="AL51" s="21"/>
+      <c r="AM51" s="21"/>
+      <c r="AN51" s="21"/>
+      <c r="AO51" s="21"/>
+      <c r="AP51" s="21"/>
+      <c r="AQ51" s="21"/>
+      <c r="AR51" s="21"/>
+      <c r="AS51" s="21"/>
+      <c r="AT51" s="21"/>
+      <c r="AU51" s="21"/>
+      <c r="AV51" s="21"/>
+      <c r="AW51" s="21"/>
+      <c r="AX51" s="21"/>
+      <c r="AY51" s="21"/>
+      <c r="AZ51" s="21"/>
+      <c r="BA51" s="21"/>
+      <c r="BB51" s="21"/>
+      <c r="BC51" s="21"/>
+      <c r="BD51" s="21"/>
+      <c r="BE51" s="21"/>
+      <c r="BF51" s="21"/>
+      <c r="BG51" s="21"/>
+      <c r="BH51" s="21"/>
+      <c r="BI51" s="21"/>
+      <c r="BJ51" s="21"/>
+      <c r="BK51" s="21"/>
+      <c r="BL51" s="21"/>
+      <c r="BM51" s="21"/>
     </row>
     <row r="52" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="4" t="s">
-        <v>230</v>
+        <v>75</v>
       </c>
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
@@ -24137,7 +25179,7 @@
     </row>
     <row r="53" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="4" t="s">
-        <v>231</v>
+        <v>246</v>
       </c>
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
@@ -24204,8 +25246,560 @@
       <c r="BL53" s="4"/>
       <c r="BM53" s="4"/>
     </row>
+    <row r="54" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="B54" s="4"/>
+      <c r="C54" s="4"/>
+      <c r="D54" s="4"/>
+      <c r="E54" s="4"/>
+      <c r="F54" s="4"/>
+      <c r="G54" s="4"/>
+      <c r="H54" s="4"/>
+      <c r="I54" s="4"/>
+      <c r="J54" s="4"/>
+      <c r="K54" s="4"/>
+      <c r="L54" s="4"/>
+      <c r="M54" s="4"/>
+      <c r="N54" s="4"/>
+      <c r="O54" s="4"/>
+      <c r="P54" s="4"/>
+      <c r="Q54" s="4"/>
+      <c r="R54" s="4"/>
+      <c r="S54" s="4"/>
+      <c r="T54" s="4"/>
+      <c r="U54" s="4"/>
+      <c r="V54" s="4"/>
+      <c r="W54" s="4"/>
+      <c r="X54" s="4"/>
+      <c r="Y54" s="4"/>
+      <c r="Z54" s="4"/>
+      <c r="AA54" s="4"/>
+      <c r="AB54" s="4"/>
+      <c r="AC54" s="4"/>
+      <c r="AD54" s="4"/>
+      <c r="AE54" s="4"/>
+      <c r="AF54" s="4"/>
+      <c r="AG54" s="4"/>
+      <c r="AH54" s="4"/>
+      <c r="AI54" s="4"/>
+      <c r="AJ54" s="4"/>
+      <c r="AK54" s="4"/>
+      <c r="AL54" s="4"/>
+      <c r="AM54" s="4"/>
+      <c r="AN54" s="4"/>
+      <c r="AO54" s="4"/>
+      <c r="AP54" s="4"/>
+      <c r="AQ54" s="4"/>
+      <c r="AR54" s="4"/>
+      <c r="AS54" s="4"/>
+      <c r="AT54" s="4"/>
+      <c r="AU54" s="4"/>
+      <c r="AV54" s="4"/>
+      <c r="AW54" s="4"/>
+      <c r="AX54" s="4"/>
+      <c r="AY54" s="4"/>
+      <c r="AZ54" s="4"/>
+      <c r="BA54" s="4"/>
+      <c r="BB54" s="4"/>
+      <c r="BC54" s="4"/>
+      <c r="BD54" s="4"/>
+      <c r="BE54" s="4"/>
+      <c r="BF54" s="4"/>
+      <c r="BG54" s="4"/>
+      <c r="BH54" s="4"/>
+      <c r="BI54" s="4"/>
+      <c r="BJ54" s="4"/>
+      <c r="BK54" s="4"/>
+      <c r="BL54" s="4"/>
+      <c r="BM54" s="4"/>
+    </row>
+    <row r="55" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="B55" s="4"/>
+      <c r="C55" s="4"/>
+      <c r="D55" s="4"/>
+      <c r="E55" s="4"/>
+      <c r="F55" s="4"/>
+      <c r="G55" s="4"/>
+      <c r="H55" s="4"/>
+      <c r="I55" s="4"/>
+      <c r="J55" s="4"/>
+      <c r="K55" s="4"/>
+      <c r="L55" s="4"/>
+      <c r="M55" s="4"/>
+      <c r="N55" s="4"/>
+      <c r="O55" s="4"/>
+      <c r="P55" s="4"/>
+      <c r="Q55" s="4"/>
+      <c r="R55" s="4"/>
+      <c r="S55" s="4"/>
+      <c r="T55" s="4"/>
+      <c r="U55" s="4"/>
+      <c r="V55" s="4"/>
+      <c r="W55" s="4"/>
+      <c r="X55" s="4"/>
+      <c r="Y55" s="4"/>
+      <c r="Z55" s="4"/>
+      <c r="AA55" s="4"/>
+      <c r="AB55" s="4"/>
+      <c r="AC55" s="4"/>
+      <c r="AD55" s="4"/>
+      <c r="AE55" s="4"/>
+      <c r="AF55" s="4"/>
+      <c r="AG55" s="4"/>
+      <c r="AH55" s="4"/>
+      <c r="AI55" s="4"/>
+      <c r="AJ55" s="4"/>
+      <c r="AK55" s="4"/>
+      <c r="AL55" s="4"/>
+      <c r="AM55" s="4"/>
+      <c r="AN55" s="4"/>
+      <c r="AO55" s="4"/>
+      <c r="AP55" s="4"/>
+      <c r="AQ55" s="4"/>
+      <c r="AR55" s="4"/>
+      <c r="AS55" s="4"/>
+      <c r="AT55" s="4"/>
+      <c r="AU55" s="4"/>
+      <c r="AV55" s="4"/>
+      <c r="AW55" s="4"/>
+      <c r="AX55" s="4"/>
+      <c r="AY55" s="4"/>
+      <c r="AZ55" s="4"/>
+      <c r="BA55" s="4"/>
+      <c r="BB55" s="4"/>
+      <c r="BC55" s="4"/>
+      <c r="BD55" s="4"/>
+      <c r="BE55" s="4"/>
+      <c r="BF55" s="4"/>
+      <c r="BG55" s="4"/>
+      <c r="BH55" s="4"/>
+      <c r="BI55" s="4"/>
+      <c r="BJ55" s="4"/>
+      <c r="BK55" s="4"/>
+      <c r="BL55" s="4"/>
+      <c r="BM55" s="4"/>
+    </row>
+    <row r="56" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B56" s="4"/>
+      <c r="C56" s="4"/>
+      <c r="D56" s="4"/>
+      <c r="E56" s="4"/>
+      <c r="F56" s="4"/>
+      <c r="G56" s="4"/>
+      <c r="H56" s="4"/>
+      <c r="I56" s="4"/>
+      <c r="J56" s="4"/>
+      <c r="K56" s="4"/>
+      <c r="L56" s="4"/>
+      <c r="M56" s="4"/>
+      <c r="N56" s="4"/>
+      <c r="O56" s="4"/>
+      <c r="P56" s="4"/>
+      <c r="Q56" s="4"/>
+      <c r="R56" s="4"/>
+      <c r="S56" s="4"/>
+      <c r="T56" s="4"/>
+      <c r="U56" s="4"/>
+      <c r="V56" s="4"/>
+      <c r="W56" s="4"/>
+      <c r="X56" s="4"/>
+      <c r="Y56" s="4"/>
+      <c r="Z56" s="4"/>
+      <c r="AA56" s="4"/>
+      <c r="AB56" s="4"/>
+      <c r="AC56" s="4"/>
+      <c r="AD56" s="4"/>
+      <c r="AE56" s="4"/>
+      <c r="AF56" s="4"/>
+      <c r="AG56" s="4"/>
+      <c r="AH56" s="4"/>
+      <c r="AI56" s="4"/>
+      <c r="AJ56" s="4"/>
+      <c r="AK56" s="4"/>
+      <c r="AL56" s="4"/>
+      <c r="AM56" s="4"/>
+      <c r="AN56" s="4"/>
+      <c r="AO56" s="4"/>
+      <c r="AP56" s="4"/>
+      <c r="AQ56" s="4"/>
+      <c r="AR56" s="4"/>
+      <c r="AS56" s="4"/>
+      <c r="AT56" s="4"/>
+      <c r="AU56" s="4"/>
+      <c r="AV56" s="4"/>
+      <c r="AW56" s="4"/>
+      <c r="AX56" s="4"/>
+      <c r="AY56" s="4"/>
+      <c r="AZ56" s="4"/>
+      <c r="BA56" s="4"/>
+      <c r="BB56" s="4"/>
+      <c r="BC56" s="4"/>
+      <c r="BD56" s="4"/>
+      <c r="BE56" s="4"/>
+      <c r="BF56" s="4"/>
+      <c r="BG56" s="4"/>
+      <c r="BH56" s="4"/>
+      <c r="BI56" s="4"/>
+      <c r="BJ56" s="4"/>
+      <c r="BK56" s="4"/>
+      <c r="BL56" s="4"/>
+      <c r="BM56" s="4"/>
+    </row>
+    <row r="57" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="B57" s="4"/>
+      <c r="C57" s="4"/>
+      <c r="D57" s="4"/>
+      <c r="E57" s="4"/>
+      <c r="F57" s="4"/>
+      <c r="G57" s="4"/>
+      <c r="H57" s="4"/>
+      <c r="I57" s="4"/>
+      <c r="J57" s="4"/>
+      <c r="K57" s="4"/>
+      <c r="L57" s="4"/>
+      <c r="M57" s="4"/>
+      <c r="N57" s="4"/>
+      <c r="O57" s="4"/>
+      <c r="P57" s="4"/>
+      <c r="Q57" s="4"/>
+      <c r="R57" s="4"/>
+      <c r="S57" s="4"/>
+      <c r="T57" s="4"/>
+      <c r="U57" s="4"/>
+      <c r="V57" s="4"/>
+      <c r="W57" s="4"/>
+      <c r="X57" s="4"/>
+      <c r="Y57" s="4"/>
+      <c r="Z57" s="4"/>
+      <c r="AA57" s="4"/>
+      <c r="AB57" s="4"/>
+      <c r="AC57" s="4"/>
+      <c r="AD57" s="4"/>
+      <c r="AE57" s="4"/>
+      <c r="AF57" s="4"/>
+      <c r="AG57" s="4"/>
+      <c r="AH57" s="4"/>
+      <c r="AI57" s="4"/>
+      <c r="AJ57" s="4"/>
+      <c r="AK57" s="4"/>
+      <c r="AL57" s="4"/>
+      <c r="AM57" s="4"/>
+      <c r="AN57" s="4"/>
+      <c r="AO57" s="4"/>
+      <c r="AP57" s="4"/>
+      <c r="AQ57" s="4"/>
+      <c r="AR57" s="4"/>
+      <c r="AS57" s="4"/>
+      <c r="AT57" s="4"/>
+      <c r="AU57" s="4"/>
+      <c r="AV57" s="4"/>
+      <c r="AW57" s="4"/>
+      <c r="AX57" s="4"/>
+      <c r="AY57" s="4"/>
+      <c r="AZ57" s="4"/>
+      <c r="BA57" s="4"/>
+      <c r="BB57" s="4"/>
+      <c r="BC57" s="4"/>
+      <c r="BD57" s="4"/>
+      <c r="BE57" s="4"/>
+      <c r="BF57" s="4"/>
+      <c r="BG57" s="4"/>
+      <c r="BH57" s="4"/>
+      <c r="BI57" s="4"/>
+      <c r="BJ57" s="4"/>
+      <c r="BK57" s="4"/>
+      <c r="BL57" s="4"/>
+      <c r="BM57" s="4"/>
+    </row>
+    <row r="58" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="B58" s="4"/>
+      <c r="C58" s="4"/>
+      <c r="D58" s="4"/>
+      <c r="E58" s="4"/>
+      <c r="F58" s="4"/>
+      <c r="G58" s="4"/>
+      <c r="H58" s="4"/>
+      <c r="I58" s="4"/>
+      <c r="J58" s="4"/>
+      <c r="K58" s="4"/>
+      <c r="L58" s="4"/>
+      <c r="M58" s="4"/>
+      <c r="N58" s="4"/>
+      <c r="O58" s="4"/>
+      <c r="P58" s="4"/>
+      <c r="Q58" s="4"/>
+      <c r="R58" s="4"/>
+      <c r="S58" s="4"/>
+      <c r="T58" s="4"/>
+      <c r="U58" s="4"/>
+      <c r="V58" s="4"/>
+      <c r="W58" s="4"/>
+      <c r="X58" s="4"/>
+      <c r="Y58" s="4"/>
+      <c r="Z58" s="4"/>
+      <c r="AA58" s="4"/>
+      <c r="AB58" s="4"/>
+      <c r="AC58" s="4"/>
+      <c r="AD58" s="4"/>
+      <c r="AE58" s="4"/>
+      <c r="AF58" s="4"/>
+      <c r="AG58" s="4"/>
+      <c r="AH58" s="4"/>
+      <c r="AI58" s="4"/>
+      <c r="AJ58" s="4"/>
+      <c r="AK58" s="4"/>
+      <c r="AL58" s="4"/>
+      <c r="AM58" s="4"/>
+      <c r="AN58" s="4"/>
+      <c r="AO58" s="4"/>
+      <c r="AP58" s="4"/>
+      <c r="AQ58" s="4"/>
+      <c r="AR58" s="4"/>
+      <c r="AS58" s="4"/>
+      <c r="AT58" s="4"/>
+      <c r="AU58" s="4"/>
+      <c r="AV58" s="4"/>
+      <c r="AW58" s="4"/>
+      <c r="AX58" s="4"/>
+      <c r="AY58" s="4"/>
+      <c r="AZ58" s="4"/>
+      <c r="BA58" s="4"/>
+      <c r="BB58" s="4"/>
+      <c r="BC58" s="4"/>
+      <c r="BD58" s="4"/>
+      <c r="BE58" s="4"/>
+      <c r="BF58" s="4"/>
+      <c r="BG58" s="4"/>
+      <c r="BH58" s="4"/>
+      <c r="BI58" s="4"/>
+      <c r="BJ58" s="4"/>
+      <c r="BK58" s="4"/>
+      <c r="BL58" s="4"/>
+      <c r="BM58" s="4"/>
+    </row>
+    <row r="59" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="B59" s="4"/>
+      <c r="C59" s="4"/>
+      <c r="D59" s="4"/>
+      <c r="E59" s="4"/>
+      <c r="F59" s="4"/>
+      <c r="G59" s="4"/>
+      <c r="H59" s="4"/>
+      <c r="I59" s="4"/>
+      <c r="J59" s="4"/>
+      <c r="K59" s="4"/>
+      <c r="L59" s="4"/>
+      <c r="M59" s="4"/>
+      <c r="N59" s="4"/>
+      <c r="O59" s="4"/>
+      <c r="P59" s="4"/>
+      <c r="Q59" s="4"/>
+      <c r="R59" s="4"/>
+      <c r="S59" s="4"/>
+      <c r="T59" s="4"/>
+      <c r="U59" s="4"/>
+      <c r="V59" s="4"/>
+      <c r="W59" s="4"/>
+      <c r="X59" s="4"/>
+      <c r="Y59" s="4"/>
+      <c r="Z59" s="4"/>
+      <c r="AA59" s="4"/>
+      <c r="AB59" s="4"/>
+      <c r="AC59" s="4"/>
+      <c r="AD59" s="4"/>
+      <c r="AE59" s="4"/>
+      <c r="AF59" s="4"/>
+      <c r="AG59" s="4"/>
+      <c r="AH59" s="4"/>
+      <c r="AI59" s="4"/>
+      <c r="AJ59" s="4"/>
+      <c r="AK59" s="4"/>
+      <c r="AL59" s="4"/>
+      <c r="AM59" s="4"/>
+      <c r="AN59" s="4"/>
+      <c r="AO59" s="4"/>
+      <c r="AP59" s="4"/>
+      <c r="AQ59" s="4"/>
+      <c r="AR59" s="4"/>
+      <c r="AS59" s="4"/>
+      <c r="AT59" s="4"/>
+      <c r="AU59" s="4"/>
+      <c r="AV59" s="4"/>
+      <c r="AW59" s="4"/>
+      <c r="AX59" s="4"/>
+      <c r="AY59" s="4"/>
+      <c r="AZ59" s="4"/>
+      <c r="BA59" s="4"/>
+      <c r="BB59" s="4"/>
+      <c r="BC59" s="4"/>
+      <c r="BD59" s="4"/>
+      <c r="BE59" s="4"/>
+      <c r="BF59" s="4"/>
+      <c r="BG59" s="4"/>
+      <c r="BH59" s="4"/>
+      <c r="BI59" s="4"/>
+      <c r="BJ59" s="4"/>
+      <c r="BK59" s="4"/>
+      <c r="BL59" s="4"/>
+      <c r="BM59" s="4"/>
+    </row>
+    <row r="60" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="B60" s="4"/>
+      <c r="C60" s="4"/>
+      <c r="D60" s="4"/>
+      <c r="E60" s="4"/>
+      <c r="F60" s="4"/>
+      <c r="G60" s="4"/>
+      <c r="H60" s="4"/>
+      <c r="I60" s="4"/>
+      <c r="J60" s="4"/>
+      <c r="K60" s="4"/>
+      <c r="L60" s="4"/>
+      <c r="M60" s="4"/>
+      <c r="N60" s="4"/>
+      <c r="O60" s="4"/>
+      <c r="P60" s="4"/>
+      <c r="Q60" s="4"/>
+      <c r="R60" s="4"/>
+      <c r="S60" s="4"/>
+      <c r="T60" s="4"/>
+      <c r="U60" s="4"/>
+      <c r="V60" s="4"/>
+      <c r="W60" s="4"/>
+      <c r="X60" s="4"/>
+      <c r="Y60" s="4"/>
+      <c r="Z60" s="4"/>
+      <c r="AA60" s="4"/>
+      <c r="AB60" s="4"/>
+      <c r="AC60" s="4"/>
+      <c r="AD60" s="4"/>
+      <c r="AE60" s="4"/>
+      <c r="AF60" s="4"/>
+      <c r="AG60" s="4"/>
+      <c r="AH60" s="4"/>
+      <c r="AI60" s="4"/>
+      <c r="AJ60" s="4"/>
+      <c r="AK60" s="4"/>
+      <c r="AL60" s="4"/>
+      <c r="AM60" s="4"/>
+      <c r="AN60" s="4"/>
+      <c r="AO60" s="4"/>
+      <c r="AP60" s="4"/>
+      <c r="AQ60" s="4"/>
+      <c r="AR60" s="4"/>
+      <c r="AS60" s="4"/>
+      <c r="AT60" s="4"/>
+      <c r="AU60" s="4"/>
+      <c r="AV60" s="4"/>
+      <c r="AW60" s="4"/>
+      <c r="AX60" s="4"/>
+      <c r="AY60" s="4"/>
+      <c r="AZ60" s="4"/>
+      <c r="BA60" s="4"/>
+      <c r="BB60" s="4"/>
+      <c r="BC60" s="4"/>
+      <c r="BD60" s="4"/>
+      <c r="BE60" s="4"/>
+      <c r="BF60" s="4"/>
+      <c r="BG60" s="4"/>
+      <c r="BH60" s="4"/>
+      <c r="BI60" s="4"/>
+      <c r="BJ60" s="4"/>
+      <c r="BK60" s="4"/>
+      <c r="BL60" s="4"/>
+      <c r="BM60" s="4"/>
+    </row>
+    <row r="61" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="B61" s="4"/>
+      <c r="C61" s="4"/>
+      <c r="D61" s="4"/>
+      <c r="E61" s="4"/>
+      <c r="F61" s="4"/>
+      <c r="G61" s="4"/>
+      <c r="H61" s="4"/>
+      <c r="I61" s="4"/>
+      <c r="J61" s="4"/>
+      <c r="K61" s="4"/>
+      <c r="L61" s="4"/>
+      <c r="M61" s="4"/>
+      <c r="N61" s="4"/>
+      <c r="O61" s="4"/>
+      <c r="P61" s="4"/>
+      <c r="Q61" s="4"/>
+      <c r="R61" s="4"/>
+      <c r="S61" s="4"/>
+      <c r="T61" s="4"/>
+      <c r="U61" s="4"/>
+      <c r="V61" s="4"/>
+      <c r="W61" s="4"/>
+      <c r="X61" s="4"/>
+      <c r="Y61" s="4"/>
+      <c r="Z61" s="4"/>
+      <c r="AA61" s="4"/>
+      <c r="AB61" s="4"/>
+      <c r="AC61" s="4"/>
+      <c r="AD61" s="4"/>
+      <c r="AE61" s="4"/>
+      <c r="AF61" s="4"/>
+      <c r="AG61" s="4"/>
+      <c r="AH61" s="4"/>
+      <c r="AI61" s="4"/>
+      <c r="AJ61" s="4"/>
+      <c r="AK61" s="4"/>
+      <c r="AL61" s="4"/>
+      <c r="AM61" s="4"/>
+      <c r="AN61" s="4"/>
+      <c r="AO61" s="4"/>
+      <c r="AP61" s="4"/>
+      <c r="AQ61" s="4"/>
+      <c r="AR61" s="4"/>
+      <c r="AS61" s="4"/>
+      <c r="AT61" s="4"/>
+      <c r="AU61" s="4"/>
+      <c r="AV61" s="4"/>
+      <c r="AW61" s="4"/>
+      <c r="AX61" s="4"/>
+      <c r="AY61" s="4"/>
+      <c r="AZ61" s="4"/>
+      <c r="BA61" s="4"/>
+      <c r="BB61" s="4"/>
+      <c r="BC61" s="4"/>
+      <c r="BD61" s="4"/>
+      <c r="BE61" s="4"/>
+      <c r="BF61" s="4"/>
+      <c r="BG61" s="4"/>
+      <c r="BH61" s="4"/>
+      <c r="BI61" s="4"/>
+      <c r="BJ61" s="4"/>
+      <c r="BK61" s="4"/>
+      <c r="BL61" s="4"/>
+      <c r="BM61" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="47">
+  <mergeCells count="55">
     <mergeCell ref="A1:BI1"/>
     <mergeCell ref="BJ1:BM1"/>
     <mergeCell ref="A2:BM2"/>
@@ -24241,18 +25835,26 @@
     <mergeCell ref="B33:E33"/>
     <mergeCell ref="B34:E34"/>
     <mergeCell ref="B35:E35"/>
-    <mergeCell ref="A37:V37"/>
-    <mergeCell ref="A43:BM43"/>
-    <mergeCell ref="A44:BM44"/>
-    <mergeCell ref="A45:BM45"/>
-    <mergeCell ref="A46:BM46"/>
-    <mergeCell ref="A47:BM47"/>
-    <mergeCell ref="A48:BM48"/>
-    <mergeCell ref="A49:BM49"/>
-    <mergeCell ref="A50:BM50"/>
+    <mergeCell ref="B36:E36"/>
+    <mergeCell ref="B37:E37"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="B42:E42"/>
+    <mergeCell ref="B43:E43"/>
+    <mergeCell ref="A45:V45"/>
     <mergeCell ref="A51:BM51"/>
     <mergeCell ref="A52:BM52"/>
     <mergeCell ref="A53:BM53"/>
+    <mergeCell ref="A54:BM54"/>
+    <mergeCell ref="A55:BM55"/>
+    <mergeCell ref="A56:BM56"/>
+    <mergeCell ref="A57:BM57"/>
+    <mergeCell ref="A58:BM58"/>
+    <mergeCell ref="A59:BM59"/>
+    <mergeCell ref="A60:BM60"/>
+    <mergeCell ref="A61:BM61"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>

--- a/tratando_tabelas/finitura/entradas_finitura.xlsx
+++ b/tratando_tabelas/finitura/entradas_finitura.xlsx
@@ -20,12 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1352" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1232" uniqueCount="208">
   <si>
     <t xml:space="preserve">Santri ADM 1.1.5.7 R1</t>
   </si>
   <si>
-    <t xml:space="preserve">Emitido em: 12/05/2026 07:50:03</t>
+    <t xml:space="preserve">Emitido em: 14/05/2026 07:28:18</t>
   </si>
   <si>
     <t xml:space="preserve">Relação de entradas - Sintético</t>
@@ -217,7 +217,7 @@
     <t xml:space="preserve">1.856 - DEXCO S.A - METAIS</t>
   </si>
   <si>
-    <t xml:space="preserve">5.071.467</t>
+    <t xml:space="preserve">5.071.473</t>
   </si>
   <si>
     <t xml:space="preserve">1</t>
@@ -232,7 +232,7 @@
     <t xml:space="preserve">XML</t>
   </si>
   <si>
-    <t xml:space="preserve">126,70</t>
+    <t xml:space="preserve">290,09</t>
   </si>
   <si>
     <t xml:space="preserve">Ag. chegada da mercadoria</t>
@@ -253,76 +253,19 @@
     <t xml:space="preserve">2.949</t>
   </si>
   <si>
-    <t xml:space="preserve">35260497837181002190550010050714671217480571</t>
+    <t xml:space="preserve">35260497837181002190550010050714731527694305</t>
   </si>
   <si>
     <t xml:space="preserve">Não</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.071.473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">290,09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050714731527694305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.134 - L.MARTINKOSKI &amp; CIA LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.260</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.070,21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41260408028676000103550010000562601004422817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.730,39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41260408028676000103550010000562311004422203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.576 - GRUPO METAL DESIGN LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">900,38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.910</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260486895448000560550010000006961367561442</t>
   </si>
   <si>
     <t xml:space="preserve">13.419 - METALDOMADO METALURGICA LTDA</t>
   </si>
   <si>
     <t xml:space="preserve">27.418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28/04/2026</t>
   </si>
   <si>
     <t xml:space="preserve">04/05/2026</t>
@@ -334,10 +277,16 @@
     <t xml:space="preserve">3.167,76</t>
   </si>
   <si>
+    <t xml:space="preserve">2.102</t>
+  </si>
+  <si>
     <t xml:space="preserve">35260400516639000124550010000274181095610391</t>
   </si>
   <si>
     <t xml:space="preserve">5.075.259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30/04/2026</t>
   </si>
   <si>
     <t xml:space="preserve">28/05/2026</t>
@@ -373,58 +322,10 @@
     <t xml:space="preserve">5.384,20</t>
   </si>
   <si>
-    <t xml:space="preserve">35260461413282000143550010029723801722131595</t>
+    <t xml:space="preserve">2.910</t>
   </si>
   <si>
-    <t xml:space="preserve">16.059 - JLR COM IMPORT. E EXP. DE MATERIAIS DE CONSTRUCAO LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.638,26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41260417781412000109550010000120391000336745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.171,52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260486895448000560550010000006981526909671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">700</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260486895448000560550010000007001016408174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.540 - LEXXA METAIS SANITARIOS LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.038,11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260400700221000253550010000108841638050409</t>
+    <t xml:space="preserve">35260461413282000143550010029723801722131595</t>
   </si>
   <si>
     <t xml:space="preserve">632.793</t>
@@ -440,21 +341,6 @@
   </si>
   <si>
     <t xml:space="preserve">42260575339051000141550080006327931688529359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.715 - LUMIERE COMERCIO INTERNACIONAL LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.485,60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260424855633000140550010000763681140081427</t>
   </si>
   <si>
     <t xml:space="preserve">30.850 - DEXCO S.A</t>
@@ -632,6 +518,75 @@
   </si>
   <si>
     <t xml:space="preserve">43260586895448000136550010000649101026177588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.134 - L.MARTINKOSKI &amp; CIA LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.188,23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41260508028676000103550010000564311004435113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.080.413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">404,81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050804131517661247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48,67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260597837181005378550010001627311454274477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.082.995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">461,96</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050829951181500130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">638.818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.077,92</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006388181323119663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.718 - STELLA IMPORTACAO E EXPORTACAO DE LUMINARIAS LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">292.997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">497,70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260510691158000370550010002929971371918584</t>
   </si>
   <si>
     <t xml:space="preserve">Total geral</t>
@@ -16877,7 +16832,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BM53"/>
+  <dimension ref="A1:BM50"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="18"/>
@@ -17249,7 +17204,7 @@
     </row>
     <row r="5" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="n">
-        <v>305957</v>
+        <v>305966</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>64</v>
@@ -17276,25 +17231,25 @@
         <v>69</v>
       </c>
       <c r="L5" s="12" t="n">
-        <v>126.7</v>
+        <v>290.09</v>
       </c>
       <c r="M5" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N5" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O5" s="12" t="n">
-        <v>118.97</v>
+        <v>272.38</v>
       </c>
       <c r="P5" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q5" s="13" t="n">
-        <v>0.001512</v>
+        <v>0.003202</v>
       </c>
       <c r="R5" s="12" t="n">
-        <v>1.58</v>
+        <v>1.93</v>
       </c>
       <c r="S5" s="12" t="n">
         <v>0</v>
@@ -17315,13 +17270,13 @@
         <v>67</v>
       </c>
       <c r="Y5" s="12" t="n">
-        <v>7.73</v>
+        <v>17.71</v>
       </c>
       <c r="Z5" s="12" t="n">
-        <v>118.97</v>
+        <v>272.38</v>
       </c>
       <c r="AA5" s="12" t="n">
-        <v>4.76</v>
+        <v>10.89</v>
       </c>
       <c r="AB5" s="12" t="n">
         <v>0</v>
@@ -17440,79 +17395,79 @@
     </row>
     <row r="6" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="n">
-        <v>305966</v>
+        <v>306454</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
       <c r="E6" s="9"/>
       <c r="F6" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G6" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="K6" s="11" t="s">
         <v>69</v>
       </c>
       <c r="L6" s="12" t="n">
-        <v>290.09</v>
+        <v>3167.76</v>
       </c>
       <c r="M6" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N6" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O6" s="12" t="n">
-        <v>272.38</v>
+        <v>3167.76</v>
       </c>
       <c r="P6" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q6" s="13" t="n">
-        <v>0.003202</v>
+        <v>0</v>
       </c>
       <c r="R6" s="12" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S6" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T6" s="14" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="U6" s="15" t="s">
         <v>71</v>
       </c>
       <c r="V6" s="12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W6" s="9" t="s">
         <v>72</v>
       </c>
       <c r="X6" s="9" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="Y6" s="12" t="n">
-        <v>17.71</v>
+        <v>0</v>
       </c>
       <c r="Z6" s="12" t="n">
-        <v>272.38</v>
+        <v>3167.76</v>
       </c>
       <c r="AA6" s="12" t="n">
-        <v>10.89</v>
+        <v>117.52</v>
       </c>
       <c r="AB6" s="12" t="n">
         <v>0</v>
@@ -17581,7 +17536,7 @@
         <v>75</v>
       </c>
       <c r="AX6" s="10" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AY6" s="14" t="s">
         <v>74</v>
@@ -17617,7 +17572,7 @@
         <v>68</v>
       </c>
       <c r="BJ6" s="9" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="BK6" s="9" t="s">
         <v>74</v>
@@ -17631,34 +17586,34 @@
     </row>
     <row r="7" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="n">
-        <v>306150</v>
+        <v>306477</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
       <c r="F7" s="9" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="G7" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="K7" s="11" t="s">
         <v>69</v>
       </c>
       <c r="L7" s="12" t="n">
-        <v>2070.21</v>
+        <v>3108.72</v>
       </c>
       <c r="M7" s="12" t="n">
         <v>0</v>
@@ -17667,22 +17622,22 @@
         <v>2</v>
       </c>
       <c r="O7" s="12" t="n">
-        <v>1970.21</v>
+        <v>3108.72</v>
       </c>
       <c r="P7" s="12" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="13" t="n">
-        <v>0</v>
+        <v>0.001598</v>
       </c>
       <c r="R7" s="12" t="n">
-        <v>4.15</v>
+        <v>2.6</v>
       </c>
       <c r="S7" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T7" s="14" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="U7" s="15" t="s">
         <v>71</v>
@@ -17694,16 +17649,16 @@
         <v>72</v>
       </c>
       <c r="X7" s="9" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="Y7" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z7" s="12" t="n">
-        <v>2070.21</v>
+        <v>3108.72</v>
       </c>
       <c r="AA7" s="12" t="n">
-        <v>144.92</v>
+        <v>217.61</v>
       </c>
       <c r="AB7" s="12" t="n">
         <v>0</v>
@@ -17772,7 +17727,7 @@
         <v>75</v>
       </c>
       <c r="AX7" s="10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="AY7" s="14" t="s">
         <v>74</v>
@@ -17808,7 +17763,7 @@
         <v>68</v>
       </c>
       <c r="BJ7" s="9" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="BK7" s="9" t="s">
         <v>74</v>
@@ -17822,79 +17777,79 @@
     </row>
     <row r="8" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="n">
-        <v>306173</v>
+        <v>306493</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
       <c r="F8" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="J8" s="9" t="s">
         <v>89</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="I8" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="J8" s="9" t="s">
-        <v>85</v>
       </c>
       <c r="K8" s="11" t="s">
         <v>69</v>
       </c>
       <c r="L8" s="12" t="n">
-        <v>3730.39</v>
+        <v>2876.8</v>
       </c>
       <c r="M8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N8" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O8" s="12" t="n">
-        <v>3730.39</v>
+        <v>2701.22</v>
       </c>
       <c r="P8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q8" s="13" t="n">
-        <v>0</v>
+        <v>0.027908</v>
       </c>
       <c r="R8" s="12" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="S8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T8" s="14" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="U8" s="15" t="s">
         <v>71</v>
       </c>
       <c r="V8" s="12" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="W8" s="9" t="s">
         <v>72</v>
       </c>
       <c r="X8" s="9" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="Y8" s="12" t="n">
-        <v>0</v>
+        <v>175.58</v>
       </c>
       <c r="Z8" s="12" t="n">
-        <v>3730.39</v>
+        <v>2701.22</v>
       </c>
       <c r="AA8" s="12" t="n">
-        <v>261.14</v>
+        <v>189.09</v>
       </c>
       <c r="AB8" s="12" t="n">
         <v>0</v>
@@ -17963,7 +17918,7 @@
         <v>75</v>
       </c>
       <c r="AX8" s="10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="AY8" s="14" t="s">
         <v>74</v>
@@ -17999,7 +17954,7 @@
         <v>68</v>
       </c>
       <c r="BJ8" s="9" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="BK8" s="9" t="s">
         <v>74</v>
@@ -18013,25 +17968,25 @@
     </row>
     <row r="9" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="n">
-        <v>306338</v>
+        <v>306535</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="9" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="G9" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="J9" s="9" t="s">
         <v>68</v>
@@ -18040,31 +17995,31 @@
         <v>69</v>
       </c>
       <c r="L9" s="12" t="n">
-        <v>900.38</v>
+        <v>5384.2</v>
       </c>
       <c r="M9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N9" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O9" s="12" t="n">
-        <v>900.38</v>
+        <v>5384.2</v>
       </c>
       <c r="P9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q9" s="13" t="n">
-        <v>0</v>
+        <v>0.023054</v>
       </c>
       <c r="R9" s="12" t="n">
-        <v>0</v>
+        <v>28.62</v>
       </c>
       <c r="S9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T9" s="14" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="U9" s="15" t="s">
         <v>71</v>
@@ -18076,16 +18031,16 @@
         <v>72</v>
       </c>
       <c r="X9" s="9" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="Y9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z9" s="12" t="n">
-        <v>900.38</v>
+        <v>0</v>
       </c>
       <c r="AA9" s="12" t="n">
-        <v>36.02</v>
+        <v>0</v>
       </c>
       <c r="AB9" s="12" t="n">
         <v>0</v>
@@ -18154,7 +18109,7 @@
         <v>75</v>
       </c>
       <c r="AX9" s="10" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="AY9" s="14" t="s">
         <v>74</v>
@@ -18190,7 +18145,7 @@
         <v>68</v>
       </c>
       <c r="BJ9" s="9" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="BK9" s="9" t="s">
         <v>74</v>
@@ -18204,79 +18159,79 @@
     </row>
     <row r="10" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="n">
-        <v>306454</v>
+        <v>306675</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
       <c r="F10" s="9" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K10" s="11" t="s">
         <v>69</v>
       </c>
       <c r="L10" s="12" t="n">
-        <v>3167.76</v>
+        <v>3116.85</v>
       </c>
       <c r="M10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N10" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O10" s="12" t="n">
-        <v>3167.76</v>
+        <v>3116.85</v>
       </c>
       <c r="P10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q10" s="13" t="n">
-        <v>0</v>
+        <v>0.011766</v>
       </c>
       <c r="R10" s="12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T10" s="14" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="U10" s="15" t="s">
         <v>71</v>
       </c>
       <c r="V10" s="12" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="W10" s="9" t="s">
         <v>72</v>
       </c>
       <c r="X10" s="9" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="Y10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z10" s="12" t="n">
-        <v>3167.76</v>
+        <v>3116.85</v>
       </c>
       <c r="AA10" s="12" t="n">
-        <v>117.52</v>
+        <v>218.18</v>
       </c>
       <c r="AB10" s="12" t="n">
         <v>0</v>
@@ -18345,7 +18300,7 @@
         <v>75</v>
       </c>
       <c r="AX10" s="10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="AY10" s="14" t="s">
         <v>74</v>
@@ -18381,7 +18336,7 @@
         <v>68</v>
       </c>
       <c r="BJ10" s="9" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="BK10" s="9" t="s">
         <v>74</v>
@@ -18395,79 +18350,79 @@
     </row>
     <row r="11" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="n">
-        <v>306477</v>
+        <v>306724</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>64</v>
+        <v>107</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
       <c r="F11" s="9" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="G11" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>106</v>
+        <v>68</v>
       </c>
       <c r="K11" s="11" t="s">
         <v>69</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>3108.72</v>
+        <v>976.79</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O11" s="12" t="n">
-        <v>3108.72</v>
+        <v>970.48</v>
       </c>
       <c r="P11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q11" s="13" t="n">
-        <v>0.001598</v>
+        <v>0</v>
       </c>
       <c r="R11" s="12" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T11" s="14" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="U11" s="15" t="s">
         <v>71</v>
       </c>
       <c r="V11" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W11" s="9" t="s">
         <v>72</v>
       </c>
       <c r="X11" s="9" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="Y11" s="12" t="n">
-        <v>0</v>
+        <v>6.31</v>
       </c>
       <c r="Z11" s="12" t="n">
-        <v>3108.72</v>
+        <v>976.79</v>
       </c>
       <c r="AA11" s="12" t="n">
-        <v>217.61</v>
+        <v>68.38</v>
       </c>
       <c r="AB11" s="12" t="n">
         <v>0</v>
@@ -18536,7 +18491,7 @@
         <v>75</v>
       </c>
       <c r="AX11" s="10" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AY11" s="14" t="s">
         <v>74</v>
@@ -18572,7 +18527,7 @@
         <v>68</v>
       </c>
       <c r="BJ11" s="9" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="BK11" s="9" t="s">
         <v>74</v>
@@ -18586,34 +18541,34 @@
     </row>
     <row r="12" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="n">
-        <v>306493</v>
+        <v>306726</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
       <c r="F12" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="K12" s="11" t="s">
         <v>69</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>2876.8</v>
+        <v>846.74</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>0</v>
@@ -18622,16 +18577,16 @@
         <v>1</v>
       </c>
       <c r="O12" s="12" t="n">
-        <v>2701.22</v>
+        <v>846.74</v>
       </c>
       <c r="P12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" s="13" t="n">
-        <v>0.027908</v>
+        <v>0</v>
       </c>
       <c r="R12" s="12" t="n">
-        <v>3.56</v>
+        <v>0.43</v>
       </c>
       <c r="S12" s="12" t="n">
         <v>0</v>
@@ -18649,16 +18604,16 @@
         <v>72</v>
       </c>
       <c r="X12" s="9" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="Y12" s="12" t="n">
-        <v>175.58</v>
+        <v>0</v>
       </c>
       <c r="Z12" s="12" t="n">
-        <v>2701.22</v>
+        <v>846.74</v>
       </c>
       <c r="AA12" s="12" t="n">
-        <v>189.09</v>
+        <v>59.27</v>
       </c>
       <c r="AB12" s="12" t="n">
         <v>0</v>
@@ -18727,7 +18682,7 @@
         <v>75</v>
       </c>
       <c r="AX12" s="10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="AY12" s="14" t="s">
         <v>74</v>
@@ -18777,7 +18732,7 @@
     </row>
     <row r="13" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="n">
-        <v>306535</v>
+        <v>306823</v>
       </c>
       <c r="B13" s="9" t="s">
         <v>114</v>
@@ -18792,64 +18747,64 @@
         <v>66</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>68</v>
+        <v>116</v>
       </c>
       <c r="K13" s="11" t="s">
         <v>69</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>5384.2</v>
+        <v>5775.71</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O13" s="12" t="n">
-        <v>5384.2</v>
+        <v>5510.71</v>
       </c>
       <c r="P13" s="12" t="n">
-        <v>0</v>
+        <v>265</v>
       </c>
       <c r="Q13" s="13" t="n">
-        <v>0.023054</v>
+        <v>0</v>
       </c>
       <c r="R13" s="12" t="n">
-        <v>28.62</v>
+        <v>3.5</v>
       </c>
       <c r="S13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T13" s="14" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="U13" s="15" t="s">
         <v>71</v>
       </c>
       <c r="V13" s="12" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="W13" s="9" t="s">
         <v>72</v>
       </c>
       <c r="X13" s="9" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="Y13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z13" s="12" t="n">
-        <v>0</v>
+        <v>5775.71</v>
       </c>
       <c r="AA13" s="12" t="n">
-        <v>0</v>
+        <v>404.3</v>
       </c>
       <c r="AB13" s="12" t="n">
         <v>0</v>
@@ -18918,7 +18873,7 @@
         <v>75</v>
       </c>
       <c r="AX13" s="10" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="AY13" s="14" t="s">
         <v>74</v>
@@ -18954,7 +18909,7 @@
         <v>68</v>
       </c>
       <c r="BJ13" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="BK13" s="9" t="s">
         <v>74</v>
@@ -18968,43 +18923,43 @@
     </row>
     <row r="14" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="n">
-        <v>306540</v>
+        <v>306845</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
       <c r="F14" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G14" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K14" s="11" t="s">
         <v>69</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>6638.26</v>
+        <v>935.55</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>1067.38</v>
+        <v>0</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O14" s="12" t="n">
-        <v>7115.9</v>
+        <v>935.55</v>
       </c>
       <c r="P14" s="12" t="n">
         <v>0</v>
@@ -19019,28 +18974,28 @@
         <v>0</v>
       </c>
       <c r="T14" s="14" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="U14" s="15" t="s">
         <v>71</v>
       </c>
       <c r="V14" s="12" t="n">
-        <v>105</v>
+        <v>28</v>
       </c>
       <c r="W14" s="9" t="s">
         <v>72</v>
       </c>
       <c r="X14" s="9" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="Y14" s="12" t="n">
-        <v>589.74</v>
+        <v>0</v>
       </c>
       <c r="Z14" s="12" t="n">
-        <v>6048.52</v>
+        <v>935.55</v>
       </c>
       <c r="AA14" s="12" t="n">
-        <v>241.94</v>
+        <v>65.49</v>
       </c>
       <c r="AB14" s="12" t="n">
         <v>0</v>
@@ -19109,7 +19064,7 @@
         <v>75</v>
       </c>
       <c r="AX14" s="10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="AY14" s="14" t="s">
         <v>74</v>
@@ -19145,7 +19100,7 @@
         <v>68</v>
       </c>
       <c r="BJ14" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="BK14" s="9" t="s">
         <v>74</v>
@@ -19159,43 +19114,43 @@
     </row>
     <row r="15" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="n">
-        <v>306545</v>
+        <v>306871</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>92</v>
+        <v>119</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
       <c r="F15" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G15" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="K15" s="11" t="s">
         <v>69</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>7171.52</v>
+        <v>1978.02</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O15" s="12" t="n">
-        <v>7171.52</v>
+        <v>1978.02</v>
       </c>
       <c r="P15" s="12" t="n">
         <v>0</v>
@@ -19210,28 +19165,28 @@
         <v>0</v>
       </c>
       <c r="T15" s="14" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="U15" s="15" t="s">
         <v>71</v>
       </c>
       <c r="V15" s="12" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="W15" s="9" t="s">
         <v>72</v>
       </c>
       <c r="X15" s="9" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="Y15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z15" s="12" t="n">
-        <v>7171.52</v>
+        <v>1978.02</v>
       </c>
       <c r="AA15" s="12" t="n">
-        <v>286.86</v>
+        <v>138.46</v>
       </c>
       <c r="AB15" s="12" t="n">
         <v>0</v>
@@ -19300,7 +19255,7 @@
         <v>75</v>
       </c>
       <c r="AX15" s="10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="AY15" s="14" t="s">
         <v>74</v>
@@ -19336,7 +19291,7 @@
         <v>68</v>
       </c>
       <c r="BJ15" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BK15" s="9" t="s">
         <v>74</v>
@@ -19350,79 +19305,79 @@
     </row>
     <row r="16" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="n">
-        <v>306579</v>
+        <v>306872</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>92</v>
+        <v>119</v>
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
       <c r="F16" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G16" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>124</v>
+        <v>68</v>
       </c>
       <c r="K16" s="11" t="s">
         <v>69</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>7171.52</v>
+        <v>569.02</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O16" s="12" t="n">
-        <v>7171.52</v>
+        <v>569.02</v>
       </c>
       <c r="P16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q16" s="13" t="n">
-        <v>0</v>
+        <v>0.003038</v>
       </c>
       <c r="R16" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T16" s="14" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="U16" s="15" t="s">
         <v>71</v>
       </c>
       <c r="V16" s="12" t="n">
-        <v>61.66</v>
+        <v>0</v>
       </c>
       <c r="W16" s="9" t="s">
         <v>72</v>
       </c>
       <c r="X16" s="9" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="Y16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z16" s="12" t="n">
-        <v>7171.52</v>
+        <v>569.02</v>
       </c>
       <c r="AA16" s="12" t="n">
-        <v>286.86</v>
+        <v>39.83</v>
       </c>
       <c r="AB16" s="12" t="n">
         <v>0</v>
@@ -19488,10 +19443,10 @@
         <v>73</v>
       </c>
       <c r="AW16" s="14" t="s">
-        <v>128</v>
+        <v>75</v>
       </c>
       <c r="AX16" s="10" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="AY16" s="14" t="s">
         <v>74</v>
@@ -19527,7 +19482,7 @@
         <v>68</v>
       </c>
       <c r="BJ16" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="BK16" s="9" t="s">
         <v>74</v>
@@ -19541,10 +19496,10 @@
     </row>
     <row r="17" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="n">
-        <v>306585</v>
+        <v>306873</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
@@ -19556,64 +19511,64 @@
         <v>66</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="K17" s="11" t="s">
         <v>69</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>24038.11</v>
+        <v>2954.76</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="O17" s="12" t="n">
-        <v>22949.18</v>
+        <v>2954.76</v>
       </c>
       <c r="P17" s="12" t="n">
-        <v>659</v>
+        <v>0</v>
       </c>
       <c r="Q17" s="13" t="n">
-        <v>0.022336</v>
+        <v>0.00726</v>
       </c>
       <c r="R17" s="12" t="n">
-        <v>5.96</v>
+        <v>9</v>
       </c>
       <c r="S17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T17" s="14" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="U17" s="15" t="s">
         <v>71</v>
       </c>
       <c r="V17" s="12" t="n">
-        <v>82.46</v>
+        <v>42</v>
       </c>
       <c r="W17" s="9" t="s">
         <v>72</v>
       </c>
       <c r="X17" s="9" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="Y17" s="12" t="n">
-        <v>429.93</v>
+        <v>0</v>
       </c>
       <c r="Z17" s="12" t="n">
-        <v>23608.18</v>
+        <v>2954.76</v>
       </c>
       <c r="AA17" s="12" t="n">
-        <v>944.32</v>
+        <v>206.83</v>
       </c>
       <c r="AB17" s="12" t="n">
         <v>0</v>
@@ -19682,7 +19637,7 @@
         <v>75</v>
       </c>
       <c r="AX17" s="10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="AY17" s="14" t="s">
         <v>74</v>
@@ -19718,7 +19673,7 @@
         <v>68</v>
       </c>
       <c r="BJ17" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="BK17" s="9" t="s">
         <v>74</v>
@@ -19732,79 +19687,79 @@
     </row>
     <row r="18" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="n">
-        <v>306675</v>
+        <v>306874</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
       <c r="F18" s="9" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>111</v>
+        <v>66</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="K18" s="11" t="s">
         <v>69</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>3116.85</v>
+        <v>2271.36</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O18" s="12" t="n">
-        <v>3116.85</v>
+        <v>2271.36</v>
       </c>
       <c r="P18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q18" s="13" t="n">
-        <v>0.011766</v>
+        <v>0.011638</v>
       </c>
       <c r="R18" s="12" t="n">
-        <v>2.1</v>
+        <v>17</v>
       </c>
       <c r="S18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T18" s="14" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="U18" s="15" t="s">
         <v>71</v>
       </c>
       <c r="V18" s="12" t="n">
-        <v>28</v>
+        <v>41.99</v>
       </c>
       <c r="W18" s="9" t="s">
         <v>72</v>
       </c>
       <c r="X18" s="9" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="Y18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z18" s="12" t="n">
-        <v>3116.85</v>
+        <v>2271.36</v>
       </c>
       <c r="AA18" s="12" t="n">
-        <v>218.18</v>
+        <v>159</v>
       </c>
       <c r="AB18" s="12" t="n">
         <v>0</v>
@@ -19873,7 +19828,7 @@
         <v>75</v>
       </c>
       <c r="AX18" s="10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="AY18" s="14" t="s">
         <v>74</v>
@@ -19909,7 +19864,7 @@
         <v>68</v>
       </c>
       <c r="BJ18" s="9" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="BK18" s="9" t="s">
         <v>74</v>
@@ -19923,79 +19878,79 @@
     </row>
     <row r="19" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="n">
-        <v>306713</v>
+        <v>306875</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>140</v>
+        <v>119</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
       <c r="F19" s="9" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="G19" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>142</v>
+        <v>121</v>
       </c>
       <c r="K19" s="11" t="s">
         <v>69</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>3485.6</v>
+        <v>5436.26</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O19" s="12" t="n">
-        <v>3288.3</v>
+        <v>5436.26</v>
       </c>
       <c r="P19" s="12" t="n">
-        <v>197.3</v>
+        <v>0</v>
       </c>
       <c r="Q19" s="13" t="n">
-        <v>0</v>
+        <v>0.022294</v>
       </c>
       <c r="R19" s="12" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="S19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T19" s="14" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="U19" s="15" t="s">
         <v>71</v>
       </c>
       <c r="V19" s="12" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="W19" s="9" t="s">
         <v>72</v>
       </c>
       <c r="X19" s="9" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="Y19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z19" s="12" t="n">
-        <v>3485.6</v>
+        <v>5436.26</v>
       </c>
       <c r="AA19" s="12" t="n">
-        <v>139.42</v>
+        <v>380.54</v>
       </c>
       <c r="AB19" s="12" t="n">
         <v>0</v>
@@ -20064,7 +20019,7 @@
         <v>75</v>
       </c>
       <c r="AX19" s="10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="AY19" s="14" t="s">
         <v>74</v>
@@ -20100,7 +20055,7 @@
         <v>68</v>
       </c>
       <c r="BJ19" s="9" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="BK19" s="9" t="s">
         <v>74</v>
@@ -20114,79 +20069,79 @@
     </row>
     <row r="20" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="n">
-        <v>306724</v>
+        <v>306876</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>145</v>
+        <v>119</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
       <c r="F20" s="9" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="G20" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>68</v>
+        <v>121</v>
       </c>
       <c r="K20" s="11" t="s">
         <v>69</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>976.79</v>
+        <v>6157.12</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O20" s="12" t="n">
-        <v>970.48</v>
+        <v>6157.12</v>
       </c>
       <c r="P20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q20" s="13" t="n">
-        <v>0</v>
+        <v>0.030068</v>
       </c>
       <c r="R20" s="12" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="S20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T20" s="14" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="U20" s="15" t="s">
         <v>71</v>
       </c>
       <c r="V20" s="12" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="W20" s="9" t="s">
         <v>72</v>
       </c>
       <c r="X20" s="9" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="Y20" s="12" t="n">
-        <v>6.31</v>
+        <v>0</v>
       </c>
       <c r="Z20" s="12" t="n">
-        <v>976.79</v>
+        <v>6157.12</v>
       </c>
       <c r="AA20" s="12" t="n">
-        <v>68.38</v>
+        <v>431</v>
       </c>
       <c r="AB20" s="12" t="n">
         <v>0</v>
@@ -20255,7 +20210,7 @@
         <v>75</v>
       </c>
       <c r="AX20" s="10" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AY20" s="14" t="s">
         <v>74</v>
@@ -20291,7 +20246,7 @@
         <v>68</v>
       </c>
       <c r="BJ20" s="9" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="BK20" s="9" t="s">
         <v>74</v>
@@ -20305,34 +20260,34 @@
     </row>
     <row r="21" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="n">
-        <v>306726</v>
+        <v>306880</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>109</v>
+        <v>143</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
       <c r="F21" s="9" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>111</v>
+        <v>145</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>137</v>
+        <v>68</v>
       </c>
       <c r="K21" s="11" t="s">
         <v>69</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>846.74</v>
+        <v>39.5</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>0</v>
@@ -20341,7 +20296,7 @@
         <v>1</v>
       </c>
       <c r="O21" s="12" t="n">
-        <v>846.74</v>
+        <v>35.99</v>
       </c>
       <c r="P21" s="12" t="n">
         <v>0</v>
@@ -20350,34 +20305,34 @@
         <v>0</v>
       </c>
       <c r="R21" s="12" t="n">
-        <v>0.43</v>
+        <v>0</v>
       </c>
       <c r="S21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T21" s="14" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="U21" s="15" t="s">
         <v>71</v>
       </c>
       <c r="V21" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W21" s="9" t="s">
         <v>72</v>
       </c>
       <c r="X21" s="9" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="Y21" s="12" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="Z21" s="12" t="n">
-        <v>846.74</v>
+        <v>35.99</v>
       </c>
       <c r="AA21" s="12" t="n">
-        <v>59.27</v>
+        <v>2.52</v>
       </c>
       <c r="AB21" s="12" t="n">
         <v>0</v>
@@ -20446,7 +20401,7 @@
         <v>75</v>
       </c>
       <c r="AX21" s="10" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="AY21" s="14" t="s">
         <v>74</v>
@@ -20482,7 +20437,7 @@
         <v>68</v>
       </c>
       <c r="BJ21" s="9" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="BK21" s="9" t="s">
         <v>74</v>
@@ -20496,79 +20451,79 @@
     </row>
     <row r="22" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="n">
-        <v>306823</v>
+        <v>306969</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
       <c r="F22" s="9" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="G22" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>136</v>
+        <v>83</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>102</v>
+        <v>150</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="K22" s="11" t="s">
         <v>69</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>5775.71</v>
+        <v>3625.8</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O22" s="12" t="n">
-        <v>5510.71</v>
+        <v>3315.52</v>
       </c>
       <c r="P22" s="12" t="n">
-        <v>265</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R22" s="12" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="S22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T22" s="14" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="U22" s="15" t="s">
         <v>71</v>
       </c>
       <c r="V22" s="12" t="n">
-        <v>42</v>
+        <v>60.33</v>
       </c>
       <c r="W22" s="9" t="s">
         <v>72</v>
       </c>
       <c r="X22" s="9" t="s">
-        <v>102</v>
+        <v>150</v>
       </c>
       <c r="Y22" s="12" t="n">
-        <v>0</v>
+        <v>310.28</v>
       </c>
       <c r="Z22" s="12" t="n">
-        <v>5775.71</v>
+        <v>3315.52</v>
       </c>
       <c r="AA22" s="12" t="n">
-        <v>404.3</v>
+        <v>132.63</v>
       </c>
       <c r="AB22" s="12" t="n">
         <v>0</v>
@@ -20637,7 +20592,7 @@
         <v>75</v>
       </c>
       <c r="AX22" s="10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="AY22" s="14" t="s">
         <v>74</v>
@@ -20673,7 +20628,7 @@
         <v>68</v>
       </c>
       <c r="BJ22" s="9" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="BK22" s="9" t="s">
         <v>74</v>
@@ -20687,34 +20642,34 @@
     </row>
     <row r="23" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="n">
-        <v>306845</v>
+        <v>306975</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>157</v>
+        <v>119</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="9" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="G23" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>102</v>
+        <v>125</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>102</v>
+        <v>150</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="K23" s="11" t="s">
         <v>69</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>935.55</v>
+        <v>985.72</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>0</v>
@@ -20723,43 +20678,43 @@
         <v>1</v>
       </c>
       <c r="O23" s="12" t="n">
-        <v>935.55</v>
+        <v>985.72</v>
       </c>
       <c r="P23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q23" s="13" t="n">
-        <v>0</v>
+        <v>0.002368</v>
       </c>
       <c r="R23" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T23" s="14" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="U23" s="15" t="s">
         <v>71</v>
       </c>
       <c r="V23" s="12" t="n">
-        <v>28</v>
+        <v>41.98</v>
       </c>
       <c r="W23" s="9" t="s">
         <v>72</v>
       </c>
       <c r="X23" s="9" t="s">
-        <v>102</v>
+        <v>150</v>
       </c>
       <c r="Y23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z23" s="12" t="n">
-        <v>935.55</v>
+        <v>985.72</v>
       </c>
       <c r="AA23" s="12" t="n">
-        <v>65.49</v>
+        <v>69</v>
       </c>
       <c r="AB23" s="12" t="n">
         <v>0</v>
@@ -20828,7 +20783,7 @@
         <v>75</v>
       </c>
       <c r="AX23" s="10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="AY23" s="14" t="s">
         <v>74</v>
@@ -20864,7 +20819,7 @@
         <v>68</v>
       </c>
       <c r="BJ23" s="9" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="BK23" s="9" t="s">
         <v>74</v>
@@ -20878,34 +20833,34 @@
     </row>
     <row r="24" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="n">
-        <v>306871</v>
+        <v>306976</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>157</v>
+        <v>119</v>
       </c>
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
       <c r="F24" s="9" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="G24" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>102</v>
+        <v>125</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="K24" s="11" t="s">
         <v>69</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>1978.02</v>
+        <v>1478.58</v>
       </c>
       <c r="M24" s="12" t="n">
         <v>0</v>
@@ -20914,43 +20869,43 @@
         <v>1</v>
       </c>
       <c r="O24" s="12" t="n">
-        <v>1978.02</v>
+        <v>1478.58</v>
       </c>
       <c r="P24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q24" s="13" t="n">
-        <v>0</v>
+        <v>0.007104</v>
       </c>
       <c r="R24" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T24" s="14" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="U24" s="15" t="s">
         <v>71</v>
       </c>
       <c r="V24" s="12" t="n">
-        <v>28</v>
+        <v>41.99</v>
       </c>
       <c r="W24" s="9" t="s">
         <v>72</v>
       </c>
       <c r="X24" s="9" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="Y24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z24" s="12" t="n">
-        <v>1978.02</v>
+        <v>1478.58</v>
       </c>
       <c r="AA24" s="12" t="n">
-        <v>138.46</v>
+        <v>103.5</v>
       </c>
       <c r="AB24" s="12" t="n">
         <v>0</v>
@@ -21019,7 +20974,7 @@
         <v>75</v>
       </c>
       <c r="AX24" s="10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="AY24" s="14" t="s">
         <v>74</v>
@@ -21055,7 +21010,7 @@
         <v>68</v>
       </c>
       <c r="BJ24" s="9" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="BK24" s="9" t="s">
         <v>74</v>
@@ -21069,79 +21024,79 @@
     </row>
     <row r="25" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="n">
-        <v>306872</v>
+        <v>306977</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>157</v>
+        <v>119</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="G25" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>102</v>
+        <v>125</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>68</v>
+        <v>155</v>
       </c>
       <c r="K25" s="11" t="s">
         <v>69</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>569.02</v>
+        <v>1478.58</v>
       </c>
       <c r="M25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O25" s="12" t="n">
-        <v>569.02</v>
+        <v>1478.58</v>
       </c>
       <c r="P25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q25" s="13" t="n">
-        <v>0.003038</v>
+        <v>0.007104</v>
       </c>
       <c r="R25" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T25" s="14" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="U25" s="15" t="s">
         <v>71</v>
       </c>
       <c r="V25" s="12" t="n">
-        <v>0</v>
+        <v>41.99</v>
       </c>
       <c r="W25" s="9" t="s">
         <v>72</v>
       </c>
       <c r="X25" s="9" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="Y25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z25" s="12" t="n">
-        <v>569.02</v>
+        <v>1478.58</v>
       </c>
       <c r="AA25" s="12" t="n">
-        <v>39.83</v>
+        <v>103.5</v>
       </c>
       <c r="AB25" s="12" t="n">
         <v>0</v>
@@ -21210,7 +21165,7 @@
         <v>75</v>
       </c>
       <c r="AX25" s="10" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="AY25" s="14" t="s">
         <v>74</v>
@@ -21246,7 +21201,7 @@
         <v>68</v>
       </c>
       <c r="BJ25" s="9" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="BK25" s="9" t="s">
         <v>74</v>
@@ -21260,79 +21215,79 @@
     </row>
     <row r="26" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="n">
-        <v>306873</v>
+        <v>307040</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>157</v>
+        <v>119</v>
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="G26" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>102</v>
+        <v>125</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="K26" s="11" t="s">
         <v>69</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>2954.76</v>
+        <v>1478.58</v>
       </c>
       <c r="M26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O26" s="12" t="n">
-        <v>2954.76</v>
+        <v>1478.58</v>
       </c>
       <c r="P26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q26" s="13" t="n">
-        <v>0.00726</v>
+        <v>0.007104</v>
       </c>
       <c r="R26" s="12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="S26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T26" s="14" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="U26" s="15" t="s">
         <v>71</v>
       </c>
       <c r="V26" s="12" t="n">
-        <v>42</v>
+        <v>41.99</v>
       </c>
       <c r="W26" s="9" t="s">
         <v>72</v>
       </c>
       <c r="X26" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Y26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z26" s="12" t="n">
-        <v>2954.76</v>
+        <v>1478.58</v>
       </c>
       <c r="AA26" s="12" t="n">
-        <v>206.83</v>
+        <v>103.5</v>
       </c>
       <c r="AB26" s="12" t="n">
         <v>0</v>
@@ -21401,7 +21356,7 @@
         <v>75</v>
       </c>
       <c r="AX26" s="10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="AY26" s="14" t="s">
         <v>74</v>
@@ -21437,7 +21392,7 @@
         <v>68</v>
       </c>
       <c r="BJ26" s="9" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="BK26" s="9" t="s">
         <v>74</v>
@@ -21451,79 +21406,79 @@
     </row>
     <row r="27" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="n">
-        <v>306874</v>
+        <v>307120</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G27" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>102</v>
+        <v>150</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="J27" s="9" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="K27" s="11" t="s">
         <v>69</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>2271.36</v>
+        <v>1188.23</v>
       </c>
       <c r="M27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O27" s="12" t="n">
-        <v>2271.36</v>
+        <v>1088.23</v>
       </c>
       <c r="P27" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q27" s="13" t="n">
-        <v>0.011638</v>
+        <v>0</v>
       </c>
       <c r="R27" s="12" t="n">
-        <v>17</v>
+        <v>3.9</v>
       </c>
       <c r="S27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T27" s="14" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="U27" s="15" t="s">
         <v>71</v>
       </c>
       <c r="V27" s="12" t="n">
-        <v>41.99</v>
+        <v>28</v>
       </c>
       <c r="W27" s="9" t="s">
         <v>72</v>
       </c>
       <c r="X27" s="9" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="Y27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z27" s="12" t="n">
-        <v>2271.36</v>
+        <v>1188.23</v>
       </c>
       <c r="AA27" s="12" t="n">
-        <v>159</v>
+        <v>83.18</v>
       </c>
       <c r="AB27" s="12" t="n">
         <v>0</v>
@@ -21592,7 +21547,7 @@
         <v>75</v>
       </c>
       <c r="AX27" s="10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="AY27" s="14" t="s">
         <v>74</v>
@@ -21628,7 +21583,7 @@
         <v>68</v>
       </c>
       <c r="BJ27" s="9" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="BK27" s="9" t="s">
         <v>74</v>
@@ -21642,79 +21597,79 @@
     </row>
     <row r="28" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="n">
-        <v>306875</v>
+        <v>307172</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>157</v>
+        <v>64</v>
       </c>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="G28" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>102</v>
+        <v>150</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>159</v>
+        <v>68</v>
       </c>
       <c r="K28" s="11" t="s">
         <v>69</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>5436.26</v>
+        <v>404.81</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O28" s="12" t="n">
-        <v>5436.26</v>
+        <v>404.81</v>
       </c>
       <c r="P28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q28" s="13" t="n">
-        <v>0.022294</v>
+        <v>0.000858</v>
       </c>
       <c r="R28" s="12" t="n">
-        <v>26</v>
+        <v>2.43</v>
       </c>
       <c r="S28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T28" s="14" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="U28" s="15" t="s">
         <v>71</v>
       </c>
       <c r="V28" s="12" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="W28" s="9" t="s">
         <v>72</v>
       </c>
       <c r="X28" s="9" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="Y28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z28" s="12" t="n">
-        <v>5436.26</v>
+        <v>404.81</v>
       </c>
       <c r="AA28" s="12" t="n">
-        <v>380.54</v>
+        <v>16.19</v>
       </c>
       <c r="AB28" s="12" t="n">
         <v>0</v>
@@ -21783,7 +21738,7 @@
         <v>75</v>
       </c>
       <c r="AX28" s="10" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AY28" s="14" t="s">
         <v>74</v>
@@ -21819,7 +21774,7 @@
         <v>68</v>
       </c>
       <c r="BJ28" s="9" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="BK28" s="9" t="s">
         <v>74</v>
@@ -21833,79 +21788,79 @@
     </row>
     <row r="29" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="n">
-        <v>306876</v>
+        <v>307205</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>157</v>
+        <v>107</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
       <c r="F29" s="9" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="G29" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>102</v>
+        <v>150</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>159</v>
+        <v>68</v>
       </c>
       <c r="K29" s="11" t="s">
         <v>69</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>6157.12</v>
+        <v>48.67</v>
       </c>
       <c r="M29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O29" s="12" t="n">
-        <v>6157.12</v>
+        <v>48.36</v>
       </c>
       <c r="P29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q29" s="13" t="n">
-        <v>0.030068</v>
+        <v>0.01185</v>
       </c>
       <c r="R29" s="12" t="n">
-        <v>34</v>
+        <v>34.5</v>
       </c>
       <c r="S29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T29" s="14" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="U29" s="15" t="s">
         <v>71</v>
       </c>
       <c r="V29" s="12" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="W29" s="9" t="s">
         <v>72</v>
       </c>
       <c r="X29" s="9" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="Y29" s="12" t="n">
-        <v>0</v>
+        <v>0.31</v>
       </c>
       <c r="Z29" s="12" t="n">
-        <v>6157.12</v>
+        <v>48.36</v>
       </c>
       <c r="AA29" s="12" t="n">
-        <v>431</v>
+        <v>3.39</v>
       </c>
       <c r="AB29" s="12" t="n">
         <v>0</v>
@@ -21974,7 +21929,7 @@
         <v>75</v>
       </c>
       <c r="AX29" s="10" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AY29" s="14" t="s">
         <v>74</v>
@@ -22010,7 +21965,7 @@
         <v>68</v>
       </c>
       <c r="BJ29" s="9" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="BK29" s="9" t="s">
         <v>74</v>
@@ -22024,25 +21979,25 @@
     </row>
     <row r="30" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="n">
-        <v>306880</v>
+        <v>307219</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>181</v>
+        <v>64</v>
       </c>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
       <c r="F30" s="9" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="G30" s="10" t="s">
-        <v>183</v>
+        <v>66</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>102</v>
+        <v>168</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="J30" s="9" t="s">
         <v>68</v>
@@ -22051,7 +22006,7 @@
         <v>69</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>39.5</v>
+        <v>461.96</v>
       </c>
       <c r="M30" s="12" t="n">
         <v>0</v>
@@ -22060,22 +22015,22 @@
         <v>1</v>
       </c>
       <c r="O30" s="12" t="n">
-        <v>35.99</v>
+        <v>461.96</v>
       </c>
       <c r="P30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q30" s="13" t="n">
-        <v>0</v>
+        <v>0.002057</v>
       </c>
       <c r="R30" s="12" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T30" s="14" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="U30" s="15" t="s">
         <v>71</v>
@@ -22087,16 +22042,16 @@
         <v>72</v>
       </c>
       <c r="X30" s="9" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="Y30" s="12" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="Z30" s="12" t="n">
-        <v>35.99</v>
+        <v>461.96</v>
       </c>
       <c r="AA30" s="12" t="n">
-        <v>2.52</v>
+        <v>18.48</v>
       </c>
       <c r="AB30" s="12" t="n">
         <v>0</v>
@@ -22165,7 +22120,7 @@
         <v>75</v>
       </c>
       <c r="AX30" s="10" t="s">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="AY30" s="14" t="s">
         <v>74</v>
@@ -22201,7 +22156,7 @@
         <v>68</v>
       </c>
       <c r="BJ30" s="9" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="BK30" s="9" t="s">
         <v>74</v>
@@ -22215,79 +22170,79 @@
     </row>
     <row r="31" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="n">
-        <v>306969</v>
+        <v>307243</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>186</v>
+        <v>92</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
       <c r="F31" s="9" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>102</v>
+        <v>168</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="J31" s="9" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="K31" s="11" t="s">
         <v>69</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>3625.8</v>
+        <v>2077.92</v>
       </c>
       <c r="M31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O31" s="12" t="n">
-        <v>3315.52</v>
+        <v>2077.92</v>
       </c>
       <c r="P31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q31" s="13" t="n">
-        <v>0</v>
+        <v>0.007844</v>
       </c>
       <c r="R31" s="12" t="n">
-        <v>0</v>
+        <v>0.81</v>
       </c>
       <c r="S31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T31" s="14" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="U31" s="15" t="s">
         <v>71</v>
       </c>
       <c r="V31" s="12" t="n">
-        <v>60.33</v>
+        <v>28</v>
       </c>
       <c r="W31" s="9" t="s">
         <v>72</v>
       </c>
       <c r="X31" s="9" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="Y31" s="12" t="n">
-        <v>310.28</v>
+        <v>0</v>
       </c>
       <c r="Z31" s="12" t="n">
-        <v>3315.52</v>
+        <v>2077.92</v>
       </c>
       <c r="AA31" s="12" t="n">
-        <v>132.63</v>
+        <v>145.45</v>
       </c>
       <c r="AB31" s="12" t="n">
         <v>0</v>
@@ -22356,7 +22311,7 @@
         <v>75</v>
       </c>
       <c r="AX31" s="10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="AY31" s="14" t="s">
         <v>74</v>
@@ -22392,7 +22347,7 @@
         <v>68</v>
       </c>
       <c r="BJ31" s="9" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="BK31" s="9" t="s">
         <v>74</v>
@@ -22406,34 +22361,34 @@
     </row>
     <row r="32" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="n">
-        <v>306975</v>
+        <v>307275</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>157</v>
+        <v>185</v>
       </c>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
       <c r="F32" s="9" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="G32" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="J32" s="9" t="s">
-        <v>193</v>
+        <v>68</v>
       </c>
       <c r="K32" s="11" t="s">
         <v>69</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>985.72</v>
+        <v>497.7</v>
       </c>
       <c r="M32" s="12" t="n">
         <v>0</v>
@@ -22442,43 +22397,43 @@
         <v>1</v>
       </c>
       <c r="O32" s="12" t="n">
-        <v>985.72</v>
+        <v>497.7</v>
       </c>
       <c r="P32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q32" s="13" t="n">
-        <v>0.002368</v>
+        <v>0</v>
       </c>
       <c r="R32" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T32" s="14" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="U32" s="15" t="s">
         <v>71</v>
       </c>
       <c r="V32" s="12" t="n">
-        <v>41.98</v>
+        <v>0</v>
       </c>
       <c r="W32" s="9" t="s">
         <v>72</v>
       </c>
       <c r="X32" s="9" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="Y32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z32" s="12" t="n">
-        <v>985.72</v>
+        <v>497.7</v>
       </c>
       <c r="AA32" s="12" t="n">
-        <v>69</v>
+        <v>19.91</v>
       </c>
       <c r="AB32" s="12" t="n">
         <v>0</v>
@@ -22547,7 +22502,7 @@
         <v>75</v>
       </c>
       <c r="AX32" s="10" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="AY32" s="14" t="s">
         <v>74</v>
@@ -22583,7 +22538,7 @@
         <v>68</v>
       </c>
       <c r="BJ32" s="9" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="BK32" s="9" t="s">
         <v>74</v>
@@ -22596,900 +22551,534 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="8" t="n">
-        <v>306976</v>
-      </c>
-      <c r="B33" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9" t="s">
-        <v>196</v>
-      </c>
-      <c r="G33" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="H33" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="I33" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="J33" s="9" t="s">
+      <c r="A33" s="4"/>
+    </row>
+    <row r="34" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="17" t="s">
+        <v>189</v>
+      </c>
+      <c r="B34" s="17"/>
+      <c r="C34" s="17"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="17"/>
+      <c r="F34" s="17"/>
+      <c r="G34" s="17"/>
+      <c r="H34" s="17"/>
+      <c r="I34" s="17"/>
+      <c r="J34" s="17"/>
+      <c r="K34" s="17"/>
+      <c r="L34" s="17"/>
+      <c r="M34" s="17"/>
+      <c r="N34" s="17"/>
+      <c r="O34" s="17"/>
+      <c r="P34" s="17"/>
+      <c r="Q34" s="17"/>
+      <c r="R34" s="17"/>
+      <c r="S34" s="17"/>
+      <c r="T34" s="17"/>
+      <c r="U34" s="17"/>
+      <c r="V34" s="17"/>
+    </row>
+    <row r="35" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="B35" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C35" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D35" s="18" t="s">
+        <v>191</v>
+      </c>
+      <c r="E35" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F35" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="G35" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H35" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="I35" s="18" t="s">
+        <v>192</v>
+      </c>
+      <c r="J35" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="K35" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="L35" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="M35" s="18" t="s">
         <v>193</v>
       </c>
-      <c r="K33" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="L33" s="12" t="n">
-        <v>1478.58</v>
-      </c>
-      <c r="M33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O33" s="12" t="n">
-        <v>1478.58</v>
-      </c>
-      <c r="P33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="13" t="n">
-        <v>0.007104</v>
-      </c>
-      <c r="R33" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="S33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="U33" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="V33" s="12" t="n">
-        <v>41.99</v>
-      </c>
-      <c r="W33" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="X33" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="Y33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z33" s="12" t="n">
-        <v>1478.58</v>
-      </c>
-      <c r="AA33" s="12" t="n">
-        <v>103.5</v>
-      </c>
-      <c r="AB33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH33" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AI33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ33" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AK33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM33" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AN33" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AO33" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AP33" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AQ33" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AR33" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AS33" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AT33" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AU33" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AV33" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW33" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AX33" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="AY33" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AZ33" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BA33" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BB33" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BC33" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BD33" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BE33" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BF33" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="BG33" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="BH33" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BI33" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="BJ33" s="9" t="s">
-        <v>198</v>
-      </c>
-      <c r="BK33" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="BL33" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="BM33" s="16" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="8" t="n">
-        <v>306977</v>
-      </c>
-      <c r="B34" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9" t="s">
-        <v>199</v>
-      </c>
-      <c r="G34" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="H34" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="I34" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="J34" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="K34" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="L34" s="12" t="n">
-        <v>1478.58</v>
-      </c>
-      <c r="M34" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O34" s="12" t="n">
-        <v>1478.58</v>
-      </c>
-      <c r="P34" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="13" t="n">
-        <v>0.007104</v>
-      </c>
-      <c r="R34" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="S34" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="U34" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="V34" s="12" t="n">
-        <v>41.99</v>
-      </c>
-      <c r="W34" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="X34" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="Y34" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z34" s="12" t="n">
-        <v>1478.58</v>
-      </c>
-      <c r="AA34" s="12" t="n">
-        <v>103.5</v>
-      </c>
-      <c r="AB34" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC34" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD34" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE34" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF34" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG34" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH34" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AI34" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ34" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AK34" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL34" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM34" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AN34" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AO34" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AP34" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AQ34" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AR34" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AS34" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AT34" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AU34" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AV34" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW34" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AX34" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="AY34" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AZ34" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BA34" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BB34" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BC34" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BD34" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BE34" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BF34" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="BG34" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="BH34" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BI34" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="BJ34" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="BK34" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="BL34" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="BM34" s="16" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="8" t="n">
-        <v>307040</v>
-      </c>
-      <c r="B35" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="G35" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="H35" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="I35" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="J35" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="K35" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="L35" s="12" t="n">
-        <v>1478.58</v>
-      </c>
-      <c r="M35" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O35" s="12" t="n">
-        <v>1478.58</v>
-      </c>
-      <c r="P35" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" s="13" t="n">
-        <v>0.007104</v>
-      </c>
-      <c r="R35" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="S35" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="U35" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="V35" s="12" t="n">
-        <v>41.99</v>
-      </c>
-      <c r="W35" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="X35" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="Y35" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z35" s="12" t="n">
-        <v>1478.58</v>
-      </c>
-      <c r="AA35" s="12" t="n">
-        <v>103.5</v>
-      </c>
-      <c r="AB35" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC35" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD35" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE35" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF35" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG35" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH35" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AI35" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ35" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AK35" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL35" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM35" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AN35" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AO35" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AP35" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AQ35" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AR35" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AS35" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AT35" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AU35" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AV35" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW35" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AX35" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="AY35" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AZ35" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BA35" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BB35" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BC35" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BD35" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BE35" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BF35" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="BG35" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="BH35" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BI35" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="BJ35" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="BK35" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="BL35" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="BM35" s="16" t="s">
-        <v>78</v>
+      <c r="N35" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="O35" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="P35" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q35" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="R35" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="S35" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="T35" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="U35" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="V35" s="18" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="4"/>
+      <c r="A36" s="19" t="n">
+        <v>28</v>
+      </c>
+      <c r="B36" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="19" t="n">
+        <v>365</v>
+      </c>
+      <c r="D36" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="19" t="n">
+        <v>513.7</v>
+      </c>
+      <c r="F36" s="19" t="n">
+        <v>53720.21</v>
+      </c>
+      <c r="G36" s="19" t="n">
+        <v>3507.64</v>
+      </c>
+      <c r="H36" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="19" t="n">
+        <v>59611.8</v>
+      </c>
+      <c r="L36" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" s="20" t="n">
+        <v>0.188115</v>
+      </c>
+      <c r="S36" s="19" t="n">
+        <v>58733.1</v>
+      </c>
+      <c r="T36" s="19" t="n">
+        <v>59611.8</v>
+      </c>
+      <c r="U36" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="17" t="s">
-        <v>204</v>
-      </c>
-      <c r="B37" s="17"/>
-      <c r="C37" s="17"/>
-      <c r="D37" s="17"/>
-      <c r="E37" s="17"/>
-      <c r="F37" s="17"/>
-      <c r="G37" s="17"/>
-      <c r="H37" s="17"/>
-      <c r="I37" s="17"/>
-      <c r="J37" s="17"/>
-      <c r="K37" s="17"/>
-      <c r="L37" s="17"/>
-      <c r="M37" s="17"/>
-      <c r="N37" s="17"/>
-      <c r="O37" s="17"/>
-      <c r="P37" s="17"/>
-      <c r="Q37" s="17"/>
-      <c r="R37" s="17"/>
-      <c r="S37" s="17"/>
-      <c r="T37" s="17"/>
-      <c r="U37" s="17"/>
-      <c r="V37" s="17"/>
+      <c r="A37" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B37" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C37" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D37" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="E37" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="F37" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="G37" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="H37" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="I37" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="J37" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="K37" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="L37" s="18" t="s">
+        <v>197</v>
+      </c>
+      <c r="M37" s="18" t="s">
+        <v>198</v>
+      </c>
     </row>
-    <row r="38" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="18" t="s">
-        <v>205</v>
-      </c>
-      <c r="B38" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C38" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D38" s="18" t="s">
-        <v>206</v>
-      </c>
-      <c r="E38" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F38" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="G38" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="H38" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="I38" s="18" t="s">
-        <v>207</v>
-      </c>
-      <c r="J38" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="K38" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="L38" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="M38" s="18" t="s">
-        <v>208</v>
-      </c>
-      <c r="N38" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="O38" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="P38" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q38" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="R38" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="S38" s="18" t="s">
-        <v>209</v>
-      </c>
-      <c r="T38" s="18" t="s">
-        <v>210</v>
-      </c>
-      <c r="U38" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="V38" s="18" t="s">
-        <v>37</v>
+    <row r="38" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="19" t="n">
+        <v>196.8</v>
+      </c>
+      <c r="B38" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="19" t="n">
+        <v>31.41</v>
+      </c>
+      <c r="E38" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" s="19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="19" t="n">
-        <v>31</v>
-      </c>
-      <c r="B39" s="19" t="n">
-        <v>1067.38</v>
-      </c>
-      <c r="C39" s="19" t="n">
-        <v>1221.3</v>
-      </c>
-      <c r="D39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" s="19" t="n">
-        <v>1540.79</v>
-      </c>
-      <c r="F39" s="19" t="n">
-        <v>103346.52</v>
-      </c>
-      <c r="G39" s="19" t="n">
-        <v>5567.28</v>
-      </c>
-      <c r="H39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" s="19" t="n">
-        <v>110265.2</v>
-      </c>
-      <c r="L39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" s="20" t="n">
-        <v>0.189354</v>
-      </c>
-      <c r="S39" s="19" t="n">
-        <v>108570.49</v>
-      </c>
-      <c r="T39" s="19" t="n">
-        <v>110265.2</v>
-      </c>
-      <c r="U39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" s="19" t="n">
-        <v>0</v>
-      </c>
+      <c r="A39" s="4"/>
     </row>
     <row r="40" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="B40" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C40" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="D40" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E40" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="F40" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="G40" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="H40" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="I40" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="J40" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="K40" s="18" t="s">
-        <v>211</v>
-      </c>
-      <c r="L40" s="18" t="s">
-        <v>212</v>
-      </c>
-      <c r="M40" s="18" t="s">
-        <v>213</v>
-      </c>
+      <c r="A40" s="21" t="s">
+        <v>199</v>
+      </c>
+      <c r="B40" s="21"/>
+      <c r="C40" s="21"/>
+      <c r="D40" s="21"/>
+      <c r="E40" s="21"/>
+      <c r="F40" s="21"/>
+      <c r="G40" s="21"/>
+      <c r="H40" s="21"/>
+      <c r="I40" s="21"/>
+      <c r="J40" s="21"/>
+      <c r="K40" s="21"/>
+      <c r="L40" s="21"/>
+      <c r="M40" s="21"/>
+      <c r="N40" s="21"/>
+      <c r="O40" s="21"/>
+      <c r="P40" s="21"/>
+      <c r="Q40" s="21"/>
+      <c r="R40" s="21"/>
+      <c r="S40" s="21"/>
+      <c r="T40" s="21"/>
+      <c r="U40" s="21"/>
+      <c r="V40" s="21"/>
+      <c r="W40" s="21"/>
+      <c r="X40" s="21"/>
+      <c r="Y40" s="21"/>
+      <c r="Z40" s="21"/>
+      <c r="AA40" s="21"/>
+      <c r="AB40" s="21"/>
+      <c r="AC40" s="21"/>
+      <c r="AD40" s="21"/>
+      <c r="AE40" s="21"/>
+      <c r="AF40" s="21"/>
+      <c r="AG40" s="21"/>
+      <c r="AH40" s="21"/>
+      <c r="AI40" s="21"/>
+      <c r="AJ40" s="21"/>
+      <c r="AK40" s="21"/>
+      <c r="AL40" s="21"/>
+      <c r="AM40" s="21"/>
+      <c r="AN40" s="21"/>
+      <c r="AO40" s="21"/>
+      <c r="AP40" s="21"/>
+      <c r="AQ40" s="21"/>
+      <c r="AR40" s="21"/>
+      <c r="AS40" s="21"/>
+      <c r="AT40" s="21"/>
+      <c r="AU40" s="21"/>
+      <c r="AV40" s="21"/>
+      <c r="AW40" s="21"/>
+      <c r="AX40" s="21"/>
+      <c r="AY40" s="21"/>
+      <c r="AZ40" s="21"/>
+      <c r="BA40" s="21"/>
+      <c r="BB40" s="21"/>
+      <c r="BC40" s="21"/>
+      <c r="BD40" s="21"/>
+      <c r="BE40" s="21"/>
+      <c r="BF40" s="21"/>
+      <c r="BG40" s="21"/>
+      <c r="BH40" s="21"/>
+      <c r="BI40" s="21"/>
+      <c r="BJ40" s="21"/>
+      <c r="BK40" s="21"/>
+      <c r="BL40" s="21"/>
+      <c r="BM40" s="21"/>
     </row>
     <row r="41" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="19" t="n">
-        <v>180.43</v>
-      </c>
-      <c r="B41" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C41" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" s="19" t="n">
-        <v>50.33</v>
-      </c>
-      <c r="E41" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" s="19" t="n">
-        <v>0</v>
-      </c>
+      <c r="A41" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="K41" s="4"/>
+      <c r="L41" s="4"/>
+      <c r="M41" s="4"/>
+      <c r="N41" s="4"/>
+      <c r="O41" s="4"/>
+      <c r="P41" s="4"/>
+      <c r="Q41" s="4"/>
+      <c r="R41" s="4"/>
+      <c r="S41" s="4"/>
+      <c r="T41" s="4"/>
+      <c r="U41" s="4"/>
+      <c r="V41" s="4"/>
+      <c r="W41" s="4"/>
+      <c r="X41" s="4"/>
+      <c r="Y41" s="4"/>
+      <c r="Z41" s="4"/>
+      <c r="AA41" s="4"/>
+      <c r="AB41" s="4"/>
+      <c r="AC41" s="4"/>
+      <c r="AD41" s="4"/>
+      <c r="AE41" s="4"/>
+      <c r="AF41" s="4"/>
+      <c r="AG41" s="4"/>
+      <c r="AH41" s="4"/>
+      <c r="AI41" s="4"/>
+      <c r="AJ41" s="4"/>
+      <c r="AK41" s="4"/>
+      <c r="AL41" s="4"/>
+      <c r="AM41" s="4"/>
+      <c r="AN41" s="4"/>
+      <c r="AO41" s="4"/>
+      <c r="AP41" s="4"/>
+      <c r="AQ41" s="4"/>
+      <c r="AR41" s="4"/>
+      <c r="AS41" s="4"/>
+      <c r="AT41" s="4"/>
+      <c r="AU41" s="4"/>
+      <c r="AV41" s="4"/>
+      <c r="AW41" s="4"/>
+      <c r="AX41" s="4"/>
+      <c r="AY41" s="4"/>
+      <c r="AZ41" s="4"/>
+      <c r="BA41" s="4"/>
+      <c r="BB41" s="4"/>
+      <c r="BC41" s="4"/>
+      <c r="BD41" s="4"/>
+      <c r="BE41" s="4"/>
+      <c r="BF41" s="4"/>
+      <c r="BG41" s="4"/>
+      <c r="BH41" s="4"/>
+      <c r="BI41" s="4"/>
+      <c r="BJ41" s="4"/>
+      <c r="BK41" s="4"/>
+      <c r="BL41" s="4"/>
+      <c r="BM41" s="4"/>
     </row>
     <row r="42" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="4"/>
+      <c r="A42" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="B42" s="4"/>
+      <c r="C42" s="4"/>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4"/>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+      <c r="K42" s="4"/>
+      <c r="L42" s="4"/>
+      <c r="M42" s="4"/>
+      <c r="N42" s="4"/>
+      <c r="O42" s="4"/>
+      <c r="P42" s="4"/>
+      <c r="Q42" s="4"/>
+      <c r="R42" s="4"/>
+      <c r="S42" s="4"/>
+      <c r="T42" s="4"/>
+      <c r="U42" s="4"/>
+      <c r="V42" s="4"/>
+      <c r="W42" s="4"/>
+      <c r="X42" s="4"/>
+      <c r="Y42" s="4"/>
+      <c r="Z42" s="4"/>
+      <c r="AA42" s="4"/>
+      <c r="AB42" s="4"/>
+      <c r="AC42" s="4"/>
+      <c r="AD42" s="4"/>
+      <c r="AE42" s="4"/>
+      <c r="AF42" s="4"/>
+      <c r="AG42" s="4"/>
+      <c r="AH42" s="4"/>
+      <c r="AI42" s="4"/>
+      <c r="AJ42" s="4"/>
+      <c r="AK42" s="4"/>
+      <c r="AL42" s="4"/>
+      <c r="AM42" s="4"/>
+      <c r="AN42" s="4"/>
+      <c r="AO42" s="4"/>
+      <c r="AP42" s="4"/>
+      <c r="AQ42" s="4"/>
+      <c r="AR42" s="4"/>
+      <c r="AS42" s="4"/>
+      <c r="AT42" s="4"/>
+      <c r="AU42" s="4"/>
+      <c r="AV42" s="4"/>
+      <c r="AW42" s="4"/>
+      <c r="AX42" s="4"/>
+      <c r="AY42" s="4"/>
+      <c r="AZ42" s="4"/>
+      <c r="BA42" s="4"/>
+      <c r="BB42" s="4"/>
+      <c r="BC42" s="4"/>
+      <c r="BD42" s="4"/>
+      <c r="BE42" s="4"/>
+      <c r="BF42" s="4"/>
+      <c r="BG42" s="4"/>
+      <c r="BH42" s="4"/>
+      <c r="BI42" s="4"/>
+      <c r="BJ42" s="4"/>
+      <c r="BK42" s="4"/>
+      <c r="BL42" s="4"/>
+      <c r="BM42" s="4"/>
     </row>
-    <row r="43" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="21" t="s">
-        <v>214</v>
-      </c>
-      <c r="B43" s="21"/>
-      <c r="C43" s="21"/>
-      <c r="D43" s="21"/>
-      <c r="E43" s="21"/>
-      <c r="F43" s="21"/>
-      <c r="G43" s="21"/>
-      <c r="H43" s="21"/>
-      <c r="I43" s="21"/>
-      <c r="J43" s="21"/>
-      <c r="K43" s="21"/>
-      <c r="L43" s="21"/>
-      <c r="M43" s="21"/>
-      <c r="N43" s="21"/>
-      <c r="O43" s="21"/>
-      <c r="P43" s="21"/>
-      <c r="Q43" s="21"/>
-      <c r="R43" s="21"/>
-      <c r="S43" s="21"/>
-      <c r="T43" s="21"/>
-      <c r="U43" s="21"/>
-      <c r="V43" s="21"/>
-      <c r="W43" s="21"/>
-      <c r="X43" s="21"/>
-      <c r="Y43" s="21"/>
-      <c r="Z43" s="21"/>
-      <c r="AA43" s="21"/>
-      <c r="AB43" s="21"/>
-      <c r="AC43" s="21"/>
-      <c r="AD43" s="21"/>
-      <c r="AE43" s="21"/>
-      <c r="AF43" s="21"/>
-      <c r="AG43" s="21"/>
-      <c r="AH43" s="21"/>
-      <c r="AI43" s="21"/>
-      <c r="AJ43" s="21"/>
-      <c r="AK43" s="21"/>
-      <c r="AL43" s="21"/>
-      <c r="AM43" s="21"/>
-      <c r="AN43" s="21"/>
-      <c r="AO43" s="21"/>
-      <c r="AP43" s="21"/>
-      <c r="AQ43" s="21"/>
-      <c r="AR43" s="21"/>
-      <c r="AS43" s="21"/>
-      <c r="AT43" s="21"/>
-      <c r="AU43" s="21"/>
-      <c r="AV43" s="21"/>
-      <c r="AW43" s="21"/>
-      <c r="AX43" s="21"/>
-      <c r="AY43" s="21"/>
-      <c r="AZ43" s="21"/>
-      <c r="BA43" s="21"/>
-      <c r="BB43" s="21"/>
-      <c r="BC43" s="21"/>
-      <c r="BD43" s="21"/>
-      <c r="BE43" s="21"/>
-      <c r="BF43" s="21"/>
-      <c r="BG43" s="21"/>
-      <c r="BH43" s="21"/>
-      <c r="BI43" s="21"/>
-      <c r="BJ43" s="21"/>
-      <c r="BK43" s="21"/>
-      <c r="BL43" s="21"/>
-      <c r="BM43" s="21"/>
+    <row r="43" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="B43" s="4"/>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="K43" s="4"/>
+      <c r="L43" s="4"/>
+      <c r="M43" s="4"/>
+      <c r="N43" s="4"/>
+      <c r="O43" s="4"/>
+      <c r="P43" s="4"/>
+      <c r="Q43" s="4"/>
+      <c r="R43" s="4"/>
+      <c r="S43" s="4"/>
+      <c r="T43" s="4"/>
+      <c r="U43" s="4"/>
+      <c r="V43" s="4"/>
+      <c r="W43" s="4"/>
+      <c r="X43" s="4"/>
+      <c r="Y43" s="4"/>
+      <c r="Z43" s="4"/>
+      <c r="AA43" s="4"/>
+      <c r="AB43" s="4"/>
+      <c r="AC43" s="4"/>
+      <c r="AD43" s="4"/>
+      <c r="AE43" s="4"/>
+      <c r="AF43" s="4"/>
+      <c r="AG43" s="4"/>
+      <c r="AH43" s="4"/>
+      <c r="AI43" s="4"/>
+      <c r="AJ43" s="4"/>
+      <c r="AK43" s="4"/>
+      <c r="AL43" s="4"/>
+      <c r="AM43" s="4"/>
+      <c r="AN43" s="4"/>
+      <c r="AO43" s="4"/>
+      <c r="AP43" s="4"/>
+      <c r="AQ43" s="4"/>
+      <c r="AR43" s="4"/>
+      <c r="AS43" s="4"/>
+      <c r="AT43" s="4"/>
+      <c r="AU43" s="4"/>
+      <c r="AV43" s="4"/>
+      <c r="AW43" s="4"/>
+      <c r="AX43" s="4"/>
+      <c r="AY43" s="4"/>
+      <c r="AZ43" s="4"/>
+      <c r="BA43" s="4"/>
+      <c r="BB43" s="4"/>
+      <c r="BC43" s="4"/>
+      <c r="BD43" s="4"/>
+      <c r="BE43" s="4"/>
+      <c r="BF43" s="4"/>
+      <c r="BG43" s="4"/>
+      <c r="BH43" s="4"/>
+      <c r="BI43" s="4"/>
+      <c r="BJ43" s="4"/>
+      <c r="BK43" s="4"/>
+      <c r="BL43" s="4"/>
+      <c r="BM43" s="4"/>
     </row>
     <row r="44" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="s">
-        <v>74</v>
+        <v>202</v>
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
@@ -23558,7 +23147,7 @@
     </row>
     <row r="45" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="4" t="s">
-        <v>215</v>
+        <v>22</v>
       </c>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
@@ -23627,7 +23216,7 @@
     </row>
     <row r="46" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="4" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
@@ -23696,7 +23285,7 @@
     </row>
     <row r="47" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
@@ -23765,7 +23354,7 @@
     </row>
     <row r="48" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="4" t="s">
-        <v>22</v>
+        <v>205</v>
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
@@ -23834,7 +23423,7 @@
     </row>
     <row r="49" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="4" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
@@ -23903,7 +23492,7 @@
     </row>
     <row r="50" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="4" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
@@ -23970,215 +23559,8 @@
       <c r="BL50" s="4"/>
       <c r="BM50" s="4"/>
     </row>
-    <row r="51" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="B51" s="4"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="4"/>
-      <c r="E51" s="4"/>
-      <c r="F51" s="4"/>
-      <c r="G51" s="4"/>
-      <c r="H51" s="4"/>
-      <c r="I51" s="4"/>
-      <c r="J51" s="4"/>
-      <c r="K51" s="4"/>
-      <c r="L51" s="4"/>
-      <c r="M51" s="4"/>
-      <c r="N51" s="4"/>
-      <c r="O51" s="4"/>
-      <c r="P51" s="4"/>
-      <c r="Q51" s="4"/>
-      <c r="R51" s="4"/>
-      <c r="S51" s="4"/>
-      <c r="T51" s="4"/>
-      <c r="U51" s="4"/>
-      <c r="V51" s="4"/>
-      <c r="W51" s="4"/>
-      <c r="X51" s="4"/>
-      <c r="Y51" s="4"/>
-      <c r="Z51" s="4"/>
-      <c r="AA51" s="4"/>
-      <c r="AB51" s="4"/>
-      <c r="AC51" s="4"/>
-      <c r="AD51" s="4"/>
-      <c r="AE51" s="4"/>
-      <c r="AF51" s="4"/>
-      <c r="AG51" s="4"/>
-      <c r="AH51" s="4"/>
-      <c r="AI51" s="4"/>
-      <c r="AJ51" s="4"/>
-      <c r="AK51" s="4"/>
-      <c r="AL51" s="4"/>
-      <c r="AM51" s="4"/>
-      <c r="AN51" s="4"/>
-      <c r="AO51" s="4"/>
-      <c r="AP51" s="4"/>
-      <c r="AQ51" s="4"/>
-      <c r="AR51" s="4"/>
-      <c r="AS51" s="4"/>
-      <c r="AT51" s="4"/>
-      <c r="AU51" s="4"/>
-      <c r="AV51" s="4"/>
-      <c r="AW51" s="4"/>
-      <c r="AX51" s="4"/>
-      <c r="AY51" s="4"/>
-      <c r="AZ51" s="4"/>
-      <c r="BA51" s="4"/>
-      <c r="BB51" s="4"/>
-      <c r="BC51" s="4"/>
-      <c r="BD51" s="4"/>
-      <c r="BE51" s="4"/>
-      <c r="BF51" s="4"/>
-      <c r="BG51" s="4"/>
-      <c r="BH51" s="4"/>
-      <c r="BI51" s="4"/>
-      <c r="BJ51" s="4"/>
-      <c r="BK51" s="4"/>
-      <c r="BL51" s="4"/>
-      <c r="BM51" s="4"/>
-    </row>
-    <row r="52" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="B52" s="4"/>
-      <c r="C52" s="4"/>
-      <c r="D52" s="4"/>
-      <c r="E52" s="4"/>
-      <c r="F52" s="4"/>
-      <c r="G52" s="4"/>
-      <c r="H52" s="4"/>
-      <c r="I52" s="4"/>
-      <c r="J52" s="4"/>
-      <c r="K52" s="4"/>
-      <c r="L52" s="4"/>
-      <c r="M52" s="4"/>
-      <c r="N52" s="4"/>
-      <c r="O52" s="4"/>
-      <c r="P52" s="4"/>
-      <c r="Q52" s="4"/>
-      <c r="R52" s="4"/>
-      <c r="S52" s="4"/>
-      <c r="T52" s="4"/>
-      <c r="U52" s="4"/>
-      <c r="V52" s="4"/>
-      <c r="W52" s="4"/>
-      <c r="X52" s="4"/>
-      <c r="Y52" s="4"/>
-      <c r="Z52" s="4"/>
-      <c r="AA52" s="4"/>
-      <c r="AB52" s="4"/>
-      <c r="AC52" s="4"/>
-      <c r="AD52" s="4"/>
-      <c r="AE52" s="4"/>
-      <c r="AF52" s="4"/>
-      <c r="AG52" s="4"/>
-      <c r="AH52" s="4"/>
-      <c r="AI52" s="4"/>
-      <c r="AJ52" s="4"/>
-      <c r="AK52" s="4"/>
-      <c r="AL52" s="4"/>
-      <c r="AM52" s="4"/>
-      <c r="AN52" s="4"/>
-      <c r="AO52" s="4"/>
-      <c r="AP52" s="4"/>
-      <c r="AQ52" s="4"/>
-      <c r="AR52" s="4"/>
-      <c r="AS52" s="4"/>
-      <c r="AT52" s="4"/>
-      <c r="AU52" s="4"/>
-      <c r="AV52" s="4"/>
-      <c r="AW52" s="4"/>
-      <c r="AX52" s="4"/>
-      <c r="AY52" s="4"/>
-      <c r="AZ52" s="4"/>
-      <c r="BA52" s="4"/>
-      <c r="BB52" s="4"/>
-      <c r="BC52" s="4"/>
-      <c r="BD52" s="4"/>
-      <c r="BE52" s="4"/>
-      <c r="BF52" s="4"/>
-      <c r="BG52" s="4"/>
-      <c r="BH52" s="4"/>
-      <c r="BI52" s="4"/>
-      <c r="BJ52" s="4"/>
-      <c r="BK52" s="4"/>
-      <c r="BL52" s="4"/>
-      <c r="BM52" s="4"/>
-    </row>
-    <row r="53" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="B53" s="4"/>
-      <c r="C53" s="4"/>
-      <c r="D53" s="4"/>
-      <c r="E53" s="4"/>
-      <c r="F53" s="4"/>
-      <c r="G53" s="4"/>
-      <c r="H53" s="4"/>
-      <c r="I53" s="4"/>
-      <c r="J53" s="4"/>
-      <c r="K53" s="4"/>
-      <c r="L53" s="4"/>
-      <c r="M53" s="4"/>
-      <c r="N53" s="4"/>
-      <c r="O53" s="4"/>
-      <c r="P53" s="4"/>
-      <c r="Q53" s="4"/>
-      <c r="R53" s="4"/>
-      <c r="S53" s="4"/>
-      <c r="T53" s="4"/>
-      <c r="U53" s="4"/>
-      <c r="V53" s="4"/>
-      <c r="W53" s="4"/>
-      <c r="X53" s="4"/>
-      <c r="Y53" s="4"/>
-      <c r="Z53" s="4"/>
-      <c r="AA53" s="4"/>
-      <c r="AB53" s="4"/>
-      <c r="AC53" s="4"/>
-      <c r="AD53" s="4"/>
-      <c r="AE53" s="4"/>
-      <c r="AF53" s="4"/>
-      <c r="AG53" s="4"/>
-      <c r="AH53" s="4"/>
-      <c r="AI53" s="4"/>
-      <c r="AJ53" s="4"/>
-      <c r="AK53" s="4"/>
-      <c r="AL53" s="4"/>
-      <c r="AM53" s="4"/>
-      <c r="AN53" s="4"/>
-      <c r="AO53" s="4"/>
-      <c r="AP53" s="4"/>
-      <c r="AQ53" s="4"/>
-      <c r="AR53" s="4"/>
-      <c r="AS53" s="4"/>
-      <c r="AT53" s="4"/>
-      <c r="AU53" s="4"/>
-      <c r="AV53" s="4"/>
-      <c r="AW53" s="4"/>
-      <c r="AX53" s="4"/>
-      <c r="AY53" s="4"/>
-      <c r="AZ53" s="4"/>
-      <c r="BA53" s="4"/>
-      <c r="BB53" s="4"/>
-      <c r="BC53" s="4"/>
-      <c r="BD53" s="4"/>
-      <c r="BE53" s="4"/>
-      <c r="BF53" s="4"/>
-      <c r="BG53" s="4"/>
-      <c r="BH53" s="4"/>
-      <c r="BI53" s="4"/>
-      <c r="BJ53" s="4"/>
-      <c r="BK53" s="4"/>
-      <c r="BL53" s="4"/>
-      <c r="BM53" s="4"/>
-    </row>
   </sheetData>
-  <mergeCells count="47">
+  <mergeCells count="44">
     <mergeCell ref="A1:BI1"/>
     <mergeCell ref="BJ1:BM1"/>
     <mergeCell ref="A2:BM2"/>
@@ -24211,10 +23593,10 @@
     <mergeCell ref="B30:E30"/>
     <mergeCell ref="B31:E31"/>
     <mergeCell ref="B32:E32"/>
-    <mergeCell ref="B33:E33"/>
-    <mergeCell ref="B34:E34"/>
-    <mergeCell ref="B35:E35"/>
-    <mergeCell ref="A37:V37"/>
+    <mergeCell ref="A34:V34"/>
+    <mergeCell ref="A40:BM40"/>
+    <mergeCell ref="A41:BM41"/>
+    <mergeCell ref="A42:BM42"/>
     <mergeCell ref="A43:BM43"/>
     <mergeCell ref="A44:BM44"/>
     <mergeCell ref="A45:BM45"/>
@@ -24223,9 +23605,6 @@
     <mergeCell ref="A48:BM48"/>
     <mergeCell ref="A49:BM49"/>
     <mergeCell ref="A50:BM50"/>
-    <mergeCell ref="A51:BM51"/>
-    <mergeCell ref="A52:BM52"/>
-    <mergeCell ref="A53:BM53"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>

--- a/tratando_tabelas/finitura/entradas_finitura.xlsx
+++ b/tratando_tabelas/finitura/entradas_finitura.xlsx
@@ -20,12 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1232" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1352" uniqueCount="220">
   <si>
     <t xml:space="preserve">Santri ADM 1.1.5.7 R1</t>
   </si>
   <si>
-    <t xml:space="preserve">Emitido em: 14/05/2026 07:28:18</t>
+    <t xml:space="preserve">Emitido em: 15/05/2026 07:59:54</t>
   </si>
   <si>
     <t xml:space="preserve">Relação de entradas - Sintético</t>
@@ -587,6 +587,42 @@
   </si>
   <si>
     <t xml:space="preserve">42260510691158000370550010002929971371918584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">638.522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.402,37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006385221064002290</t>
+  </si>
+  <si>
+    <t xml:space="preserve">639.834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.494,11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006398341511429770</t>
+  </si>
+  <si>
+    <t xml:space="preserve">640.316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.360,01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006403161190056807</t>
   </si>
   <si>
     <t xml:space="preserve">Total geral</t>
@@ -16832,7 +16868,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BM50"/>
+  <dimension ref="A1:BM53"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="18"/>
@@ -22551,534 +22587,900 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="4"/>
+      <c r="A33" s="8" t="n">
+        <v>307294</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="G33" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="H33" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="I33" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="J33" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="K33" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="L33" s="12" t="n">
+        <v>4402.37</v>
+      </c>
+      <c r="M33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O33" s="12" t="n">
+        <v>4402.37</v>
+      </c>
+      <c r="P33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" s="12" t="n">
+        <v>8.3</v>
+      </c>
+      <c r="S33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="U33" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="V33" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="W33" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="X33" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="Y33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="12" t="n">
+        <v>4402.37</v>
+      </c>
+      <c r="AA33" s="12" t="n">
+        <v>308.17</v>
+      </c>
+      <c r="AB33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AI33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ33" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AK33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM33" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AN33" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AO33" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AP33" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AQ33" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR33" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AS33" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AT33" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AU33" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AV33" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AW33" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AX33" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="AY33" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AZ33" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BA33" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BB33" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BC33" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BD33" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BE33" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BF33" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="BG33" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="BH33" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BI33" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="BJ33" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="BK33" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="BL33" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="BM33" s="16" t="s">
+        <v>78</v>
+      </c>
     </row>
-    <row r="34" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="17" t="s">
-        <v>189</v>
-      </c>
-      <c r="B34" s="17"/>
-      <c r="C34" s="17"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="17"/>
-      <c r="G34" s="17"/>
-      <c r="H34" s="17"/>
-      <c r="I34" s="17"/>
-      <c r="J34" s="17"/>
-      <c r="K34" s="17"/>
-      <c r="L34" s="17"/>
-      <c r="M34" s="17"/>
-      <c r="N34" s="17"/>
-      <c r="O34" s="17"/>
-      <c r="P34" s="17"/>
-      <c r="Q34" s="17"/>
-      <c r="R34" s="17"/>
-      <c r="S34" s="17"/>
-      <c r="T34" s="17"/>
-      <c r="U34" s="17"/>
-      <c r="V34" s="17"/>
+    <row r="34" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="8" t="n">
+        <v>307332</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="G34" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="H34" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="I34" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="J34" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="K34" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="L34" s="12" t="n">
+        <v>1494.11</v>
+      </c>
+      <c r="M34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O34" s="12" t="n">
+        <v>1494.11</v>
+      </c>
+      <c r="P34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="13" t="n">
+        <v>0.002473</v>
+      </c>
+      <c r="R34" s="12" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="S34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="U34" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="V34" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="W34" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="X34" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="Y34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="12" t="n">
+        <v>1494.11</v>
+      </c>
+      <c r="AA34" s="12" t="n">
+        <v>104.59</v>
+      </c>
+      <c r="AB34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AI34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ34" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AK34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM34" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AN34" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AO34" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AP34" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AQ34" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR34" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AS34" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AT34" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AU34" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AV34" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AW34" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AX34" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="AY34" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AZ34" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BA34" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BB34" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BC34" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BD34" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BE34" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BF34" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="BG34" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="BH34" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BI34" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="BJ34" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="BK34" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="BL34" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="BM34" s="16" t="s">
+        <v>78</v>
+      </c>
     </row>
-    <row r="35" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="18" t="s">
+    <row r="35" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="8" t="n">
+        <v>307348</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="9"/>
+      <c r="F35" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="G35" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="H35" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="B35" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C35" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D35" s="18" t="s">
-        <v>191</v>
-      </c>
-      <c r="E35" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F35" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="G35" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="H35" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="I35" s="18" t="s">
-        <v>192</v>
-      </c>
-      <c r="J35" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="K35" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="L35" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="M35" s="18" t="s">
-        <v>193</v>
-      </c>
-      <c r="N35" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="O35" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="P35" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q35" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="R35" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="S35" s="18" t="s">
-        <v>194</v>
-      </c>
-      <c r="T35" s="18" t="s">
-        <v>195</v>
-      </c>
-      <c r="U35" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="V35" s="18" t="s">
-        <v>37</v>
+      <c r="I35" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="J35" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="K35" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="L35" s="12" t="n">
+        <v>1360.01</v>
+      </c>
+      <c r="M35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O35" s="12" t="n">
+        <v>1277</v>
+      </c>
+      <c r="P35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="13" t="n">
+        <v>0.013954</v>
+      </c>
+      <c r="R35" s="12" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="S35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="U35" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="V35" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="W35" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="X35" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="Y35" s="12" t="n">
+        <v>83.01</v>
+      </c>
+      <c r="Z35" s="12" t="n">
+        <v>1277</v>
+      </c>
+      <c r="AA35" s="12" t="n">
+        <v>89.39</v>
+      </c>
+      <c r="AB35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AI35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ35" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AK35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM35" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AN35" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AO35" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AP35" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AQ35" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR35" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AS35" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AT35" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AU35" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AV35" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AW35" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AX35" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="AY35" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AZ35" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BA35" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BB35" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BC35" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BD35" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BE35" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BF35" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="BG35" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="BH35" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BI35" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="BJ35" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="BK35" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="BL35" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="BM35" s="16" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="19" t="n">
-        <v>28</v>
-      </c>
-      <c r="B36" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C36" s="19" t="n">
-        <v>365</v>
-      </c>
-      <c r="D36" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" s="19" t="n">
-        <v>513.7</v>
-      </c>
-      <c r="F36" s="19" t="n">
-        <v>53720.21</v>
-      </c>
-      <c r="G36" s="19" t="n">
-        <v>3507.64</v>
-      </c>
-      <c r="H36" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" s="19" t="n">
-        <v>59611.8</v>
-      </c>
-      <c r="L36" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" s="20" t="n">
-        <v>0.188115</v>
-      </c>
-      <c r="S36" s="19" t="n">
-        <v>58733.1</v>
-      </c>
-      <c r="T36" s="19" t="n">
-        <v>59611.8</v>
-      </c>
-      <c r="U36" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" s="19" t="n">
-        <v>0</v>
-      </c>
+      <c r="A36" s="4"/>
     </row>
     <row r="37" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="B37" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C37" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="D37" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E37" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="F37" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="G37" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="H37" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="I37" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="J37" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="K37" s="18" t="s">
-        <v>196</v>
-      </c>
-      <c r="L37" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="M37" s="18" t="s">
-        <v>198</v>
-      </c>
+      <c r="A37" s="17" t="s">
+        <v>201</v>
+      </c>
+      <c r="B37" s="17"/>
+      <c r="C37" s="17"/>
+      <c r="D37" s="17"/>
+      <c r="E37" s="17"/>
+      <c r="F37" s="17"/>
+      <c r="G37" s="17"/>
+      <c r="H37" s="17"/>
+      <c r="I37" s="17"/>
+      <c r="J37" s="17"/>
+      <c r="K37" s="17"/>
+      <c r="L37" s="17"/>
+      <c r="M37" s="17"/>
+      <c r="N37" s="17"/>
+      <c r="O37" s="17"/>
+      <c r="P37" s="17"/>
+      <c r="Q37" s="17"/>
+      <c r="R37" s="17"/>
+      <c r="S37" s="17"/>
+      <c r="T37" s="17"/>
+      <c r="U37" s="17"/>
+      <c r="V37" s="17"/>
     </row>
-    <row r="38" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="19" t="n">
-        <v>196.8</v>
-      </c>
-      <c r="B38" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C38" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" s="19" t="n">
-        <v>31.41</v>
-      </c>
-      <c r="E38" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" s="19" t="n">
-        <v>0</v>
+    <row r="38" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="18" t="s">
+        <v>202</v>
+      </c>
+      <c r="B38" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C38" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D38" s="18" t="s">
+        <v>203</v>
+      </c>
+      <c r="E38" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F38" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="G38" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H38" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="I38" s="18" t="s">
+        <v>204</v>
+      </c>
+      <c r="J38" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="K38" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="L38" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="M38" s="18" t="s">
+        <v>205</v>
+      </c>
+      <c r="N38" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="O38" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="P38" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q38" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="R38" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="S38" s="18" t="s">
+        <v>206</v>
+      </c>
+      <c r="T38" s="18" t="s">
+        <v>207</v>
+      </c>
+      <c r="U38" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="V38" s="18" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="4"/>
+      <c r="A39" s="19" t="n">
+        <v>31</v>
+      </c>
+      <c r="B39" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="19" t="n">
+        <v>365</v>
+      </c>
+      <c r="D39" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="19" t="n">
+        <v>596.71</v>
+      </c>
+      <c r="F39" s="19" t="n">
+        <v>60893.69</v>
+      </c>
+      <c r="G39" s="19" t="n">
+        <v>4009.79</v>
+      </c>
+      <c r="H39" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" s="19" t="n">
+        <v>66868.29</v>
+      </c>
+      <c r="L39" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" s="20" t="n">
+        <v>0.204542</v>
+      </c>
+      <c r="S39" s="19" t="n">
+        <v>65906.58</v>
+      </c>
+      <c r="T39" s="19" t="n">
+        <v>66868.29</v>
+      </c>
+      <c r="U39" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="21" t="s">
-        <v>199</v>
-      </c>
-      <c r="B40" s="21"/>
-      <c r="C40" s="21"/>
-      <c r="D40" s="21"/>
-      <c r="E40" s="21"/>
-      <c r="F40" s="21"/>
-      <c r="G40" s="21"/>
-      <c r="H40" s="21"/>
-      <c r="I40" s="21"/>
-      <c r="J40" s="21"/>
-      <c r="K40" s="21"/>
-      <c r="L40" s="21"/>
-      <c r="M40" s="21"/>
-      <c r="N40" s="21"/>
-      <c r="O40" s="21"/>
-      <c r="P40" s="21"/>
-      <c r="Q40" s="21"/>
-      <c r="R40" s="21"/>
-      <c r="S40" s="21"/>
-      <c r="T40" s="21"/>
-      <c r="U40" s="21"/>
-      <c r="V40" s="21"/>
-      <c r="W40" s="21"/>
-      <c r="X40" s="21"/>
-      <c r="Y40" s="21"/>
-      <c r="Z40" s="21"/>
-      <c r="AA40" s="21"/>
-      <c r="AB40" s="21"/>
-      <c r="AC40" s="21"/>
-      <c r="AD40" s="21"/>
-      <c r="AE40" s="21"/>
-      <c r="AF40" s="21"/>
-      <c r="AG40" s="21"/>
-      <c r="AH40" s="21"/>
-      <c r="AI40" s="21"/>
-      <c r="AJ40" s="21"/>
-      <c r="AK40" s="21"/>
-      <c r="AL40" s="21"/>
-      <c r="AM40" s="21"/>
-      <c r="AN40" s="21"/>
-      <c r="AO40" s="21"/>
-      <c r="AP40" s="21"/>
-      <c r="AQ40" s="21"/>
-      <c r="AR40" s="21"/>
-      <c r="AS40" s="21"/>
-      <c r="AT40" s="21"/>
-      <c r="AU40" s="21"/>
-      <c r="AV40" s="21"/>
-      <c r="AW40" s="21"/>
-      <c r="AX40" s="21"/>
-      <c r="AY40" s="21"/>
-      <c r="AZ40" s="21"/>
-      <c r="BA40" s="21"/>
-      <c r="BB40" s="21"/>
-      <c r="BC40" s="21"/>
-      <c r="BD40" s="21"/>
-      <c r="BE40" s="21"/>
-      <c r="BF40" s="21"/>
-      <c r="BG40" s="21"/>
-      <c r="BH40" s="21"/>
-      <c r="BI40" s="21"/>
-      <c r="BJ40" s="21"/>
-      <c r="BK40" s="21"/>
-      <c r="BL40" s="21"/>
-      <c r="BM40" s="21"/>
+      <c r="A40" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B40" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C40" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D40" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="E40" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="F40" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="G40" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="H40" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="I40" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="J40" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="K40" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="L40" s="18" t="s">
+        <v>209</v>
+      </c>
+      <c r="M40" s="18" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="B41" s="4"/>
-      <c r="C41" s="4"/>
-      <c r="D41" s="4"/>
-      <c r="E41" s="4"/>
-      <c r="F41" s="4"/>
-      <c r="G41" s="4"/>
-      <c r="H41" s="4"/>
-      <c r="I41" s="4"/>
-      <c r="J41" s="4"/>
-      <c r="K41" s="4"/>
-      <c r="L41" s="4"/>
-      <c r="M41" s="4"/>
-      <c r="N41" s="4"/>
-      <c r="O41" s="4"/>
-      <c r="P41" s="4"/>
-      <c r="Q41" s="4"/>
-      <c r="R41" s="4"/>
-      <c r="S41" s="4"/>
-      <c r="T41" s="4"/>
-      <c r="U41" s="4"/>
-      <c r="V41" s="4"/>
-      <c r="W41" s="4"/>
-      <c r="X41" s="4"/>
-      <c r="Y41" s="4"/>
-      <c r="Z41" s="4"/>
-      <c r="AA41" s="4"/>
-      <c r="AB41" s="4"/>
-      <c r="AC41" s="4"/>
-      <c r="AD41" s="4"/>
-      <c r="AE41" s="4"/>
-      <c r="AF41" s="4"/>
-      <c r="AG41" s="4"/>
-      <c r="AH41" s="4"/>
-      <c r="AI41" s="4"/>
-      <c r="AJ41" s="4"/>
-      <c r="AK41" s="4"/>
-      <c r="AL41" s="4"/>
-      <c r="AM41" s="4"/>
-      <c r="AN41" s="4"/>
-      <c r="AO41" s="4"/>
-      <c r="AP41" s="4"/>
-      <c r="AQ41" s="4"/>
-      <c r="AR41" s="4"/>
-      <c r="AS41" s="4"/>
-      <c r="AT41" s="4"/>
-      <c r="AU41" s="4"/>
-      <c r="AV41" s="4"/>
-      <c r="AW41" s="4"/>
-      <c r="AX41" s="4"/>
-      <c r="AY41" s="4"/>
-      <c r="AZ41" s="4"/>
-      <c r="BA41" s="4"/>
-      <c r="BB41" s="4"/>
-      <c r="BC41" s="4"/>
-      <c r="BD41" s="4"/>
-      <c r="BE41" s="4"/>
-      <c r="BF41" s="4"/>
-      <c r="BG41" s="4"/>
-      <c r="BH41" s="4"/>
-      <c r="BI41" s="4"/>
-      <c r="BJ41" s="4"/>
-      <c r="BK41" s="4"/>
-      <c r="BL41" s="4"/>
-      <c r="BM41" s="4"/>
+      <c r="A41" s="19" t="n">
+        <v>207.64</v>
+      </c>
+      <c r="B41" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="19" t="n">
+        <v>31.04</v>
+      </c>
+      <c r="E41" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="B42" s="4"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="4"/>
-      <c r="E42" s="4"/>
-      <c r="F42" s="4"/>
-      <c r="G42" s="4"/>
-      <c r="H42" s="4"/>
-      <c r="I42" s="4"/>
-      <c r="J42" s="4"/>
-      <c r="K42" s="4"/>
-      <c r="L42" s="4"/>
-      <c r="M42" s="4"/>
-      <c r="N42" s="4"/>
-      <c r="O42" s="4"/>
-      <c r="P42" s="4"/>
-      <c r="Q42" s="4"/>
-      <c r="R42" s="4"/>
-      <c r="S42" s="4"/>
-      <c r="T42" s="4"/>
-      <c r="U42" s="4"/>
-      <c r="V42" s="4"/>
-      <c r="W42" s="4"/>
-      <c r="X42" s="4"/>
-      <c r="Y42" s="4"/>
-      <c r="Z42" s="4"/>
-      <c r="AA42" s="4"/>
-      <c r="AB42" s="4"/>
-      <c r="AC42" s="4"/>
-      <c r="AD42" s="4"/>
-      <c r="AE42" s="4"/>
-      <c r="AF42" s="4"/>
-      <c r="AG42" s="4"/>
-      <c r="AH42" s="4"/>
-      <c r="AI42" s="4"/>
-      <c r="AJ42" s="4"/>
-      <c r="AK42" s="4"/>
-      <c r="AL42" s="4"/>
-      <c r="AM42" s="4"/>
-      <c r="AN42" s="4"/>
-      <c r="AO42" s="4"/>
-      <c r="AP42" s="4"/>
-      <c r="AQ42" s="4"/>
-      <c r="AR42" s="4"/>
-      <c r="AS42" s="4"/>
-      <c r="AT42" s="4"/>
-      <c r="AU42" s="4"/>
-      <c r="AV42" s="4"/>
-      <c r="AW42" s="4"/>
-      <c r="AX42" s="4"/>
-      <c r="AY42" s="4"/>
-      <c r="AZ42" s="4"/>
-      <c r="BA42" s="4"/>
-      <c r="BB42" s="4"/>
-      <c r="BC42" s="4"/>
-      <c r="BD42" s="4"/>
-      <c r="BE42" s="4"/>
-      <c r="BF42" s="4"/>
-      <c r="BG42" s="4"/>
-      <c r="BH42" s="4"/>
-      <c r="BI42" s="4"/>
-      <c r="BJ42" s="4"/>
-      <c r="BK42" s="4"/>
-      <c r="BL42" s="4"/>
-      <c r="BM42" s="4"/>
+      <c r="A42" s="4"/>
     </row>
-    <row r="43" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="B43" s="4"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="4"/>
-      <c r="E43" s="4"/>
-      <c r="F43" s="4"/>
-      <c r="G43" s="4"/>
-      <c r="H43" s="4"/>
-      <c r="I43" s="4"/>
-      <c r="J43" s="4"/>
-      <c r="K43" s="4"/>
-      <c r="L43" s="4"/>
-      <c r="M43" s="4"/>
-      <c r="N43" s="4"/>
-      <c r="O43" s="4"/>
-      <c r="P43" s="4"/>
-      <c r="Q43" s="4"/>
-      <c r="R43" s="4"/>
-      <c r="S43" s="4"/>
-      <c r="T43" s="4"/>
-      <c r="U43" s="4"/>
-      <c r="V43" s="4"/>
-      <c r="W43" s="4"/>
-      <c r="X43" s="4"/>
-      <c r="Y43" s="4"/>
-      <c r="Z43" s="4"/>
-      <c r="AA43" s="4"/>
-      <c r="AB43" s="4"/>
-      <c r="AC43" s="4"/>
-      <c r="AD43" s="4"/>
-      <c r="AE43" s="4"/>
-      <c r="AF43" s="4"/>
-      <c r="AG43" s="4"/>
-      <c r="AH43" s="4"/>
-      <c r="AI43" s="4"/>
-      <c r="AJ43" s="4"/>
-      <c r="AK43" s="4"/>
-      <c r="AL43" s="4"/>
-      <c r="AM43" s="4"/>
-      <c r="AN43" s="4"/>
-      <c r="AO43" s="4"/>
-      <c r="AP43" s="4"/>
-      <c r="AQ43" s="4"/>
-      <c r="AR43" s="4"/>
-      <c r="AS43" s="4"/>
-      <c r="AT43" s="4"/>
-      <c r="AU43" s="4"/>
-      <c r="AV43" s="4"/>
-      <c r="AW43" s="4"/>
-      <c r="AX43" s="4"/>
-      <c r="AY43" s="4"/>
-      <c r="AZ43" s="4"/>
-      <c r="BA43" s="4"/>
-      <c r="BB43" s="4"/>
-      <c r="BC43" s="4"/>
-      <c r="BD43" s="4"/>
-      <c r="BE43" s="4"/>
-      <c r="BF43" s="4"/>
-      <c r="BG43" s="4"/>
-      <c r="BH43" s="4"/>
-      <c r="BI43" s="4"/>
-      <c r="BJ43" s="4"/>
-      <c r="BK43" s="4"/>
-      <c r="BL43" s="4"/>
-      <c r="BM43" s="4"/>
+    <row r="43" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="21" t="s">
+        <v>211</v>
+      </c>
+      <c r="B43" s="21"/>
+      <c r="C43" s="21"/>
+      <c r="D43" s="21"/>
+      <c r="E43" s="21"/>
+      <c r="F43" s="21"/>
+      <c r="G43" s="21"/>
+      <c r="H43" s="21"/>
+      <c r="I43" s="21"/>
+      <c r="J43" s="21"/>
+      <c r="K43" s="21"/>
+      <c r="L43" s="21"/>
+      <c r="M43" s="21"/>
+      <c r="N43" s="21"/>
+      <c r="O43" s="21"/>
+      <c r="P43" s="21"/>
+      <c r="Q43" s="21"/>
+      <c r="R43" s="21"/>
+      <c r="S43" s="21"/>
+      <c r="T43" s="21"/>
+      <c r="U43" s="21"/>
+      <c r="V43" s="21"/>
+      <c r="W43" s="21"/>
+      <c r="X43" s="21"/>
+      <c r="Y43" s="21"/>
+      <c r="Z43" s="21"/>
+      <c r="AA43" s="21"/>
+      <c r="AB43" s="21"/>
+      <c r="AC43" s="21"/>
+      <c r="AD43" s="21"/>
+      <c r="AE43" s="21"/>
+      <c r="AF43" s="21"/>
+      <c r="AG43" s="21"/>
+      <c r="AH43" s="21"/>
+      <c r="AI43" s="21"/>
+      <c r="AJ43" s="21"/>
+      <c r="AK43" s="21"/>
+      <c r="AL43" s="21"/>
+      <c r="AM43" s="21"/>
+      <c r="AN43" s="21"/>
+      <c r="AO43" s="21"/>
+      <c r="AP43" s="21"/>
+      <c r="AQ43" s="21"/>
+      <c r="AR43" s="21"/>
+      <c r="AS43" s="21"/>
+      <c r="AT43" s="21"/>
+      <c r="AU43" s="21"/>
+      <c r="AV43" s="21"/>
+      <c r="AW43" s="21"/>
+      <c r="AX43" s="21"/>
+      <c r="AY43" s="21"/>
+      <c r="AZ43" s="21"/>
+      <c r="BA43" s="21"/>
+      <c r="BB43" s="21"/>
+      <c r="BC43" s="21"/>
+      <c r="BD43" s="21"/>
+      <c r="BE43" s="21"/>
+      <c r="BF43" s="21"/>
+      <c r="BG43" s="21"/>
+      <c r="BH43" s="21"/>
+      <c r="BI43" s="21"/>
+      <c r="BJ43" s="21"/>
+      <c r="BK43" s="21"/>
+      <c r="BL43" s="21"/>
+      <c r="BM43" s="21"/>
     </row>
     <row r="44" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="s">
-        <v>202</v>
+        <v>74</v>
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
@@ -23147,7 +23549,7 @@
     </row>
     <row r="45" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="4" t="s">
-        <v>22</v>
+        <v>212</v>
       </c>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
@@ -23216,7 +23618,7 @@
     </row>
     <row r="46" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="4" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
@@ -23285,7 +23687,7 @@
     </row>
     <row r="47" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
@@ -23354,7 +23756,7 @@
     </row>
     <row r="48" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="4" t="s">
-        <v>205</v>
+        <v>22</v>
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
@@ -23423,7 +23825,7 @@
     </row>
     <row r="49" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="4" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
@@ -23492,7 +23894,7 @@
     </row>
     <row r="50" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="4" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
@@ -23559,8 +23961,215 @@
       <c r="BL50" s="4"/>
       <c r="BM50" s="4"/>
     </row>
+    <row r="51" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="B51" s="4"/>
+      <c r="C51" s="4"/>
+      <c r="D51" s="4"/>
+      <c r="E51" s="4"/>
+      <c r="F51" s="4"/>
+      <c r="G51" s="4"/>
+      <c r="H51" s="4"/>
+      <c r="I51" s="4"/>
+      <c r="J51" s="4"/>
+      <c r="K51" s="4"/>
+      <c r="L51" s="4"/>
+      <c r="M51" s="4"/>
+      <c r="N51" s="4"/>
+      <c r="O51" s="4"/>
+      <c r="P51" s="4"/>
+      <c r="Q51" s="4"/>
+      <c r="R51" s="4"/>
+      <c r="S51" s="4"/>
+      <c r="T51" s="4"/>
+      <c r="U51" s="4"/>
+      <c r="V51" s="4"/>
+      <c r="W51" s="4"/>
+      <c r="X51" s="4"/>
+      <c r="Y51" s="4"/>
+      <c r="Z51" s="4"/>
+      <c r="AA51" s="4"/>
+      <c r="AB51" s="4"/>
+      <c r="AC51" s="4"/>
+      <c r="AD51" s="4"/>
+      <c r="AE51" s="4"/>
+      <c r="AF51" s="4"/>
+      <c r="AG51" s="4"/>
+      <c r="AH51" s="4"/>
+      <c r="AI51" s="4"/>
+      <c r="AJ51" s="4"/>
+      <c r="AK51" s="4"/>
+      <c r="AL51" s="4"/>
+      <c r="AM51" s="4"/>
+      <c r="AN51" s="4"/>
+      <c r="AO51" s="4"/>
+      <c r="AP51" s="4"/>
+      <c r="AQ51" s="4"/>
+      <c r="AR51" s="4"/>
+      <c r="AS51" s="4"/>
+      <c r="AT51" s="4"/>
+      <c r="AU51" s="4"/>
+      <c r="AV51" s="4"/>
+      <c r="AW51" s="4"/>
+      <c r="AX51" s="4"/>
+      <c r="AY51" s="4"/>
+      <c r="AZ51" s="4"/>
+      <c r="BA51" s="4"/>
+      <c r="BB51" s="4"/>
+      <c r="BC51" s="4"/>
+      <c r="BD51" s="4"/>
+      <c r="BE51" s="4"/>
+      <c r="BF51" s="4"/>
+      <c r="BG51" s="4"/>
+      <c r="BH51" s="4"/>
+      <c r="BI51" s="4"/>
+      <c r="BJ51" s="4"/>
+      <c r="BK51" s="4"/>
+      <c r="BL51" s="4"/>
+      <c r="BM51" s="4"/>
+    </row>
+    <row r="52" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="B52" s="4"/>
+      <c r="C52" s="4"/>
+      <c r="D52" s="4"/>
+      <c r="E52" s="4"/>
+      <c r="F52" s="4"/>
+      <c r="G52" s="4"/>
+      <c r="H52" s="4"/>
+      <c r="I52" s="4"/>
+      <c r="J52" s="4"/>
+      <c r="K52" s="4"/>
+      <c r="L52" s="4"/>
+      <c r="M52" s="4"/>
+      <c r="N52" s="4"/>
+      <c r="O52" s="4"/>
+      <c r="P52" s="4"/>
+      <c r="Q52" s="4"/>
+      <c r="R52" s="4"/>
+      <c r="S52" s="4"/>
+      <c r="T52" s="4"/>
+      <c r="U52" s="4"/>
+      <c r="V52" s="4"/>
+      <c r="W52" s="4"/>
+      <c r="X52" s="4"/>
+      <c r="Y52" s="4"/>
+      <c r="Z52" s="4"/>
+      <c r="AA52" s="4"/>
+      <c r="AB52" s="4"/>
+      <c r="AC52" s="4"/>
+      <c r="AD52" s="4"/>
+      <c r="AE52" s="4"/>
+      <c r="AF52" s="4"/>
+      <c r="AG52" s="4"/>
+      <c r="AH52" s="4"/>
+      <c r="AI52" s="4"/>
+      <c r="AJ52" s="4"/>
+      <c r="AK52" s="4"/>
+      <c r="AL52" s="4"/>
+      <c r="AM52" s="4"/>
+      <c r="AN52" s="4"/>
+      <c r="AO52" s="4"/>
+      <c r="AP52" s="4"/>
+      <c r="AQ52" s="4"/>
+      <c r="AR52" s="4"/>
+      <c r="AS52" s="4"/>
+      <c r="AT52" s="4"/>
+      <c r="AU52" s="4"/>
+      <c r="AV52" s="4"/>
+      <c r="AW52" s="4"/>
+      <c r="AX52" s="4"/>
+      <c r="AY52" s="4"/>
+      <c r="AZ52" s="4"/>
+      <c r="BA52" s="4"/>
+      <c r="BB52" s="4"/>
+      <c r="BC52" s="4"/>
+      <c r="BD52" s="4"/>
+      <c r="BE52" s="4"/>
+      <c r="BF52" s="4"/>
+      <c r="BG52" s="4"/>
+      <c r="BH52" s="4"/>
+      <c r="BI52" s="4"/>
+      <c r="BJ52" s="4"/>
+      <c r="BK52" s="4"/>
+      <c r="BL52" s="4"/>
+      <c r="BM52" s="4"/>
+    </row>
+    <row r="53" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="B53" s="4"/>
+      <c r="C53" s="4"/>
+      <c r="D53" s="4"/>
+      <c r="E53" s="4"/>
+      <c r="F53" s="4"/>
+      <c r="G53" s="4"/>
+      <c r="H53" s="4"/>
+      <c r="I53" s="4"/>
+      <c r="J53" s="4"/>
+      <c r="K53" s="4"/>
+      <c r="L53" s="4"/>
+      <c r="M53" s="4"/>
+      <c r="N53" s="4"/>
+      <c r="O53" s="4"/>
+      <c r="P53" s="4"/>
+      <c r="Q53" s="4"/>
+      <c r="R53" s="4"/>
+      <c r="S53" s="4"/>
+      <c r="T53" s="4"/>
+      <c r="U53" s="4"/>
+      <c r="V53" s="4"/>
+      <c r="W53" s="4"/>
+      <c r="X53" s="4"/>
+      <c r="Y53" s="4"/>
+      <c r="Z53" s="4"/>
+      <c r="AA53" s="4"/>
+      <c r="AB53" s="4"/>
+      <c r="AC53" s="4"/>
+      <c r="AD53" s="4"/>
+      <c r="AE53" s="4"/>
+      <c r="AF53" s="4"/>
+      <c r="AG53" s="4"/>
+      <c r="AH53" s="4"/>
+      <c r="AI53" s="4"/>
+      <c r="AJ53" s="4"/>
+      <c r="AK53" s="4"/>
+      <c r="AL53" s="4"/>
+      <c r="AM53" s="4"/>
+      <c r="AN53" s="4"/>
+      <c r="AO53" s="4"/>
+      <c r="AP53" s="4"/>
+      <c r="AQ53" s="4"/>
+      <c r="AR53" s="4"/>
+      <c r="AS53" s="4"/>
+      <c r="AT53" s="4"/>
+      <c r="AU53" s="4"/>
+      <c r="AV53" s="4"/>
+      <c r="AW53" s="4"/>
+      <c r="AX53" s="4"/>
+      <c r="AY53" s="4"/>
+      <c r="AZ53" s="4"/>
+      <c r="BA53" s="4"/>
+      <c r="BB53" s="4"/>
+      <c r="BC53" s="4"/>
+      <c r="BD53" s="4"/>
+      <c r="BE53" s="4"/>
+      <c r="BF53" s="4"/>
+      <c r="BG53" s="4"/>
+      <c r="BH53" s="4"/>
+      <c r="BI53" s="4"/>
+      <c r="BJ53" s="4"/>
+      <c r="BK53" s="4"/>
+      <c r="BL53" s="4"/>
+      <c r="BM53" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="44">
+  <mergeCells count="47">
     <mergeCell ref="A1:BI1"/>
     <mergeCell ref="BJ1:BM1"/>
     <mergeCell ref="A2:BM2"/>
@@ -23593,10 +24202,10 @@
     <mergeCell ref="B30:E30"/>
     <mergeCell ref="B31:E31"/>
     <mergeCell ref="B32:E32"/>
-    <mergeCell ref="A34:V34"/>
-    <mergeCell ref="A40:BM40"/>
-    <mergeCell ref="A41:BM41"/>
-    <mergeCell ref="A42:BM42"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="B34:E34"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="A37:V37"/>
     <mergeCell ref="A43:BM43"/>
     <mergeCell ref="A44:BM44"/>
     <mergeCell ref="A45:BM45"/>
@@ -23605,6 +24214,9 @@
     <mergeCell ref="A48:BM48"/>
     <mergeCell ref="A49:BM49"/>
     <mergeCell ref="A50:BM50"/>
+    <mergeCell ref="A51:BM51"/>
+    <mergeCell ref="A52:BM52"/>
+    <mergeCell ref="A53:BM53"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>

--- a/tratando_tabelas/finitura/entradas_finitura.xlsx
+++ b/tratando_tabelas/finitura/entradas_finitura.xlsx
@@ -20,12 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1352" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1112" uniqueCount="199">
   <si>
     <t xml:space="preserve">Santri ADM 1.1.5.7 R1</t>
   </si>
   <si>
-    <t xml:space="preserve">Emitido em: 15/05/2026 07:59:54</t>
+    <t xml:space="preserve">Emitido em: 18/05/2026 07:30:58</t>
   </si>
   <si>
     <t xml:space="preserve">Relação de entradas - Sintético</t>
@@ -214,25 +214,28 @@
     <t xml:space="preserve">Fornecedor substituto tributário</t>
   </si>
   <si>
-    <t xml:space="preserve">1.856 - DEXCO S.A - METAIS</t>
+    <t xml:space="preserve">13.419 - METALDOMADO METALURGICA LTDA</t>
   </si>
   <si>
-    <t xml:space="preserve">5.071.473</t>
+    <t xml:space="preserve">27.418</t>
   </si>
   <si>
     <t xml:space="preserve">1</t>
   </si>
   <si>
-    <t xml:space="preserve">27/04/2026</t>
+    <t xml:space="preserve">28/04/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">          </t>
+    <t xml:space="preserve">04/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06/05/2026</t>
   </si>
   <si>
     <t xml:space="preserve">XML</t>
   </si>
   <si>
-    <t xml:space="preserve">290,09</t>
+    <t xml:space="preserve">3.167,76</t>
   </si>
   <si>
     <t xml:space="preserve">Ag. chegada da mercadoria</t>
@@ -250,73 +253,25 @@
     <t xml:space="preserve">N</t>
   </si>
   <si>
-    <t xml:space="preserve">2.949</t>
+    <t xml:space="preserve">2.102</t>
   </si>
   <si>
-    <t xml:space="preserve">35260497837181002190550010050714731527694305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Não</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.419 - METALDOMADO METALURGICA LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.167,76</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.102</t>
+    <t xml:space="preserve">          </t>
   </si>
   <si>
     <t xml:space="preserve">35260400516639000124550010000274181095610391</t>
   </si>
   <si>
-    <t xml:space="preserve">5.075.259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.108,72</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050752591800655701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">761 - DOCOL FV IND.E COM. DE METAIS SANITARIOS LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">630.877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.876,80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260475339051000141550080006308771523531623</t>
+    <t xml:space="preserve">Não</t>
   </si>
   <si>
     <t xml:space="preserve">547 - LORENZETTI S/A INDU.BRASILEIRAS ELETROMETALURGICAS</t>
   </si>
   <si>
     <t xml:space="preserve">2.972.380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30/04/2026</t>
   </si>
   <si>
     <t xml:space="preserve">5.384,20</t>
@@ -328,40 +283,22 @@
     <t xml:space="preserve">35260461413282000143550010029723801722131595</t>
   </si>
   <si>
-    <t xml:space="preserve">632.793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.116,85</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260575339051000141550080006327931688529359</t>
-  </si>
-  <si>
     <t xml:space="preserve">30.850 - DEXCO S.A</t>
   </si>
   <si>
     <t xml:space="preserve">161.164</t>
   </si>
   <si>
+    <t xml:space="preserve">05/05/2026</t>
+  </si>
+  <si>
     <t xml:space="preserve">976,79</t>
   </si>
   <si>
-    <t xml:space="preserve">42260497837181005378550010001611641514144027</t>
+    <t xml:space="preserve">2.949</t>
   </si>
   <si>
-    <t xml:space="preserve">632.423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">846,74</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260575339051000141550080006324231892898250</t>
+    <t xml:space="preserve">42260497837181005378550010001611641514144027</t>
   </si>
   <si>
     <t xml:space="preserve">25.941 - AQUECE METAIS FABRICACAO E MANUTENCAO LTDA</t>
@@ -520,22 +457,13 @@
     <t xml:space="preserve">43260586895448000136550010000649101026177588</t>
   </si>
   <si>
-    <t xml:space="preserve">9.134 - L.MARTINKOSKI &amp; CIA LTDA</t>
+    <t xml:space="preserve">1.856 - DEXCO S.A - METAIS</t>
   </si>
   <si>
-    <t xml:space="preserve">56.431</t>
+    <t xml:space="preserve">5.080.413</t>
   </si>
   <si>
     <t xml:space="preserve">12/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.188,23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41260508028676000103550010000564311004435113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.080.413</t>
   </si>
   <si>
     <t xml:space="preserve">404,81</t>
@@ -565,7 +493,13 @@
     <t xml:space="preserve">35260597837181002190550010050829951181500130</t>
   </si>
   <si>
+    <t xml:space="preserve">761 - DOCOL FV IND.E COM. DE METAIS SANITARIOS LTDA</t>
+  </si>
+  <si>
     <t xml:space="preserve">638.818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8</t>
   </si>
   <si>
     <t xml:space="preserve">09/06/2026</t>
@@ -584,6 +518,9 @@
   </si>
   <si>
     <t xml:space="preserve">497,70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S</t>
   </si>
   <si>
     <t xml:space="preserve">42260510691158000370550010002929971371918584</t>
@@ -16868,7 +16805,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BM53"/>
+  <dimension ref="A1:BM47"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="18"/>
@@ -17240,7 +17177,7 @@
     </row>
     <row r="5" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="n">
-        <v>305966</v>
+        <v>306454</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>64</v>
@@ -17258,61 +17195,61 @@
         <v>67</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J5" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="K5" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L5" s="12" t="n">
+        <v>3167.76</v>
+      </c>
+      <c r="M5" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="O5" s="12" t="n">
+        <v>3167.76</v>
+      </c>
+      <c r="P5" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="U5" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V5" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="W5" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X5" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="K5" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="L5" s="12" t="n">
-        <v>290.09</v>
-      </c>
-      <c r="M5" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="O5" s="12" t="n">
-        <v>272.38</v>
-      </c>
-      <c r="P5" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="13" t="n">
-        <v>0.003202</v>
-      </c>
-      <c r="R5" s="12" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="S5" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="U5" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="V5" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="X5" s="9" t="s">
-        <v>67</v>
-      </c>
       <c r="Y5" s="12" t="n">
-        <v>17.71</v>
+        <v>0</v>
       </c>
       <c r="Z5" s="12" t="n">
-        <v>272.38</v>
+        <v>3167.76</v>
       </c>
       <c r="AA5" s="12" t="n">
-        <v>10.89</v>
+        <v>117.52</v>
       </c>
       <c r="AB5" s="12" t="n">
         <v>0</v>
@@ -17333,13 +17270,13 @@
         <v>0</v>
       </c>
       <c r="AH5" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI5" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AJ5" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AK5" s="12" t="n">
         <v>0</v>
@@ -17348,135 +17285,135 @@
         <v>0</v>
       </c>
       <c r="AM5" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AN5" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AO5" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AP5" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AQ5" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AR5" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AS5" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AT5" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AU5" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AV5" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AW5" s="14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AX5" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AY5" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AZ5" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BA5" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BB5" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BC5" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BD5" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BE5" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BF5" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BG5" s="9" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="BH5" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BI5" s="9" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="BJ5" s="9" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="BK5" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BL5" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BM5" s="16" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="n">
-        <v>306454</v>
+        <v>306535</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
       <c r="E6" s="9"/>
       <c r="F6" s="9" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G6" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L6" s="12" t="n">
-        <v>3167.76</v>
+        <v>5384.2</v>
       </c>
       <c r="M6" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N6" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O6" s="12" t="n">
-        <v>3167.76</v>
+        <v>5384.2</v>
       </c>
       <c r="P6" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q6" s="13" t="n">
-        <v>0</v>
+        <v>0.023054</v>
       </c>
       <c r="R6" s="12" t="n">
-        <v>0</v>
+        <v>28.62</v>
       </c>
       <c r="S6" s="12" t="n">
         <v>0</v>
@@ -17485,25 +17422,25 @@
         <v>84</v>
       </c>
       <c r="U6" s="15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V6" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W6" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X6" s="9" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="Y6" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z6" s="12" t="n">
-        <v>3167.76</v>
+        <v>0</v>
       </c>
       <c r="AA6" s="12" t="n">
-        <v>117.52</v>
+        <v>0</v>
       </c>
       <c r="AB6" s="12" t="n">
         <v>0</v>
@@ -17524,13 +17461,13 @@
         <v>0</v>
       </c>
       <c r="AH6" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI6" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AJ6" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AK6" s="12" t="n">
         <v>0</v>
@@ -17539,135 +17476,135 @@
         <v>0</v>
       </c>
       <c r="AM6" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AN6" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AO6" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AP6" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AQ6" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AR6" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AS6" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AT6" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AU6" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AV6" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AW6" s="14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AX6" s="10" t="s">
         <v>85</v>
       </c>
       <c r="AY6" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AZ6" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BA6" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BB6" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BC6" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BD6" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BE6" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BF6" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BG6" s="9" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="BH6" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BI6" s="9" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="BJ6" s="9" t="s">
         <v>86</v>
       </c>
       <c r="BK6" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BL6" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BM6" s="16" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="n">
-        <v>306477</v>
+        <v>306724</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
       <c r="F7" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G7" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K7" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L7" s="12" t="n">
-        <v>3108.72</v>
+        <v>976.79</v>
       </c>
       <c r="M7" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N7" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O7" s="12" t="n">
-        <v>3108.72</v>
+        <v>970.48</v>
       </c>
       <c r="P7" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q7" s="13" t="n">
-        <v>0.001598</v>
+        <v>0</v>
       </c>
       <c r="R7" s="12" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S7" s="12" t="n">
         <v>0</v>
@@ -17676,25 +17613,25 @@
         <v>90</v>
       </c>
       <c r="U7" s="15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V7" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W7" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X7" s="9" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="Y7" s="12" t="n">
-        <v>0</v>
+        <v>6.31</v>
       </c>
       <c r="Z7" s="12" t="n">
-        <v>3108.72</v>
+        <v>976.79</v>
       </c>
       <c r="AA7" s="12" t="n">
-        <v>217.61</v>
+        <v>68.38</v>
       </c>
       <c r="AB7" s="12" t="n">
         <v>0</v>
@@ -17715,13 +17652,13 @@
         <v>0</v>
       </c>
       <c r="AH7" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI7" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AJ7" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AK7" s="12" t="n">
         <v>0</v>
@@ -17730,117 +17667,117 @@
         <v>0</v>
       </c>
       <c r="AM7" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AN7" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AO7" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AP7" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AQ7" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AR7" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AS7" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AT7" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AU7" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AV7" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AW7" s="14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AX7" s="10" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="AY7" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AZ7" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BA7" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BB7" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BC7" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BD7" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BE7" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BF7" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BG7" s="9" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="BH7" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BI7" s="9" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="BJ7" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="BK7" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BL7" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BM7" s="16" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="n">
-        <v>306493</v>
+        <v>306823</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
       <c r="F8" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="K8" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L8" s="12" t="n">
-        <v>2876.8</v>
+        <v>5775.71</v>
       </c>
       <c r="M8" s="12" t="n">
         <v>0</v>
@@ -17849,43 +17786,43 @@
         <v>1</v>
       </c>
       <c r="O8" s="12" t="n">
-        <v>2701.22</v>
+        <v>5510.71</v>
       </c>
       <c r="P8" s="12" t="n">
-        <v>0</v>
+        <v>265</v>
       </c>
       <c r="Q8" s="13" t="n">
-        <v>0.027908</v>
+        <v>0</v>
       </c>
       <c r="R8" s="12" t="n">
-        <v>3.56</v>
+        <v>3.5</v>
       </c>
       <c r="S8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T8" s="14" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="U8" s="15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V8" s="12" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="W8" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X8" s="9" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="Y8" s="12" t="n">
-        <v>175.58</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="12" t="n">
-        <v>2701.22</v>
+        <v>5775.71</v>
       </c>
       <c r="AA8" s="12" t="n">
-        <v>189.09</v>
+        <v>404.3</v>
       </c>
       <c r="AB8" s="12" t="n">
         <v>0</v>
@@ -17906,13 +17843,13 @@
         <v>0</v>
       </c>
       <c r="AH8" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AJ8" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AK8" s="12" t="n">
         <v>0</v>
@@ -17921,162 +17858,162 @@
         <v>0</v>
       </c>
       <c r="AM8" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AN8" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AO8" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AP8" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AQ8" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AR8" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AS8" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AT8" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AU8" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AV8" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AW8" s="14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AX8" s="10" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AY8" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AZ8" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BA8" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BB8" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BC8" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BD8" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BE8" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BF8" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BG8" s="9" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="BH8" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BI8" s="9" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="BJ8" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="BK8" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BL8" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BM8" s="16" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="n">
-        <v>306535</v>
+        <v>306845</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G9" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="K9" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L9" s="12" t="n">
+        <v>935.55</v>
+      </c>
+      <c r="M9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" s="12" t="n">
+        <v>935.55</v>
+      </c>
+      <c r="P9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="U9" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V9" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="W9" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X9" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="L9" s="12" t="n">
-        <v>5384.2</v>
-      </c>
-      <c r="M9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="O9" s="12" t="n">
-        <v>5384.2</v>
-      </c>
-      <c r="P9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="13" t="n">
-        <v>0.023054</v>
-      </c>
-      <c r="R9" s="12" t="n">
-        <v>28.62</v>
-      </c>
-      <c r="S9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="U9" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="V9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="X9" s="9" t="s">
-        <v>82</v>
-      </c>
       <c r="Y9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z9" s="12" t="n">
-        <v>0</v>
+        <v>935.55</v>
       </c>
       <c r="AA9" s="12" t="n">
-        <v>0</v>
+        <v>65.49</v>
       </c>
       <c r="AB9" s="12" t="n">
         <v>0</v>
@@ -18097,13 +18034,13 @@
         <v>0</v>
       </c>
       <c r="AH9" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AJ9" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AK9" s="12" t="n">
         <v>0</v>
@@ -18112,117 +18049,117 @@
         <v>0</v>
       </c>
       <c r="AM9" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AN9" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AO9" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AP9" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AQ9" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AR9" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AS9" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AT9" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AU9" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AV9" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AW9" s="14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AX9" s="10" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AY9" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AZ9" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BA9" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BB9" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BC9" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BD9" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BE9" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BF9" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BG9" s="9" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="BH9" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BI9" s="9" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="BJ9" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="BK9" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BL9" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BM9" s="16" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="n">
-        <v>306675</v>
+        <v>306871</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
       <c r="F10" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="K10" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L10" s="12" t="n">
-        <v>3116.85</v>
+        <v>1978.02</v>
       </c>
       <c r="M10" s="12" t="n">
         <v>0</v>
@@ -18231,16 +18168,16 @@
         <v>1</v>
       </c>
       <c r="O10" s="12" t="n">
-        <v>3116.85</v>
+        <v>1978.02</v>
       </c>
       <c r="P10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q10" s="13" t="n">
-        <v>0.011766</v>
+        <v>0</v>
       </c>
       <c r="R10" s="12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S10" s="12" t="n">
         <v>0</v>
@@ -18249,25 +18186,25 @@
         <v>105</v>
       </c>
       <c r="U10" s="15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V10" s="12" t="n">
         <v>28</v>
       </c>
       <c r="W10" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X10" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Y10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z10" s="12" t="n">
-        <v>3116.85</v>
+        <v>1978.02</v>
       </c>
       <c r="AA10" s="12" t="n">
-        <v>218.18</v>
+        <v>138.46</v>
       </c>
       <c r="AB10" s="12" t="n">
         <v>0</v>
@@ -18288,13 +18225,13 @@
         <v>0</v>
       </c>
       <c r="AH10" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AJ10" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AK10" s="12" t="n">
         <v>0</v>
@@ -18303,544 +18240,544 @@
         <v>0</v>
       </c>
       <c r="AM10" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AN10" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AO10" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AP10" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AQ10" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AR10" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AS10" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AT10" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AU10" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AV10" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AW10" s="14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AX10" s="10" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AY10" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AZ10" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BA10" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BB10" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BC10" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BD10" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BE10" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BF10" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BG10" s="9" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="BH10" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BI10" s="9" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="BJ10" s="9" t="s">
         <v>106</v>
       </c>
       <c r="BK10" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BL10" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BM10" s="16" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="n">
-        <v>306724</v>
+        <v>306872</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
       <c r="F11" s="9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G11" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="K11" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>976.79</v>
+        <v>569.02</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O11" s="12" t="n">
-        <v>970.48</v>
+        <v>569.02</v>
       </c>
       <c r="P11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q11" s="13" t="n">
-        <v>0</v>
+        <v>0.003038</v>
       </c>
       <c r="R11" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T11" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="U11" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X11" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="12" t="n">
+        <v>569.02</v>
+      </c>
+      <c r="AA11" s="12" t="n">
+        <v>39.83</v>
+      </c>
+      <c r="AB11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN11" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO11" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP11" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ11" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR11" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS11" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT11" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU11" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV11" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW11" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX11" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="AY11" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ11" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA11" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB11" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC11" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD11" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE11" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF11" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG11" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH11" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI11" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ11" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="U11" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="V11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="X11" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="Y11" s="12" t="n">
-        <v>6.31</v>
-      </c>
-      <c r="Z11" s="12" t="n">
-        <v>976.79</v>
-      </c>
-      <c r="AA11" s="12" t="n">
-        <v>68.38</v>
-      </c>
-      <c r="AB11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH11" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AI11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ11" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AK11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM11" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AN11" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AO11" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AP11" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AQ11" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AR11" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AS11" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AT11" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AU11" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AV11" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW11" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AX11" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="AY11" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AZ11" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BA11" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BB11" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BC11" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BD11" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BE11" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BF11" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="BG11" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="BH11" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BI11" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="BJ11" s="9" t="s">
-        <v>110</v>
-      </c>
       <c r="BK11" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BL11" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BM11" s="16" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="n">
-        <v>306726</v>
+        <v>306873</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
       <c r="F12" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="K12" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L12" s="12" t="n">
+        <v>2954.76</v>
+      </c>
+      <c r="M12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="O12" s="12" t="n">
+        <v>2954.76</v>
+      </c>
+      <c r="P12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="13" t="n">
+        <v>0.00726</v>
+      </c>
+      <c r="R12" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="S12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="G12" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="I12" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="J12" s="9" t="s">
+      <c r="U12" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V12" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="W12" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X12" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="K12" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="L12" s="12" t="n">
-        <v>846.74</v>
-      </c>
-      <c r="M12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O12" s="12" t="n">
-        <v>846.74</v>
-      </c>
-      <c r="P12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" s="12" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="S12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" s="14" t="s">
+      <c r="Y12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="12" t="n">
+        <v>2954.76</v>
+      </c>
+      <c r="AA12" s="12" t="n">
+        <v>206.83</v>
+      </c>
+      <c r="AB12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN12" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO12" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP12" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ12" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR12" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS12" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT12" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU12" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV12" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW12" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX12" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY12" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ12" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA12" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB12" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC12" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD12" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE12" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF12" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG12" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH12" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI12" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ12" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="U12" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="V12" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="W12" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="X12" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="Y12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" s="12" t="n">
-        <v>846.74</v>
-      </c>
-      <c r="AA12" s="12" t="n">
-        <v>59.27</v>
-      </c>
-      <c r="AB12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AI12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ12" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AK12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AN12" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AO12" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AP12" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AQ12" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AR12" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AS12" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AT12" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AU12" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AV12" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW12" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AX12" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="AY12" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AZ12" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BA12" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BB12" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BC12" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BD12" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BE12" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BF12" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="BG12" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="BH12" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BI12" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="BJ12" s="9" t="s">
-        <v>113</v>
-      </c>
       <c r="BK12" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BL12" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BM12" s="16" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="n">
-        <v>306823</v>
+        <v>306874</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
       <c r="F13" s="9" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G13" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>103</v>
+        <v>69</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="K13" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>5775.71</v>
+        <v>2271.36</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O13" s="12" t="n">
-        <v>5510.71</v>
+        <v>2271.36</v>
       </c>
       <c r="P13" s="12" t="n">
-        <v>265</v>
+        <v>0</v>
       </c>
       <c r="Q13" s="13" t="n">
-        <v>0</v>
+        <v>0.011638</v>
       </c>
       <c r="R13" s="12" t="n">
-        <v>3.5</v>
+        <v>17</v>
       </c>
       <c r="S13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T13" s="14" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="U13" s="15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V13" s="12" t="n">
-        <v>42</v>
+        <v>41.99</v>
       </c>
       <c r="W13" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X13" s="9" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="Y13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z13" s="12" t="n">
-        <v>5775.71</v>
+        <v>2271.36</v>
       </c>
       <c r="AA13" s="12" t="n">
-        <v>404.3</v>
+        <v>159</v>
       </c>
       <c r="AB13" s="12" t="n">
         <v>0</v>
@@ -18861,13 +18798,13 @@
         <v>0</v>
       </c>
       <c r="AH13" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AJ13" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AK13" s="12" t="n">
         <v>0</v>
@@ -18876,162 +18813,162 @@
         <v>0</v>
       </c>
       <c r="AM13" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AN13" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AO13" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AP13" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AQ13" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AR13" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AS13" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AT13" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AU13" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AV13" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AW13" s="14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AX13" s="10" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AY13" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AZ13" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BA13" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BB13" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BC13" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BD13" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BE13" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BF13" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BG13" s="9" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="BH13" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BI13" s="9" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="BJ13" s="9" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="BK13" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BL13" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BM13" s="16" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="n">
-        <v>306845</v>
+        <v>306875</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>119</v>
+        <v>98</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
       <c r="F14" s="9" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="G14" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="K14" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>935.55</v>
+        <v>5436.26</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O14" s="12" t="n">
-        <v>935.55</v>
+        <v>5436.26</v>
       </c>
       <c r="P14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q14" s="13" t="n">
-        <v>0</v>
+        <v>0.022294</v>
       </c>
       <c r="R14" s="12" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="S14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T14" s="14" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="U14" s="15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V14" s="12" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="W14" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X14" s="9" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="Y14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z14" s="12" t="n">
-        <v>935.55</v>
+        <v>5436.26</v>
       </c>
       <c r="AA14" s="12" t="n">
-        <v>65.49</v>
+        <v>380.54</v>
       </c>
       <c r="AB14" s="12" t="n">
         <v>0</v>
@@ -19052,13 +18989,13 @@
         <v>0</v>
       </c>
       <c r="AH14" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AJ14" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AK14" s="12" t="n">
         <v>0</v>
@@ -19067,353 +19004,353 @@
         <v>0</v>
       </c>
       <c r="AM14" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AN14" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AO14" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AP14" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AQ14" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AR14" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AS14" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AT14" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AU14" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AV14" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AW14" s="14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AX14" s="10" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AY14" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AZ14" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BA14" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BB14" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BC14" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BD14" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BE14" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BF14" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BG14" s="9" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="BH14" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BI14" s="9" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="BJ14" s="9" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="BK14" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BL14" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BM14" s="16" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="n">
-        <v>306871</v>
+        <v>306876</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>119</v>
+        <v>98</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
       <c r="F15" s="9" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="G15" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="J15" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="K15" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L15" s="12" t="n">
+        <v>6157.12</v>
+      </c>
+      <c r="M15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="O15" s="12" t="n">
+        <v>6157.12</v>
+      </c>
+      <c r="P15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="13" t="n">
+        <v>0.030068</v>
+      </c>
+      <c r="R15" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="S15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="U15" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V15" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="W15" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X15" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="12" t="n">
+        <v>6157.12</v>
+      </c>
+      <c r="AA15" s="12" t="n">
+        <v>431</v>
+      </c>
+      <c r="AB15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN15" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO15" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP15" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ15" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR15" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS15" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT15" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU15" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV15" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW15" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX15" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY15" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ15" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA15" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB15" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC15" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD15" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE15" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF15" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG15" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH15" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI15" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ15" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="K15" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="L15" s="12" t="n">
-        <v>1978.02</v>
-      </c>
-      <c r="M15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O15" s="12" t="n">
-        <v>1978.02</v>
-      </c>
-      <c r="P15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" s="14" t="s">
-        <v>126</v>
-      </c>
-      <c r="U15" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="V15" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="W15" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="X15" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="Y15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="12" t="n">
-        <v>1978.02</v>
-      </c>
-      <c r="AA15" s="12" t="n">
-        <v>138.46</v>
-      </c>
-      <c r="AB15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH15" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AI15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ15" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AK15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM15" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AN15" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AO15" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AP15" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AQ15" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AR15" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AS15" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AT15" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AU15" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AV15" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW15" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AX15" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="AY15" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AZ15" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BA15" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BB15" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BC15" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BD15" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BE15" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BF15" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="BG15" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="BH15" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BI15" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="BJ15" s="9" t="s">
-        <v>127</v>
-      </c>
       <c r="BK15" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BL15" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BM15" s="16" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="n">
-        <v>306872</v>
+        <v>306880</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
       <c r="F16" s="9" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>66</v>
+        <v>124</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="I16" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="J16" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K16" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L16" s="12" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="M16" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" s="12" t="n">
+        <v>35.99</v>
+      </c>
+      <c r="P16" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="J16" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="K16" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="L16" s="12" t="n">
-        <v>569.02</v>
-      </c>
-      <c r="M16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="O16" s="12" t="n">
-        <v>569.02</v>
-      </c>
-      <c r="P16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="13" t="n">
-        <v>0.003038</v>
-      </c>
-      <c r="R16" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="S16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" s="14" t="s">
-        <v>129</v>
-      </c>
       <c r="U16" s="15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="W16" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X16" s="9" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="Y16" s="12" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="Z16" s="12" t="n">
-        <v>569.02</v>
+        <v>35.99</v>
       </c>
       <c r="AA16" s="12" t="n">
-        <v>39.83</v>
+        <v>2.52</v>
       </c>
       <c r="AB16" s="12" t="n">
         <v>0</v>
@@ -19434,13 +19371,13 @@
         <v>0</v>
       </c>
       <c r="AH16" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AJ16" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AK16" s="12" t="n">
         <v>0</v>
@@ -19449,326 +19386,326 @@
         <v>0</v>
       </c>
       <c r="AM16" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AN16" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AO16" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AP16" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AQ16" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AR16" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AS16" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AT16" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AU16" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AV16" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AW16" s="14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AX16" s="10" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AY16" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AZ16" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BA16" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BB16" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BC16" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BD16" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BE16" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BF16" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BG16" s="9" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="BH16" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BI16" s="9" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="BJ16" s="9" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="BK16" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BL16" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BM16" s="16" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="n">
-        <v>306873</v>
+        <v>306969</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
       <c r="F17" s="9" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="G17" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="K17" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>2954.76</v>
+        <v>3625.8</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O17" s="12" t="n">
-        <v>2954.76</v>
+        <v>3315.52</v>
       </c>
       <c r="P17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q17" s="13" t="n">
-        <v>0.00726</v>
+        <v>0</v>
       </c>
       <c r="R17" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="S17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T17" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="U17" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V17" s="12" t="n">
+        <v>60.33</v>
+      </c>
+      <c r="W17" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X17" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="Y17" s="12" t="n">
+        <v>310.28</v>
+      </c>
+      <c r="Z17" s="12" t="n">
+        <v>3315.52</v>
+      </c>
+      <c r="AA17" s="12" t="n">
+        <v>132.63</v>
+      </c>
+      <c r="AB17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN17" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO17" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP17" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ17" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR17" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS17" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT17" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU17" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV17" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW17" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX17" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY17" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ17" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA17" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB17" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC17" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD17" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE17" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF17" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG17" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH17" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI17" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ17" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="U17" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="V17" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="W17" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="X17" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="Y17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" s="12" t="n">
-        <v>2954.76</v>
-      </c>
-      <c r="AA17" s="12" t="n">
-        <v>206.83</v>
-      </c>
-      <c r="AB17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AI17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ17" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AK17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM17" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AN17" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AO17" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AP17" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AQ17" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AR17" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AS17" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AT17" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AU17" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AV17" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW17" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AX17" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="AY17" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AZ17" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BA17" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BB17" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BC17" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BD17" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BE17" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BF17" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="BG17" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="BH17" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BI17" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="BJ17" s="9" t="s">
-        <v>133</v>
-      </c>
       <c r="BK17" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BL17" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BM17" s="16" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="n">
-        <v>306874</v>
+        <v>306975</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>119</v>
+        <v>98</v>
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
       <c r="F18" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G18" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="K18" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>2271.36</v>
+        <v>985.72</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O18" s="12" t="n">
-        <v>2271.36</v>
+        <v>985.72</v>
       </c>
       <c r="P18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q18" s="13" t="n">
-        <v>0.011638</v>
+        <v>0.002368</v>
       </c>
       <c r="R18" s="12" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="S18" s="12" t="n">
         <v>0</v>
@@ -19777,25 +19714,25 @@
         <v>135</v>
       </c>
       <c r="U18" s="15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V18" s="12" t="n">
-        <v>41.99</v>
+        <v>41.98</v>
       </c>
       <c r="W18" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X18" s="9" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="Y18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z18" s="12" t="n">
-        <v>2271.36</v>
+        <v>985.72</v>
       </c>
       <c r="AA18" s="12" t="n">
-        <v>159</v>
+        <v>69</v>
       </c>
       <c r="AB18" s="12" t="n">
         <v>0</v>
@@ -19816,13 +19753,13 @@
         <v>0</v>
       </c>
       <c r="AH18" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AJ18" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AK18" s="12" t="n">
         <v>0</v>
@@ -19831,93 +19768,93 @@
         <v>0</v>
       </c>
       <c r="AM18" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AN18" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AO18" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AP18" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AQ18" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AR18" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AS18" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AT18" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AU18" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AV18" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AW18" s="14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AX18" s="10" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AY18" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AZ18" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BA18" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BB18" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BC18" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BD18" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BE18" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BF18" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BG18" s="9" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="BH18" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BI18" s="9" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="BJ18" s="9" t="s">
         <v>136</v>
       </c>
       <c r="BK18" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BL18" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BM18" s="16" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="n">
-        <v>306875</v>
+        <v>306976</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>119</v>
+        <v>98</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
@@ -19929,37 +19866,37 @@
         <v>66</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="K19" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>5436.26</v>
+        <v>1478.58</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O19" s="12" t="n">
-        <v>5436.26</v>
+        <v>1478.58</v>
       </c>
       <c r="P19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q19" s="13" t="n">
-        <v>0.022294</v>
+        <v>0.007104</v>
       </c>
       <c r="R19" s="12" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="S19" s="12" t="n">
         <v>0</v>
@@ -19968,25 +19905,25 @@
         <v>138</v>
       </c>
       <c r="U19" s="15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V19" s="12" t="n">
-        <v>42</v>
+        <v>41.99</v>
       </c>
       <c r="W19" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X19" s="9" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="Y19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z19" s="12" t="n">
-        <v>5436.26</v>
+        <v>1478.58</v>
       </c>
       <c r="AA19" s="12" t="n">
-        <v>380.54</v>
+        <v>103.5</v>
       </c>
       <c r="AB19" s="12" t="n">
         <v>0</v>
@@ -20007,13 +19944,13 @@
         <v>0</v>
       </c>
       <c r="AH19" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AJ19" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AK19" s="12" t="n">
         <v>0</v>
@@ -20022,93 +19959,93 @@
         <v>0</v>
       </c>
       <c r="AM19" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AN19" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AO19" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AP19" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AQ19" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AR19" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AS19" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AT19" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AU19" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AV19" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AW19" s="14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AX19" s="10" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AY19" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AZ19" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BA19" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BB19" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BC19" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BD19" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BE19" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BF19" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BG19" s="9" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="BH19" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BI19" s="9" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="BJ19" s="9" t="s">
         <v>139</v>
       </c>
       <c r="BK19" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BL19" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BM19" s="16" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="n">
-        <v>306876</v>
+        <v>306977</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>119</v>
+        <v>98</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
@@ -20120,210 +20057,210 @@
         <v>66</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="K20" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>6157.12</v>
+        <v>1478.58</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O20" s="12" t="n">
-        <v>6157.12</v>
+        <v>1478.58</v>
       </c>
       <c r="P20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q20" s="13" t="n">
-        <v>0.030068</v>
+        <v>0.007104</v>
       </c>
       <c r="R20" s="12" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="S20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T20" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="U20" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V20" s="12" t="n">
+        <v>41.99</v>
+      </c>
+      <c r="W20" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X20" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="Y20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="12" t="n">
+        <v>1478.58</v>
+      </c>
+      <c r="AA20" s="12" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="AB20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN20" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO20" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP20" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ20" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR20" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS20" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT20" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU20" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV20" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW20" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX20" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY20" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ20" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA20" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB20" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC20" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD20" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE20" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF20" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG20" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH20" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI20" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ20" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="U20" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="V20" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="W20" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="X20" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="Y20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="12" t="n">
-        <v>6157.12</v>
-      </c>
-      <c r="AA20" s="12" t="n">
-        <v>431</v>
-      </c>
-      <c r="AB20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH20" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AI20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ20" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AK20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM20" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AN20" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AO20" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AP20" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AQ20" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AR20" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AS20" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AT20" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AU20" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AV20" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW20" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AX20" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="AY20" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AZ20" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BA20" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BB20" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BC20" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BD20" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BE20" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BF20" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="BG20" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="BH20" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BI20" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="BJ20" s="9" t="s">
-        <v>142</v>
-      </c>
       <c r="BK20" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BL20" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BM20" s="16" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="n">
-        <v>306880</v>
+        <v>307040</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>143</v>
+        <v>98</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
       <c r="F21" s="9" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>145</v>
+        <v>66</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>68</v>
+        <v>134</v>
       </c>
       <c r="K21" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>39.5</v>
+        <v>1478.58</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>0</v>
@@ -20332,43 +20269,43 @@
         <v>1</v>
       </c>
       <c r="O21" s="12" t="n">
-        <v>35.99</v>
+        <v>1478.58</v>
       </c>
       <c r="P21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q21" s="13" t="n">
-        <v>0</v>
+        <v>0.007104</v>
       </c>
       <c r="R21" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T21" s="14" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="U21" s="15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V21" s="12" t="n">
-        <v>0</v>
+        <v>41.99</v>
       </c>
       <c r="W21" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X21" s="9" t="s">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="Y21" s="12" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="Z21" s="12" t="n">
-        <v>35.99</v>
+        <v>1478.58</v>
       </c>
       <c r="AA21" s="12" t="n">
-        <v>2.52</v>
+        <v>103.5</v>
       </c>
       <c r="AB21" s="12" t="n">
         <v>0</v>
@@ -20389,13 +20326,13 @@
         <v>0</v>
       </c>
       <c r="AH21" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AJ21" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AK21" s="12" t="n">
         <v>0</v>
@@ -20404,162 +20341,162 @@
         <v>0</v>
       </c>
       <c r="AM21" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AN21" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AO21" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AP21" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AQ21" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AR21" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AS21" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AT21" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AU21" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AV21" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AW21" s="14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AX21" s="10" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AY21" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AZ21" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BA21" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BB21" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BC21" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BD21" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BE21" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BF21" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BG21" s="9" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="BH21" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BI21" s="9" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="BJ21" s="9" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="BK21" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BL21" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BM21" s="16" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="n">
-        <v>306969</v>
+        <v>307172</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
       <c r="F22" s="9" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="G22" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>83</v>
+        <v>129</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>151</v>
+        <v>78</v>
       </c>
       <c r="K22" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>3625.8</v>
+        <v>404.81</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O22" s="12" t="n">
-        <v>3315.52</v>
+        <v>404.81</v>
       </c>
       <c r="P22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q22" s="13" t="n">
-        <v>0</v>
+        <v>0.000858</v>
       </c>
       <c r="R22" s="12" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T22" s="14" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="U22" s="15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V22" s="12" t="n">
-        <v>60.33</v>
+        <v>0</v>
       </c>
       <c r="W22" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X22" s="9" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="Y22" s="12" t="n">
-        <v>310.28</v>
+        <v>0</v>
       </c>
       <c r="Z22" s="12" t="n">
-        <v>3315.52</v>
+        <v>404.81</v>
       </c>
       <c r="AA22" s="12" t="n">
-        <v>132.63</v>
+        <v>16.19</v>
       </c>
       <c r="AB22" s="12" t="n">
         <v>0</v>
@@ -20580,13 +20517,13 @@
         <v>0</v>
       </c>
       <c r="AH22" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AJ22" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AK22" s="12" t="n">
         <v>0</v>
@@ -20595,117 +20532,117 @@
         <v>0</v>
       </c>
       <c r="AM22" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AN22" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AO22" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AP22" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AQ22" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AR22" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AS22" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AT22" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AU22" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AV22" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AW22" s="14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AX22" s="10" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="AY22" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AZ22" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BA22" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BB22" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BC22" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BD22" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BE22" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BF22" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BG22" s="9" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="BH22" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BI22" s="9" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="BJ22" s="9" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="BK22" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BL22" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BM22" s="16" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="n">
-        <v>306975</v>
+        <v>307205</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>119</v>
+        <v>87</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="9" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="G23" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>155</v>
+        <v>78</v>
       </c>
       <c r="K23" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>985.72</v>
+        <v>48.67</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>0</v>
@@ -20714,43 +20651,43 @@
         <v>1</v>
       </c>
       <c r="O23" s="12" t="n">
-        <v>985.72</v>
+        <v>48.36</v>
       </c>
       <c r="P23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q23" s="13" t="n">
-        <v>0.002368</v>
+        <v>0.01185</v>
       </c>
       <c r="R23" s="12" t="n">
-        <v>2</v>
+        <v>34.5</v>
       </c>
       <c r="S23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T23" s="14" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="U23" s="15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V23" s="12" t="n">
-        <v>41.98</v>
+        <v>0</v>
       </c>
       <c r="W23" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X23" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Y23" s="12" t="n">
-        <v>0</v>
+        <v>0.31</v>
       </c>
       <c r="Z23" s="12" t="n">
-        <v>985.72</v>
+        <v>48.36</v>
       </c>
       <c r="AA23" s="12" t="n">
-        <v>69</v>
+        <v>3.39</v>
       </c>
       <c r="AB23" s="12" t="n">
         <v>0</v>
@@ -20771,13 +20708,13 @@
         <v>0</v>
       </c>
       <c r="AH23" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AJ23" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AK23" s="12" t="n">
         <v>0</v>
@@ -20786,117 +20723,117 @@
         <v>0</v>
       </c>
       <c r="AM23" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AN23" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AO23" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AP23" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AQ23" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AR23" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AS23" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AT23" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AU23" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AV23" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AW23" s="14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AX23" s="10" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="AY23" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AZ23" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BA23" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BB23" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BC23" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BD23" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BE23" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BF23" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BG23" s="9" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="BH23" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BI23" s="9" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="BJ23" s="9" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="BK23" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BL23" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BM23" s="16" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="n">
-        <v>306976</v>
+        <v>307219</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>119</v>
+        <v>145</v>
       </c>
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
       <c r="F24" s="9" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="G24" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>155</v>
+        <v>78</v>
       </c>
       <c r="K24" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>1478.58</v>
+        <v>461.96</v>
       </c>
       <c r="M24" s="12" t="n">
         <v>0</v>
@@ -20905,43 +20842,43 @@
         <v>1</v>
       </c>
       <c r="O24" s="12" t="n">
-        <v>1478.58</v>
+        <v>461.96</v>
       </c>
       <c r="P24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q24" s="13" t="n">
-        <v>0.007104</v>
+        <v>0.002057</v>
       </c>
       <c r="R24" s="12" t="n">
-        <v>6</v>
+        <v>2.43</v>
       </c>
       <c r="S24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T24" s="14" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="U24" s="15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V24" s="12" t="n">
-        <v>41.99</v>
+        <v>0</v>
       </c>
       <c r="W24" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X24" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Y24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z24" s="12" t="n">
-        <v>1478.58</v>
+        <v>461.96</v>
       </c>
       <c r="AA24" s="12" t="n">
-        <v>103.5</v>
+        <v>18.48</v>
       </c>
       <c r="AB24" s="12" t="n">
         <v>0</v>
@@ -20962,13 +20899,13 @@
         <v>0</v>
       </c>
       <c r="AH24" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AJ24" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AK24" s="12" t="n">
         <v>0</v>
@@ -20977,117 +20914,117 @@
         <v>0</v>
       </c>
       <c r="AM24" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AN24" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AO24" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AP24" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AQ24" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AR24" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AS24" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AT24" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AU24" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AV24" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AW24" s="14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AX24" s="10" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="AY24" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AZ24" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BA24" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BB24" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BC24" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BD24" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BE24" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BF24" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BG24" s="9" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="BH24" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BI24" s="9" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="BJ24" s="9" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="BK24" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BL24" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BM24" s="16" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="n">
-        <v>306977</v>
+        <v>307243</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>119</v>
+        <v>157</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>66</v>
+        <v>159</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="K25" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>1478.58</v>
+        <v>2077.92</v>
       </c>
       <c r="M25" s="12" t="n">
         <v>0</v>
@@ -21096,43 +21033,43 @@
         <v>1</v>
       </c>
       <c r="O25" s="12" t="n">
-        <v>1478.58</v>
+        <v>2077.92</v>
       </c>
       <c r="P25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q25" s="13" t="n">
-        <v>0.007104</v>
+        <v>0.007844</v>
       </c>
       <c r="R25" s="12" t="n">
-        <v>6</v>
+        <v>0.81</v>
       </c>
       <c r="S25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T25" s="14" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="U25" s="15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V25" s="12" t="n">
-        <v>41.99</v>
+        <v>28</v>
       </c>
       <c r="W25" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X25" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Y25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z25" s="12" t="n">
-        <v>1478.58</v>
+        <v>2077.92</v>
       </c>
       <c r="AA25" s="12" t="n">
-        <v>103.5</v>
+        <v>145.45</v>
       </c>
       <c r="AB25" s="12" t="n">
         <v>0</v>
@@ -21153,13 +21090,13 @@
         <v>0</v>
       </c>
       <c r="AH25" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AJ25" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AK25" s="12" t="n">
         <v>0</v>
@@ -21168,117 +21105,117 @@
         <v>0</v>
       </c>
       <c r="AM25" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AN25" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AO25" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AP25" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AQ25" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AR25" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AS25" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AT25" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AU25" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AV25" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AW25" s="14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AX25" s="10" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AY25" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AZ25" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BA25" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BB25" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BC25" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BD25" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BE25" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BF25" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BG25" s="9" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="BH25" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BI25" s="9" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="BJ25" s="9" t="s">
         <v>162</v>
       </c>
       <c r="BK25" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BL25" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BM25" s="16" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="n">
-        <v>307040</v>
+        <v>307275</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>119</v>
+        <v>163</v>
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G26" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>155</v>
+        <v>78</v>
       </c>
       <c r="K26" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>1478.58</v>
+        <v>497.7</v>
       </c>
       <c r="M26" s="12" t="n">
         <v>0</v>
@@ -21287,43 +21224,43 @@
         <v>1</v>
       </c>
       <c r="O26" s="12" t="n">
-        <v>1478.58</v>
+        <v>497.7</v>
       </c>
       <c r="P26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q26" s="13" t="n">
-        <v>0.007104</v>
+        <v>0</v>
       </c>
       <c r="R26" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T26" s="14" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="U26" s="15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V26" s="12" t="n">
-        <v>41.99</v>
+        <v>0</v>
       </c>
       <c r="W26" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X26" s="9" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="Y26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z26" s="12" t="n">
-        <v>1478.58</v>
+        <v>497.7</v>
       </c>
       <c r="AA26" s="12" t="n">
-        <v>103.5</v>
+        <v>19.91</v>
       </c>
       <c r="AB26" s="12" t="n">
         <v>0</v>
@@ -21344,13 +21281,13 @@
         <v>0</v>
       </c>
       <c r="AH26" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AJ26" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AK26" s="12" t="n">
         <v>0</v>
@@ -21359,117 +21296,117 @@
         <v>0</v>
       </c>
       <c r="AM26" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AN26" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AO26" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AP26" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AQ26" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AR26" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AS26" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AT26" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AU26" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AV26" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AW26" s="14" t="s">
-        <v>75</v>
+        <v>166</v>
       </c>
       <c r="AX26" s="10" t="s">
         <v>85</v>
       </c>
       <c r="AY26" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AZ26" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BA26" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BB26" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BC26" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BD26" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BE26" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BF26" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BG26" s="9" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="BH26" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BI26" s="9" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="BJ26" s="9" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="BK26" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BL26" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BM26" s="16" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="n">
-        <v>307120</v>
+        <v>307294</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>66</v>
+        <v>159</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J27" s="9" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="K27" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>1188.23</v>
+        <v>4402.37</v>
       </c>
       <c r="M27" s="12" t="n">
         <v>0</v>
@@ -21478,43 +21415,43 @@
         <v>1</v>
       </c>
       <c r="O27" s="12" t="n">
-        <v>1088.23</v>
+        <v>4402.37</v>
       </c>
       <c r="P27" s="12" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q27" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R27" s="12" t="n">
-        <v>3.9</v>
+        <v>8.3</v>
       </c>
       <c r="S27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T27" s="14" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="U27" s="15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V27" s="12" t="n">
         <v>28</v>
       </c>
       <c r="W27" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X27" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Y27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z27" s="12" t="n">
-        <v>1188.23</v>
+        <v>4402.37</v>
       </c>
       <c r="AA27" s="12" t="n">
-        <v>83.18</v>
+        <v>308.17</v>
       </c>
       <c r="AB27" s="12" t="n">
         <v>0</v>
@@ -21535,13 +21472,13 @@
         <v>0</v>
       </c>
       <c r="AH27" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AJ27" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AK27" s="12" t="n">
         <v>0</v>
@@ -21550,117 +21487,117 @@
         <v>0</v>
       </c>
       <c r="AM27" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AN27" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AO27" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AP27" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AQ27" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AR27" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AS27" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AT27" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AU27" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AV27" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AW27" s="14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AX27" s="10" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AY27" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AZ27" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BA27" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BB27" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BC27" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BD27" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BE27" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BF27" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BG27" s="9" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="BH27" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BI27" s="9" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="BJ27" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="BK27" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BL27" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BM27" s="16" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="n">
-        <v>307172</v>
+        <v>307332</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>64</v>
+        <v>157</v>
       </c>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>66</v>
+        <v>159</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>68</v>
+        <v>173</v>
       </c>
       <c r="K28" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>404.81</v>
+        <v>1494.11</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>0</v>
@@ -21669,43 +21606,43 @@
         <v>1</v>
       </c>
       <c r="O28" s="12" t="n">
-        <v>404.81</v>
+        <v>1494.11</v>
       </c>
       <c r="P28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q28" s="13" t="n">
-        <v>0.000858</v>
+        <v>0.002473</v>
       </c>
       <c r="R28" s="12" t="n">
-        <v>2.43</v>
+        <v>0.77</v>
       </c>
       <c r="S28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T28" s="14" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="U28" s="15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V28" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W28" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X28" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Y28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z28" s="12" t="n">
-        <v>404.81</v>
+        <v>1494.11</v>
       </c>
       <c r="AA28" s="12" t="n">
-        <v>16.19</v>
+        <v>104.59</v>
       </c>
       <c r="AB28" s="12" t="n">
         <v>0</v>
@@ -21726,13 +21663,13 @@
         <v>0</v>
       </c>
       <c r="AH28" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AJ28" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AK28" s="12" t="n">
         <v>0</v>
@@ -21741,117 +21678,117 @@
         <v>0</v>
       </c>
       <c r="AM28" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AN28" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AO28" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AP28" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AQ28" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AR28" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AS28" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AT28" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AU28" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AV28" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AW28" s="14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AX28" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AY28" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AZ28" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BA28" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BB28" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BC28" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BD28" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BE28" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BF28" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BG28" s="9" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="BH28" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BI28" s="9" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="BJ28" s="9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="BK28" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BL28" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BM28" s="16" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="n">
-        <v>307205</v>
+        <v>307348</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>107</v>
+        <v>157</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
       <c r="F29" s="9" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>66</v>
+        <v>159</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>68</v>
+        <v>177</v>
       </c>
       <c r="K29" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>48.67</v>
+        <v>1360.01</v>
       </c>
       <c r="M29" s="12" t="n">
         <v>0</v>
@@ -21860,43 +21797,43 @@
         <v>1</v>
       </c>
       <c r="O29" s="12" t="n">
-        <v>48.36</v>
+        <v>1277</v>
       </c>
       <c r="P29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q29" s="13" t="n">
-        <v>0.01185</v>
+        <v>0.013954</v>
       </c>
       <c r="R29" s="12" t="n">
-        <v>34.5</v>
+        <v>1.78</v>
       </c>
       <c r="S29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T29" s="14" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="U29" s="15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V29" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W29" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X29" s="9" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="Y29" s="12" t="n">
-        <v>0.31</v>
+        <v>83.01</v>
       </c>
       <c r="Z29" s="12" t="n">
-        <v>48.36</v>
+        <v>1277</v>
       </c>
       <c r="AA29" s="12" t="n">
-        <v>3.39</v>
+        <v>89.39</v>
       </c>
       <c r="AB29" s="12" t="n">
         <v>0</v>
@@ -21917,13 +21854,13 @@
         <v>0</v>
       </c>
       <c r="AH29" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AJ29" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AK29" s="12" t="n">
         <v>0</v>
@@ -21932,1555 +21869,823 @@
         <v>0</v>
       </c>
       <c r="AM29" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AN29" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AO29" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AP29" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AQ29" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AR29" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AS29" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AT29" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AU29" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AV29" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AW29" s="14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AX29" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AY29" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AZ29" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BA29" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BB29" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BC29" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BD29" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BE29" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BF29" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BG29" s="9" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="BH29" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BI29" s="9" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="BJ29" s="9" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BK29" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BL29" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BM29" s="16" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="8" t="n">
-        <v>307219</v>
-      </c>
-      <c r="B30" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="G30" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="H30" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="I30" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="J30" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="K30" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="L30" s="12" t="n">
-        <v>461.96</v>
-      </c>
-      <c r="M30" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O30" s="12" t="n">
-        <v>461.96</v>
-      </c>
-      <c r="P30" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" s="13" t="n">
-        <v>0.002057</v>
-      </c>
-      <c r="R30" s="12" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="S30" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="U30" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="V30" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="X30" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="Y30" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z30" s="12" t="n">
-        <v>461.96</v>
-      </c>
-      <c r="AA30" s="12" t="n">
-        <v>18.48</v>
-      </c>
-      <c r="AB30" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC30" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD30" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE30" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF30" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG30" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH30" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AI30" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ30" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AK30" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL30" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM30" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AN30" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AO30" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AP30" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AQ30" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AR30" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AS30" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AT30" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AU30" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AV30" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW30" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AX30" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="AY30" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AZ30" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BA30" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BB30" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BC30" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BD30" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BE30" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BF30" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="BG30" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="BH30" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BI30" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="BJ30" s="9" t="s">
+      <c r="A30" s="4"/>
+    </row>
+    <row r="31" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="17" t="s">
         <v>180</v>
       </c>
-      <c r="BK30" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="BL30" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="BM30" s="16" t="s">
-        <v>78</v>
-      </c>
+      <c r="B31" s="17"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
+      <c r="F31" s="17"/>
+      <c r="G31" s="17"/>
+      <c r="H31" s="17"/>
+      <c r="I31" s="17"/>
+      <c r="J31" s="17"/>
+      <c r="K31" s="17"/>
+      <c r="L31" s="17"/>
+      <c r="M31" s="17"/>
+      <c r="N31" s="17"/>
+      <c r="O31" s="17"/>
+      <c r="P31" s="17"/>
+      <c r="Q31" s="17"/>
+      <c r="R31" s="17"/>
+      <c r="S31" s="17"/>
+      <c r="T31" s="17"/>
+      <c r="U31" s="17"/>
+      <c r="V31" s="17"/>
     </row>
-    <row r="31" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="8" t="n">
-        <v>307243</v>
-      </c>
-      <c r="B31" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9" t="s">
+    <row r="32" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="18" t="s">
         <v>181</v>
       </c>
-      <c r="G31" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="H31" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="I31" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="J31" s="9" t="s">
+      <c r="B32" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C32" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D32" s="18" t="s">
         <v>182</v>
       </c>
-      <c r="K31" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="L31" s="12" t="n">
-        <v>2077.92</v>
-      </c>
-      <c r="M31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O31" s="12" t="n">
-        <v>2077.92</v>
-      </c>
-      <c r="P31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="13" t="n">
-        <v>0.007844</v>
-      </c>
-      <c r="R31" s="12" t="n">
-        <v>0.81</v>
-      </c>
-      <c r="S31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" s="14" t="s">
+      <c r="E32" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F32" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="G32" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H32" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="I32" s="18" t="s">
         <v>183</v>
       </c>
-      <c r="U31" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="V31" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="W31" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="X31" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="Y31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z31" s="12" t="n">
-        <v>2077.92</v>
-      </c>
-      <c r="AA31" s="12" t="n">
-        <v>145.45</v>
-      </c>
-      <c r="AB31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH31" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AI31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ31" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AK31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM31" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AN31" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AO31" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AP31" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AQ31" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AR31" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AS31" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AT31" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AU31" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AV31" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW31" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AX31" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="AY31" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AZ31" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BA31" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BB31" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BC31" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BD31" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BE31" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BF31" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="BG31" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="BH31" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BI31" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="BJ31" s="9" t="s">
+      <c r="J32" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="K32" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="L32" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="M32" s="18" t="s">
         <v>184</v>
       </c>
-      <c r="BK31" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="BL31" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="BM31" s="16" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="8" t="n">
-        <v>307275</v>
-      </c>
-      <c r="B32" s="9" t="s">
+      <c r="N32" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="O32" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="P32" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q32" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="R32" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="S32" s="18" t="s">
         <v>185</v>
       </c>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9" t="s">
+      <c r="T32" s="18" t="s">
         <v>186</v>
       </c>
-      <c r="G32" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="H32" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="I32" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="J32" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="K32" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="L32" s="12" t="n">
-        <v>497.7</v>
-      </c>
-      <c r="M32" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O32" s="12" t="n">
-        <v>497.7</v>
-      </c>
-      <c r="P32" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="U32" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="V32" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="X32" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="Y32" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z32" s="12" t="n">
-        <v>497.7</v>
-      </c>
-      <c r="AA32" s="12" t="n">
-        <v>19.91</v>
-      </c>
-      <c r="AB32" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC32" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD32" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE32" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF32" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG32" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH32" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AI32" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ32" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AK32" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL32" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM32" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AN32" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AO32" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AP32" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AQ32" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AR32" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AS32" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AT32" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AU32" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AV32" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW32" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AX32" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="AY32" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AZ32" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BA32" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BB32" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BC32" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BD32" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BE32" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BF32" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="BG32" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="BH32" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BI32" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="BJ32" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="BK32" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="BL32" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="BM32" s="16" t="s">
-        <v>78</v>
+      <c r="U32" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="V32" s="18" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="8" t="n">
-        <v>307294</v>
-      </c>
-      <c r="B33" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9" t="s">
+      <c r="A33" s="19" t="n">
+        <v>25</v>
+      </c>
+      <c r="B33" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="19" t="n">
+        <v>265</v>
+      </c>
+      <c r="D33" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="19" t="n">
+        <v>403.42</v>
+      </c>
+      <c r="F33" s="19" t="n">
+        <v>49659.55</v>
+      </c>
+      <c r="G33" s="19" t="n">
+        <v>3231.57</v>
+      </c>
+      <c r="H33" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="19" t="n">
+        <v>55440.86</v>
+      </c>
+      <c r="L33" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" s="20" t="n">
+        <v>0.160068</v>
+      </c>
+      <c r="S33" s="19" t="n">
+        <v>54772.44</v>
+      </c>
+      <c r="T33" s="19" t="n">
+        <v>55440.86</v>
+      </c>
+      <c r="U33" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B34" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C34" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D34" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="E34" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="F34" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="G34" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="H34" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="I34" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="J34" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="K34" s="18" t="s">
+        <v>187</v>
+      </c>
+      <c r="L34" s="18" t="s">
+        <v>188</v>
+      </c>
+      <c r="M34" s="18" t="s">
         <v>189</v>
-      </c>
-      <c r="G33" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="H33" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="I33" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="J33" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="K33" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="L33" s="12" t="n">
-        <v>4402.37</v>
-      </c>
-      <c r="M33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O33" s="12" t="n">
-        <v>4402.37</v>
-      </c>
-      <c r="P33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" s="12" t="n">
-        <v>8.3</v>
-      </c>
-      <c r="S33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" s="14" t="s">
-        <v>191</v>
-      </c>
-      <c r="U33" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="V33" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="W33" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="X33" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="Y33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z33" s="12" t="n">
-        <v>4402.37</v>
-      </c>
-      <c r="AA33" s="12" t="n">
-        <v>308.17</v>
-      </c>
-      <c r="AB33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH33" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AI33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ33" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AK33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM33" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AN33" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AO33" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AP33" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AQ33" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AR33" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AS33" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AT33" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AU33" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AV33" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW33" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AX33" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="AY33" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AZ33" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BA33" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BB33" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BC33" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BD33" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BE33" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BF33" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="BG33" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="BH33" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BI33" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="BJ33" s="9" t="s">
-        <v>192</v>
-      </c>
-      <c r="BK33" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="BL33" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="BM33" s="16" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="8" t="n">
-        <v>307332</v>
-      </c>
-      <c r="B34" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="G34" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="H34" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="I34" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="J34" s="9" t="s">
-        <v>194</v>
-      </c>
-      <c r="K34" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="L34" s="12" t="n">
-        <v>1494.11</v>
-      </c>
-      <c r="M34" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O34" s="12" t="n">
-        <v>1494.11</v>
-      </c>
-      <c r="P34" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="13" t="n">
-        <v>0.002473</v>
-      </c>
-      <c r="R34" s="12" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="S34" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" s="14" t="s">
-        <v>195</v>
-      </c>
-      <c r="U34" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="V34" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="W34" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="X34" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="Y34" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z34" s="12" t="n">
-        <v>1494.11</v>
-      </c>
-      <c r="AA34" s="12" t="n">
-        <v>104.59</v>
-      </c>
-      <c r="AB34" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC34" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD34" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE34" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF34" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG34" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH34" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AI34" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ34" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AK34" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL34" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM34" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AN34" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AO34" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AP34" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AQ34" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AR34" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AS34" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AT34" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AU34" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AV34" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW34" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AX34" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="AY34" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AZ34" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BA34" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BB34" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BC34" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BD34" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BE34" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BF34" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="BG34" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="BH34" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BI34" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="BJ34" s="9" t="s">
-        <v>196</v>
-      </c>
-      <c r="BK34" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="BL34" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="BM34" s="16" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="8" t="n">
-        <v>307348</v>
-      </c>
-      <c r="B35" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9" t="s">
-        <v>197</v>
-      </c>
-      <c r="G35" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="H35" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="I35" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="J35" s="9" t="s">
-        <v>198</v>
-      </c>
-      <c r="K35" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="L35" s="12" t="n">
-        <v>1360.01</v>
-      </c>
-      <c r="M35" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O35" s="12" t="n">
-        <v>1277</v>
-      </c>
-      <c r="P35" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" s="13" t="n">
-        <v>0.013954</v>
-      </c>
-      <c r="R35" s="12" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="S35" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="U35" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="V35" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="W35" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="X35" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="Y35" s="12" t="n">
-        <v>83.01</v>
-      </c>
-      <c r="Z35" s="12" t="n">
-        <v>1277</v>
-      </c>
-      <c r="AA35" s="12" t="n">
-        <v>89.39</v>
-      </c>
-      <c r="AB35" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC35" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD35" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE35" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF35" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG35" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH35" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AI35" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ35" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AK35" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL35" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM35" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AN35" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AO35" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AP35" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AQ35" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AR35" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AS35" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AT35" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AU35" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AV35" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW35" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AX35" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="AY35" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AZ35" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BA35" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BB35" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BC35" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BD35" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BE35" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BF35" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="BG35" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="BH35" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="BI35" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="BJ35" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="BK35" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="BL35" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="BM35" s="16" t="s">
-        <v>78</v>
+      <c r="A35" s="19" t="n">
+        <v>193.12</v>
+      </c>
+      <c r="B35" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="19" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="E35" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" s="19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="4"/>
     </row>
     <row r="37" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="17" t="s">
-        <v>201</v>
-      </c>
-      <c r="B37" s="17"/>
-      <c r="C37" s="17"/>
-      <c r="D37" s="17"/>
-      <c r="E37" s="17"/>
-      <c r="F37" s="17"/>
-      <c r="G37" s="17"/>
-      <c r="H37" s="17"/>
-      <c r="I37" s="17"/>
-      <c r="J37" s="17"/>
-      <c r="K37" s="17"/>
-      <c r="L37" s="17"/>
-      <c r="M37" s="17"/>
-      <c r="N37" s="17"/>
-      <c r="O37" s="17"/>
-      <c r="P37" s="17"/>
-      <c r="Q37" s="17"/>
-      <c r="R37" s="17"/>
-      <c r="S37" s="17"/>
-      <c r="T37" s="17"/>
-      <c r="U37" s="17"/>
-      <c r="V37" s="17"/>
+      <c r="A37" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="B37" s="21"/>
+      <c r="C37" s="21"/>
+      <c r="D37" s="21"/>
+      <c r="E37" s="21"/>
+      <c r="F37" s="21"/>
+      <c r="G37" s="21"/>
+      <c r="H37" s="21"/>
+      <c r="I37" s="21"/>
+      <c r="J37" s="21"/>
+      <c r="K37" s="21"/>
+      <c r="L37" s="21"/>
+      <c r="M37" s="21"/>
+      <c r="N37" s="21"/>
+      <c r="O37" s="21"/>
+      <c r="P37" s="21"/>
+      <c r="Q37" s="21"/>
+      <c r="R37" s="21"/>
+      <c r="S37" s="21"/>
+      <c r="T37" s="21"/>
+      <c r="U37" s="21"/>
+      <c r="V37" s="21"/>
+      <c r="W37" s="21"/>
+      <c r="X37" s="21"/>
+      <c r="Y37" s="21"/>
+      <c r="Z37" s="21"/>
+      <c r="AA37" s="21"/>
+      <c r="AB37" s="21"/>
+      <c r="AC37" s="21"/>
+      <c r="AD37" s="21"/>
+      <c r="AE37" s="21"/>
+      <c r="AF37" s="21"/>
+      <c r="AG37" s="21"/>
+      <c r="AH37" s="21"/>
+      <c r="AI37" s="21"/>
+      <c r="AJ37" s="21"/>
+      <c r="AK37" s="21"/>
+      <c r="AL37" s="21"/>
+      <c r="AM37" s="21"/>
+      <c r="AN37" s="21"/>
+      <c r="AO37" s="21"/>
+      <c r="AP37" s="21"/>
+      <c r="AQ37" s="21"/>
+      <c r="AR37" s="21"/>
+      <c r="AS37" s="21"/>
+      <c r="AT37" s="21"/>
+      <c r="AU37" s="21"/>
+      <c r="AV37" s="21"/>
+      <c r="AW37" s="21"/>
+      <c r="AX37" s="21"/>
+      <c r="AY37" s="21"/>
+      <c r="AZ37" s="21"/>
+      <c r="BA37" s="21"/>
+      <c r="BB37" s="21"/>
+      <c r="BC37" s="21"/>
+      <c r="BD37" s="21"/>
+      <c r="BE37" s="21"/>
+      <c r="BF37" s="21"/>
+      <c r="BG37" s="21"/>
+      <c r="BH37" s="21"/>
+      <c r="BI37" s="21"/>
+      <c r="BJ37" s="21"/>
+      <c r="BK37" s="21"/>
+      <c r="BL37" s="21"/>
+      <c r="BM37" s="21"/>
     </row>
-    <row r="38" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="18" t="s">
-        <v>202</v>
-      </c>
-      <c r="B38" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C38" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D38" s="18" t="s">
-        <v>203</v>
-      </c>
-      <c r="E38" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F38" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="G38" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="H38" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="I38" s="18" t="s">
-        <v>204</v>
-      </c>
-      <c r="J38" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="K38" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="L38" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="M38" s="18" t="s">
-        <v>205</v>
-      </c>
-      <c r="N38" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="O38" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="P38" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q38" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="R38" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="S38" s="18" t="s">
-        <v>206</v>
-      </c>
-      <c r="T38" s="18" t="s">
-        <v>207</v>
-      </c>
-      <c r="U38" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="V38" s="18" t="s">
-        <v>37</v>
-      </c>
+    <row r="38" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="K38" s="4"/>
+      <c r="L38" s="4"/>
+      <c r="M38" s="4"/>
+      <c r="N38" s="4"/>
+      <c r="O38" s="4"/>
+      <c r="P38" s="4"/>
+      <c r="Q38" s="4"/>
+      <c r="R38" s="4"/>
+      <c r="S38" s="4"/>
+      <c r="T38" s="4"/>
+      <c r="U38" s="4"/>
+      <c r="V38" s="4"/>
+      <c r="W38" s="4"/>
+      <c r="X38" s="4"/>
+      <c r="Y38" s="4"/>
+      <c r="Z38" s="4"/>
+      <c r="AA38" s="4"/>
+      <c r="AB38" s="4"/>
+      <c r="AC38" s="4"/>
+      <c r="AD38" s="4"/>
+      <c r="AE38" s="4"/>
+      <c r="AF38" s="4"/>
+      <c r="AG38" s="4"/>
+      <c r="AH38" s="4"/>
+      <c r="AI38" s="4"/>
+      <c r="AJ38" s="4"/>
+      <c r="AK38" s="4"/>
+      <c r="AL38" s="4"/>
+      <c r="AM38" s="4"/>
+      <c r="AN38" s="4"/>
+      <c r="AO38" s="4"/>
+      <c r="AP38" s="4"/>
+      <c r="AQ38" s="4"/>
+      <c r="AR38" s="4"/>
+      <c r="AS38" s="4"/>
+      <c r="AT38" s="4"/>
+      <c r="AU38" s="4"/>
+      <c r="AV38" s="4"/>
+      <c r="AW38" s="4"/>
+      <c r="AX38" s="4"/>
+      <c r="AY38" s="4"/>
+      <c r="AZ38" s="4"/>
+      <c r="BA38" s="4"/>
+      <c r="BB38" s="4"/>
+      <c r="BC38" s="4"/>
+      <c r="BD38" s="4"/>
+      <c r="BE38" s="4"/>
+      <c r="BF38" s="4"/>
+      <c r="BG38" s="4"/>
+      <c r="BH38" s="4"/>
+      <c r="BI38" s="4"/>
+      <c r="BJ38" s="4"/>
+      <c r="BK38" s="4"/>
+      <c r="BL38" s="4"/>
+      <c r="BM38" s="4"/>
     </row>
     <row r="39" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="19" t="n">
-        <v>31</v>
-      </c>
-      <c r="B39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C39" s="19" t="n">
-        <v>365</v>
-      </c>
-      <c r="D39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" s="19" t="n">
-        <v>596.71</v>
-      </c>
-      <c r="F39" s="19" t="n">
-        <v>60893.69</v>
-      </c>
-      <c r="G39" s="19" t="n">
-        <v>4009.79</v>
-      </c>
-      <c r="H39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" s="19" t="n">
-        <v>66868.29</v>
-      </c>
-      <c r="L39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" s="20" t="n">
-        <v>0.204542</v>
-      </c>
-      <c r="S39" s="19" t="n">
-        <v>65906.58</v>
-      </c>
-      <c r="T39" s="19" t="n">
-        <v>66868.29</v>
-      </c>
-      <c r="U39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" s="19" t="n">
-        <v>0</v>
-      </c>
+      <c r="A39" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B39" s="4"/>
+      <c r="C39" s="4"/>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+      <c r="K39" s="4"/>
+      <c r="L39" s="4"/>
+      <c r="M39" s="4"/>
+      <c r="N39" s="4"/>
+      <c r="O39" s="4"/>
+      <c r="P39" s="4"/>
+      <c r="Q39" s="4"/>
+      <c r="R39" s="4"/>
+      <c r="S39" s="4"/>
+      <c r="T39" s="4"/>
+      <c r="U39" s="4"/>
+      <c r="V39" s="4"/>
+      <c r="W39" s="4"/>
+      <c r="X39" s="4"/>
+      <c r="Y39" s="4"/>
+      <c r="Z39" s="4"/>
+      <c r="AA39" s="4"/>
+      <c r="AB39" s="4"/>
+      <c r="AC39" s="4"/>
+      <c r="AD39" s="4"/>
+      <c r="AE39" s="4"/>
+      <c r="AF39" s="4"/>
+      <c r="AG39" s="4"/>
+      <c r="AH39" s="4"/>
+      <c r="AI39" s="4"/>
+      <c r="AJ39" s="4"/>
+      <c r="AK39" s="4"/>
+      <c r="AL39" s="4"/>
+      <c r="AM39" s="4"/>
+      <c r="AN39" s="4"/>
+      <c r="AO39" s="4"/>
+      <c r="AP39" s="4"/>
+      <c r="AQ39" s="4"/>
+      <c r="AR39" s="4"/>
+      <c r="AS39" s="4"/>
+      <c r="AT39" s="4"/>
+      <c r="AU39" s="4"/>
+      <c r="AV39" s="4"/>
+      <c r="AW39" s="4"/>
+      <c r="AX39" s="4"/>
+      <c r="AY39" s="4"/>
+      <c r="AZ39" s="4"/>
+      <c r="BA39" s="4"/>
+      <c r="BB39" s="4"/>
+      <c r="BC39" s="4"/>
+      <c r="BD39" s="4"/>
+      <c r="BE39" s="4"/>
+      <c r="BF39" s="4"/>
+      <c r="BG39" s="4"/>
+      <c r="BH39" s="4"/>
+      <c r="BI39" s="4"/>
+      <c r="BJ39" s="4"/>
+      <c r="BK39" s="4"/>
+      <c r="BL39" s="4"/>
+      <c r="BM39" s="4"/>
     </row>
-    <row r="40" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="B40" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C40" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="D40" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E40" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="F40" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="G40" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="H40" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="I40" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="J40" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="K40" s="18" t="s">
-        <v>208</v>
-      </c>
-      <c r="L40" s="18" t="s">
-        <v>209</v>
-      </c>
-      <c r="M40" s="18" t="s">
-        <v>210</v>
-      </c>
+    <row r="40" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="K40" s="4"/>
+      <c r="L40" s="4"/>
+      <c r="M40" s="4"/>
+      <c r="N40" s="4"/>
+      <c r="O40" s="4"/>
+      <c r="P40" s="4"/>
+      <c r="Q40" s="4"/>
+      <c r="R40" s="4"/>
+      <c r="S40" s="4"/>
+      <c r="T40" s="4"/>
+      <c r="U40" s="4"/>
+      <c r="V40" s="4"/>
+      <c r="W40" s="4"/>
+      <c r="X40" s="4"/>
+      <c r="Y40" s="4"/>
+      <c r="Z40" s="4"/>
+      <c r="AA40" s="4"/>
+      <c r="AB40" s="4"/>
+      <c r="AC40" s="4"/>
+      <c r="AD40" s="4"/>
+      <c r="AE40" s="4"/>
+      <c r="AF40" s="4"/>
+      <c r="AG40" s="4"/>
+      <c r="AH40" s="4"/>
+      <c r="AI40" s="4"/>
+      <c r="AJ40" s="4"/>
+      <c r="AK40" s="4"/>
+      <c r="AL40" s="4"/>
+      <c r="AM40" s="4"/>
+      <c r="AN40" s="4"/>
+      <c r="AO40" s="4"/>
+      <c r="AP40" s="4"/>
+      <c r="AQ40" s="4"/>
+      <c r="AR40" s="4"/>
+      <c r="AS40" s="4"/>
+      <c r="AT40" s="4"/>
+      <c r="AU40" s="4"/>
+      <c r="AV40" s="4"/>
+      <c r="AW40" s="4"/>
+      <c r="AX40" s="4"/>
+      <c r="AY40" s="4"/>
+      <c r="AZ40" s="4"/>
+      <c r="BA40" s="4"/>
+      <c r="BB40" s="4"/>
+      <c r="BC40" s="4"/>
+      <c r="BD40" s="4"/>
+      <c r="BE40" s="4"/>
+      <c r="BF40" s="4"/>
+      <c r="BG40" s="4"/>
+      <c r="BH40" s="4"/>
+      <c r="BI40" s="4"/>
+      <c r="BJ40" s="4"/>
+      <c r="BK40" s="4"/>
+      <c r="BL40" s="4"/>
+      <c r="BM40" s="4"/>
     </row>
     <row r="41" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="19" t="n">
-        <v>207.64</v>
-      </c>
-      <c r="B41" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C41" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" s="19" t="n">
-        <v>31.04</v>
-      </c>
-      <c r="E41" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" s="19" t="n">
-        <v>0</v>
-      </c>
+      <c r="A41" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="K41" s="4"/>
+      <c r="L41" s="4"/>
+      <c r="M41" s="4"/>
+      <c r="N41" s="4"/>
+      <c r="O41" s="4"/>
+      <c r="P41" s="4"/>
+      <c r="Q41" s="4"/>
+      <c r="R41" s="4"/>
+      <c r="S41" s="4"/>
+      <c r="T41" s="4"/>
+      <c r="U41" s="4"/>
+      <c r="V41" s="4"/>
+      <c r="W41" s="4"/>
+      <c r="X41" s="4"/>
+      <c r="Y41" s="4"/>
+      <c r="Z41" s="4"/>
+      <c r="AA41" s="4"/>
+      <c r="AB41" s="4"/>
+      <c r="AC41" s="4"/>
+      <c r="AD41" s="4"/>
+      <c r="AE41" s="4"/>
+      <c r="AF41" s="4"/>
+      <c r="AG41" s="4"/>
+      <c r="AH41" s="4"/>
+      <c r="AI41" s="4"/>
+      <c r="AJ41" s="4"/>
+      <c r="AK41" s="4"/>
+      <c r="AL41" s="4"/>
+      <c r="AM41" s="4"/>
+      <c r="AN41" s="4"/>
+      <c r="AO41" s="4"/>
+      <c r="AP41" s="4"/>
+      <c r="AQ41" s="4"/>
+      <c r="AR41" s="4"/>
+      <c r="AS41" s="4"/>
+      <c r="AT41" s="4"/>
+      <c r="AU41" s="4"/>
+      <c r="AV41" s="4"/>
+      <c r="AW41" s="4"/>
+      <c r="AX41" s="4"/>
+      <c r="AY41" s="4"/>
+      <c r="AZ41" s="4"/>
+      <c r="BA41" s="4"/>
+      <c r="BB41" s="4"/>
+      <c r="BC41" s="4"/>
+      <c r="BD41" s="4"/>
+      <c r="BE41" s="4"/>
+      <c r="BF41" s="4"/>
+      <c r="BG41" s="4"/>
+      <c r="BH41" s="4"/>
+      <c r="BI41" s="4"/>
+      <c r="BJ41" s="4"/>
+      <c r="BK41" s="4"/>
+      <c r="BL41" s="4"/>
+      <c r="BM41" s="4"/>
     </row>
     <row r="42" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="4"/>
+      <c r="A42" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B42" s="4"/>
+      <c r="C42" s="4"/>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4"/>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+      <c r="K42" s="4"/>
+      <c r="L42" s="4"/>
+      <c r="M42" s="4"/>
+      <c r="N42" s="4"/>
+      <c r="O42" s="4"/>
+      <c r="P42" s="4"/>
+      <c r="Q42" s="4"/>
+      <c r="R42" s="4"/>
+      <c r="S42" s="4"/>
+      <c r="T42" s="4"/>
+      <c r="U42" s="4"/>
+      <c r="V42" s="4"/>
+      <c r="W42" s="4"/>
+      <c r="X42" s="4"/>
+      <c r="Y42" s="4"/>
+      <c r="Z42" s="4"/>
+      <c r="AA42" s="4"/>
+      <c r="AB42" s="4"/>
+      <c r="AC42" s="4"/>
+      <c r="AD42" s="4"/>
+      <c r="AE42" s="4"/>
+      <c r="AF42" s="4"/>
+      <c r="AG42" s="4"/>
+      <c r="AH42" s="4"/>
+      <c r="AI42" s="4"/>
+      <c r="AJ42" s="4"/>
+      <c r="AK42" s="4"/>
+      <c r="AL42" s="4"/>
+      <c r="AM42" s="4"/>
+      <c r="AN42" s="4"/>
+      <c r="AO42" s="4"/>
+      <c r="AP42" s="4"/>
+      <c r="AQ42" s="4"/>
+      <c r="AR42" s="4"/>
+      <c r="AS42" s="4"/>
+      <c r="AT42" s="4"/>
+      <c r="AU42" s="4"/>
+      <c r="AV42" s="4"/>
+      <c r="AW42" s="4"/>
+      <c r="AX42" s="4"/>
+      <c r="AY42" s="4"/>
+      <c r="AZ42" s="4"/>
+      <c r="BA42" s="4"/>
+      <c r="BB42" s="4"/>
+      <c r="BC42" s="4"/>
+      <c r="BD42" s="4"/>
+      <c r="BE42" s="4"/>
+      <c r="BF42" s="4"/>
+      <c r="BG42" s="4"/>
+      <c r="BH42" s="4"/>
+      <c r="BI42" s="4"/>
+      <c r="BJ42" s="4"/>
+      <c r="BK42" s="4"/>
+      <c r="BL42" s="4"/>
+      <c r="BM42" s="4"/>
     </row>
-    <row r="43" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="21" t="s">
-        <v>211</v>
-      </c>
-      <c r="B43" s="21"/>
-      <c r="C43" s="21"/>
-      <c r="D43" s="21"/>
-      <c r="E43" s="21"/>
-      <c r="F43" s="21"/>
-      <c r="G43" s="21"/>
-      <c r="H43" s="21"/>
-      <c r="I43" s="21"/>
-      <c r="J43" s="21"/>
-      <c r="K43" s="21"/>
-      <c r="L43" s="21"/>
-      <c r="M43" s="21"/>
-      <c r="N43" s="21"/>
-      <c r="O43" s="21"/>
-      <c r="P43" s="21"/>
-      <c r="Q43" s="21"/>
-      <c r="R43" s="21"/>
-      <c r="S43" s="21"/>
-      <c r="T43" s="21"/>
-      <c r="U43" s="21"/>
-      <c r="V43" s="21"/>
-      <c r="W43" s="21"/>
-      <c r="X43" s="21"/>
-      <c r="Y43" s="21"/>
-      <c r="Z43" s="21"/>
-      <c r="AA43" s="21"/>
-      <c r="AB43" s="21"/>
-      <c r="AC43" s="21"/>
-      <c r="AD43" s="21"/>
-      <c r="AE43" s="21"/>
-      <c r="AF43" s="21"/>
-      <c r="AG43" s="21"/>
-      <c r="AH43" s="21"/>
-      <c r="AI43" s="21"/>
-      <c r="AJ43" s="21"/>
-      <c r="AK43" s="21"/>
-      <c r="AL43" s="21"/>
-      <c r="AM43" s="21"/>
-      <c r="AN43" s="21"/>
-      <c r="AO43" s="21"/>
-      <c r="AP43" s="21"/>
-      <c r="AQ43" s="21"/>
-      <c r="AR43" s="21"/>
-      <c r="AS43" s="21"/>
-      <c r="AT43" s="21"/>
-      <c r="AU43" s="21"/>
-      <c r="AV43" s="21"/>
-      <c r="AW43" s="21"/>
-      <c r="AX43" s="21"/>
-      <c r="AY43" s="21"/>
-      <c r="AZ43" s="21"/>
-      <c r="BA43" s="21"/>
-      <c r="BB43" s="21"/>
-      <c r="BC43" s="21"/>
-      <c r="BD43" s="21"/>
-      <c r="BE43" s="21"/>
-      <c r="BF43" s="21"/>
-      <c r="BG43" s="21"/>
-      <c r="BH43" s="21"/>
-      <c r="BI43" s="21"/>
-      <c r="BJ43" s="21"/>
-      <c r="BK43" s="21"/>
-      <c r="BL43" s="21"/>
-      <c r="BM43" s="21"/>
+    <row r="43" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B43" s="4"/>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="K43" s="4"/>
+      <c r="L43" s="4"/>
+      <c r="M43" s="4"/>
+      <c r="N43" s="4"/>
+      <c r="O43" s="4"/>
+      <c r="P43" s="4"/>
+      <c r="Q43" s="4"/>
+      <c r="R43" s="4"/>
+      <c r="S43" s="4"/>
+      <c r="T43" s="4"/>
+      <c r="U43" s="4"/>
+      <c r="V43" s="4"/>
+      <c r="W43" s="4"/>
+      <c r="X43" s="4"/>
+      <c r="Y43" s="4"/>
+      <c r="Z43" s="4"/>
+      <c r="AA43" s="4"/>
+      <c r="AB43" s="4"/>
+      <c r="AC43" s="4"/>
+      <c r="AD43" s="4"/>
+      <c r="AE43" s="4"/>
+      <c r="AF43" s="4"/>
+      <c r="AG43" s="4"/>
+      <c r="AH43" s="4"/>
+      <c r="AI43" s="4"/>
+      <c r="AJ43" s="4"/>
+      <c r="AK43" s="4"/>
+      <c r="AL43" s="4"/>
+      <c r="AM43" s="4"/>
+      <c r="AN43" s="4"/>
+      <c r="AO43" s="4"/>
+      <c r="AP43" s="4"/>
+      <c r="AQ43" s="4"/>
+      <c r="AR43" s="4"/>
+      <c r="AS43" s="4"/>
+      <c r="AT43" s="4"/>
+      <c r="AU43" s="4"/>
+      <c r="AV43" s="4"/>
+      <c r="AW43" s="4"/>
+      <c r="AX43" s="4"/>
+      <c r="AY43" s="4"/>
+      <c r="AZ43" s="4"/>
+      <c r="BA43" s="4"/>
+      <c r="BB43" s="4"/>
+      <c r="BC43" s="4"/>
+      <c r="BD43" s="4"/>
+      <c r="BE43" s="4"/>
+      <c r="BF43" s="4"/>
+      <c r="BG43" s="4"/>
+      <c r="BH43" s="4"/>
+      <c r="BI43" s="4"/>
+      <c r="BJ43" s="4"/>
+      <c r="BK43" s="4"/>
+      <c r="BL43" s="4"/>
+      <c r="BM43" s="4"/>
     </row>
     <row r="44" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="s">
-        <v>74</v>
+        <v>195</v>
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
@@ -23549,7 +22754,7 @@
     </row>
     <row r="45" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="4" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
@@ -23618,7 +22823,7 @@
     </row>
     <row r="46" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="4" t="s">
-        <v>213</v>
+        <v>197</v>
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
@@ -23687,7 +22892,7 @@
     </row>
     <row r="47" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="s">
-        <v>214</v>
+        <v>198</v>
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
@@ -23754,422 +22959,8 @@
       <c r="BL47" s="4"/>
       <c r="BM47" s="4"/>
     </row>
-    <row r="48" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B48" s="4"/>
-      <c r="C48" s="4"/>
-      <c r="D48" s="4"/>
-      <c r="E48" s="4"/>
-      <c r="F48" s="4"/>
-      <c r="G48" s="4"/>
-      <c r="H48" s="4"/>
-      <c r="I48" s="4"/>
-      <c r="J48" s="4"/>
-      <c r="K48" s="4"/>
-      <c r="L48" s="4"/>
-      <c r="M48" s="4"/>
-      <c r="N48" s="4"/>
-      <c r="O48" s="4"/>
-      <c r="P48" s="4"/>
-      <c r="Q48" s="4"/>
-      <c r="R48" s="4"/>
-      <c r="S48" s="4"/>
-      <c r="T48" s="4"/>
-      <c r="U48" s="4"/>
-      <c r="V48" s="4"/>
-      <c r="W48" s="4"/>
-      <c r="X48" s="4"/>
-      <c r="Y48" s="4"/>
-      <c r="Z48" s="4"/>
-      <c r="AA48" s="4"/>
-      <c r="AB48" s="4"/>
-      <c r="AC48" s="4"/>
-      <c r="AD48" s="4"/>
-      <c r="AE48" s="4"/>
-      <c r="AF48" s="4"/>
-      <c r="AG48" s="4"/>
-      <c r="AH48" s="4"/>
-      <c r="AI48" s="4"/>
-      <c r="AJ48" s="4"/>
-      <c r="AK48" s="4"/>
-      <c r="AL48" s="4"/>
-      <c r="AM48" s="4"/>
-      <c r="AN48" s="4"/>
-      <c r="AO48" s="4"/>
-      <c r="AP48" s="4"/>
-      <c r="AQ48" s="4"/>
-      <c r="AR48" s="4"/>
-      <c r="AS48" s="4"/>
-      <c r="AT48" s="4"/>
-      <c r="AU48" s="4"/>
-      <c r="AV48" s="4"/>
-      <c r="AW48" s="4"/>
-      <c r="AX48" s="4"/>
-      <c r="AY48" s="4"/>
-      <c r="AZ48" s="4"/>
-      <c r="BA48" s="4"/>
-      <c r="BB48" s="4"/>
-      <c r="BC48" s="4"/>
-      <c r="BD48" s="4"/>
-      <c r="BE48" s="4"/>
-      <c r="BF48" s="4"/>
-      <c r="BG48" s="4"/>
-      <c r="BH48" s="4"/>
-      <c r="BI48" s="4"/>
-      <c r="BJ48" s="4"/>
-      <c r="BK48" s="4"/>
-      <c r="BL48" s="4"/>
-      <c r="BM48" s="4"/>
-    </row>
-    <row r="49" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="B49" s="4"/>
-      <c r="C49" s="4"/>
-      <c r="D49" s="4"/>
-      <c r="E49" s="4"/>
-      <c r="F49" s="4"/>
-      <c r="G49" s="4"/>
-      <c r="H49" s="4"/>
-      <c r="I49" s="4"/>
-      <c r="J49" s="4"/>
-      <c r="K49" s="4"/>
-      <c r="L49" s="4"/>
-      <c r="M49" s="4"/>
-      <c r="N49" s="4"/>
-      <c r="O49" s="4"/>
-      <c r="P49" s="4"/>
-      <c r="Q49" s="4"/>
-      <c r="R49" s="4"/>
-      <c r="S49" s="4"/>
-      <c r="T49" s="4"/>
-      <c r="U49" s="4"/>
-      <c r="V49" s="4"/>
-      <c r="W49" s="4"/>
-      <c r="X49" s="4"/>
-      <c r="Y49" s="4"/>
-      <c r="Z49" s="4"/>
-      <c r="AA49" s="4"/>
-      <c r="AB49" s="4"/>
-      <c r="AC49" s="4"/>
-      <c r="AD49" s="4"/>
-      <c r="AE49" s="4"/>
-      <c r="AF49" s="4"/>
-      <c r="AG49" s="4"/>
-      <c r="AH49" s="4"/>
-      <c r="AI49" s="4"/>
-      <c r="AJ49" s="4"/>
-      <c r="AK49" s="4"/>
-      <c r="AL49" s="4"/>
-      <c r="AM49" s="4"/>
-      <c r="AN49" s="4"/>
-      <c r="AO49" s="4"/>
-      <c r="AP49" s="4"/>
-      <c r="AQ49" s="4"/>
-      <c r="AR49" s="4"/>
-      <c r="AS49" s="4"/>
-      <c r="AT49" s="4"/>
-      <c r="AU49" s="4"/>
-      <c r="AV49" s="4"/>
-      <c r="AW49" s="4"/>
-      <c r="AX49" s="4"/>
-      <c r="AY49" s="4"/>
-      <c r="AZ49" s="4"/>
-      <c r="BA49" s="4"/>
-      <c r="BB49" s="4"/>
-      <c r="BC49" s="4"/>
-      <c r="BD49" s="4"/>
-      <c r="BE49" s="4"/>
-      <c r="BF49" s="4"/>
-      <c r="BG49" s="4"/>
-      <c r="BH49" s="4"/>
-      <c r="BI49" s="4"/>
-      <c r="BJ49" s="4"/>
-      <c r="BK49" s="4"/>
-      <c r="BL49" s="4"/>
-      <c r="BM49" s="4"/>
-    </row>
-    <row r="50" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="B50" s="4"/>
-      <c r="C50" s="4"/>
-      <c r="D50" s="4"/>
-      <c r="E50" s="4"/>
-      <c r="F50" s="4"/>
-      <c r="G50" s="4"/>
-      <c r="H50" s="4"/>
-      <c r="I50" s="4"/>
-      <c r="J50" s="4"/>
-      <c r="K50" s="4"/>
-      <c r="L50" s="4"/>
-      <c r="M50" s="4"/>
-      <c r="N50" s="4"/>
-      <c r="O50" s="4"/>
-      <c r="P50" s="4"/>
-      <c r="Q50" s="4"/>
-      <c r="R50" s="4"/>
-      <c r="S50" s="4"/>
-      <c r="T50" s="4"/>
-      <c r="U50" s="4"/>
-      <c r="V50" s="4"/>
-      <c r="W50" s="4"/>
-      <c r="X50" s="4"/>
-      <c r="Y50" s="4"/>
-      <c r="Z50" s="4"/>
-      <c r="AA50" s="4"/>
-      <c r="AB50" s="4"/>
-      <c r="AC50" s="4"/>
-      <c r="AD50" s="4"/>
-      <c r="AE50" s="4"/>
-      <c r="AF50" s="4"/>
-      <c r="AG50" s="4"/>
-      <c r="AH50" s="4"/>
-      <c r="AI50" s="4"/>
-      <c r="AJ50" s="4"/>
-      <c r="AK50" s="4"/>
-      <c r="AL50" s="4"/>
-      <c r="AM50" s="4"/>
-      <c r="AN50" s="4"/>
-      <c r="AO50" s="4"/>
-      <c r="AP50" s="4"/>
-      <c r="AQ50" s="4"/>
-      <c r="AR50" s="4"/>
-      <c r="AS50" s="4"/>
-      <c r="AT50" s="4"/>
-      <c r="AU50" s="4"/>
-      <c r="AV50" s="4"/>
-      <c r="AW50" s="4"/>
-      <c r="AX50" s="4"/>
-      <c r="AY50" s="4"/>
-      <c r="AZ50" s="4"/>
-      <c r="BA50" s="4"/>
-      <c r="BB50" s="4"/>
-      <c r="BC50" s="4"/>
-      <c r="BD50" s="4"/>
-      <c r="BE50" s="4"/>
-      <c r="BF50" s="4"/>
-      <c r="BG50" s="4"/>
-      <c r="BH50" s="4"/>
-      <c r="BI50" s="4"/>
-      <c r="BJ50" s="4"/>
-      <c r="BK50" s="4"/>
-      <c r="BL50" s="4"/>
-      <c r="BM50" s="4"/>
-    </row>
-    <row r="51" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="B51" s="4"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="4"/>
-      <c r="E51" s="4"/>
-      <c r="F51" s="4"/>
-      <c r="G51" s="4"/>
-      <c r="H51" s="4"/>
-      <c r="I51" s="4"/>
-      <c r="J51" s="4"/>
-      <c r="K51" s="4"/>
-      <c r="L51" s="4"/>
-      <c r="M51" s="4"/>
-      <c r="N51" s="4"/>
-      <c r="O51" s="4"/>
-      <c r="P51" s="4"/>
-      <c r="Q51" s="4"/>
-      <c r="R51" s="4"/>
-      <c r="S51" s="4"/>
-      <c r="T51" s="4"/>
-      <c r="U51" s="4"/>
-      <c r="V51" s="4"/>
-      <c r="W51" s="4"/>
-      <c r="X51" s="4"/>
-      <c r="Y51" s="4"/>
-      <c r="Z51" s="4"/>
-      <c r="AA51" s="4"/>
-      <c r="AB51" s="4"/>
-      <c r="AC51" s="4"/>
-      <c r="AD51" s="4"/>
-      <c r="AE51" s="4"/>
-      <c r="AF51" s="4"/>
-      <c r="AG51" s="4"/>
-      <c r="AH51" s="4"/>
-      <c r="AI51" s="4"/>
-      <c r="AJ51" s="4"/>
-      <c r="AK51" s="4"/>
-      <c r="AL51" s="4"/>
-      <c r="AM51" s="4"/>
-      <c r="AN51" s="4"/>
-      <c r="AO51" s="4"/>
-      <c r="AP51" s="4"/>
-      <c r="AQ51" s="4"/>
-      <c r="AR51" s="4"/>
-      <c r="AS51" s="4"/>
-      <c r="AT51" s="4"/>
-      <c r="AU51" s="4"/>
-      <c r="AV51" s="4"/>
-      <c r="AW51" s="4"/>
-      <c r="AX51" s="4"/>
-      <c r="AY51" s="4"/>
-      <c r="AZ51" s="4"/>
-      <c r="BA51" s="4"/>
-      <c r="BB51" s="4"/>
-      <c r="BC51" s="4"/>
-      <c r="BD51" s="4"/>
-      <c r="BE51" s="4"/>
-      <c r="BF51" s="4"/>
-      <c r="BG51" s="4"/>
-      <c r="BH51" s="4"/>
-      <c r="BI51" s="4"/>
-      <c r="BJ51" s="4"/>
-      <c r="BK51" s="4"/>
-      <c r="BL51" s="4"/>
-      <c r="BM51" s="4"/>
-    </row>
-    <row r="52" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="B52" s="4"/>
-      <c r="C52" s="4"/>
-      <c r="D52" s="4"/>
-      <c r="E52" s="4"/>
-      <c r="F52" s="4"/>
-      <c r="G52" s="4"/>
-      <c r="H52" s="4"/>
-      <c r="I52" s="4"/>
-      <c r="J52" s="4"/>
-      <c r="K52" s="4"/>
-      <c r="L52" s="4"/>
-      <c r="M52" s="4"/>
-      <c r="N52" s="4"/>
-      <c r="O52" s="4"/>
-      <c r="P52" s="4"/>
-      <c r="Q52" s="4"/>
-      <c r="R52" s="4"/>
-      <c r="S52" s="4"/>
-      <c r="T52" s="4"/>
-      <c r="U52" s="4"/>
-      <c r="V52" s="4"/>
-      <c r="W52" s="4"/>
-      <c r="X52" s="4"/>
-      <c r="Y52" s="4"/>
-      <c r="Z52" s="4"/>
-      <c r="AA52" s="4"/>
-      <c r="AB52" s="4"/>
-      <c r="AC52" s="4"/>
-      <c r="AD52" s="4"/>
-      <c r="AE52" s="4"/>
-      <c r="AF52" s="4"/>
-      <c r="AG52" s="4"/>
-      <c r="AH52" s="4"/>
-      <c r="AI52" s="4"/>
-      <c r="AJ52" s="4"/>
-      <c r="AK52" s="4"/>
-      <c r="AL52" s="4"/>
-      <c r="AM52" s="4"/>
-      <c r="AN52" s="4"/>
-      <c r="AO52" s="4"/>
-      <c r="AP52" s="4"/>
-      <c r="AQ52" s="4"/>
-      <c r="AR52" s="4"/>
-      <c r="AS52" s="4"/>
-      <c r="AT52" s="4"/>
-      <c r="AU52" s="4"/>
-      <c r="AV52" s="4"/>
-      <c r="AW52" s="4"/>
-      <c r="AX52" s="4"/>
-      <c r="AY52" s="4"/>
-      <c r="AZ52" s="4"/>
-      <c r="BA52" s="4"/>
-      <c r="BB52" s="4"/>
-      <c r="BC52" s="4"/>
-      <c r="BD52" s="4"/>
-      <c r="BE52" s="4"/>
-      <c r="BF52" s="4"/>
-      <c r="BG52" s="4"/>
-      <c r="BH52" s="4"/>
-      <c r="BI52" s="4"/>
-      <c r="BJ52" s="4"/>
-      <c r="BK52" s="4"/>
-      <c r="BL52" s="4"/>
-      <c r="BM52" s="4"/>
-    </row>
-    <row r="53" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="B53" s="4"/>
-      <c r="C53" s="4"/>
-      <c r="D53" s="4"/>
-      <c r="E53" s="4"/>
-      <c r="F53" s="4"/>
-      <c r="G53" s="4"/>
-      <c r="H53" s="4"/>
-      <c r="I53" s="4"/>
-      <c r="J53" s="4"/>
-      <c r="K53" s="4"/>
-      <c r="L53" s="4"/>
-      <c r="M53" s="4"/>
-      <c r="N53" s="4"/>
-      <c r="O53" s="4"/>
-      <c r="P53" s="4"/>
-      <c r="Q53" s="4"/>
-      <c r="R53" s="4"/>
-      <c r="S53" s="4"/>
-      <c r="T53" s="4"/>
-      <c r="U53" s="4"/>
-      <c r="V53" s="4"/>
-      <c r="W53" s="4"/>
-      <c r="X53" s="4"/>
-      <c r="Y53" s="4"/>
-      <c r="Z53" s="4"/>
-      <c r="AA53" s="4"/>
-      <c r="AB53" s="4"/>
-      <c r="AC53" s="4"/>
-      <c r="AD53" s="4"/>
-      <c r="AE53" s="4"/>
-      <c r="AF53" s="4"/>
-      <c r="AG53" s="4"/>
-      <c r="AH53" s="4"/>
-      <c r="AI53" s="4"/>
-      <c r="AJ53" s="4"/>
-      <c r="AK53" s="4"/>
-      <c r="AL53" s="4"/>
-      <c r="AM53" s="4"/>
-      <c r="AN53" s="4"/>
-      <c r="AO53" s="4"/>
-      <c r="AP53" s="4"/>
-      <c r="AQ53" s="4"/>
-      <c r="AR53" s="4"/>
-      <c r="AS53" s="4"/>
-      <c r="AT53" s="4"/>
-      <c r="AU53" s="4"/>
-      <c r="AV53" s="4"/>
-      <c r="AW53" s="4"/>
-      <c r="AX53" s="4"/>
-      <c r="AY53" s="4"/>
-      <c r="AZ53" s="4"/>
-      <c r="BA53" s="4"/>
-      <c r="BB53" s="4"/>
-      <c r="BC53" s="4"/>
-      <c r="BD53" s="4"/>
-      <c r="BE53" s="4"/>
-      <c r="BF53" s="4"/>
-      <c r="BG53" s="4"/>
-      <c r="BH53" s="4"/>
-      <c r="BI53" s="4"/>
-      <c r="BJ53" s="4"/>
-      <c r="BK53" s="4"/>
-      <c r="BL53" s="4"/>
-      <c r="BM53" s="4"/>
-    </row>
   </sheetData>
-  <mergeCells count="47">
+  <mergeCells count="41">
     <mergeCell ref="A1:BI1"/>
     <mergeCell ref="BJ1:BM1"/>
     <mergeCell ref="A2:BM2"/>
@@ -24199,24 +22990,18 @@
     <mergeCell ref="B27:E27"/>
     <mergeCell ref="B28:E28"/>
     <mergeCell ref="B29:E29"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="B31:E31"/>
-    <mergeCell ref="B32:E32"/>
-    <mergeCell ref="B33:E33"/>
-    <mergeCell ref="B34:E34"/>
-    <mergeCell ref="B35:E35"/>
-    <mergeCell ref="A37:V37"/>
+    <mergeCell ref="A31:V31"/>
+    <mergeCell ref="A37:BM37"/>
+    <mergeCell ref="A38:BM38"/>
+    <mergeCell ref="A39:BM39"/>
+    <mergeCell ref="A40:BM40"/>
+    <mergeCell ref="A41:BM41"/>
+    <mergeCell ref="A42:BM42"/>
     <mergeCell ref="A43:BM43"/>
     <mergeCell ref="A44:BM44"/>
     <mergeCell ref="A45:BM45"/>
     <mergeCell ref="A46:BM46"/>
     <mergeCell ref="A47:BM47"/>
-    <mergeCell ref="A48:BM48"/>
-    <mergeCell ref="A49:BM49"/>
-    <mergeCell ref="A50:BM50"/>
-    <mergeCell ref="A51:BM51"/>
-    <mergeCell ref="A52:BM52"/>
-    <mergeCell ref="A53:BM53"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>

--- a/tratando_tabelas/finitura/entradas_finitura.xlsx
+++ b/tratando_tabelas/finitura/entradas_finitura.xlsx
@@ -20,12 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1112" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1072" uniqueCount="195">
   <si>
     <t xml:space="preserve">Santri ADM 1.1.5.7 R1</t>
   </si>
   <si>
-    <t xml:space="preserve">Emitido em: 18/05/2026 07:30:58</t>
+    <t xml:space="preserve">Emitido em: 19/05/2026 05:30:31</t>
   </si>
   <si>
     <t xml:space="preserve">Relação de entradas - Sintético</t>
@@ -265,28 +265,13 @@
     <t xml:space="preserve">Não</t>
   </si>
   <si>
-    <t xml:space="preserve">547 - LORENZETTI S/A INDU.BRASILEIRAS ELETROMETALURGICAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.972.380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.384,20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.910</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260461413282000143550010029723801722131595</t>
-  </si>
-  <si>
     <t xml:space="preserve">30.850 - DEXCO S.A</t>
   </si>
   <si>
     <t xml:space="preserve">161.164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30/04/2026</t>
   </si>
   <si>
     <t xml:space="preserve">05/05/2026</t>
@@ -331,10 +316,19 @@
     <t xml:space="preserve">43260586895448000136550010000648961248387979</t>
   </si>
   <si>
-    <t xml:space="preserve">64.895</t>
+    <t xml:space="preserve">64.894</t>
   </si>
   <si>
     <t xml:space="preserve">07/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.725,01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43260586895448000136550010000648941804845676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.895</t>
   </si>
   <si>
     <t xml:space="preserve">1.978,02</t>
@@ -347,6 +341,9 @@
   </si>
   <si>
     <t xml:space="preserve">569,02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.910</t>
   </si>
   <si>
     <t xml:space="preserve">43260586895448000136550010000648971591022939</t>
@@ -403,25 +400,10 @@
     <t xml:space="preserve">35260512077181000133550030002245691053712641</t>
   </si>
   <si>
-    <t xml:space="preserve">26.619 - DICAN COMERCIO EXTERIOR LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.077</t>
+    <t xml:space="preserve">64.914</t>
   </si>
   <si>
     <t xml:space="preserve">08/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.625,80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260505761373000107550010001200771315409772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.914</t>
   </si>
   <si>
     <t xml:space="preserve">04/06/2026</t>
@@ -472,19 +454,10 @@
     <t xml:space="preserve">35260597837181002190550010050804131517661247</t>
   </si>
   <si>
-    <t xml:space="preserve">162.731</t>
+    <t xml:space="preserve">5.082.995</t>
   </si>
   <si>
     <t xml:space="preserve">13/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48,67</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260597837181005378550010001627311454274477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.082.995</t>
   </si>
   <si>
     <t xml:space="preserve">461,96</t>
@@ -511,21 +484,6 @@
     <t xml:space="preserve">42260575339051000141550080006388181323119663</t>
   </si>
   <si>
-    <t xml:space="preserve">10.718 - STELLA IMPORTACAO E EXPORTACAO DE LUMINARIAS LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">292.997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">497,70</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260510691158000370550010002929971371918584</t>
-  </si>
-  <si>
     <t xml:space="preserve">638.522</t>
   </si>
   <si>
@@ -536,6 +494,18 @@
   </si>
   <si>
     <t xml:space="preserve">42260575339051000141550080006385221064002290</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.705 - DOKA - INDUSTRIA E COMERCIO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260501136190000131550010000622581125328628</t>
   </si>
   <si>
     <t xml:space="preserve">639.834</t>
@@ -560,6 +530,24 @@
   </si>
   <si>
     <t xml:space="preserve">42260575339051000141550080006403161190056807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">642.479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.812,04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006424791298308020</t>
   </si>
   <si>
     <t xml:space="preserve">Total geral</t>
@@ -16805,7 +16793,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BM47"/>
+  <dimension ref="A1:BM46"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="18"/>
@@ -17368,7 +17356,7 @@
     </row>
     <row r="6" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="n">
-        <v>306535</v>
+        <v>306724</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>81</v>
@@ -17386,7 +17374,7 @@
         <v>83</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="J6" s="9" t="s">
         <v>78</v>
@@ -17395,31 +17383,31 @@
         <v>70</v>
       </c>
       <c r="L6" s="12" t="n">
-        <v>5384.2</v>
+        <v>976.79</v>
       </c>
       <c r="M6" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N6" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O6" s="12" t="n">
-        <v>5384.2</v>
+        <v>970.48</v>
       </c>
       <c r="P6" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q6" s="13" t="n">
-        <v>0.023054</v>
+        <v>0</v>
       </c>
       <c r="R6" s="12" t="n">
-        <v>28.62</v>
+        <v>0</v>
       </c>
       <c r="S6" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T6" s="14" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U6" s="15" t="s">
         <v>72</v>
@@ -17431,16 +17419,16 @@
         <v>73</v>
       </c>
       <c r="X6" s="9" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="Y6" s="12" t="n">
-        <v>0</v>
+        <v>6.31</v>
       </c>
       <c r="Z6" s="12" t="n">
-        <v>0</v>
+        <v>976.79</v>
       </c>
       <c r="AA6" s="12" t="n">
-        <v>0</v>
+        <v>68.38</v>
       </c>
       <c r="AB6" s="12" t="n">
         <v>0</v>
@@ -17509,7 +17497,7 @@
         <v>76</v>
       </c>
       <c r="AX6" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AY6" s="14" t="s">
         <v>75</v>
@@ -17545,7 +17533,7 @@
         <v>78</v>
       </c>
       <c r="BJ6" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="BK6" s="9" t="s">
         <v>75</v>
@@ -17559,79 +17547,79 @@
     </row>
     <row r="7" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="n">
-        <v>306724</v>
+        <v>306823</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
       <c r="F7" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G7" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K7" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L7" s="12" t="n">
-        <v>976.79</v>
+        <v>5775.71</v>
       </c>
       <c r="M7" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N7" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O7" s="12" t="n">
-        <v>970.48</v>
+        <v>5510.71</v>
       </c>
       <c r="P7" s="12" t="n">
-        <v>0</v>
+        <v>265</v>
       </c>
       <c r="Q7" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R7" s="12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="S7" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T7" s="14" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="U7" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V7" s="12" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="W7" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X7" s="9" t="s">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="Y7" s="12" t="n">
-        <v>6.31</v>
+        <v>0</v>
       </c>
       <c r="Z7" s="12" t="n">
-        <v>976.79</v>
+        <v>5775.71</v>
       </c>
       <c r="AA7" s="12" t="n">
-        <v>68.38</v>
+        <v>404.3</v>
       </c>
       <c r="AB7" s="12" t="n">
         <v>0</v>
@@ -17700,7 +17688,7 @@
         <v>76</v>
       </c>
       <c r="AX7" s="10" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="AY7" s="14" t="s">
         <v>75</v>
@@ -17750,7 +17738,7 @@
     </row>
     <row r="8" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="n">
-        <v>306823</v>
+        <v>306845</v>
       </c>
       <c r="B8" s="9" t="s">
         <v>93</v>
@@ -17765,7 +17753,7 @@
         <v>66</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="I8" s="9" t="s">
         <v>69</v>
@@ -17777,7 +17765,7 @@
         <v>70</v>
       </c>
       <c r="L8" s="12" t="n">
-        <v>5775.71</v>
+        <v>935.55</v>
       </c>
       <c r="M8" s="12" t="n">
         <v>0</v>
@@ -17786,16 +17774,16 @@
         <v>1</v>
       </c>
       <c r="O8" s="12" t="n">
-        <v>5510.71</v>
+        <v>935.55</v>
       </c>
       <c r="P8" s="12" t="n">
-        <v>265</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R8" s="12" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="S8" s="12" t="n">
         <v>0</v>
@@ -17807,7 +17795,7 @@
         <v>72</v>
       </c>
       <c r="V8" s="12" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="W8" s="9" t="s">
         <v>73</v>
@@ -17819,10 +17807,10 @@
         <v>0</v>
       </c>
       <c r="Z8" s="12" t="n">
-        <v>5775.71</v>
+        <v>935.55</v>
       </c>
       <c r="AA8" s="12" t="n">
-        <v>404.3</v>
+        <v>65.49</v>
       </c>
       <c r="AB8" s="12" t="n">
         <v>0</v>
@@ -17941,16 +17929,16 @@
     </row>
     <row r="9" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="n">
-        <v>306845</v>
+        <v>306869</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G9" s="10" t="s">
         <v>66</v>
@@ -17959,16 +17947,16 @@
         <v>69</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="K9" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L9" s="12" t="n">
-        <v>935.55</v>
+        <v>1725.01</v>
       </c>
       <c r="M9" s="12" t="n">
         <v>0</v>
@@ -17977,43 +17965,43 @@
         <v>1</v>
       </c>
       <c r="O9" s="12" t="n">
-        <v>935.55</v>
+        <v>1725.01</v>
       </c>
       <c r="P9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q9" s="13" t="n">
-        <v>0</v>
+        <v>0.008288</v>
       </c>
       <c r="R9" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="S9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T9" s="14" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="U9" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V9" s="12" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="W9" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X9" s="9" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="Y9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z9" s="12" t="n">
-        <v>935.55</v>
+        <v>1725.01</v>
       </c>
       <c r="AA9" s="12" t="n">
-        <v>65.49</v>
+        <v>120.75</v>
       </c>
       <c r="AB9" s="12" t="n">
         <v>0</v>
@@ -18118,7 +18106,7 @@
         <v>78</v>
       </c>
       <c r="BJ9" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="BK9" s="9" t="s">
         <v>75</v>
@@ -18135,13 +18123,13 @@
         <v>306871</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
       <c r="F10" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G10" s="10" t="s">
         <v>66</v>
@@ -18150,10 +18138,10 @@
         <v>69</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="K10" s="11" t="s">
         <v>70</v>
@@ -18183,7 +18171,7 @@
         <v>0</v>
       </c>
       <c r="T10" s="14" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="U10" s="15" t="s">
         <v>72</v>
@@ -18195,7 +18183,7 @@
         <v>73</v>
       </c>
       <c r="X10" s="9" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="Y10" s="12" t="n">
         <v>0</v>
@@ -18309,7 +18297,7 @@
         <v>78</v>
       </c>
       <c r="BJ10" s="9" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="BK10" s="9" t="s">
         <v>75</v>
@@ -18326,13 +18314,13 @@
         <v>306872</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
       <c r="F11" s="9" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G11" s="10" t="s">
         <v>66</v>
@@ -18341,7 +18329,7 @@
         <v>69</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="J11" s="9" t="s">
         <v>78</v>
@@ -18374,7 +18362,7 @@
         <v>0</v>
       </c>
       <c r="T11" s="14" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="U11" s="15" t="s">
         <v>72</v>
@@ -18386,7 +18374,7 @@
         <v>73</v>
       </c>
       <c r="X11" s="9" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="Y11" s="12" t="n">
         <v>0</v>
@@ -18464,7 +18452,7 @@
         <v>76</v>
       </c>
       <c r="AX11" s="10" t="s">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="AY11" s="14" t="s">
         <v>75</v>
@@ -18500,7 +18488,7 @@
         <v>78</v>
       </c>
       <c r="BJ11" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BK11" s="9" t="s">
         <v>75</v>
@@ -18517,13 +18505,13 @@
         <v>306873</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
       <c r="F12" s="9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G12" s="10" t="s">
         <v>66</v>
@@ -18532,10 +18520,10 @@
         <v>69</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="K12" s="11" t="s">
         <v>70</v>
@@ -18565,7 +18553,7 @@
         <v>0</v>
       </c>
       <c r="T12" s="14" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="U12" s="15" t="s">
         <v>72</v>
@@ -18577,7 +18565,7 @@
         <v>73</v>
       </c>
       <c r="X12" s="9" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="Y12" s="12" t="n">
         <v>0</v>
@@ -18691,7 +18679,7 @@
         <v>78</v>
       </c>
       <c r="BJ12" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BK12" s="9" t="s">
         <v>75</v>
@@ -18708,13 +18696,13 @@
         <v>306874</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
       <c r="F13" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G13" s="10" t="s">
         <v>66</v>
@@ -18723,10 +18711,10 @@
         <v>69</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="K13" s="11" t="s">
         <v>70</v>
@@ -18756,7 +18744,7 @@
         <v>0</v>
       </c>
       <c r="T13" s="14" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="U13" s="15" t="s">
         <v>72</v>
@@ -18768,7 +18756,7 @@
         <v>73</v>
       </c>
       <c r="X13" s="9" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="Y13" s="12" t="n">
         <v>0</v>
@@ -18882,7 +18870,7 @@
         <v>78</v>
       </c>
       <c r="BJ13" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="BK13" s="9" t="s">
         <v>75</v>
@@ -18899,13 +18887,13 @@
         <v>306875</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
       <c r="F14" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G14" s="10" t="s">
         <v>66</v>
@@ -18914,10 +18902,10 @@
         <v>69</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="K14" s="11" t="s">
         <v>70</v>
@@ -18947,7 +18935,7 @@
         <v>0</v>
       </c>
       <c r="T14" s="14" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U14" s="15" t="s">
         <v>72</v>
@@ -18959,7 +18947,7 @@
         <v>73</v>
       </c>
       <c r="X14" s="9" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="Y14" s="12" t="n">
         <v>0</v>
@@ -19073,7 +19061,7 @@
         <v>78</v>
       </c>
       <c r="BJ14" s="9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="BK14" s="9" t="s">
         <v>75</v>
@@ -19090,13 +19078,13 @@
         <v>306876</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
       <c r="F15" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G15" s="10" t="s">
         <v>66</v>
@@ -19105,10 +19093,10 @@
         <v>69</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="K15" s="11" t="s">
         <v>70</v>
@@ -19138,7 +19126,7 @@
         <v>0</v>
       </c>
       <c r="T15" s="14" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="U15" s="15" t="s">
         <v>72</v>
@@ -19150,7 +19138,7 @@
         <v>73</v>
       </c>
       <c r="X15" s="9" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="Y15" s="12" t="n">
         <v>0</v>
@@ -19264,7 +19252,7 @@
         <v>78</v>
       </c>
       <c r="BJ15" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="BK15" s="9" t="s">
         <v>75</v>
@@ -19281,22 +19269,22 @@
         <v>306880</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
       <c r="F16" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="G16" s="10" t="s">
         <v>123</v>
-      </c>
-      <c r="G16" s="10" t="s">
-        <v>124</v>
       </c>
       <c r="H16" s="9" t="s">
         <v>69</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="J16" s="9" t="s">
         <v>78</v>
@@ -19329,7 +19317,7 @@
         <v>0</v>
       </c>
       <c r="T16" s="14" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="U16" s="15" t="s">
         <v>72</v>
@@ -19341,7 +19329,7 @@
         <v>73</v>
       </c>
       <c r="X16" s="9" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="Y16" s="12" t="n">
         <v>3.51</v>
@@ -19419,7 +19407,7 @@
         <v>76</v>
       </c>
       <c r="AX16" s="10" t="s">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="AY16" s="14" t="s">
         <v>75</v>
@@ -19455,7 +19443,7 @@
         <v>78</v>
       </c>
       <c r="BJ16" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="BK16" s="9" t="s">
         <v>75</v>
@@ -19469,79 +19457,79 @@
     </row>
     <row r="17" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="n">
-        <v>306969</v>
+        <v>306975</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>127</v>
+        <v>93</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
       <c r="F17" s="9" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G17" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="K17" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>3625.8</v>
+        <v>985.72</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O17" s="12" t="n">
-        <v>3315.52</v>
+        <v>985.72</v>
       </c>
       <c r="P17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q17" s="13" t="n">
-        <v>0</v>
+        <v>0.002368</v>
       </c>
       <c r="R17" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T17" s="14" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="U17" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V17" s="12" t="n">
-        <v>60.33</v>
+        <v>41.98</v>
       </c>
       <c r="W17" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X17" s="9" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="Y17" s="12" t="n">
-        <v>310.28</v>
+        <v>0</v>
       </c>
       <c r="Z17" s="12" t="n">
-        <v>3315.52</v>
+        <v>985.72</v>
       </c>
       <c r="AA17" s="12" t="n">
-        <v>132.63</v>
+        <v>69</v>
       </c>
       <c r="AB17" s="12" t="n">
         <v>0</v>
@@ -19646,7 +19634,7 @@
         <v>78</v>
       </c>
       <c r="BJ17" s="9" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="BK17" s="9" t="s">
         <v>75</v>
@@ -19660,34 +19648,34 @@
     </row>
     <row r="18" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="n">
-        <v>306975</v>
+        <v>306976</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
       <c r="F18" s="9" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G18" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="K18" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>985.72</v>
+        <v>1478.58</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>0</v>
@@ -19696,43 +19684,43 @@
         <v>1</v>
       </c>
       <c r="O18" s="12" t="n">
-        <v>985.72</v>
+        <v>1478.58</v>
       </c>
       <c r="P18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q18" s="13" t="n">
-        <v>0.002368</v>
+        <v>0.007104</v>
       </c>
       <c r="R18" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T18" s="14" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="U18" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V18" s="12" t="n">
-        <v>41.98</v>
+        <v>41.99</v>
       </c>
       <c r="W18" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X18" s="9" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="Y18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z18" s="12" t="n">
-        <v>985.72</v>
+        <v>1478.58</v>
       </c>
       <c r="AA18" s="12" t="n">
-        <v>69</v>
+        <v>103.5</v>
       </c>
       <c r="AB18" s="12" t="n">
         <v>0</v>
@@ -19837,7 +19825,7 @@
         <v>78</v>
       </c>
       <c r="BJ18" s="9" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="BK18" s="9" t="s">
         <v>75</v>
@@ -19851,28 +19839,28 @@
     </row>
     <row r="19" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="n">
-        <v>306976</v>
+        <v>306977</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
       <c r="F19" s="9" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="G19" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="K19" s="11" t="s">
         <v>70</v>
@@ -19902,7 +19890,7 @@
         <v>0</v>
       </c>
       <c r="T19" s="14" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="U19" s="15" t="s">
         <v>72</v>
@@ -19914,7 +19902,7 @@
         <v>73</v>
       </c>
       <c r="X19" s="9" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="Y19" s="12" t="n">
         <v>0</v>
@@ -20028,7 +20016,7 @@
         <v>78</v>
       </c>
       <c r="BJ19" s="9" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="BK19" s="9" t="s">
         <v>75</v>
@@ -20042,28 +20030,28 @@
     </row>
     <row r="20" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="n">
-        <v>306977</v>
+        <v>307040</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
       <c r="F20" s="9" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="G20" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="K20" s="11" t="s">
         <v>70</v>
@@ -20093,7 +20081,7 @@
         <v>0</v>
       </c>
       <c r="T20" s="14" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="U20" s="15" t="s">
         <v>72</v>
@@ -20105,7 +20093,7 @@
         <v>73</v>
       </c>
       <c r="X20" s="9" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="Y20" s="12" t="n">
         <v>0</v>
@@ -20219,7 +20207,7 @@
         <v>78</v>
       </c>
       <c r="BJ20" s="9" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="BK20" s="9" t="s">
         <v>75</v>
@@ -20233,34 +20221,34 @@
     </row>
     <row r="21" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="n">
-        <v>307040</v>
+        <v>307172</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>98</v>
+        <v>139</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
       <c r="F21" s="9" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G21" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>104</v>
+        <v>127</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="K21" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>1478.58</v>
+        <v>404.81</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>0</v>
@@ -20269,43 +20257,43 @@
         <v>1</v>
       </c>
       <c r="O21" s="12" t="n">
-        <v>1478.58</v>
+        <v>404.81</v>
       </c>
       <c r="P21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q21" s="13" t="n">
-        <v>0.007104</v>
+        <v>0.000858</v>
       </c>
       <c r="R21" s="12" t="n">
-        <v>6</v>
+        <v>2.43</v>
       </c>
       <c r="S21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T21" s="14" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="U21" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V21" s="12" t="n">
-        <v>41.99</v>
+        <v>0</v>
       </c>
       <c r="W21" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X21" s="9" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="Y21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z21" s="12" t="n">
-        <v>1478.58</v>
+        <v>404.81</v>
       </c>
       <c r="AA21" s="12" t="n">
-        <v>103.5</v>
+        <v>16.19</v>
       </c>
       <c r="AB21" s="12" t="n">
         <v>0</v>
@@ -20374,7 +20362,7 @@
         <v>76</v>
       </c>
       <c r="AX21" s="10" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AY21" s="14" t="s">
         <v>75</v>
@@ -20410,7 +20398,7 @@
         <v>78</v>
       </c>
       <c r="BJ21" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="BK21" s="9" t="s">
         <v>75</v>
@@ -20424,25 +20412,25 @@
     </row>
     <row r="22" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="n">
-        <v>307172</v>
+        <v>307219</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
       <c r="F22" s="9" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G22" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J22" s="9" t="s">
         <v>78</v>
@@ -20451,7 +20439,7 @@
         <v>70</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>404.81</v>
+        <v>461.96</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>0</v>
@@ -20460,13 +20448,13 @@
         <v>1</v>
       </c>
       <c r="O22" s="12" t="n">
-        <v>404.81</v>
+        <v>461.96</v>
       </c>
       <c r="P22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q22" s="13" t="n">
-        <v>0.000858</v>
+        <v>0.002057</v>
       </c>
       <c r="R22" s="12" t="n">
         <v>2.43</v>
@@ -20475,7 +20463,7 @@
         <v>0</v>
       </c>
       <c r="T22" s="14" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="U22" s="15" t="s">
         <v>72</v>
@@ -20487,16 +20475,16 @@
         <v>73</v>
       </c>
       <c r="X22" s="9" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="Y22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z22" s="12" t="n">
-        <v>404.81</v>
+        <v>461.96</v>
       </c>
       <c r="AA22" s="12" t="n">
-        <v>16.19</v>
+        <v>18.48</v>
       </c>
       <c r="AB22" s="12" t="n">
         <v>0</v>
@@ -20565,7 +20553,7 @@
         <v>76</v>
       </c>
       <c r="AX22" s="10" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="AY22" s="14" t="s">
         <v>75</v>
@@ -20601,7 +20589,7 @@
         <v>78</v>
       </c>
       <c r="BJ22" s="9" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="BK22" s="9" t="s">
         <v>75</v>
@@ -20615,34 +20603,34 @@
     </row>
     <row r="23" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="n">
-        <v>307205</v>
+        <v>307243</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>87</v>
+        <v>148</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="G23" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="G23" s="10" t="s">
-        <v>66</v>
-      </c>
       <c r="H23" s="9" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="I23" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="J23" s="9" t="s">
         <v>151</v>
-      </c>
-      <c r="J23" s="9" t="s">
-        <v>78</v>
       </c>
       <c r="K23" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>48.67</v>
+        <v>2077.92</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>0</v>
@@ -20651,16 +20639,16 @@
         <v>1</v>
       </c>
       <c r="O23" s="12" t="n">
-        <v>48.36</v>
+        <v>2077.92</v>
       </c>
       <c r="P23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q23" s="13" t="n">
-        <v>0.01185</v>
+        <v>0.007844</v>
       </c>
       <c r="R23" s="12" t="n">
-        <v>34.5</v>
+        <v>0.81</v>
       </c>
       <c r="S23" s="12" t="n">
         <v>0</v>
@@ -20672,22 +20660,22 @@
         <v>72</v>
       </c>
       <c r="V23" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W23" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X23" s="9" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="Y23" s="12" t="n">
-        <v>0.31</v>
+        <v>0</v>
       </c>
       <c r="Z23" s="12" t="n">
-        <v>48.36</v>
+        <v>2077.92</v>
       </c>
       <c r="AA23" s="12" t="n">
-        <v>3.39</v>
+        <v>145.45</v>
       </c>
       <c r="AB23" s="12" t="n">
         <v>0</v>
@@ -20756,7 +20744,7 @@
         <v>76</v>
       </c>
       <c r="AX23" s="10" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="AY23" s="14" t="s">
         <v>75</v>
@@ -20806,10 +20794,10 @@
     </row>
     <row r="24" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="n">
-        <v>307219</v>
+        <v>307294</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
@@ -20818,22 +20806,22 @@
         <v>154</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>66</v>
+        <v>150</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="I24" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="J24" s="9" t="s">
         <v>151</v>
-      </c>
-      <c r="J24" s="9" t="s">
-        <v>78</v>
       </c>
       <c r="K24" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>461.96</v>
+        <v>4402.37</v>
       </c>
       <c r="M24" s="12" t="n">
         <v>0</v>
@@ -20842,43 +20830,43 @@
         <v>1</v>
       </c>
       <c r="O24" s="12" t="n">
-        <v>461.96</v>
+        <v>4402.37</v>
       </c>
       <c r="P24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q24" s="13" t="n">
-        <v>0.002057</v>
+        <v>0</v>
       </c>
       <c r="R24" s="12" t="n">
-        <v>2.43</v>
+        <v>8.3</v>
       </c>
       <c r="S24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T24" s="14" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="U24" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V24" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W24" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X24" s="9" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="Y24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z24" s="12" t="n">
-        <v>461.96</v>
+        <v>4402.37</v>
       </c>
       <c r="AA24" s="12" t="n">
-        <v>18.48</v>
+        <v>308.17</v>
       </c>
       <c r="AB24" s="12" t="n">
         <v>0</v>
@@ -20947,7 +20935,7 @@
         <v>76</v>
       </c>
       <c r="AX24" s="10" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="AY24" s="14" t="s">
         <v>75</v>
@@ -20983,7 +20971,7 @@
         <v>78</v>
       </c>
       <c r="BJ24" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="BK24" s="9" t="s">
         <v>75</v>
@@ -20997,34 +20985,34 @@
     </row>
     <row r="25" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="n">
-        <v>307243</v>
+        <v>307310</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>159</v>
+        <v>66</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>160</v>
+        <v>78</v>
       </c>
       <c r="K25" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>2077.92</v>
+        <v>30</v>
       </c>
       <c r="M25" s="12" t="n">
         <v>0</v>
@@ -21033,43 +21021,43 @@
         <v>1</v>
       </c>
       <c r="O25" s="12" t="n">
-        <v>2077.92</v>
+        <v>30</v>
       </c>
       <c r="P25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q25" s="13" t="n">
-        <v>0.007844</v>
+        <v>0</v>
       </c>
       <c r="R25" s="12" t="n">
-        <v>0.81</v>
+        <v>38</v>
       </c>
       <c r="S25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T25" s="14" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="U25" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V25" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W25" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X25" s="9" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="Y25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z25" s="12" t="n">
-        <v>2077.92</v>
+        <v>30</v>
       </c>
       <c r="AA25" s="12" t="n">
-        <v>145.45</v>
+        <v>1.2</v>
       </c>
       <c r="AB25" s="12" t="n">
         <v>0</v>
@@ -21138,7 +21126,7 @@
         <v>76</v>
       </c>
       <c r="AX25" s="10" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AY25" s="14" t="s">
         <v>75</v>
@@ -21174,7 +21162,7 @@
         <v>78</v>
       </c>
       <c r="BJ25" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="BK25" s="9" t="s">
         <v>75</v>
@@ -21188,34 +21176,34 @@
     </row>
     <row r="26" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="n">
-        <v>307275</v>
+        <v>307332</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>66</v>
+        <v>150</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>78</v>
+        <v>163</v>
       </c>
       <c r="K26" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>497.7</v>
+        <v>1494.11</v>
       </c>
       <c r="M26" s="12" t="n">
         <v>0</v>
@@ -21224,43 +21212,43 @@
         <v>1</v>
       </c>
       <c r="O26" s="12" t="n">
-        <v>497.7</v>
+        <v>1494.11</v>
       </c>
       <c r="P26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q26" s="13" t="n">
-        <v>0</v>
+        <v>0.002473</v>
       </c>
       <c r="R26" s="12" t="n">
-        <v>0</v>
+        <v>0.77</v>
       </c>
       <c r="S26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T26" s="14" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="U26" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V26" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W26" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X26" s="9" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="Y26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z26" s="12" t="n">
-        <v>497.7</v>
+        <v>1494.11</v>
       </c>
       <c r="AA26" s="12" t="n">
-        <v>19.91</v>
+        <v>104.59</v>
       </c>
       <c r="AB26" s="12" t="n">
         <v>0</v>
@@ -21326,10 +21314,10 @@
         <v>74</v>
       </c>
       <c r="AW26" s="14" t="s">
-        <v>166</v>
+        <v>76</v>
       </c>
       <c r="AX26" s="10" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AY26" s="14" t="s">
         <v>75</v>
@@ -21365,7 +21353,7 @@
         <v>78</v>
       </c>
       <c r="BJ26" s="9" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="BK26" s="9" t="s">
         <v>75</v>
@@ -21379,34 +21367,34 @@
     </row>
     <row r="27" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="n">
-        <v>307294</v>
+        <v>307348</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="J27" s="9" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="K27" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>4402.37</v>
+        <v>1360.01</v>
       </c>
       <c r="M27" s="12" t="n">
         <v>0</v>
@@ -21415,22 +21403,22 @@
         <v>1</v>
       </c>
       <c r="O27" s="12" t="n">
-        <v>4402.37</v>
+        <v>1277</v>
       </c>
       <c r="P27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q27" s="13" t="n">
-        <v>0</v>
+        <v>0.013954</v>
       </c>
       <c r="R27" s="12" t="n">
-        <v>8.3</v>
+        <v>1.78</v>
       </c>
       <c r="S27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T27" s="14" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="U27" s="15" t="s">
         <v>72</v>
@@ -21442,16 +21430,16 @@
         <v>73</v>
       </c>
       <c r="X27" s="9" t="s">
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="Y27" s="12" t="n">
-        <v>0</v>
+        <v>83.01</v>
       </c>
       <c r="Z27" s="12" t="n">
-        <v>4402.37</v>
+        <v>1277</v>
       </c>
       <c r="AA27" s="12" t="n">
-        <v>308.17</v>
+        <v>89.39</v>
       </c>
       <c r="AB27" s="12" t="n">
         <v>0</v>
@@ -21556,7 +21544,7 @@
         <v>78</v>
       </c>
       <c r="BJ27" s="9" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="BK27" s="9" t="s">
         <v>75</v>
@@ -21570,25 +21558,25 @@
     </row>
     <row r="28" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="n">
-        <v>307332</v>
+        <v>307432</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="G28" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="H28" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="I28" s="9" t="s">
         <v>172</v>
-      </c>
-      <c r="G28" s="10" t="s">
-        <v>159</v>
-      </c>
-      <c r="H28" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="I28" s="9" t="s">
-        <v>169</v>
       </c>
       <c r="J28" s="9" t="s">
         <v>173</v>
@@ -21597,7 +21585,7 @@
         <v>70</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>1494.11</v>
+        <v>2812.04</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>0</v>
@@ -21606,16 +21594,16 @@
         <v>1</v>
       </c>
       <c r="O28" s="12" t="n">
-        <v>1494.11</v>
+        <v>2812.04</v>
       </c>
       <c r="P28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q28" s="13" t="n">
-        <v>0.002473</v>
+        <v>0.007844</v>
       </c>
       <c r="R28" s="12" t="n">
-        <v>0.77</v>
+        <v>1.78</v>
       </c>
       <c r="S28" s="12" t="n">
         <v>0</v>
@@ -21633,16 +21621,16 @@
         <v>73</v>
       </c>
       <c r="X28" s="9" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="Y28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z28" s="12" t="n">
-        <v>1494.11</v>
+        <v>2812.04</v>
       </c>
       <c r="AA28" s="12" t="n">
-        <v>104.59</v>
+        <v>196.84</v>
       </c>
       <c r="AB28" s="12" t="n">
         <v>0</v>
@@ -21760,518 +21748,396 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="8" t="n">
-        <v>307348</v>
-      </c>
-      <c r="B29" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9" t="s">
+      <c r="A29" s="4"/>
+    </row>
+    <row r="30" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="17" t="s">
         <v>176</v>
       </c>
-      <c r="G29" s="10" t="s">
-        <v>159</v>
-      </c>
-      <c r="H29" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="I29" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="J29" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="K29" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="L29" s="12" t="n">
-        <v>1360.01</v>
-      </c>
-      <c r="M29" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O29" s="12" t="n">
-        <v>1277</v>
-      </c>
-      <c r="P29" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="13" t="n">
-        <v>0.013954</v>
-      </c>
-      <c r="R29" s="12" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="S29" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" s="14" t="s">
-        <v>178</v>
-      </c>
-      <c r="U29" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="V29" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="W29" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="X29" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="Y29" s="12" t="n">
-        <v>83.01</v>
-      </c>
-      <c r="Z29" s="12" t="n">
-        <v>1277</v>
-      </c>
-      <c r="AA29" s="12" t="n">
-        <v>89.39</v>
-      </c>
-      <c r="AB29" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC29" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD29" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE29" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF29" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG29" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH29" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI29" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ29" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AK29" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL29" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM29" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AN29" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AO29" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AP29" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ29" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR29" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS29" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT29" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU29" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV29" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW29" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="AX29" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="AY29" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ29" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA29" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB29" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BC29" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD29" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE29" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BF29" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BG29" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="BH29" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BI29" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="BJ29" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="BK29" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BL29" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BM29" s="16" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="4"/>
+      <c r="B30" s="17"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="17"/>
+      <c r="F30" s="17"/>
+      <c r="G30" s="17"/>
+      <c r="H30" s="17"/>
+      <c r="I30" s="17"/>
+      <c r="J30" s="17"/>
+      <c r="K30" s="17"/>
+      <c r="L30" s="17"/>
+      <c r="M30" s="17"/>
+      <c r="N30" s="17"/>
+      <c r="O30" s="17"/>
+      <c r="P30" s="17"/>
+      <c r="Q30" s="17"/>
+      <c r="R30" s="17"/>
+      <c r="S30" s="17"/>
+      <c r="T30" s="17"/>
+      <c r="U30" s="17"/>
+      <c r="V30" s="17"/>
     </row>
     <row r="31" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="17" t="s">
+      <c r="A31" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="B31" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" s="18" t="s">
+        <v>178</v>
+      </c>
+      <c r="E31" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F31" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="G31" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H31" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="I31" s="18" t="s">
+        <v>179</v>
+      </c>
+      <c r="J31" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="K31" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="L31" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="M31" s="18" t="s">
         <v>180</v>
       </c>
-      <c r="B31" s="17"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
-      <c r="G31" s="17"/>
-      <c r="H31" s="17"/>
-      <c r="I31" s="17"/>
-      <c r="J31" s="17"/>
-      <c r="K31" s="17"/>
-      <c r="L31" s="17"/>
-      <c r="M31" s="17"/>
-      <c r="N31" s="17"/>
-      <c r="O31" s="17"/>
-      <c r="P31" s="17"/>
-      <c r="Q31" s="17"/>
-      <c r="R31" s="17"/>
-      <c r="S31" s="17"/>
-      <c r="T31" s="17"/>
-      <c r="U31" s="17"/>
-      <c r="V31" s="17"/>
+      <c r="N31" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="O31" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="P31" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q31" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="R31" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="S31" s="18" t="s">
+        <v>181</v>
+      </c>
+      <c r="T31" s="18" t="s">
+        <v>182</v>
+      </c>
+      <c r="U31" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="V31" s="18" t="s">
+        <v>37</v>
+      </c>
     </row>
-    <row r="32" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="18" t="s">
-        <v>181</v>
-      </c>
-      <c r="B32" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C32" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D32" s="18" t="s">
-        <v>182</v>
-      </c>
-      <c r="E32" s="18" t="s">
+    <row r="32" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="19" t="n">
         <v>24</v>
       </c>
-      <c r="F32" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="G32" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="H32" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="I32" s="18" t="s">
+      <c r="B32" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="19" t="n">
+        <v>265</v>
+      </c>
+      <c r="D32" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="19" t="n">
+        <v>92.83</v>
+      </c>
+      <c r="F32" s="19" t="n">
+        <v>50365.02</v>
+      </c>
+      <c r="G32" s="19" t="n">
+        <v>3394.43</v>
+      </c>
+      <c r="H32" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="19" t="n">
+        <v>50451.54</v>
+      </c>
+      <c r="L32" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" s="20" t="n">
+        <v>0.141296</v>
+      </c>
+      <c r="S32" s="19" t="n">
+        <v>50093.71</v>
+      </c>
+      <c r="T32" s="19" t="n">
+        <v>50451.54</v>
+      </c>
+      <c r="U32" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B33" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C33" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D33" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="E33" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="F33" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="G33" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="H33" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="I33" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="J33" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="K33" s="18" t="s">
         <v>183</v>
       </c>
-      <c r="J32" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="K32" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="L32" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="M32" s="18" t="s">
+      <c r="L33" s="18" t="s">
         <v>184</v>
       </c>
-      <c r="N32" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="O32" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="P32" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q32" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="R32" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="S32" s="18" t="s">
+      <c r="M33" s="18" t="s">
         <v>185</v>
       </c>
-      <c r="T32" s="18" t="s">
-        <v>186</v>
-      </c>
-      <c r="U32" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="V32" s="18" t="s">
-        <v>37</v>
-      </c>
     </row>
-    <row r="33" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="19" t="n">
-        <v>25</v>
-      </c>
-      <c r="B33" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" s="19" t="n">
-        <v>265</v>
-      </c>
-      <c r="D33" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" s="19" t="n">
-        <v>403.42</v>
-      </c>
-      <c r="F33" s="19" t="n">
-        <v>49659.55</v>
-      </c>
-      <c r="G33" s="19" t="n">
-        <v>3231.57</v>
-      </c>
-      <c r="H33" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" s="19" t="n">
-        <v>55440.86</v>
-      </c>
-      <c r="L33" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" s="20" t="n">
-        <v>0.160068</v>
-      </c>
-      <c r="S33" s="19" t="n">
-        <v>54772.44</v>
-      </c>
-      <c r="T33" s="19" t="n">
-        <v>55440.86</v>
-      </c>
-      <c r="U33" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" s="19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="B34" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C34" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="D34" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E34" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="F34" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="G34" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="H34" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="I34" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="J34" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="K34" s="18" t="s">
-        <v>187</v>
-      </c>
-      <c r="L34" s="18" t="s">
-        <v>188</v>
-      </c>
-      <c r="M34" s="18" t="s">
-        <v>189</v>
+    <row r="34" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="19" t="n">
+        <v>176.79</v>
+      </c>
+      <c r="B34" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="19" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="E34" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="19" t="n">
-        <v>193.12</v>
-      </c>
-      <c r="B35" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C35" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" s="19" t="n">
-        <v>31.81</v>
-      </c>
-      <c r="E35" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" s="19" t="n">
-        <v>0</v>
-      </c>
+      <c r="A35" s="4"/>
     </row>
-    <row r="36" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="4"/>
+    <row r="36" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="21" t="s">
+        <v>186</v>
+      </c>
+      <c r="B36" s="21"/>
+      <c r="C36" s="21"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="21"/>
+      <c r="F36" s="21"/>
+      <c r="G36" s="21"/>
+      <c r="H36" s="21"/>
+      <c r="I36" s="21"/>
+      <c r="J36" s="21"/>
+      <c r="K36" s="21"/>
+      <c r="L36" s="21"/>
+      <c r="M36" s="21"/>
+      <c r="N36" s="21"/>
+      <c r="O36" s="21"/>
+      <c r="P36" s="21"/>
+      <c r="Q36" s="21"/>
+      <c r="R36" s="21"/>
+      <c r="S36" s="21"/>
+      <c r="T36" s="21"/>
+      <c r="U36" s="21"/>
+      <c r="V36" s="21"/>
+      <c r="W36" s="21"/>
+      <c r="X36" s="21"/>
+      <c r="Y36" s="21"/>
+      <c r="Z36" s="21"/>
+      <c r="AA36" s="21"/>
+      <c r="AB36" s="21"/>
+      <c r="AC36" s="21"/>
+      <c r="AD36" s="21"/>
+      <c r="AE36" s="21"/>
+      <c r="AF36" s="21"/>
+      <c r="AG36" s="21"/>
+      <c r="AH36" s="21"/>
+      <c r="AI36" s="21"/>
+      <c r="AJ36" s="21"/>
+      <c r="AK36" s="21"/>
+      <c r="AL36" s="21"/>
+      <c r="AM36" s="21"/>
+      <c r="AN36" s="21"/>
+      <c r="AO36" s="21"/>
+      <c r="AP36" s="21"/>
+      <c r="AQ36" s="21"/>
+      <c r="AR36" s="21"/>
+      <c r="AS36" s="21"/>
+      <c r="AT36" s="21"/>
+      <c r="AU36" s="21"/>
+      <c r="AV36" s="21"/>
+      <c r="AW36" s="21"/>
+      <c r="AX36" s="21"/>
+      <c r="AY36" s="21"/>
+      <c r="AZ36" s="21"/>
+      <c r="BA36" s="21"/>
+      <c r="BB36" s="21"/>
+      <c r="BC36" s="21"/>
+      <c r="BD36" s="21"/>
+      <c r="BE36" s="21"/>
+      <c r="BF36" s="21"/>
+      <c r="BG36" s="21"/>
+      <c r="BH36" s="21"/>
+      <c r="BI36" s="21"/>
+      <c r="BJ36" s="21"/>
+      <c r="BK36" s="21"/>
+      <c r="BL36" s="21"/>
+      <c r="BM36" s="21"/>
     </row>
-    <row r="37" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="21" t="s">
-        <v>190</v>
-      </c>
-      <c r="B37" s="21"/>
-      <c r="C37" s="21"/>
-      <c r="D37" s="21"/>
-      <c r="E37" s="21"/>
-      <c r="F37" s="21"/>
-      <c r="G37" s="21"/>
-      <c r="H37" s="21"/>
-      <c r="I37" s="21"/>
-      <c r="J37" s="21"/>
-      <c r="K37" s="21"/>
-      <c r="L37" s="21"/>
-      <c r="M37" s="21"/>
-      <c r="N37" s="21"/>
-      <c r="O37" s="21"/>
-      <c r="P37" s="21"/>
-      <c r="Q37" s="21"/>
-      <c r="R37" s="21"/>
-      <c r="S37" s="21"/>
-      <c r="T37" s="21"/>
-      <c r="U37" s="21"/>
-      <c r="V37" s="21"/>
-      <c r="W37" s="21"/>
-      <c r="X37" s="21"/>
-      <c r="Y37" s="21"/>
-      <c r="Z37" s="21"/>
-      <c r="AA37" s="21"/>
-      <c r="AB37" s="21"/>
-      <c r="AC37" s="21"/>
-      <c r="AD37" s="21"/>
-      <c r="AE37" s="21"/>
-      <c r="AF37" s="21"/>
-      <c r="AG37" s="21"/>
-      <c r="AH37" s="21"/>
-      <c r="AI37" s="21"/>
-      <c r="AJ37" s="21"/>
-      <c r="AK37" s="21"/>
-      <c r="AL37" s="21"/>
-      <c r="AM37" s="21"/>
-      <c r="AN37" s="21"/>
-      <c r="AO37" s="21"/>
-      <c r="AP37" s="21"/>
-      <c r="AQ37" s="21"/>
-      <c r="AR37" s="21"/>
-      <c r="AS37" s="21"/>
-      <c r="AT37" s="21"/>
-      <c r="AU37" s="21"/>
-      <c r="AV37" s="21"/>
-      <c r="AW37" s="21"/>
-      <c r="AX37" s="21"/>
-      <c r="AY37" s="21"/>
-      <c r="AZ37" s="21"/>
-      <c r="BA37" s="21"/>
-      <c r="BB37" s="21"/>
-      <c r="BC37" s="21"/>
-      <c r="BD37" s="21"/>
-      <c r="BE37" s="21"/>
-      <c r="BF37" s="21"/>
-      <c r="BG37" s="21"/>
-      <c r="BH37" s="21"/>
-      <c r="BI37" s="21"/>
-      <c r="BJ37" s="21"/>
-      <c r="BK37" s="21"/>
-      <c r="BL37" s="21"/>
-      <c r="BM37" s="21"/>
+    <row r="37" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
+      <c r="K37" s="4"/>
+      <c r="L37" s="4"/>
+      <c r="M37" s="4"/>
+      <c r="N37" s="4"/>
+      <c r="O37" s="4"/>
+      <c r="P37" s="4"/>
+      <c r="Q37" s="4"/>
+      <c r="R37" s="4"/>
+      <c r="S37" s="4"/>
+      <c r="T37" s="4"/>
+      <c r="U37" s="4"/>
+      <c r="V37" s="4"/>
+      <c r="W37" s="4"/>
+      <c r="X37" s="4"/>
+      <c r="Y37" s="4"/>
+      <c r="Z37" s="4"/>
+      <c r="AA37" s="4"/>
+      <c r="AB37" s="4"/>
+      <c r="AC37" s="4"/>
+      <c r="AD37" s="4"/>
+      <c r="AE37" s="4"/>
+      <c r="AF37" s="4"/>
+      <c r="AG37" s="4"/>
+      <c r="AH37" s="4"/>
+      <c r="AI37" s="4"/>
+      <c r="AJ37" s="4"/>
+      <c r="AK37" s="4"/>
+      <c r="AL37" s="4"/>
+      <c r="AM37" s="4"/>
+      <c r="AN37" s="4"/>
+      <c r="AO37" s="4"/>
+      <c r="AP37" s="4"/>
+      <c r="AQ37" s="4"/>
+      <c r="AR37" s="4"/>
+      <c r="AS37" s="4"/>
+      <c r="AT37" s="4"/>
+      <c r="AU37" s="4"/>
+      <c r="AV37" s="4"/>
+      <c r="AW37" s="4"/>
+      <c r="AX37" s="4"/>
+      <c r="AY37" s="4"/>
+      <c r="AZ37" s="4"/>
+      <c r="BA37" s="4"/>
+      <c r="BB37" s="4"/>
+      <c r="BC37" s="4"/>
+      <c r="BD37" s="4"/>
+      <c r="BE37" s="4"/>
+      <c r="BF37" s="4"/>
+      <c r="BG37" s="4"/>
+      <c r="BH37" s="4"/>
+      <c r="BI37" s="4"/>
+      <c r="BJ37" s="4"/>
+      <c r="BK37" s="4"/>
+      <c r="BL37" s="4"/>
+      <c r="BM37" s="4"/>
     </row>
     <row r="38" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="s">
-        <v>75</v>
+        <v>187</v>
       </c>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
@@ -22340,7 +22206,7 @@
     </row>
     <row r="39" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
@@ -22409,7 +22275,7 @@
     </row>
     <row r="40" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
@@ -22478,7 +22344,7 @@
     </row>
     <row r="41" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
-        <v>193</v>
+        <v>22</v>
       </c>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
@@ -22547,7 +22413,7 @@
     </row>
     <row r="42" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="s">
-        <v>22</v>
+        <v>190</v>
       </c>
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
@@ -22616,7 +22482,7 @@
     </row>
     <row r="43" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
@@ -22685,7 +22551,7 @@
     </row>
     <row r="44" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
@@ -22754,7 +22620,7 @@
     </row>
     <row r="45" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="4" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
@@ -22823,7 +22689,7 @@
     </row>
     <row r="46" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="4" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
@@ -22890,77 +22756,8 @@
       <c r="BL46" s="4"/>
       <c r="BM46" s="4"/>
     </row>
-    <row r="47" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="B47" s="4"/>
-      <c r="C47" s="4"/>
-      <c r="D47" s="4"/>
-      <c r="E47" s="4"/>
-      <c r="F47" s="4"/>
-      <c r="G47" s="4"/>
-      <c r="H47" s="4"/>
-      <c r="I47" s="4"/>
-      <c r="J47" s="4"/>
-      <c r="K47" s="4"/>
-      <c r="L47" s="4"/>
-      <c r="M47" s="4"/>
-      <c r="N47" s="4"/>
-      <c r="O47" s="4"/>
-      <c r="P47" s="4"/>
-      <c r="Q47" s="4"/>
-      <c r="R47" s="4"/>
-      <c r="S47" s="4"/>
-      <c r="T47" s="4"/>
-      <c r="U47" s="4"/>
-      <c r="V47" s="4"/>
-      <c r="W47" s="4"/>
-      <c r="X47" s="4"/>
-      <c r="Y47" s="4"/>
-      <c r="Z47" s="4"/>
-      <c r="AA47" s="4"/>
-      <c r="AB47" s="4"/>
-      <c r="AC47" s="4"/>
-      <c r="AD47" s="4"/>
-      <c r="AE47" s="4"/>
-      <c r="AF47" s="4"/>
-      <c r="AG47" s="4"/>
-      <c r="AH47" s="4"/>
-      <c r="AI47" s="4"/>
-      <c r="AJ47" s="4"/>
-      <c r="AK47" s="4"/>
-      <c r="AL47" s="4"/>
-      <c r="AM47" s="4"/>
-      <c r="AN47" s="4"/>
-      <c r="AO47" s="4"/>
-      <c r="AP47" s="4"/>
-      <c r="AQ47" s="4"/>
-      <c r="AR47" s="4"/>
-      <c r="AS47" s="4"/>
-      <c r="AT47" s="4"/>
-      <c r="AU47" s="4"/>
-      <c r="AV47" s="4"/>
-      <c r="AW47" s="4"/>
-      <c r="AX47" s="4"/>
-      <c r="AY47" s="4"/>
-      <c r="AZ47" s="4"/>
-      <c r="BA47" s="4"/>
-      <c r="BB47" s="4"/>
-      <c r="BC47" s="4"/>
-      <c r="BD47" s="4"/>
-      <c r="BE47" s="4"/>
-      <c r="BF47" s="4"/>
-      <c r="BG47" s="4"/>
-      <c r="BH47" s="4"/>
-      <c r="BI47" s="4"/>
-      <c r="BJ47" s="4"/>
-      <c r="BK47" s="4"/>
-      <c r="BL47" s="4"/>
-      <c r="BM47" s="4"/>
-    </row>
   </sheetData>
-  <mergeCells count="41">
+  <mergeCells count="40">
     <mergeCell ref="A1:BI1"/>
     <mergeCell ref="BJ1:BM1"/>
     <mergeCell ref="A2:BM2"/>
@@ -22989,8 +22786,8 @@
     <mergeCell ref="B26:E26"/>
     <mergeCell ref="B27:E27"/>
     <mergeCell ref="B28:E28"/>
-    <mergeCell ref="B29:E29"/>
-    <mergeCell ref="A31:V31"/>
+    <mergeCell ref="A30:V30"/>
+    <mergeCell ref="A36:BM36"/>
     <mergeCell ref="A37:BM37"/>
     <mergeCell ref="A38:BM38"/>
     <mergeCell ref="A39:BM39"/>
@@ -23001,7 +22798,6 @@
     <mergeCell ref="A44:BM44"/>
     <mergeCell ref="A45:BM45"/>
     <mergeCell ref="A46:BM46"/>
-    <mergeCell ref="A47:BM47"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>

--- a/tratando_tabelas/finitura/entradas_finitura.xlsx
+++ b/tratando_tabelas/finitura/entradas_finitura.xlsx
@@ -20,12 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1072" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="148">
   <si>
     <t xml:space="preserve">Santri ADM 1.1.5.7 R1</t>
   </si>
   <si>
-    <t xml:space="preserve">Emitido em: 19/05/2026 05:30:31</t>
+    <t xml:space="preserve">Emitido em: 20/05/2026 05:30:32</t>
   </si>
   <si>
     <t xml:space="preserve">Relação de entradas - Sintético</t>
@@ -286,105 +286,6 @@
     <t xml:space="preserve">42260497837181005378550010001611641514144027</t>
   </si>
   <si>
-    <t xml:space="preserve">25.941 - AQUECE METAIS FABRICACAO E MANUTENCAO LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">02/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.775,71</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43260527254297000178550010000105291836436270</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.123 - RUBINETTOS ACABAMENTOS EXCLUSIVOS LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">03/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">935,55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43260586895448000136550010000648961248387979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.725,01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43260586895448000136550010000648941804845676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.978,02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43260586895448000136550010000648951883526940</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">569,02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.910</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43260586895448000136550010000648971591022939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.954,76</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43260586895448000136550010000648981605277600</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.271,36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43260586895448000136550010000649011440833070</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.900</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.436,26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43260586895448000136550010000649001101985597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.157,12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43260586895448000136550010000648991337116425</t>
-  </si>
-  <si>
     <t xml:space="preserve">2.923 - NEW LINE ILUMINACAO LTDA</t>
   </si>
   <si>
@@ -394,55 +295,25 @@
     <t xml:space="preserve">3</t>
   </si>
   <si>
+    <t xml:space="preserve">07/05/2026</t>
+  </si>
+  <si>
     <t xml:space="preserve">39,50</t>
   </si>
   <si>
-    <t xml:space="preserve">35260512077181000133550030002245691053712641</t>
+    <t xml:space="preserve">2.910</t>
   </si>
   <si>
-    <t xml:space="preserve">64.914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">985,72</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43260586895448000136550010000649141474712664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.478,58</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43260586895448000136550010000649121041239909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43260586895448000136550010000649111298829132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.910</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43260586895448000136550010000649101026177588</t>
+    <t xml:space="preserve">35260512077181000133550030002245691053712641</t>
   </si>
   <si>
     <t xml:space="preserve">1.856 - DEXCO S.A - METAIS</t>
   </si>
   <si>
     <t xml:space="preserve">5.080.413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08/05/2026</t>
   </si>
   <si>
     <t xml:space="preserve">12/05/2026</t>
@@ -494,18 +365,6 @@
   </si>
   <si>
     <t xml:space="preserve">42260575339051000141550080006385221064002290</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.705 - DOKA - INDUSTRIA E COMERCIO LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30,00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260501136190000131550010000622581125328628</t>
   </si>
   <si>
     <t xml:space="preserve">639.834</t>
@@ -16793,7 +16652,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BM46"/>
+  <dimension ref="A1:BM32"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="18"/>
@@ -17547,7 +17406,7 @@
     </row>
     <row r="7" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="n">
-        <v>306823</v>
+        <v>306880</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>88</v>
@@ -17559,22 +17418,22 @@
         <v>89</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K7" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L7" s="12" t="n">
-        <v>5775.71</v>
+        <v>39.5</v>
       </c>
       <c r="M7" s="12" t="n">
         <v>0</v>
@@ -17583,43 +17442,43 @@
         <v>1</v>
       </c>
       <c r="O7" s="12" t="n">
-        <v>5510.71</v>
+        <v>35.99</v>
       </c>
       <c r="P7" s="12" t="n">
-        <v>265</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R7" s="12" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="S7" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T7" s="14" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="U7" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V7" s="12" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="W7" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X7" s="9" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="Y7" s="12" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="Z7" s="12" t="n">
-        <v>5775.71</v>
+        <v>35.99</v>
       </c>
       <c r="AA7" s="12" t="n">
-        <v>404.3</v>
+        <v>2.52</v>
       </c>
       <c r="AB7" s="12" t="n">
         <v>0</v>
@@ -17688,7 +17547,7 @@
         <v>76</v>
       </c>
       <c r="AX7" s="10" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="AY7" s="14" t="s">
         <v>75</v>
@@ -17724,7 +17583,7 @@
         <v>78</v>
       </c>
       <c r="BJ7" s="9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="BK7" s="9" t="s">
         <v>75</v>
@@ -17738,34 +17597,34 @@
     </row>
     <row r="8" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="n">
-        <v>306845</v>
+        <v>307172</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
       <c r="F8" s="9" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G8" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="K8" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L8" s="12" t="n">
-        <v>935.55</v>
+        <v>404.81</v>
       </c>
       <c r="M8" s="12" t="n">
         <v>0</v>
@@ -17774,43 +17633,43 @@
         <v>1</v>
       </c>
       <c r="O8" s="12" t="n">
-        <v>935.55</v>
+        <v>404.81</v>
       </c>
       <c r="P8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q8" s="13" t="n">
-        <v>0</v>
+        <v>0.000858</v>
       </c>
       <c r="R8" s="12" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T8" s="14" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="U8" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V8" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W8" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X8" s="9" t="s">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="Y8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z8" s="12" t="n">
-        <v>935.55</v>
+        <v>404.81</v>
       </c>
       <c r="AA8" s="12" t="n">
-        <v>65.49</v>
+        <v>16.19</v>
       </c>
       <c r="AB8" s="12" t="n">
         <v>0</v>
@@ -17879,7 +17738,7 @@
         <v>76</v>
       </c>
       <c r="AX8" s="10" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AY8" s="14" t="s">
         <v>75</v>
@@ -17915,7 +17774,7 @@
         <v>78</v>
       </c>
       <c r="BJ8" s="9" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="BK8" s="9" t="s">
         <v>75</v>
@@ -17929,34 +17788,34 @@
     </row>
     <row r="9" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="n">
-        <v>306869</v>
+        <v>307219</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="9" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G9" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="K9" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L9" s="12" t="n">
-        <v>1725.01</v>
+        <v>461.96</v>
       </c>
       <c r="M9" s="12" t="n">
         <v>0</v>
@@ -17965,43 +17824,43 @@
         <v>1</v>
       </c>
       <c r="O9" s="12" t="n">
-        <v>1725.01</v>
+        <v>461.96</v>
       </c>
       <c r="P9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q9" s="13" t="n">
-        <v>0.008288</v>
+        <v>0.002057</v>
       </c>
       <c r="R9" s="12" t="n">
-        <v>7</v>
+        <v>2.43</v>
       </c>
       <c r="S9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T9" s="14" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="U9" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V9" s="12" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="W9" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X9" s="9" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="Y9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z9" s="12" t="n">
-        <v>1725.01</v>
+        <v>461.96</v>
       </c>
       <c r="AA9" s="12" t="n">
-        <v>120.75</v>
+        <v>18.48</v>
       </c>
       <c r="AB9" s="12" t="n">
         <v>0</v>
@@ -18070,7 +17929,7 @@
         <v>76</v>
       </c>
       <c r="AX9" s="10" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AY9" s="14" t="s">
         <v>75</v>
@@ -18106,7 +17965,7 @@
         <v>78</v>
       </c>
       <c r="BJ9" s="9" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="BK9" s="9" t="s">
         <v>75</v>
@@ -18120,34 +17979,34 @@
     </row>
     <row r="10" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="n">
-        <v>306871</v>
+        <v>307243</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
       <c r="F10" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="I10" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="G10" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>99</v>
-      </c>
       <c r="J10" s="9" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="K10" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L10" s="12" t="n">
-        <v>1978.02</v>
+        <v>2077.92</v>
       </c>
       <c r="M10" s="12" t="n">
         <v>0</v>
@@ -18156,22 +18015,22 @@
         <v>1</v>
       </c>
       <c r="O10" s="12" t="n">
-        <v>1978.02</v>
+        <v>2077.92</v>
       </c>
       <c r="P10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q10" s="13" t="n">
-        <v>0</v>
+        <v>0.007844</v>
       </c>
       <c r="R10" s="12" t="n">
-        <v>0</v>
+        <v>0.81</v>
       </c>
       <c r="S10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T10" s="14" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="U10" s="15" t="s">
         <v>72</v>
@@ -18183,16 +18042,16 @@
         <v>73</v>
       </c>
       <c r="X10" s="9" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="Y10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z10" s="12" t="n">
-        <v>1978.02</v>
+        <v>2077.92</v>
       </c>
       <c r="AA10" s="12" t="n">
-        <v>138.46</v>
+        <v>145.45</v>
       </c>
       <c r="AB10" s="12" t="n">
         <v>0</v>
@@ -18297,7 +18156,7 @@
         <v>78</v>
       </c>
       <c r="BJ10" s="9" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="BK10" s="9" t="s">
         <v>75</v>
@@ -18311,79 +18170,79 @@
     </row>
     <row r="11" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="n">
-        <v>306872</v>
+        <v>307294</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
       <c r="F11" s="9" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>66</v>
+        <v>107</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="K11" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>569.02</v>
+        <v>4402.37</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O11" s="12" t="n">
-        <v>569.02</v>
+        <v>4402.37</v>
       </c>
       <c r="P11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q11" s="13" t="n">
-        <v>0.003038</v>
+        <v>0</v>
       </c>
       <c r="R11" s="12" t="n">
-        <v>4</v>
+        <v>8.3</v>
       </c>
       <c r="S11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T11" s="14" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="U11" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V11" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W11" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X11" s="9" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="Y11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z11" s="12" t="n">
-        <v>569.02</v>
+        <v>4402.37</v>
       </c>
       <c r="AA11" s="12" t="n">
-        <v>39.83</v>
+        <v>308.17</v>
       </c>
       <c r="AB11" s="12" t="n">
         <v>0</v>
@@ -18452,7 +18311,7 @@
         <v>76</v>
       </c>
       <c r="AX11" s="10" t="s">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AY11" s="14" t="s">
         <v>75</v>
@@ -18488,7 +18347,7 @@
         <v>78</v>
       </c>
       <c r="BJ11" s="9" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="BK11" s="9" t="s">
         <v>75</v>
@@ -18502,79 +18361,79 @@
     </row>
     <row r="12" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="n">
-        <v>306873</v>
+        <v>307332</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
       <c r="F12" s="9" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>66</v>
+        <v>107</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>69</v>
+        <v>102</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="K12" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>2954.76</v>
+        <v>1494.11</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O12" s="12" t="n">
-        <v>2954.76</v>
+        <v>1494.11</v>
       </c>
       <c r="P12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" s="13" t="n">
-        <v>0.00726</v>
+        <v>0.002473</v>
       </c>
       <c r="R12" s="12" t="n">
-        <v>9</v>
+        <v>0.77</v>
       </c>
       <c r="S12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T12" s="14" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="U12" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V12" s="12" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="W12" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X12" s="9" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="Y12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z12" s="12" t="n">
-        <v>2954.76</v>
+        <v>1494.11</v>
       </c>
       <c r="AA12" s="12" t="n">
-        <v>206.83</v>
+        <v>104.59</v>
       </c>
       <c r="AB12" s="12" t="n">
         <v>0</v>
@@ -18679,7 +18538,7 @@
         <v>78</v>
       </c>
       <c r="BJ12" s="9" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="BK12" s="9" t="s">
         <v>75</v>
@@ -18693,79 +18552,79 @@
     </row>
     <row r="13" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="n">
-        <v>306874</v>
+        <v>307348</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
       <c r="F13" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="H13" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="G13" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>69</v>
-      </c>
       <c r="I13" s="9" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="K13" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>2271.36</v>
+        <v>1360.01</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O13" s="12" t="n">
-        <v>2271.36</v>
+        <v>1277</v>
       </c>
       <c r="P13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q13" s="13" t="n">
-        <v>0.011638</v>
+        <v>0.013954</v>
       </c>
       <c r="R13" s="12" t="n">
-        <v>17</v>
+        <v>1.78</v>
       </c>
       <c r="S13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T13" s="14" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="U13" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V13" s="12" t="n">
-        <v>41.99</v>
+        <v>28</v>
       </c>
       <c r="W13" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X13" s="9" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="Y13" s="12" t="n">
-        <v>0</v>
+        <v>83.01</v>
       </c>
       <c r="Z13" s="12" t="n">
-        <v>2271.36</v>
+        <v>1277</v>
       </c>
       <c r="AA13" s="12" t="n">
-        <v>159</v>
+        <v>89.39</v>
       </c>
       <c r="AB13" s="12" t="n">
         <v>0</v>
@@ -18870,7 +18729,7 @@
         <v>78</v>
       </c>
       <c r="BJ13" s="9" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="BK13" s="9" t="s">
         <v>75</v>
@@ -18884,79 +18743,79 @@
     </row>
     <row r="14" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="n">
-        <v>306875</v>
+        <v>307432</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
       <c r="F14" s="9" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>66</v>
+        <v>107</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>69</v>
+        <v>124</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>99</v>
+        <v>125</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>95</v>
+        <v>126</v>
       </c>
       <c r="K14" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>5436.26</v>
+        <v>2812.04</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O14" s="12" t="n">
-        <v>5436.26</v>
+        <v>2812.04</v>
       </c>
       <c r="P14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q14" s="13" t="n">
-        <v>0.022294</v>
+        <v>0.007844</v>
       </c>
       <c r="R14" s="12" t="n">
-        <v>26</v>
+        <v>1.78</v>
       </c>
       <c r="S14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T14" s="14" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="U14" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V14" s="12" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="W14" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X14" s="9" t="s">
-        <v>99</v>
+        <v>125</v>
       </c>
       <c r="Y14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z14" s="12" t="n">
-        <v>5436.26</v>
+        <v>2812.04</v>
       </c>
       <c r="AA14" s="12" t="n">
-        <v>380.54</v>
+        <v>196.84</v>
       </c>
       <c r="AB14" s="12" t="n">
         <v>0</v>
@@ -19061,7 +18920,7 @@
         <v>78</v>
       </c>
       <c r="BJ14" s="9" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="BK14" s="9" t="s">
         <v>75</v>
@@ -19074,3690 +18933,1016 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="8" t="n">
-        <v>306876</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="G15" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="I15" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="J15" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="K15" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="L15" s="12" t="n">
-        <v>6157.12</v>
-      </c>
-      <c r="M15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="O15" s="12" t="n">
-        <v>6157.12</v>
-      </c>
-      <c r="P15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="13" t="n">
-        <v>0.030068</v>
-      </c>
-      <c r="R15" s="12" t="n">
+      <c r="A15" s="4"/>
+    </row>
+    <row r="16" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="B16" s="17"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="17"/>
+      <c r="I16" s="17"/>
+      <c r="J16" s="17"/>
+      <c r="K16" s="17"/>
+      <c r="L16" s="17"/>
+      <c r="M16" s="17"/>
+      <c r="N16" s="17"/>
+      <c r="O16" s="17"/>
+      <c r="P16" s="17"/>
+      <c r="Q16" s="17"/>
+      <c r="R16" s="17"/>
+      <c r="S16" s="17"/>
+      <c r="T16" s="17"/>
+      <c r="U16" s="17"/>
+      <c r="V16" s="17"/>
+    </row>
+    <row r="17" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="E17" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F17" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="G17" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H17" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="I17" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="J17" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="K17" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="L17" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="M17" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="N17" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="O17" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="P17" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="S15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="U15" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="V15" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="W15" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="X15" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="Y15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="12" t="n">
-        <v>6157.12</v>
-      </c>
-      <c r="AA15" s="12" t="n">
-        <v>431</v>
-      </c>
-      <c r="AB15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH15" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ15" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AK15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM15" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AN15" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AO15" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AP15" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ15" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR15" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS15" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT15" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU15" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV15" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW15" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="AX15" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="AY15" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ15" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA15" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB15" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BC15" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD15" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE15" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BF15" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BG15" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="BH15" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BI15" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="BJ15" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="BK15" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BL15" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BM15" s="16" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="8" t="n">
-        <v>306880</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="G16" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="H16" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="I16" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="J16" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="K16" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="L16" s="12" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="M16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" s="12" t="n">
-        <v>35.99</v>
-      </c>
-      <c r="P16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="U16" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="V16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="X16" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="Y16" s="12" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="Z16" s="12" t="n">
-        <v>35.99</v>
-      </c>
-      <c r="AA16" s="12" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AB16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ16" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AK16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM16" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AN16" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AO16" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AP16" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ16" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR16" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS16" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT16" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU16" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV16" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW16" s="14" t="s">
-        <v>76</v>
-      </c